--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="1518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="1519">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6962614059448</t>
+    <t xml:space="preserve">15.6962604522705</t>
   </si>
   <si>
     <t xml:space="preserve">DAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8255224227905</t>
+    <t xml:space="preserve">15.8255252838135</t>
   </si>
   <si>
     <t xml:space="preserve">15.3269386291504</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6344528198242</t>
+    <t xml:space="preserve">14.6344556808472</t>
   </si>
   <si>
     <t xml:space="preserve">14.3112964630127</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0343027114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.385160446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1358671188354</t>
+    <t xml:space="preserve">14.0343046188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3851613998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1358680725098</t>
   </si>
   <si>
     <t xml:space="preserve">13.9604396820068</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1940927505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8801679611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9724979400635</t>
+    <t xml:space="preserve">13.1940908432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.880166053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9724988937378</t>
   </si>
   <si>
     <t xml:space="preserve">12.3723459243774</t>
@@ -86,109 +86,109 @@
     <t xml:space="preserve">13.221791267395</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0009536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1579132080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4349060058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1948490142822</t>
+    <t xml:space="preserve">16.0009517669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1579170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.434907913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1948471069336</t>
   </si>
   <si>
     <t xml:space="preserve">16.4718437194824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2289543151855</t>
+    <t xml:space="preserve">17.2289524078369</t>
   </si>
   <si>
     <t xml:space="preserve">16.7119007110596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5762300491333</t>
+    <t xml:space="preserve">15.5762338638306</t>
   </si>
   <si>
     <t xml:space="preserve">16.2133140563965</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4100360870361</t>
+    <t xml:space="preserve">15.4100379943848</t>
   </si>
   <si>
     <t xml:space="preserve">15.0407123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0499439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4561996459961</t>
+    <t xml:space="preserve">15.0499420166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4562005996704</t>
   </si>
   <si>
     <t xml:space="preserve">15.2069063186646</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1053419113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0194206237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3425769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.878101348877</t>
+    <t xml:space="preserve">15.1053447723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0194225311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3425788879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8780994415283</t>
   </si>
   <si>
     <t xml:space="preserve">17.0350608825684</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1735591888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0812244415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8227005004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4626083374023</t>
+    <t xml:space="preserve">17.1735553741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.081226348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.822696685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4626045227051</t>
   </si>
   <si>
     <t xml:space="preserve">16.4533767700195</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9427299499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7488327026367</t>
+    <t xml:space="preserve">16.9427318572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.748836517334</t>
   </si>
   <si>
     <t xml:space="preserve">17.293586730957</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4228515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4874801635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5521106719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6472721099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.339750289917</t>
+    <t xml:space="preserve">17.4228496551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4874839782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5521125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6472702026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3397521972656</t>
   </si>
   <si>
     <t xml:space="preserve">17.6352119445801</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9888916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3766822814941</t>
+    <t xml:space="preserve">16.9888935089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3766841888428</t>
   </si>
   <si>
     <t xml:space="preserve">17.5798110961914</t>
@@ -197,28 +197,28 @@
     <t xml:space="preserve">17.1273918151855</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3241138458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.665735244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0535259246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4043807983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6842021942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6380367279053</t>
+    <t xml:space="preserve">16.3241100311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6657333374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0535278320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4043846130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6842002868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6380386352539</t>
   </si>
   <si>
     <t xml:space="preserve">17.238187789917</t>
   </si>
   <si>
-    <t xml:space="preserve">17.68137550354</t>
+    <t xml:space="preserve">17.6813735961914</t>
   </si>
   <si>
     <t xml:space="preserve">17.7552394866943</t>
@@ -227,28 +227,28 @@
     <t xml:space="preserve">17.5244121551514</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9860687255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2353649139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1430282592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9122047424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7183113098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4661922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.530818939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5585174560547</t>
+    <t xml:space="preserve">17.9860649108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2353630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.143030166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.912202835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7183094024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4661903381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5308208465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.558521270752</t>
   </si>
   <si>
     <t xml:space="preserve">18.2168960571289</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">18.4477233886719</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1522655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0137710571289</t>
+    <t xml:space="preserve">18.1522617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0137672424316</t>
   </si>
   <si>
     <t xml:space="preserve">17.5890445709229</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">17.2658882141113</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6075115203857</t>
+    <t xml:space="preserve">17.6075077056885</t>
   </si>
   <si>
     <t xml:space="preserve">17.284351348877</t>
@@ -278,34 +278,34 @@
     <t xml:space="preserve">17.1920223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8873310089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9519634246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6749706268311</t>
+    <t xml:space="preserve">16.8873329162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9519596099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6749687194824</t>
   </si>
   <si>
     <t xml:space="preserve">16.4256782531738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2594795227051</t>
+    <t xml:space="preserve">16.2594814300537</t>
   </si>
   <si>
     <t xml:space="preserve">16.3610401153564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8596343994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.564172744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5272407531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2779426574707</t>
+    <t xml:space="preserve">16.8596305847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5641765594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5272388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.277946472168</t>
   </si>
   <si>
     <t xml:space="preserve">17.47825050354</t>
@@ -314,115 +314,115 @@
     <t xml:space="preserve">16.6288032531738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6103382110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3582191467285</t>
+    <t xml:space="preserve">16.6103363037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3582153320312</t>
   </si>
   <si>
     <t xml:space="preserve">17.1089248657227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1550884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.917857170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9547901153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0591773986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8652830123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1699752807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4377326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0655860900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.086877822876</t>
+    <t xml:space="preserve">17.1550922393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.917854309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9547882080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.059178352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8652839660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1699771881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4377355575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0655841827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0868768692017</t>
   </si>
   <si>
     <t xml:space="preserve">14.5513582229614</t>
   </si>
   <si>
-    <t xml:space="preserve">14.985312461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.62522315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7821836471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5115995407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1330423355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7267866134644</t>
+    <t xml:space="preserve">14.9853115081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6252222061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7821846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5115985870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1330413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7267847061157</t>
   </si>
   <si>
     <t xml:space="preserve">14.0989360809326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3574628829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7544851303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.502366065979</t>
+    <t xml:space="preserve">14.3574619293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7544841766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5023670196533</t>
   </si>
   <si>
     <t xml:space="preserve">15.4192686080933</t>
   </si>
   <si>
-    <t xml:space="preserve">15.603928565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3546342849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4285001754761</t>
+    <t xml:space="preserve">15.6039295196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3546371459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4285020828247</t>
   </si>
   <si>
     <t xml:space="preserve">15.4008016586304</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4839029312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2502479553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7239589691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4931335449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.231782913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9363212585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1856155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2871780395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.176383972168</t>
+    <t xml:space="preserve">15.4838991165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2502460479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7239599227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4931344985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2317810058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9363241195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1856174468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2871761322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1763820648193</t>
   </si>
   <si>
     <t xml:space="preserve">16.093282699585</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">17.2566547393799</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9242630004883</t>
+    <t xml:space="preserve">16.9242610931396</t>
   </si>
   <si>
     <t xml:space="preserve">16.7211360931396</t>
@@ -440,46 +440,46 @@
     <t xml:space="preserve">16.7580661773682</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7275409698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2751197814941</t>
+    <t xml:space="preserve">17.7275447845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2751159667969</t>
   </si>
   <si>
     <t xml:space="preserve">17.1458549499512</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3120536804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4505500793457</t>
+    <t xml:space="preserve">17.3120555877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4505481719971</t>
   </si>
   <si>
     <t xml:space="preserve">16.204080581665</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8901557922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.862455368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9270887374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0563526153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7424230575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7701263427734</t>
+    <t xml:space="preserve">15.8901529312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8624572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270877838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0563488006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7424278259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7701253890991</t>
   </si>
   <si>
     <t xml:space="preserve">15.6685628890991</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5946941375732</t>
+    <t xml:space="preserve">15.5946979522705</t>
   </si>
   <si>
     <t xml:space="preserve">15.7147274017334</t>
@@ -491,58 +491,58 @@
     <t xml:space="preserve">16.8134632110596</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1671466827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6408643722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6500959396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8070573806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4654359817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2623071670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3366212844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4109354019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.652455329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7360620498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8939790725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.624587059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0765190124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4295129776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5224056243896</t>
+    <t xml:space="preserve">16.1671504974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6408634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6500940322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8070592880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4654331207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2623062133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3366203308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4109334945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6524562835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7360610961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8939752578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6245880126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0765199661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4295139312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.522406578064</t>
   </si>
   <si>
     <t xml:space="preserve">15.5131168365479</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1601219177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8661108016968</t>
+    <t xml:space="preserve">15.1601238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8661079406738</t>
   </si>
   <si>
     <t xml:space="preserve">16.3305759429932</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">15.9311361312866</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4945383071899</t>
+    <t xml:space="preserve">15.4945373535156</t>
   </si>
   <si>
     <t xml:space="preserve">15.6060094833374</t>
@@ -560,52 +560,52 @@
     <t xml:space="preserve">15.3180418014526</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8846883773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0518989562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8382387161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5813846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.185188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2595024108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.138744354248</t>
+    <t xml:space="preserve">15.8846893310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0518951416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8382406234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5813865661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1851921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2595043182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1387405395508</t>
   </si>
   <si>
     <t xml:space="preserve">17.2223453521729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.027271270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9529571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4884910583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0922946929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9065093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1666126251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7425479888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.900463104248</t>
+    <t xml:space="preserve">17.0272693634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9529590606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4884929656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0922985076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9065113067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1666107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.742546081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9004669189453</t>
   </si>
   <si>
     <t xml:space="preserve">17.9376220703125</t>
@@ -614,28 +614,28 @@
     <t xml:space="preserve">17.8818855285645</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4299564361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9037075042725</t>
+    <t xml:space="preserve">18.42995262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9037094116211</t>
   </si>
   <si>
     <t xml:space="preserve">18.9501533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5539608001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6282711029053</t>
+    <t xml:space="preserve">19.5539569854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6282749176025</t>
   </si>
   <si>
     <t xml:space="preserve">19.1173648834229</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9129962921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.461067199707</t>
+    <t xml:space="preserve">18.9129981994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4610652923584</t>
   </si>
   <si>
     <t xml:space="preserve">19.3310127258301</t>
@@ -644,154 +644,154 @@
     <t xml:space="preserve">19.1823863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0802040100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8572616577148</t>
+    <t xml:space="preserve">19.080207824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8572597503662</t>
   </si>
   <si>
     <t xml:space="preserve">19.0151786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9408626556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9315738677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7550830841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5785846710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4020843505859</t>
+    <t xml:space="preserve">18.9408645629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9315757751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7550792694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5785827636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4020862579346</t>
   </si>
   <si>
     <t xml:space="preserve">18.1141166687012</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4578247070312</t>
+    <t xml:space="preserve">18.457820892334</t>
   </si>
   <si>
     <t xml:space="preserve">18.5321369171143</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4671096801758</t>
+    <t xml:space="preserve">18.467113494873</t>
   </si>
   <si>
     <t xml:space="preserve">18.3742179870605</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4856910705566</t>
+    <t xml:space="preserve">18.485689163208</t>
   </si>
   <si>
     <t xml:space="preserve">18.2813262939453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3277721405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5135555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6157417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6250247955322</t>
+    <t xml:space="preserve">18.3277702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.513557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6157398223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6250305175781</t>
   </si>
   <si>
     <t xml:space="preserve">18.7272129058838</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0430469512939</t>
+    <t xml:space="preserve">19.0430488586426</t>
   </si>
   <si>
     <t xml:space="preserve">19.4146213531494</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0894908905029</t>
+    <t xml:space="preserve">19.0894927978516</t>
   </si>
   <si>
     <t xml:space="preserve">19.126651763916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3681735992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4517765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9594440460205</t>
+    <t xml:space="preserve">19.3681755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4517784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9594459533691</t>
   </si>
   <si>
     <t xml:space="preserve">19.2474098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5075092315674</t>
+    <t xml:space="preserve">19.5075130462646</t>
   </si>
   <si>
     <t xml:space="preserve">19.0987815856934</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2195434570312</t>
+    <t xml:space="preserve">19.2195453643799</t>
   </si>
   <si>
     <t xml:space="preserve">19.3495941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0337562561035</t>
+    <t xml:space="preserve">19.0337581634521</t>
   </si>
   <si>
     <t xml:space="preserve">19.2288341522217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3867530822754</t>
+    <t xml:space="preserve">19.386754989624</t>
   </si>
   <si>
     <t xml:space="preserve">19.2845687866211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9162425994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0091361999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3807048797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6222286224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8544578552246</t>
+    <t xml:space="preserve">19.9162406921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0091342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3807067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6222267150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8544654846191</t>
   </si>
   <si>
     <t xml:space="preserve">20.9659309387207</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9473514556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.148473739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6129379272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3899974822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2506561279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5757827758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6500911712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6036491394043</t>
+    <t xml:space="preserve">20.9473533630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1484756469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6129398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3899955749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2506542205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5757808685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6500930786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6036510467529</t>
   </si>
   <si>
     <t xml:space="preserve">20.50146484375</t>
@@ -800,31 +800,31 @@
     <t xml:space="preserve">20.529333114624</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6593837738037</t>
+    <t xml:space="preserve">20.6593856811523</t>
   </si>
   <si>
     <t xml:space="preserve">20.4828872680664</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8173027038574</t>
+    <t xml:space="preserve">20.8172988891602</t>
   </si>
   <si>
     <t xml:space="preserve">20.863748550415</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4550228118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7801475524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6440486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.495418548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3653697967529</t>
+    <t xml:space="preserve">20.455020904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7801456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6440505981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4954204559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3653717041016</t>
   </si>
   <si>
     <t xml:space="preserve">21.3189239501953</t>
@@ -833,28 +833,28 @@
     <t xml:space="preserve">21.1331386566162</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1238460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9287738800049</t>
+    <t xml:space="preserve">21.1238498687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9287757873535</t>
   </si>
   <si>
     <t xml:space="preserve">21.2724761962891</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1052703857422</t>
+    <t xml:space="preserve">21.1052722930908</t>
   </si>
   <si>
     <t xml:space="preserve">21.3467922210693</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2260303497314</t>
+    <t xml:space="preserve">21.2260284423828</t>
   </si>
   <si>
     <t xml:space="preserve">20.6408061981201</t>
   </si>
   <si>
-    <t xml:space="preserve">21.170295715332</t>
+    <t xml:space="preserve">21.1702938079834</t>
   </si>
   <si>
     <t xml:space="preserve">20.9566402435303</t>
@@ -863,13 +863,13 @@
     <t xml:space="preserve">21.114559173584</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2539005279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2446098327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3374996185303</t>
+    <t xml:space="preserve">21.2538986206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.244607925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3375053405762</t>
   </si>
   <si>
     <t xml:space="preserve">21.2817668914795</t>
@@ -881,40 +881,40 @@
     <t xml:space="preserve">21.1795864105225</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7336959838867</t>
+    <t xml:space="preserve">20.7336978912354</t>
   </si>
   <si>
     <t xml:space="preserve">20.3156795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">20.399284362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4085731506348</t>
+    <t xml:space="preserve">20.3992824554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4085712432861</t>
   </si>
   <si>
     <t xml:space="preserve">20.3249683380127</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6315155029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2785243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0462894439697</t>
+    <t xml:space="preserve">20.6315174102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2785224914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0462913513184</t>
   </si>
   <si>
     <t xml:space="preserve">20.2134990692139</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7954807281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9069499969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2692337036133</t>
+    <t xml:space="preserve">19.7954788208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9069538116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2692356109619</t>
   </si>
   <si>
     <t xml:space="preserve">20.2971019744873</t>
@@ -923,34 +923,34 @@
     <t xml:space="preserve">20.5479145050049</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4364414215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9533977508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8326396942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.888370513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7211647033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9255275726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.074161529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9998455047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1113166809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6747188568115</t>
+    <t xml:space="preserve">20.4364433288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9533996582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8326358795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8883724212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7211666107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9255294799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0741596221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9998435974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1113185882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6747207641602</t>
   </si>
   <si>
     <t xml:space="preserve">20.6686744689941</t>
@@ -959,31 +959,31 @@
     <t xml:space="preserve">20.2413673400879</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9719772338867</t>
+    <t xml:space="preserve">19.9719753265381</t>
   </si>
   <si>
     <t xml:space="preserve">19.7304553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4178638458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1298942565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4921779632568</t>
+    <t xml:space="preserve">20.4178619384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1298961639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4921760559082</t>
   </si>
   <si>
     <t xml:space="preserve">20.8451709747314</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3435478210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5664920806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8916149139404</t>
+    <t xml:space="preserve">20.3435459136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5664901733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8916168212891</t>
   </si>
   <si>
     <t xml:space="preserve">21.1981620788574</t>
@@ -992,52 +992,52 @@
     <t xml:space="preserve">20.7244091033936</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4736003875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3342571258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3714179992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8790836334229</t>
+    <t xml:space="preserve">20.4735984802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3342590332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3714160919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8790874481201</t>
   </si>
   <si>
     <t xml:space="preserve">19.8419284820557</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7676162719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9812679290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0927352905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5200443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9905548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5353775024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2567024230957</t>
+    <t xml:space="preserve">19.7676105499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9812660217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.092737197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5200481414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9905567169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5353813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2567005157471</t>
   </si>
   <si>
     <t xml:space="preserve">18.7829456329346</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8386859893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6343173980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.996603012085</t>
+    <t xml:space="preserve">18.8386840820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6343212127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9966011047363</t>
   </si>
   <si>
     <t xml:space="preserve">18.6807651519775</t>
@@ -1046,10 +1046,10 @@
     <t xml:space="preserve">18.5600032806396</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6621894836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4392433166504</t>
+    <t xml:space="preserve">18.6621875762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4392471313477</t>
   </si>
   <si>
     <t xml:space="preserve">18.8108158111572</t>
@@ -1058,28 +1058,28 @@
     <t xml:space="preserve">19.1359424591064</t>
   </si>
   <si>
-    <t xml:space="preserve">18.977933883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9499282836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5298519134521</t>
+    <t xml:space="preserve">18.9779281616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9499244689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5298538208008</t>
   </si>
   <si>
     <t xml:space="preserve">18.3058166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9044132232666</t>
+    <t xml:space="preserve">17.904411315918</t>
   </si>
   <si>
     <t xml:space="preserve">17.8484039306641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6430358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6710414886475</t>
+    <t xml:space="preserve">17.6430339813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6710395812988</t>
   </si>
   <si>
     <t xml:space="preserve">17.9417533874512</t>
@@ -1088,13 +1088,13 @@
     <t xml:space="preserve">17.8950786590576</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9697551727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2684783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4645080566406</t>
+    <t xml:space="preserve">17.9697570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2684745788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4645099639893</t>
   </si>
   <si>
     <t xml:space="preserve">18.5858631134033</t>
@@ -1103,31 +1103,31 @@
     <t xml:space="preserve">18.4084987640381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1657905578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4925136566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3618240356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2217998504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6698799133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7725620269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6978816986084</t>
+    <t xml:space="preserve">18.16579246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4925155639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3618259429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2218017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6698780059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7725639343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.697883605957</t>
   </si>
   <si>
     <t xml:space="preserve">18.688549041748</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6138668060303</t>
+    <t xml:space="preserve">18.6138706207275</t>
   </si>
   <si>
     <t xml:space="preserve">18.3524913787842</t>
@@ -1136,49 +1136,49 @@
     <t xml:space="preserve">18.3804950714111</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4458389282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4831790924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4738483428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6605453491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7072200775146</t>
+    <t xml:space="preserve">18.4458408355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4831771850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4738464355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6605434417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7072162628174</t>
   </si>
   <si>
     <t xml:space="preserve">18.5951995849609</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3898296356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5018501281738</t>
+    <t xml:space="preserve">18.3898334503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5018482208252</t>
   </si>
   <si>
     <t xml:space="preserve">18.9032516479492</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1833000183105</t>
+    <t xml:space="preserve">19.1832962036133</t>
   </si>
   <si>
     <t xml:space="preserve">19.4633502960205</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7433967590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5368671417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2836627960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5637111663818</t>
+    <t xml:space="preserve">19.7433948516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5368690490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2836608886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5637073516846</t>
   </si>
   <si>
     <t xml:space="preserve">21.5170345306396</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">21.377010345459</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6103839874268</t>
+    <t xml:space="preserve">21.6103820800781</t>
   </si>
   <si>
     <t xml:space="preserve">21.4703598022461</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">21.7504081726074</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7970848083496</t>
+    <t xml:space="preserve">21.797082901001</t>
   </si>
   <si>
     <t xml:space="preserve">21.0036106109619</t>
@@ -1208,49 +1208,49 @@
     <t xml:space="preserve">21.0502872467041</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6302127838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7702388763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7235641479492</t>
+    <t xml:space="preserve">20.6302165985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7702407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7235679626465</t>
   </si>
   <si>
     <t xml:space="preserve">21.0969638824463</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1903114318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1436367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8635864257812</t>
+    <t xml:space="preserve">21.1903133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1436386108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8635883331299</t>
   </si>
   <si>
     <t xml:space="preserve">20.6768913269043</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7037353515625</t>
+    <t xml:space="preserve">21.7037334442139</t>
   </si>
   <si>
     <t xml:space="preserve">22.2171535491943</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8904323577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0771293640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9837818145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.816915512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.236988067627</t>
+    <t xml:space="preserve">21.8904342651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.077127456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9837799072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8169136047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2369861602783</t>
   </si>
   <si>
     <t xml:space="preserve">20.3034915924072</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">20.9102611541748</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5835380554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.956937789917</t>
+    <t xml:space="preserve">20.5835399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9569358825684</t>
   </si>
   <si>
     <t xml:space="preserve">21.3303375244141</t>
@@ -1274,52 +1274,49 @@
     <t xml:space="preserve">20.3968410491943</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4901924133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1167945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9966011047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0432758331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1366233825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3233242034912</t>
+    <t xml:space="preserve">20.4901943206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1167964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0432739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.136625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3233261108398</t>
   </si>
   <si>
     <t xml:space="preserve">19.7900695800781</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6033706665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3501663208008</t>
+    <t xml:space="preserve">19.6033725738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3501644134521</t>
   </si>
   <si>
     <t xml:space="preserve">20.2568168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">19.976770401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1634674072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0234432220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8834209442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9300975799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4166698455811</t>
+    <t xml:space="preserve">19.9767684936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1634693145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0234451293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8834190368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9300956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4166736602783</t>
   </si>
   <si>
     <t xml:space="preserve">19.556697845459</t>
@@ -1328,16 +1325,16 @@
     <t xml:space="preserve">19.5100231170654</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6500473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6967220306396</t>
+    <t xml:space="preserve">19.6500434875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.696720123291</t>
   </si>
   <si>
     <t xml:space="preserve">19.276647567749</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2299766540527</t>
+    <t xml:space="preserve">19.2299728393555</t>
   </si>
   <si>
     <t xml:space="preserve">19.3699989318848</t>
@@ -1346,397 +1343,400 @@
     <t xml:space="preserve">19.8367443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4236888885498</t>
+    <t xml:space="preserve">21.4236869812012</t>
   </si>
   <si>
     <t xml:space="preserve">20.0701198577881</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7177124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3092985153198</t>
+    <t xml:space="preserve">17.7177143096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3092994689941</t>
   </si>
   <si>
     <t xml:space="preserve">15.7013673782349</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7678737640381</t>
+    <t xml:space="preserve">14.7678728103638</t>
   </si>
   <si>
     <t xml:space="preserve">14.4691553115845</t>
   </si>
   <si>
-    <t xml:space="preserve">14.805212020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4026498794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6266870498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0000858306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333395004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3279705047607</t>
+    <t xml:space="preserve">14.8052129745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4026489257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6266889572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0000839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333375930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3279695510864</t>
   </si>
   <si>
     <t xml:space="preserve">15.4586591720581</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8693962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7947177886963</t>
+    <t xml:space="preserve">15.8693990707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.794716835022</t>
   </si>
   <si>
     <t xml:space="preserve">15.6640272140503</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5893478393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3839807510376</t>
+    <t xml:space="preserve">15.5893497467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.383978843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0105810165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8602876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5784873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4094076156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4469814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9166479110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9354362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6536350250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.14208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4426765441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2735948562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0712471008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.920952796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6015777587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7330856323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3342599868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1651811599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1463937759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2215414047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9585247039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6391525268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6203651428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7894458770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0524587631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2027530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5221271514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7475671768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2172374725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1233024597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.029369354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0669422149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8978614807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1045150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1608743667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1984481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366106033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9687070846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8141059875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.889253616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9080390930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4947299957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.419584274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2692909240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3632221221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.987491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8747720718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8184118270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1377849578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1565704345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2505016326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.62624168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5135173797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2880783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4383716583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4571590423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2317180633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6074523925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7201709747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.475944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3256511688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8559837341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9499197006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9311294555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1189975738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0062789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3444366455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4007968902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5323066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7765350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.945613861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4716396331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2794704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.260684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2418937683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1103897094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5279979705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1334819793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.001974105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9831867218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7389602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6450271606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9643993377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8328952789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0583343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1522674560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2274131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7577457427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2129325866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4990358352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5178232192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4614639282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1796607971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6912088394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8039293289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0857276916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7663555145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9730081558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8415012359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5033407211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6724224090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3718347549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8227138519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5597009658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4657669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6348476409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5741834640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4051027297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3863153457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6681184768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2360229492188</t>
   </si>
   <si>
     <t xml:space="preserve">15.0105819702148</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8602886199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5784883499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4094076156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4469814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9166488647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.935435295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6536340713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.14208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4426765441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2735967636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0712451934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.920952796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6015787124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7330856323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3342599868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1651792526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1463937759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2215414047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9585256576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6391534805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6203651428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7894468307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0524587631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2027540206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5221281051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7475681304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2172374725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1233015060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.029369354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0669441223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8978605270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1045160293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1608743667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984481811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5366106033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9687023162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8141059875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8892517089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9080410003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4947319030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4195861816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2692909240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3632259368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9874906539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8747711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8184108734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1377849578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1565704345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2505054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6262378692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5135192871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2880783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4383735656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4571571350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2317199707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6074542999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7201728820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.475944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3256511688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8559827804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9499187469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9311304092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1189975738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0062770843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3444385528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4007968902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5323066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7765331268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9456157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4716415405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2794666290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.260684967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2418956756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1103916168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.528003692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1334800720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0019721984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9831867218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7389602661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6450233459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9643993377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.832893371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0583324432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1522693634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2274150848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7577476501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2129325866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4990367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.517822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.461462020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1796627044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6912078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8039274215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0857276916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7663555145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9730081558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8415021896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5033416748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.672420501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3718338012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.822714805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5597009658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4657678604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6348476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5741834640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.405101776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3863153457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.668116569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2360219955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5929708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4238910675049</t>
+    <t xml:space="preserve">15.5929727554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4238891601562</t>
   </si>
   <si>
     <t xml:space="preserve">15.3299551010132</t>
@@ -1745,52 +1745,52 @@
     <t xml:space="preserve">15.0481557846069</t>
   </si>
   <si>
-    <t xml:space="preserve">14.879075050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5409145355225</t>
+    <t xml:space="preserve">14.8790760040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5409126281738</t>
   </si>
   <si>
     <t xml:space="preserve">14.7851419448853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6160612106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.296688079834</t>
+    <t xml:space="preserve">14.616060256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2966871261597</t>
   </si>
   <si>
     <t xml:space="preserve">14.2778997421265</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0900325775146</t>
+    <t xml:space="preserve">14.090033531189</t>
   </si>
   <si>
     <t xml:space="preserve">13.9021663665771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7706575393677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4281940460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2591133117676</t>
+    <t xml:space="preserve">13.7706594467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4281930923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2591142654419</t>
   </si>
   <si>
     <t xml:space="preserve">13.8082332611084</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8458061218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.033673286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9397401809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2403259277344</t>
+    <t xml:space="preserve">13.8458051681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0336713790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9397392272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.240327835083</t>
   </si>
   <si>
     <t xml:space="preserve">14.0148868560791</t>
@@ -1802,25 +1802,25 @@
     <t xml:space="preserve">13.9960994720459</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3675289154053</t>
+    <t xml:space="preserve">15.3675308227539</t>
   </si>
   <si>
     <t xml:space="preserve">14.1839666366577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1088218688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4845542907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9917945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2923831939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0758934020996</t>
+    <t xml:space="preserve">14.1088209152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4845533370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9917964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.292384147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0758943557739</t>
   </si>
   <si>
     <t xml:space="preserve">15.0569305419922</t>
@@ -1829,16 +1829,16 @@
     <t xml:space="preserve">14.9052238464355</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8104057312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8862600326538</t>
+    <t xml:space="preserve">14.8104066848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8862590789795</t>
   </si>
   <si>
     <t xml:space="preserve">15.3793067932129</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6827230453491</t>
+    <t xml:space="preserve">15.6827239990234</t>
   </si>
   <si>
     <t xml:space="preserve">16.4602203369141</t>
@@ -1847,58 +1847,58 @@
     <t xml:space="preserve">16.3274765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7016859054565</t>
+    <t xml:space="preserve">15.7016849517822</t>
   </si>
   <si>
     <t xml:space="preserve">15.6637582778931</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5310153961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5499773025513</t>
+    <t xml:space="preserve">15.5310144424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5499801635742</t>
   </si>
   <si>
     <t xml:space="preserve">15.4551610946655</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7585754394531</t>
+    <t xml:space="preserve">15.7585763931274</t>
   </si>
   <si>
     <t xml:space="preserve">15.7965021133423</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1757717132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.720648765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6068687438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6447944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0430240631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9861373901367</t>
+    <t xml:space="preserve">16.1757678985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7206497192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6068668365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6447954177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.043025970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9861345291138</t>
   </si>
   <si>
     <t xml:space="preserve">15.4172344207764</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8344287872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5689420700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4361982345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5879049301147</t>
+    <t xml:space="preserve">15.8344278335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.568941116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4361991882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5879058837891</t>
   </si>
   <si>
     <t xml:space="preserve">15.246563911438</t>
@@ -1907,19 +1907,19 @@
     <t xml:space="preserve">15.1138191223145</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9810771942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2086391448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7535152435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9431505203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5069923400879</t>
+    <t xml:space="preserve">14.9810752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2086372375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7535161972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.943151473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5069913864136</t>
   </si>
   <si>
     <t xml:space="preserve">14.0329074859619</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">14.5828456878662</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3932123184204</t>
+    <t xml:space="preserve">14.3932104110718</t>
   </si>
   <si>
     <t xml:space="preserve">14.4311380386353</t>
@@ -1955,40 +1955,40 @@
     <t xml:space="preserve">14.2794313430786</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0518703460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6915664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1416263580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0088844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3691892623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0847387313843</t>
+    <t xml:space="preserve">14.051869392395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6915655136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1416273117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0088834762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3691883087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.08473777771</t>
   </si>
   <si>
     <t xml:space="preserve">12.8002862930298</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4210195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1744947433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9469347000122</t>
+    <t xml:space="preserve">12.4210186004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1744956970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9469337463379</t>
   </si>
   <si>
     <t xml:space="preserve">11.4728498458862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0366926193237</t>
+    <t xml:space="preserve">11.0366916656494</t>
   </si>
   <si>
     <t xml:space="preserve">10.1264495849609</t>
@@ -2000,40 +2000,40 @@
     <t xml:space="preserve">9.59547424316406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91279220581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41532325744629</t>
+    <t xml:space="preserve">8.91279315948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41532230377197</t>
   </si>
   <si>
     <t xml:space="preserve">8.09736633300781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55248928070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10242652893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1643762588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7522411346436</t>
+    <t xml:space="preserve">8.55248832702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10242557525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1643753051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7522420883179</t>
   </si>
   <si>
     <t xml:space="preserve">11.9279708862305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8951044082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6055936813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9608383178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9229125976562</t>
+    <t xml:space="preserve">12.8951034545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6055927276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9608392715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9229116439819</t>
   </si>
   <si>
     <t xml:space="preserve">10.6384611129761</t>
@@ -2042,37 +2042,37 @@
     <t xml:space="preserve">10.0695581436157</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3350458145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.61949634552</t>
+    <t xml:space="preserve">10.3350467681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6194972991943</t>
   </si>
   <si>
     <t xml:space="preserve">10.7332773208618</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1125469207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9039487838745</t>
+    <t xml:space="preserve">11.1125450134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9039478302002</t>
   </si>
   <si>
     <t xml:space="preserve">10.5815696716309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2023019790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87992477416992</t>
+    <t xml:space="preserve">10.2023029327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87992572784424</t>
   </si>
   <si>
     <t xml:space="preserve">10.2212657928467</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5057172775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4298639297485</t>
+    <t xml:space="preserve">10.5057182312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4298629760742</t>
   </si>
   <si>
     <t xml:space="preserve">10.771203994751</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">10.7143144607544</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6953496932983</t>
+    <t xml:space="preserve">10.6953506469727</t>
   </si>
   <si>
     <t xml:space="preserve">10.8091306686401</t>
@@ -2099,22 +2099,22 @@
     <t xml:space="preserve">10.9418754577637</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4918127059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.567666053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0556554794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4159603118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5107765197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7952280044556</t>
+    <t xml:space="preserve">11.491813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5676670074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0556545257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4159593582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5107774734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7952270507812</t>
   </si>
   <si>
     <t xml:space="preserve">12.0038242340088</t>
@@ -2123,61 +2123,61 @@
     <t xml:space="preserve">12.2882747650146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2124223709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0986413955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8521165847778</t>
+    <t xml:space="preserve">12.2124214172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0986423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8521175384521</t>
   </si>
   <si>
     <t xml:space="preserve">11.2263259887695</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177278518677</t>
+    <t xml:space="preserve">11.017728805542</t>
   </si>
   <si>
     <t xml:space="preserve">11.1883993148804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0935821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8849840164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7901678085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6763868331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4109001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4488277435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6574239730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2073621749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3401050567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2832145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0746192932129</t>
+    <t xml:space="preserve">11.0935831069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8849849700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7901668548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6763877868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4108991622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.448826789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6574230194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2073612213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.340106010437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2832155227661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0746183395386</t>
   </si>
   <si>
     <t xml:space="preserve">10.9798021316528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6005334854126</t>
+    <t xml:space="preserve">10.6005344390869</t>
   </si>
   <si>
     <t xml:space="preserve">10.3729734420776</t>
@@ -2186,106 +2186,106 @@
     <t xml:space="preserve">10.4677906036377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6435194015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4349222183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6814479827881</t>
+    <t xml:space="preserve">11.6435203552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4349241256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6814470291138</t>
   </si>
   <si>
     <t xml:space="preserve">11.5297393798828</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6245565414429</t>
+    <t xml:space="preserve">11.6245574951172</t>
   </si>
   <si>
     <t xml:space="preserve">11.5487041473389</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6624841690063</t>
+    <t xml:space="preserve">11.662483215332</t>
   </si>
   <si>
     <t xml:space="preserve">11.7383375167847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2313852310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.136568069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1176042556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9658975601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9848613739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.814190864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7573003768921</t>
+    <t xml:space="preserve">12.2313861846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1365690231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1176052093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9658985137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9848623275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8141899108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7573013305664</t>
   </si>
   <si>
     <t xml:space="preserve">11.245288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6485805511475</t>
+    <t xml:space="preserve">12.6485795974731</t>
   </si>
   <si>
     <t xml:space="preserve">13.653639793396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3881521224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8622360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5967502593994</t>
+    <t xml:space="preserve">13.3881511688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8622369766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5967493057251</t>
   </si>
   <si>
     <t xml:space="preserve">13.2364444732666</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4260778427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4640045166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1037015914917</t>
+    <t xml:space="preserve">13.4260787963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4640054702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1037006378174</t>
   </si>
   <si>
     <t xml:space="preserve">13.3312616348267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1277227401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.407114982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1226654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4829683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1795539855957</t>
+    <t xml:space="preserve">14.1277236938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7294931411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4071159362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1226644515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4829692840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.17955493927</t>
   </si>
   <si>
     <t xml:space="preserve">12.0227880477905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.060715675354</t>
+    <t xml:space="preserve">12.0607147216797</t>
   </si>
   <si>
     <t xml:space="preserve">12.3262023925781</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">12.4399824142456</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8571767807007</t>
+    <t xml:space="preserve">12.8571786880493</t>
   </si>
   <si>
     <t xml:space="preserve">12.8192510604858</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">13.3122987747192</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4450416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5588226318359</t>
+    <t xml:space="preserve">13.4450426101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5588235855103</t>
   </si>
   <si>
     <t xml:space="preserve">13.6179914474487</t>
@@ -2321,19 +2321,19 @@
     <t xml:space="preserve">13.4073057174683</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4456119537354</t>
+    <t xml:space="preserve">13.4456129074097</t>
   </si>
   <si>
     <t xml:space="preserve">13.3115377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5030727386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8478307723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8861379623413</t>
+    <t xml:space="preserve">13.5030717849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8478298187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.886137008667</t>
   </si>
   <si>
     <t xml:space="preserve">13.7520637512207</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">14.1734371185303</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1542825698853</t>
+    <t xml:space="preserve">14.1542835235596</t>
   </si>
   <si>
     <t xml:space="preserve">14.2117433547974</t>
@@ -2351,31 +2351,31 @@
     <t xml:space="preserve">13.9819040298462</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6946048736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4647655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7712173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.598837852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5413780212402</t>
+    <t xml:space="preserve">13.6946058273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4647645950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7712182998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5988368988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5413789749146</t>
   </si>
   <si>
     <t xml:space="preserve">13.7903709411621</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7137575149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8669834136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1351308822632</t>
+    <t xml:space="preserve">13.7137565612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8669843673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1351299285889</t>
   </si>
   <si>
     <t xml:space="preserve">14.3458156585693</t>
@@ -2384,10 +2384,10 @@
     <t xml:space="preserve">14.7097291946411</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6331148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9970273971558</t>
+    <t xml:space="preserve">14.6331157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9970283508301</t>
   </si>
   <si>
     <t xml:space="preserve">15.0353345870972</t>
@@ -2396,43 +2396,43 @@
     <t xml:space="preserve">16.4909839630127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3377590179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.184534072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8206176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9546937942505</t>
+    <t xml:space="preserve">16.3377571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1845321655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8206205368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9546928405762</t>
   </si>
   <si>
     <t xml:space="preserve">15.8014659881592</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6099338531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3226337432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7440071105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3417882919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.437554359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7248544692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8589267730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2611465454102</t>
+    <t xml:space="preserve">15.6099328994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3226346969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.74400806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3417873382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4375553131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7248525619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8589248657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2611446380615</t>
   </si>
   <si>
     <t xml:space="preserve">16.6059036254883</t>
@@ -2447,37 +2447,37 @@
     <t xml:space="preserve">16.6442108154297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7208251953125</t>
+    <t xml:space="preserve">16.7208232879639</t>
   </si>
   <si>
     <t xml:space="preserve">16.7016716003418</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1613502502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1421985626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1996555328369</t>
+    <t xml:space="preserve">17.1613521575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1421966552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1996574401855</t>
   </si>
   <si>
     <t xml:space="preserve">16.9889698028564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4526786804199</t>
+    <t xml:space="preserve">16.4526805877686</t>
   </si>
   <si>
     <t xml:space="preserve">16.4335250854492</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9123592376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6633644104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9506645202637</t>
+    <t xml:space="preserve">16.9123554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.663366317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9506664276123</t>
   </si>
   <si>
     <t xml:space="preserve">16.9315128326416</t>
@@ -2501,43 +2501,43 @@
     <t xml:space="preserve">19.9194240570068</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3024921417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7757740020752</t>
+    <t xml:space="preserve">20.302490234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7757759094238</t>
   </si>
   <si>
     <t xml:space="preserve">20.7334384918213</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4940223693848</t>
+    <t xml:space="preserve">20.4940242767334</t>
   </si>
   <si>
     <t xml:space="preserve">20.1109580993652</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9673099517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8715419769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0151920318604</t>
+    <t xml:space="preserve">19.9673080444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8715400695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0151901245117</t>
   </si>
   <si>
     <t xml:space="preserve">20.3982563018799</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5419063568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6376705169678</t>
+    <t xml:space="preserve">20.5419082641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.637674331665</t>
   </si>
   <si>
     <t xml:space="preserve">20.9728546142578</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8770866394043</t>
+    <t xml:space="preserve">20.8770885467529</t>
   </si>
   <si>
     <t xml:space="preserve">20.3503742218018</t>
@@ -2546,28 +2546,28 @@
     <t xml:space="preserve">20.0630760192871</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9249706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7278938293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4884757995605</t>
+    <t xml:space="preserve">20.9249725341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7278919219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4884777069092</t>
   </si>
   <si>
     <t xml:space="preserve">19.3448276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5363578796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.823657989502</t>
+    <t xml:space="preserve">19.5363597869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8236598968506</t>
   </si>
   <si>
     <t xml:space="preserve">19.1532936096191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2546081542969</t>
+    <t xml:space="preserve">20.2546062469482</t>
   </si>
   <si>
     <t xml:space="preserve">20.4461402893066</t>
@@ -2576,16 +2576,16 @@
     <t xml:space="preserve">20.2067241668701</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1165027618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6911010742188</t>
+    <t xml:space="preserve">21.1165046691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6911029815674</t>
   </si>
   <si>
     <t xml:space="preserve">21.3080368041992</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7868709564209</t>
+    <t xml:space="preserve">21.7868690490723</t>
   </si>
   <si>
     <t xml:space="preserve">21.7389869689941</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">21.834753036499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5474529266357</t>
+    <t xml:space="preserve">21.5474548339844</t>
   </si>
   <si>
     <t xml:space="preserve">21.8826370239258</t>
@@ -2606,13 +2606,13 @@
     <t xml:space="preserve">21.2122707366943</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3559226989746</t>
+    <t xml:space="preserve">21.355920791626</t>
   </si>
   <si>
     <t xml:space="preserve">21.4516868591309</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3135852813721</t>
+    <t xml:space="preserve">22.3135833740234</t>
   </si>
   <si>
     <t xml:space="preserve">22.7924175262451</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">23.3191337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6487674713135</t>
+    <t xml:space="preserve">22.6487693786621</t>
   </si>
   <si>
     <t xml:space="preserve">22.4093532562256</t>
@@ -2633,70 +2633,70 @@
     <t xml:space="preserve">21.6432209014893</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4038047790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8292045593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.781322479248</t>
+    <t xml:space="preserve">21.4038066864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8292064666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7813243865967</t>
   </si>
   <si>
     <t xml:space="preserve">21.9305191040039</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5162143707275</t>
+    <t xml:space="preserve">24.5162162780762</t>
   </si>
   <si>
     <t xml:space="preserve">23.9416160583496</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4627819061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4148998260498</t>
+    <t xml:space="preserve">23.4627857208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4149036407471</t>
   </si>
   <si>
     <t xml:space="preserve">23.1754856109619</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2712516784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5106678009033</t>
+    <t xml:space="preserve">23.2712497711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5106658935547</t>
   </si>
   <si>
     <t xml:space="preserve">23.22336769104</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7500820159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6064319610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0797157287598</t>
+    <t xml:space="preserve">23.7500839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6064338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0797176361084</t>
   </si>
   <si>
     <t xml:space="preserve">23.797966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7021999359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6543159484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.031831741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5585498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8403015136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6008853912354</t>
+    <t xml:space="preserve">23.7022018432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.654317855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0318336486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5585517883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8403034210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.600887298584</t>
   </si>
   <si>
     <t xml:space="preserve">22.2657012939453</t>
@@ -2705,19 +2705,19 @@
     <t xml:space="preserve">21.5953369140625</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2178192138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1699371337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2289161682129</t>
+    <t xml:space="preserve">22.2178173065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1699352264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2289142608643</t>
   </si>
   <si>
     <t xml:space="preserve">23.8937339782715</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4683303833008</t>
+    <t xml:space="preserve">24.4683322906494</t>
   </si>
   <si>
     <t xml:space="preserve">24.0373821258545</t>
@@ -2726,37 +2726,37 @@
     <t xml:space="preserve">23.8458499908447</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4738788604736</t>
+    <t xml:space="preserve">25.4738807678223</t>
   </si>
   <si>
     <t xml:space="preserve">25.7611789703369</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1442451477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8569450378418</t>
+    <t xml:space="preserve">26.1442432403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8569431304932</t>
   </si>
   <si>
     <t xml:space="preserve">25.8090629577637</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9527130126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.665412902832</t>
+    <t xml:space="preserve">25.9527111053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6654109954834</t>
   </si>
   <si>
     <t xml:space="preserve">26.4794273376465</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5751934051514</t>
+    <t xml:space="preserve">26.5751953125</t>
   </si>
   <si>
     <t xml:space="preserve">27.4849758148193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3892097473145</t>
+    <t xml:space="preserve">27.3892116546631</t>
   </si>
   <si>
     <t xml:space="preserve">27.3413257598877</t>
@@ -2771,16 +2771,16 @@
     <t xml:space="preserve">27.9638080596924</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2989902496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7722759246826</t>
+    <t xml:space="preserve">28.2989883422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.772274017334</t>
   </si>
   <si>
     <t xml:space="preserve">27.628625869751</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7243938446045</t>
+    <t xml:space="preserve">27.7243919372559</t>
   </si>
   <si>
     <t xml:space="preserve">27.5328598022461</t>
@@ -2792,19 +2792,19 @@
     <t xml:space="preserve">26.9582595825195</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1497936248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.054027557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7188453674316</t>
+    <t xml:space="preserve">27.1497917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0540256500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.718843460083</t>
   </si>
   <si>
     <t xml:space="preserve">26.9287757873535</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2543506622314</t>
+    <t xml:space="preserve">26.2543525695801</t>
   </si>
   <si>
     <t xml:space="preserve">25.8207931518555</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">24.760986328125</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6646385192871</t>
+    <t xml:space="preserve">24.6646404266357</t>
   </si>
   <si>
     <t xml:space="preserve">25.0981960296631</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">26.4470443725586</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9171390533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8689651489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4835834503174</t>
+    <t xml:space="preserve">25.9171409606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8689670562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4835815429688</t>
   </si>
   <si>
     <t xml:space="preserve">25.7244491577148</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">26.0616588592529</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9653129577637</t>
+    <t xml:space="preserve">25.9653148651123</t>
   </si>
   <si>
     <t xml:space="preserve">26.1580047607422</t>
@@ -2885,19 +2885,19 @@
     <t xml:space="preserve">25.0500240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4719467163086</t>
+    <t xml:space="preserve">24.47194480896</t>
   </si>
   <si>
     <t xml:space="preserve">22.9785804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7858848571777</t>
+    <t xml:space="preserve">22.7858867645264</t>
   </si>
   <si>
     <t xml:space="preserve">23.6530017852783</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0267505645752</t>
+    <t xml:space="preserve">23.0267524719238</t>
   </si>
   <si>
     <t xml:space="preserve">22.9304046630859</t>
@@ -2906,16 +2906,16 @@
     <t xml:space="preserve">23.2194442749023</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4121379852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4486751556396</t>
+    <t xml:space="preserve">23.4121360778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.448673248291</t>
   </si>
   <si>
     <t xml:space="preserve">21.9669437408447</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8224258422852</t>
+    <t xml:space="preserve">21.8224239349365</t>
   </si>
   <si>
     <t xml:space="preserve">21.5815582275391</t>
@@ -2924,25 +2924,25 @@
     <t xml:space="preserve">22.6413669586182</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8340606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4968490600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1114654541016</t>
+    <t xml:space="preserve">22.8340625762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.49684715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1114635467529</t>
   </si>
   <si>
     <t xml:space="preserve">23.1712703704834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1596374511719</t>
+    <t xml:space="preserve">22.1596355438232</t>
   </si>
   <si>
     <t xml:space="preserve">22.063289642334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3888683319092</t>
+    <t xml:space="preserve">21.3888664245605</t>
   </si>
   <si>
     <t xml:space="preserve">21.1480007171631</t>
@@ -2957,19 +2957,19 @@
     <t xml:space="preserve">20.1845397949219</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9436721801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9609413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1536312103271</t>
+    <t xml:space="preserve">19.9436740875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9609432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1536331176758</t>
   </si>
   <si>
     <t xml:space="preserve">18.1323623657227</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8991317749023</t>
+    <t xml:space="preserve">16.899133682251</t>
   </si>
   <si>
     <t xml:space="preserve">16.9569396972656</t>
@@ -2996,10 +2996,10 @@
     <t xml:space="preserve">18.6719017028809</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2672481536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3250560760498</t>
+    <t xml:space="preserve">18.2672462463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3250579833984</t>
   </si>
   <si>
     <t xml:space="preserve">18.6911716461182</t>
@@ -3026,10 +3026,10 @@
     <t xml:space="preserve">19.2114410400391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6333637237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7662487030029</t>
+    <t xml:space="preserve">18.6333618164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7662506103516</t>
   </si>
   <si>
     <t xml:space="preserve">18.6526336669922</t>
@@ -3041,13 +3041,13 @@
     <t xml:space="preserve">18.7297115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4137706756592</t>
+    <t xml:space="preserve">19.4137687683105</t>
   </si>
   <si>
     <t xml:space="preserve">19.7509803771973</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1343650817871</t>
+    <t xml:space="preserve">19.1343631744385</t>
   </si>
   <si>
     <t xml:space="preserve">18.7489795684814</t>
@@ -3056,13 +3056,13 @@
     <t xml:space="preserve">18.9224014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3655967712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.269250869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5350170135498</t>
+    <t xml:space="preserve">19.3655948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2692489624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5350189208984</t>
   </si>
   <si>
     <t xml:space="preserve">17.7277088165283</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">21.0034809112549</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7144412994385</t>
+    <t xml:space="preserve">20.7144432067871</t>
   </si>
   <si>
     <t xml:space="preserve">21.0516548156738</t>
@@ -3095,10 +3095,10 @@
     <t xml:space="preserve">21.8705978393555</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4005031585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1230983734131</t>
+    <t xml:space="preserve">22.4005012512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1231002807617</t>
   </si>
   <si>
     <t xml:space="preserve">23.3157920837402</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">22.5450229644775</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2078094482422</t>
+    <t xml:space="preserve">22.2078075408936</t>
   </si>
   <si>
     <t xml:space="preserve">20.4254035949707</t>
@@ -3116,19 +3116,19 @@
     <t xml:space="preserve">20.8107891082764</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8954982757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2327098846436</t>
+    <t xml:space="preserve">19.8955001831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2327117919922</t>
   </si>
   <si>
     <t xml:space="preserve">20.4735774993896</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8473243713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.249979019165</t>
+    <t xml:space="preserve">19.8473262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2499809265137</t>
   </si>
   <si>
     <t xml:space="preserve">18.7875175476074</t>
@@ -3137,16 +3137,16 @@
     <t xml:space="preserve">18.5948257446289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5735549926758</t>
+    <t xml:space="preserve">17.5735530853271</t>
   </si>
   <si>
     <t xml:space="preserve">18.8067874908447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4984798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2287082672119</t>
+    <t xml:space="preserve">18.498477935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2287101745605</t>
   </si>
   <si>
     <t xml:space="preserve">18.0745544433594</t>
@@ -3164,10 +3164,10 @@
     <t xml:space="preserve">18.5370178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4406719207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2865180969238</t>
+    <t xml:space="preserve">18.4406700134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2865161895752</t>
   </si>
   <si>
     <t xml:space="preserve">17.9782104492188</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">18.5755558013916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3174228668213</t>
+    <t xml:space="preserve">19.3174209594727</t>
   </si>
   <si>
     <t xml:space="preserve">18.8453235626221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9802131652832</t>
+    <t xml:space="preserve">18.9802112579346</t>
   </si>
   <si>
     <t xml:space="preserve">19.4619426727295</t>
@@ -3191,16 +3191,16 @@
     <t xml:space="preserve">18.1709022521973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.708438873291</t>
+    <t xml:space="preserve">17.7084369659424</t>
   </si>
   <si>
     <t xml:space="preserve">17.9204006195068</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6313610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2094402313232</t>
+    <t xml:space="preserve">17.6313629150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2094383239746</t>
   </si>
   <si>
     <t xml:space="preserve">18.2479801177979</t>
@@ -3221,13 +3221,13 @@
     <t xml:space="preserve">16.4559383392334</t>
   </si>
   <si>
-    <t xml:space="preserve">16.205436706543</t>
+    <t xml:space="preserve">16.2054386138916</t>
   </si>
   <si>
     <t xml:space="preserve">16.0512847900391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2247066497803</t>
+    <t xml:space="preserve">16.2247085571289</t>
   </si>
   <si>
     <t xml:space="preserve">15.4153995513916</t>
@@ -3236,22 +3236,22 @@
     <t xml:space="preserve">15.5502834320068</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3575897216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7257099151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1283588409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7642459869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8798637390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1110954284668</t>
+    <t xml:space="preserve">15.357590675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7257080078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7642478942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.879861831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1110935211182</t>
   </si>
   <si>
     <t xml:space="preserve">17.4386692047119</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">17.1689014434814</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1303615570068</t>
+    <t xml:space="preserve">17.1303634643555</t>
   </si>
   <si>
     <t xml:space="preserve">17.9589405059814</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">20.1363639831543</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7028064727783</t>
+    <t xml:space="preserve">19.702808380127</t>
   </si>
   <si>
     <t xml:space="preserve">20.5699234008789</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">20.3290576934814</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7626152038574</t>
+    <t xml:space="preserve">20.7626171112061</t>
   </si>
   <si>
     <t xml:space="preserve">20.8589611053467</t>
@@ -4566,6 +4566,9 @@
   </si>
   <si>
     <t xml:space="preserve">50.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2000007629395</t>
   </si>
 </sst>
 </file>
@@ -20860,7 +20863,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G614" t="s">
-        <v>422</v>
+        <v>341</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -20938,7 +20941,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G617" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -20964,7 +20967,7 @@
         <v>20.5</v>
       </c>
       <c r="G618" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -20990,7 +20993,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G619" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21016,7 +21019,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G620" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21042,7 +21045,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G621" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21068,7 +21071,7 @@
         <v>21</v>
       </c>
       <c r="G622" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21146,7 +21149,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G625" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21198,7 +21201,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G627" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21250,7 +21253,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G629" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21276,7 +21279,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G630" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21328,7 +21331,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G632" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21354,7 +21357,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G633" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21380,7 +21383,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G634" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21432,7 +21435,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G636" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -21458,7 +21461,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G637" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21484,7 +21487,7 @@
         <v>21</v>
       </c>
       <c r="G638" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -21510,7 +21513,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G639" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21562,7 +21565,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G641" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21588,7 +21591,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G642" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -21640,7 +21643,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G644" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -21666,7 +21669,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G645" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -21848,7 +21851,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G652" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -21874,7 +21877,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G653" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -21900,7 +21903,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G654" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -21926,7 +21929,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G655" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -21952,7 +21955,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G656" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -22004,7 +22007,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G658" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22030,7 +22033,7 @@
         <v>21</v>
       </c>
       <c r="G659" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22082,7 +22085,7 @@
         <v>21</v>
       </c>
       <c r="G661" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22108,7 +22111,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G662" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22134,7 +22137,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G663" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22186,7 +22189,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22264,7 +22267,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G668" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22290,7 +22293,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G669" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22316,7 +22319,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G670" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22368,7 +22371,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G672" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22394,7 +22397,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22420,7 +22423,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -22446,7 +22449,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -22472,7 +22475,7 @@
         <v>20.75</v>
       </c>
       <c r="G676" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -22498,7 +22501,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G677" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -22524,7 +22527,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G678" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -22550,7 +22553,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G679" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -22576,7 +22579,7 @@
         <v>21.25</v>
       </c>
       <c r="G680" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -22602,7 +22605,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G681" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -22628,7 +22631,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G682" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -22654,7 +22657,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G683" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -23122,7 +23125,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G701" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23278,7 +23281,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G707" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -23304,7 +23307,7 @@
         <v>21.5</v>
       </c>
       <c r="G708" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -23330,7 +23333,7 @@
         <v>21.5</v>
       </c>
       <c r="G709" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -23356,7 +23359,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G710" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -23382,7 +23385,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G711" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -23408,7 +23411,7 @@
         <v>21</v>
       </c>
       <c r="G712" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -23434,7 +23437,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G713" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -23460,7 +23463,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G714" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -23486,7 +23489,7 @@
         <v>21</v>
       </c>
       <c r="G715" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -23512,7 +23515,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G716" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -23538,7 +23541,7 @@
         <v>20.75</v>
       </c>
       <c r="G717" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -23564,7 +23567,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G718" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -23590,7 +23593,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G719" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -23616,7 +23619,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G720" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -23642,7 +23645,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G721" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -23668,7 +23671,7 @@
         <v>15.5</v>
       </c>
       <c r="G722" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -23694,7 +23697,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G723" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -23720,7 +23723,7 @@
         <v>16.5</v>
       </c>
       <c r="G724" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -23746,7 +23749,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G725" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -23772,7 +23775,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G726" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -23798,7 +23801,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G727" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -23824,7 +23827,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G728" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -23850,7 +23853,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G729" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -23876,7 +23879,7 @@
         <v>17</v>
       </c>
       <c r="G730" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -23902,7 +23905,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G731" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -23928,7 +23931,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G732" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -23954,7 +23957,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G733" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -23980,7 +23983,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G734" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -24006,7 +24009,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G735" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -24032,7 +24035,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G736" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -24058,7 +24061,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G737" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -24084,7 +24087,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G738" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -24110,7 +24113,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G739" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24136,7 +24139,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G740" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24162,7 +24165,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G741" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24188,7 +24191,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G742" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24214,7 +24217,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G743" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24240,7 +24243,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G744" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -24266,7 +24269,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G745" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -24292,7 +24295,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G746" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -24318,7 +24321,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G747" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -24344,7 +24347,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G748" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -24370,7 +24373,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G749" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -24396,7 +24399,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G750" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -24422,7 +24425,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G751" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -24448,7 +24451,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G752" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -24474,7 +24477,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G753" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -24500,7 +24503,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G754" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -24526,7 +24529,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G755" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -24552,7 +24555,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G756" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -24578,7 +24581,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G757" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -24604,7 +24607,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G758" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -24630,7 +24633,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G759" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -24656,7 +24659,7 @@
         <v>14.5</v>
       </c>
       <c r="G760" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -24682,7 +24685,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G761" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -24708,7 +24711,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G762" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -24734,7 +24737,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G763" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -24760,7 +24763,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G764" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -24786,7 +24789,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G765" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -24812,7 +24815,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G766" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -24838,7 +24841,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G767" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -24864,7 +24867,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G768" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -24890,7 +24893,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G769" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -24916,7 +24919,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G770" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -24942,7 +24945,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G771" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -24968,7 +24971,7 @@
         <v>16</v>
       </c>
       <c r="G772" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -24994,7 +24997,7 @@
         <v>16</v>
       </c>
       <c r="G773" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25020,7 +25023,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G774" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -25046,7 +25049,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G775" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25072,7 +25075,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G776" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -25098,7 +25101,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G777" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25124,7 +25127,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G778" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25150,7 +25153,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G779" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25176,7 +25179,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G780" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25202,7 +25205,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G781" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25228,7 +25231,7 @@
         <v>17</v>
       </c>
       <c r="G782" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -25254,7 +25257,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G783" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -25280,7 +25283,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G784" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25306,7 +25309,7 @@
         <v>18</v>
       </c>
       <c r="G785" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -25332,7 +25335,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G786" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25358,7 +25361,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G787" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -25384,7 +25387,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G788" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -25410,7 +25413,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G789" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25436,7 +25439,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G790" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -25462,7 +25465,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25488,7 +25491,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G792" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -25514,7 +25517,7 @@
         <v>17</v>
       </c>
       <c r="G793" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -25540,7 +25543,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G794" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -25566,7 +25569,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G795" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -25592,7 +25595,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G796" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -25618,7 +25621,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -25644,7 +25647,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G798" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -25670,7 +25673,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G799" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -25696,7 +25699,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -25722,7 +25725,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G801" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -25748,7 +25751,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G802" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -25774,7 +25777,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G803" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -25800,7 +25803,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G804" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -25826,7 +25829,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -25852,7 +25855,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G806" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -25878,7 +25881,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G807" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -25904,7 +25907,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G808" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -25930,7 +25933,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G809" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -25956,7 +25959,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G810" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -25982,7 +25985,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G811" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26008,7 +26011,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G812" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26034,7 +26037,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G813" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26060,7 +26063,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G814" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26086,7 +26089,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G815" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -26112,7 +26115,7 @@
         <v>17</v>
       </c>
       <c r="G816" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -26138,7 +26141,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G817" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -26164,7 +26167,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G818" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26190,7 +26193,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G819" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26216,7 +26219,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G820" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -26242,7 +26245,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G821" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -26268,7 +26271,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G822" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -26294,7 +26297,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G823" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26320,7 +26323,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26346,7 +26349,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G825" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -26372,7 +26375,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G826" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26398,7 +26401,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G827" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -26424,7 +26427,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G828" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -26450,7 +26453,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G829" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -26476,7 +26479,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G830" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -26502,7 +26505,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G831" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -26528,7 +26531,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G832" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -26554,7 +26557,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G833" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -26580,7 +26583,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G834" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -26606,7 +26609,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G835" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -26632,7 +26635,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G836" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -26658,7 +26661,7 @@
         <v>18</v>
       </c>
       <c r="G837" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -26684,7 +26687,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G838" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -26710,7 +26713,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G839" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -26736,7 +26739,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G840" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -26762,7 +26765,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G841" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -26788,7 +26791,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G842" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -26814,7 +26817,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G843" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -26840,7 +26843,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G844" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -26866,7 +26869,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G845" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -26892,7 +26895,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G846" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -26918,7 +26921,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G847" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -26944,7 +26947,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G848" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -26970,7 +26973,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G849" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -26996,7 +26999,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G850" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27022,7 +27025,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G851" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27048,7 +27051,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G852" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -27074,7 +27077,7 @@
         <v>17</v>
       </c>
       <c r="G853" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27100,7 +27103,7 @@
         <v>16.5</v>
       </c>
       <c r="G854" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -27126,7 +27129,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G855" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -27152,7 +27155,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G856" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -27178,7 +27181,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G857" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -27204,7 +27207,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G858" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -27230,7 +27233,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G859" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -27256,7 +27259,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G860" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -27282,7 +27285,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G861" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -27308,7 +27311,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G862" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -27334,7 +27337,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G863" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -27360,7 +27363,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G864" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -27386,7 +27389,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G865" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -27412,7 +27415,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G866" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -27438,7 +27441,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G867" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -27464,7 +27467,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G868" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -27490,7 +27493,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G869" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -27516,7 +27519,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G870" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -27542,7 +27545,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G871" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -27568,7 +27571,7 @@
         <v>15.5</v>
       </c>
       <c r="G872" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -27594,7 +27597,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G873" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -27620,7 +27623,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G874" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -27646,7 +27649,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G875" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -27672,7 +27675,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G876" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -27698,7 +27701,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G877" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -27724,7 +27727,7 @@
         <v>16.5</v>
       </c>
       <c r="G878" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -27750,7 +27753,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G879" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -27776,7 +27779,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G880" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -27802,7 +27805,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G881" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -27828,7 +27831,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G882" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -27854,7 +27857,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G883" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -27880,7 +27883,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G884" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -27906,7 +27909,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G885" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -27932,7 +27935,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G886" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -27958,7 +27961,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G887" t="s">
-        <v>463</v>
+        <v>572</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -27984,7 +27987,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G888" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -28036,7 +28039,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G890" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -28062,7 +28065,7 @@
         <v>16.5</v>
       </c>
       <c r="G891" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -28088,7 +28091,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G892" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -28192,7 +28195,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G896" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -28218,7 +28221,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G897" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -28244,7 +28247,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G898" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -28270,7 +28273,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G899" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -28348,7 +28351,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G902" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -28400,7 +28403,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G904" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -28426,7 +28429,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -28452,7 +28455,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G906" t="s">
-        <v>463</v>
+        <v>572</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -28478,7 +28481,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G907" t="s">
-        <v>463</v>
+        <v>572</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -28504,7 +28507,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -28556,7 +28559,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G910" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -28582,7 +28585,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G911" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -28634,7 +28637,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G913" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -28660,7 +28663,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G914" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -28712,7 +28715,7 @@
         <v>15.5</v>
       </c>
       <c r="G916" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -28738,7 +28741,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G917" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -28946,7 +28949,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G925" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -28998,7 +29001,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G927" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -29050,7 +29053,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G929" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -29232,7 +29235,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G936" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -29258,7 +29261,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G937" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -29284,7 +29287,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G938" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -29310,7 +29313,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G939" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -29336,7 +29339,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G940" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -29362,7 +29365,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G941" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -29388,7 +29391,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G942" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -29414,7 +29417,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G943" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -29440,7 +29443,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G944" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -29492,7 +29495,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G946" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -29518,7 +29521,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G947" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -29544,7 +29547,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G948" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -29570,7 +29573,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G949" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -29674,7 +29677,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G953" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -29700,7 +29703,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G954" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -29804,7 +29807,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G958" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -29934,7 +29937,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G963" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -30012,7 +30015,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G966" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -30064,7 +30067,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G968" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -30090,7 +30093,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G969" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -30116,7 +30119,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G970" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -30142,7 +30145,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G971" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -30168,7 +30171,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G972" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -30194,7 +30197,7 @@
         <v>16</v>
       </c>
       <c r="G973" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -30298,7 +30301,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G977" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -30324,7 +30327,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -30402,7 +30405,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G981" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -30428,7 +30431,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G982" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -30454,7 +30457,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G983" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -30506,7 +30509,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G985" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -30532,7 +30535,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G986" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -30558,7 +30561,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G987" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -69566,7 +69569,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6495486111</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>93646</v>
@@ -69587,6 +69590,32 @@
         <v>1517</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6495138889</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>83956</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>48.4000015258789</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>49.2000007629395</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1518</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="1519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="1520">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6962604522705</t>
+    <t xml:space="preserve">15.6962614059448</t>
   </si>
   <si>
     <t xml:space="preserve">DAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8255252838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3269386291504</t>
+    <t xml:space="preserve">15.8255243301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3269367218018</t>
   </si>
   <si>
     <t xml:space="preserve">14.6344556808472</t>
@@ -56,28 +56,28 @@
     <t xml:space="preserve">14.3112964630127</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0343046188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3851613998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1358680725098</t>
+    <t xml:space="preserve">14.0343036651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3851623535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1358690261841</t>
   </si>
   <si>
     <t xml:space="preserve">13.9604396820068</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1940908432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.880166053772</t>
+    <t xml:space="preserve">13.194091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8801670074463</t>
   </si>
   <si>
     <t xml:space="preserve">12.9724988937378</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3723459243774</t>
+    <t xml:space="preserve">12.3723468780518</t>
   </si>
   <si>
     <t xml:space="preserve">13.037130355835</t>
@@ -86,58 +86,58 @@
     <t xml:space="preserve">13.221791267395</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0009517669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1579170227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.434907913208</t>
+    <t xml:space="preserve">16.0009536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1579189300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4349098205566</t>
   </si>
   <si>
     <t xml:space="preserve">16.1948471069336</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4718437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2289524078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7119007110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5762338638306</t>
+    <t xml:space="preserve">16.4718418121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2289543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7118988037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5762300491333</t>
   </si>
   <si>
     <t xml:space="preserve">16.2133140563965</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4100379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0407123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0499420166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4562005996704</t>
+    <t xml:space="preserve">15.4100332260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0407114028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0499458312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4561986923218</t>
   </si>
   <si>
     <t xml:space="preserve">15.2069063186646</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1053447723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0194225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3425788879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8780994415283</t>
+    <t xml:space="preserve">15.1053438186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.019416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3425769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8780956268311</t>
   </si>
   <si>
     <t xml:space="preserve">17.0350608825684</t>
@@ -146,70 +146,70 @@
     <t xml:space="preserve">17.1735553741455</t>
   </si>
   <si>
-    <t xml:space="preserve">17.081226348877</t>
+    <t xml:space="preserve">17.0812244415283</t>
   </si>
   <si>
     <t xml:space="preserve">16.822696685791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4626045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4533767700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9427318572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.748836517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.293586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4228496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4874839782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5521125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6472702026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3397521972656</t>
+    <t xml:space="preserve">16.4626083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4533748626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9427280426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7488327026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2935886383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4874801635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5521144866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6472721099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3397541046143</t>
   </si>
   <si>
     <t xml:space="preserve">17.6352119445801</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9888935089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3766841888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5798110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1273918151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3241100311279</t>
+    <t xml:space="preserve">16.9888954162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3766860961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.57981300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1273880004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3241119384766</t>
   </si>
   <si>
     <t xml:space="preserve">16.6657333374023</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0535278320312</t>
+    <t xml:space="preserve">17.0535259246826</t>
   </si>
   <si>
     <t xml:space="preserve">17.4043846130371</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6842002868652</t>
+    <t xml:space="preserve">16.6842021942139</t>
   </si>
   <si>
     <t xml:space="preserve">16.6380386352539</t>
@@ -218,19 +218,19 @@
     <t xml:space="preserve">17.238187789917</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6813735961914</t>
+    <t xml:space="preserve">17.68137550354</t>
   </si>
   <si>
     <t xml:space="preserve">17.7552394866943</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5244121551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9860649108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2353630065918</t>
+    <t xml:space="preserve">17.5244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9860668182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2353610992432</t>
   </si>
   <si>
     <t xml:space="preserve">18.143030166626</t>
@@ -239,28 +239,28 @@
     <t xml:space="preserve">17.912202835083</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7183094024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4661903381348</t>
+    <t xml:space="preserve">17.7183074951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4661922454834</t>
   </si>
   <si>
     <t xml:space="preserve">18.5308208465576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.558521270752</t>
+    <t xml:space="preserve">18.5585231781006</t>
   </si>
   <si>
     <t xml:space="preserve">18.2168960571289</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4477233886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1522617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0137672424316</t>
+    <t xml:space="preserve">18.4477214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1522655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.013765335083</t>
   </si>
   <si>
     <t xml:space="preserve">17.5890445709229</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">17.2658882141113</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6075077056885</t>
+    <t xml:space="preserve">17.6075096130371</t>
   </si>
   <si>
     <t xml:space="preserve">17.284351348877</t>
@@ -278,13 +278,13 @@
     <t xml:space="preserve">17.1920223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8873329162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9519596099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6749687194824</t>
+    <t xml:space="preserve">16.8873310089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.951961517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6749668121338</t>
   </si>
   <si>
     <t xml:space="preserve">16.4256782531738</t>
@@ -293,64 +293,64 @@
     <t xml:space="preserve">16.2594814300537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3610401153564</t>
+    <t xml:space="preserve">16.3610420227051</t>
   </si>
   <si>
     <t xml:space="preserve">16.8596305847168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5641765594482</t>
+    <t xml:space="preserve">16.564172744751</t>
   </si>
   <si>
     <t xml:space="preserve">16.5272388458252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.277946472168</t>
+    <t xml:space="preserve">16.2779445648193</t>
   </si>
   <si>
     <t xml:space="preserve">17.47825050354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6288032531738</t>
+    <t xml:space="preserve">16.6288013458252</t>
   </si>
   <si>
     <t xml:space="preserve">16.6103363037109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3582153320312</t>
+    <t xml:space="preserve">17.3582191467285</t>
   </si>
   <si>
     <t xml:space="preserve">17.1089248657227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1550922393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.917854309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9547882080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.059178352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8652839660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1699771881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4377355575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0655841827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0868768692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5513582229614</t>
+    <t xml:space="preserve">17.1550903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9178533554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9547891616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0591773986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8652830123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1699752807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4377336502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.065580368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0868759155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5513572692871</t>
   </si>
   <si>
     <t xml:space="preserve">14.9853115081787</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">14.7821846008301</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5115985870361</t>
+    <t xml:space="preserve">15.5116004943848</t>
   </si>
   <si>
     <t xml:space="preserve">15.1330413818359</t>
@@ -377,22 +377,22 @@
     <t xml:space="preserve">14.3574619293213</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7544841766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5023670196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4192686080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6039295196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3546371459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4285020828247</t>
+    <t xml:space="preserve">14.7544860839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.502366065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4192714691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6039304733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3546342849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4285001754761</t>
   </si>
   <si>
     <t xml:space="preserve">15.4008016586304</t>
@@ -401,55 +401,55 @@
     <t xml:space="preserve">15.4838991165161</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2502460479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7239599227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4931344985962</t>
+    <t xml:space="preserve">16.2502498626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7239608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4931325912476</t>
   </si>
   <si>
     <t xml:space="preserve">16.2317810058594</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9363241195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1856174468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2871761322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1763820648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.093282699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2566547393799</t>
+    <t xml:space="preserve">15.9363222122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1856136322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2871780395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.176383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0932846069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2566566467285</t>
   </si>
   <si>
     <t xml:space="preserve">16.9242610931396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7211360931396</t>
+    <t xml:space="preserve">16.7211322784424</t>
   </si>
   <si>
     <t xml:space="preserve">16.7580661773682</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7275447845459</t>
+    <t xml:space="preserve">17.7275428771973</t>
   </si>
   <si>
     <t xml:space="preserve">17.2751159667969</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1458549499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3120555877686</t>
+    <t xml:space="preserve">17.1458587646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3120536804199</t>
   </si>
   <si>
     <t xml:space="preserve">17.4505481719971</t>
@@ -458,73 +458,73 @@
     <t xml:space="preserve">16.204080581665</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8901529312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8624572753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9270877838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0563488006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7424278259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7701253890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6685628890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5946979522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7147274017334</t>
+    <t xml:space="preserve">15.8901519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8624563217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270896911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0563507080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7424268722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7701272964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6685609817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5946969985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7147264480591</t>
   </si>
   <si>
     <t xml:space="preserve">16.1394481658936</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8134632110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1671504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6408634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6500940322876</t>
+    <t xml:space="preserve">16.8134670257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1671485900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6408624649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6500978469849</t>
   </si>
   <si>
     <t xml:space="preserve">15.8070592880249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4654331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2623062133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3366203308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4109334945679</t>
+    <t xml:space="preserve">15.4654350280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2623052597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3366212844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4109354019165</t>
   </si>
   <si>
     <t xml:space="preserve">15.6524562835693</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7360610961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8939752578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6245880126953</t>
+    <t xml:space="preserve">15.7360601425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8939771652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6245861053467</t>
   </si>
   <si>
     <t xml:space="preserve">15.0765199661255</t>
@@ -533,28 +533,28 @@
     <t xml:space="preserve">15.4295139312744</t>
   </si>
   <si>
-    <t xml:space="preserve">15.522406578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5131168365479</t>
+    <t xml:space="preserve">15.5224056243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131196975708</t>
   </si>
   <si>
     <t xml:space="preserve">15.1601238250732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8661079406738</t>
+    <t xml:space="preserve">15.8661108016968</t>
   </si>
   <si>
     <t xml:space="preserve">16.3305759429932</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9311361312866</t>
+    <t xml:space="preserve">15.9311351776123</t>
   </si>
   <si>
     <t xml:space="preserve">15.4945373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6060094833374</t>
+    <t xml:space="preserve">15.606011390686</t>
   </si>
   <si>
     <t xml:space="preserve">15.3180418014526</t>
@@ -563,25 +563,25 @@
     <t xml:space="preserve">15.8846893310547</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0518951416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8382406234741</t>
+    <t xml:space="preserve">16.0518989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8382425308228</t>
   </si>
   <si>
     <t xml:space="preserve">16.5813865661621</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1851921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2595043182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1387405395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2223453521729</t>
+    <t xml:space="preserve">17.1851902008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2595024108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.138744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2223491668701</t>
   </si>
   <si>
     <t xml:space="preserve">17.0272693634033</t>
@@ -590,100 +590,100 @@
     <t xml:space="preserve">16.9529590606689</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4884929656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0922985076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9065113067627</t>
+    <t xml:space="preserve">16.488489151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0922966003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9065093994141</t>
   </si>
   <si>
     <t xml:space="preserve">17.1666107177734</t>
   </si>
   <si>
-    <t xml:space="preserve">17.742546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9004669189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9376220703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8818855285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.42995262146</t>
+    <t xml:space="preserve">17.7425479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.900463104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9376201629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8818893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4299507141113</t>
   </si>
   <si>
     <t xml:space="preserve">18.9037094116211</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9501533508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5539569854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6282749176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1173648834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9129981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4610652923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3310127258301</t>
+    <t xml:space="preserve">18.9501552581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.553955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6282730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1173629760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9129962921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.461067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3310165405273</t>
   </si>
   <si>
     <t xml:space="preserve">19.1823863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">19.080207824707</t>
+    <t xml:space="preserve">19.0802040100098</t>
   </si>
   <si>
     <t xml:space="preserve">18.8572597503662</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0151786804199</t>
+    <t xml:space="preserve">19.0151824951172</t>
   </si>
   <si>
     <t xml:space="preserve">18.9408645629883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9315757751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7550792694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5785827636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4020862579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1141166687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.457820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5321369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.467113494873</t>
+    <t xml:space="preserve">18.9315738677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7550773620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5785865783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4020881652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1141204833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4578227996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5321388244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4671115875244</t>
   </si>
   <si>
     <t xml:space="preserve">18.3742179870605</t>
   </si>
   <si>
-    <t xml:space="preserve">18.485689163208</t>
+    <t xml:space="preserve">18.4856929779053</t>
   </si>
   <si>
     <t xml:space="preserve">18.2813262939453</t>
@@ -701,46 +701,46 @@
     <t xml:space="preserve">18.6250305175781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7272129058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0430488586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4146213531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0894927978516</t>
+    <t xml:space="preserve">18.7272109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0430450439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4146175384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0894908905029</t>
   </si>
   <si>
     <t xml:space="preserve">19.126651763916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3681755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4517784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9594459533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2474098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5075130462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0987815856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2195453643799</t>
+    <t xml:space="preserve">19.3681716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4517765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9594440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2474117279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.507511138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0987854003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2195434570312</t>
   </si>
   <si>
     <t xml:space="preserve">19.3495941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0337581634521</t>
+    <t xml:space="preserve">19.0337543487549</t>
   </si>
   <si>
     <t xml:space="preserve">19.2288341522217</t>
@@ -749,55 +749,55 @@
     <t xml:space="preserve">19.386754989624</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2845687866211</t>
+    <t xml:space="preserve">19.2845726013184</t>
   </si>
   <si>
     <t xml:space="preserve">19.9162406921387</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0091342926025</t>
+    <t xml:space="preserve">20.0091361999512</t>
   </si>
   <si>
     <t xml:space="preserve">20.3807067871094</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6222267150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8544654846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9659309387207</t>
+    <t xml:space="preserve">20.6222286224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8544597625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9659290313721</t>
   </si>
   <si>
     <t xml:space="preserve">20.9473533630371</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1484756469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6129398345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3899955749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2506542205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5757808685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6500930786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6036510467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.50146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.529333114624</t>
+    <t xml:space="preserve">20.148473739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6129379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3899936676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2506561279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5757789611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6500968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6036529541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5014686584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5293350219727</t>
   </si>
   <si>
     <t xml:space="preserve">20.6593856811523</t>
@@ -806,16 +806,16 @@
     <t xml:space="preserve">20.4828872680664</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8172988891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.863748550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.455020904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7801456451416</t>
+    <t xml:space="preserve">20.8173007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8637466430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4550228118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7801475524902</t>
   </si>
   <si>
     <t xml:space="preserve">21.6440505981445</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">21.3653717041016</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3189239501953</t>
+    <t xml:space="preserve">21.3189258575439</t>
   </si>
   <si>
     <t xml:space="preserve">21.1331386566162</t>
@@ -836,124 +836,124 @@
     <t xml:space="preserve">21.1238498687744</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9287757873535</t>
+    <t xml:space="preserve">20.9287738800049</t>
   </si>
   <si>
     <t xml:space="preserve">21.2724761962891</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1052722930908</t>
+    <t xml:space="preserve">21.1052684783936</t>
   </si>
   <si>
     <t xml:space="preserve">21.3467922210693</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2260284423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6408061981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1702938079834</t>
+    <t xml:space="preserve">21.2260322570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6408042907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1702976226807</t>
   </si>
   <si>
     <t xml:space="preserve">20.9566402435303</t>
   </si>
   <si>
-    <t xml:space="preserve">21.114559173584</t>
+    <t xml:space="preserve">21.1145629882812</t>
   </si>
   <si>
     <t xml:space="preserve">21.2538986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.244607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3375053405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2817668914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9380645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1795864105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7336978912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3156795501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3992824554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4085712432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3249683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6315174102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2785224914551</t>
+    <t xml:space="preserve">21.2446117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3375034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2817649841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9380664825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1795825958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.733699798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3156814575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.399284362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4085731506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.32497215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6315155029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2785263061523</t>
   </si>
   <si>
     <t xml:space="preserve">20.0462913513184</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2134990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7954788208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9069538116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2692356109619</t>
+    <t xml:space="preserve">20.2134971618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7954807281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9069519042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2692317962646</t>
   </si>
   <si>
     <t xml:space="preserve">20.2971019744873</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5479145050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4364433288574</t>
+    <t xml:space="preserve">20.5479164123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4364395141602</t>
   </si>
   <si>
     <t xml:space="preserve">19.9533996582031</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8326358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8883724212646</t>
+    <t xml:space="preserve">19.8326377868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8883743286133</t>
   </si>
   <si>
     <t xml:space="preserve">19.7211666107178</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9255294799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0741596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9998435974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1113185882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6747207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6686744689941</t>
+    <t xml:space="preserve">19.9255275726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0741577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9998455047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1113166809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6747188568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6686725616455</t>
   </si>
   <si>
     <t xml:space="preserve">20.2413673400879</t>
@@ -962,22 +962,22 @@
     <t xml:space="preserve">19.9719753265381</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7304553985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4178619384766</t>
+    <t xml:space="preserve">19.7304534912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4178638458252</t>
   </si>
   <si>
     <t xml:space="preserve">20.1298961639404</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4921760559082</t>
+    <t xml:space="preserve">20.4921741485596</t>
   </si>
   <si>
     <t xml:space="preserve">20.8451709747314</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3435459136963</t>
+    <t xml:space="preserve">20.3435478210449</t>
   </si>
   <si>
     <t xml:space="preserve">20.5664901733398</t>
@@ -989,25 +989,25 @@
     <t xml:space="preserve">21.1981620788574</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7244091033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4735984802246</t>
+    <t xml:space="preserve">20.7244110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4736003875732</t>
   </si>
   <si>
     <t xml:space="preserve">20.3342590332031</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3714160919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8790874481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8419284820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7676105499268</t>
+    <t xml:space="preserve">20.3714179992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8790817260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8419303894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.767614364624</t>
   </si>
   <si>
     <t xml:space="preserve">19.9812660217285</t>
@@ -1016,16 +1016,16 @@
     <t xml:space="preserve">20.092737197876</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5200481414795</t>
+    <t xml:space="preserve">20.5200443267822</t>
   </si>
   <si>
     <t xml:space="preserve">19.9905567169189</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5353813171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2567005157471</t>
+    <t xml:space="preserve">19.5353832244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2566986083984</t>
   </si>
   <si>
     <t xml:space="preserve">18.7829456329346</t>
@@ -1034,31 +1034,31 @@
     <t xml:space="preserve">18.8386840820312</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6343212127686</t>
+    <t xml:space="preserve">18.6343193054199</t>
   </si>
   <si>
     <t xml:space="preserve">18.9966011047363</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6807651519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5600032806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6621875762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4392471313477</t>
+    <t xml:space="preserve">18.6807670593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.560001373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6621856689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4392433166504</t>
   </si>
   <si>
     <t xml:space="preserve">18.8108158111572</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1359424591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9779281616211</t>
+    <t xml:space="preserve">19.1359367370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9779319763184</t>
   </si>
   <si>
     <t xml:space="preserve">18.9499244689941</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">18.5298538208008</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3058166503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.904411315918</t>
+    <t xml:space="preserve">18.305814743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9044132232666</t>
   </si>
   <si>
     <t xml:space="preserve">17.8484039306641</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">17.6430339813232</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6710395812988</t>
+    <t xml:space="preserve">17.6710414886475</t>
   </si>
   <si>
     <t xml:space="preserve">17.9417533874512</t>
@@ -1088,16 +1088,16 @@
     <t xml:space="preserve">17.8950786590576</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9697570800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2684745788574</t>
+    <t xml:space="preserve">17.9697589874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2684783935547</t>
   </si>
   <si>
     <t xml:space="preserve">18.4645099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5858631134033</t>
+    <t xml:space="preserve">18.585865020752</t>
   </si>
   <si>
     <t xml:space="preserve">18.4084987640381</t>
@@ -1109,37 +1109,37 @@
     <t xml:space="preserve">18.4925155639648</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3618259429932</t>
+    <t xml:space="preserve">18.3618240356445</t>
   </si>
   <si>
     <t xml:space="preserve">18.2218017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6698780059814</t>
+    <t xml:space="preserve">18.6698799133301</t>
   </si>
   <si>
     <t xml:space="preserve">18.7725639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">18.697883605957</t>
+    <t xml:space="preserve">18.6978816986084</t>
   </si>
   <si>
     <t xml:space="preserve">18.688549041748</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6138706207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3524913787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3804950714111</t>
+    <t xml:space="preserve">18.6138687133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3524894714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3804969787598</t>
   </si>
   <si>
     <t xml:space="preserve">18.4458408355713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4831771850586</t>
+    <t xml:space="preserve">18.4831790924072</t>
   </si>
   <si>
     <t xml:space="preserve">18.4738464355469</t>
@@ -1148,103 +1148,103 @@
     <t xml:space="preserve">18.6605434417725</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7072162628174</t>
+    <t xml:space="preserve">18.707218170166</t>
   </si>
   <si>
     <t xml:space="preserve">18.5951995849609</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3898334503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5018482208252</t>
+    <t xml:space="preserve">18.3898315429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5018501281738</t>
   </si>
   <si>
     <t xml:space="preserve">18.9032516479492</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1832962036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4633502960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7433948516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5368690490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2836608886719</t>
+    <t xml:space="preserve">19.1832981109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4633464813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7433929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.536865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2836589813232</t>
   </si>
   <si>
     <t xml:space="preserve">21.5637073516846</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5170345306396</t>
+    <t xml:space="preserve">21.517032623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.377010345459</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6103820800781</t>
+    <t xml:space="preserve">21.6103839874268</t>
   </si>
   <si>
     <t xml:space="preserve">21.4703598022461</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7504081726074</t>
+    <t xml:space="preserve">21.7504100799561</t>
   </si>
   <si>
     <t xml:space="preserve">21.797082901001</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0036106109619</t>
+    <t xml:space="preserve">21.0036125183105</t>
   </si>
   <si>
     <t xml:space="preserve">20.4435157775879</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0502872467041</t>
+    <t xml:space="preserve">21.0502891540527</t>
   </si>
   <si>
     <t xml:space="preserve">20.6302165985107</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7702407836914</t>
+    <t xml:space="preserve">20.7702369689941</t>
   </si>
   <si>
     <t xml:space="preserve">20.7235679626465</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0969638824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1903133392334</t>
+    <t xml:space="preserve">21.0969619750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1903114318848</t>
   </si>
   <si>
     <t xml:space="preserve">21.1436386108398</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8635883331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6768913269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7037334442139</t>
+    <t xml:space="preserve">20.8635902404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6768894195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7037353515625</t>
   </si>
   <si>
     <t xml:space="preserve">22.2171535491943</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8904342651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.077127456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9837799072266</t>
+    <t xml:space="preserve">21.8904323577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0771293640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9837818145752</t>
   </si>
   <si>
     <t xml:space="preserve">20.8169136047363</t>
@@ -1253,19 +1253,19 @@
     <t xml:space="preserve">21.2369861602783</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3034915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2101421356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9102611541748</t>
+    <t xml:space="preserve">20.3034934997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2101440429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9102649688721</t>
   </si>
   <si>
     <t xml:space="preserve">20.5835399627686</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9569358825684</t>
+    <t xml:space="preserve">20.9569396972656</t>
   </si>
   <si>
     <t xml:space="preserve">21.3303375244141</t>
@@ -1274,31 +1274,34 @@
     <t xml:space="preserve">20.3968410491943</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4901943206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1167964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0432739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.136625289917</t>
+    <t xml:space="preserve">20.4901905059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.116792678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.996603012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0432758331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1366233825684</t>
   </si>
   <si>
     <t xml:space="preserve">19.3233261108398</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7900695800781</t>
+    <t xml:space="preserve">19.7900714874268</t>
   </si>
   <si>
     <t xml:space="preserve">19.6033725738525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3501644134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2568168640137</t>
+    <t xml:space="preserve">20.3501682281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2568187713623</t>
   </si>
   <si>
     <t xml:space="preserve">19.9767684936523</t>
@@ -1307,7 +1310,7 @@
     <t xml:space="preserve">20.1634693145752</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0234451293945</t>
+    <t xml:space="preserve">20.0234432220459</t>
   </si>
   <si>
     <t xml:space="preserve">19.8834190368652</t>
@@ -1316,91 +1319,91 @@
     <t xml:space="preserve">19.9300956726074</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4166736602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.556697845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5100231170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6500434875488</t>
+    <t xml:space="preserve">19.4166717529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5566997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5100212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6500453948975</t>
   </si>
   <si>
     <t xml:space="preserve">19.696720123291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.276647567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2299728393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3699989318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8367443084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4236869812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0701198577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7177143096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3092994689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7013673782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7678728103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4691553115845</t>
+    <t xml:space="preserve">19.2766494750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2299709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3699970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8367462158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4236888885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0701179504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.717716217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3093004226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7013654708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7678737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4691543579102</t>
   </si>
   <si>
     <t xml:space="preserve">14.8052129745483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4026489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6266889572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0000839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333375930786</t>
+    <t xml:space="preserve">15.4026498794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6266851425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0000858306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333395004272</t>
   </si>
   <si>
     <t xml:space="preserve">15.3279695510864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4586591720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8693990707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.794716835022</t>
+    <t xml:space="preserve">15.4586601257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8693971633911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7947158813477</t>
   </si>
   <si>
     <t xml:space="preserve">15.6640272140503</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5893497467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.383978843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0105810165405</t>
+    <t xml:space="preserve">15.5893507003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3839797973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0105829238892</t>
   </si>
   <si>
     <t xml:space="preserve">14.8602876663208</t>
@@ -1412,34 +1415,34 @@
     <t xml:space="preserve">14.4094076156616</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4469814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9166479110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9354362487793</t>
+    <t xml:space="preserve">14.4469804763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9166488647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.935435295105</t>
   </si>
   <si>
     <t xml:space="preserve">14.6536350250244</t>
   </si>
   <si>
-    <t xml:space="preserve">15.14208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4426765441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2735948562622</t>
+    <t xml:space="preserve">15.1420907974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4426774978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2735958099365</t>
   </si>
   <si>
     <t xml:space="preserve">14.0712471008301</t>
   </si>
   <si>
-    <t xml:space="preserve">13.920952796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6015777587891</t>
+    <t xml:space="preserve">13.9209518432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6015787124634</t>
   </si>
   <si>
     <t xml:space="preserve">13.7330856323242</t>
@@ -1454,34 +1457,34 @@
     <t xml:space="preserve">14.1463937759399</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2215414047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9585247039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6391525268555</t>
+    <t xml:space="preserve">14.2215404510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9585256576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6391534805298</t>
   </si>
   <si>
     <t xml:space="preserve">13.6203651428223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7894458770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0524587631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2027530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5221271514893</t>
+    <t xml:space="preserve">13.7894468307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0524597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2027540206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5221281051636</t>
   </si>
   <si>
     <t xml:space="preserve">14.7475671768188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2172374725342</t>
+    <t xml:space="preserve">15.2172365188599</t>
   </si>
   <si>
     <t xml:space="preserve">15.1233024597168</t>
@@ -1493,25 +1496,25 @@
     <t xml:space="preserve">15.0669422149658</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8978614807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1045150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1608743667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984481811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5366106033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9687070846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8141059875488</t>
+    <t xml:space="preserve">14.8978605270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1045160293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1608762741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1984491348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366125106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9687061309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8141040802002</t>
   </si>
   <si>
     <t xml:space="preserve">16.889253616333</t>
@@ -1520,7 +1523,7 @@
     <t xml:space="preserve">16.9080390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4947299957275</t>
+    <t xml:space="preserve">16.4947319030762</t>
   </si>
   <si>
     <t xml:space="preserve">16.419584274292</t>
@@ -1529,31 +1532,31 @@
     <t xml:space="preserve">16.2692909240723</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3632221221924</t>
+    <t xml:space="preserve">16.3632259368896</t>
   </si>
   <si>
     <t xml:space="preserve">15.987491607666</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8747720718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8184118270874</t>
+    <t xml:space="preserve">15.8747711181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8184099197388</t>
   </si>
   <si>
     <t xml:space="preserve">16.1377849578857</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1565704345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2505016326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.62624168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5135173797607</t>
+    <t xml:space="preserve">16.1565742492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2505035400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6262378692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5135192871094</t>
   </si>
   <si>
     <t xml:space="preserve">16.2880783081055</t>
@@ -1562,13 +1565,13 @@
     <t xml:space="preserve">16.4383716583252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4571590423584</t>
+    <t xml:space="preserve">16.457160949707</t>
   </si>
   <si>
     <t xml:space="preserve">16.2317180633545</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6074523925781</t>
+    <t xml:space="preserve">16.6074542999268</t>
   </si>
   <si>
     <t xml:space="preserve">16.7201709747314</t>
@@ -1577,19 +1580,19 @@
     <t xml:space="preserve">16.475944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3256511688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8559837341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9499197006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9311294555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1189975738525</t>
+    <t xml:space="preserve">16.3256492614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8559827804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9499158859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.931131362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1189994812012</t>
   </si>
   <si>
     <t xml:space="preserve">16.0062789916992</t>
@@ -1598,13 +1601,13 @@
     <t xml:space="preserve">16.3444366455078</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4007968902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5323066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7765350341797</t>
+    <t xml:space="preserve">16.4007987976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5323047637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7765331268311</t>
   </si>
   <si>
     <t xml:space="preserve">16.945613861084</t>
@@ -1613,46 +1616,46 @@
     <t xml:space="preserve">17.4716396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2794704437256</t>
+    <t xml:space="preserve">18.279468536377</t>
   </si>
   <si>
     <t xml:space="preserve">18.260684967041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2418937683105</t>
+    <t xml:space="preserve">18.2418956756592</t>
   </si>
   <si>
     <t xml:space="preserve">18.1103897094727</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5279979705811</t>
+    <t xml:space="preserve">17.5280017852783</t>
   </si>
   <si>
     <t xml:space="preserve">17.1334819793701</t>
   </si>
   <si>
-    <t xml:space="preserve">17.001974105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9831867218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7389602661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6450271606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9643993377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8328952789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0583343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1522674560547</t>
+    <t xml:space="preserve">17.0019721984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9831886291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7389583587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6450252532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9643974304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.832893371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0583324432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1522655487061</t>
   </si>
   <si>
     <t xml:space="preserve">17.2274131774902</t>
@@ -1661,19 +1664,19 @@
     <t xml:space="preserve">16.7577457427979</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2129325866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4990358352661</t>
+    <t xml:space="preserve">16.2129344940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4990367889404</t>
   </si>
   <si>
     <t xml:space="preserve">15.5178232192993</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4614639282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1796607971191</t>
+    <t xml:space="preserve">15.461462020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1796627044678</t>
   </si>
   <si>
     <t xml:space="preserve">14.6912088394165</t>
@@ -1682,13 +1685,13 @@
     <t xml:space="preserve">14.8039293289185</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0857276916504</t>
+    <t xml:space="preserve">15.0857286453247</t>
   </si>
   <si>
     <t xml:space="preserve">14.7663555145264</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9730081558228</t>
+    <t xml:space="preserve">14.9730062484741</t>
   </si>
   <si>
     <t xml:space="preserve">14.8415012359619</t>
@@ -1700,7 +1703,7 @@
     <t xml:space="preserve">14.6724224090576</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3718347549438</t>
+    <t xml:space="preserve">14.3718338012695</t>
   </si>
   <si>
     <t xml:space="preserve">14.8227138519287</t>
@@ -1712,28 +1715,25 @@
     <t xml:space="preserve">14.4657669067383</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6348476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5741834640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4051027297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3863153457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6681184768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2360229492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0105819702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5929727554321</t>
+    <t xml:space="preserve">14.6348466873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.574182510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.405104637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3863162994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6681175231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2360219955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5929708480835</t>
   </si>
   <si>
     <t xml:space="preserve">15.4238891601562</t>
@@ -1748,19 +1748,19 @@
     <t xml:space="preserve">14.8790760040283</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5409126281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7851419448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.616060256958</t>
+    <t xml:space="preserve">14.5409135818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7851409912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6160621643066</t>
   </si>
   <si>
     <t xml:space="preserve">14.2966871261597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2778997421265</t>
+    <t xml:space="preserve">14.2779006958008</t>
   </si>
   <si>
     <t xml:space="preserve">14.090033531189</t>
@@ -1769,58 +1769,58 @@
     <t xml:space="preserve">13.9021663665771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7706594467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4281930923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2591142654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8082332611084</t>
+    <t xml:space="preserve">13.770658493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4281949996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2591133117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8082323074341</t>
   </si>
   <si>
     <t xml:space="preserve">13.8458051681519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0336713790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9397392272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.240327835083</t>
+    <t xml:space="preserve">14.0336723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9397411346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2403259277344</t>
   </si>
   <si>
     <t xml:space="preserve">14.0148868560791</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5972747802734</t>
+    <t xml:space="preserve">14.5972738265991</t>
   </si>
   <si>
     <t xml:space="preserve">13.9960994720459</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3675308227539</t>
+    <t xml:space="preserve">15.3675298690796</t>
   </si>
   <si>
     <t xml:space="preserve">14.1839666366577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1088209152222</t>
+    <t xml:space="preserve">14.1088190078735</t>
   </si>
   <si>
     <t xml:space="preserve">14.4845533370972</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9917964935303</t>
+    <t xml:space="preserve">14.9917945861816</t>
   </si>
   <si>
     <t xml:space="preserve">15.292384147644</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0758943557739</t>
+    <t xml:space="preserve">15.0758934020996</t>
   </si>
   <si>
     <t xml:space="preserve">15.0569305419922</t>
@@ -1841,13 +1841,13 @@
     <t xml:space="preserve">15.6827239990234</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4602203369141</t>
+    <t xml:space="preserve">16.4602222442627</t>
   </si>
   <si>
     <t xml:space="preserve">16.3274765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7016849517822</t>
+    <t xml:space="preserve">15.7016859054565</t>
   </si>
   <si>
     <t xml:space="preserve">15.6637582778931</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">16.1757678985596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7206497192383</t>
+    <t xml:space="preserve">15.7206478118896</t>
   </si>
   <si>
     <t xml:space="preserve">15.6068668365479</t>
@@ -1883,13 +1883,13 @@
     <t xml:space="preserve">16.043025970459</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9861345291138</t>
+    <t xml:space="preserve">15.9861364364624</t>
   </si>
   <si>
     <t xml:space="preserve">15.4172344207764</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8344278335571</t>
+    <t xml:space="preserve">15.8344297409058</t>
   </si>
   <si>
     <t xml:space="preserve">15.568941116333</t>
@@ -1904,19 +1904,19 @@
     <t xml:space="preserve">15.246563911438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1138191223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9810752868652</t>
+    <t xml:space="preserve">15.1138181686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9810762405396</t>
   </si>
   <si>
     <t xml:space="preserve">15.2086372375488</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7535161972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.943151473999</t>
+    <t xml:space="preserve">14.7535171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9431505203247</t>
   </si>
   <si>
     <t xml:space="preserve">14.5069913864136</t>
@@ -1937,16 +1937,16 @@
     <t xml:space="preserve">14.7914428710938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5828456878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3932104110718</t>
+    <t xml:space="preserve">14.5828447341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3932113647461</t>
   </si>
   <si>
     <t xml:space="preserve">14.4311380386353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6207723617554</t>
+    <t xml:space="preserve">14.6207714080811</t>
   </si>
   <si>
     <t xml:space="preserve">14.3363218307495</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">13.1416273117065</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0088834762573</t>
+    <t xml:space="preserve">13.0088844299316</t>
   </si>
   <si>
     <t xml:space="preserve">13.3691883087158</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">12.8002862930298</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4210186004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1744956970215</t>
+    <t xml:space="preserve">12.4210195541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1744947433472</t>
   </si>
   <si>
     <t xml:space="preserve">11.9469337463379</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">11.0366916656494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1264495849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95577907562256</t>
+    <t xml:space="preserve">10.1264486312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95577812194824</t>
   </si>
   <si>
     <t xml:space="preserve">9.59547424316406</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">8.91279315948486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41532230377197</t>
+    <t xml:space="preserve">9.41532325744629</t>
   </si>
   <si>
     <t xml:space="preserve">8.09736633300781</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">8.55248832702637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10242557525635</t>
+    <t xml:space="preserve">9.10242652893066</t>
   </si>
   <si>
     <t xml:space="preserve">10.1643753051758</t>
@@ -2030,13 +2030,13 @@
     <t xml:space="preserve">11.6055927276611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9608392715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9229116439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6384611129761</t>
+    <t xml:space="preserve">10.9608383178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9229106903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6384620666504</t>
   </si>
   <si>
     <t xml:space="preserve">10.0695581436157</t>
@@ -2054,22 +2054,22 @@
     <t xml:space="preserve">11.1125450134277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9039478302002</t>
+    <t xml:space="preserve">10.9039487838745</t>
   </si>
   <si>
     <t xml:space="preserve">10.5815696716309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2023029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87992572784424</t>
+    <t xml:space="preserve">10.2023038864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87992477416992</t>
   </si>
   <si>
     <t xml:space="preserve">10.2212657928467</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5057182312012</t>
+    <t xml:space="preserve">10.5057172775269</t>
   </si>
   <si>
     <t xml:space="preserve">10.4298629760742</t>
@@ -2087,13 +2087,13 @@
     <t xml:space="preserve">10.8091306686401</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8280944824219</t>
+    <t xml:space="preserve">10.8280954360962</t>
   </si>
   <si>
     <t xml:space="preserve">10.543643951416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9987649917603</t>
+    <t xml:space="preserve">10.9987659454346</t>
   </si>
   <si>
     <t xml:space="preserve">10.9418754577637</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">11.491813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5676670074463</t>
+    <t xml:space="preserve">11.567666053772</t>
   </si>
   <si>
     <t xml:space="preserve">11.0556545257568</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">12.2124214172363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0986423492432</t>
+    <t xml:space="preserve">12.0986413955688</t>
   </si>
   <si>
     <t xml:space="preserve">11.8521175384521</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">11.017728805542</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1883993148804</t>
+    <t xml:space="preserve">11.1883983612061</t>
   </si>
   <si>
     <t xml:space="preserve">11.0935831069946</t>
@@ -2147,16 +2147,16 @@
     <t xml:space="preserve">10.8849849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7901668548584</t>
+    <t xml:space="preserve">10.7901678085327</t>
   </si>
   <si>
     <t xml:space="preserve">10.6763877868652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4108991622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.448826789856</t>
+    <t xml:space="preserve">10.4109001159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4488277435303</t>
   </si>
   <si>
     <t xml:space="preserve">10.6574230194092</t>
@@ -2186,22 +2186,22 @@
     <t xml:space="preserve">10.4677906036377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6435203552246</t>
+    <t xml:space="preserve">11.6435194015503</t>
   </si>
   <si>
     <t xml:space="preserve">11.4349241256714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6814470291138</t>
+    <t xml:space="preserve">11.6814460754395</t>
   </si>
   <si>
     <t xml:space="preserve">11.5297393798828</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6245574951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5487041473389</t>
+    <t xml:space="preserve">11.6245584487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5487031936646</t>
   </si>
   <si>
     <t xml:space="preserve">11.662483215332</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">12.2313861846924</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1365690231323</t>
+    <t xml:space="preserve">12.136568069458</t>
   </si>
   <si>
     <t xml:space="preserve">12.1176052093506</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">11.8141899108887</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7573013305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.245288848877</t>
+    <t xml:space="preserve">11.7573003768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2452898025513</t>
   </si>
   <si>
     <t xml:space="preserve">12.6485795974731</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">13.653639793396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3881511688232</t>
+    <t xml:space="preserve">13.3881521224976</t>
   </si>
   <si>
     <t xml:space="preserve">13.8622369766235</t>
@@ -2249,13 +2249,13 @@
     <t xml:space="preserve">13.5967493057251</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2364444732666</t>
+    <t xml:space="preserve">13.2364454269409</t>
   </si>
   <si>
     <t xml:space="preserve">13.4260787963867</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4640054702759</t>
+    <t xml:space="preserve">13.4640064239502</t>
   </si>
   <si>
     <t xml:space="preserve">13.1037006378174</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">13.4071159362793</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1226644515991</t>
+    <t xml:space="preserve">13.1226654052734</t>
   </si>
   <si>
     <t xml:space="preserve">13.4829692840576</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">13.17955493927</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0227880477905</t>
+    <t xml:space="preserve">12.0227870941162</t>
   </si>
   <si>
     <t xml:space="preserve">12.0607147216797</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">12.3262023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4399824142456</t>
+    <t xml:space="preserve">12.4399814605713</t>
   </si>
   <si>
     <t xml:space="preserve">12.8571786880493</t>
@@ -2300,22 +2300,22 @@
     <t xml:space="preserve">12.8192510604858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0468111038208</t>
+    <t xml:space="preserve">13.0468120574951</t>
   </si>
   <si>
     <t xml:space="preserve">13.3122987747192</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4450426101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5588235855103</t>
+    <t xml:space="preserve">13.4450416564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5588226318359</t>
   </si>
   <si>
     <t xml:space="preserve">13.6179914474487</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6371440887451</t>
+    <t xml:space="preserve">13.6371450424194</t>
   </si>
   <si>
     <t xml:space="preserve">13.4073057174683</t>
@@ -2348,10 +2348,10 @@
     <t xml:space="preserve">14.2117433547974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9819040298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6946058273315</t>
+    <t xml:space="preserve">13.9819049835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6946048736572</t>
   </si>
   <si>
     <t xml:space="preserve">13.4647645950317</t>
@@ -2360,7 +2360,7 @@
     <t xml:space="preserve">13.7712182998657</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5988368988037</t>
+    <t xml:space="preserve">13.598837852478</t>
   </si>
   <si>
     <t xml:space="preserve">13.5413789749146</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">13.7903709411621</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7137565612793</t>
+    <t xml:space="preserve">13.7137575149536</t>
   </si>
   <si>
     <t xml:space="preserve">13.8669843673706</t>
@@ -2384,10 +2384,10 @@
     <t xml:space="preserve">14.7097291946411</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6331157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9970283508301</t>
+    <t xml:space="preserve">14.6331148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9970273971558</t>
   </si>
   <si>
     <t xml:space="preserve">15.0353345870972</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">15.8014659881592</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6099328994751</t>
+    <t xml:space="preserve">15.6099338531494</t>
   </si>
   <si>
     <t xml:space="preserve">15.3226346969604</t>
@@ -2429,16 +2429,16 @@
     <t xml:space="preserve">15.7248525619507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8589248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2611446380615</t>
+    <t xml:space="preserve">15.8589267730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2611427307129</t>
   </si>
   <si>
     <t xml:space="preserve">16.6059036254883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.778284072876</t>
+    <t xml:space="preserve">16.7782859802246</t>
   </si>
   <si>
     <t xml:space="preserve">16.6825180053711</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">17.1421966552734</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1996574401855</t>
+    <t xml:space="preserve">17.1996555328369</t>
   </si>
   <si>
     <t xml:space="preserve">16.9889698028564</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">16.4335250854492</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9123554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.663366317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9506664276123</t>
+    <t xml:space="preserve">16.9123573303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6633644104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9506645202637</t>
   </si>
   <si>
     <t xml:space="preserve">16.9315128326416</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">20.302490234375</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7757759094238</t>
+    <t xml:space="preserve">19.7757740020752</t>
   </si>
   <si>
     <t xml:space="preserve">20.7334384918213</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">20.4940242767334</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1109580993652</t>
+    <t xml:space="preserve">20.1109561920166</t>
   </si>
   <si>
     <t xml:space="preserve">19.9673080444336</t>
@@ -2528,10 +2528,10 @@
     <t xml:space="preserve">20.3982563018799</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5419082641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.637674331665</t>
+    <t xml:space="preserve">20.5419063568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6376724243164</t>
   </si>
   <si>
     <t xml:space="preserve">20.9728546142578</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">20.9249725341797</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7278919219971</t>
+    <t xml:space="preserve">19.7278900146484</t>
   </si>
   <si>
     <t xml:space="preserve">19.4884777069092</t>
@@ -2561,10 +2561,10 @@
     <t xml:space="preserve">19.5363597869873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8236598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1532936096191</t>
+    <t xml:space="preserve">19.823657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1532955169678</t>
   </si>
   <si>
     <t xml:space="preserve">20.2546062469482</t>
@@ -2579,7 +2579,7 @@
     <t xml:space="preserve">21.1165046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6911029815674</t>
+    <t xml:space="preserve">21.691104888916</t>
   </si>
   <si>
     <t xml:space="preserve">21.3080368041992</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">21.8826370239258</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9784030914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2122707366943</t>
+    <t xml:space="preserve">21.9784049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.212272644043</t>
   </si>
   <si>
     <t xml:space="preserve">21.355920791626</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">21.4516868591309</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3135833740234</t>
+    <t xml:space="preserve">22.3135852813721</t>
   </si>
   <si>
     <t xml:space="preserve">22.7924175262451</t>
@@ -2621,19 +2621,19 @@
     <t xml:space="preserve">23.3191337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6487693786621</t>
+    <t xml:space="preserve">22.6487674713135</t>
   </si>
   <si>
     <t xml:space="preserve">22.4093532562256</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0262851715088</t>
+    <t xml:space="preserve">22.0262870788574</t>
   </si>
   <si>
     <t xml:space="preserve">21.6432209014893</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4038066864014</t>
+    <t xml:space="preserve">21.4038047790527</t>
   </si>
   <si>
     <t xml:space="preserve">20.8292064666748</t>
@@ -2645,22 +2645,22 @@
     <t xml:space="preserve">21.9305191040039</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5162162780762</t>
+    <t xml:space="preserve">24.5162143707275</t>
   </si>
   <si>
     <t xml:space="preserve">23.9416160583496</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4627857208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4149036407471</t>
+    <t xml:space="preserve">23.4627838134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4149017333984</t>
   </si>
   <si>
     <t xml:space="preserve">23.1754856109619</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2712497711182</t>
+    <t xml:space="preserve">23.2712516784668</t>
   </si>
   <si>
     <t xml:space="preserve">23.5106658935547</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">23.22336769104</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7500839233398</t>
+    <t xml:space="preserve">23.7500820159912</t>
   </si>
   <si>
     <t xml:space="preserve">23.6064338684082</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">23.797966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7022018432617</t>
+    <t xml:space="preserve">23.7021999359131</t>
   </si>
   <si>
     <t xml:space="preserve">23.654317855835</t>
@@ -2696,16 +2696,16 @@
     <t xml:space="preserve">22.8403034210205</t>
   </si>
   <si>
-    <t xml:space="preserve">22.600887298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2657012939453</t>
+    <t xml:space="preserve">22.6008853912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2657032012939</t>
   </si>
   <si>
     <t xml:space="preserve">21.5953369140625</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2178173065186</t>
+    <t xml:space="preserve">22.2178192138672</t>
   </si>
   <si>
     <t xml:space="preserve">22.1699352264404</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">24.4683322906494</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0373821258545</t>
+    <t xml:space="preserve">24.0373840332031</t>
   </si>
   <si>
     <t xml:space="preserve">23.8458499908447</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">25.4738807678223</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7611789703369</t>
+    <t xml:space="preserve">25.7611770629883</t>
   </si>
   <si>
     <t xml:space="preserve">26.1442432403564</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">25.8569431304932</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8090629577637</t>
+    <t xml:space="preserve">25.809061050415</t>
   </si>
   <si>
     <t xml:space="preserve">25.9527111053467</t>
@@ -2747,19 +2747,19 @@
     <t xml:space="preserve">25.6654109954834</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4794273376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5751953125</t>
+    <t xml:space="preserve">26.4794254302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5751934051514</t>
   </si>
   <si>
     <t xml:space="preserve">27.4849758148193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3892116546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3413257598877</t>
+    <t xml:space="preserve">27.3892097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3413238525391</t>
   </si>
   <si>
     <t xml:space="preserve">27.8680419921875</t>
@@ -2768,10 +2768,10 @@
     <t xml:space="preserve">28.4905223846436</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9638080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2989883422852</t>
+    <t xml:space="preserve">27.963809967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2989902496338</t>
   </si>
   <si>
     <t xml:space="preserve">27.772274017334</t>
@@ -2786,13 +2786,13 @@
     <t xml:space="preserve">27.5328598022461</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2455596923828</t>
+    <t xml:space="preserve">27.2455615997314</t>
   </si>
   <si>
     <t xml:space="preserve">26.9582595825195</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1497917175293</t>
+    <t xml:space="preserve">27.1497936248779</t>
   </si>
   <si>
     <t xml:space="preserve">27.0540256500244</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">26.9287757873535</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2543525695801</t>
+    <t xml:space="preserve">26.2543506622314</t>
   </si>
   <si>
     <t xml:space="preserve">25.8207931518555</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">24.760986328125</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6646404266357</t>
+    <t xml:space="preserve">24.6646385192871</t>
   </si>
   <si>
     <t xml:space="preserve">25.0981960296631</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">26.4470443725586</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9171409606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8689670562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4835815429688</t>
+    <t xml:space="preserve">25.9171390533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8689651489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4835834503174</t>
   </si>
   <si>
     <t xml:space="preserve">25.7244491577148</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">26.0616588592529</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9653148651123</t>
+    <t xml:space="preserve">25.9653129577637</t>
   </si>
   <si>
     <t xml:space="preserve">26.1580047607422</t>
@@ -2885,19 +2885,19 @@
     <t xml:space="preserve">25.0500240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">24.47194480896</t>
+    <t xml:space="preserve">24.4719467163086</t>
   </si>
   <si>
     <t xml:space="preserve">22.9785804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7858867645264</t>
+    <t xml:space="preserve">22.7858848571777</t>
   </si>
   <si>
     <t xml:space="preserve">23.6530017852783</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0267524719238</t>
+    <t xml:space="preserve">23.0267505645752</t>
   </si>
   <si>
     <t xml:space="preserve">22.9304046630859</t>
@@ -2906,16 +2906,16 @@
     <t xml:space="preserve">23.2194442749023</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4121360778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.448673248291</t>
+    <t xml:space="preserve">23.4121379852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4486751556396</t>
   </si>
   <si>
     <t xml:space="preserve">21.9669437408447</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8224239349365</t>
+    <t xml:space="preserve">21.8224258422852</t>
   </si>
   <si>
     <t xml:space="preserve">21.5815582275391</t>
@@ -2924,25 +2924,25 @@
     <t xml:space="preserve">22.6413669586182</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8340625762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.49684715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1114635467529</t>
+    <t xml:space="preserve">22.8340606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4968490600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1114654541016</t>
   </si>
   <si>
     <t xml:space="preserve">23.1712703704834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1596355438232</t>
+    <t xml:space="preserve">22.1596374511719</t>
   </si>
   <si>
     <t xml:space="preserve">22.063289642334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3888664245605</t>
+    <t xml:space="preserve">21.3888683319092</t>
   </si>
   <si>
     <t xml:space="preserve">21.1480007171631</t>
@@ -2957,19 +2957,19 @@
     <t xml:space="preserve">20.1845397949219</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9436740875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9609432220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1536331176758</t>
+    <t xml:space="preserve">19.9436721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9609413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1536312103271</t>
   </si>
   <si>
     <t xml:space="preserve">18.1323623657227</t>
   </si>
   <si>
-    <t xml:space="preserve">16.899133682251</t>
+    <t xml:space="preserve">16.8991317749023</t>
   </si>
   <si>
     <t xml:space="preserve">16.9569396972656</t>
@@ -2996,10 +2996,10 @@
     <t xml:space="preserve">18.6719017028809</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2672462463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3250579833984</t>
+    <t xml:space="preserve">18.2672481536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3250560760498</t>
   </si>
   <si>
     <t xml:space="preserve">18.6911716461182</t>
@@ -3026,10 +3026,10 @@
     <t xml:space="preserve">19.2114410400391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6333618164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7662506103516</t>
+    <t xml:space="preserve">18.6333637237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7662487030029</t>
   </si>
   <si>
     <t xml:space="preserve">18.6526336669922</t>
@@ -3041,13 +3041,13 @@
     <t xml:space="preserve">18.7297115325928</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4137687683105</t>
+    <t xml:space="preserve">19.4137706756592</t>
   </si>
   <si>
     <t xml:space="preserve">19.7509803771973</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1343631744385</t>
+    <t xml:space="preserve">19.1343650817871</t>
   </si>
   <si>
     <t xml:space="preserve">18.7489795684814</t>
@@ -3056,13 +3056,13 @@
     <t xml:space="preserve">18.9224014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3655948638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2692489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5350189208984</t>
+    <t xml:space="preserve">19.3655967712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.269250869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5350170135498</t>
   </si>
   <si>
     <t xml:space="preserve">17.7277088165283</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">21.0034809112549</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7144432067871</t>
+    <t xml:space="preserve">20.7144412994385</t>
   </si>
   <si>
     <t xml:space="preserve">21.0516548156738</t>
@@ -3095,10 +3095,10 @@
     <t xml:space="preserve">21.8705978393555</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4005012512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1231002807617</t>
+    <t xml:space="preserve">22.4005031585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1230983734131</t>
   </si>
   <si>
     <t xml:space="preserve">23.3157920837402</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">22.5450229644775</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2078075408936</t>
+    <t xml:space="preserve">22.2078094482422</t>
   </si>
   <si>
     <t xml:space="preserve">20.4254035949707</t>
@@ -3116,19 +3116,19 @@
     <t xml:space="preserve">20.8107891082764</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8955001831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2327117919922</t>
+    <t xml:space="preserve">19.8954982757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2327098846436</t>
   </si>
   <si>
     <t xml:space="preserve">20.4735774993896</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8473262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2499809265137</t>
+    <t xml:space="preserve">19.8473243713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.249979019165</t>
   </si>
   <si>
     <t xml:space="preserve">18.7875175476074</t>
@@ -3137,16 +3137,16 @@
     <t xml:space="preserve">18.5948257446289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5735530853271</t>
+    <t xml:space="preserve">17.5735549926758</t>
   </si>
   <si>
     <t xml:space="preserve">18.8067874908447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.498477935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2287101745605</t>
+    <t xml:space="preserve">18.4984798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2287082672119</t>
   </si>
   <si>
     <t xml:space="preserve">18.0745544433594</t>
@@ -3164,10 +3164,10 @@
     <t xml:space="preserve">18.5370178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4406700134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2865161895752</t>
+    <t xml:space="preserve">18.4406719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2865180969238</t>
   </si>
   <si>
     <t xml:space="preserve">17.9782104492188</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">18.5755558013916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3174209594727</t>
+    <t xml:space="preserve">19.3174228668213</t>
   </si>
   <si>
     <t xml:space="preserve">18.8453235626221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9802112579346</t>
+    <t xml:space="preserve">18.9802131652832</t>
   </si>
   <si>
     <t xml:space="preserve">19.4619426727295</t>
@@ -3191,16 +3191,16 @@
     <t xml:space="preserve">18.1709022521973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7084369659424</t>
+    <t xml:space="preserve">17.708438873291</t>
   </si>
   <si>
     <t xml:space="preserve">17.9204006195068</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6313629150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2094383239746</t>
+    <t xml:space="preserve">17.6313610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2094402313232</t>
   </si>
   <si>
     <t xml:space="preserve">18.2479801177979</t>
@@ -3221,13 +3221,13 @@
     <t xml:space="preserve">16.4559383392334</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2054386138916</t>
+    <t xml:space="preserve">16.205436706543</t>
   </si>
   <si>
     <t xml:space="preserve">16.0512847900391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2247085571289</t>
+    <t xml:space="preserve">16.2247066497803</t>
   </si>
   <si>
     <t xml:space="preserve">15.4153995513916</t>
@@ -3236,22 +3236,22 @@
     <t xml:space="preserve">15.5502834320068</t>
   </si>
   <si>
-    <t xml:space="preserve">15.357590675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7257080078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.128360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7642478942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.879861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1110935211182</t>
+    <t xml:space="preserve">15.3575897216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7257099151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1283588409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7642459869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8798637390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1110954284668</t>
   </si>
   <si>
     <t xml:space="preserve">17.4386692047119</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">17.1689014434814</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1303634643555</t>
+    <t xml:space="preserve">17.1303615570068</t>
   </si>
   <si>
     <t xml:space="preserve">17.9589405059814</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">20.1363639831543</t>
   </si>
   <si>
-    <t xml:space="preserve">19.702808380127</t>
+    <t xml:space="preserve">19.7028064727783</t>
   </si>
   <si>
     <t xml:space="preserve">20.5699234008789</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">20.3290576934814</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7626171112061</t>
+    <t xml:space="preserve">20.7626152038574</t>
   </si>
   <si>
     <t xml:space="preserve">20.8589611053467</t>
@@ -4569,6 +4569,9 @@
   </si>
   <si>
     <t xml:space="preserve">49.2000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49</t>
   </si>
 </sst>
 </file>
@@ -20863,7 +20866,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G614" t="s">
-        <v>341</v>
+        <v>422</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -20941,7 +20944,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G617" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -20967,7 +20970,7 @@
         <v>20.5</v>
       </c>
       <c r="G618" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -20993,7 +20996,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G619" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21019,7 +21022,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G620" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21045,7 +21048,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G621" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21071,7 +21074,7 @@
         <v>21</v>
       </c>
       <c r="G622" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21149,7 +21152,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G625" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21201,7 +21204,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G627" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21253,7 +21256,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G629" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21279,7 +21282,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G630" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21331,7 +21334,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G632" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21357,7 +21360,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G633" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21383,7 +21386,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G634" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21435,7 +21438,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G636" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -21461,7 +21464,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G637" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21487,7 +21490,7 @@
         <v>21</v>
       </c>
       <c r="G638" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -21513,7 +21516,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G639" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21565,7 +21568,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G641" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21591,7 +21594,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G642" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -21643,7 +21646,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G644" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -21669,7 +21672,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G645" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -21851,7 +21854,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G652" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -21877,7 +21880,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G653" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -21903,7 +21906,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G654" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -21929,7 +21932,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G655" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -21955,7 +21958,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G656" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -22007,7 +22010,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G658" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22033,7 +22036,7 @@
         <v>21</v>
       </c>
       <c r="G659" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22085,7 +22088,7 @@
         <v>21</v>
       </c>
       <c r="G661" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22111,7 +22114,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G662" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22137,7 +22140,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G663" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22189,7 +22192,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22267,7 +22270,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G668" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22293,7 +22296,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G669" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22319,7 +22322,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G670" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22371,7 +22374,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G672" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22397,7 +22400,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22423,7 +22426,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G674" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -22449,7 +22452,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -22475,7 +22478,7 @@
         <v>20.75</v>
       </c>
       <c r="G676" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -22501,7 +22504,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G677" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -22527,7 +22530,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G678" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -22553,7 +22556,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G679" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -22579,7 +22582,7 @@
         <v>21.25</v>
       </c>
       <c r="G680" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -22605,7 +22608,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G681" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -22631,7 +22634,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G682" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -22657,7 +22660,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G683" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -23125,7 +23128,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G701" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23281,7 +23284,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G707" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -23307,7 +23310,7 @@
         <v>21.5</v>
       </c>
       <c r="G708" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -23333,7 +23336,7 @@
         <v>21.5</v>
       </c>
       <c r="G709" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -23359,7 +23362,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G710" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -23385,7 +23388,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G711" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -23411,7 +23414,7 @@
         <v>21</v>
       </c>
       <c r="G712" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -23437,7 +23440,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G713" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -23463,7 +23466,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G714" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -23489,7 +23492,7 @@
         <v>21</v>
       </c>
       <c r="G715" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -23515,7 +23518,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G716" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -23541,7 +23544,7 @@
         <v>20.75</v>
       </c>
       <c r="G717" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -23567,7 +23570,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G718" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -23593,7 +23596,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G719" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -23619,7 +23622,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G720" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -23645,7 +23648,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G721" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -23671,7 +23674,7 @@
         <v>15.5</v>
       </c>
       <c r="G722" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -23697,7 +23700,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G723" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -23723,7 +23726,7 @@
         <v>16.5</v>
       </c>
       <c r="G724" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -23749,7 +23752,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G725" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -23775,7 +23778,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G726" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -23801,7 +23804,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G727" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -23827,7 +23830,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G728" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -23853,7 +23856,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G729" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -23879,7 +23882,7 @@
         <v>17</v>
       </c>
       <c r="G730" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -23905,7 +23908,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G731" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -23931,7 +23934,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G732" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -23957,7 +23960,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G733" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -23983,7 +23986,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G734" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -24009,7 +24012,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G735" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -24035,7 +24038,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G736" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -24061,7 +24064,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G737" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -24087,7 +24090,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G738" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -24113,7 +24116,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G739" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24139,7 +24142,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G740" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24165,7 +24168,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G741" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24191,7 +24194,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G742" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24217,7 +24220,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G743" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24243,7 +24246,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G744" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -24269,7 +24272,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G745" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -24295,7 +24298,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G746" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -24321,7 +24324,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G747" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -24347,7 +24350,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G748" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -24373,7 +24376,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G749" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -24399,7 +24402,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G750" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -24425,7 +24428,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G751" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -24451,7 +24454,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G752" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -24477,7 +24480,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G753" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -24503,7 +24506,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G754" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -24529,7 +24532,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G755" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -24555,7 +24558,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G756" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -24581,7 +24584,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G757" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -24607,7 +24610,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G758" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -24633,7 +24636,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G759" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -24659,7 +24662,7 @@
         <v>14.5</v>
       </c>
       <c r="G760" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -24685,7 +24688,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G761" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -24711,7 +24714,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G762" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -24737,7 +24740,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G763" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -24763,7 +24766,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G764" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -24789,7 +24792,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G765" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -24815,7 +24818,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G766" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -24841,7 +24844,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G767" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -24867,7 +24870,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G768" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -24893,7 +24896,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G769" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -24919,7 +24922,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G770" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -24945,7 +24948,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G771" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -24971,7 +24974,7 @@
         <v>16</v>
       </c>
       <c r="G772" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -24997,7 +25000,7 @@
         <v>16</v>
       </c>
       <c r="G773" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25023,7 +25026,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G774" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -25049,7 +25052,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G775" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25075,7 +25078,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G776" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -25101,7 +25104,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G777" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25127,7 +25130,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G778" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25153,7 +25156,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G779" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25179,7 +25182,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G780" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25205,7 +25208,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G781" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25231,7 +25234,7 @@
         <v>17</v>
       </c>
       <c r="G782" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -25257,7 +25260,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G783" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -25283,7 +25286,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G784" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25309,7 +25312,7 @@
         <v>18</v>
       </c>
       <c r="G785" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -25335,7 +25338,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G786" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25361,7 +25364,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G787" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -25387,7 +25390,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G788" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -25413,7 +25416,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G789" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25439,7 +25442,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G790" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -25465,7 +25468,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25491,7 +25494,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G792" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -25517,7 +25520,7 @@
         <v>17</v>
       </c>
       <c r="G793" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -25543,7 +25546,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G794" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -25569,7 +25572,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G795" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -25595,7 +25598,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G796" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -25621,7 +25624,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -25647,7 +25650,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G798" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -25673,7 +25676,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G799" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -25699,7 +25702,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -25725,7 +25728,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G801" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -25751,7 +25754,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G802" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -25777,7 +25780,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G803" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -25803,7 +25806,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G804" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -25829,7 +25832,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -25855,7 +25858,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G806" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -25881,7 +25884,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G807" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -25907,7 +25910,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G808" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -25933,7 +25936,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G809" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -25959,7 +25962,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G810" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -25985,7 +25988,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G811" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26011,7 +26014,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G812" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26037,7 +26040,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G813" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26063,7 +26066,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G814" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26089,7 +26092,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G815" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -26115,7 +26118,7 @@
         <v>17</v>
       </c>
       <c r="G816" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -26141,7 +26144,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G817" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -26167,7 +26170,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G818" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26193,7 +26196,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G819" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26219,7 +26222,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G820" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -26245,7 +26248,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G821" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -26271,7 +26274,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G822" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -26297,7 +26300,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G823" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26323,7 +26326,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26349,7 +26352,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G825" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -26375,7 +26378,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G826" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26401,7 +26404,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G827" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -26427,7 +26430,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G828" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -26453,7 +26456,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G829" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -26479,7 +26482,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G830" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -26505,7 +26508,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G831" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -26531,7 +26534,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G832" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -26557,7 +26560,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G833" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -26583,7 +26586,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G834" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -26609,7 +26612,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G835" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -26635,7 +26638,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G836" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -26661,7 +26664,7 @@
         <v>18</v>
       </c>
       <c r="G837" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -26687,7 +26690,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G838" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -26713,7 +26716,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G839" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -26739,7 +26742,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G840" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -26765,7 +26768,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G841" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -26791,7 +26794,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G842" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -26817,7 +26820,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G843" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -26843,7 +26846,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G844" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -26869,7 +26872,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G845" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -26895,7 +26898,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G846" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -26921,7 +26924,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G847" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -26947,7 +26950,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G848" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -26973,7 +26976,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G849" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -26999,7 +27002,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G850" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27025,7 +27028,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G851" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27051,7 +27054,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G852" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -27077,7 +27080,7 @@
         <v>17</v>
       </c>
       <c r="G853" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27103,7 +27106,7 @@
         <v>16.5</v>
       </c>
       <c r="G854" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -27129,7 +27132,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G855" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -27155,7 +27158,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G856" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -27181,7 +27184,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G857" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -27207,7 +27210,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G858" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -27233,7 +27236,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G859" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -27259,7 +27262,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G860" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -27285,7 +27288,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G861" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -27311,7 +27314,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G862" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -27337,7 +27340,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G863" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -27363,7 +27366,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G864" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -27389,7 +27392,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G865" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -27415,7 +27418,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G866" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -27441,7 +27444,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G867" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -27467,7 +27470,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G868" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -27493,7 +27496,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G869" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -27519,7 +27522,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G870" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -27545,7 +27548,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G871" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -27571,7 +27574,7 @@
         <v>15.5</v>
       </c>
       <c r="G872" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -27597,7 +27600,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G873" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -27623,7 +27626,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G874" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -27649,7 +27652,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G875" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -27675,7 +27678,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G876" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -27701,7 +27704,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G877" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -27727,7 +27730,7 @@
         <v>16.5</v>
       </c>
       <c r="G878" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -27753,7 +27756,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G879" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -27779,7 +27782,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G880" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -27805,7 +27808,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G881" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -27831,7 +27834,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G882" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -27857,7 +27860,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G883" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -27883,7 +27886,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G884" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -27909,7 +27912,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G885" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -27935,7 +27938,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G886" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -27961,7 +27964,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G887" t="s">
-        <v>572</v>
+        <v>463</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -27987,7 +27990,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G888" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -28039,7 +28042,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G890" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -28065,7 +28068,7 @@
         <v>16.5</v>
       </c>
       <c r="G891" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -28091,7 +28094,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G892" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -28195,7 +28198,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G896" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -28221,7 +28224,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G897" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -28247,7 +28250,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G898" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -28273,7 +28276,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G899" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -28351,7 +28354,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G902" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -28403,7 +28406,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G904" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -28429,7 +28432,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -28455,7 +28458,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G906" t="s">
-        <v>572</v>
+        <v>463</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -28481,7 +28484,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G907" t="s">
-        <v>572</v>
+        <v>463</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -28507,7 +28510,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -28559,7 +28562,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G910" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -28585,7 +28588,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G911" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -28637,7 +28640,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G913" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -28663,7 +28666,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G914" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -28715,7 +28718,7 @@
         <v>15.5</v>
       </c>
       <c r="G916" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -28741,7 +28744,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G917" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -28949,7 +28952,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G925" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -29001,7 +29004,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G927" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -29053,7 +29056,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G929" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -29235,7 +29238,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G936" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -29261,7 +29264,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G937" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -29287,7 +29290,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G938" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -29313,7 +29316,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G939" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -29339,7 +29342,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G940" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -29365,7 +29368,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G941" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -29391,7 +29394,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G942" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -29417,7 +29420,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G943" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -29443,7 +29446,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G944" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -29495,7 +29498,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G946" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -29521,7 +29524,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G947" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -29547,7 +29550,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G948" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -29573,7 +29576,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G949" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -29677,7 +29680,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G953" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -29703,7 +29706,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G954" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -29807,7 +29810,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G958" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -29937,7 +29940,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G963" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -30015,7 +30018,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G966" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -30067,7 +30070,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G968" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -30093,7 +30096,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G969" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -30119,7 +30122,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G970" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -30145,7 +30148,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G971" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -30171,7 +30174,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G972" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -30197,7 +30200,7 @@
         <v>16</v>
       </c>
       <c r="G973" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -30301,7 +30304,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G977" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -30327,7 +30330,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -30405,7 +30408,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G981" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -30431,7 +30434,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G982" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -30457,7 +30460,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G983" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -30509,7 +30512,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G985" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -30535,7 +30538,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G986" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -30561,7 +30564,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G987" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -69595,7 +69598,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6495138889</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>83956</v>
@@ -69616,6 +69619,32 @@
         <v>1518</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6495023148</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>68472</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>50.4000015258789</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>49</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="1520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="1521">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6962604522705</t>
+    <t xml:space="preserve">15.6962623596191</t>
   </si>
   <si>
     <t xml:space="preserve">DAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8255271911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3269386291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6344556808472</t>
+    <t xml:space="preserve">15.8255233764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3269376754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6344566345215</t>
   </si>
   <si>
     <t xml:space="preserve">14.311297416687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0343036651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3851613998413</t>
+    <t xml:space="preserve">14.0343027114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.385160446167</t>
   </si>
   <si>
     <t xml:space="preserve">14.1358690261841</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">13.9604387283325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1940937042236</t>
+    <t xml:space="preserve">13.194091796875</t>
   </si>
   <si>
     <t xml:space="preserve">12.8801670074463</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">12.3723468780518</t>
   </si>
   <si>
-    <t xml:space="preserve">13.037130355835</t>
+    <t xml:space="preserve">13.0371294021606</t>
   </si>
   <si>
     <t xml:space="preserve">13.221791267395</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">16.434907913208</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1948471069336</t>
+    <t xml:space="preserve">16.1948509216309</t>
   </si>
   <si>
     <t xml:space="preserve">16.4718399047852</t>
@@ -104,16 +104,16 @@
     <t xml:space="preserve">17.2289543151855</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7119026184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5762329101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2133178710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4100360870361</t>
+    <t xml:space="preserve">16.7119045257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5762300491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2133140563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4100341796875</t>
   </si>
   <si>
     <t xml:space="preserve">15.0407123565674</t>
@@ -122,40 +122,40 @@
     <t xml:space="preserve">15.0499439239502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.456202507019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2069063186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1053457260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0194187164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3425807952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.878101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0350608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1735553741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0812282562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.822696685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4626064300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4533767700195</t>
+    <t xml:space="preserve">15.4561986923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2069044113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1053438186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0194206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3425769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8780975341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0350589752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1735534667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.081226348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8226985931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.462610244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4533748626709</t>
   </si>
   <si>
     <t xml:space="preserve">16.9427299499512</t>
@@ -164,82 +164,82 @@
     <t xml:space="preserve">16.7488346099854</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2935886383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4228477478027</t>
+    <t xml:space="preserve">17.2935848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4228515625</t>
   </si>
   <si>
     <t xml:space="preserve">17.4874801635742</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5521125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6472721099854</t>
+    <t xml:space="preserve">17.5521144866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6472702026367</t>
   </si>
   <si>
     <t xml:space="preserve">17.3397541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6352100372314</t>
+    <t xml:space="preserve">17.6352138519287</t>
   </si>
   <si>
     <t xml:space="preserve">16.9888935089111</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3766841888428</t>
+    <t xml:space="preserve">17.3766860961914</t>
   </si>
   <si>
     <t xml:space="preserve">17.5798149108887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1273899078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3241119384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6657371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0535278320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4043827056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6842021942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6380367279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.238187789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.68137550354</t>
+    <t xml:space="preserve">17.1273918151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3241100311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6657333374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0535259246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4043865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6842002868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6380386352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2381858825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6813774108887</t>
   </si>
   <si>
     <t xml:space="preserve">17.755241394043</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9860668182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2353649139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1430263519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.912202835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7183094024658</t>
+    <t xml:space="preserve">17.5244121551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9860649108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2353630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1430282592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9122009277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7183113098145</t>
   </si>
   <si>
     <t xml:space="preserve">18.4661903381348</t>
@@ -248,10 +248,10 @@
     <t xml:space="preserve">18.5308208465576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.558521270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2168941497803</t>
+    <t xml:space="preserve">18.5585174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2168960571289</t>
   </si>
   <si>
     <t xml:space="preserve">18.4477233886719</t>
@@ -260,97 +260,97 @@
     <t xml:space="preserve">18.1522636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0137672424316</t>
+    <t xml:space="preserve">18.0137691497803</t>
   </si>
   <si>
     <t xml:space="preserve">17.5890445709229</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2658882141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6075115203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2843551635742</t>
+    <t xml:space="preserve">17.26589012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6075134277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2843532562256</t>
   </si>
   <si>
     <t xml:space="preserve">17.192024230957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8873271942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9519634246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6749668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4256763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2594776153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3610401153564</t>
+    <t xml:space="preserve">16.8873329162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.951961517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6749706268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4256801605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2594795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3610458374023</t>
   </si>
   <si>
     <t xml:space="preserve">16.8596305847168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.564172744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5272426605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2779445648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4782485961914</t>
+    <t xml:space="preserve">16.5641746520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5272388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.277946472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.47825050354</t>
   </si>
   <si>
     <t xml:space="preserve">16.6288051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6103363037109</t>
+    <t xml:space="preserve">16.6103401184082</t>
   </si>
   <si>
     <t xml:space="preserve">17.3582172393799</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1089248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1550941467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.917854309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9547863006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.059178352356</t>
+    <t xml:space="preserve">17.108922958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1550903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9178552627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9547872543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0591773986816</t>
   </si>
   <si>
     <t xml:space="preserve">14.8652830123901</t>
   </si>
   <si>
-    <t xml:space="preserve">15.169976234436</t>
+    <t xml:space="preserve">15.1699724197388</t>
   </si>
   <si>
     <t xml:space="preserve">15.4377317428589</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0655822753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.086874961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5513572692871</t>
+    <t xml:space="preserve">16.0655841827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0868787765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5513563156128</t>
   </si>
   <si>
     <t xml:space="preserve">14.985312461853</t>
@@ -359,13 +359,13 @@
     <t xml:space="preserve">14.6252212524414</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7821855545044</t>
+    <t xml:space="preserve">14.7821836471558</t>
   </si>
   <si>
     <t xml:space="preserve">15.5115985870361</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1330404281616</t>
+    <t xml:space="preserve">15.1330394744873</t>
   </si>
   <si>
     <t xml:space="preserve">14.7267866134644</t>
@@ -374,70 +374,70 @@
     <t xml:space="preserve">14.0989360809326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3574619293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7544860839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5023679733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4192686080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.603928565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3546342849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4285020828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4008026123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4839000701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2502479553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7239580154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4931325912476</t>
+    <t xml:space="preserve">14.3574647903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7544851303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5023632049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4192695617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6039295196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3546352386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4284982681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4008007049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4839010238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2502460479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7239599227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4931335449219</t>
   </si>
   <si>
     <t xml:space="preserve">16.2317790985107</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9363241195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1856136322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2871761322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.176383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.093282699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2566547393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9242610931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7211322784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7580642700195</t>
+    <t xml:space="preserve">15.9363231658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1856155395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2871780395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1763801574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0932846069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2566528320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9242649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.721134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7580661773682</t>
   </si>
   <si>
     <t xml:space="preserve">17.7275409698486</t>
@@ -452,37 +452,37 @@
     <t xml:space="preserve">17.3120517730713</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4505481719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2040824890137</t>
+    <t xml:space="preserve">17.4505500793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.204080581665</t>
   </si>
   <si>
     <t xml:space="preserve">15.890154838562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8624582290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9270906448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0563507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7424249649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7701234817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6685600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5946969985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7147264480591</t>
+    <t xml:space="preserve">15.8624572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270877838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0563526153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7424268722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7701282501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6685571670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5946960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7147274017334</t>
   </si>
   <si>
     <t xml:space="preserve">16.1394500732422</t>
@@ -494,76 +494,76 @@
     <t xml:space="preserve">16.1671485900879</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6408653259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6500959396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8070592880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4654350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2623052597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3366193771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4109315872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6524562835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7360620498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8939790725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.624587059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0765199661255</t>
+    <t xml:space="preserve">15.6408634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6500940322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8070573806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4654312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2623081207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3366184234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4109344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.652458190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7360591888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8939781188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6245880126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0765180587769</t>
   </si>
   <si>
     <t xml:space="preserve">15.4295139312744</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5224075317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5131168365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1601238250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8661079406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3305740356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.931134223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4945392608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6060085296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3180418014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8846893310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0518932342529</t>
+    <t xml:space="preserve">15.522403717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131177902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1601247787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8661098480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3305759429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9311361312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4945383071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6060094833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.318039894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8846912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0518951416016</t>
   </si>
   <si>
     <t xml:space="preserve">15.8382415771484</t>
@@ -572,13 +572,13 @@
     <t xml:space="preserve">16.5813846588135</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1851921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2595062255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1387424468994</t>
+    <t xml:space="preserve">17.1851902008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2595043182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.138744354248</t>
   </si>
   <si>
     <t xml:space="preserve">17.2223472595215</t>
@@ -587,34 +587,34 @@
     <t xml:space="preserve">17.0272693634033</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9529571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4884929656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0922966003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9065113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1666107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7425441741943</t>
+    <t xml:space="preserve">16.9529552459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4884910583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0922946929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9065093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1666145324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7425479888916</t>
   </si>
   <si>
     <t xml:space="preserve">17.9004650115967</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9376201629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8818836212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4299545288086</t>
+    <t xml:space="preserve">17.9376220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8818855285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.42995262146</t>
   </si>
   <si>
     <t xml:space="preserve">18.9037075042725</t>
@@ -623,49 +623,49 @@
     <t xml:space="preserve">18.9501552581787</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5539569854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6282730102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1173629760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9129962921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4610652923584</t>
+    <t xml:space="preserve">19.5539588928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6282711029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1173610687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9130001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.461067199707</t>
   </si>
   <si>
     <t xml:space="preserve">19.3310165405273</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1823863983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0802059173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8572635650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0151786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9408664703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9315776824951</t>
+    <t xml:space="preserve">19.1823883056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.080207824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8572597503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0151767730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9408645629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9315738677979</t>
   </si>
   <si>
     <t xml:space="preserve">18.7550811767578</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5785827636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4020862579346</t>
+    <t xml:space="preserve">18.5785846710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4020843505859</t>
   </si>
   <si>
     <t xml:space="preserve">18.1141166687012</t>
@@ -674,85 +674,85 @@
     <t xml:space="preserve">18.4578227996826</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5321369171143</t>
+    <t xml:space="preserve">18.5321350097656</t>
   </si>
   <si>
     <t xml:space="preserve">18.4671096801758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3742179870605</t>
+    <t xml:space="preserve">18.3742198944092</t>
   </si>
   <si>
     <t xml:space="preserve">18.485689163208</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2813262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3277702331543</t>
+    <t xml:space="preserve">18.2813243865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3277721405029</t>
   </si>
   <si>
     <t xml:space="preserve">18.513557434082</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6157398223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6250305175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7272109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0430488586426</t>
+    <t xml:space="preserve">18.6157379150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6250324249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7272129058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0430469512939</t>
   </si>
   <si>
     <t xml:space="preserve">19.4146194458008</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0894927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1266498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3681735992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4517765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9594440460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2474098205566</t>
+    <t xml:space="preserve">19.0894908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1266536712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3681755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4517784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9594459533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2474136352539</t>
   </si>
   <si>
     <t xml:space="preserve">19.5075130462646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0987815856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2195453643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3495960235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0337581634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2288360595703</t>
+    <t xml:space="preserve">19.0987854003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2195415496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3495941162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0337600708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.228832244873</t>
   </si>
   <si>
     <t xml:space="preserve">19.3867530822754</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2845687866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9162425994873</t>
+    <t xml:space="preserve">19.2845706939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9162406921387</t>
   </si>
   <si>
     <t xml:space="preserve">20.0091361999512</t>
@@ -761,22 +761,22 @@
     <t xml:space="preserve">20.3807048797607</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6222267150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8544635772705</t>
+    <t xml:space="preserve">20.6222305297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8544578552246</t>
   </si>
   <si>
     <t xml:space="preserve">20.9659309387207</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9473533630371</t>
+    <t xml:space="preserve">20.9473495483398</t>
   </si>
   <si>
     <t xml:space="preserve">20.148473739624</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6129360198975</t>
+    <t xml:space="preserve">20.6129379272461</t>
   </si>
   <si>
     <t xml:space="preserve">20.3899955749512</t>
@@ -785,13 +785,13 @@
     <t xml:space="preserve">20.2506542205811</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5757789611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6500968933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6036472320557</t>
+    <t xml:space="preserve">20.5757808685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6500930786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.603645324707</t>
   </si>
   <si>
     <t xml:space="preserve">20.5014667510986</t>
@@ -803,73 +803,73 @@
     <t xml:space="preserve">20.6593837738037</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4828853607178</t>
+    <t xml:space="preserve">20.482889175415</t>
   </si>
   <si>
     <t xml:space="preserve">20.8173027038574</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8637466430664</t>
+    <t xml:space="preserve">20.863748550415</t>
   </si>
   <si>
     <t xml:space="preserve">20.455020904541</t>
   </si>
   <si>
-    <t xml:space="preserve">20.780143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6440486907959</t>
+    <t xml:space="preserve">20.7801475524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6440505981445</t>
   </si>
   <si>
     <t xml:space="preserve">21.4954204559326</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3653678894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3189239501953</t>
+    <t xml:space="preserve">21.3653736114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3189258575439</t>
   </si>
   <si>
     <t xml:space="preserve">21.1331386566162</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1238498687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9287757873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2724781036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1052722930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3467922210693</t>
+    <t xml:space="preserve">21.1238479614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9287719726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2724761962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1052703857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3467903137207</t>
   </si>
   <si>
     <t xml:space="preserve">21.2260303497314</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6408081054688</t>
+    <t xml:space="preserve">20.6408042907715</t>
   </si>
   <si>
     <t xml:space="preserve">21.170295715332</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9566402435303</t>
+    <t xml:space="preserve">20.9566421508789</t>
   </si>
   <si>
     <t xml:space="preserve">21.114559173584</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2538967132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.244607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3375034332275</t>
+    <t xml:space="preserve">21.2538986206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2446117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3375053405762</t>
   </si>
   <si>
     <t xml:space="preserve">21.2817668914795</t>
@@ -878,31 +878,31 @@
     <t xml:space="preserve">20.9380645751953</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1795864105225</t>
+    <t xml:space="preserve">21.1795845031738</t>
   </si>
   <si>
     <t xml:space="preserve">20.733699798584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3156833648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.399284362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4085712432861</t>
+    <t xml:space="preserve">20.3156814575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3992824554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4085750579834</t>
   </si>
   <si>
     <t xml:space="preserve">20.3249683380127</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6315174102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2785224914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0462894439697</t>
+    <t xml:space="preserve">20.6315155029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2785243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0462875366211</t>
   </si>
   <si>
     <t xml:space="preserve">20.2134990692139</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">19.9069519042969</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2692356109619</t>
+    <t xml:space="preserve">20.2692337036133</t>
   </si>
   <si>
     <t xml:space="preserve">20.2971019744873</t>
@@ -926,25 +926,25 @@
     <t xml:space="preserve">20.4364433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9533958435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8326358795166</t>
+    <t xml:space="preserve">19.9533996582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8326377868652</t>
   </si>
   <si>
     <t xml:space="preserve">19.8883724212646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7211666107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9255332946777</t>
+    <t xml:space="preserve">19.7211647033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9255313873291</t>
   </si>
   <si>
     <t xml:space="preserve">20.0741596221924</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9998455047607</t>
+    <t xml:space="preserve">19.9998435974121</t>
   </si>
   <si>
     <t xml:space="preserve">20.1113166809082</t>
@@ -956,34 +956,34 @@
     <t xml:space="preserve">20.6686744689941</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2413673400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9719772338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7304534912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4178619384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1298942565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4921760559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8451709747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3435497283936</t>
+    <t xml:space="preserve">20.2413654327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9719734191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7304553985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4178638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1298961639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4921779632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8451690673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3435478210449</t>
   </si>
   <si>
     <t xml:space="preserve">20.5664920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8916149139404</t>
+    <t xml:space="preserve">20.8916168212891</t>
   </si>
   <si>
     <t xml:space="preserve">21.1981620788574</t>
@@ -992,19 +992,19 @@
     <t xml:space="preserve">20.7244091033936</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4736003875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3342590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3714141845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8790855407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.841926574707</t>
+    <t xml:space="preserve">20.4735984802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3342609405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3714160919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8790836334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8419246673584</t>
   </si>
   <si>
     <t xml:space="preserve">19.7676105499268</t>
@@ -1013,106 +1013,106 @@
     <t xml:space="preserve">19.9812679290771</t>
   </si>
   <si>
-    <t xml:space="preserve">20.092737197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5200462341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9905548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5353775024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2567024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7829456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8386840820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6343193054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9966011047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6807651519775</t>
+    <t xml:space="preserve">20.0927352905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5200443267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9905567169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5353813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2566986083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7829475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8386821746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6343173980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.996603012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6807670593262</t>
   </si>
   <si>
     <t xml:space="preserve">18.5600032806396</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6621875762939</t>
+    <t xml:space="preserve">18.6621856689453</t>
   </si>
   <si>
     <t xml:space="preserve">18.439245223999</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8108177185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1359424591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9779300689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9499263763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5298538208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.305814743042</t>
+    <t xml:space="preserve">18.8108139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1359405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9779319763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9499282836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5298557281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3058166503906</t>
   </si>
   <si>
     <t xml:space="preserve">17.9044132232666</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8484039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6430358886719</t>
+    <t xml:space="preserve">17.8484058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6430339813232</t>
   </si>
   <si>
     <t xml:space="preserve">17.6710414886475</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9417533874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8950786590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9697570800781</t>
+    <t xml:space="preserve">17.9417514801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.895076751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9697589874268</t>
   </si>
   <si>
     <t xml:space="preserve">18.2684764862061</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4645099639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5858631134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4084987640381</t>
+    <t xml:space="preserve">18.4645080566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5858612060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4084968566895</t>
   </si>
   <si>
     <t xml:space="preserve">18.1657905578613</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4925117492676</t>
+    <t xml:space="preserve">18.4925136566162</t>
   </si>
   <si>
     <t xml:space="preserve">18.3618259429932</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2217979431152</t>
+    <t xml:space="preserve">18.2218017578125</t>
   </si>
   <si>
     <t xml:space="preserve">18.6698760986328</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">18.6978816986084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.688549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6138687133789</t>
+    <t xml:space="preserve">18.6885471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6138706207275</t>
   </si>
   <si>
     <t xml:space="preserve">18.3524894714355</t>
@@ -1136,28 +1136,28 @@
     <t xml:space="preserve">18.3804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4458389282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4831790924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4738445281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6605472564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7072162628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5951995849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3898315429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5018482208252</t>
+    <t xml:space="preserve">18.4458427429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4831771850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4738464355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6605453491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7072200775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5951957702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3898296356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5018501281738</t>
   </si>
   <si>
     <t xml:space="preserve">18.9032516479492</t>
@@ -1169,49 +1169,49 @@
     <t xml:space="preserve">19.4633483886719</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7433967590332</t>
+    <t xml:space="preserve">19.7433948516846</t>
   </si>
   <si>
     <t xml:space="preserve">20.5368671417236</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2836589813232</t>
+    <t xml:space="preserve">21.2836608886719</t>
   </si>
   <si>
     <t xml:space="preserve">21.5637092590332</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5170345306396</t>
+    <t xml:space="preserve">21.517032623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3770122528076</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6103820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4703617095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7504062652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.797082901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0036144256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4435195922852</t>
+    <t xml:space="preserve">21.6103839874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4703578948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7504081726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7970848083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0036125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4435157775879</t>
   </si>
   <si>
     <t xml:space="preserve">21.0502872467041</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6302127838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.77024269104</t>
+    <t xml:space="preserve">20.6302146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7702407836914</t>
   </si>
   <si>
     <t xml:space="preserve">20.7235660552979</t>
@@ -1220,28 +1220,28 @@
     <t xml:space="preserve">21.0969638824463</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1903114318848</t>
+    <t xml:space="preserve">21.1903133392334</t>
   </si>
   <si>
     <t xml:space="preserve">21.1436367034912</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8635883331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6768913269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7037334442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.217155456543</t>
+    <t xml:space="preserve">20.8635902404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.676887512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7037296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2171516418457</t>
   </si>
   <si>
     <t xml:space="preserve">21.8904323577881</t>
   </si>
   <si>
-    <t xml:space="preserve">22.077127456665</t>
+    <t xml:space="preserve">22.0771312713623</t>
   </si>
   <si>
     <t xml:space="preserve">21.9837818145752</t>
@@ -1250,22 +1250,22 @@
     <t xml:space="preserve">20.8169136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">21.236988067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3034934997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2101402282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9102630615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5835380554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.956937789917</t>
+    <t xml:space="preserve">21.2369861602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3034954071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2101421356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9102649688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5835399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9569396972656</t>
   </si>
   <si>
     <t xml:space="preserve">21.3303356170654</t>
@@ -1274,25 +1274,25 @@
     <t xml:space="preserve">20.3968410491943</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4901924133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1167945861816</t>
+    <t xml:space="preserve">20.4901905059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.116792678833</t>
   </si>
   <si>
     <t xml:space="preserve">19.0432758331299</t>
   </si>
   <si>
-    <t xml:space="preserve">19.136625289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3233222961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7900733947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6033706665039</t>
+    <t xml:space="preserve">19.1366271972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3233261108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7900714874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6033725738525</t>
   </si>
   <si>
     <t xml:space="preserve">20.3501663208008</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">19.9767684936523</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1634693145752</t>
+    <t xml:space="preserve">20.1634674072266</t>
   </si>
   <si>
     <t xml:space="preserve">20.0234451293945</t>
@@ -1313,91 +1313,91 @@
     <t xml:space="preserve">19.8834171295166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9300937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4166717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5566959381104</t>
+    <t xml:space="preserve">19.9300956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4166736602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5566997528076</t>
   </si>
   <si>
     <t xml:space="preserve">19.5100231170654</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6500434875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.696720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.276647567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2299709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3699989318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8367481231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4236850738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0701217651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7177124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3092985153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7013664245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7678737640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4691553115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.805212020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4026489257812</t>
+    <t xml:space="preserve">19.6500453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6967182159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2766494750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2299766540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3699970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8367462158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4236869812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0701179504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7177143096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3092994689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7013673782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7678747177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4691543579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8052129745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4026498794556</t>
   </si>
   <si>
     <t xml:space="preserve">15.62668800354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0000839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333395004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3279705047607</t>
+    <t xml:space="preserve">16.0000877380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333375930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3279695510864</t>
   </si>
   <si>
     <t xml:space="preserve">15.4586572647095</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8693962097168</t>
+    <t xml:space="preserve">15.8693990707397</t>
   </si>
   <si>
     <t xml:space="preserve">15.794716835022</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6640272140503</t>
+    <t xml:space="preserve">15.6640281677246</t>
   </si>
   <si>
     <t xml:space="preserve">15.5893497467041</t>
   </si>
   <si>
-    <t xml:space="preserve">15.383978843689</t>
+    <t xml:space="preserve">15.3839797973633</t>
   </si>
   <si>
     <t xml:space="preserve">15.0105819702148</t>
@@ -1406,13 +1406,13 @@
     <t xml:space="preserve">14.8602886199951</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5784893035889</t>
+    <t xml:space="preserve">14.5784873962402</t>
   </si>
   <si>
     <t xml:space="preserve">14.4094085693359</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4469804763794</t>
+    <t xml:space="preserve">14.4469795227051</t>
   </si>
   <si>
     <t xml:space="preserve">14.9166479110718</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">14.9354343414307</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6536359786987</t>
+    <t xml:space="preserve">14.6536350250244</t>
   </si>
   <si>
     <t xml:space="preserve">15.1420888900757</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">15.4426774978638</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2735958099365</t>
+    <t xml:space="preserve">15.2735977172852</t>
   </si>
   <si>
     <t xml:space="preserve">14.0712461471558</t>
@@ -1439,58 +1439,58 @@
     <t xml:space="preserve">13.920952796936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6015777587891</t>
+    <t xml:space="preserve">13.6015787124634</t>
   </si>
   <si>
     <t xml:space="preserve">13.7330856323242</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3342599868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1651811599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1463937759399</t>
+    <t xml:space="preserve">14.3342609405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1651802062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1463928222656</t>
   </si>
   <si>
     <t xml:space="preserve">14.2215414047241</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9585247039795</t>
+    <t xml:space="preserve">13.9585256576538</t>
   </si>
   <si>
     <t xml:space="preserve">13.6391525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6203641891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7894468307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0524597167969</t>
+    <t xml:space="preserve">13.6203660964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7894458770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0524587631226</t>
   </si>
   <si>
     <t xml:space="preserve">14.2027530670166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5221281051636</t>
+    <t xml:space="preserve">14.5221261978149</t>
   </si>
   <si>
     <t xml:space="preserve">14.7475671768188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2172365188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1233015060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0293684005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0669441223145</t>
+    <t xml:space="preserve">15.2172355651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1233024597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.029369354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0669431686401</t>
   </si>
   <si>
     <t xml:space="preserve">14.8978605270386</t>
@@ -1511,31 +1511,31 @@
     <t xml:space="preserve">15.9687042236328</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8141059875488</t>
+    <t xml:space="preserve">16.8141078948975</t>
   </si>
   <si>
     <t xml:space="preserve">16.8892517089844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9080371856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4947299957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.419584274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2692909240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3632278442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.987491607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8747730255127</t>
+    <t xml:space="preserve">16.9080390930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4947319030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4195861816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2692928314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3632259368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9874925613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8747720718384</t>
   </si>
   <si>
     <t xml:space="preserve">15.8184108734131</t>
@@ -1544,34 +1544,34 @@
     <t xml:space="preserve">16.1377849578857</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1565742492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2505035400391</t>
+    <t xml:space="preserve">16.1565704345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2505054473877</t>
   </si>
   <si>
     <t xml:space="preserve">16.6262397766113</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5135192871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2880764007568</t>
+    <t xml:space="preserve">16.5135173797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2880802154541</t>
   </si>
   <si>
     <t xml:space="preserve">16.4383735656738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4571571350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2317180633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6074542999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7201728820801</t>
+    <t xml:space="preserve">16.4571590423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2317199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6074504852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7201747894287</t>
   </si>
   <si>
     <t xml:space="preserve">16.4759464263916</t>
@@ -1583,13 +1583,13 @@
     <t xml:space="preserve">15.8559846878052</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9499177932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9311275482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1189994812012</t>
+    <t xml:space="preserve">15.9499187469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9311304092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1189956665039</t>
   </si>
   <si>
     <t xml:space="preserve">16.0062789916992</t>
@@ -1604,19 +1604,19 @@
     <t xml:space="preserve">16.5323066711426</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7765331268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.945613861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4716396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.279468536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2606830596924</t>
+    <t xml:space="preserve">16.7765350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9456119537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.471643447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2794704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.260684967041</t>
   </si>
   <si>
     <t xml:space="preserve">18.2418975830078</t>
@@ -1625,52 +1625,52 @@
     <t xml:space="preserve">18.1103916168213</t>
   </si>
   <si>
-    <t xml:space="preserve">17.528003692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1334819793701</t>
+    <t xml:space="preserve">17.5280017852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1334800720215</t>
   </si>
   <si>
     <t xml:space="preserve">17.0019721984863</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9831867218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7389583587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6450252532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9643993377686</t>
+    <t xml:space="preserve">16.9831886291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7389602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6450233459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9644012451172</t>
   </si>
   <si>
     <t xml:space="preserve">16.832893371582</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0583343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1522674560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2274131774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7577457427979</t>
+    <t xml:space="preserve">17.0583324432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1522655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2274150848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7577476501465</t>
   </si>
   <si>
     <t xml:space="preserve">16.2129325866699</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4990358352661</t>
+    <t xml:space="preserve">15.4990367889404</t>
   </si>
   <si>
     <t xml:space="preserve">15.517822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4614639282227</t>
+    <t xml:space="preserve">15.4614629745483</t>
   </si>
   <si>
     <t xml:space="preserve">15.1796617507935</t>
@@ -1682,13 +1682,13 @@
     <t xml:space="preserve">14.8039283752441</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0857286453247</t>
+    <t xml:space="preserve">15.0857276916504</t>
   </si>
   <si>
     <t xml:space="preserve">14.7663555145264</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9730081558228</t>
+    <t xml:space="preserve">14.9730072021484</t>
   </si>
   <si>
     <t xml:space="preserve">14.8415021896362</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">14.3718347549438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.822714805603</t>
+    <t xml:space="preserve">14.8227138519287</t>
   </si>
   <si>
     <t xml:space="preserve">14.5597009658813</t>
@@ -1712,43 +1712,43 @@
     <t xml:space="preserve">14.4657669067383</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6348476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5741834640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.405101776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3863162994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6681203842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2360219955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5929708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4238901138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3299551010132</t>
+    <t xml:space="preserve">14.6348485946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.574182510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4051027297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3863153457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6681156158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2360229492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5929698944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4238882064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3299541473389</t>
   </si>
   <si>
     <t xml:space="preserve">15.0481567382812</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8790760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5409126281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7851409912109</t>
+    <t xml:space="preserve">14.8790769577026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5409145355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7851419448853</t>
   </si>
   <si>
     <t xml:space="preserve">14.6160612106323</t>
@@ -1757,37 +1757,37 @@
     <t xml:space="preserve">14.2966871261597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2779006958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.090033531189</t>
+    <t xml:space="preserve">14.2778987884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0900344848633</t>
   </si>
   <si>
     <t xml:space="preserve">13.9021663665771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.770658493042</t>
+    <t xml:space="preserve">13.7706594467163</t>
   </si>
   <si>
     <t xml:space="preserve">14.4281930923462</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2591133117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8082323074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8458061218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.033673286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9397401809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2403259277344</t>
+    <t xml:space="preserve">14.2591142654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8082313537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8458070755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0336723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9397392272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2403268814087</t>
   </si>
   <si>
     <t xml:space="preserve">14.0148868560791</t>
@@ -1802,19 +1802,19 @@
     <t xml:space="preserve">15.3675298690796</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1839666366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1088190078735</t>
+    <t xml:space="preserve">14.183967590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1088199615479</t>
   </si>
   <si>
     <t xml:space="preserve">14.4845542907715</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9917945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2923851013184</t>
+    <t xml:space="preserve">14.991795539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.292384147644</t>
   </si>
   <si>
     <t xml:space="preserve">15.0758924484253</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">14.8104057312012</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8862590789795</t>
+    <t xml:space="preserve">14.8862581253052</t>
   </si>
   <si>
     <t xml:space="preserve">15.3793067932129</t>
@@ -1850,13 +1850,13 @@
     <t xml:space="preserve">15.6637573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5310144424438</t>
+    <t xml:space="preserve">15.5310134887695</t>
   </si>
   <si>
     <t xml:space="preserve">15.5499773025513</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4551620483398</t>
+    <t xml:space="preserve">15.4551610946655</t>
   </si>
   <si>
     <t xml:space="preserve">15.7585763931274</t>
@@ -1868,10 +1868,10 @@
     <t xml:space="preserve">16.1757698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">15.720648765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6068687438965</t>
+    <t xml:space="preserve">15.7206478118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6068677902222</t>
   </si>
   <si>
     <t xml:space="preserve">15.6447944641113</t>
@@ -1880,19 +1880,19 @@
     <t xml:space="preserve">16.043025970459</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9861354827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4172344207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344297409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5689420700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4362001419067</t>
+    <t xml:space="preserve">15.986138343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.417236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344287872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.568941116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4361991882324</t>
   </si>
   <si>
     <t xml:space="preserve">15.5879058837891</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">14.9810771942139</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2086391448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7535161972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9431495666504</t>
+    <t xml:space="preserve">15.2086381912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7535152435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9431505203247</t>
   </si>
   <si>
     <t xml:space="preserve">14.5069923400879</t>
@@ -1922,13 +1922,13 @@
     <t xml:space="preserve">14.0329074859619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9380903244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2225408554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6018085479736</t>
+    <t xml:space="preserve">13.9380893707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.222541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6018075942993</t>
   </si>
   <si>
     <t xml:space="preserve">14.7914438247681</t>
@@ -1946,40 +1946,40 @@
     <t xml:space="preserve">14.6207723617554</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3363208770752</t>
+    <t xml:space="preserve">14.3363218307495</t>
   </si>
   <si>
     <t xml:space="preserve">14.2794313430786</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0518703460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6915664672852</t>
+    <t xml:space="preserve">14.0518712997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6915645599365</t>
   </si>
   <si>
     <t xml:space="preserve">13.1416273117065</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0088834762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3691892623901</t>
+    <t xml:space="preserve">13.0088844299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3691883087158</t>
   </si>
   <si>
     <t xml:space="preserve">13.0847387313843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8002862930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4210195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1744956970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9469356536865</t>
+    <t xml:space="preserve">12.8002872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4210186004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1744966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9469347000122</t>
   </si>
   <si>
     <t xml:space="preserve">11.4728498458862</t>
@@ -1988,28 +1988,28 @@
     <t xml:space="preserve">11.0366926193237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1264495849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95577812194824</t>
+    <t xml:space="preserve">10.1264486312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95577907562256</t>
   </si>
   <si>
     <t xml:space="preserve">9.59547519683838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91279220581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41532230377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09736728668213</t>
+    <t xml:space="preserve">8.91279315948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41532325744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09736633300781</t>
   </si>
   <si>
     <t xml:space="preserve">8.55248832702637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10242748260498</t>
+    <t xml:space="preserve">9.10242652893066</t>
   </si>
   <si>
     <t xml:space="preserve">10.1643772125244</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">10.7522411346436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9279708862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8951044082642</t>
+    <t xml:space="preserve">11.9279718399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8951034545898</t>
   </si>
   <si>
     <t xml:space="preserve">11.6055936813354</t>
@@ -2030,16 +2030,16 @@
     <t xml:space="preserve">10.9608383178711</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9229125976562</t>
+    <t xml:space="preserve">10.9229116439819</t>
   </si>
   <si>
     <t xml:space="preserve">10.6384611129761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0695600509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3350458145142</t>
+    <t xml:space="preserve">10.06955909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3350467681885</t>
   </si>
   <si>
     <t xml:space="preserve">10.6194972991943</t>
@@ -2051,13 +2051,13 @@
     <t xml:space="preserve">11.1125459671021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9039487838745</t>
+    <t xml:space="preserve">10.9039478302002</t>
   </si>
   <si>
     <t xml:space="preserve">10.5815696716309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2023029327393</t>
+    <t xml:space="preserve">10.2023019790649</t>
   </si>
   <si>
     <t xml:space="preserve">9.87992572784424</t>
@@ -2069,22 +2069,22 @@
     <t xml:space="preserve">10.5057163238525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4298639297485</t>
+    <t xml:space="preserve">10.4298629760742</t>
   </si>
   <si>
     <t xml:space="preserve">10.771203994751</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7143144607544</t>
+    <t xml:space="preserve">10.7143135070801</t>
   </si>
   <si>
     <t xml:space="preserve">10.6953496932983</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8091306686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8280944824219</t>
+    <t xml:space="preserve">10.8091316223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8280954360962</t>
   </si>
   <si>
     <t xml:space="preserve">10.543643951416</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">10.9987649917603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9418745040894</t>
+    <t xml:space="preserve">10.9418754577637</t>
   </si>
   <si>
     <t xml:space="preserve">11.4918127059937</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">11.7952270507812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0038242340088</t>
+    <t xml:space="preserve">12.0038251876831</t>
   </si>
   <si>
     <t xml:space="preserve">12.2882747650146</t>
@@ -2123,22 +2123,22 @@
     <t xml:space="preserve">12.2124223709106</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0986413955688</t>
+    <t xml:space="preserve">12.0986404418945</t>
   </si>
   <si>
     <t xml:space="preserve">11.8521175384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2263259887695</t>
+    <t xml:space="preserve">11.2263269424438</t>
   </si>
   <si>
     <t xml:space="preserve">11.017728805542</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1883993148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.093581199646</t>
+    <t xml:space="preserve">11.1883983612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0935821533203</t>
   </si>
   <si>
     <t xml:space="preserve">10.8849840164185</t>
@@ -2147,19 +2147,19 @@
     <t xml:space="preserve">10.7901678085327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6763877868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4109001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.448826789856</t>
+    <t xml:space="preserve">10.6763868331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4108991622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4488277435303</t>
   </si>
   <si>
     <t xml:space="preserve">10.6574249267578</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2073631286621</t>
+    <t xml:space="preserve">11.2073621749878</t>
   </si>
   <si>
     <t xml:space="preserve">11.3401050567627</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">11.0746183395386</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9798011779785</t>
+    <t xml:space="preserve">10.9798021316528</t>
   </si>
   <si>
     <t xml:space="preserve">10.6005334854126</t>
@@ -2180,22 +2180,22 @@
     <t xml:space="preserve">10.3729734420776</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4677896499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6435203552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4349231719971</t>
+    <t xml:space="preserve">10.4677906036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6435194015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4349241256714</t>
   </si>
   <si>
     <t xml:space="preserve">11.6814470291138</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5297393798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6245565414429</t>
+    <t xml:space="preserve">11.5297403335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6245555877686</t>
   </si>
   <si>
     <t xml:space="preserve">11.5487031936646</t>
@@ -2204,16 +2204,16 @@
     <t xml:space="preserve">11.6624841690063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7383365631104</t>
+    <t xml:space="preserve">11.7383375167847</t>
   </si>
   <si>
     <t xml:space="preserve">12.2313852310181</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1365690231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1176042556763</t>
+    <t xml:space="preserve">12.136568069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.117603302002</t>
   </si>
   <si>
     <t xml:space="preserve">11.9658975601196</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">11.7573003768921</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2452878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6485805511475</t>
+    <t xml:space="preserve">11.245288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6485815048218</t>
   </si>
   <si>
     <t xml:space="preserve">13.6536388397217</t>
@@ -2243,22 +2243,22 @@
     <t xml:space="preserve">13.8622369766235</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5967493057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2364435195923</t>
+    <t xml:space="preserve">13.5967502593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2364444732666</t>
   </si>
   <si>
     <t xml:space="preserve">13.4260787963867</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4640064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1037006378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.331262588501</t>
+    <t xml:space="preserve">13.4640045166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1037015914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3312616348267</t>
   </si>
   <si>
     <t xml:space="preserve">14.1277236938477</t>
@@ -2276,28 +2276,28 @@
     <t xml:space="preserve">13.4829683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.17955493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0227870941162</t>
+    <t xml:space="preserve">13.1795539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0227880477905</t>
   </si>
   <si>
     <t xml:space="preserve">12.0607147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3262014389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4399833679199</t>
+    <t xml:space="preserve">12.3262023925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4399824142456</t>
   </si>
   <si>
     <t xml:space="preserve">12.857177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8192501068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0468101501465</t>
+    <t xml:space="preserve">12.8192510604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0468111038208</t>
   </si>
   <si>
     <t xml:space="preserve">13.3122987747192</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">13.4450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5588226318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6179904937744</t>
+    <t xml:space="preserve">13.5588235855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6179914474487</t>
   </si>
   <si>
     <t xml:space="preserve">13.6371440887451</t>
@@ -2321,19 +2321,19 @@
     <t xml:space="preserve">13.4456119537354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3115386962891</t>
+    <t xml:space="preserve">13.3115377426147</t>
   </si>
   <si>
     <t xml:space="preserve">13.5030717849731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8478307723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8861360549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7520637512207</t>
+    <t xml:space="preserve">13.8478298187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8861379623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7520627975464</t>
   </si>
   <si>
     <t xml:space="preserve">14.1734371185303</t>
@@ -2357,13 +2357,13 @@
     <t xml:space="preserve">13.7712173461914</t>
   </si>
   <si>
-    <t xml:space="preserve">13.598837852478</t>
+    <t xml:space="preserve">13.5988368988037</t>
   </si>
   <si>
     <t xml:space="preserve">13.5413789749146</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7903709411621</t>
+    <t xml:space="preserve">13.7903699874878</t>
   </si>
   <si>
     <t xml:space="preserve">13.7137575149536</t>
@@ -2372,13 +2372,13 @@
     <t xml:space="preserve">13.8669834136963</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1351289749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3458156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7097282409668</t>
+    <t xml:space="preserve">14.1351308822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3458166122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7097272872925</t>
   </si>
   <si>
     <t xml:space="preserve">14.6331148147583</t>
@@ -2387,10 +2387,10 @@
     <t xml:space="preserve">14.9970273971558</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0353345870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4909858703613</t>
+    <t xml:space="preserve">15.0353336334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4909839630127</t>
   </si>
   <si>
     <t xml:space="preserve">16.3377590179443</t>
@@ -2402,16 +2402,16 @@
     <t xml:space="preserve">15.8206195831299</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9546937942505</t>
+    <t xml:space="preserve">15.9546928405762</t>
   </si>
   <si>
     <t xml:space="preserve">15.8014659881592</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6099348068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3226337432861</t>
+    <t xml:space="preserve">15.6099338531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3226346969604</t>
   </si>
   <si>
     <t xml:space="preserve">15.7440071105957</t>
@@ -2423,16 +2423,16 @@
     <t xml:space="preserve">15.4375534057617</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7248544692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8589248657227</t>
+    <t xml:space="preserve">15.7248525619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.858925819397</t>
   </si>
   <si>
     <t xml:space="preserve">16.2611446380615</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6059036254883</t>
+    <t xml:space="preserve">16.6059055328369</t>
   </si>
   <si>
     <t xml:space="preserve">16.778284072876</t>
@@ -2447,25 +2447,25 @@
     <t xml:space="preserve">16.7208251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7016716003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1613483428955</t>
+    <t xml:space="preserve">16.7016735076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1613502502441</t>
   </si>
   <si>
     <t xml:space="preserve">17.1421985626221</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1996555328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9889698028564</t>
+    <t xml:space="preserve">17.1996574401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9889678955078</t>
   </si>
   <si>
     <t xml:space="preserve">16.4526786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4335269927979</t>
+    <t xml:space="preserve">16.4335231781006</t>
   </si>
   <si>
     <t xml:space="preserve">16.9123573303223</t>
@@ -2477,10 +2477,10 @@
     <t xml:space="preserve">16.9506645202637</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9315128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8548965454102</t>
+    <t xml:space="preserve">16.931510925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8548984527588</t>
   </si>
   <si>
     <t xml:space="preserve">17.9657897949219</t>
@@ -2510,13 +2510,13 @@
     <t xml:space="preserve">20.4940223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1109561920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9673080444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8715400695801</t>
+    <t xml:space="preserve">20.1109580993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.967306137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8715419769287</t>
   </si>
   <si>
     <t xml:space="preserve">20.0151920318604</t>
@@ -2525,10 +2525,10 @@
     <t xml:space="preserve">20.3982563018799</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5419063568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.637674331665</t>
+    <t xml:space="preserve">20.5419082641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6376724243164</t>
   </si>
   <si>
     <t xml:space="preserve">20.9728565216064</t>
@@ -2540,25 +2540,25 @@
     <t xml:space="preserve">20.3503742218018</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0630741119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9249725341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7278900146484</t>
+    <t xml:space="preserve">20.0630760192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9249706268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7278919219971</t>
   </si>
   <si>
     <t xml:space="preserve">19.4884757995605</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3448276519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5363597869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.823657989502</t>
+    <t xml:space="preserve">19.3448257446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5363578796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8236598968506</t>
   </si>
   <si>
     <t xml:space="preserve">19.1532917022705</t>
@@ -2585,19 +2585,19 @@
     <t xml:space="preserve">21.7868709564209</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7389869689941</t>
+    <t xml:space="preserve">21.7389888763428</t>
   </si>
   <si>
     <t xml:space="preserve">21.834753036499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5474548339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8826370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9784030914307</t>
+    <t xml:space="preserve">21.5474529266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8826351165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9784049987793</t>
   </si>
   <si>
     <t xml:space="preserve">21.212272644043</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">22.7924175262451</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3191356658936</t>
+    <t xml:space="preserve">23.3191337585449</t>
   </si>
   <si>
     <t xml:space="preserve">22.6487674713135</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">20.8292064666748</t>
   </si>
   <si>
-    <t xml:space="preserve">20.781322479248</t>
+    <t xml:space="preserve">20.7813243865967</t>
   </si>
   <si>
     <t xml:space="preserve">21.9305210113525</t>
@@ -2648,19 +2648,19 @@
     <t xml:space="preserve">23.9416160583496</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4627838134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4148998260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1754837036133</t>
+    <t xml:space="preserve">23.4627819061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4149017333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1754856109619</t>
   </si>
   <si>
     <t xml:space="preserve">23.2712497711182</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5106658935547</t>
+    <t xml:space="preserve">23.5106678009033</t>
   </si>
   <si>
     <t xml:space="preserve">23.22336769104</t>
@@ -2672,28 +2672,28 @@
     <t xml:space="preserve">23.6064319610596</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0797176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7979679107666</t>
+    <t xml:space="preserve">23.0797157287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.797966003418</t>
   </si>
   <si>
     <t xml:space="preserve">23.7021999359131</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6543159484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.031831741333</t>
+    <t xml:space="preserve">23.654317855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0318336486816</t>
   </si>
   <si>
     <t xml:space="preserve">23.5585517883301</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8403034210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.600887298584</t>
+    <t xml:space="preserve">22.8402996063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6008853912354</t>
   </si>
   <si>
     <t xml:space="preserve">22.2657032012939</t>
@@ -2714,10 +2714,10 @@
     <t xml:space="preserve">23.8937339782715</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4683303833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0373821258545</t>
+    <t xml:space="preserve">24.4683322906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0373840332031</t>
   </si>
   <si>
     <t xml:space="preserve">23.8458499908447</t>
@@ -2729,28 +2729,28 @@
     <t xml:space="preserve">25.7611789703369</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1442451477051</t>
+    <t xml:space="preserve">26.1442432403564</t>
   </si>
   <si>
     <t xml:space="preserve">25.8569450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8090648651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9527111053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.665412902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4794254302979</t>
+    <t xml:space="preserve">25.8090629577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9527130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6654109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4794273376465</t>
   </si>
   <si>
     <t xml:space="preserve">26.5751934051514</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4849739074707</t>
+    <t xml:space="preserve">27.4849758148193</t>
   </si>
   <si>
     <t xml:space="preserve">27.3892097473145</t>
@@ -2759,7 +2759,7 @@
     <t xml:space="preserve">27.3413257598877</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8680400848389</t>
+    <t xml:space="preserve">27.8680419921875</t>
   </si>
   <si>
     <t xml:space="preserve">28.4905242919922</t>
@@ -2771,43 +2771,43 @@
     <t xml:space="preserve">28.2989902496338</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7722721099854</t>
+    <t xml:space="preserve">27.7722759246826</t>
   </si>
   <si>
     <t xml:space="preserve">27.6286239624023</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7243938446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5328578948975</t>
+    <t xml:space="preserve">27.7243919372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5328598022461</t>
   </si>
   <si>
     <t xml:space="preserve">27.2455596923828</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9582614898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1497917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0540256500244</t>
+    <t xml:space="preserve">26.9582595825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1497936248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.054027557373</t>
   </si>
   <si>
     <t xml:space="preserve">26.718843460083</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9287757873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2543525695801</t>
+    <t xml:space="preserve">26.9287776947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2543506622314</t>
   </si>
   <si>
     <t xml:space="preserve">25.8207931518555</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4354095458984</t>
+    <t xml:space="preserve">25.4354076385498</t>
   </si>
   <si>
     <t xml:space="preserve">24.5682926177979</t>
@@ -2816,10 +2816,10 @@
     <t xml:space="preserve">24.7128105163574</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1347351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7609844207764</t>
+    <t xml:space="preserve">24.1347332000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.760986328125</t>
   </si>
   <si>
     <t xml:space="preserve">24.6646404266357</t>
@@ -2828,25 +2828,25 @@
     <t xml:space="preserve">25.0981960296631</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3988723754883</t>
+    <t xml:space="preserve">26.3988704681396</t>
   </si>
   <si>
     <t xml:space="preserve">26.8324298858643</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4470443725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9171409606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8689670562744</t>
+    <t xml:space="preserve">26.4470462799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9171390533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.868968963623</t>
   </si>
   <si>
     <t xml:space="preserve">25.4835815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7244472503662</t>
+    <t xml:space="preserve">25.7244491577148</t>
   </si>
   <si>
     <t xml:space="preserve">25.1463718414307</t>
@@ -2858,31 +2858,31 @@
     <t xml:space="preserve">26.1098327636719</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0616588592529</t>
+    <t xml:space="preserve">26.0616569519043</t>
   </si>
   <si>
     <t xml:space="preserve">25.9653129577637</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1580066680908</t>
+    <t xml:space="preserve">26.1580047607422</t>
   </si>
   <si>
     <t xml:space="preserve">25.628101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8573303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6762752532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5317535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0500221252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4719467163086</t>
+    <t xml:space="preserve">24.857328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6762733459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5317554473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0500240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.47194480896</t>
   </si>
   <si>
     <t xml:space="preserve">22.9785804748535</t>
@@ -2894,13 +2894,13 @@
     <t xml:space="preserve">23.6530017852783</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0267524719238</t>
+    <t xml:space="preserve">23.0267543792725</t>
   </si>
   <si>
     <t xml:space="preserve">22.9304046630859</t>
   </si>
   <si>
-    <t xml:space="preserve">23.219446182251</t>
+    <t xml:space="preserve">23.2194442749023</t>
   </si>
   <si>
     <t xml:space="preserve">23.4121360778809</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">21.9669437408447</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8224239349365</t>
+    <t xml:space="preserve">21.8224258422852</t>
   </si>
   <si>
     <t xml:space="preserve">21.5815582275391</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">22.4968490600586</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1114616394043</t>
+    <t xml:space="preserve">22.1114635467529</t>
   </si>
   <si>
     <t xml:space="preserve">23.1712703704834</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">22.1596355438232</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0632915496826</t>
+    <t xml:space="preserve">22.063289642334</t>
   </si>
   <si>
     <t xml:space="preserve">21.3888664245605</t>
@@ -2948,13 +2948,13 @@
     <t xml:space="preserve">20.52174949646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5101127624512</t>
+    <t xml:space="preserve">19.5101146697998</t>
   </si>
   <si>
     <t xml:space="preserve">20.1845378875732</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9436740875244</t>
+    <t xml:space="preserve">19.9436721801758</t>
   </si>
   <si>
     <t xml:space="preserve">18.9609413146973</t>
@@ -2966,13 +2966,13 @@
     <t xml:space="preserve">18.1323623657227</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8991317749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9569396972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0167484283447</t>
+    <t xml:space="preserve">16.899133682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9569416046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0167503356934</t>
   </si>
   <si>
     <t xml:space="preserve">18.15163230896</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">18.3057861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8433265686035</t>
+    <t xml:space="preserve">17.8433246612549</t>
   </si>
   <si>
     <t xml:space="preserve">17.4964771270752</t>
@@ -3008,58 +3008,58 @@
     <t xml:space="preserve">18.7682476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0765552520752</t>
+    <t xml:space="preserve">19.0765571594238</t>
   </si>
   <si>
     <t xml:space="preserve">19.1921730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6064624786377</t>
+    <t xml:space="preserve">19.6064605712891</t>
   </si>
   <si>
     <t xml:space="preserve">19.1150951385498</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2114410400391</t>
+    <t xml:space="preserve">19.2114429473877</t>
   </si>
   <si>
     <t xml:space="preserve">18.6333637237549</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7662487030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6526336669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4021339416504</t>
+    <t xml:space="preserve">17.7662467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6526355743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4021320343018</t>
   </si>
   <si>
     <t xml:space="preserve">18.7297096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4137687683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7509784698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1343650817871</t>
+    <t xml:space="preserve">19.4137668609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7509803771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1343669891357</t>
   </si>
   <si>
     <t xml:space="preserve">18.7489776611328</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9224014282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3655967712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2692489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5350170135498</t>
+    <t xml:space="preserve">18.9224033355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3655948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2692470550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5350189208984</t>
   </si>
   <si>
     <t xml:space="preserve">17.7277088165283</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">18.0938262939453</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7991523742676</t>
+    <t xml:space="preserve">19.7991542816162</t>
   </si>
   <si>
     <t xml:space="preserve">20.040018081665</t>
@@ -3083,19 +3083,19 @@
     <t xml:space="preserve">21.0516548156738</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4852123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4370384216309</t>
+    <t xml:space="preserve">21.4852142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4370403289795</t>
   </si>
   <si>
     <t xml:space="preserve">21.8705978393555</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4005012512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1230983734131</t>
+    <t xml:space="preserve">22.4005031585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1231002807617</t>
   </si>
   <si>
     <t xml:space="preserve">23.3157920837402</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">22.5450229644775</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2078094482422</t>
+    <t xml:space="preserve">22.2078075408936</t>
   </si>
   <si>
     <t xml:space="preserve">20.4254035949707</t>
@@ -3113,13 +3113,13 @@
     <t xml:space="preserve">20.8107891082764</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8955001831055</t>
+    <t xml:space="preserve">19.8954982757568</t>
   </si>
   <si>
     <t xml:space="preserve">20.2327117919922</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4735774993896</t>
+    <t xml:space="preserve">20.473575592041</t>
   </si>
   <si>
     <t xml:space="preserve">19.8473262786865</t>
@@ -3134,28 +3134,28 @@
     <t xml:space="preserve">18.5948257446289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5735530853271</t>
+    <t xml:space="preserve">17.5735549926758</t>
   </si>
   <si>
     <t xml:space="preserve">18.8067874908447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.498477935791</t>
+    <t xml:space="preserve">18.4984817504883</t>
   </si>
   <si>
     <t xml:space="preserve">18.2287101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0745544433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5562858581543</t>
+    <t xml:space="preserve">18.0745582580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5562877655029</t>
   </si>
   <si>
     <t xml:space="preserve">18.7104415893555</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9416732788086</t>
+    <t xml:space="preserve">18.94167137146</t>
   </si>
   <si>
     <t xml:space="preserve">18.5370178222656</t>
@@ -3164,22 +3164,22 @@
     <t xml:space="preserve">18.4406719207764</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2865161895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9782104492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5755558013916</t>
+    <t xml:space="preserve">18.2865180969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9782085418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5755577087402</t>
   </si>
   <si>
     <t xml:space="preserve">19.3174209594727</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8453254699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9802093505859</t>
+    <t xml:space="preserve">18.8453235626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9802112579346</t>
   </si>
   <si>
     <t xml:space="preserve">19.4619426727295</t>
@@ -3188,34 +3188,34 @@
     <t xml:space="preserve">18.1709022521973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.708438873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9204025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6313629150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2094402313232</t>
+    <t xml:space="preserve">17.7084369659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9204006195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6313610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2094383239746</t>
   </si>
   <si>
     <t xml:space="preserve">18.2479782104492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6699028015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3423252105713</t>
+    <t xml:space="preserve">17.669900894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3423233032227</t>
   </si>
   <si>
     <t xml:space="preserve">16.6293621063232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9934787750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4559383392334</t>
+    <t xml:space="preserve">15.9934778213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.455940246582</t>
   </si>
   <si>
     <t xml:space="preserve">16.2054386138916</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">16.0512847900391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2247085571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4153985977173</t>
+    <t xml:space="preserve">16.2247066497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4153995513916</t>
   </si>
   <si>
     <t xml:space="preserve">15.5502834320068</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3575916290283</t>
+    <t xml:space="preserve">15.357590675354</t>
   </si>
   <si>
     <t xml:space="preserve">16.7257080078125</t>
@@ -3242,16 +3242,16 @@
     <t xml:space="preserve">16.128360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7642478942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.879861831665</t>
+    <t xml:space="preserve">16.7642459869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8798637390137</t>
   </si>
   <si>
     <t xml:space="preserve">17.1110935211182</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4386711120605</t>
+    <t xml:space="preserve">17.4386730194092</t>
   </si>
   <si>
     <t xml:space="preserve">17.2459774017334</t>
@@ -3260,19 +3260,19 @@
     <t xml:space="preserve">17.1689014434814</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1303634643555</t>
+    <t xml:space="preserve">17.1303615570068</t>
   </si>
   <si>
     <t xml:space="preserve">17.9589405059814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8838653564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.826057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5582866668701</t>
+    <t xml:space="preserve">18.8838634490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8260555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5582885742188</t>
   </si>
   <si>
     <t xml:space="preserve">20.088191986084</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">20.3290576934814</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7626152038574</t>
+    <t xml:space="preserve">20.7626171112061</t>
   </si>
   <si>
     <t xml:space="preserve">20.8589630126953</t>
@@ -4572,6 +4572,9 @@
   </si>
   <si>
     <t xml:space="preserve">48.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.25</t>
   </si>
 </sst>
 </file>
@@ -69650,7 +69653,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6495833333</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>55658</v>
@@ -69671,6 +69674,32 @@
         <v>1519</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6494212963</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>80262</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>48.7999992370605</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>47.2999992370605</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>47.9500007629395</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1520</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="1522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="1523">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6962604522705</t>
+    <t xml:space="preserve">15.6962614059448</t>
   </si>
   <si>
     <t xml:space="preserve">DAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8255243301392</t>
+    <t xml:space="preserve">15.8255224227905</t>
   </si>
   <si>
     <t xml:space="preserve">15.3269376754761</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6344537734985</t>
+    <t xml:space="preserve">14.6344547271729</t>
   </si>
   <si>
     <t xml:space="preserve">14.3112964630127</t>
@@ -62,76 +62,76 @@
     <t xml:space="preserve">14.3851613998413</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1358699798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9604396820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1940927505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8801670074463</t>
+    <t xml:space="preserve">14.1358671188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9604387283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.194091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8801651000977</t>
   </si>
   <si>
     <t xml:space="preserve">12.9724979400635</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3723487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0371294021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2217903137207</t>
+    <t xml:space="preserve">12.3723468780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0371313095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.221791267395</t>
   </si>
   <si>
     <t xml:space="preserve">16.0009517669678</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1579189300537</t>
+    <t xml:space="preserve">16.1579151153564</t>
   </si>
   <si>
     <t xml:space="preserve">16.434907913208</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1948509216309</t>
+    <t xml:space="preserve">16.1948490142822</t>
   </si>
   <si>
     <t xml:space="preserve">16.4718399047852</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2289562225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7119007110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5762329101562</t>
+    <t xml:space="preserve">17.2289543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7119026184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5762310028076</t>
   </si>
   <si>
     <t xml:space="preserve">16.2133121490479</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4100332260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0407123565674</t>
+    <t xml:space="preserve">15.4100341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0407114028931</t>
   </si>
   <si>
     <t xml:space="preserve">15.0499448776245</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4561996459961</t>
+    <t xml:space="preserve">15.4562005996704</t>
   </si>
   <si>
     <t xml:space="preserve">15.2069063186646</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1053419113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0194225311279</t>
+    <t xml:space="preserve">15.1053457260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0194187164307</t>
   </si>
   <si>
     <t xml:space="preserve">16.3425769805908</t>
@@ -140,13 +140,13 @@
     <t xml:space="preserve">16.8780994415283</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0350589752197</t>
+    <t xml:space="preserve">17.0350608825684</t>
   </si>
   <si>
     <t xml:space="preserve">17.1735553741455</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0812225341797</t>
+    <t xml:space="preserve">17.0812244415283</t>
   </si>
   <si>
     <t xml:space="preserve">16.8227005004883</t>
@@ -155,40 +155,40 @@
     <t xml:space="preserve">16.4626064300537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4533748626709</t>
+    <t xml:space="preserve">16.4533710479736</t>
   </si>
   <si>
     <t xml:space="preserve">16.9427299499512</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7488327026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.293586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4228515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4874801635742</t>
+    <t xml:space="preserve">16.7488346099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2935848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4228534698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4874820709229</t>
   </si>
   <si>
     <t xml:space="preserve">17.5521144866943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6472682952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3397521972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6352081298828</t>
+    <t xml:space="preserve">16.6472702026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3397541046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6352100372314</t>
   </si>
   <si>
     <t xml:space="preserve">16.9888954162598</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3766841888428</t>
+    <t xml:space="preserve">17.3766822814941</t>
   </si>
   <si>
     <t xml:space="preserve">17.57981300354</t>
@@ -197,67 +197,67 @@
     <t xml:space="preserve">17.1273899078369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3241100311279</t>
+    <t xml:space="preserve">16.3241119384766</t>
   </si>
   <si>
     <t xml:space="preserve">16.665735244751</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0535259246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4043846130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6842021942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6380386352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.238187789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.68137550354</t>
+    <t xml:space="preserve">17.053524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4043827056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6842002868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6380367279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2381896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6813735961914</t>
   </si>
   <si>
     <t xml:space="preserve">17.755241394043</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5244102478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9860687255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2353630065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1430282592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9122047424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7183094024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4661884307861</t>
+    <t xml:space="preserve">17.5244121551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9860668182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2353610992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1430320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.912202835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7183113098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4661903381348</t>
   </si>
   <si>
     <t xml:space="preserve">18.530818939209</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5585193634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2168960571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4477252960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1522636413574</t>
+    <t xml:space="preserve">18.5585250854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2168941497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4477214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1522655487061</t>
   </si>
   <si>
     <t xml:space="preserve">18.0137672424316</t>
@@ -266,10 +266,10 @@
     <t xml:space="preserve">17.5890445709229</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2658863067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6075096130371</t>
+    <t xml:space="preserve">17.26589012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6075115203857</t>
   </si>
   <si>
     <t xml:space="preserve">17.2843532562256</t>
@@ -278,25 +278,25 @@
     <t xml:space="preserve">17.192024230957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8873291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9519634246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6749706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4256801605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2594795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3610420227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8596324920654</t>
+    <t xml:space="preserve">16.8873329162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.951961517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6749687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4256782531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2594814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3610401153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8596305847168</t>
   </si>
   <si>
     <t xml:space="preserve">16.5641708374023</t>
@@ -305,37 +305,37 @@
     <t xml:space="preserve">16.5272426605225</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2779445648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4782466888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6287994384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6103401184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3582172393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.108922958374</t>
+    <t xml:space="preserve">16.2779502868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.47825050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6288051605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6103363037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3582210540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1089248657227</t>
   </si>
   <si>
     <t xml:space="preserve">17.1550884246826</t>
   </si>
   <si>
-    <t xml:space="preserve">15.917857170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9547910690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0591764450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8652839660645</t>
+    <t xml:space="preserve">15.9178562164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9547872543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.059178352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8652830123901</t>
   </si>
   <si>
     <t xml:space="preserve">15.1699752807617</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">15.4377326965332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0655860900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0868768692017</t>
+    <t xml:space="preserve">16.0655822753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.086877822876</t>
   </si>
   <si>
     <t xml:space="preserve">14.5513572692871</t>
@@ -356,19 +356,19 @@
     <t xml:space="preserve">14.985312461853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6252241134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7821846008301</t>
+    <t xml:space="preserve">14.6252212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7821855545044</t>
   </si>
   <si>
     <t xml:space="preserve">15.5115976333618</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1330423355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.72678565979</t>
+    <t xml:space="preserve">15.1330413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7267847061157</t>
   </si>
   <si>
     <t xml:space="preserve">14.0989360809326</t>
@@ -380,70 +380,70 @@
     <t xml:space="preserve">14.7544841766357</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5023679733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4192676544189</t>
+    <t xml:space="preserve">15.5023670196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4192695617676</t>
   </si>
   <si>
     <t xml:space="preserve">15.6039304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3546342849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4285001754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.400803565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4839000701904</t>
+    <t xml:space="preserve">15.3546371459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4285020828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4008007049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4839010238647</t>
   </si>
   <si>
     <t xml:space="preserve">16.2502479553223</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7239580154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4931335449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2317790985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9363222122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1856155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.287181854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.176383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0932846069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2566528320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9242610931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7211380004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7580642700195</t>
+    <t xml:space="preserve">15.7239608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4931316375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2317810058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9363241195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1856174468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2871799468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1763820648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.093282699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2566547393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9242630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.721134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7580680847168</t>
   </si>
   <si>
     <t xml:space="preserve">17.7275428771973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2751197814941</t>
+    <t xml:space="preserve">17.2751178741455</t>
   </si>
   <si>
     <t xml:space="preserve">17.1458549499512</t>
@@ -455,46 +455,46 @@
     <t xml:space="preserve">17.4505481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">16.204080581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8901519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.862452507019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9270896911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0563526153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7424259185791</t>
+    <t xml:space="preserve">16.2040786743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8901567459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8624563217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270877838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0563488006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7424278259277</t>
   </si>
   <si>
     <t xml:space="preserve">15.7701263427734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6685609817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5946969985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7147283554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1394481658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8134632110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1671466827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6408634185791</t>
+    <t xml:space="preserve">15.6685638427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5946979522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7147302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1394500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8134670257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1671524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6408624649048</t>
   </si>
   <si>
     <t xml:space="preserve">15.6500949859619</t>
@@ -506,67 +506,67 @@
     <t xml:space="preserve">15.4654340744019</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2623071670532</t>
+    <t xml:space="preserve">15.2623052597046</t>
   </si>
   <si>
     <t xml:space="preserve">15.3366203308105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4109344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.652458190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7360610961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8939790725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6245889663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0765190124512</t>
+    <t xml:space="preserve">15.4109334945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6524543762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7360601425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8939771652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.624587059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0765199661255</t>
   </si>
   <si>
     <t xml:space="preserve">15.4295139312744</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5224046707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5131168365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1601228713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8661088943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3305740356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9311332702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4945392608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6060075759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3180418014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8846912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0518989562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8382406234741</t>
+    <t xml:space="preserve">15.522406578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131177902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1601238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8661108016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3305759429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9311351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4945373535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6060085296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3180437088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8846893310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0518951416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8382434844971</t>
   </si>
   <si>
     <t xml:space="preserve">16.5813865661621</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">17.2595024108887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1387424468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2223472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0272693634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9529590606689</t>
+    <t xml:space="preserve">17.138744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2223491668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.027271270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9529571533203</t>
   </si>
   <si>
     <t xml:space="preserve">16.4884929656982</t>
@@ -599,73 +599,73 @@
     <t xml:space="preserve">16.9065113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1666088104248</t>
+    <t xml:space="preserve">17.1666107177734</t>
   </si>
   <si>
     <t xml:space="preserve">17.742546081543</t>
   </si>
   <si>
-    <t xml:space="preserve">17.900463104248</t>
+    <t xml:space="preserve">17.9004650115967</t>
   </si>
   <si>
     <t xml:space="preserve">17.9376239776611</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8818893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4299545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9037094116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9501552581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5539569854736</t>
+    <t xml:space="preserve">17.8818836212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.42995262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9037113189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9501533508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5539608001709</t>
   </si>
   <si>
     <t xml:space="preserve">19.6282730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1173648834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9129981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4610691070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3310146331787</t>
+    <t xml:space="preserve">19.1173629760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9130001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.461067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3310127258301</t>
   </si>
   <si>
     <t xml:space="preserve">19.1823863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0802021026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8572597503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0151786804199</t>
+    <t xml:space="preserve">19.0802059173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8572616577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0151824951172</t>
   </si>
   <si>
     <t xml:space="preserve">18.9408626556396</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9315757751465</t>
+    <t xml:space="preserve">18.9315738677979</t>
   </si>
   <si>
     <t xml:space="preserve">18.7550792694092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5785827636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4020862579346</t>
+    <t xml:space="preserve">18.5785846710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4020881652832</t>
   </si>
   <si>
     <t xml:space="preserve">18.1141185760498</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">18.4578227996826</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5321369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4671096801758</t>
+    <t xml:space="preserve">18.5321388244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.467113494873</t>
   </si>
   <si>
     <t xml:space="preserve">18.3742198944092</t>
@@ -686,58 +686,58 @@
     <t xml:space="preserve">18.4856910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2813282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3277721405029</t>
+    <t xml:space="preserve">18.2813243865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3277702331543</t>
   </si>
   <si>
     <t xml:space="preserve">18.5135593414307</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6157398223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6250267028809</t>
+    <t xml:space="preserve">18.6157417297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6250305175781</t>
   </si>
   <si>
     <t xml:space="preserve">18.7272109985352</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0430469512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4146194458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0894947052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.126651763916</t>
+    <t xml:space="preserve">19.0430450439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4146175384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0894927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1266498565674</t>
   </si>
   <si>
     <t xml:space="preserve">19.3681716918945</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4517726898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9594440460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2474098205566</t>
+    <t xml:space="preserve">19.4517784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9594421386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2474136352539</t>
   </si>
   <si>
     <t xml:space="preserve">19.507511138916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0987815856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2195434570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3495960235596</t>
+    <t xml:space="preserve">19.098783493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2195453643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3495941162109</t>
   </si>
   <si>
     <t xml:space="preserve">19.0337600708008</t>
@@ -746,58 +746,58 @@
     <t xml:space="preserve">19.2288341522217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3867530822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2845687866211</t>
+    <t xml:space="preserve">19.3867511749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2845668792725</t>
   </si>
   <si>
     <t xml:space="preserve">19.9162406921387</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0091323852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3807029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6222286224365</t>
+    <t xml:space="preserve">20.0091342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3807048797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6222267150879</t>
   </si>
   <si>
     <t xml:space="preserve">20.8544597625732</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9659328460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9473495483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1484718322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6129379272461</t>
+    <t xml:space="preserve">20.9659290313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9473533630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1484756469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6129341125488</t>
   </si>
   <si>
     <t xml:space="preserve">20.3899974822998</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2506542205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5757808685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6500949859619</t>
+    <t xml:space="preserve">20.2506523132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5757789611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6500968933105</t>
   </si>
   <si>
     <t xml:space="preserve">20.6036491394043</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5014686584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5293350219727</t>
+    <t xml:space="preserve">20.50146484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.529333114624</t>
   </si>
   <si>
     <t xml:space="preserve">20.6593837738037</t>
@@ -806,22 +806,22 @@
     <t xml:space="preserve">20.4828872680664</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8173007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8637466430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4550228118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7801475524902</t>
+    <t xml:space="preserve">20.8173027038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8637447357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4550189971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7801494598389</t>
   </si>
   <si>
     <t xml:space="preserve">21.6440486907959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4954204559326</t>
+    <t xml:space="preserve">21.495418548584</t>
   </si>
   <si>
     <t xml:space="preserve">21.3653697967529</t>
@@ -833,13 +833,13 @@
     <t xml:space="preserve">21.1331367492676</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1238498687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9287757873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2724781036377</t>
+    <t xml:space="preserve">21.1238460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9287776947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2724761962891</t>
   </si>
   <si>
     <t xml:space="preserve">21.1052684783936</t>
@@ -848,73 +848,73 @@
     <t xml:space="preserve">21.3467922210693</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2260322570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6408081054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1702976226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9566402435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1145610809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2538986206055</t>
+    <t xml:space="preserve">21.2260303497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6408042907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.170295715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9566440582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1145572662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2538967132568</t>
   </si>
   <si>
     <t xml:space="preserve">21.2446098327637</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3375015258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2817649841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.938060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1795825958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.733699798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3156833648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3992824554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4085750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3249702453613</t>
+    <t xml:space="preserve">21.3375034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2817687988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9380626678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1795845031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7336959838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3156814575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3992862701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4085712432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3249683380127</t>
   </si>
   <si>
     <t xml:space="preserve">20.6315135955811</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2785224914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.046293258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2134971618652</t>
+    <t xml:space="preserve">20.2785243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0462894439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2134990692139</t>
   </si>
   <si>
     <t xml:space="preserve">19.7954807281494</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9069519042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2692356109619</t>
+    <t xml:space="preserve">19.9069499969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2692337036133</t>
   </si>
   <si>
     <t xml:space="preserve">20.2971019744873</t>
@@ -923,58 +923,58 @@
     <t xml:space="preserve">20.5479145050049</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4364395141602</t>
+    <t xml:space="preserve">20.4364433288574</t>
   </si>
   <si>
     <t xml:space="preserve">19.9533977508545</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8326396942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8883743286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7211666107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9255294799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0741577148438</t>
+    <t xml:space="preserve">19.8326377868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.888370513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7211647033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9255275726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0741596221924</t>
   </si>
   <si>
     <t xml:space="preserve">19.9998455047607</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1113147735596</t>
+    <t xml:space="preserve">20.1113185882568</t>
   </si>
   <si>
     <t xml:space="preserve">19.6747188568115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6686725616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2413654327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9719791412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7304534912109</t>
+    <t xml:space="preserve">20.6686763763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2413692474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9719753265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7304573059082</t>
   </si>
   <si>
     <t xml:space="preserve">20.4178638458252</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1298961639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4921741485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8451728820801</t>
+    <t xml:space="preserve">20.1298942565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4921760559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8451690673828</t>
   </si>
   <si>
     <t xml:space="preserve">20.3435497283936</t>
@@ -986,34 +986,34 @@
     <t xml:space="preserve">20.8916149139404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1981639862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7244071960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4735984802246</t>
+    <t xml:space="preserve">21.1981658935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7244091033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4736003875732</t>
   </si>
   <si>
     <t xml:space="preserve">20.3342590332031</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3714179992676</t>
+    <t xml:space="preserve">20.3714160919189</t>
   </si>
   <si>
     <t xml:space="preserve">19.8790836334229</t>
   </si>
   <si>
-    <t xml:space="preserve">19.841926574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7676124572754</t>
+    <t xml:space="preserve">19.8419284820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7676105499268</t>
   </si>
   <si>
     <t xml:space="preserve">19.9812660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0927352905273</t>
+    <t xml:space="preserve">20.0927391052246</t>
   </si>
   <si>
     <t xml:space="preserve">20.5200443267822</t>
@@ -1022,49 +1022,49 @@
     <t xml:space="preserve">19.9905567169189</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5353813171387</t>
+    <t xml:space="preserve">19.5353775024414</t>
   </si>
   <si>
     <t xml:space="preserve">19.2567005157471</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7829456329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8386859893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6343193054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9965991973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6807670593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5600051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6621856689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4392433166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8108158111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1359405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9779319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9499244689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5298538208008</t>
+    <t xml:space="preserve">18.7829475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.838680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6343173980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.996603012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6807632446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5600032806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6621875762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4392414093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8108177185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1359424591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9779300689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9499263763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5298519134521</t>
   </si>
   <si>
     <t xml:space="preserve">18.3058166503906</t>
@@ -1076,73 +1076,73 @@
     <t xml:space="preserve">17.8484039306641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6430358886719</t>
+    <t xml:space="preserve">17.6430339813232</t>
   </si>
   <si>
     <t xml:space="preserve">17.6710395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9417533874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8950805664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9697570800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2684764862061</t>
+    <t xml:space="preserve">17.9417514801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8950786590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9697551727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2684745788574</t>
   </si>
   <si>
     <t xml:space="preserve">18.4645118713379</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5858631134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4084968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.16579246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4925136566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3618240356445</t>
+    <t xml:space="preserve">18.585865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4084987640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1657905578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4925155639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3618259429932</t>
   </si>
   <si>
     <t xml:space="preserve">18.2218017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6698760986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7725639343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6978816986084</t>
+    <t xml:space="preserve">18.6698799133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7725620269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6978855133057</t>
   </si>
   <si>
     <t xml:space="preserve">18.6885471343994</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6138668060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3524894714355</t>
+    <t xml:space="preserve">18.6138706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3524913787842</t>
   </si>
   <si>
     <t xml:space="preserve">18.3804931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4458408355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4831790924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4738464355469</t>
+    <t xml:space="preserve">18.4458389282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4831771850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4738445281982</t>
   </si>
   <si>
     <t xml:space="preserve">18.6605434417725</t>
@@ -1151,31 +1151,31 @@
     <t xml:space="preserve">18.707218170166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5951976776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3898258209229</t>
+    <t xml:space="preserve">18.5951995849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3898277282715</t>
   </si>
   <si>
     <t xml:space="preserve">18.5018482208252</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9032516479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1833019256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4633483886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7433967590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.536865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2836627960205</t>
+    <t xml:space="preserve">18.9032535552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1832981109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4633464813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7433948516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5368671417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2836608886719</t>
   </si>
   <si>
     <t xml:space="preserve">21.5637092590332</t>
@@ -1184,16 +1184,16 @@
     <t xml:space="preserve">21.5170345306396</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3770122528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6103839874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4703578948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7504081726074</t>
+    <t xml:space="preserve">21.3770084381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6103801727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4703598022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7504062652588</t>
   </si>
   <si>
     <t xml:space="preserve">21.797082901001</t>
@@ -1205,31 +1205,31 @@
     <t xml:space="preserve">20.4435157775879</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0502891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6302165985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7702388763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7235679626465</t>
+    <t xml:space="preserve">21.0502872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6302146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7702407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7235641479492</t>
   </si>
   <si>
     <t xml:space="preserve">21.0969619750977</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1903114318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1436347961426</t>
+    <t xml:space="preserve">21.190315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1436367034912</t>
   </si>
   <si>
     <t xml:space="preserve">20.8635902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6768913269043</t>
+    <t xml:space="preserve">20.676887512207</t>
   </si>
   <si>
     <t xml:space="preserve">21.7037334442139</t>
@@ -1244,25 +1244,25 @@
     <t xml:space="preserve">22.0771312713623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9837799072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8169116973877</t>
+    <t xml:space="preserve">21.9837818145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8169136047363</t>
   </si>
   <si>
     <t xml:space="preserve">21.2369861602783</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3034954071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2101421356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9102649688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5835399627686</t>
+    <t xml:space="preserve">20.3034934997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2101440429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9102668762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5835418701172</t>
   </si>
   <si>
     <t xml:space="preserve">20.9569396972656</t>
@@ -1274,16 +1274,16 @@
     <t xml:space="preserve">20.3968410491943</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4901924133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.116792678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0432739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.136625289917</t>
+    <t xml:space="preserve">20.4901943206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1167907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0432758331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1366233825684</t>
   </si>
   <si>
     <t xml:space="preserve">19.3233242034912</t>
@@ -1295,22 +1295,22 @@
     <t xml:space="preserve">19.6033706665039</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3501682281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2568168640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9767723083496</t>
+    <t xml:space="preserve">20.3501663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2568187713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.976770401001</t>
   </si>
   <si>
     <t xml:space="preserve">20.1634674072266</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0234451293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8834209442139</t>
+    <t xml:space="preserve">20.0234432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8834171295166</t>
   </si>
   <si>
     <t xml:space="preserve">19.9300956726074</t>
@@ -1319,16 +1319,16 @@
     <t xml:space="preserve">19.4166736602783</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5566997528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5100250244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6500473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6967220306396</t>
+    <t xml:space="preserve">19.556697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5100212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6500492095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6967239379883</t>
   </si>
   <si>
     <t xml:space="preserve">19.2766494750977</t>
@@ -1340,58 +1340,58 @@
     <t xml:space="preserve">19.3699989318848</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8367443084717</t>
+    <t xml:space="preserve">19.8367462158203</t>
   </si>
   <si>
     <t xml:space="preserve">21.4236869812012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0701217651367</t>
+    <t xml:space="preserve">20.0701160430908</t>
   </si>
   <si>
     <t xml:space="preserve">17.7177124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3093004226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7013692855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7678737640381</t>
+    <t xml:space="preserve">15.3092994689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7013664245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7678728103638</t>
   </si>
   <si>
     <t xml:space="preserve">14.4691553115845</t>
   </si>
   <si>
-    <t xml:space="preserve">14.805212020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4026489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6266870498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0000858306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333385467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3279695510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4586563110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8693952560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7947158813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6640281677246</t>
+    <t xml:space="preserve">14.805214881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4026508331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.62668800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0000839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333375930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3279705047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4586582183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8693962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7947187423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6640272140503</t>
   </si>
   <si>
     <t xml:space="preserve">15.5893487930298</t>
@@ -1403,37 +1403,37 @@
     <t xml:space="preserve">15.0105819702148</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8602886199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5784883499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4094066619873</t>
+    <t xml:space="preserve">14.8602876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5784873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4094076156616</t>
   </si>
   <si>
     <t xml:space="preserve">14.4469814300537</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9166479110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9354333877563</t>
+    <t xml:space="preserve">14.9166498184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.935435295105</t>
   </si>
   <si>
     <t xml:space="preserve">14.6536359786987</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1420888900757</t>
+    <t xml:space="preserve">15.14208984375</t>
   </si>
   <si>
     <t xml:space="preserve">15.4426774978638</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2735967636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0712471008301</t>
+    <t xml:space="preserve">15.2735948562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0712461471558</t>
   </si>
   <si>
     <t xml:space="preserve">13.920952796936</t>
@@ -1448,19 +1448,19 @@
     <t xml:space="preserve">14.3342599868774</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1651802062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1463937759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2215404510498</t>
+    <t xml:space="preserve">14.1651811599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1463947296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2215414047241</t>
   </si>
   <si>
     <t xml:space="preserve">13.9585256576538</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6391534805298</t>
+    <t xml:space="preserve">13.6391525268555</t>
   </si>
   <si>
     <t xml:space="preserve">13.6203651428223</t>
@@ -1469,13 +1469,13 @@
     <t xml:space="preserve">13.7894458770752</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0524597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2027540206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5221271514893</t>
+    <t xml:space="preserve">14.0524587631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2027530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5221290588379</t>
   </si>
   <si>
     <t xml:space="preserve">14.7475671768188</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">15.0293684005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0669441223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8978605270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1045160293579</t>
+    <t xml:space="preserve">15.0669422149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8978624343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1045150756836</t>
   </si>
   <si>
     <t xml:space="preserve">15.1608753204346</t>
@@ -1505,10 +1505,10 @@
     <t xml:space="preserve">15.1984491348267</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5366086959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9687042236328</t>
+    <t xml:space="preserve">15.5366096496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9687032699585</t>
   </si>
   <si>
     <t xml:space="preserve">16.8141059875488</t>
@@ -1517,22 +1517,22 @@
     <t xml:space="preserve">16.8892517089844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9080371856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4947299957275</t>
+    <t xml:space="preserve">16.9080390930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4947319030762</t>
   </si>
   <si>
     <t xml:space="preserve">16.4195861816406</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2692909240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3632259368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.987491607666</t>
+    <t xml:space="preserve">16.2692928314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3632221221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9874935150146</t>
   </si>
   <si>
     <t xml:space="preserve">15.8747711181641</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">16.1377849578857</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1565742492676</t>
+    <t xml:space="preserve">16.1565704345703</t>
   </si>
   <si>
     <t xml:space="preserve">16.2505035400391</t>
@@ -1559,13 +1559,13 @@
     <t xml:space="preserve">16.2880783081055</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4383735656738</t>
+    <t xml:space="preserve">16.4383716583252</t>
   </si>
   <si>
     <t xml:space="preserve">16.4571590423584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2317199707031</t>
+    <t xml:space="preserve">16.2317180633545</t>
   </si>
   <si>
     <t xml:space="preserve">16.6074523925781</t>
@@ -1574,28 +1574,28 @@
     <t xml:space="preserve">16.7201728820801</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4759464263916</t>
+    <t xml:space="preserve">16.4759483337402</t>
   </si>
   <si>
     <t xml:space="preserve">16.3256511688232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8559846878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9499177932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9311294555664</t>
+    <t xml:space="preserve">15.8559837341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9499158859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.931131362915</t>
   </si>
   <si>
     <t xml:space="preserve">16.1189994812012</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0062808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3444385528564</t>
+    <t xml:space="preserve">16.0062789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3444366455078</t>
   </si>
   <si>
     <t xml:space="preserve">16.4007968902588</t>
@@ -1604,16 +1604,16 @@
     <t xml:space="preserve">16.5323066711426</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7765350341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9456157684326</t>
+    <t xml:space="preserve">16.7765331268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.945613861084</t>
   </si>
   <si>
     <t xml:space="preserve">17.4716396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2794704437256</t>
+    <t xml:space="preserve">18.279468536377</t>
   </si>
   <si>
     <t xml:space="preserve">18.260684967041</t>
@@ -1625,19 +1625,19 @@
     <t xml:space="preserve">18.1103897094727</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5280017852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1334819793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0019721984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9831867218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7389621734619</t>
+    <t xml:space="preserve">17.5279998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1334781646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0019760131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9831886291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7389583587646</t>
   </si>
   <si>
     <t xml:space="preserve">16.6450233459473</t>
@@ -1649,25 +1649,25 @@
     <t xml:space="preserve">16.832893371582</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0583343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1522693634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2274150848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7577476501465</t>
+    <t xml:space="preserve">17.0583324432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1522674560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2274131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7577457427979</t>
   </si>
   <si>
     <t xml:space="preserve">16.2129325866699</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4990358352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5178241729736</t>
+    <t xml:space="preserve">15.4990377426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5178232192993</t>
   </si>
   <si>
     <t xml:space="preserve">15.4614639282227</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">15.1796627044678</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6912088394165</t>
+    <t xml:space="preserve">14.6912078857422</t>
   </si>
   <si>
     <t xml:space="preserve">14.8039283752441</t>
@@ -1688,13 +1688,13 @@
     <t xml:space="preserve">14.7663555145264</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9730091094971</t>
+    <t xml:space="preserve">14.9730081558228</t>
   </si>
   <si>
     <t xml:space="preserve">14.8415012359619</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5033416748047</t>
+    <t xml:space="preserve">14.5033407211304</t>
   </si>
   <si>
     <t xml:space="preserve">14.6724224090576</t>
@@ -1703,58 +1703,58 @@
     <t xml:space="preserve">14.3718347549438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.822714805603</t>
+    <t xml:space="preserve">14.8227138519287</t>
   </si>
   <si>
     <t xml:space="preserve">14.5597009658813</t>
   </si>
   <si>
-    <t xml:space="preserve">14.465765953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6348466873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5741844177246</t>
+    <t xml:space="preserve">14.4657669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6348485946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5741834640503</t>
   </si>
   <si>
     <t xml:space="preserve">15.4051027297974</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3863153457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6681175231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2360219955444</t>
+    <t xml:space="preserve">15.3863162994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6681156158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2360210418701</t>
   </si>
   <si>
     <t xml:space="preserve">15.5929708480835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4238891601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3299541473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0481548309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8790760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5409135818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7851419448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.616060256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.296688079834</t>
+    <t xml:space="preserve">15.4238901138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3299560546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0481557846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.879075050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5409126281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7851409912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6160612106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2966871261597</t>
   </si>
   <si>
     <t xml:space="preserve">14.2778997421265</t>
@@ -1769,22 +1769,22 @@
     <t xml:space="preserve">13.7706594467163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4281930923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2591142654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8082313537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8458061218262</t>
+    <t xml:space="preserve">14.4281949996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2591133117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8082332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8458051681519</t>
   </si>
   <si>
     <t xml:space="preserve">14.0336723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9397411346436</t>
+    <t xml:space="preserve">13.9397401809692</t>
   </si>
   <si>
     <t xml:space="preserve">14.2403268814087</t>
@@ -1793,34 +1793,34 @@
     <t xml:space="preserve">14.0148868560791</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5972757339478</t>
+    <t xml:space="preserve">14.5972738265991</t>
   </si>
   <si>
     <t xml:space="preserve">13.9960985183716</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3675289154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.183967590332</t>
+    <t xml:space="preserve">15.3675317764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1839666366577</t>
   </si>
   <si>
     <t xml:space="preserve">14.1088199615479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4845542907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9917945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2923851013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.075891494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0569295883179</t>
+    <t xml:space="preserve">14.4845533370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.991795539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2923822402954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0758934020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0569314956665</t>
   </si>
   <si>
     <t xml:space="preserve">14.9052238464355</t>
@@ -1832,67 +1832,67 @@
     <t xml:space="preserve">14.8862590789795</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3793067932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6827201843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4602184295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3274784088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7016830444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6637592315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5310134887695</t>
+    <t xml:space="preserve">15.3793058395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6827220916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4602222442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3274765014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7016849517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6637582778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5310144424438</t>
   </si>
   <si>
     <t xml:space="preserve">15.5499782562256</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4551610946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7585773468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.796501159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1757678985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7206497192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6068687438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6447944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.043025970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9861364364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4172353744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344287872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.568941116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4362001419067</t>
+    <t xml:space="preserve">15.4551620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7585763931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7965021133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1757698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.720648765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6068677902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.64479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0430278778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9861345291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4172334671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344297409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5689420700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4361972808838</t>
   </si>
   <si>
     <t xml:space="preserve">15.5879058837891</t>
@@ -1901,16 +1901,16 @@
     <t xml:space="preserve">15.246563911438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1138210296631</t>
+    <t xml:space="preserve">15.1138200759888</t>
   </si>
   <si>
     <t xml:space="preserve">14.9810762405396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2086391448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7535152435303</t>
+    <t xml:space="preserve">15.2086372375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7535161972046</t>
   </si>
   <si>
     <t xml:space="preserve">14.9431495666504</t>
@@ -1922,13 +1922,13 @@
     <t xml:space="preserve">14.0329074859619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9380893707275</t>
+    <t xml:space="preserve">13.9380903244019</t>
   </si>
   <si>
     <t xml:space="preserve">14.2225408554077</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6018075942993</t>
+    <t xml:space="preserve">14.6018085479736</t>
   </si>
   <si>
     <t xml:space="preserve">14.7914438247681</t>
@@ -1937,28 +1937,28 @@
     <t xml:space="preserve">14.5828456878662</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3932123184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4311389923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6207723617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3363218307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2794313430786</t>
+    <t xml:space="preserve">14.3932113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4311380386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6207714080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3363208770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2794322967529</t>
   </si>
   <si>
     <t xml:space="preserve">14.0518703460693</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6915655136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1416273117065</t>
+    <t xml:space="preserve">13.6915664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1416282653809</t>
   </si>
   <si>
     <t xml:space="preserve">13.0088844299316</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">12.8002872467041</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4210186004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1744966506958</t>
+    <t xml:space="preserve">12.4210195541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1744956970215</t>
   </si>
   <si>
     <t xml:space="preserve">11.9469347000122</t>
@@ -1997,31 +1997,31 @@
     <t xml:space="preserve">9.59547424316406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91279220581055</t>
+    <t xml:space="preserve">8.91279315948486</t>
   </si>
   <si>
     <t xml:space="preserve">9.41532325744629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09736633300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55248928070068</t>
+    <t xml:space="preserve">8.09736728668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55248832702637</t>
   </si>
   <si>
     <t xml:space="preserve">9.10242652893066</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1643762588501</t>
+    <t xml:space="preserve">10.1643753051758</t>
   </si>
   <si>
     <t xml:space="preserve">10.7522411346436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9279718399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8951044082642</t>
+    <t xml:space="preserve">11.9279699325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8951034545898</t>
   </si>
   <si>
     <t xml:space="preserve">11.6055927276611</t>
@@ -2030,28 +2030,28 @@
     <t xml:space="preserve">10.9608383178711</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9229135513306</t>
+    <t xml:space="preserve">10.9229116439819</t>
   </si>
   <si>
     <t xml:space="preserve">10.6384611129761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0695581436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3350467681885</t>
+    <t xml:space="preserve">10.06955909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3350458145142</t>
   </si>
   <si>
     <t xml:space="preserve">10.6194982528687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7332763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1125469207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9039478302002</t>
+    <t xml:space="preserve">10.7332773208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1125459671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9039487838745</t>
   </si>
   <si>
     <t xml:space="preserve">10.5815696716309</t>
@@ -2060,34 +2060,34 @@
     <t xml:space="preserve">10.2023029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87992572784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2212657928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5057172775269</t>
+    <t xml:space="preserve">9.87992382049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2212648391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5057163238525</t>
   </si>
   <si>
     <t xml:space="preserve">10.4298629760742</t>
   </si>
   <si>
-    <t xml:space="preserve">10.771203994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7143144607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6953506469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8091316223145</t>
+    <t xml:space="preserve">10.7712030410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7143135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.695351600647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8091297149658</t>
   </si>
   <si>
     <t xml:space="preserve">10.8280954360962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5436429977417</t>
+    <t xml:space="preserve">10.543643951416</t>
   </si>
   <si>
     <t xml:space="preserve">10.9987659454346</t>
@@ -2096,13 +2096,13 @@
     <t xml:space="preserve">10.9418754577637</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4918127059937</t>
+    <t xml:space="preserve">11.491813659668</t>
   </si>
   <si>
     <t xml:space="preserve">11.567666053772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0556545257568</t>
+    <t xml:space="preserve">11.0556535720825</t>
   </si>
   <si>
     <t xml:space="preserve">11.4159603118896</t>
@@ -2111,58 +2111,58 @@
     <t xml:space="preserve">11.5107765197754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7952260971069</t>
+    <t xml:space="preserve">11.7952270507812</t>
   </si>
   <si>
     <t xml:space="preserve">12.0038242340088</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2882747650146</t>
+    <t xml:space="preserve">12.288275718689</t>
   </si>
   <si>
     <t xml:space="preserve">12.2124214172363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0986404418945</t>
+    <t xml:space="preserve">12.0986413955688</t>
   </si>
   <si>
     <t xml:space="preserve">11.8521175384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2263269424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.017728805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1883983612061</t>
+    <t xml:space="preserve">11.2263259887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0177278518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1883993148804</t>
   </si>
   <si>
     <t xml:space="preserve">11.093581199646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8849830627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7901668548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6763868331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4108991622925</t>
+    <t xml:space="preserve">10.8849849700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7901678085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6763877868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4109010696411</t>
   </si>
   <si>
     <t xml:space="preserve">10.4488277435303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6574239730835</t>
+    <t xml:space="preserve">10.6574249267578</t>
   </si>
   <si>
     <t xml:space="preserve">11.2073621749878</t>
   </si>
   <si>
-    <t xml:space="preserve">11.340106010437</t>
+    <t xml:space="preserve">11.3401050567627</t>
   </si>
   <si>
     <t xml:space="preserve">11.2832155227661</t>
@@ -2174,34 +2174,34 @@
     <t xml:space="preserve">10.9798011779785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6005334854126</t>
+    <t xml:space="preserve">10.6005344390869</t>
   </si>
   <si>
     <t xml:space="preserve">10.3729724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4677906036377</t>
+    <t xml:space="preserve">10.4677896499634</t>
   </si>
   <si>
     <t xml:space="preserve">11.6435203552246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4349231719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6814460754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5297403335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6245565414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5487041473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.662483215332</t>
+    <t xml:space="preserve">11.4349241256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6814470291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5297393798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6245574951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5487031936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6624841690063</t>
   </si>
   <si>
     <t xml:space="preserve">11.7383375167847</t>
@@ -2213,13 +2213,13 @@
     <t xml:space="preserve">12.136568069458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1176042556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9658975601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9848613739014</t>
+    <t xml:space="preserve">12.1176052093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9658985137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9848623275757</t>
   </si>
   <si>
     <t xml:space="preserve">11.8141899108887</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">11.245288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6485815048218</t>
+    <t xml:space="preserve">12.6485795974731</t>
   </si>
   <si>
     <t xml:space="preserve">13.6536388397217</t>
@@ -2240,22 +2240,22 @@
     <t xml:space="preserve">13.3881521224976</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8622369766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5967502593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2364454269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4260787963867</t>
+    <t xml:space="preserve">13.8622360229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5967493057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2364435195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.426079750061</t>
   </si>
   <si>
     <t xml:space="preserve">13.4640054702759</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1037006378174</t>
+    <t xml:space="preserve">13.1037015914917</t>
   </si>
   <si>
     <t xml:space="preserve">13.3312616348267</t>
@@ -2273,31 +2273,31 @@
     <t xml:space="preserve">13.1226654052734</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4829692840576</t>
+    <t xml:space="preserve">13.4829683303833</t>
   </si>
   <si>
     <t xml:space="preserve">13.17955493927</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0227890014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.060715675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3262014389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4399824142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8571767807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8192501068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0468111038208</t>
+    <t xml:space="preserve">12.0227880477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0607147216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3262033462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4399814605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.857177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8192510604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0468101501465</t>
   </si>
   <si>
     <t xml:space="preserve">13.3122987747192</t>
@@ -2309,22 +2309,22 @@
     <t xml:space="preserve">13.5588235855103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6179914474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6371440887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4073057174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4456119537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3115377426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5030727386475</t>
+    <t xml:space="preserve">13.6179904937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6371450424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4073047637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4456129074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3115386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5030717849731</t>
   </si>
   <si>
     <t xml:space="preserve">13.8478307723999</t>
@@ -2333,43 +2333,43 @@
     <t xml:space="preserve">13.886137008667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7520637512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1734371185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1542825698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2117443084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9819040298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6946039199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4647655487061</t>
+    <t xml:space="preserve">13.7520627975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.173436164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1542835235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2117433547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9819049835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6946058273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4647645950317</t>
   </si>
   <si>
     <t xml:space="preserve">13.7712182998657</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5988368988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5413789749146</t>
+    <t xml:space="preserve">13.598837852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5413780212402</t>
   </si>
   <si>
     <t xml:space="preserve">13.7903699874878</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7137565612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8669834136963</t>
+    <t xml:space="preserve">13.7137575149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8669843673706</t>
   </si>
   <si>
     <t xml:space="preserve">14.1351299285889</t>
@@ -2384,22 +2384,22 @@
     <t xml:space="preserve">14.6331148147583</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9970273971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0353345870972</t>
+    <t xml:space="preserve">14.9970283508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0353355407715</t>
   </si>
   <si>
     <t xml:space="preserve">16.4909839630127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3377590179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.184534072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8206195831299</t>
+    <t xml:space="preserve">16.3377571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1845321655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8206205368042</t>
   </si>
   <si>
     <t xml:space="preserve">15.9546928405762</t>
@@ -2408,16 +2408,16 @@
     <t xml:space="preserve">15.8014659881592</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6099348068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3226337432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7440061569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3417882919312</t>
+    <t xml:space="preserve">15.6099328994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3226346969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.74400806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3417873382568</t>
   </si>
   <si>
     <t xml:space="preserve">15.437554359436</t>
@@ -2435,19 +2435,19 @@
     <t xml:space="preserve">16.6059036254883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.778284072876</t>
+    <t xml:space="preserve">16.7782859802246</t>
   </si>
   <si>
     <t xml:space="preserve">16.6825180053711</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6442089080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7208251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7016735076904</t>
+    <t xml:space="preserve">16.6442127227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7208232879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7016716003418</t>
   </si>
   <si>
     <t xml:space="preserve">17.1613502502441</t>
@@ -2465,10 +2465,10 @@
     <t xml:space="preserve">16.4526786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4335231781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9123592376709</t>
+    <t xml:space="preserve">16.4335250854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9123573303223</t>
   </si>
   <si>
     <t xml:space="preserve">16.6633644104004</t>
@@ -2480,19 +2480,19 @@
     <t xml:space="preserve">16.931510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8548984527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9657897949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0807075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3105487823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6321239471436</t>
+    <t xml:space="preserve">16.8549003601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9657917022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0807056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6321258544922</t>
   </si>
   <si>
     <t xml:space="preserve">19.9194240570068</t>
@@ -2504,13 +2504,13 @@
     <t xml:space="preserve">19.7757740020752</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7334384918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4940223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1109561920166</t>
+    <t xml:space="preserve">20.7334403991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4940242767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1109580993652</t>
   </si>
   <si>
     <t xml:space="preserve">19.9673080444336</t>
@@ -2519,34 +2519,34 @@
     <t xml:space="preserve">19.8715419769287</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0151901245117</t>
+    <t xml:space="preserve">20.0151920318604</t>
   </si>
   <si>
     <t xml:space="preserve">20.3982563018799</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5419082641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6376724243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9728565216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8770866394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3503742218018</t>
+    <t xml:space="preserve">20.5419063568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.637674331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9728546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8770885467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3503723144531</t>
   </si>
   <si>
     <t xml:space="preserve">20.0630741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9249706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7278938293457</t>
+    <t xml:space="preserve">20.9249725341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7278919219971</t>
   </si>
   <si>
     <t xml:space="preserve">19.4884757995605</t>
@@ -2555,16 +2555,16 @@
     <t xml:space="preserve">19.3448276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5363578796387</t>
+    <t xml:space="preserve">19.5363597869873</t>
   </si>
   <si>
     <t xml:space="preserve">19.823657989502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1532936096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2546081542969</t>
+    <t xml:space="preserve">19.1532917022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2546062469482</t>
   </si>
   <si>
     <t xml:space="preserve">20.4461402893066</t>
@@ -2573,16 +2573,16 @@
     <t xml:space="preserve">20.2067241668701</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1165027618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6911029815674</t>
+    <t xml:space="preserve">21.1165046691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.691104888916</t>
   </si>
   <si>
     <t xml:space="preserve">21.3080387115479</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7868728637695</t>
+    <t xml:space="preserve">21.7868709564209</t>
   </si>
   <si>
     <t xml:space="preserve">21.7389869689941</t>
@@ -2603,19 +2603,19 @@
     <t xml:space="preserve">21.212272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">21.355920791626</t>
+    <t xml:space="preserve">21.3559226989746</t>
   </si>
   <si>
     <t xml:space="preserve">21.4516868591309</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3135852813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7924156188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3191337585449</t>
+    <t xml:space="preserve">22.3135833740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7924175262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3191356658936</t>
   </si>
   <si>
     <t xml:space="preserve">22.6487693786621</t>
@@ -2624,16 +2624,16 @@
     <t xml:space="preserve">22.4093532562256</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0262870788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6432228088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4038047790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8292064666748</t>
+    <t xml:space="preserve">22.0262851715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6432209014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4038028717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8292045593262</t>
   </si>
   <si>
     <t xml:space="preserve">20.7813243865967</t>
@@ -2645,22 +2645,22 @@
     <t xml:space="preserve">24.5162162780762</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9416160583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4627838134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4148998260498</t>
+    <t xml:space="preserve">23.9416179656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4627857208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4149017333984</t>
   </si>
   <si>
     <t xml:space="preserve">23.1754856109619</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2712516784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5106678009033</t>
+    <t xml:space="preserve">23.2712497711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5106658935547</t>
   </si>
   <si>
     <t xml:space="preserve">23.22336769104</t>
@@ -2675,10 +2675,10 @@
     <t xml:space="preserve">23.0797176361084</t>
   </si>
   <si>
-    <t xml:space="preserve">23.797966003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7022018432617</t>
+    <t xml:space="preserve">23.7979679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7021999359131</t>
   </si>
   <si>
     <t xml:space="preserve">23.6543159484863</t>
@@ -2687,10 +2687,10 @@
     <t xml:space="preserve">23.0318336486816</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5585498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8403015136719</t>
+    <t xml:space="preserve">23.5585517883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8403034210205</t>
   </si>
   <si>
     <t xml:space="preserve">22.6008853912354</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">22.2657032012939</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5953388214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2178211212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1699371337891</t>
+    <t xml:space="preserve">21.5953350067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2178192138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1699352264404</t>
   </si>
   <si>
     <t xml:space="preserve">24.2289142608643</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">24.4683303833008</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0373821258545</t>
+    <t xml:space="preserve">24.0373840332031</t>
   </si>
   <si>
     <t xml:space="preserve">23.8458480834961</t>
@@ -2726,19 +2726,19 @@
     <t xml:space="preserve">25.4738788604736</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7611789703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1442432403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8569450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8090629577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9527130126953</t>
+    <t xml:space="preserve">25.7611770629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1442451477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8569431304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.809061050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9527111053467</t>
   </si>
   <si>
     <t xml:space="preserve">25.6654109954834</t>
@@ -2747,25 +2747,25 @@
     <t xml:space="preserve">26.4794273376465</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5751953125</t>
+    <t xml:space="preserve">26.5751934051514</t>
   </si>
   <si>
     <t xml:space="preserve">27.4849758148193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3892078399658</t>
+    <t xml:space="preserve">27.3892116546631</t>
   </si>
   <si>
     <t xml:space="preserve">27.3413257598877</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8680419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4905242919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9638080596924</t>
+    <t xml:space="preserve">27.8680400848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4905223846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.963809967041</t>
   </si>
   <si>
     <t xml:space="preserve">28.2989902496338</t>
@@ -2774,25 +2774,25 @@
     <t xml:space="preserve">27.772274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">27.628625869751</t>
+    <t xml:space="preserve">27.6286239624023</t>
   </si>
   <si>
     <t xml:space="preserve">27.7243919372559</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5328598022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2455596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9582595825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1497917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.054027557373</t>
+    <t xml:space="preserve">27.5328578948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2455615997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9582576751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1497936248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0540256500244</t>
   </si>
   <si>
     <t xml:space="preserve">26.718843460083</t>
@@ -2804,25 +2804,25 @@
     <t xml:space="preserve">26.2543506622314</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8207950592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4354057312012</t>
+    <t xml:space="preserve">25.8207931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4354076385498</t>
   </si>
   <si>
     <t xml:space="preserve">24.5682926177979</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7128124237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1347351074219</t>
+    <t xml:space="preserve">24.7128105163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1347332000732</t>
   </si>
   <si>
     <t xml:space="preserve">24.760986328125</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6646385192871</t>
+    <t xml:space="preserve">24.6646404266357</t>
   </si>
   <si>
     <t xml:space="preserve">25.0981960296631</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">25.9171390533447</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8689670562744</t>
+    <t xml:space="preserve">25.868968963623</t>
   </si>
   <si>
     <t xml:space="preserve">25.4835815429688</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">25.7244491577148</t>
   </si>
   <si>
-    <t xml:space="preserve">25.146369934082</t>
+    <t xml:space="preserve">25.1463718414307</t>
   </si>
   <si>
     <t xml:space="preserve">25.579927444458</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">26.1098327636719</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0616588592529</t>
+    <t xml:space="preserve">26.0616569519043</t>
   </si>
   <si>
     <t xml:space="preserve">25.9653129577637</t>
@@ -2870,19 +2870,19 @@
     <t xml:space="preserve">25.628101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8573303222656</t>
+    <t xml:space="preserve">24.857328414917</t>
   </si>
   <si>
     <t xml:space="preserve">25.6762733459473</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5317535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0500221252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4719467163086</t>
+    <t xml:space="preserve">25.5317554473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0500240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.47194480896</t>
   </si>
   <si>
     <t xml:space="preserve">22.9785804748535</t>
@@ -2891,22 +2891,22 @@
     <t xml:space="preserve">22.7858867645264</t>
   </si>
   <si>
-    <t xml:space="preserve">23.653003692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0267524719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9304065704346</t>
+    <t xml:space="preserve">23.6530017852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0267543792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9304046630859</t>
   </si>
   <si>
     <t xml:space="preserve">23.2194442749023</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4121379852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4486751556396</t>
+    <t xml:space="preserve">23.4121360778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.448673248291</t>
   </si>
   <si>
     <t xml:space="preserve">21.9669437408447</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">21.5815582275391</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6413650512695</t>
+    <t xml:space="preserve">22.6413669586182</t>
   </si>
   <si>
     <t xml:space="preserve">22.8340606689453</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">22.063289642334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3888683319092</t>
+    <t xml:space="preserve">21.3888664245605</t>
   </si>
   <si>
     <t xml:space="preserve">21.1480007171631</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">19.5101146697998</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1845397949219</t>
+    <t xml:space="preserve">20.1845378875732</t>
   </si>
   <si>
     <t xml:space="preserve">19.9436721801758</t>
@@ -2963,22 +2963,22 @@
     <t xml:space="preserve">19.1536331176758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1323642730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8991317749023</t>
+    <t xml:space="preserve">18.1323623657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.899133682251</t>
   </si>
   <si>
     <t xml:space="preserve">16.9569416046143</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0167484283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1516304016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5542869567871</t>
+    <t xml:space="preserve">18.0167503356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.15163230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5542850494385</t>
   </si>
   <si>
     <t xml:space="preserve">18.3057861328125</t>
@@ -2987,10 +2987,10 @@
     <t xml:space="preserve">17.8433246612549</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4964790344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6719036102295</t>
+    <t xml:space="preserve">17.4964771270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6719017028809</t>
   </si>
   <si>
     <t xml:space="preserve">18.2672462463379</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">18.6911716461182</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3828620910645</t>
+    <t xml:space="preserve">18.3828639984131</t>
   </si>
   <si>
     <t xml:space="preserve">18.7682476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0765552520752</t>
+    <t xml:space="preserve">19.0765571594238</t>
   </si>
   <si>
     <t xml:space="preserve">19.1921730041504</t>
@@ -3032,16 +3032,16 @@
     <t xml:space="preserve">18.6526355743408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4021339416504</t>
+    <t xml:space="preserve">18.4021320343018</t>
   </si>
   <si>
     <t xml:space="preserve">18.7297096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4137687683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7509822845459</t>
+    <t xml:space="preserve">19.4137668609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7509803771973</t>
   </si>
   <si>
     <t xml:space="preserve">19.1343669891357</t>
@@ -3050,16 +3050,16 @@
     <t xml:space="preserve">18.7489776611328</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9224014282227</t>
+    <t xml:space="preserve">18.9224033355713</t>
   </si>
   <si>
     <t xml:space="preserve">19.3655948638916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2692489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5350170135498</t>
+    <t xml:space="preserve">19.2692470550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5350189208984</t>
   </si>
   <si>
     <t xml:space="preserve">17.7277088165283</t>
@@ -3080,10 +3080,10 @@
     <t xml:space="preserve">20.7144432067871</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0516529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4852123260498</t>
+    <t xml:space="preserve">21.0516548156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4852142333984</t>
   </si>
   <si>
     <t xml:space="preserve">21.4370403289795</t>
@@ -3092,10 +3092,10 @@
     <t xml:space="preserve">21.8705978393555</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4005012512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1230983734131</t>
+    <t xml:space="preserve">22.4005031585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1231002807617</t>
   </si>
   <si>
     <t xml:space="preserve">23.3157920837402</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">22.5450229644775</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2078094482422</t>
+    <t xml:space="preserve">22.2078075408936</t>
   </si>
   <si>
     <t xml:space="preserve">20.4254035949707</t>
@@ -3119,13 +3119,13 @@
     <t xml:space="preserve">20.2327117919922</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4735774993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8473243713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2499809265137</t>
+    <t xml:space="preserve">20.473575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8473262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.249979019165</t>
   </si>
   <si>
     <t xml:space="preserve">18.7875175476074</t>
@@ -3134,25 +3134,25 @@
     <t xml:space="preserve">18.5948257446289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5735569000244</t>
+    <t xml:space="preserve">17.5735549926758</t>
   </si>
   <si>
     <t xml:space="preserve">18.8067874908447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4984798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2287082672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.074556350708</t>
+    <t xml:space="preserve">18.4984817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2287101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0745582580566</t>
   </si>
   <si>
     <t xml:space="preserve">18.5562877655029</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7104396820068</t>
+    <t xml:space="preserve">18.7104415893555</t>
   </si>
   <si>
     <t xml:space="preserve">18.94167137146</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">18.2865180969238</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9782104492188</t>
+    <t xml:space="preserve">17.9782085418701</t>
   </si>
   <si>
     <t xml:space="preserve">18.5755577087402</t>
@@ -3182,22 +3182,22 @@
     <t xml:space="preserve">18.9802112579346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4619407653809</t>
+    <t xml:space="preserve">19.4619426727295</t>
   </si>
   <si>
     <t xml:space="preserve">18.1709022521973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.708438873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9204025268555</t>
+    <t xml:space="preserve">17.7084369659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9204006195068</t>
   </si>
   <si>
     <t xml:space="preserve">17.6313610076904</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2094402313232</t>
+    <t xml:space="preserve">18.2094383239746</t>
   </si>
   <si>
     <t xml:space="preserve">18.2479782104492</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">17.669900894165</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3423252105713</t>
+    <t xml:space="preserve">17.3423233032227</t>
   </si>
   <si>
     <t xml:space="preserve">16.6293621063232</t>
@@ -3218,13 +3218,13 @@
     <t xml:space="preserve">16.455940246582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.205436706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0512828826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2247085571289</t>
+    <t xml:space="preserve">16.2054386138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0512847900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2247066497803</t>
   </si>
   <si>
     <t xml:space="preserve">15.4153995513916</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">15.357590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7257099151611</t>
+    <t xml:space="preserve">16.7257080078125</t>
   </si>
   <si>
     <t xml:space="preserve">16.128360748291</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">17.1110935211182</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4386711120605</t>
+    <t xml:space="preserve">17.4386730194092</t>
   </si>
   <si>
     <t xml:space="preserve">17.2459774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1688995361328</t>
+    <t xml:space="preserve">17.1689014434814</t>
   </si>
   <si>
     <t xml:space="preserve">17.1303615570068</t>
@@ -3266,13 +3266,13 @@
     <t xml:space="preserve">17.9589405059814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8838653564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.826057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5582866668701</t>
+    <t xml:space="preserve">18.8838634490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8260555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5582885742188</t>
   </si>
   <si>
     <t xml:space="preserve">20.088191986084</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">20.3290576934814</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7626152038574</t>
+    <t xml:space="preserve">20.7626171112061</t>
   </si>
   <si>
     <t xml:space="preserve">20.8589630126953</t>
@@ -3305,13 +3305,13 @@
     <t xml:space="preserve">20.8875617980957</t>
   </si>
   <si>
-    <t xml:space="preserve">20.741153717041</t>
+    <t xml:space="preserve">20.7411518096924</t>
   </si>
   <si>
     <t xml:space="preserve">20.6435470581055</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4483375549316</t>
+    <t xml:space="preserve">20.448335647583</t>
   </si>
   <si>
     <t xml:space="preserve">20.6923503875732</t>
@@ -3320,13 +3320,13 @@
     <t xml:space="preserve">20.5947437286377</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5459403991699</t>
+    <t xml:space="preserve">20.5459423065186</t>
   </si>
   <si>
     <t xml:space="preserve">20.3019275665283</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3267841339111</t>
+    <t xml:space="preserve">21.3267860412598</t>
   </si>
   <si>
     <t xml:space="preserve">20.4971389770508</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">20.1555194854736</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1067161560059</t>
+    <t xml:space="preserve">20.1067180633545</t>
   </si>
   <si>
     <t xml:space="preserve">20.2531261444092</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">21.0827713012695</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7660083770752</t>
+    <t xml:space="preserve">21.7660102844238</t>
   </si>
   <si>
     <t xml:space="preserve">21.8636150360107</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">22.5956554412842</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9372730255127</t>
+    <t xml:space="preserve">22.9372749328613</t>
   </si>
   <si>
     <t xml:space="preserve">23.083683013916</t>
@@ -3392,10 +3392,10 @@
     <t xml:space="preserve">23.4741039276123</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2300910949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7181186676025</t>
+    <t xml:space="preserve">23.2300891876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7181167602539</t>
   </si>
   <si>
     <t xml:space="preserve">23.6693153381348</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">23.6205139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7669200897217</t>
+    <t xml:space="preserve">23.7669219970703</t>
   </si>
   <si>
     <t xml:space="preserve">23.8645267486572</t>
@@ -3413,22 +3413,22 @@
     <t xml:space="preserve">23.2788944244385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3276958465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9621315002441</t>
+    <t xml:space="preserve">23.3276977539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9621295928955</t>
   </si>
   <si>
     <t xml:space="preserve">24.6941719055176</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3286094665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.986988067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7917785644531</t>
+    <t xml:space="preserve">25.3286075592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9869899749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7917766571045</t>
   </si>
   <si>
     <t xml:space="preserve">24.4989624023438</t>
@@ -3437,25 +3437,25 @@
     <t xml:space="preserve">24.5965671539307</t>
   </si>
   <si>
-    <t xml:space="preserve">24.450159072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3037509918213</t>
+    <t xml:space="preserve">24.4501571655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3037490844727</t>
   </si>
   <si>
     <t xml:space="preserve">24.0109348297119</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7420635223389</t>
+    <t xml:space="preserve">22.7420616149902</t>
   </si>
   <si>
     <t xml:space="preserve">22.644458770752</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1812877655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8884735107422</t>
+    <t xml:space="preserve">23.1812896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8884716033936</t>
   </si>
   <si>
     <t xml:space="preserve">23.0348796844482</t>
@@ -3464,10 +3464,10 @@
     <t xml:space="preserve">23.1324863433838</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0597381591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2549476623535</t>
+    <t xml:space="preserve">24.0597362518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2549495697021</t>
   </si>
   <si>
     <t xml:space="preserve">24.3525543212891</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">22.3516426086426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9612216949463</t>
+    <t xml:space="preserve">21.9612197875977</t>
   </si>
   <si>
     <t xml:space="preserve">21.9124183654785</t>
@@ -3488,19 +3488,19 @@
     <t xml:space="preserve">22.3028392791748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5468521118164</t>
+    <t xml:space="preserve">22.546854019165</t>
   </si>
   <si>
     <t xml:space="preserve">22.7908668518066</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4980506896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6932601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6684055328369</t>
+    <t xml:space="preserve">22.4980487823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6932621002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6684036254883</t>
   </si>
   <si>
     <t xml:space="preserve">21.5707988739014</t>
@@ -3524,16 +3524,16 @@
     <t xml:space="preserve">21.4731941223145</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2291812896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0339679718018</t>
+    <t xml:space="preserve">21.2291793823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0339698791504</t>
   </si>
   <si>
     <t xml:space="preserve">21.1803779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0100231170654</t>
+    <t xml:space="preserve">22.0100212097168</t>
   </si>
   <si>
     <t xml:space="preserve">22.107629776001</t>
@@ -3548,7 +3548,7 @@
     <t xml:space="preserve">24.2061443328857</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1821994781494</t>
+    <t xml:space="preserve">25.1821975708008</t>
   </si>
   <si>
     <t xml:space="preserve">26.2558574676514</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">26.0118446350098</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8654365539551</t>
+    <t xml:space="preserve">25.8654384613037</t>
   </si>
   <si>
     <t xml:space="preserve">25.8166351318359</t>
@@ -3575,13 +3575,13 @@
     <t xml:space="preserve">27.0855045318604</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4022674560547</t>
+    <t xml:space="preserve">26.4022655487061</t>
   </si>
   <si>
     <t xml:space="preserve">26.548677444458</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4750156402588</t>
+    <t xml:space="preserve">25.4750175476074</t>
   </si>
   <si>
     <t xml:space="preserve">24.5477638244629</t>
@@ -3590,10 +3590,10 @@
     <t xml:space="preserve">24.88938331604</t>
   </si>
   <si>
-    <t xml:space="preserve">24.157341003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4013557434082</t>
+    <t xml:space="preserve">24.1573429107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4013576507568</t>
   </si>
   <si>
     <t xml:space="preserve">24.7429752349854</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">25.5726222991943</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6702270507812</t>
+    <t xml:space="preserve">25.6702251434326</t>
   </si>
   <si>
     <t xml:space="preserve">25.5238170623779</t>
@@ -4578,6 +4578,9 @@
   </si>
   <si>
     <t xml:space="preserve">48.2000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2999992370605</t>
   </si>
 </sst>
 </file>
@@ -69734,7 +69737,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6494444444</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>52721</v>
@@ -69755,6 +69758,32 @@
         <v>1521</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6494791667</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>81934</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>48.2999992370605</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>47.1500015258789</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>48.0499992370605</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>47.2999992370605</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1522</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6962585449219</t>
+    <t xml:space="preserve">15.6962604522705</t>
   </si>
   <si>
     <t xml:space="preserve">DAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8255262374878</t>
+    <t xml:space="preserve">15.8255271911621</t>
   </si>
   <si>
     <t xml:space="preserve">15.3269376754761</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6344556808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3112964630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0343027114868</t>
+    <t xml:space="preserve">14.6344566345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.311297416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0343046188354</t>
   </si>
   <si>
     <t xml:space="preserve">14.3851613998413</t>
@@ -71,19 +71,19 @@
     <t xml:space="preserve">13.1940927505493</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8801679611206</t>
+    <t xml:space="preserve">12.8801670074463</t>
   </si>
   <si>
     <t xml:space="preserve">12.9724988937378</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3723449707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0371294021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2217903137207</t>
+    <t xml:space="preserve">12.3723459243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0371313095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2217922210693</t>
   </si>
   <si>
     <t xml:space="preserve">16.0009536743164</t>
@@ -92,64 +92,64 @@
     <t xml:space="preserve">16.1579151153564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.434907913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1948490142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4718379974365</t>
+    <t xml:space="preserve">16.4349098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1948509216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4718399047852</t>
   </si>
   <si>
     <t xml:space="preserve">17.2289524078369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7119026184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5762300491333</t>
+    <t xml:space="preserve">16.7119007110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5762310028076</t>
   </si>
   <si>
     <t xml:space="preserve">16.2133140563965</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4100341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.040714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0499458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4562005996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2069082260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1053419113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0194187164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3425788879395</t>
+    <t xml:space="preserve">15.4100360870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0407133102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0499448776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.456202507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2069063186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1053428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0194206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3425807952881</t>
   </si>
   <si>
     <t xml:space="preserve">16.8780975341797</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0350589752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1735572814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0812244415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8226985931396</t>
+    <t xml:space="preserve">17.0350608825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1735534667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.081226348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.822696685791</t>
   </si>
   <si>
     <t xml:space="preserve">16.4626083374023</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">16.4533729553223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9427299499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7488346099854</t>
+    <t xml:space="preserve">16.9427280426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.748836517334</t>
   </si>
   <si>
     <t xml:space="preserve">17.293586730957</t>
@@ -173,172 +173,172 @@
     <t xml:space="preserve">17.4874820709229</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5521144866943</t>
+    <t xml:space="preserve">17.5521125793457</t>
   </si>
   <si>
     <t xml:space="preserve">16.6472721099854</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3397521972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6352100372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9888973236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3766841888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5798110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1273918151855</t>
+    <t xml:space="preserve">17.3397541046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6352119445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9888954162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3766822814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5798149108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1273899078369</t>
   </si>
   <si>
     <t xml:space="preserve">16.3241119384766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6657371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0535259246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4043827056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6842041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6380367279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2381896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.68137550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7552394866943</t>
+    <t xml:space="preserve">16.665735244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.053524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4043865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6842021942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6380348205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.238187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6813774108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.755241394043</t>
   </si>
   <si>
     <t xml:space="preserve">17.5244140625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9860725402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2353630065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1430320739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9122009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7183074951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4661865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.530818939209</t>
+    <t xml:space="preserve">17.9860649108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2353649139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.143030166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.912202835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7183094024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4661884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5308227539062</t>
   </si>
   <si>
     <t xml:space="preserve">18.5585231781006</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2168941497803</t>
+    <t xml:space="preserve">18.2168960571289</t>
   </si>
   <si>
     <t xml:space="preserve">18.4477214813232</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1522636413574</t>
+    <t xml:space="preserve">18.1522655487061</t>
   </si>
   <si>
     <t xml:space="preserve">18.0137672424316</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5890426635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2658920288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6075077056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.284351348877</t>
+    <t xml:space="preserve">17.5890445709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.26589012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6075115203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2843532562256</t>
   </si>
   <si>
     <t xml:space="preserve">17.1920223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8873348236084</t>
+    <t xml:space="preserve">16.8873310089111</t>
   </si>
   <si>
     <t xml:space="preserve">16.9519634246826</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6749687194824</t>
+    <t xml:space="preserve">16.6749668121338</t>
   </si>
   <si>
     <t xml:space="preserve">16.4256763458252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2594795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3610458374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8596324920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5641708374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5272407531738</t>
+    <t xml:space="preserve">16.2594776153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3610420227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8596305847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5641746520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5272388458252</t>
   </si>
   <si>
     <t xml:space="preserve">16.277946472168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4782466888428</t>
+    <t xml:space="preserve">17.4782485961914</t>
   </si>
   <si>
     <t xml:space="preserve">16.6288051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6103401184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3582172393799</t>
+    <t xml:space="preserve">16.6103382110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3582191467285</t>
   </si>
   <si>
     <t xml:space="preserve">17.1089248657227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1550903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9178552627563</t>
+    <t xml:space="preserve">17.1550884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9178533554077</t>
   </si>
   <si>
     <t xml:space="preserve">15.9547891616821</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0591764450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8652811050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1699743270874</t>
+    <t xml:space="preserve">15.059175491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8652830123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.169976234436</t>
   </si>
   <si>
     <t xml:space="preserve">15.4377336502075</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">16.0655860900879</t>
   </si>
   <si>
-    <t xml:space="preserve">15.086874961853</t>
+    <t xml:space="preserve">15.0868759155273</t>
   </si>
   <si>
     <t xml:space="preserve">14.5513582229614</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">14.985312461853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.62522315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7821846008301</t>
+    <t xml:space="preserve">14.6252212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7821836471558</t>
   </si>
   <si>
     <t xml:space="preserve">15.5115985870361</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1330394744873</t>
+    <t xml:space="preserve">15.1330404281616</t>
   </si>
   <si>
     <t xml:space="preserve">14.72678565979</t>
@@ -374,16 +374,16 @@
     <t xml:space="preserve">14.0989360809326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.357460975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7544860839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.502368927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4192676544189</t>
+    <t xml:space="preserve">14.3574628829956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7544851303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5023651123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4192686080933</t>
   </si>
   <si>
     <t xml:space="preserve">15.6039295196533</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">15.3546361923218</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4285001754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4008007049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4839000701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2502498626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7239599227905</t>
+    <t xml:space="preserve">15.4285039901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4007997512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4839019775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2502479553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7239608764648</t>
   </si>
   <si>
     <t xml:space="preserve">15.4931335449219</t>
@@ -413,70 +413,70 @@
     <t xml:space="preserve">16.2317810058594</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9363241195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1856155395508</t>
+    <t xml:space="preserve">15.9363222122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1856136322021</t>
   </si>
   <si>
     <t xml:space="preserve">16.2871799468994</t>
   </si>
   <si>
-    <t xml:space="preserve">16.176383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0932846069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2566528320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9242649078369</t>
+    <t xml:space="preserve">16.1763782501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0932884216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2566566467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9242610931396</t>
   </si>
   <si>
     <t xml:space="preserve">16.7211360931396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7580623626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7275409698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2751216888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1458549499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3120498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4505500793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.204080581665</t>
+    <t xml:space="preserve">16.7580680847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7275447845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2751178741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1458568572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3120536804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4505481719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2040786743164</t>
   </si>
   <si>
     <t xml:space="preserve">15.890154838562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8624563217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9270896911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0563526153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7424249649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7701234817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6685609817505</t>
+    <t xml:space="preserve">15.8624544143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270877838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0563488006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7424240112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7701244354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6685600280762</t>
   </si>
   <si>
     <t xml:space="preserve">15.5946960449219</t>
@@ -485,28 +485,28 @@
     <t xml:space="preserve">15.7147274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1394481658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8134632110596</t>
+    <t xml:space="preserve">16.1394500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8134613037109</t>
   </si>
   <si>
     <t xml:space="preserve">16.1671504974365</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6408615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6500968933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8070602416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4654331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.262303352356</t>
+    <t xml:space="preserve">15.6408634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6500949859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8070611953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4654350280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2623052597046</t>
   </si>
   <si>
     <t xml:space="preserve">15.3366203308105</t>
@@ -515,13 +515,13 @@
     <t xml:space="preserve">15.4109344482422</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6524572372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7360591888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8939771652222</t>
+    <t xml:space="preserve">15.652455329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7360610961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8939790725708</t>
   </si>
   <si>
     <t xml:space="preserve">15.6245889663696</t>
@@ -530,79 +530,79 @@
     <t xml:space="preserve">15.0765199661255</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4295148849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5224046707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5131158828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1601247787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8661079406738</t>
+    <t xml:space="preserve">15.4295139312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5224084854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131168365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1601238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8661088943481</t>
   </si>
   <si>
     <t xml:space="preserve">16.3305740356445</t>
   </si>
   <si>
-    <t xml:space="preserve">15.931134223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4945373535156</t>
+    <t xml:space="preserve">15.9311332702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4945363998413</t>
   </si>
   <si>
     <t xml:space="preserve">15.6060094833374</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3180418014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8846921920776</t>
+    <t xml:space="preserve">15.318042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8846893310547</t>
   </si>
   <si>
     <t xml:space="preserve">16.0518970489502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8382406234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5813846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.185188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2595043182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1387424468994</t>
+    <t xml:space="preserve">15.8382396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5813865661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1851902008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2595024108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.138744354248</t>
   </si>
   <si>
     <t xml:space="preserve">17.2223472595215</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0272731781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9529552459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4884929656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0922985076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9065132141113</t>
+    <t xml:space="preserve">17.0272693634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9529590606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4884910583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0922966003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9065113067627</t>
   </si>
   <si>
     <t xml:space="preserve">17.1666107177734</t>
   </si>
   <si>
-    <t xml:space="preserve">17.742546081543</t>
+    <t xml:space="preserve">17.7425479888916</t>
   </si>
   <si>
     <t xml:space="preserve">17.9004669189453</t>
@@ -614,16 +614,16 @@
     <t xml:space="preserve">17.8818855285645</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4299545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9037075042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9501571655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5539588928223</t>
+    <t xml:space="preserve">18.42995262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9037094116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9501552581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.553955078125</t>
   </si>
   <si>
     <t xml:space="preserve">19.6282711029053</t>
@@ -635,25 +635,25 @@
     <t xml:space="preserve">18.9129981994629</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4610633850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3310146331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1823844909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0802040100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8572578430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0151767730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9408664703369</t>
+    <t xml:space="preserve">19.461067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3310165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1823863983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0802059173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8572616577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0151805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9408626556396</t>
   </si>
   <si>
     <t xml:space="preserve">18.9315757751465</t>
@@ -662,25 +662,25 @@
     <t xml:space="preserve">18.7550792694092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5785808563232</t>
+    <t xml:space="preserve">18.5785827636719</t>
   </si>
   <si>
     <t xml:space="preserve">18.4020881652832</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1141166687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4578247070312</t>
+    <t xml:space="preserve">18.1141185760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4578227996826</t>
   </si>
   <si>
     <t xml:space="preserve">18.5321388244629</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4671096801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3742237091064</t>
+    <t xml:space="preserve">18.4671115875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3742198944092</t>
   </si>
   <si>
     <t xml:space="preserve">18.4856910705566</t>
@@ -689,16 +689,16 @@
     <t xml:space="preserve">18.2813262939453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3277702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5135593414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6157379150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6250305175781</t>
+    <t xml:space="preserve">18.3277721405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.513557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6157398223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6250286102295</t>
   </si>
   <si>
     <t xml:space="preserve">18.7272109985352</t>
@@ -707,28 +707,28 @@
     <t xml:space="preserve">19.0430469512939</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4146194458008</t>
+    <t xml:space="preserve">19.4146175384521</t>
   </si>
   <si>
     <t xml:space="preserve">19.0894947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">19.126651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3681735992432</t>
+    <t xml:space="preserve">19.1266479492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3681716918945</t>
   </si>
   <si>
     <t xml:space="preserve">19.4517765045166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9594440460205</t>
+    <t xml:space="preserve">18.9594459533691</t>
   </si>
   <si>
     <t xml:space="preserve">19.2474117279053</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5075130462646</t>
+    <t xml:space="preserve">19.507511138916</t>
   </si>
   <si>
     <t xml:space="preserve">19.098783493042</t>
@@ -737,19 +737,19 @@
     <t xml:space="preserve">19.2195453643799</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3495941162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0337581634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2288360595703</t>
+    <t xml:space="preserve">19.3495960235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0337600708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.228832244873</t>
   </si>
   <si>
     <t xml:space="preserve">19.3867530822754</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2845687866211</t>
+    <t xml:space="preserve">19.2845706939697</t>
   </si>
   <si>
     <t xml:space="preserve">19.9162406921387</t>
@@ -758,58 +758,58 @@
     <t xml:space="preserve">20.0091342926025</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3807067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6222286224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8544597625732</t>
+    <t xml:space="preserve">20.3807048797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6222305297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8544578552246</t>
   </si>
   <si>
     <t xml:space="preserve">20.9659309387207</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9473533630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1484718322754</t>
+    <t xml:space="preserve">20.9473495483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.148473739624</t>
   </si>
   <si>
     <t xml:space="preserve">20.6129379272461</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3899955749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2506561279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5757827758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6500930786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6036472320557</t>
+    <t xml:space="preserve">20.3899936676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2506542205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5757789611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6500968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6036491394043</t>
   </si>
   <si>
     <t xml:space="preserve">20.5014667510986</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5293350219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6593856811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4828853607178</t>
+    <t xml:space="preserve">20.529333114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6593818664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4828872680664</t>
   </si>
   <si>
     <t xml:space="preserve">20.8172988891602</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8637504577637</t>
+    <t xml:space="preserve">20.863748550415</t>
   </si>
   <si>
     <t xml:space="preserve">20.455020904541</t>
@@ -818,37 +818,37 @@
     <t xml:space="preserve">20.7801475524902</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6440448760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.495418548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3653678894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3189220428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1331405639648</t>
+    <t xml:space="preserve">21.6440486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4954204559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3653717041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3189258575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1331367492676</t>
   </si>
   <si>
     <t xml:space="preserve">21.1238498687744</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9287719726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2724781036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1052684783936</t>
+    <t xml:space="preserve">20.9287738800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2724742889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1052703857422</t>
   </si>
   <si>
     <t xml:space="preserve">21.3467903137207</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2260322570801</t>
+    <t xml:space="preserve">21.2260303497314</t>
   </si>
   <si>
     <t xml:space="preserve">20.6408042907715</t>
@@ -857,61 +857,61 @@
     <t xml:space="preserve">21.1702976226807</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9566421508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.114559173584</t>
+    <t xml:space="preserve">20.9566402435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1145610809326</t>
   </si>
   <si>
     <t xml:space="preserve">21.2538986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2446117401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3375015258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2817668914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9380626678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1795806884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7336959838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3156814575195</t>
+    <t xml:space="preserve">21.2446098327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3375034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2817649841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9380645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1795864105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7336978912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3156795501709</t>
   </si>
   <si>
     <t xml:space="preserve">20.3992824554443</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4085731506348</t>
+    <t xml:space="preserve">20.4085750579834</t>
   </si>
   <si>
     <t xml:space="preserve">20.3249683380127</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6315174102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2785263061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.046293258667</t>
+    <t xml:space="preserve">20.6315155029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2785243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0462894439697</t>
   </si>
   <si>
     <t xml:space="preserve">20.2134990692139</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7954788208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9069519042969</t>
+    <t xml:space="preserve">19.7954807281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9069538116455</t>
   </si>
   <si>
     <t xml:space="preserve">20.2692337036133</t>
@@ -920,46 +920,46 @@
     <t xml:space="preserve">20.2971019744873</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5479125976562</t>
+    <t xml:space="preserve">20.5479145050049</t>
   </si>
   <si>
     <t xml:space="preserve">20.4364414215088</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9533977508545</t>
+    <t xml:space="preserve">19.9533958435059</t>
   </si>
   <si>
     <t xml:space="preserve">19.8326377868652</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8883743286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7211647033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9255294799805</t>
+    <t xml:space="preserve">19.8883724212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7211685180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9255313873291</t>
   </si>
   <si>
     <t xml:space="preserve">20.0741577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9998455047607</t>
+    <t xml:space="preserve">19.9998435974121</t>
   </si>
   <si>
     <t xml:space="preserve">20.1113166809082</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6747188568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6686763763428</t>
+    <t xml:space="preserve">19.6747226715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6686744689941</t>
   </si>
   <si>
     <t xml:space="preserve">20.2413654327393</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9719772338867</t>
+    <t xml:space="preserve">19.9719734191895</t>
   </si>
   <si>
     <t xml:space="preserve">19.7304553985596</t>
@@ -971,82 +971,82 @@
     <t xml:space="preserve">20.1298961639404</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4921760559082</t>
+    <t xml:space="preserve">20.4921779632568</t>
   </si>
   <si>
     <t xml:space="preserve">20.8451709747314</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3435497283936</t>
+    <t xml:space="preserve">20.3435478210449</t>
   </si>
   <si>
     <t xml:space="preserve">20.5664901733398</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8916168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1981639862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7244110107422</t>
+    <t xml:space="preserve">20.8916149139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1981601715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7244091033936</t>
   </si>
   <si>
     <t xml:space="preserve">20.4735984802246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3342590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3714179992676</t>
+    <t xml:space="preserve">20.3342609405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3714160919189</t>
   </si>
   <si>
     <t xml:space="preserve">19.8790836334229</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8419322967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.767614364624</t>
+    <t xml:space="preserve">19.841926574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7676124572754</t>
   </si>
   <si>
     <t xml:space="preserve">19.9812660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">20.092737197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5200443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9905548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5353813171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2567005157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7829475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8386859893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6343193054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9966011047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6807670593262</t>
+    <t xml:space="preserve">20.0927391052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5200462341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9905586242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.53537940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2566986083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7829456329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8386840820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6343173980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9965972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6807651519775</t>
   </si>
   <si>
     <t xml:space="preserve">18.5600032806396</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6621894836426</t>
+    <t xml:space="preserve">18.6621875762939</t>
   </si>
   <si>
     <t xml:space="preserve">18.4392433166504</t>
@@ -1055,31 +1055,31 @@
     <t xml:space="preserve">18.8108158111572</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1359386444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9779319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9499282836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5298519134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3058204650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9044132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8484039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6430339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6710414886475</t>
+    <t xml:space="preserve">19.1359424591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.977933883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9499263763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5298538208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3058166503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9044151306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8484058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6430320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6710395812988</t>
   </si>
   <si>
     <t xml:space="preserve">17.9417514801025</t>
@@ -1091,25 +1091,25 @@
     <t xml:space="preserve">17.9697570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2684783935547</t>
+    <t xml:space="preserve">18.2684745788574</t>
   </si>
   <si>
     <t xml:space="preserve">18.4645080566406</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5858631134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4084987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1657905578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4925117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3618259429932</t>
+    <t xml:space="preserve">18.585865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4084968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1657886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4925155639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3618240356445</t>
   </si>
   <si>
     <t xml:space="preserve">18.2218017578125</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">18.6698780059814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7725620269775</t>
+    <t xml:space="preserve">18.7725639343262</t>
   </si>
   <si>
     <t xml:space="preserve">18.6978816986084</t>
@@ -1130,22 +1130,22 @@
     <t xml:space="preserve">18.6138687133789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3524894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3804969787598</t>
+    <t xml:space="preserve">18.3524875640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3804950714111</t>
   </si>
   <si>
     <t xml:space="preserve">18.4458389282227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4831790924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4738445281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6605434417725</t>
+    <t xml:space="preserve">18.4831809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4738426208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6605415344238</t>
   </si>
   <si>
     <t xml:space="preserve">18.7072162628174</t>
@@ -1154,43 +1154,43 @@
     <t xml:space="preserve">18.5951976776123</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3898315429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5018463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9032535552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1833000183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4633445739746</t>
+    <t xml:space="preserve">18.3898334503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5018482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9032516479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1832981109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4633483886719</t>
   </si>
   <si>
     <t xml:space="preserve">19.7433967590332</t>
   </si>
   <si>
-    <t xml:space="preserve">20.536865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2836570739746</t>
+    <t xml:space="preserve">20.5368633270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2836589813232</t>
   </si>
   <si>
     <t xml:space="preserve">21.5637111663818</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5170364379883</t>
+    <t xml:space="preserve">21.517032623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.3770122528076</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6103820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4703617095947</t>
+    <t xml:space="preserve">21.6103839874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4703598022461</t>
   </si>
   <si>
     <t xml:space="preserve">21.7504062652588</t>
@@ -1202,43 +1202,43 @@
     <t xml:space="preserve">21.0036144256592</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4435176849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0502853393555</t>
+    <t xml:space="preserve">20.4435157775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0502872467041</t>
   </si>
   <si>
     <t xml:space="preserve">20.6302146911621</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7702407836914</t>
+    <t xml:space="preserve">20.7702388763428</t>
   </si>
   <si>
     <t xml:space="preserve">20.7235641479492</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0969638824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1903114318848</t>
+    <t xml:space="preserve">21.0969619750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1903133392334</t>
   </si>
   <si>
     <t xml:space="preserve">21.1436367034912</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8635883331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6768913269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7037315368652</t>
+    <t xml:space="preserve">20.8635902404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6768894195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7037334442139</t>
   </si>
   <si>
     <t xml:space="preserve">22.2171535491943</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8904323577881</t>
+    <t xml:space="preserve">21.8904342651367</t>
   </si>
   <si>
     <t xml:space="preserve">22.0771312713623</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">20.8169136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2369842529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3034915924072</t>
+    <t xml:space="preserve">21.2369861602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3034954071045</t>
   </si>
   <si>
     <t xml:space="preserve">20.2101440429688</t>
@@ -1262,16 +1262,16 @@
     <t xml:space="preserve">20.9102630615234</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5835418701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.956937789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3303356170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3968410491943</t>
+    <t xml:space="preserve">20.5835380554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9569396972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3303375244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3968391418457</t>
   </si>
   <si>
     <t xml:space="preserve">20.4901905059814</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">19.0432739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">19.136625289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3233222961426</t>
+    <t xml:space="preserve">19.1366233825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3233242034912</t>
   </si>
   <si>
     <t xml:space="preserve">19.7900714874268</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6033725738525</t>
+    <t xml:space="preserve">19.6033744812012</t>
   </si>
   <si>
     <t xml:space="preserve">20.3501682281494</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">20.2568187713623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9767684936523</t>
+    <t xml:space="preserve">19.9767723083496</t>
   </si>
   <si>
     <t xml:space="preserve">20.1634693145752</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">19.9300956726074</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4166717529297</t>
+    <t xml:space="preserve">19.4166736602783</t>
   </si>
   <si>
     <t xml:space="preserve">19.556697845459</t>
@@ -1325,16 +1325,16 @@
     <t xml:space="preserve">19.5100231170654</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6500473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6967220306396</t>
+    <t xml:space="preserve">19.6500492095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.696720123291</t>
   </si>
   <si>
     <t xml:space="preserve">19.2766494750977</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2299747467041</t>
+    <t xml:space="preserve">19.2299728393555</t>
   </si>
   <si>
     <t xml:space="preserve">19.3699989318848</t>
@@ -1346,22 +1346,22 @@
     <t xml:space="preserve">21.4236869812012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0701179504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7177143096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3093004226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7013673782349</t>
+    <t xml:space="preserve">20.0701198577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.717716217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3092985153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7013683319092</t>
   </si>
   <si>
     <t xml:space="preserve">14.7678737640381</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4691553115845</t>
+    <t xml:space="preserve">14.4691543579102</t>
   </si>
   <si>
     <t xml:space="preserve">14.8052129745483</t>
@@ -1373,52 +1373,52 @@
     <t xml:space="preserve">15.6266860961914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0000877380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333385467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3279695510864</t>
+    <t xml:space="preserve">16.0000858306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333375930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3279705047607</t>
   </si>
   <si>
     <t xml:space="preserve">15.4586582183838</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8693981170654</t>
+    <t xml:space="preserve">15.8693952560425</t>
   </si>
   <si>
     <t xml:space="preserve">15.7947177886963</t>
   </si>
   <si>
-    <t xml:space="preserve">15.664026260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5893478393555</t>
+    <t xml:space="preserve">15.6640291213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5893487930298</t>
   </si>
   <si>
     <t xml:space="preserve">15.3839797973633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0105819702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8602876663208</t>
+    <t xml:space="preserve">15.0105829238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8602886199951</t>
   </si>
   <si>
     <t xml:space="preserve">14.5784883499146</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4094066619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4469804763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9166479110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9354343414307</t>
+    <t xml:space="preserve">14.4094076156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4469814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9166488647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.935435295105</t>
   </si>
   <si>
     <t xml:space="preserve">14.6536350250244</t>
@@ -1436,13 +1436,13 @@
     <t xml:space="preserve">14.0712461471558</t>
   </si>
   <si>
-    <t xml:space="preserve">13.920952796936</t>
+    <t xml:space="preserve">13.9209537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.6015777587891</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7330856323242</t>
+    <t xml:space="preserve">13.7330846786499</t>
   </si>
   <si>
     <t xml:space="preserve">14.3342609405518</t>
@@ -1451,28 +1451,28 @@
     <t xml:space="preserve">14.1651802062988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1463928222656</t>
+    <t xml:space="preserve">14.1463937759399</t>
   </si>
   <si>
     <t xml:space="preserve">14.2215404510498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9585266113281</t>
+    <t xml:space="preserve">13.9585247039795</t>
   </si>
   <si>
     <t xml:space="preserve">13.6391534805298</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6203641891479</t>
+    <t xml:space="preserve">13.6203651428223</t>
   </si>
   <si>
     <t xml:space="preserve">13.7894468307495</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0524606704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2027540206909</t>
+    <t xml:space="preserve">14.0524597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2027530670166</t>
   </si>
   <si>
     <t xml:space="preserve">14.5221281051636</t>
@@ -1484,61 +1484,61 @@
     <t xml:space="preserve">15.2172374725342</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1233024597168</t>
+    <t xml:space="preserve">15.1233034133911</t>
   </si>
   <si>
     <t xml:space="preserve">15.0293684005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0669431686401</t>
+    <t xml:space="preserve">15.0669441223145</t>
   </si>
   <si>
     <t xml:space="preserve">14.8978614807129</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1045150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1608762741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984491348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5366106033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9687032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8141059875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8892517089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9080390930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4947319030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.419584274292</t>
+    <t xml:space="preserve">15.1045160293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1608753204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1984481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366115570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9687042236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8141040802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.889253616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9080371856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4947299957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4195861816406</t>
   </si>
   <si>
     <t xml:space="preserve">16.2692909240723</t>
   </si>
   <si>
-    <t xml:space="preserve">16.363224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9874925613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8747701644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8184118270874</t>
+    <t xml:space="preserve">16.3632278442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.987491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8747692108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8184108734131</t>
   </si>
   <si>
     <t xml:space="preserve">16.1377849578857</t>
@@ -1547,25 +1547,25 @@
     <t xml:space="preserve">16.1565723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2505054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6262397766113</t>
+    <t xml:space="preserve">16.2505035400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.62624168396</t>
   </si>
   <si>
     <t xml:space="preserve">16.5135192871094</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2880802154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4383697509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.457160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2317199707031</t>
+    <t xml:space="preserve">16.2880783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4383716583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4571571350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2317161560059</t>
   </si>
   <si>
     <t xml:space="preserve">16.6074523925781</t>
@@ -1574,40 +1574,40 @@
     <t xml:space="preserve">16.7201728820801</t>
   </si>
   <si>
-    <t xml:space="preserve">16.475944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3256511688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8559837341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9499168395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9311304092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1189994812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0062770843506</t>
+    <t xml:space="preserve">16.4759483337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3256530761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8559827804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9499158859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9311275482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1190013885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0062808990479</t>
   </si>
   <si>
     <t xml:space="preserve">16.3444385528564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4008007049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5323047637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7765331268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9456119537354</t>
+    <t xml:space="preserve">16.4007949829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5323066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7765350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9456157684326</t>
   </si>
   <si>
     <t xml:space="preserve">17.4716396331787</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">18.2794704437256</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2606830596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2418975830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1103897094727</t>
+    <t xml:space="preserve">18.260684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2418956756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.110387802124</t>
   </si>
   <si>
     <t xml:space="preserve">17.5279998779297</t>
@@ -1631,13 +1631,13 @@
     <t xml:space="preserve">17.1334800720215</t>
   </si>
   <si>
-    <t xml:space="preserve">17.001974105835</t>
+    <t xml:space="preserve">17.0019760131836</t>
   </si>
   <si>
     <t xml:space="preserve">16.9831867218018</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7389583587646</t>
+    <t xml:space="preserve">16.7389602661133</t>
   </si>
   <si>
     <t xml:space="preserve">16.6450233459473</t>
@@ -1646,34 +1646,34 @@
     <t xml:space="preserve">16.9643993377686</t>
   </si>
   <si>
-    <t xml:space="preserve">16.832893371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0583305358887</t>
+    <t xml:space="preserve">16.8328952789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0583324432373</t>
   </si>
   <si>
     <t xml:space="preserve">17.1522674560547</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2274150848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7577476501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2129306793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4990367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5178241729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4614629745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1796607971191</t>
+    <t xml:space="preserve">17.2274131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7577438354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2129325866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4990348815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.517822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.461462020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1796617507935</t>
   </si>
   <si>
     <t xml:space="preserve">14.6912078857422</t>
@@ -1688,10 +1688,10 @@
     <t xml:space="preserve">14.7663545608521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9730081558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8415021896362</t>
+    <t xml:space="preserve">14.9730072021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8415012359619</t>
   </si>
   <si>
     <t xml:space="preserve">14.5033407211304</t>
@@ -1703,49 +1703,49 @@
     <t xml:space="preserve">14.3718338012695</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8227157592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.559700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4657678604126</t>
+    <t xml:space="preserve">14.8227138519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5597009658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4657669067383</t>
   </si>
   <si>
     <t xml:space="preserve">14.6348476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5741844177246</t>
+    <t xml:space="preserve">15.5741834640503</t>
   </si>
   <si>
     <t xml:space="preserve">15.405101776123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3863153457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6681175231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2360219955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5929698944092</t>
+    <t xml:space="preserve">15.3863162994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6681184768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2360239028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5929718017578</t>
   </si>
   <si>
     <t xml:space="preserve">15.4238901138306</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3299560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0481557846069</t>
+    <t xml:space="preserve">15.3299551010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0481548309326</t>
   </si>
   <si>
     <t xml:space="preserve">14.879075050354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5409135818481</t>
+    <t xml:space="preserve">14.5409126281738</t>
   </si>
   <si>
     <t xml:space="preserve">14.7851409912109</t>
@@ -1757,19 +1757,19 @@
     <t xml:space="preserve">14.2966871261597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2778997421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0900325775146</t>
+    <t xml:space="preserve">14.2779006958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0900344848633</t>
   </si>
   <si>
     <t xml:space="preserve">13.9021663665771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.770658493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4281940460205</t>
+    <t xml:space="preserve">13.7706594467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4281930923462</t>
   </si>
   <si>
     <t xml:space="preserve">14.2591142654419</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">13.8082323074341</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8458070755005</t>
+    <t xml:space="preserve">13.8458051681519</t>
   </si>
   <si>
     <t xml:space="preserve">14.0336723327637</t>
@@ -1787,22 +1787,22 @@
     <t xml:space="preserve">13.9397392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2403259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0148859024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5972747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9961004257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3675298690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.183967590332</t>
+    <t xml:space="preserve">14.2403268814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0148868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5972757339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9960994720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3675308227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1839666366577</t>
   </si>
   <si>
     <t xml:space="preserve">14.1088199615479</t>
@@ -1811,16 +1811,16 @@
     <t xml:space="preserve">14.4845542907715</t>
   </si>
   <si>
-    <t xml:space="preserve">14.991795539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2923831939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0758924484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0569295883179</t>
+    <t xml:space="preserve">14.9917945861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2923822402954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0758934020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0569305419922</t>
   </si>
   <si>
     <t xml:space="preserve">14.9052228927612</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">14.8104057312012</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8862590789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3793077468872</t>
+    <t xml:space="preserve">14.8862600326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3793087005615</t>
   </si>
   <si>
     <t xml:space="preserve">15.6827230453491</t>
@@ -1841,13 +1841,13 @@
     <t xml:space="preserve">16.4602222442627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3274765014648</t>
+    <t xml:space="preserve">16.3274745941162</t>
   </si>
   <si>
     <t xml:space="preserve">15.7016839981079</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6637601852417</t>
+    <t xml:space="preserve">15.6637573242188</t>
   </si>
   <si>
     <t xml:space="preserve">15.5310144424438</t>
@@ -1856,28 +1856,28 @@
     <t xml:space="preserve">15.5499773025513</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4551610946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7585763931274</t>
+    <t xml:space="preserve">15.4551601409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7585754394531</t>
   </si>
   <si>
     <t xml:space="preserve">15.7965030670166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1757678985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7206497192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6068677902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6447944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0430240631104</t>
+    <t xml:space="preserve">16.1757698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.720648765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6068668365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.644793510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0430278778076</t>
   </si>
   <si>
     <t xml:space="preserve">15.9861373901367</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">15.5689420700073</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4361982345581</t>
+    <t xml:space="preserve">15.4361972808838</t>
   </si>
   <si>
     <t xml:space="preserve">15.5879058837891</t>
@@ -1901,22 +1901,22 @@
     <t xml:space="preserve">15.246563911438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1138200759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9810771942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2086381912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7535152435303</t>
+    <t xml:space="preserve">15.1138191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9810762405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2086391448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7535161972046</t>
   </si>
   <si>
     <t xml:space="preserve">14.9431505203247</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5069923400879</t>
+    <t xml:space="preserve">14.5069913864136</t>
   </si>
   <si>
     <t xml:space="preserve">14.0329074859619</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">13.9380903244019</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2225408554077</t>
+    <t xml:space="preserve">14.222541809082</t>
   </si>
   <si>
     <t xml:space="preserve">14.6018085479736</t>
@@ -1934,7 +1934,7 @@
     <t xml:space="preserve">14.7914428710938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5828447341919</t>
+    <t xml:space="preserve">14.5828456878662</t>
   </si>
   <si>
     <t xml:space="preserve">14.3932123184204</t>
@@ -1946,16 +1946,16 @@
     <t xml:space="preserve">14.6207723617554</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3363218307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2794303894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0518703460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6915645599365</t>
+    <t xml:space="preserve">14.3363208770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2794313430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0518712997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6915655136108</t>
   </si>
   <si>
     <t xml:space="preserve">13.1416263580322</t>
@@ -1970,16 +1970,16 @@
     <t xml:space="preserve">13.0847387313843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8002872467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4210186004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1744956970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9469337463379</t>
+    <t xml:space="preserve">12.8002862930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4210195541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1744947433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9469347000122</t>
   </si>
   <si>
     <t xml:space="preserve">11.4728498458862</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">10.1264495849609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95577812194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59547424316406</t>
+    <t xml:space="preserve">9.95577907562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59547519683838</t>
   </si>
   <si>
     <t xml:space="preserve">8.91279220581055</t>
@@ -2003,22 +2003,22 @@
     <t xml:space="preserve">9.41532230377197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09736728668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55248832702637</t>
+    <t xml:space="preserve">8.09736633300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55248928070068</t>
   </si>
   <si>
     <t xml:space="preserve">9.10242748260498</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1643772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7522420883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9279708862305</t>
+    <t xml:space="preserve">10.1643762588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7522411346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9279718399048</t>
   </si>
   <si>
     <t xml:space="preserve">12.8951044082642</t>
@@ -2027,13 +2027,13 @@
     <t xml:space="preserve">11.6055936813354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9608392715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9229116439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6384611129761</t>
+    <t xml:space="preserve">10.9608383178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9229125976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6384601593018</t>
   </si>
   <si>
     <t xml:space="preserve">10.06955909729</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">10.3350458145142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.61949634552</t>
+    <t xml:space="preserve">10.6194972991943</t>
   </si>
   <si>
     <t xml:space="preserve">10.7332773208618</t>
@@ -2051,16 +2051,16 @@
     <t xml:space="preserve">11.1125459671021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9039478302002</t>
+    <t xml:space="preserve">10.9039487838745</t>
   </si>
   <si>
     <t xml:space="preserve">10.5815706253052</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2023029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87992382049561</t>
+    <t xml:space="preserve">10.2023038864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87992572784424</t>
   </si>
   <si>
     <t xml:space="preserve">10.2212657928467</t>
@@ -2072,28 +2072,28 @@
     <t xml:space="preserve">10.4298639297485</t>
   </si>
   <si>
-    <t xml:space="preserve">10.771203994751</t>
+    <t xml:space="preserve">10.7712049484253</t>
   </si>
   <si>
     <t xml:space="preserve">10.7143144607544</t>
   </si>
   <si>
-    <t xml:space="preserve">10.695351600647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8091297149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8280954360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.543643951416</t>
+    <t xml:space="preserve">10.6953496932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8091306686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8280944824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5436449050903</t>
   </si>
   <si>
     <t xml:space="preserve">10.9987659454346</t>
   </si>
   <si>
-    <t xml:space="preserve">10.941873550415</t>
+    <t xml:space="preserve">10.9418745040894</t>
   </si>
   <si>
     <t xml:space="preserve">11.4918127059937</t>
@@ -2105,67 +2105,67 @@
     <t xml:space="preserve">11.0556545257568</t>
   </si>
   <si>
-    <t xml:space="preserve">11.415958404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5107765197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7952270507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0038251876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2882747650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2124214172363</t>
+    <t xml:space="preserve">11.4159593582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5107774734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7952260971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0038242340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.288275718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2124223709106</t>
   </si>
   <si>
     <t xml:space="preserve">12.0986413955688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8521184921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2263269424438</t>
+    <t xml:space="preserve">11.8521175384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2263259887695</t>
   </si>
   <si>
     <t xml:space="preserve">11.017728805542</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1883993148804</t>
+    <t xml:space="preserve">11.1883983612061</t>
   </si>
   <si>
     <t xml:space="preserve">11.0935821533203</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8849840164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7901678085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6763877868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4108991622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4488277435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6574230194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2073612213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.340106010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2832145690918</t>
+    <t xml:space="preserve">10.8849859237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.790168762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6763887405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4109001159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.448826789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6574239730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2073621749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3401050567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2832155227661</t>
   </si>
   <si>
     <t xml:space="preserve">11.0746183395386</t>
@@ -2174,10 +2174,10 @@
     <t xml:space="preserve">10.9798011779785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6005344390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3729734420776</t>
+    <t xml:space="preserve">10.6005334854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3729724884033</t>
   </si>
   <si>
     <t xml:space="preserve">10.4677896499634</t>
@@ -2186,13 +2186,13 @@
     <t xml:space="preserve">11.6435203552246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4349241256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6814460754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5297403335571</t>
+    <t xml:space="preserve">11.4349231719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6814451217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5297393798828</t>
   </si>
   <si>
     <t xml:space="preserve">11.6245574951172</t>
@@ -2219,19 +2219,19 @@
     <t xml:space="preserve">11.9658975601196</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9848613739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8141899108887</t>
+    <t xml:space="preserve">11.9848623275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.814190864563</t>
   </si>
   <si>
     <t xml:space="preserve">11.7573003768921</t>
   </si>
   <si>
-    <t xml:space="preserve">11.245288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6485805511475</t>
+    <t xml:space="preserve">11.2452898025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6485795974731</t>
   </si>
   <si>
     <t xml:space="preserve">13.653639793396</t>
@@ -2240,19 +2240,19 @@
     <t xml:space="preserve">13.3881521224976</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8622369766235</t>
+    <t xml:space="preserve">13.8622360229492</t>
   </si>
   <si>
     <t xml:space="preserve">13.5967493057251</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2364463806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4260787963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4640045166016</t>
+    <t xml:space="preserve">13.2364454269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.426079750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4640054702759</t>
   </si>
   <si>
     <t xml:space="preserve">13.1037006378174</t>
@@ -2276,16 +2276,16 @@
     <t xml:space="preserve">13.4829683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.17955493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0227890014648</t>
+    <t xml:space="preserve">13.1795539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0227870941162</t>
   </si>
   <si>
     <t xml:space="preserve">12.060715675354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3262033462524</t>
+    <t xml:space="preserve">12.3262023925781</t>
   </si>
   <si>
     <t xml:space="preserve">12.4399824142456</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">12.857177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8192501068115</t>
+    <t xml:space="preserve">12.8192510604858</t>
   </si>
   <si>
     <t xml:space="preserve">13.0468111038208</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">13.3122987747192</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4450426101685</t>
+    <t xml:space="preserve">13.4450435638428</t>
   </si>
   <si>
     <t xml:space="preserve">13.5588235855103</t>
@@ -2312,13 +2312,13 @@
     <t xml:space="preserve">13.6179904937744</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6371450424194</t>
+    <t xml:space="preserve">13.6371440887451</t>
   </si>
   <si>
     <t xml:space="preserve">13.4073047637939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4456119537354</t>
+    <t xml:space="preserve">13.445611000061</t>
   </si>
   <si>
     <t xml:space="preserve">13.3115386962891</t>
@@ -2327,16 +2327,16 @@
     <t xml:space="preserve">13.5030717849731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8478317260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8861360549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7520627975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1734371185303</t>
+    <t xml:space="preserve">13.8478307723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.886137008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7520637512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.173436164856</t>
   </si>
   <si>
     <t xml:space="preserve">14.1542825698853</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">13.9819040298462</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6946058273315</t>
+    <t xml:space="preserve">13.6946048736572</t>
   </si>
   <si>
     <t xml:space="preserve">13.4647655487061</t>
@@ -2378,19 +2378,19 @@
     <t xml:space="preserve">14.3458156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7097291946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6331157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9970273971558</t>
+    <t xml:space="preserve">14.7097282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6331148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9970283508301</t>
   </si>
   <si>
     <t xml:space="preserve">15.0353345870972</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4909839630127</t>
+    <t xml:space="preserve">16.4909858703613</t>
   </si>
   <si>
     <t xml:space="preserve">16.3377571105957</t>
@@ -2399,16 +2399,16 @@
     <t xml:space="preserve">16.1845321655273</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8206214904785</t>
+    <t xml:space="preserve">15.8206195831299</t>
   </si>
   <si>
     <t xml:space="preserve">15.9546937942505</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8014659881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6099338531494</t>
+    <t xml:space="preserve">15.8014650344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6099328994751</t>
   </si>
   <si>
     <t xml:space="preserve">15.3226337432861</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">15.437554359436</t>
   </si>
   <si>
-    <t xml:space="preserve">15.724853515625</t>
+    <t xml:space="preserve">15.7248544692993</t>
   </si>
   <si>
     <t xml:space="preserve">15.8589248657227</t>
@@ -2432,19 +2432,19 @@
     <t xml:space="preserve">16.2611446380615</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6059055328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7782859802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6825160980225</t>
+    <t xml:space="preserve">16.6059036254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.778284072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6825180053711</t>
   </si>
   <si>
     <t xml:space="preserve">16.6442108154297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7208251953125</t>
+    <t xml:space="preserve">16.7208232879639</t>
   </si>
   <si>
     <t xml:space="preserve">16.7016716003418</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">17.1421966552734</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1996574401855</t>
+    <t xml:space="preserve">17.1996555328369</t>
   </si>
   <si>
     <t xml:space="preserve">16.9889698028564</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">16.4335269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9123554229736</t>
+    <t xml:space="preserve">16.9123573303223</t>
   </si>
   <si>
     <t xml:space="preserve">16.6633644104004</t>
@@ -2480,28 +2480,28 @@
     <t xml:space="preserve">16.931510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8548965454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9657917022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0807056427002</t>
+    <t xml:space="preserve">16.8548984527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9657897949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0807075500488</t>
   </si>
   <si>
     <t xml:space="preserve">18.3105487823486</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6321239471436</t>
+    <t xml:space="preserve">19.6321258544922</t>
   </si>
   <si>
     <t xml:space="preserve">19.9194240570068</t>
   </si>
   <si>
-    <t xml:space="preserve">20.302490234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7757759094238</t>
+    <t xml:space="preserve">20.3024921417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7757740020752</t>
   </si>
   <si>
     <t xml:space="preserve">20.7334403991699</t>
@@ -2510,13 +2510,13 @@
     <t xml:space="preserve">20.4940223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1109561920166</t>
+    <t xml:space="preserve">20.1109580993652</t>
   </si>
   <si>
     <t xml:space="preserve">19.9673080444336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8715400695801</t>
+    <t xml:space="preserve">19.8715419769287</t>
   </si>
   <si>
     <t xml:space="preserve">20.0151901245117</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">20.5419063568115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.637674331665</t>
+    <t xml:space="preserve">20.6376724243164</t>
   </si>
   <si>
     <t xml:space="preserve">20.9728546142578</t>
@@ -2537,16 +2537,16 @@
     <t xml:space="preserve">20.8770885467529</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3503723144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0630722045898</t>
+    <t xml:space="preserve">20.3503742218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0630741119385</t>
   </si>
   <si>
     <t xml:space="preserve">20.9249725341797</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7278919219971</t>
+    <t xml:space="preserve">19.7278900146484</t>
   </si>
   <si>
     <t xml:space="preserve">19.4884757995605</t>
@@ -2561,7 +2561,7 @@
     <t xml:space="preserve">19.823657989502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1532917022705</t>
+    <t xml:space="preserve">19.1532936096191</t>
   </si>
   <si>
     <t xml:space="preserve">20.2546081542969</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">20.4461402893066</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2067241668701</t>
+    <t xml:space="preserve">20.2067222595215</t>
   </si>
   <si>
     <t xml:space="preserve">21.1165065765381</t>
@@ -2609,10 +2609,10 @@
     <t xml:space="preserve">21.4516868591309</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3135833740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7924156188965</t>
+    <t xml:space="preserve">22.3135852813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7924175262451</t>
   </si>
   <si>
     <t xml:space="preserve">23.3191356658936</t>
@@ -2633,31 +2633,31 @@
     <t xml:space="preserve">21.4038047790527</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8292045593262</t>
+    <t xml:space="preserve">20.8292064666748</t>
   </si>
   <si>
     <t xml:space="preserve">20.7813243865967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9305191040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5162143707275</t>
+    <t xml:space="preserve">21.9305210113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5162162780762</t>
   </si>
   <si>
     <t xml:space="preserve">23.9416179656982</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4627857208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4149017333984</t>
+    <t xml:space="preserve">23.4627838134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4148998260498</t>
   </si>
   <si>
     <t xml:space="preserve">23.1754837036133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2712478637695</t>
+    <t xml:space="preserve">23.2712497711182</t>
   </si>
   <si>
     <t xml:space="preserve">23.5106639862061</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">23.7500820159912</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6064319610596</t>
+    <t xml:space="preserve">23.6064338684082</t>
   </si>
   <si>
     <t xml:space="preserve">23.0797176361084</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">23.031831741333</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5585498809814</t>
+    <t xml:space="preserve">23.5585517883301</t>
   </si>
   <si>
     <t xml:space="preserve">22.8403034210205</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">22.6008853912354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2657032012939</t>
+    <t xml:space="preserve">22.2657012939453</t>
   </si>
   <si>
     <t xml:space="preserve">21.5953350067139</t>
@@ -2708,22 +2708,22 @@
     <t xml:space="preserve">22.1699371337891</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2289161682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8937339782715</t>
+    <t xml:space="preserve">24.2289142608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8937320709229</t>
   </si>
   <si>
     <t xml:space="preserve">24.4683303833008</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0373821258545</t>
+    <t xml:space="preserve">24.0373840332031</t>
   </si>
   <si>
     <t xml:space="preserve">23.8458480834961</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4738788604736</t>
+    <t xml:space="preserve">25.4738807678223</t>
   </si>
   <si>
     <t xml:space="preserve">25.7611770629883</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">25.8090629577637</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9527130126953</t>
+    <t xml:space="preserve">25.9527111053467</t>
   </si>
   <si>
     <t xml:space="preserve">25.665412902832</t>
@@ -2753,43 +2753,43 @@
     <t xml:space="preserve">27.4849758148193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3892116546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3413238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8680419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4905223846436</t>
+    <t xml:space="preserve">27.3892097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3413257598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8680400848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4905242919922</t>
   </si>
   <si>
     <t xml:space="preserve">27.9638080596924</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2989902496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7722721099854</t>
+    <t xml:space="preserve">28.2989883422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.772274017334</t>
   </si>
   <si>
     <t xml:space="preserve">27.6286239624023</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7243919372559</t>
+    <t xml:space="preserve">27.7243938446045</t>
   </si>
   <si>
     <t xml:space="preserve">27.5328578948975</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2455596923828</t>
+    <t xml:space="preserve">27.2455615997314</t>
   </si>
   <si>
     <t xml:space="preserve">26.9582595825195</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1497936248779</t>
+    <t xml:space="preserve">27.1497917175293</t>
   </si>
   <si>
     <t xml:space="preserve">27.0540256500244</t>
@@ -69821,7 +69821,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.649525463</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>28274</v>
@@ -69842,6 +69842,32 @@
         <v>1524</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6910300926</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>36494</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>48.4000015258789</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>47.3499984741211</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>48.0499992370605</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>47.7999992370605</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1524</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="1526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="1527">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6962604522705</t>
+    <t xml:space="preserve">15.6962623596191</t>
   </si>
   <si>
     <t xml:space="preserve">DAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8255224227905</t>
+    <t xml:space="preserve">15.8255233764648</t>
   </si>
   <si>
     <t xml:space="preserve">15.3269376754761</t>
@@ -53,85 +53,85 @@
     <t xml:space="preserve">14.6344566345215</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3112964630127</t>
+    <t xml:space="preserve">14.311297416687</t>
   </si>
   <si>
     <t xml:space="preserve">14.0343046188354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3851594924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1358690261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9604387283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.194091796875</t>
+    <t xml:space="preserve">14.385160446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1358699798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9604396820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1940927505493</t>
   </si>
   <si>
     <t xml:space="preserve">12.8801670074463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9724969863892</t>
+    <t xml:space="preserve">12.9724998474121</t>
   </si>
   <si>
     <t xml:space="preserve">12.3723459243774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0371313095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.221791267395</t>
+    <t xml:space="preserve">13.0371294021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2217922210693</t>
   </si>
   <si>
     <t xml:space="preserve">16.0009536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1579132080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.434907913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1948509216309</t>
+    <t xml:space="preserve">16.1579170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4349098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1948490142822</t>
   </si>
   <si>
     <t xml:space="preserve">16.4718418121338</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2289543151855</t>
+    <t xml:space="preserve">17.2289562225342</t>
   </si>
   <si>
     <t xml:space="preserve">16.7119007110596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5762319564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2133121490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4100332260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0407123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0499429702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4561996459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2069072723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1053438186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0194187164307</t>
+    <t xml:space="preserve">15.5762310028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2133140563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4100322723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0407104492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0499439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4562015533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2069063186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1053428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0194206237793</t>
   </si>
   <si>
     <t xml:space="preserve">16.3425788879395</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">16.8780994415283</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0350608825684</t>
+    <t xml:space="preserve">17.0350589752197</t>
   </si>
   <si>
     <t xml:space="preserve">17.1735553741455</t>
@@ -149,55 +149,55 @@
     <t xml:space="preserve">17.081226348877</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8226985931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4626064300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4533748626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9427299499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7488288879395</t>
+    <t xml:space="preserve">16.822696685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4626083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4533729553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9427318572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7488327026367</t>
   </si>
   <si>
     <t xml:space="preserve">17.293586730957</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4228496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4874820709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5521144866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6472682952881</t>
+    <t xml:space="preserve">17.4228477478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4874801635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5521125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6472702026367</t>
   </si>
   <si>
     <t xml:space="preserve">17.3397541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6352138519287</t>
+    <t xml:space="preserve">17.6352100372314</t>
   </si>
   <si>
     <t xml:space="preserve">16.9888935089111</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3766841888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.57981300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1273899078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3241119384766</t>
+    <t xml:space="preserve">17.3766860961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5798149108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1273918151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3241100311279</t>
   </si>
   <si>
     <t xml:space="preserve">16.665735244751</t>
@@ -215,16 +215,16 @@
     <t xml:space="preserve">16.6380348205566</t>
   </si>
   <si>
-    <t xml:space="preserve">17.238187789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6813774108887</t>
+    <t xml:space="preserve">17.2381858825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.68137550354</t>
   </si>
   <si>
     <t xml:space="preserve">17.755241394043</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5244121551514</t>
+    <t xml:space="preserve">17.5244140625</t>
   </si>
   <si>
     <t xml:space="preserve">17.9860668182373</t>
@@ -233,94 +233,94 @@
     <t xml:space="preserve">18.2353610992432</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1430320739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9122009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7183074951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4661903381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5308227539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5585231781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2168979644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4477195739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1522636413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0137672424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5890445709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2658863067627</t>
+    <t xml:space="preserve">18.1430282592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.912202835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7183113098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4661884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.530818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5585193634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2168941497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4477233886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1522617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0137691497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5890426635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.26589012146</t>
   </si>
   <si>
     <t xml:space="preserve">17.6075115203857</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2843532562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.192024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8873310089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9519634246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6749687194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4256782531738</t>
+    <t xml:space="preserve">17.284351348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1920261383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8873291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9519653320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6749706268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4256801605225</t>
   </si>
   <si>
     <t xml:space="preserve">16.2594795227051</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3610420227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8596286773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5641746520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5272369384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2779426574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4782485961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6288070678711</t>
+    <t xml:space="preserve">16.3610458374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8596305847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5641689300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5272407531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2779445648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.47825050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6288051605225</t>
   </si>
   <si>
     <t xml:space="preserve">16.6103382110596</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3582172393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1089248657227</t>
+    <t xml:space="preserve">17.3582153320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.108922958374</t>
   </si>
   <si>
     <t xml:space="preserve">17.1550884246826</t>
@@ -329,25 +329,25 @@
     <t xml:space="preserve">15.9178552627563</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9547882080078</t>
+    <t xml:space="preserve">15.9547891616821</t>
   </si>
   <si>
     <t xml:space="preserve">15.0591773986816</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8652820587158</t>
+    <t xml:space="preserve">14.8652830123901</t>
   </si>
   <si>
     <t xml:space="preserve">15.1699743270874</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4377317428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0655860900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0868768692017</t>
+    <t xml:space="preserve">15.4377336502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0655822753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0868787765503</t>
   </si>
   <si>
     <t xml:space="preserve">14.5513563156128</t>
@@ -359,49 +359,49 @@
     <t xml:space="preserve">14.6252212524414</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7821855545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5115995407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1330413818359</t>
+    <t xml:space="preserve">14.7821846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5115976333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1330423355103</t>
   </si>
   <si>
     <t xml:space="preserve">14.72678565979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0989370346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3574619293213</t>
+    <t xml:space="preserve">14.0989379882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3574638366699</t>
   </si>
   <si>
     <t xml:space="preserve">14.7544851303101</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5023651123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4192695617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.603931427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3546361923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4284992218018</t>
+    <t xml:space="preserve">15.5023670196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4192705154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.603928565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3546371459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4285001754761</t>
   </si>
   <si>
     <t xml:space="preserve">15.4008026123047</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4838991165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.250244140625</t>
+    <t xml:space="preserve">15.4839019775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2502460479736</t>
   </si>
   <si>
     <t xml:space="preserve">15.7239618301392</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">15.4931325912476</t>
   </si>
   <si>
-    <t xml:space="preserve">16.231782913208</t>
+    <t xml:space="preserve">16.2317790985107</t>
   </si>
   <si>
     <t xml:space="preserve">15.9363212585449</t>
@@ -419,73 +419,73 @@
     <t xml:space="preserve">16.1856155395508</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2871799468994</t>
+    <t xml:space="preserve">16.2871780395508</t>
   </si>
   <si>
     <t xml:space="preserve">16.176383972168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.093282699585</t>
+    <t xml:space="preserve">16.0932865142822</t>
   </si>
   <si>
     <t xml:space="preserve">17.2566547393799</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9242630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7211380004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7580680847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7275428771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2751178741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1458587646484</t>
+    <t xml:space="preserve">16.9242649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.721134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7580661773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7275409698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2751197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1458549499512</t>
   </si>
   <si>
     <t xml:space="preserve">17.3120536804199</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4505481719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2040786743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8901557922363</t>
+    <t xml:space="preserve">17.4505519866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2040824890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.890154838562</t>
   </si>
   <si>
     <t xml:space="preserve">15.862455368042</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9270896911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0563488006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7424259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7701272964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6685609817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5946969985962</t>
+    <t xml:space="preserve">15.9270868301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0563507080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7424230575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7701282501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6685571670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5946960449219</t>
   </si>
   <si>
     <t xml:space="preserve">15.7147274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1394481658936</t>
+    <t xml:space="preserve">16.1394500732422</t>
   </si>
   <si>
     <t xml:space="preserve">16.8134632110596</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">16.1671485900879</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6408643722534</t>
+    <t xml:space="preserve">15.6408634185791</t>
   </si>
   <si>
     <t xml:space="preserve">15.6500978469849</t>
@@ -503,19 +503,19 @@
     <t xml:space="preserve">15.8070592880249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4654340744019</t>
+    <t xml:space="preserve">15.4654321670532</t>
   </si>
   <si>
     <t xml:space="preserve">15.2623062133789</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3366212844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4109344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.652458190918</t>
+    <t xml:space="preserve">15.3366193771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4109354019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6524562835693</t>
   </si>
   <si>
     <t xml:space="preserve">15.7360610961914</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">15.8939781188965</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6245861053467</t>
+    <t xml:space="preserve">15.6245880126953</t>
   </si>
   <si>
     <t xml:space="preserve">15.0765199661255</t>
@@ -533,40 +533,40 @@
     <t xml:space="preserve">15.4295148849487</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5224075317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5131196975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1601238250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8661117553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3305740356445</t>
+    <t xml:space="preserve">15.522403717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131187438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1601228713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8661098480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3305759429932</t>
   </si>
   <si>
     <t xml:space="preserve">15.9311323165894</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4945373535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6060104370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3180389404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8846883773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0518970489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8382387161255</t>
+    <t xml:space="preserve">15.4945392608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6060085296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.318039894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8846912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0518951416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8382415771484</t>
   </si>
   <si>
     <t xml:space="preserve">16.5813846588135</t>
@@ -575,100 +575,100 @@
     <t xml:space="preserve">17.1851902008057</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2595043182373</t>
+    <t xml:space="preserve">17.2595024108887</t>
   </si>
   <si>
     <t xml:space="preserve">17.1387424468994</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2223472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0272731781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9529571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4884929656982</t>
+    <t xml:space="preserve">17.2223491668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.027271270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.952953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4884910583496</t>
   </si>
   <si>
     <t xml:space="preserve">17.0922966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9065113067627</t>
+    <t xml:space="preserve">16.9065093994141</t>
   </si>
   <si>
     <t xml:space="preserve">17.1666107177734</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7425479888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.900463104248</t>
+    <t xml:space="preserve">17.7425498962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9004669189453</t>
   </si>
   <si>
     <t xml:space="preserve">17.9376220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8818874359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4299545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9037094116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9501571655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5539569854736</t>
+    <t xml:space="preserve">17.8818836212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.42995262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9037075042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9501514434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5539588928223</t>
   </si>
   <si>
     <t xml:space="preserve">19.6282730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">19.117359161377</t>
+    <t xml:space="preserve">19.1173629760742</t>
   </si>
   <si>
     <t xml:space="preserve">18.9129981994629</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4610691070557</t>
+    <t xml:space="preserve">19.461067199707</t>
   </si>
   <si>
     <t xml:space="preserve">19.3310165405273</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1823883056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.080207824707</t>
+    <t xml:space="preserve">19.1823863983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0802059173584</t>
   </si>
   <si>
     <t xml:space="preserve">18.8572616577148</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0151805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9408645629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9315757751465</t>
+    <t xml:space="preserve">19.0151767730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9408664703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9315738677979</t>
   </si>
   <si>
     <t xml:space="preserve">18.7550792694092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5785827636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4020843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1141166687012</t>
+    <t xml:space="preserve">18.5785846710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4020881652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1141204833984</t>
   </si>
   <si>
     <t xml:space="preserve">18.457820892334</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">18.3742179870605</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4856910705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.281322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3277721405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.513557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.615743637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6250286102295</t>
+    <t xml:space="preserve">18.485689163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2813282012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3277740478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5135612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6157379150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6250305175781</t>
   </si>
   <si>
     <t xml:space="preserve">18.7272109985352</t>
@@ -707,16 +707,16 @@
     <t xml:space="preserve">19.0430469512939</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4146194458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0894947052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1266498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3681735992432</t>
+    <t xml:space="preserve">19.4146175384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0894927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1266536712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3681755065918</t>
   </si>
   <si>
     <t xml:space="preserve">19.4517765045166</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">18.9594421386719</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2474098205566</t>
+    <t xml:space="preserve">19.2474117279053</t>
   </si>
   <si>
     <t xml:space="preserve">19.507511138916</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">19.098783493042</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2195434570312</t>
+    <t xml:space="preserve">19.2195415496826</t>
   </si>
   <si>
     <t xml:space="preserve">19.3495960235596</t>
@@ -743,19 +743,19 @@
     <t xml:space="preserve">19.0337581634521</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2288341522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3867530822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2845687866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9162406921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0091361999512</t>
+    <t xml:space="preserve">19.228832244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3867492675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2845726013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9162425994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0091342926025</t>
   </si>
   <si>
     <t xml:space="preserve">20.3807067871094</t>
@@ -764,10 +764,10 @@
     <t xml:space="preserve">20.6222286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8544635772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.965934753418</t>
+    <t xml:space="preserve">20.8544597625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9659309387207</t>
   </si>
   <si>
     <t xml:space="preserve">20.9473514556885</t>
@@ -776,10 +776,10 @@
     <t xml:space="preserve">20.148473739624</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6129379272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3899955749512</t>
+    <t xml:space="preserve">20.6129360198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3899974822998</t>
   </si>
   <si>
     <t xml:space="preserve">20.2506561279297</t>
@@ -788,94 +788,94 @@
     <t xml:space="preserve">20.5757789611816</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6500949859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6036472320557</t>
+    <t xml:space="preserve">20.6500930786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6036491394043</t>
   </si>
   <si>
     <t xml:space="preserve">20.5014667510986</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5293350219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6593818664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4828872680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8172988891602</t>
+    <t xml:space="preserve">20.529333114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6593837738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.482889175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8173027038574</t>
   </si>
   <si>
     <t xml:space="preserve">20.8637466430664</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4550228118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7801475524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6440467834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4954204559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3653697967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3189258575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1331386566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1238460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9287757873535</t>
+    <t xml:space="preserve">20.4550189971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7801456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6440505981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.495418548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3653717041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3189239501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1331405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1238479614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9287738800049</t>
   </si>
   <si>
     <t xml:space="preserve">21.2724761962891</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1052684783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.346794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2260341644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6408042907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1702995300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9566402435303</t>
+    <t xml:space="preserve">21.1052722930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3467922210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2260322570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6408061981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1702938079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9566383361816</t>
   </si>
   <si>
     <t xml:space="preserve">21.114559173584</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2539005279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.244607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3374996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2817668914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9380645751953</t>
+    <t xml:space="preserve">21.2538986206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2446098327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3375015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2817707061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9380664825439</t>
   </si>
   <si>
     <t xml:space="preserve">21.1795845031738</t>
@@ -884,31 +884,31 @@
     <t xml:space="preserve">20.7336978912354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3156795501709</t>
+    <t xml:space="preserve">20.3156814575195</t>
   </si>
   <si>
     <t xml:space="preserve">20.399284362793</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4085750579834</t>
+    <t xml:space="preserve">20.4085712432861</t>
   </si>
   <si>
     <t xml:space="preserve">20.3249702453613</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6315155029297</t>
+    <t xml:space="preserve">20.6315174102783</t>
   </si>
   <si>
     <t xml:space="preserve">20.2785224914551</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0462894439697</t>
+    <t xml:space="preserve">20.0462913513184</t>
   </si>
   <si>
     <t xml:space="preserve">20.2135009765625</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7954807281494</t>
+    <t xml:space="preserve">19.795482635498</t>
   </si>
   <si>
     <t xml:space="preserve">19.9069519042969</t>
@@ -917,13 +917,13 @@
     <t xml:space="preserve">20.2692337036133</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2971019744873</t>
+    <t xml:space="preserve">20.2971038818359</t>
   </si>
   <si>
     <t xml:space="preserve">20.5479145050049</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4364395141602</t>
+    <t xml:space="preserve">20.4364414215088</t>
   </si>
   <si>
     <t xml:space="preserve">19.9533996582031</t>
@@ -932,19 +932,19 @@
     <t xml:space="preserve">19.8326377868652</t>
   </si>
   <si>
-    <t xml:space="preserve">19.888370513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7211685180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9255294799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.074161529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9998416900635</t>
+    <t xml:space="preserve">19.8883743286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7211627960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9255313873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0741596221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9998435974121</t>
   </si>
   <si>
     <t xml:space="preserve">20.1113147735596</t>
@@ -956,22 +956,22 @@
     <t xml:space="preserve">20.6686744689941</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2413692474365</t>
+    <t xml:space="preserve">20.2413654327393</t>
   </si>
   <si>
     <t xml:space="preserve">19.9719753265381</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7304553985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4178638458252</t>
+    <t xml:space="preserve">19.7304534912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4178619384766</t>
   </si>
   <si>
     <t xml:space="preserve">20.1298923492432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4921760559082</t>
+    <t xml:space="preserve">20.4921722412109</t>
   </si>
   <si>
     <t xml:space="preserve">20.8451709747314</t>
@@ -980,22 +980,22 @@
     <t xml:space="preserve">20.3435478210449</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5664901733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8916149139404</t>
+    <t xml:space="preserve">20.5664920806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8916168212891</t>
   </si>
   <si>
     <t xml:space="preserve">21.1981620788574</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7244091033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4736022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3342628479004</t>
+    <t xml:space="preserve">20.7244071960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4735984802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3342609405518</t>
   </si>
   <si>
     <t xml:space="preserve">20.3714160919189</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">19.8790817260742</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8419284820557</t>
+    <t xml:space="preserve">19.841926574707</t>
   </si>
   <si>
     <t xml:space="preserve">19.767614364624</t>
@@ -1016,16 +1016,16 @@
     <t xml:space="preserve">20.092737197876</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5200443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9905567169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5353813171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2567024230957</t>
+    <t xml:space="preserve">20.5200462341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9905529022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5353832244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2567005157471</t>
   </si>
   <si>
     <t xml:space="preserve">18.7829475402832</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">18.8386821746826</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6343193054199</t>
+    <t xml:space="preserve">18.6343173980713</t>
   </si>
   <si>
     <t xml:space="preserve">18.996603012085</t>
@@ -1049,49 +1049,49 @@
     <t xml:space="preserve">18.6621856689453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.439245223999</t>
+    <t xml:space="preserve">18.4392471313477</t>
   </si>
   <si>
     <t xml:space="preserve">18.8108139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1359424591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9779300689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9499263763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5298538208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3058166503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.904411315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8484020233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6430358886719</t>
+    <t xml:space="preserve">19.1359405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.977933883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9499282836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.529857635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.305814743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9044132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8484039306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6430339813232</t>
   </si>
   <si>
     <t xml:space="preserve">17.6710395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9417495727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.895076751709</t>
+    <t xml:space="preserve">17.9417514801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8950786590576</t>
   </si>
   <si>
     <t xml:space="preserve">17.9697570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2684764862061</t>
+    <t xml:space="preserve">18.2684745788574</t>
   </si>
   <si>
     <t xml:space="preserve">18.4645080566406</t>
@@ -1103,25 +1103,25 @@
     <t xml:space="preserve">18.4084987640381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1657886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4925117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3618278503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2217998504639</t>
+    <t xml:space="preserve">18.1657905578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4925155639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3618259429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2218036651611</t>
   </si>
   <si>
     <t xml:space="preserve">18.6698780059814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7725601196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6978816986084</t>
+    <t xml:space="preserve">18.7725639343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.697883605957</t>
   </si>
   <si>
     <t xml:space="preserve">18.688549041748</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">18.4458408355713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4831790924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4738445281982</t>
+    <t xml:space="preserve">18.4831809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4738464355469</t>
   </si>
   <si>
     <t xml:space="preserve">18.6605434417725</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7072200775146</t>
+    <t xml:space="preserve">18.707218170166</t>
   </si>
   <si>
     <t xml:space="preserve">18.5951976776123</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">18.9032516479492</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1833000183105</t>
+    <t xml:space="preserve">19.1832962036133</t>
   </si>
   <si>
     <t xml:space="preserve">19.4633483886719</t>
@@ -1172,46 +1172,46 @@
     <t xml:space="preserve">19.7433967590332</t>
   </si>
   <si>
-    <t xml:space="preserve">20.536865234375</t>
+    <t xml:space="preserve">20.5368671417236</t>
   </si>
   <si>
     <t xml:space="preserve">21.2836608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5637073516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.517032623291</t>
+    <t xml:space="preserve">21.5637092590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5170345306396</t>
   </si>
   <si>
     <t xml:space="preserve">21.377010345459</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6103801727295</t>
+    <t xml:space="preserve">21.6103839874268</t>
   </si>
   <si>
     <t xml:space="preserve">21.4703578948975</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7504062652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7970809936523</t>
+    <t xml:space="preserve">21.7504081726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7970848083496</t>
   </si>
   <si>
     <t xml:space="preserve">21.0036106109619</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4435157775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0502853393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6302127838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7702388763428</t>
+    <t xml:space="preserve">20.4435138702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0502891540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6302146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7702407836914</t>
   </si>
   <si>
     <t xml:space="preserve">20.7235660552979</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">21.0969619750977</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1903133392334</t>
+    <t xml:space="preserve">21.1903114318848</t>
   </si>
   <si>
     <t xml:space="preserve">21.1436367034912</t>
@@ -1229,34 +1229,34 @@
     <t xml:space="preserve">20.8635883331299</t>
   </si>
   <si>
-    <t xml:space="preserve">20.676887512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7037315368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2171516418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8904323577881</t>
+    <t xml:space="preserve">20.6768894195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7037353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2171535491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8904342651367</t>
   </si>
   <si>
     <t xml:space="preserve">22.0771312713623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9837799072266</t>
+    <t xml:space="preserve">21.9837818145752</t>
   </si>
   <si>
     <t xml:space="preserve">20.8169136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2369861602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3034915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2101421356201</t>
+    <t xml:space="preserve">21.236988067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3034934997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2101402282715</t>
   </si>
   <si>
     <t xml:space="preserve">20.9102630615234</t>
@@ -1265,25 +1265,25 @@
     <t xml:space="preserve">20.5835399627686</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9569416046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3303356170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3968391418457</t>
+    <t xml:space="preserve">20.956937789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3303375244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3968410491943</t>
   </si>
   <si>
     <t xml:space="preserve">20.4901924133301</t>
   </si>
   <si>
-    <t xml:space="preserve">20.116792678833</t>
+    <t xml:space="preserve">20.1167945861816</t>
   </si>
   <si>
     <t xml:space="preserve">18.9966011047363</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0432758331299</t>
+    <t xml:space="preserve">19.0432739257812</t>
   </si>
   <si>
     <t xml:space="preserve">19.1366271972656</t>
@@ -1295,28 +1295,28 @@
     <t xml:space="preserve">19.7900695800781</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6033725738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3501682281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2568168640137</t>
+    <t xml:space="preserve">19.6033706665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3501663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2568187713623</t>
   </si>
   <si>
     <t xml:space="preserve">19.9767684936523</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1634674072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0234413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8834171295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9300918579102</t>
+    <t xml:space="preserve">20.1634693145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0234470367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8834190368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9300956726074</t>
   </si>
   <si>
     <t xml:space="preserve">19.4166717529297</t>
@@ -1325,64 +1325,64 @@
     <t xml:space="preserve">19.556697845459</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5100231170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6500453948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.696720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.276647567749</t>
+    <t xml:space="preserve">19.5100212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6500473022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6967220306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2766494750977</t>
   </si>
   <si>
     <t xml:space="preserve">19.2299747467041</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3699989318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8367443084717</t>
+    <t xml:space="preserve">19.3699970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8367462158203</t>
   </si>
   <si>
     <t xml:space="preserve">21.4236850738525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0701160430908</t>
+    <t xml:space="preserve">20.0701179504395</t>
   </si>
   <si>
     <t xml:space="preserve">17.7177143096924</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3092994689941</t>
+    <t xml:space="preserve">15.3093013763428</t>
   </si>
   <si>
     <t xml:space="preserve">15.7013673782349</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7678747177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4691562652588</t>
+    <t xml:space="preserve">14.7678737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4691553115845</t>
   </si>
   <si>
     <t xml:space="preserve">14.8052129745483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4026498794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6266870498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0000839233398</t>
+    <t xml:space="preserve">15.4026489257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6266899108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0000858306885</t>
   </si>
   <si>
     <t xml:space="preserve">15.5333375930786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3279705047607</t>
+    <t xml:space="preserve">15.3279695510864</t>
   </si>
   <si>
     <t xml:space="preserve">15.4586582183838</t>
@@ -1391,22 +1391,22 @@
     <t xml:space="preserve">15.8693952560425</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7947177886963</t>
+    <t xml:space="preserve">15.794716835022</t>
   </si>
   <si>
     <t xml:space="preserve">15.6640291213989</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5893507003784</t>
+    <t xml:space="preserve">15.5893497467041</t>
   </si>
   <si>
     <t xml:space="preserve">15.3839797973633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0105829238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8602886199951</t>
+    <t xml:space="preserve">15.0105810165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8602876663208</t>
   </si>
   <si>
     <t xml:space="preserve">14.5784873962402</t>
@@ -1415,13 +1415,13 @@
     <t xml:space="preserve">14.4094076156616</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4469804763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9166479110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.935435295105</t>
+    <t xml:space="preserve">14.4469795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9166488647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9354343414307</t>
   </si>
   <si>
     <t xml:space="preserve">14.6536350250244</t>
@@ -1430,43 +1430,43 @@
     <t xml:space="preserve">15.14208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4426774978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2735948562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0712461471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9209518432617</t>
+    <t xml:space="preserve">15.4426755905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2735958099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0712451934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.920952796936</t>
   </si>
   <si>
     <t xml:space="preserve">13.6015777587891</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7330865859985</t>
+    <t xml:space="preserve">13.7330856323242</t>
   </si>
   <si>
     <t xml:space="preserve">14.3342609405518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1651792526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1463947296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2215404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9585256576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6391534805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6203641891479</t>
+    <t xml:space="preserve">14.1651802062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1463928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2215423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9585266113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6391525268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6203651428223</t>
   </si>
   <si>
     <t xml:space="preserve">13.7894458770752</t>
@@ -1475,16 +1475,16 @@
     <t xml:space="preserve">14.0524597167969</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2027530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5221281051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7475681304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2172374725342</t>
+    <t xml:space="preserve">14.2027540206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5221261978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7475690841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2172365188599</t>
   </si>
   <si>
     <t xml:space="preserve">15.1233034133911</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">15.029369354248</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0669431686401</t>
+    <t xml:space="preserve">15.0669422149658</t>
   </si>
   <si>
     <t xml:space="preserve">14.8978614807129</t>
@@ -1502,82 +1502,82 @@
     <t xml:space="preserve">15.1045160293579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1608762741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984481811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5366125106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9687023162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8141040802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.889253616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9080410003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4947338104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4195861816406</t>
+    <t xml:space="preserve">15.1608753204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1984491348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366106033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9687061309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8141059875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8892517089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9080390930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4947319030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.419584274292</t>
   </si>
   <si>
     <t xml:space="preserve">16.2692928314209</t>
   </si>
   <si>
-    <t xml:space="preserve">16.363224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.987491607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8747720718384</t>
+    <t xml:space="preserve">16.3632259368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9874906539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8747682571411</t>
   </si>
   <si>
     <t xml:space="preserve">15.8184108734131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1377868652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1565704345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2505054473877</t>
+    <t xml:space="preserve">16.1377849578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1565723419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2505035400391</t>
   </si>
   <si>
     <t xml:space="preserve">16.62624168396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5135173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2880783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4383716583252</t>
+    <t xml:space="preserve">16.513521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2880802154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4383735656738</t>
   </si>
   <si>
     <t xml:space="preserve">16.4571590423584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2317180633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6074523925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7201709747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.475944519043</t>
+    <t xml:space="preserve">16.2317199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6074504852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7201728820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4759464263916</t>
   </si>
   <si>
     <t xml:space="preserve">16.3256511688232</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">15.8559827804565</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9499206542969</t>
+    <t xml:space="preserve">15.9499187469482</t>
   </si>
   <si>
     <t xml:space="preserve">15.9311304092407</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">16.3444385528564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4007987976074</t>
+    <t xml:space="preserve">16.4007968902588</t>
   </si>
   <si>
     <t xml:space="preserve">16.5323047637939</t>
@@ -1610,22 +1610,22 @@
     <t xml:space="preserve">16.7765350341797</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9456157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4716415405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.279468536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2606811523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2418956756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.110387802124</t>
+    <t xml:space="preserve">16.9456119537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.471643447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2794723510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2606830596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2418975830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1103897094727</t>
   </si>
   <si>
     <t xml:space="preserve">17.5280017852783</t>
@@ -1634,13 +1634,13 @@
     <t xml:space="preserve">17.1334800720215</t>
   </si>
   <si>
-    <t xml:space="preserve">17.001974105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9831886291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7389602661133</t>
+    <t xml:space="preserve">17.0019760131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9831867218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7389583587646</t>
   </si>
   <si>
     <t xml:space="preserve">16.6450252532959</t>
@@ -1652,52 +1652,52 @@
     <t xml:space="preserve">16.832893371582</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0583305358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1522693634033</t>
+    <t xml:space="preserve">17.0583343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1522636413574</t>
   </si>
   <si>
     <t xml:space="preserve">17.2274131774902</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7577457427979</t>
+    <t xml:space="preserve">16.7577476501465</t>
   </si>
   <si>
     <t xml:space="preserve">16.2129325866699</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4990358352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5178241729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4614639282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1796627044678</t>
+    <t xml:space="preserve">15.4990367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.517822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4614629745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1796617507935</t>
   </si>
   <si>
     <t xml:space="preserve">14.6912078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8039293289185</t>
+    <t xml:space="preserve">14.8039283752441</t>
   </si>
   <si>
     <t xml:space="preserve">15.0857286453247</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7663555145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9730081558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8415012359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5033397674561</t>
+    <t xml:space="preserve">14.7663545608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9730072021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8415021896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5033407211304</t>
   </si>
   <si>
     <t xml:space="preserve">14.6724214553833</t>
@@ -1706,94 +1706,94 @@
     <t xml:space="preserve">14.3718347549438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8227138519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5597019195557</t>
+    <t xml:space="preserve">14.822714805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.559700012207</t>
   </si>
   <si>
     <t xml:space="preserve">14.4657669067383</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6348476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.574182510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.405104637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3863162994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6681156158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2360219955444</t>
+    <t xml:space="preserve">14.6348485946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5741815567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4051036834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3863153457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6681175231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2360229492188</t>
   </si>
   <si>
     <t xml:space="preserve">15.5929708480835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4238882064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3299560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0481557846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.879075050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5409126281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7851409912109</t>
+    <t xml:space="preserve">15.4238901138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3299551010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0481567382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8790760040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5409135818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7851419448853</t>
   </si>
   <si>
     <t xml:space="preserve">14.6160612106323</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2966861724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2779006958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0900325775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9021663665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7706604003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4281949996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2591142654419</t>
+    <t xml:space="preserve">14.296688079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2778997421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.090033531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9021654129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7706594467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4281930923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2591152191162</t>
   </si>
   <si>
     <t xml:space="preserve">13.8082323074341</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8458042144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.033673286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9397392272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2403259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0148878097534</t>
+    <t xml:space="preserve">13.8458061218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0336723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9397382736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2403268814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0148868560791</t>
   </si>
   <si>
     <t xml:space="preserve">14.5972738265991</t>
@@ -1805,25 +1805,25 @@
     <t xml:space="preserve">15.3675308227539</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1839685440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1088209152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4845542907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9917945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2923822402954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0758934020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0569305419922</t>
+    <t xml:space="preserve">14.183967590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1088199615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4845533370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9917964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.292384147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0758924484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0569295883179</t>
   </si>
   <si>
     <t xml:space="preserve">14.9052238464355</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">14.8862590789795</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3793077468872</t>
+    <t xml:space="preserve">15.3793067932129</t>
   </si>
   <si>
     <t xml:space="preserve">15.6827230453491</t>
@@ -1844,85 +1844,85 @@
     <t xml:space="preserve">16.4602203369141</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3274745941162</t>
+    <t xml:space="preserve">16.3274765014648</t>
   </si>
   <si>
     <t xml:space="preserve">15.7016839981079</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6637592315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5310144424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5499792098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551601409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7585773468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.796501159668</t>
+    <t xml:space="preserve">15.6637573242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5310134887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5499773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7585763931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7965030670166</t>
   </si>
   <si>
     <t xml:space="preserve">16.1757698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">15.720648765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6068687438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.644793510437</t>
+    <t xml:space="preserve">15.7206478118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6068677902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6447944641113</t>
   </si>
   <si>
     <t xml:space="preserve">16.043025970459</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9861373901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4172334671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344297409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5689401626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4361982345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5879058837891</t>
+    <t xml:space="preserve">15.9861364364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4172353744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344287872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5689420700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4361991882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5879049301147</t>
   </si>
   <si>
     <t xml:space="preserve">15.246563911438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1138200759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9810762405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2086381912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7535161972046</t>
+    <t xml:space="preserve">15.1138210296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9810771942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2086391448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7535152435303</t>
   </si>
   <si>
     <t xml:space="preserve">14.9431505203247</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5069913864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0329084396362</t>
+    <t xml:space="preserve">14.5069923400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0329074859619</t>
   </si>
   <si>
     <t xml:space="preserve">13.9380903244019</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">14.5828456878662</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3932123184204</t>
+    <t xml:space="preserve">14.3932113647461</t>
   </si>
   <si>
     <t xml:space="preserve">14.4311380386353</t>
@@ -1949,22 +1949,22 @@
     <t xml:space="preserve">14.6207723617554</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3363208770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2794322967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0518703460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6915664672852</t>
+    <t xml:space="preserve">14.3363227844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2794313430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0518712997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6915655136108</t>
   </si>
   <si>
     <t xml:space="preserve">13.1416273117065</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0088834762573</t>
+    <t xml:space="preserve">13.008885383606</t>
   </si>
   <si>
     <t xml:space="preserve">13.3691892623901</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">13.0847387313843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8002862930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4210195541382</t>
+    <t xml:space="preserve">12.8002872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4210186004639</t>
   </si>
   <si>
     <t xml:space="preserve">12.1744956970215</t>
@@ -1985,25 +1985,25 @@
     <t xml:space="preserve">11.9469347000122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4728507995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0366916656494</t>
+    <t xml:space="preserve">11.4728498458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0366926193237</t>
   </si>
   <si>
     <t xml:space="preserve">10.1264495849609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95577907562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59547424316406</t>
+    <t xml:space="preserve">9.95577812194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59547519683838</t>
   </si>
   <si>
     <t xml:space="preserve">8.91279220581055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41532230377197</t>
+    <t xml:space="preserve">9.41532325744629</t>
   </si>
   <si>
     <t xml:space="preserve">8.09736633300781</t>
@@ -2015,16 +2015,16 @@
     <t xml:space="preserve">9.10242652893066</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1643762588501</t>
+    <t xml:space="preserve">10.1643772125244</t>
   </si>
   <si>
     <t xml:space="preserve">10.7522411346436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9279718399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8951044082642</t>
+    <t xml:space="preserve">11.9279708862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8951034545898</t>
   </si>
   <si>
     <t xml:space="preserve">11.6055936813354</t>
@@ -2033,28 +2033,28 @@
     <t xml:space="preserve">10.9608383178711</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9229125976562</t>
+    <t xml:space="preserve">10.9229116439819</t>
   </si>
   <si>
     <t xml:space="preserve">10.6384611129761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.06955909729</t>
+    <t xml:space="preserve">10.0695581436157</t>
   </si>
   <si>
     <t xml:space="preserve">10.3350458145142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.61949634552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7332773208618</t>
+    <t xml:space="preserve">10.6194972991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7332782745361</t>
   </si>
   <si>
     <t xml:space="preserve">11.1125459671021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9039487838745</t>
+    <t xml:space="preserve">10.9039478302002</t>
   </si>
   <si>
     <t xml:space="preserve">10.5815696716309</t>
@@ -2066,16 +2066,16 @@
     <t xml:space="preserve">9.87992572784424</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2212657928467</t>
+    <t xml:space="preserve">10.2212648391724</t>
   </si>
   <si>
     <t xml:space="preserve">10.5057163238525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4298648834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7712049484253</t>
+    <t xml:space="preserve">10.4298629760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.771203994751</t>
   </si>
   <si>
     <t xml:space="preserve">10.7143144607544</t>
@@ -2084,19 +2084,19 @@
     <t xml:space="preserve">10.6953496932983</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8091306686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8280935287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5436449050903</t>
+    <t xml:space="preserve">10.8091316223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8280954360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.543643951416</t>
   </si>
   <si>
     <t xml:space="preserve">10.9987649917603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9418745040894</t>
+    <t xml:space="preserve">10.9418754577637</t>
   </si>
   <si>
     <t xml:space="preserve">11.4918127059937</t>
@@ -2105,58 +2105,58 @@
     <t xml:space="preserve">11.567666053772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0556554794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.415958404541</t>
+    <t xml:space="preserve">11.0556545257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4159603118896</t>
   </si>
   <si>
     <t xml:space="preserve">11.5107774734497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7952260971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0038242340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.288275718689</t>
+    <t xml:space="preserve">11.7952280044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0038251876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2882747650146</t>
   </si>
   <si>
     <t xml:space="preserve">12.2124223709106</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0986423492432</t>
+    <t xml:space="preserve">12.0986413955688</t>
   </si>
   <si>
     <t xml:space="preserve">11.8521175384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2263259887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.017728805542</t>
+    <t xml:space="preserve">11.2263269424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0177278518677</t>
   </si>
   <si>
     <t xml:space="preserve">11.1883983612061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0935821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8849859237671</t>
+    <t xml:space="preserve">11.0935831069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8849840164185</t>
   </si>
   <si>
     <t xml:space="preserve">10.7901678085327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6763887405396</t>
+    <t xml:space="preserve">10.6763868331909</t>
   </si>
   <si>
     <t xml:space="preserve">10.4108991622925</t>
   </si>
   <si>
-    <t xml:space="preserve">10.448826789856</t>
+    <t xml:space="preserve">10.4488277435303</t>
   </si>
   <si>
     <t xml:space="preserve">10.6574239730835</t>
@@ -2165,46 +2165,46 @@
     <t xml:space="preserve">11.2073612213135</t>
   </si>
   <si>
-    <t xml:space="preserve">11.340106010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2832155227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0746183395386</t>
+    <t xml:space="preserve">11.3401050567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2832145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0746192932129</t>
   </si>
   <si>
     <t xml:space="preserve">10.9798011779785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6005344390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3729724884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4677896499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6435203552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4349231719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6814460754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5297393798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6245565414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5487041473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6624822616577</t>
+    <t xml:space="preserve">10.6005334854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3729734420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.467791557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6435194015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4349241256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6814470291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5297403335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6245555877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5487031936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.662483215332</t>
   </si>
   <si>
     <t xml:space="preserve">11.7383375167847</t>
@@ -2219,34 +2219,34 @@
     <t xml:space="preserve">12.1176042556763</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9658985137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9848613739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.814190864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7573013305664</t>
+    <t xml:space="preserve">11.9658975601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9848604202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8141899108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7573003768921</t>
   </si>
   <si>
     <t xml:space="preserve">11.245288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6485795974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.653639793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3881511688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8622360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5967483520508</t>
+    <t xml:space="preserve">12.6485815048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6536388397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3881521224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8622369766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5967502593994</t>
   </si>
   <si>
     <t xml:space="preserve">13.2364444732666</t>
@@ -2255,13 +2255,13 @@
     <t xml:space="preserve">13.4260787963867</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4640054702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1037006378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.331262588501</t>
+    <t xml:space="preserve">13.4640045166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1037015914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3312616348267</t>
   </si>
   <si>
     <t xml:space="preserve">14.1277236938477</t>
@@ -2279,55 +2279,55 @@
     <t xml:space="preserve">13.4829683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1795530319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0227870941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.060715675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3262014389038</t>
+    <t xml:space="preserve">13.1795539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0227890014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0607147216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3262023925781</t>
   </si>
   <si>
     <t xml:space="preserve">12.4399824142456</t>
   </si>
   <si>
-    <t xml:space="preserve">12.857177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8192501068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0468111038208</t>
+    <t xml:space="preserve">12.8571767807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8192510604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0468101501465</t>
   </si>
   <si>
     <t xml:space="preserve">13.3122987747192</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4450435638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5588235855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6179904937744</t>
+    <t xml:space="preserve">13.4450426101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5588226318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6179914474487</t>
   </si>
   <si>
     <t xml:space="preserve">13.6371440887451</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4073047637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.445611000061</t>
+    <t xml:space="preserve">13.4073057174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4456119537354</t>
   </si>
   <si>
     <t xml:space="preserve">13.3115377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5030717849731</t>
+    <t xml:space="preserve">13.5030727386475</t>
   </si>
   <si>
     <t xml:space="preserve">13.8478307723999</t>
@@ -2336,28 +2336,28 @@
     <t xml:space="preserve">13.886137008667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.752064704895</t>
+    <t xml:space="preserve">13.7520637512207</t>
   </si>
   <si>
     <t xml:space="preserve">14.1734371185303</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1542816162109</t>
+    <t xml:space="preserve">14.1542825698853</t>
   </si>
   <si>
     <t xml:space="preserve">14.2117443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9819030761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6946048736572</t>
+    <t xml:space="preserve">13.9819040298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6946039199829</t>
   </si>
   <si>
     <t xml:space="preserve">13.4647655487061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7712173461914</t>
+    <t xml:space="preserve">13.7712182998657</t>
   </si>
   <si>
     <t xml:space="preserve">13.5988368988037</t>
@@ -2366,10 +2366,10 @@
     <t xml:space="preserve">13.5413789749146</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7903709411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7137575149536</t>
+    <t xml:space="preserve">13.7903699874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7137565612793</t>
   </si>
   <si>
     <t xml:space="preserve">13.8669834136963</t>
@@ -2381,43 +2381,43 @@
     <t xml:space="preserve">14.3458156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7097291946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6331157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9970283508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0353336334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4909858703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3377571105957</t>
+    <t xml:space="preserve">14.7097282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6331148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9970273971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0353345870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4909839630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3377590179443</t>
   </si>
   <si>
     <t xml:space="preserve">16.184534072876</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8206214904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9546918869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8014650344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6099328994751</t>
+    <t xml:space="preserve">15.8206195831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9546928405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8014659881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6099348068237</t>
   </si>
   <si>
     <t xml:space="preserve">15.3226337432861</t>
   </si>
   <si>
-    <t xml:space="preserve">15.74400806427</t>
+    <t xml:space="preserve">15.7440061569214</t>
   </si>
   <si>
     <t xml:space="preserve">15.3417882919312</t>
@@ -2426,16 +2426,16 @@
     <t xml:space="preserve">15.437554359436</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7248525619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8589248657227</t>
+    <t xml:space="preserve">15.724853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.858925819397</t>
   </si>
   <si>
     <t xml:space="preserve">16.2611446380615</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6059055328369</t>
+    <t xml:space="preserve">16.6059036254883</t>
   </si>
   <si>
     <t xml:space="preserve">16.778284072876</t>
@@ -2444,13 +2444,13 @@
     <t xml:space="preserve">16.6825180053711</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6442108154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7208232879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7016716003418</t>
+    <t xml:space="preserve">16.6442089080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7208251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7016735076904</t>
   </si>
   <si>
     <t xml:space="preserve">17.1613502502441</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">17.1421966552734</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1996555328369</t>
+    <t xml:space="preserve">17.1996574401855</t>
   </si>
   <si>
     <t xml:space="preserve">16.9889698028564</t>
@@ -2468,13 +2468,13 @@
     <t xml:space="preserve">16.4526786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4335250854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9123573303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.663366317749</t>
+    <t xml:space="preserve">16.4335231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9123592376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6633644104004</t>
   </si>
   <si>
     <t xml:space="preserve">16.9506645202637</t>
@@ -2483,16 +2483,16 @@
     <t xml:space="preserve">16.931510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8548965454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9657878875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0807094573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.310546875</t>
+    <t xml:space="preserve">16.8548984527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9657897949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0807075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3105487823486</t>
   </si>
   <si>
     <t xml:space="preserve">19.6321239471436</t>
@@ -2501,25 +2501,25 @@
     <t xml:space="preserve">19.9194240570068</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3024921417236</t>
+    <t xml:space="preserve">20.302490234375</t>
   </si>
   <si>
     <t xml:space="preserve">19.7757740020752</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7334403991699</t>
+    <t xml:space="preserve">20.7334384918213</t>
   </si>
   <si>
     <t xml:space="preserve">20.4940223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1109580993652</t>
+    <t xml:space="preserve">20.1109561920166</t>
   </si>
   <si>
     <t xml:space="preserve">19.9673080444336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8715400695801</t>
+    <t xml:space="preserve">19.8715419769287</t>
   </si>
   <si>
     <t xml:space="preserve">20.0151901245117</t>
@@ -2528,16 +2528,16 @@
     <t xml:space="preserve">20.3982563018799</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5419063568115</t>
+    <t xml:space="preserve">20.5419082641602</t>
   </si>
   <si>
     <t xml:space="preserve">20.6376724243164</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9728527069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8770885467529</t>
+    <t xml:space="preserve">20.9728565216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8770866394043</t>
   </si>
   <si>
     <t xml:space="preserve">20.3503742218018</t>
@@ -2546,22 +2546,22 @@
     <t xml:space="preserve">20.0630741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9249725341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7278900146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4884777069092</t>
+    <t xml:space="preserve">20.9249706268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7278938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4884757995605</t>
   </si>
   <si>
     <t xml:space="preserve">19.3448276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5363597869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8236598968506</t>
+    <t xml:space="preserve">19.5363578796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.823657989502</t>
   </si>
   <si>
     <t xml:space="preserve">19.1532936096191</t>
@@ -2573,28 +2573,28 @@
     <t xml:space="preserve">20.4461402893066</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2067222595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1165065765381</t>
+    <t xml:space="preserve">20.2067241668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1165027618408</t>
   </si>
   <si>
     <t xml:space="preserve">21.6911029815674</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3080368041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7868690490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7389888763428</t>
+    <t xml:space="preserve">21.3080387115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7868728637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7389869689941</t>
   </si>
   <si>
     <t xml:space="preserve">21.834753036499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5474548339844</t>
+    <t xml:space="preserve">21.5474529266357</t>
   </si>
   <si>
     <t xml:space="preserve">21.8826370239258</t>
@@ -2603,25 +2603,25 @@
     <t xml:space="preserve">21.9784030914307</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2122707366943</t>
+    <t xml:space="preserve">21.212272644043</t>
   </si>
   <si>
     <t xml:space="preserve">21.355920791626</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4516849517822</t>
+    <t xml:space="preserve">21.4516868591309</t>
   </si>
   <si>
     <t xml:space="preserve">22.3135852813721</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7924175262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3191356658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6487674713135</t>
+    <t xml:space="preserve">22.7924156188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3191337585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6487693786621</t>
   </si>
   <si>
     <t xml:space="preserve">22.4093532562256</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">22.0262870788574</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6432209014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4038066864014</t>
+    <t xml:space="preserve">21.6432228088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4038047790527</t>
   </si>
   <si>
     <t xml:space="preserve">20.8292064666748</t>
@@ -2642,37 +2642,37 @@
     <t xml:space="preserve">20.7813243865967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9305210113525</t>
+    <t xml:space="preserve">21.9305191040039</t>
   </si>
   <si>
     <t xml:space="preserve">24.5162162780762</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9416179656982</t>
+    <t xml:space="preserve">23.9416160583496</t>
   </si>
   <si>
     <t xml:space="preserve">23.4627838134766</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4149017333984</t>
+    <t xml:space="preserve">23.4148998260498</t>
   </si>
   <si>
     <t xml:space="preserve">23.1754856109619</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2712497711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5106639862061</t>
+    <t xml:space="preserve">23.2712516784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5106678009033</t>
   </si>
   <si>
     <t xml:space="preserve">23.22336769104</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7500839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6064338684082</t>
+    <t xml:space="preserve">23.7500820159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6064319610596</t>
   </si>
   <si>
     <t xml:space="preserve">23.0797176361084</t>
@@ -2681,31 +2681,31 @@
     <t xml:space="preserve">23.797966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7021999359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.654317855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.031831741333</t>
+    <t xml:space="preserve">23.7022018432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6543159484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0318336486816</t>
   </si>
   <si>
     <t xml:space="preserve">23.5585498809814</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8403034210205</t>
+    <t xml:space="preserve">22.8403015136719</t>
   </si>
   <si>
     <t xml:space="preserve">22.6008853912354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2657012939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5953369140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2178192138672</t>
+    <t xml:space="preserve">22.2657032012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5953388214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2178211212158</t>
   </si>
   <si>
     <t xml:space="preserve">22.1699371337891</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">24.2289142608643</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8937320709229</t>
+    <t xml:space="preserve">23.8937339782715</t>
   </si>
   <si>
     <t xml:space="preserve">24.4683303833008</t>
@@ -2741,10 +2741,10 @@
     <t xml:space="preserve">25.8090629577637</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9527111053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.665412902832</t>
+    <t xml:space="preserve">25.9527130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6654109954834</t>
   </si>
   <si>
     <t xml:space="preserve">26.4794273376465</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">26.5751953125</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4849739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3892097473145</t>
+    <t xml:space="preserve">27.4849758148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3892078399658</t>
   </si>
   <si>
     <t xml:space="preserve">27.3413257598877</t>
@@ -2768,10 +2768,10 @@
     <t xml:space="preserve">28.4905242919922</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9638061523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2989883422852</t>
+    <t xml:space="preserve">27.9638080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2989902496338</t>
   </si>
   <si>
     <t xml:space="preserve">27.772274017334</t>
@@ -2783,64 +2783,64 @@
     <t xml:space="preserve">27.7243919372559</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5328578948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2455615997314</t>
+    <t xml:space="preserve">27.5328598022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2455596923828</t>
   </si>
   <si>
     <t xml:space="preserve">26.9582595825195</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1497898101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0540256500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7188415527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9287757873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2543525695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8207931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4354095458984</t>
+    <t xml:space="preserve">27.1497917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.054027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.718843460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9287776947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2543506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8207950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4354057312012</t>
   </si>
   <si>
     <t xml:space="preserve">24.5682926177979</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7128105163574</t>
+    <t xml:space="preserve">24.7128124237061</t>
   </si>
   <si>
     <t xml:space="preserve">24.1347351074219</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7609844207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6646404266357</t>
+    <t xml:space="preserve">24.760986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6646385192871</t>
   </si>
   <si>
     <t xml:space="preserve">25.0981960296631</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3988723754883</t>
+    <t xml:space="preserve">26.3988704681396</t>
   </si>
   <si>
     <t xml:space="preserve">26.8324298858643</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4470443725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9171409606934</t>
+    <t xml:space="preserve">26.4470462799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9171390533447</t>
   </si>
   <si>
     <t xml:space="preserve">25.8689670562744</t>
@@ -2849,10 +2849,10 @@
     <t xml:space="preserve">25.4835815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7244472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1463718414307</t>
+    <t xml:space="preserve">25.7244491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.146369934082</t>
   </si>
   <si>
     <t xml:space="preserve">25.579927444458</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">25.9653129577637</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1580066680908</t>
+    <t xml:space="preserve">26.1580047607422</t>
   </si>
   <si>
     <t xml:space="preserve">25.628101348877</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">24.8573303222656</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6762752532959</t>
+    <t xml:space="preserve">25.6762733459473</t>
   </si>
   <si>
     <t xml:space="preserve">25.5317535400391</t>
@@ -2894,34 +2894,34 @@
     <t xml:space="preserve">22.7858867645264</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6530017852783</t>
+    <t xml:space="preserve">23.653003692627</t>
   </si>
   <si>
     <t xml:space="preserve">23.0267524719238</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9304046630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.219446182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4121360778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.448673248291</t>
+    <t xml:space="preserve">22.9304065704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2194442749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4121379852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4486751556396</t>
   </si>
   <si>
     <t xml:space="preserve">21.9669437408447</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8224239349365</t>
+    <t xml:space="preserve">21.8224258422852</t>
   </si>
   <si>
     <t xml:space="preserve">21.5815582275391</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6413669586182</t>
+    <t xml:space="preserve">22.6413650512695</t>
   </si>
   <si>
     <t xml:space="preserve">22.8340606689453</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">22.4968490600586</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1114616394043</t>
+    <t xml:space="preserve">22.1114635467529</t>
   </si>
   <si>
     <t xml:space="preserve">23.1712703704834</t>
@@ -2939,10 +2939,10 @@
     <t xml:space="preserve">22.1596355438232</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0632915496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3888664245605</t>
+    <t xml:space="preserve">22.063289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3888683319092</t>
   </si>
   <si>
     <t xml:space="preserve">21.1480007171631</t>
@@ -2951,13 +2951,13 @@
     <t xml:space="preserve">20.52174949646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5101127624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1845378875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9436740875244</t>
+    <t xml:space="preserve">19.5101146697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1845397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9436721801758</t>
   </si>
   <si>
     <t xml:space="preserve">18.9609413146973</t>
@@ -2966,34 +2966,34 @@
     <t xml:space="preserve">19.1536331176758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1323623657227</t>
+    <t xml:space="preserve">18.1323642730713</t>
   </si>
   <si>
     <t xml:space="preserve">16.8991317749023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9569396972656</t>
+    <t xml:space="preserve">16.9569416046143</t>
   </si>
   <si>
     <t xml:space="preserve">18.0167484283447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.15163230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5542850494385</t>
+    <t xml:space="preserve">18.1516304016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5542869567871</t>
   </si>
   <si>
     <t xml:space="preserve">18.3057861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8433265686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4964771270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6719017028809</t>
+    <t xml:space="preserve">17.8433246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4964790344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6719036102295</t>
   </si>
   <si>
     <t xml:space="preserve">18.2672462463379</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">18.6911716461182</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3828639984131</t>
+    <t xml:space="preserve">18.3828620910645</t>
   </si>
   <si>
     <t xml:space="preserve">18.7682476043701</t>
@@ -3017,22 +3017,22 @@
     <t xml:space="preserve">19.1921730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6064624786377</t>
+    <t xml:space="preserve">19.6064605712891</t>
   </si>
   <si>
     <t xml:space="preserve">19.1150951385498</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2114410400391</t>
+    <t xml:space="preserve">19.2114429473877</t>
   </si>
   <si>
     <t xml:space="preserve">18.6333637237549</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7662487030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6526336669922</t>
+    <t xml:space="preserve">17.7662467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6526355743408</t>
   </si>
   <si>
     <t xml:space="preserve">18.4021339416504</t>
@@ -3044,10 +3044,10 @@
     <t xml:space="preserve">19.4137687683105</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7509784698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1343650817871</t>
+    <t xml:space="preserve">19.7509822845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1343669891357</t>
   </si>
   <si>
     <t xml:space="preserve">18.7489776611328</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">18.9224014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3655967712402</t>
+    <t xml:space="preserve">19.3655948638916</t>
   </si>
   <si>
     <t xml:space="preserve">19.2692489624023</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">18.0938262939453</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7991523742676</t>
+    <t xml:space="preserve">19.7991542816162</t>
   </si>
   <si>
     <t xml:space="preserve">20.040018081665</t>
@@ -3083,13 +3083,13 @@
     <t xml:space="preserve">20.7144432067871</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0516548156738</t>
+    <t xml:space="preserve">21.0516529083252</t>
   </si>
   <si>
     <t xml:space="preserve">21.4852123260498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4370384216309</t>
+    <t xml:space="preserve">21.4370403289795</t>
   </si>
   <si>
     <t xml:space="preserve">21.8705978393555</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">20.8107891082764</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8955001831055</t>
+    <t xml:space="preserve">19.8954982757568</t>
   </si>
   <si>
     <t xml:space="preserve">20.2327117919922</t>
@@ -3125,10 +3125,10 @@
     <t xml:space="preserve">20.4735774993896</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8473262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.249979019165</t>
+    <t xml:space="preserve">19.8473243713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2499809265137</t>
   </si>
   <si>
     <t xml:space="preserve">18.7875175476074</t>
@@ -3137,28 +3137,28 @@
     <t xml:space="preserve">18.5948257446289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5735530853271</t>
+    <t xml:space="preserve">17.5735569000244</t>
   </si>
   <si>
     <t xml:space="preserve">18.8067874908447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.498477935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2287101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0745544433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5562858581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7104415893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9416732788086</t>
+    <t xml:space="preserve">18.4984798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2287082672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.074556350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5562877655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7104396820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.94167137146</t>
   </si>
   <si>
     <t xml:space="preserve">18.5370178222656</t>
@@ -3167,25 +3167,25 @@
     <t xml:space="preserve">18.4406719207764</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2865161895752</t>
+    <t xml:space="preserve">18.2865180969238</t>
   </si>
   <si>
     <t xml:space="preserve">17.9782104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5755558013916</t>
+    <t xml:space="preserve">18.5755577087402</t>
   </si>
   <si>
     <t xml:space="preserve">19.3174209594727</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8453254699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9802093505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4619426727295</t>
+    <t xml:space="preserve">18.8453235626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9802112579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4619407653809</t>
   </si>
   <si>
     <t xml:space="preserve">18.1709022521973</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">17.9204025268555</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6313629150391</t>
+    <t xml:space="preserve">17.6313610076904</t>
   </si>
   <si>
     <t xml:space="preserve">18.2094402313232</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">18.2479782104492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6699028015137</t>
+    <t xml:space="preserve">17.669900894165</t>
   </si>
   <si>
     <t xml:space="preserve">17.3423252105713</t>
@@ -3215,40 +3215,40 @@
     <t xml:space="preserve">16.6293621063232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9934787750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4559383392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2054386138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0512847900391</t>
+    <t xml:space="preserve">15.9934778213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.455940246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.205436706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0512828826904</t>
   </si>
   <si>
     <t xml:space="preserve">16.2247085571289</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4153985977173</t>
+    <t xml:space="preserve">15.4153995513916</t>
   </si>
   <si>
     <t xml:space="preserve">15.5502834320068</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3575916290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7257080078125</t>
+    <t xml:space="preserve">15.357590675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7257099151611</t>
   </si>
   <si>
     <t xml:space="preserve">16.128360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7642478942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.879861831665</t>
+    <t xml:space="preserve">16.7642459869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8798637390137</t>
   </si>
   <si>
     <t xml:space="preserve">17.1110935211182</t>
@@ -3260,10 +3260,10 @@
     <t xml:space="preserve">17.2459774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1689014434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1303634643555</t>
+    <t xml:space="preserve">17.1688995361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1303615570068</t>
   </si>
   <si>
     <t xml:space="preserve">17.9589405059814</t>
@@ -3308,13 +3308,13 @@
     <t xml:space="preserve">20.8875617980957</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7411518096924</t>
+    <t xml:space="preserve">20.741153717041</t>
   </si>
   <si>
     <t xml:space="preserve">20.6435470581055</t>
   </si>
   <si>
-    <t xml:space="preserve">20.448335647583</t>
+    <t xml:space="preserve">20.4483375549316</t>
   </si>
   <si>
     <t xml:space="preserve">20.6923503875732</t>
@@ -3323,13 +3323,13 @@
     <t xml:space="preserve">20.5947437286377</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5459423065186</t>
+    <t xml:space="preserve">20.5459403991699</t>
   </si>
   <si>
     <t xml:space="preserve">20.3019275665283</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3267860412598</t>
+    <t xml:space="preserve">21.3267841339111</t>
   </si>
   <si>
     <t xml:space="preserve">20.4971389770508</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">20.1555194854736</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1067180633545</t>
+    <t xml:space="preserve">20.1067161560059</t>
   </si>
   <si>
     <t xml:space="preserve">20.2531261444092</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">21.0827713012695</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7660102844238</t>
+    <t xml:space="preserve">21.7660083770752</t>
   </si>
   <si>
     <t xml:space="preserve">21.8636150360107</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">22.5956554412842</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9372749328613</t>
+    <t xml:space="preserve">22.9372730255127</t>
   </si>
   <si>
     <t xml:space="preserve">23.083683013916</t>
@@ -3395,10 +3395,10 @@
     <t xml:space="preserve">23.4741039276123</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2300891876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7181167602539</t>
+    <t xml:space="preserve">23.2300910949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7181186676025</t>
   </si>
   <si>
     <t xml:space="preserve">23.6693153381348</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">23.6205139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7669219970703</t>
+    <t xml:space="preserve">23.7669200897217</t>
   </si>
   <si>
     <t xml:space="preserve">23.8645267486572</t>
@@ -3416,22 +3416,22 @@
     <t xml:space="preserve">23.2788944244385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3276977539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9621295928955</t>
+    <t xml:space="preserve">23.3276958465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9621315002441</t>
   </si>
   <si>
     <t xml:space="preserve">24.6941719055176</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3286075592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9869899749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7917766571045</t>
+    <t xml:space="preserve">25.3286094665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.986988067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7917785644531</t>
   </si>
   <si>
     <t xml:space="preserve">24.4989624023438</t>
@@ -3440,25 +3440,25 @@
     <t xml:space="preserve">24.5965671539307</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4501571655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3037490844727</t>
+    <t xml:space="preserve">24.450159072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3037509918213</t>
   </si>
   <si>
     <t xml:space="preserve">24.0109348297119</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7420616149902</t>
+    <t xml:space="preserve">22.7420635223389</t>
   </si>
   <si>
     <t xml:space="preserve">22.644458770752</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1812896728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8884716033936</t>
+    <t xml:space="preserve">23.1812877655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8884735107422</t>
   </si>
   <si>
     <t xml:space="preserve">23.0348796844482</t>
@@ -3467,10 +3467,10 @@
     <t xml:space="preserve">23.1324863433838</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0597362518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2549495697021</t>
+    <t xml:space="preserve">24.0597381591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2549476623535</t>
   </si>
   <si>
     <t xml:space="preserve">24.3525543212891</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">22.3516426086426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9612197875977</t>
+    <t xml:space="preserve">21.9612216949463</t>
   </si>
   <si>
     <t xml:space="preserve">21.9124183654785</t>
@@ -3491,19 +3491,19 @@
     <t xml:space="preserve">22.3028392791748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.546854019165</t>
+    <t xml:space="preserve">22.5468521118164</t>
   </si>
   <si>
     <t xml:space="preserve">22.7908668518066</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4980487823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6932621002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6684036254883</t>
+    <t xml:space="preserve">22.4980506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6932601928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6684055328369</t>
   </si>
   <si>
     <t xml:space="preserve">21.5707988739014</t>
@@ -3527,16 +3527,16 @@
     <t xml:space="preserve">21.4731941223145</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2291793823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0339698791504</t>
+    <t xml:space="preserve">21.2291812896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0339679718018</t>
   </si>
   <si>
     <t xml:space="preserve">21.1803779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0100212097168</t>
+    <t xml:space="preserve">22.0100231170654</t>
   </si>
   <si>
     <t xml:space="preserve">22.107629776001</t>
@@ -3551,7 +3551,7 @@
     <t xml:space="preserve">24.2061443328857</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1821975708008</t>
+    <t xml:space="preserve">25.1821994781494</t>
   </si>
   <si>
     <t xml:space="preserve">26.2558574676514</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">26.0118446350098</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8654384613037</t>
+    <t xml:space="preserve">25.8654365539551</t>
   </si>
   <si>
     <t xml:space="preserve">25.8166351318359</t>
@@ -3578,13 +3578,13 @@
     <t xml:space="preserve">27.0855045318604</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4022655487061</t>
+    <t xml:space="preserve">26.4022674560547</t>
   </si>
   <si>
     <t xml:space="preserve">26.548677444458</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4750175476074</t>
+    <t xml:space="preserve">25.4750156402588</t>
   </si>
   <si>
     <t xml:space="preserve">24.5477638244629</t>
@@ -3593,10 +3593,10 @@
     <t xml:space="preserve">24.88938331604</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1573429107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4013576507568</t>
+    <t xml:space="preserve">24.157341003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4013557434082</t>
   </si>
   <si>
     <t xml:space="preserve">24.7429752349854</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">25.5726222991943</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6702251434326</t>
+    <t xml:space="preserve">25.6702270507812</t>
   </si>
   <si>
     <t xml:space="preserve">25.5238170623779</t>
@@ -4590,6 +4590,9 @@
   </si>
   <si>
     <t xml:space="preserve">47.7999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0999984741211</t>
   </si>
 </sst>
 </file>
@@ -69876,7 +69879,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6911921296</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>34981</v>
@@ -69897,6 +69900,32 @@
         <v>1525</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6910648148</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>55471</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>48.4000015258789</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>47</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>47.0999984741211</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1526</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="1529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="1530">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6962642669678</t>
+    <t xml:space="preserve">15.6962623596191</t>
   </si>
   <si>
     <t xml:space="preserve">DAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8255224227905</t>
+    <t xml:space="preserve">15.8255233764648</t>
   </si>
   <si>
     <t xml:space="preserve">15.3269386291504</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6344566345215</t>
+    <t xml:space="preserve">14.6344547271729</t>
   </si>
   <si>
     <t xml:space="preserve">14.3112964630127</t>
@@ -59,58 +59,58 @@
     <t xml:space="preserve">14.0343027114868</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3851623535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1358690261841</t>
+    <t xml:space="preserve">14.3851613998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1358680725098</t>
   </si>
   <si>
     <t xml:space="preserve">13.9604387283325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.194091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.880166053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9724979400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3723478317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.037130355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2217922210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0009536743164</t>
+    <t xml:space="preserve">13.1940927505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8801670074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9724988937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3723459243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0371294021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2217893600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0009517669678</t>
   </si>
   <si>
     <t xml:space="preserve">16.1579151153564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4349060058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1948490142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4718399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2289543151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7118988037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5762319564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2133140563965</t>
+    <t xml:space="preserve">16.434907913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1948509216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4718418121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2289524078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7119026184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.576229095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2133159637451</t>
   </si>
   <si>
     <t xml:space="preserve">15.4100341796875</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">15.0407114028931</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0499429702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4561977386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2069053649902</t>
+    <t xml:space="preserve">15.0499439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4562005996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2069063186646</t>
   </si>
   <si>
     <t xml:space="preserve">15.1053438186646</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">16.3425750732422</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8780975341797</t>
+    <t xml:space="preserve">16.8780994415283</t>
   </si>
   <si>
     <t xml:space="preserve">17.0350608825684</t>
@@ -146,55 +146,55 @@
     <t xml:space="preserve">17.1735553741455</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0812244415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8227005004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4626083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4533748626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9427299499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7488307952881</t>
+    <t xml:space="preserve">17.081226348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8226985931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4626064300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4533767700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9427318572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7488346099854</t>
   </si>
   <si>
     <t xml:space="preserve">17.293586730957</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4228515625</t>
+    <t xml:space="preserve">17.4228496551514</t>
   </si>
   <si>
     <t xml:space="preserve">17.4874820709229</t>
   </si>
   <si>
-    <t xml:space="preserve">17.552116394043</t>
+    <t xml:space="preserve">17.5521144866943</t>
   </si>
   <si>
     <t xml:space="preserve">16.6472702026367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3397541046143</t>
+    <t xml:space="preserve">17.3397521972656</t>
   </si>
   <si>
     <t xml:space="preserve">17.6352119445801</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9888935089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3766860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5798149108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1273918151855</t>
+    <t xml:space="preserve">16.9888954162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3766841888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5798168182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1273937225342</t>
   </si>
   <si>
     <t xml:space="preserve">16.3241119384766</t>
@@ -203,28 +203,28 @@
     <t xml:space="preserve">16.665735244751</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0535259246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4043846130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6842002868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6380367279053</t>
+    <t xml:space="preserve">17.053524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4043865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6842021942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6380386352539</t>
   </si>
   <si>
     <t xml:space="preserve">17.238187789917</t>
   </si>
   <si>
-    <t xml:space="preserve">17.68137550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7552394866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5244121551514</t>
+    <t xml:space="preserve">17.6813774108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.755241394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5244140625</t>
   </si>
   <si>
     <t xml:space="preserve">17.9860668182373</t>
@@ -233,151 +233,151 @@
     <t xml:space="preserve">18.2353610992432</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1430320739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9122009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7183055877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4661903381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5308208465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.558521270752</t>
+    <t xml:space="preserve">18.143030166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.912202835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7183113098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4661884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.530818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5585193634033</t>
   </si>
   <si>
     <t xml:space="preserve">18.2168941497803</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4477214813232</t>
+    <t xml:space="preserve">18.4477252960205</t>
   </si>
   <si>
     <t xml:space="preserve">18.1522617340088</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0137672424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5890445709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2658882141113</t>
+    <t xml:space="preserve">18.0137691497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5890426635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.26589012146</t>
   </si>
   <si>
     <t xml:space="preserve">17.6075096130371</t>
   </si>
   <si>
-    <t xml:space="preserve">17.284351348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1920223236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8873310089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9519634246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6749668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4256782531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2594795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3610420227051</t>
+    <t xml:space="preserve">17.2843532562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1920204162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8873291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9519653320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6749706268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4256744384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2594814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3610458374023</t>
   </si>
   <si>
     <t xml:space="preserve">16.8596305847168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5641689300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5272369384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.277946472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.47825050354</t>
+    <t xml:space="preserve">16.5641708374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5272407531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2779445648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4782466888428</t>
   </si>
   <si>
     <t xml:space="preserve">16.6288032531738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6103363037109</t>
+    <t xml:space="preserve">16.6103420257568</t>
   </si>
   <si>
     <t xml:space="preserve">17.3582172393799</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1089248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1550922393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.917854309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9547882080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.059178352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8652849197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.169976234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4377346038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0655841827393</t>
+    <t xml:space="preserve">17.108922958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1550884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9178552627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9547891616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0591773986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8652830123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1699743270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4377326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0655860900879</t>
   </si>
   <si>
     <t xml:space="preserve">15.0868759155273</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5513563156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9853115081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6252222061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7821855545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5115995407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1330413818359</t>
+    <t xml:space="preserve">14.5513582229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9853134155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6252212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7821836471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5115966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1330404281616</t>
   </si>
   <si>
     <t xml:space="preserve">14.72678565979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0989351272583</t>
+    <t xml:space="preserve">14.0989360809326</t>
   </si>
   <si>
     <t xml:space="preserve">14.3574628829956</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7544860839844</t>
+    <t xml:space="preserve">14.7544841766357</t>
   </si>
   <si>
     <t xml:space="preserve">15.5023651123047</t>
@@ -386,46 +386,46 @@
     <t xml:space="preserve">15.4192705154419</t>
   </si>
   <si>
-    <t xml:space="preserve">15.603931427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3546352386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4285011291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4008016586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4838981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.250244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7239608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4931325912476</t>
+    <t xml:space="preserve">15.6039323806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3546342849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4284992218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4008045196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4839019775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2502460479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7239618301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4931344985962</t>
   </si>
   <si>
     <t xml:space="preserve">16.2317790985107</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9363222122192</t>
+    <t xml:space="preserve">15.9363231658936</t>
   </si>
   <si>
     <t xml:space="preserve">16.1856155395508</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2871780395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.176383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0932846069336</t>
+    <t xml:space="preserve">16.2871799468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1763820648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0932807922363</t>
   </si>
   <si>
     <t xml:space="preserve">17.2566566467285</t>
@@ -434,193 +434,193 @@
     <t xml:space="preserve">16.9242630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.721134185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7580642700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7275447845459</t>
+    <t xml:space="preserve">16.7211322784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7580680847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7275390625</t>
   </si>
   <si>
     <t xml:space="preserve">17.2751159667969</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1458568572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3120517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4505481719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2040824890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8901567459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8624582290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9270887374878</t>
+    <t xml:space="preserve">17.1458549499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3120498657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4505500793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.204080581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.890154838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8624572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270877838135</t>
   </si>
   <si>
     <t xml:space="preserve">16.0563507080078</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7424268722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7701244354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6685638427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5946950912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7147274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1394481658936</t>
+    <t xml:space="preserve">15.7424249649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7701263427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6685590744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5946960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7147254943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1394462585449</t>
   </si>
   <si>
     <t xml:space="preserve">16.8134651184082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1671504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6408624649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6500949859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8070592880249</t>
+    <t xml:space="preserve">16.1671485900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6408634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6500978469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8070554733276</t>
   </si>
   <si>
     <t xml:space="preserve">15.4654340744019</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2623052597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3366203308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4109373092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6524572372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7360591888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8939771652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.624587059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0765190124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4295120239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5224056243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5131177902222</t>
+    <t xml:space="preserve">15.2623071670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3366193771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4109354019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6524562835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7360610961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8939762115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6245880126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0765199661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4295129776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.522403717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131196975708</t>
   </si>
   <si>
     <t xml:space="preserve">15.1601238250732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8661079406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3305721282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9311370849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4945373535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.606011390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.318042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.884690284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0518951416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8382425308228</t>
+    <t xml:space="preserve">15.8661098480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3305759429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9311323165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4945392608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6060085296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.318039894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8846912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0518970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8382415771484</t>
   </si>
   <si>
     <t xml:space="preserve">16.5813846588135</t>
   </si>
   <si>
-    <t xml:space="preserve">17.185188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2595062255859</t>
+    <t xml:space="preserve">17.1851902008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2595024108887</t>
   </si>
   <si>
     <t xml:space="preserve">17.138744354248</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2223472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0272731781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9529571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4884910583496</t>
+    <t xml:space="preserve">17.2223491668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.027271270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.952953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4884929656982</t>
   </si>
   <si>
     <t xml:space="preserve">17.0922966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9065074920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1666126251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.742546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.900463104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9376201629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8818874359131</t>
+    <t xml:space="preserve">16.9065093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1666107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7425479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9004650115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9376239776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8818836212158</t>
   </si>
   <si>
     <t xml:space="preserve">18.4299545288086</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9037055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9501552581787</t>
+    <t xml:space="preserve">18.9037075042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9501533508301</t>
   </si>
   <si>
     <t xml:space="preserve">19.5539569854736</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">18.9129981994629</t>
   </si>
   <si>
-    <t xml:space="preserve">19.461067199707</t>
+    <t xml:space="preserve">19.4610691070557</t>
   </si>
   <si>
     <t xml:space="preserve">19.3310165405273</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1823825836182</t>
+    <t xml:space="preserve">19.1823863983154</t>
   </si>
   <si>
     <t xml:space="preserve">19.0802059173584</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">18.9408645629883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9315757751465</t>
+    <t xml:space="preserve">18.9315738677979</t>
   </si>
   <si>
     <t xml:space="preserve">18.7550792694092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5785846710205</t>
+    <t xml:space="preserve">18.5785827636719</t>
   </si>
   <si>
     <t xml:space="preserve">18.4020881652832</t>
@@ -671,10 +671,10 @@
     <t xml:space="preserve">18.1141204833984</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4578227996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5321388244629</t>
+    <t xml:space="preserve">18.457820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5321369171143</t>
   </si>
   <si>
     <t xml:space="preserve">18.4671096801758</t>
@@ -683,25 +683,25 @@
     <t xml:space="preserve">18.3742179870605</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4856872558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2813262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3277702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5135555267334</t>
+    <t xml:space="preserve">18.485689163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2813282012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3277721405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5135593414307</t>
   </si>
   <si>
     <t xml:space="preserve">18.6157398223877</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6250267028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7272129058838</t>
+    <t xml:space="preserve">18.6250305175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7272109985352</t>
   </si>
   <si>
     <t xml:space="preserve">19.0430469512939</t>
@@ -713,49 +713,49 @@
     <t xml:space="preserve">19.0894947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1266498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3681716918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.451774597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9594459533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2474117279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.507511138916</t>
+    <t xml:space="preserve">19.126651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3681755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4517765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9594421386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2474098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5075130462646</t>
   </si>
   <si>
     <t xml:space="preserve">19.098783493042</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2195434570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3495960235596</t>
+    <t xml:space="preserve">19.2195415496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3495941162109</t>
   </si>
   <si>
     <t xml:space="preserve">19.0337581634521</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2288341522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.386754989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2845668792725</t>
+    <t xml:space="preserve">19.228832244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3867492675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2845706939697</t>
   </si>
   <si>
     <t xml:space="preserve">19.9162425994873</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0091342926025</t>
+    <t xml:space="preserve">20.0091361999512</t>
   </si>
   <si>
     <t xml:space="preserve">20.3807067871094</t>
@@ -764,31 +764,31 @@
     <t xml:space="preserve">20.6222286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8544616699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9659290313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9473495483398</t>
+    <t xml:space="preserve">20.8544597625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9659328460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9473514556885</t>
   </si>
   <si>
     <t xml:space="preserve">20.148473739624</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6129398345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3899955749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2506561279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5757827758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6500968933105</t>
+    <t xml:space="preserve">20.6129379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3899974822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2506580352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5757789611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6500930786133</t>
   </si>
   <si>
     <t xml:space="preserve">20.6036491394043</t>
@@ -797,85 +797,85 @@
     <t xml:space="preserve">20.5014667510986</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5293350219727</t>
+    <t xml:space="preserve">20.529333114624</t>
   </si>
   <si>
     <t xml:space="preserve">20.6593837738037</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4828853607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8173007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.863748550415</t>
+    <t xml:space="preserve">20.482889175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8173027038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8637466430664</t>
   </si>
   <si>
     <t xml:space="preserve">20.4550189971924</t>
   </si>
   <si>
-    <t xml:space="preserve">20.780143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6440467834473</t>
+    <t xml:space="preserve">20.7801475524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6440486907959</t>
   </si>
   <si>
     <t xml:space="preserve">21.495418548584</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3653697967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3189277648926</t>
+    <t xml:space="preserve">21.3653717041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3189239501953</t>
   </si>
   <si>
     <t xml:space="preserve">21.1331405639648</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1238498687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9287757873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2724800109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1052684783936</t>
+    <t xml:space="preserve">21.1238479614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9287738800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2724781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1052703857422</t>
   </si>
   <si>
     <t xml:space="preserve">21.3467922210693</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2260303497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6408023834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1702976226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9566402435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1145610809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2538967132568</t>
+    <t xml:space="preserve">21.2260322570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6408061981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1702938079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9566383361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.114559173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2538986206055</t>
   </si>
   <si>
     <t xml:space="preserve">21.2446098327637</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3374996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2817668914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9380626678467</t>
+    <t xml:space="preserve">21.3375015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2817687988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9380664825439</t>
   </si>
   <si>
     <t xml:space="preserve">21.1795845031738</t>
@@ -887,121 +887,121 @@
     <t xml:space="preserve">20.3156814575195</t>
   </si>
   <si>
-    <t xml:space="preserve">20.399284362793</t>
+    <t xml:space="preserve">20.3992824554443</t>
   </si>
   <si>
     <t xml:space="preserve">20.4085712432861</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3249702453613</t>
+    <t xml:space="preserve">20.3249683380127</t>
   </si>
   <si>
     <t xml:space="preserve">20.6315155029297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2785243988037</t>
+    <t xml:space="preserve">20.2785224914551</t>
   </si>
   <si>
     <t xml:space="preserve">20.0462913513184</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2134990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7954769134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9069538116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2692317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2971019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5479125976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4364433288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9533958435059</t>
+    <t xml:space="preserve">20.2135009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.795482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9069519042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2692337036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2971038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5479145050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4364414215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9533977508545</t>
   </si>
   <si>
     <t xml:space="preserve">19.8326377868652</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8883724212646</t>
+    <t xml:space="preserve">19.8883743286133</t>
   </si>
   <si>
     <t xml:space="preserve">19.7211647033691</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9255294799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0741577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9998455047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1113166809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6747169494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6686706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2413673400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9719772338867</t>
+    <t xml:space="preserve">19.9255313873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0741596221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9998435974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1113147735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6747188568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6686744689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2413654327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9719753265381</t>
   </si>
   <si>
     <t xml:space="preserve">19.7304534912109</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4178600311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1298961639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4921760559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8451728820801</t>
+    <t xml:space="preserve">20.4178619384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1298942565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4921741485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8451709747314</t>
   </si>
   <si>
     <t xml:space="preserve">20.3435478210449</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5664901733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8916168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1981620788574</t>
+    <t xml:space="preserve">20.5664920806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8916149139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1981601715088</t>
   </si>
   <si>
     <t xml:space="preserve">20.7244071960449</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4736022949219</t>
+    <t xml:space="preserve">20.4736003875732</t>
   </si>
   <si>
     <t xml:space="preserve">20.3342609405518</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3714160919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8790855407715</t>
+    <t xml:space="preserve">20.3714179992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8790817260742</t>
   </si>
   <si>
     <t xml:space="preserve">19.841926574707</t>
@@ -1010,319 +1010,319 @@
     <t xml:space="preserve">19.767614364624</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9812641143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0927352905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5200443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9905548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5353813171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2566986083984</t>
+    <t xml:space="preserve">19.9812660217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.092737197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5200462341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9905529022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5353832244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2567005157471</t>
   </si>
   <si>
     <t xml:space="preserve">18.7829475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8386859893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6343193054199</t>
+    <t xml:space="preserve">18.8386821746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6343154907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.996603012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6807632446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5600051879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6621875762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4392471313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8108139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1359424591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.977933883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9499282836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.529857635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3058166503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9044151306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8484039306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6430339813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6710395812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9417514801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.895076751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9697570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2684745788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4645080566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5858612060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4084987640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1657905578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4925155639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3618259429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2218017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6698760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7725620269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.697883605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.688549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6138706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3524894714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3804950714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4458408355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4831790924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4738464355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6605434417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7072200775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5951976776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3898296356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5018482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9032516479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1832981109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4633483886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7433948516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5368671417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2836608886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5637092590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.517032623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.377010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6103820800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4703578948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7504062652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7970848083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0036125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4435138702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0502891540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6302146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7702407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7235660552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0969619750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1903133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1436367034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8635883331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6768894195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7037334442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2171535491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8904323577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0771293640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9837818145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.816915512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.236988067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3034915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2101402282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9102630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5835399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.956937789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3303375244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3968410491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4901924133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.116792678833</t>
   </si>
   <si>
     <t xml:space="preserve">18.9966011047363</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6807670593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5600032806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6621856689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4392433166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8108158111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1359405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9779319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9499263763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5298538208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3058166503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9044132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8484058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6430358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6710414886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9417533874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8950786590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9697589874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2684745788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4645080566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.585865020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4084968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1657905578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4925155639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3618240356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2217998504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6698799133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7725639343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.697883605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6885471343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6138687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3524913787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3804950714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4458408355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4831790924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4738464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6605434417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.707218170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5951995849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3898315429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5018463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9032516479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1833000183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4633464813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7433929443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5368671417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2836608886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5637092590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5170364379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3770122528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6103839874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4703598022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7504062652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7970848083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0036106109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4435157775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0502853393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6302165985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7702369689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7235660552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0969619750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1903114318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1436386108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8635864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6768913269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7037353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2171516418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8904342651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0771312713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9837818145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8169136047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.236988067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3034915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2101440429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9102630615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5835380554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9569396972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3303356170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3968410491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4901924133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.116792678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9965991973877</t>
-  </si>
-  <si>
     <t xml:space="preserve">19.0432758331299</t>
   </si>
   <si>
-    <t xml:space="preserve">19.136625289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3233242034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7900733947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6033706665039</t>
+    <t xml:space="preserve">19.1366271972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3233222961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7900695800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6033725738525</t>
   </si>
   <si>
     <t xml:space="preserve">20.3501682281494</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2568206787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.976770401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1634674072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0234432220459</t>
+    <t xml:space="preserve">20.2568187713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9767684936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1634712219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0234470367432</t>
   </si>
   <si>
     <t xml:space="preserve">19.8834190368652</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9300956726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4166717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.556697845459</t>
+    <t xml:space="preserve">19.9300937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4166736602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5566997528076</t>
   </si>
   <si>
     <t xml:space="preserve">19.5100231170654</t>
@@ -1331,94 +1331,94 @@
     <t xml:space="preserve">19.6500453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">19.696720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2766456604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2299747467041</t>
+    <t xml:space="preserve">19.6967220306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2766494750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2299766540527</t>
   </si>
   <si>
     <t xml:space="preserve">19.3699989318848</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8367443084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4236888885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0701198577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7177143096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3093004226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7013664245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7678718566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4691553115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8052129745483</t>
+    <t xml:space="preserve">19.8367462158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4236850738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0701179504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.717716217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3093013763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7013673782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7678747177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4691543579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.805212020874</t>
   </si>
   <si>
     <t xml:space="preserve">15.4026489257812</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6266851425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0000839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333404541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3279685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4586601257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8694000244141</t>
+    <t xml:space="preserve">15.62668800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0000858306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333375930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3279714584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4586582183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8693952560425</t>
   </si>
   <si>
     <t xml:space="preserve">15.794716835022</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6640272140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5893487930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3839797973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0105819702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8602867126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5784893035889</t>
+    <t xml:space="preserve">15.6640291213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5893516540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3839778900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0105810165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8602876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5784873962402</t>
   </si>
   <si>
     <t xml:space="preserve">14.4094076156616</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4469804763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9166479110718</t>
+    <t xml:space="preserve">14.4469795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9166488647461</t>
   </si>
   <si>
     <t xml:space="preserve">14.9354343414307</t>
@@ -1427,22 +1427,22 @@
     <t xml:space="preserve">14.6536350250244</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1420907974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4426774978638</t>
+    <t xml:space="preserve">15.14208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4426755905151</t>
   </si>
   <si>
     <t xml:space="preserve">15.2735958099365</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0712461471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9209518432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6015787124634</t>
+    <t xml:space="preserve">14.0712451934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.920952796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6015777587891</t>
   </si>
   <si>
     <t xml:space="preserve">13.7330856323242</t>
@@ -1454,49 +1454,49 @@
     <t xml:space="preserve">14.1651802062988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1463937759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2215394973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9585256576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6391544342041</t>
+    <t xml:space="preserve">14.1463928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2215423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9585266113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6391525268555</t>
   </si>
   <si>
     <t xml:space="preserve">13.6203651428223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7894468307495</t>
+    <t xml:space="preserve">13.7894458770752</t>
   </si>
   <si>
     <t xml:space="preserve">14.0524597167969</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2027521133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5221290588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7475662231445</t>
+    <t xml:space="preserve">14.2027540206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5221261978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7475690841675</t>
   </si>
   <si>
     <t xml:space="preserve">15.2172365188599</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1233043670654</t>
+    <t xml:space="preserve">15.1233034133911</t>
   </si>
   <si>
     <t xml:space="preserve">15.029369354248</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0669431686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8978605270386</t>
+    <t xml:space="preserve">15.0669422149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8978614807129</t>
   </si>
   <si>
     <t xml:space="preserve">15.1045160293579</t>
@@ -1505,61 +1505,61 @@
     <t xml:space="preserve">15.1608753204346</t>
   </si>
   <si>
-    <t xml:space="preserve">15.198450088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5366115570068</t>
+    <t xml:space="preserve">15.1984491348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366106033325</t>
   </si>
   <si>
     <t xml:space="preserve">15.9687061309814</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8141040802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.889253616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9080410003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4947338104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4195861816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2692909240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3632278442383</t>
+    <t xml:space="preserve">16.8141059875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8892517089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9080390930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4947319030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.419584274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2692928314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3632259368896</t>
   </si>
   <si>
     <t xml:space="preserve">15.9874906539917</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8747701644897</t>
+    <t xml:space="preserve">15.8747682571411</t>
   </si>
   <si>
     <t xml:space="preserve">15.8184108734131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1377868652344</t>
+    <t xml:space="preserve">16.1377849578857</t>
   </si>
   <si>
     <t xml:space="preserve">16.1565723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2505054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6262378692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5135173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2880783081055</t>
+    <t xml:space="preserve">16.2505035400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.62624168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.513521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2880802154541</t>
   </si>
   <si>
     <t xml:space="preserve">16.4383735656738</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">16.4571590423584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2317180633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6074542999268</t>
+    <t xml:space="preserve">16.2317199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6074504852295</t>
   </si>
   <si>
     <t xml:space="preserve">16.7201728820801</t>
@@ -1583,46 +1583,46 @@
     <t xml:space="preserve">16.3256511688232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8559846878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.949914932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9311323165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1189975738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0062770843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3444366455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4007987976074</t>
+    <t xml:space="preserve">15.8559827804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9499187469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9311304092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1189956665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0062789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3444385528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4007968902588</t>
   </si>
   <si>
     <t xml:space="preserve">16.5323047637939</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7765331268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9456157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4716396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.279468536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.260684967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2418956756592</t>
+    <t xml:space="preserve">16.7765350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9456119537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.471643447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2794723510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2606830596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2418975830078</t>
   </si>
   <si>
     <t xml:space="preserve">18.1103897094727</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">17.1334800720215</t>
   </si>
   <si>
-    <t xml:space="preserve">17.001974105835</t>
+    <t xml:space="preserve">17.0019760131836</t>
   </si>
   <si>
     <t xml:space="preserve">16.9831867218018</t>
@@ -1646,43 +1646,43 @@
     <t xml:space="preserve">16.6450252532959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9643974304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8328952789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0583324432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1522655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2274150848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7577457427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2129344940186</t>
+    <t xml:space="preserve">16.9643993377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.832893371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0583343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1522636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2274131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7577476501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2129325866699</t>
   </si>
   <si>
     <t xml:space="preserve">15.4990367889404</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5178232192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.461462020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1796636581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6912088394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8039274215698</t>
+    <t xml:space="preserve">15.517822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4614629745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1796617507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6912078857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8039283752441</t>
   </si>
   <si>
     <t xml:space="preserve">15.0857286453247</t>
@@ -1703,13 +1703,13 @@
     <t xml:space="preserve">14.6724214553833</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3718338012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8227138519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5597009658813</t>
+    <t xml:space="preserve">14.3718347549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.822714805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.559700012207</t>
   </si>
   <si>
     <t xml:space="preserve">14.4657669067383</t>
@@ -1724,25 +1724,25 @@
     <t xml:space="preserve">15.4051036834717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3863162994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.668116569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2360219955444</t>
+    <t xml:space="preserve">15.3863153457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6681175231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2360229492188</t>
   </si>
   <si>
     <t xml:space="preserve">15.5929708480835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4238891601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3299560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0481557846069</t>
+    <t xml:space="preserve">15.4238901138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3299551010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0481567382812</t>
   </si>
   <si>
     <t xml:space="preserve">14.8790760040283</t>
@@ -1751,43 +1751,43 @@
     <t xml:space="preserve">14.5409135818481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7851409912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6160621643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2966871261597</t>
+    <t xml:space="preserve">14.7851419448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6160612106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.296688079834</t>
   </si>
   <si>
     <t xml:space="preserve">14.2778997421265</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0900325775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9021673202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7706575393677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4281940460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2591133117676</t>
+    <t xml:space="preserve">14.090033531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9021654129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7706594467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4281930923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2591152191162</t>
   </si>
   <si>
     <t xml:space="preserve">13.8082323074341</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8458051681519</t>
+    <t xml:space="preserve">13.8458061218262</t>
   </si>
   <si>
     <t xml:space="preserve">14.0336723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9397401809692</t>
+    <t xml:space="preserve">13.9397382736206</t>
   </si>
   <si>
     <t xml:space="preserve">14.2403268814087</t>
@@ -1796,82 +1796,82 @@
     <t xml:space="preserve">14.0148868560791</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5972747802734</t>
+    <t xml:space="preserve">14.5972738265991</t>
   </si>
   <si>
     <t xml:space="preserve">13.9960994720459</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3675289154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1839666366577</t>
+    <t xml:space="preserve">15.3675308227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.183967590332</t>
   </si>
   <si>
     <t xml:space="preserve">14.1088199615479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4845542907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.991795539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2923831939697</t>
+    <t xml:space="preserve">14.4845533370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9917964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.292384147644</t>
   </si>
   <si>
     <t xml:space="preserve">15.0758924484253</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0569305419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9052228927612</t>
+    <t xml:space="preserve">15.0569295883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9052238464355</t>
   </si>
   <si>
     <t xml:space="preserve">14.8104057312012</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8862581253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3793058395386</t>
+    <t xml:space="preserve">14.8862590789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3793067932129</t>
   </si>
   <si>
     <t xml:space="preserve">15.6827230453491</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4602222442627</t>
+    <t xml:space="preserve">16.4602203369141</t>
   </si>
   <si>
     <t xml:space="preserve">16.3274765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7016859054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6637592315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5310144424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5499792098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551610946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7585754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.796501159668</t>
+    <t xml:space="preserve">15.7016839981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6637573242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5310134887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5499773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7585763931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7965030670166</t>
   </si>
   <si>
     <t xml:space="preserve">16.1757698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">15.720645904541</t>
+    <t xml:space="preserve">15.7206478118896</t>
   </si>
   <si>
     <t xml:space="preserve">15.6068677902222</t>
@@ -1883,49 +1883,49 @@
     <t xml:space="preserve">16.043025970459</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9861373901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4172334671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344306945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5689401626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4361982345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5879058837891</t>
+    <t xml:space="preserve">15.9861364364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4172353744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344287872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5689420700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4361991882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5879049301147</t>
   </si>
   <si>
     <t xml:space="preserve">15.246563911438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1138181686401</t>
+    <t xml:space="preserve">15.1138210296631</t>
   </si>
   <si>
     <t xml:space="preserve">14.9810771942139</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2086381912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7535171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9431495666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5069913864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0329084396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9380893707275</t>
+    <t xml:space="preserve">15.2086391448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7535152435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9431505203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5069923400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0329074859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9380903244019</t>
   </si>
   <si>
     <t xml:space="preserve">14.2225408554077</t>
@@ -1934,52 +1934,52 @@
     <t xml:space="preserve">14.6018085479736</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7914438247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5828447341919</t>
+    <t xml:space="preserve">14.7914428710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5828456878662</t>
   </si>
   <si>
     <t xml:space="preserve">14.3932113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4311370849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6207714080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3363208770752</t>
+    <t xml:space="preserve">14.4311380386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6207723617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3363227844238</t>
   </si>
   <si>
     <t xml:space="preserve">14.2794313430786</t>
   </si>
   <si>
-    <t xml:space="preserve">14.051869392395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6915664672852</t>
+    <t xml:space="preserve">14.0518712997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6915655136108</t>
   </si>
   <si>
     <t xml:space="preserve">13.1416273117065</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0088844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3691883087158</t>
+    <t xml:space="preserve">13.008885383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3691892623901</t>
   </si>
   <si>
     <t xml:space="preserve">13.0847387313843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8002853393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4210195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1744947433472</t>
+    <t xml:space="preserve">12.8002872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4210186004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1744956970215</t>
   </si>
   <si>
     <t xml:space="preserve">11.9469347000122</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">11.4728498458862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0366916656494</t>
+    <t xml:space="preserve">11.0366926193237</t>
   </si>
   <si>
     <t xml:space="preserve">10.1264495849609</t>
@@ -1997,34 +1997,34 @@
     <t xml:space="preserve">9.95577812194824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59547424316406</t>
+    <t xml:space="preserve">9.59547519683838</t>
   </si>
   <si>
     <t xml:space="preserve">8.91279220581055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41532230377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0973653793335</t>
+    <t xml:space="preserve">9.41532325744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09736633300781</t>
   </si>
   <si>
     <t xml:space="preserve">8.55248832702637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10242748260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1643762588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7522401809692</t>
+    <t xml:space="preserve">9.10242652893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1643772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7522411346436</t>
   </si>
   <si>
     <t xml:space="preserve">11.9279708862305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8951044082642</t>
+    <t xml:space="preserve">12.8951034545898</t>
   </si>
   <si>
     <t xml:space="preserve">11.6055936813354</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">10.9229116439819</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6384620666504</t>
+    <t xml:space="preserve">10.6384611129761</t>
   </si>
   <si>
     <t xml:space="preserve">10.0695581436157</t>
@@ -2048,31 +2048,31 @@
     <t xml:space="preserve">10.6194972991943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7332773208618</t>
+    <t xml:space="preserve">10.7332782745361</t>
   </si>
   <si>
     <t xml:space="preserve">11.1125459671021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9039487838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5815706253052</t>
+    <t xml:space="preserve">10.9039478302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5815696716309</t>
   </si>
   <si>
     <t xml:space="preserve">10.2023029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87992382049561</t>
+    <t xml:space="preserve">9.87992572784424</t>
   </si>
   <si>
     <t xml:space="preserve">10.2212648391724</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5057172775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4298639297485</t>
+    <t xml:space="preserve">10.5057163238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4298629760742</t>
   </si>
   <si>
     <t xml:space="preserve">10.771203994751</t>
@@ -2084,19 +2084,19 @@
     <t xml:space="preserve">10.6953496932983</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8091306686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8280944824219</t>
+    <t xml:space="preserve">10.8091316223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8280954360962</t>
   </si>
   <si>
     <t xml:space="preserve">10.543643951416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9987659454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9418745040894</t>
+    <t xml:space="preserve">10.9987649917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9418754577637</t>
   </si>
   <si>
     <t xml:space="preserve">11.4918127059937</t>
@@ -2105,19 +2105,19 @@
     <t xml:space="preserve">11.567666053772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0556554794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4159593582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5107765197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7952270507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0038242340088</t>
+    <t xml:space="preserve">11.0556545257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4159603118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5107774734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7952280044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0038251876831</t>
   </si>
   <si>
     <t xml:space="preserve">12.2882747650146</t>
@@ -2129,10 +2129,10 @@
     <t xml:space="preserve">12.0986413955688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8521165847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2263250350952</t>
+    <t xml:space="preserve">11.8521175384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2263269424438</t>
   </si>
   <si>
     <t xml:space="preserve">11.0177278518677</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">11.1883983612061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0935821533203</t>
+    <t xml:space="preserve">11.0935831069946</t>
   </si>
   <si>
     <t xml:space="preserve">10.8849840164185</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">11.2073612213135</t>
   </si>
   <si>
-    <t xml:space="preserve">11.340106010437</t>
+    <t xml:space="preserve">11.3401050567627</t>
   </si>
   <si>
     <t xml:space="preserve">11.2832145690918</t>
@@ -2174,22 +2174,22 @@
     <t xml:space="preserve">11.0746192932129</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9798021316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6005344390869</t>
+    <t xml:space="preserve">10.9798011779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6005334854126</t>
   </si>
   <si>
     <t xml:space="preserve">10.3729734420776</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4677906036377</t>
+    <t xml:space="preserve">10.467791557312</t>
   </si>
   <si>
     <t xml:space="preserve">11.6435194015503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4349231719971</t>
+    <t xml:space="preserve">11.4349241256714</t>
   </si>
   <si>
     <t xml:space="preserve">11.6814470291138</t>
@@ -2198,22 +2198,22 @@
     <t xml:space="preserve">11.5297403335571</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6245574951172</t>
+    <t xml:space="preserve">11.6245555877686</t>
   </si>
   <si>
     <t xml:space="preserve">11.5487031936646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6624841690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7383365631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2313842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1365690231323</t>
+    <t xml:space="preserve">11.662483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7383375167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2313852310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.136568069458</t>
   </si>
   <si>
     <t xml:space="preserve">12.1176042556763</t>
@@ -2222,58 +2222,58 @@
     <t xml:space="preserve">11.9658975601196</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9848613739014</t>
+    <t xml:space="preserve">11.9848604202271</t>
   </si>
   <si>
     <t xml:space="preserve">11.8141899108887</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7572994232178</t>
+    <t xml:space="preserve">11.7573003768921</t>
   </si>
   <si>
     <t xml:space="preserve">11.245288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6485795974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.653639793396</t>
+    <t xml:space="preserve">12.6485815048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6536388397217</t>
   </si>
   <si>
     <t xml:space="preserve">13.3881521224976</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8622360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5967483520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2364463806152</t>
+    <t xml:space="preserve">13.8622369766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5967502593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2364444732666</t>
   </si>
   <si>
     <t xml:space="preserve">13.4260787963867</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4640054702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1037006378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3312606811523</t>
+    <t xml:space="preserve">13.4640045166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1037015914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3312616348267</t>
   </si>
   <si>
     <t xml:space="preserve">14.1277236938477</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7294931411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.407114982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1226654052734</t>
+    <t xml:space="preserve">13.7294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4071159362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1226644515991</t>
   </si>
   <si>
     <t xml:space="preserve">13.4829683303833</t>
@@ -2282,31 +2282,31 @@
     <t xml:space="preserve">13.1795539855957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0227880477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.060715675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3262014389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4399814605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.857177734375</t>
+    <t xml:space="preserve">12.0227890014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0607147216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3262023925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4399824142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8571767807007</t>
   </si>
   <si>
     <t xml:space="preserve">12.8192510604858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0468120574951</t>
+    <t xml:space="preserve">13.0468101501465</t>
   </si>
   <si>
     <t xml:space="preserve">13.3122987747192</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4450416564941</t>
+    <t xml:space="preserve">13.4450426101685</t>
   </si>
   <si>
     <t xml:space="preserve">13.5588226318359</t>
@@ -2315,10 +2315,10 @@
     <t xml:space="preserve">13.6179914474487</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6371450424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4073047637939</t>
+    <t xml:space="preserve">13.6371440887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4073057174683</t>
   </si>
   <si>
     <t xml:space="preserve">13.4456119537354</t>
@@ -2327,13 +2327,13 @@
     <t xml:space="preserve">13.3115377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5030717849731</t>
+    <t xml:space="preserve">13.5030727386475</t>
   </si>
   <si>
     <t xml:space="preserve">13.8478307723999</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8861379623413</t>
+    <t xml:space="preserve">13.886137008667</t>
   </si>
   <si>
     <t xml:space="preserve">13.7520637512207</t>
@@ -2345,52 +2345,52 @@
     <t xml:space="preserve">14.1542825698853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2117433547974</t>
+    <t xml:space="preserve">14.2117443084717</t>
   </si>
   <si>
     <t xml:space="preserve">13.9819040298462</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6946048736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4647645950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7712173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.598837852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5413780212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7903709411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7137584686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8669843673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1351308822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3458166122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7097291946411</t>
+    <t xml:space="preserve">13.6946039199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4647655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7712182998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5988368988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5413789749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7903699874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7137565612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8669834136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1351299285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3458156585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7097282409668</t>
   </si>
   <si>
     <t xml:space="preserve">14.6331148147583</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9970264434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0353336334229</t>
+    <t xml:space="preserve">14.9970273971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0353345870972</t>
   </si>
   <si>
     <t xml:space="preserve">16.4909839630127</t>
@@ -2399,67 +2399,67 @@
     <t xml:space="preserve">16.3377590179443</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1845321655273</t>
+    <t xml:space="preserve">16.184534072876</t>
   </si>
   <si>
     <t xml:space="preserve">15.8206195831299</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9546918869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8014669418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6099328994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3226346969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.74400806427</t>
+    <t xml:space="preserve">15.9546928405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8014659881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6099348068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3226337432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7440061569214</t>
   </si>
   <si>
     <t xml:space="preserve">15.3417882919312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4375553131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7248525619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8589267730713</t>
+    <t xml:space="preserve">15.437554359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.724853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.858925819397</t>
   </si>
   <si>
     <t xml:space="preserve">16.2611446380615</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6059055328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7782859802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6825199127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6442108154297</t>
+    <t xml:space="preserve">16.6059036254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.778284072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6825180053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6442089080811</t>
   </si>
   <si>
     <t xml:space="preserve">16.7208251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7016716003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1613521575928</t>
+    <t xml:space="preserve">16.7016735076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1613502502441</t>
   </si>
   <si>
     <t xml:space="preserve">17.1421966552734</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1996555328369</t>
+    <t xml:space="preserve">17.1996574401855</t>
   </si>
   <si>
     <t xml:space="preserve">16.9889698028564</t>
@@ -2468,46 +2468,46 @@
     <t xml:space="preserve">16.4526786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4335250854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9123573303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6633625030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.950662612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9315128326416</t>
+    <t xml:space="preserve">16.4335231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9123592376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6633644104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9506645202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.931510925293</t>
   </si>
   <si>
     <t xml:space="preserve">16.8548984527588</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9657878875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0807094573975</t>
+    <t xml:space="preserve">17.9657897949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0807075500488</t>
   </si>
   <si>
     <t xml:space="preserve">18.3105487823486</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6321258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9194221496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3024921417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7757720947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7334403991699</t>
+    <t xml:space="preserve">19.6321239471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9194240570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.302490234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7757740020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7334384918213</t>
   </si>
   <si>
     <t xml:space="preserve">20.4940223693848</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">19.9673080444336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8715400695801</t>
+    <t xml:space="preserve">19.8715419769287</t>
   </si>
   <si>
     <t xml:space="preserve">20.0151901245117</t>
@@ -2528,28 +2528,28 @@
     <t xml:space="preserve">20.3982563018799</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5419063568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6376705169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9728546142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8770885467529</t>
+    <t xml:space="preserve">20.5419082641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6376724243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9728565216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8770866394043</t>
   </si>
   <si>
     <t xml:space="preserve">20.3503742218018</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0630760192871</t>
+    <t xml:space="preserve">20.0630741119385</t>
   </si>
   <si>
     <t xml:space="preserve">20.9249706268311</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7278900146484</t>
+    <t xml:space="preserve">19.7278938293457</t>
   </si>
   <si>
     <t xml:space="preserve">19.4884757995605</t>
@@ -2567,40 +2567,40 @@
     <t xml:space="preserve">19.1532936096191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2546043395996</t>
+    <t xml:space="preserve">20.2546081542969</t>
   </si>
   <si>
     <t xml:space="preserve">20.4461402893066</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2067222595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1165046691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.691104888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3080368041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7868709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7389888763428</t>
+    <t xml:space="preserve">20.2067241668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1165027618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6911029815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3080387115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7868728637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7389869689941</t>
   </si>
   <si>
     <t xml:space="preserve">21.834753036499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5474548339844</t>
+    <t xml:space="preserve">21.5474529266357</t>
   </si>
   <si>
     <t xml:space="preserve">21.8826370239258</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9784049987793</t>
+    <t xml:space="preserve">21.9784030914307</t>
   </si>
   <si>
     <t xml:space="preserve">21.212272644043</t>
@@ -2609,19 +2609,19 @@
     <t xml:space="preserve">21.355920791626</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4516887664795</t>
+    <t xml:space="preserve">21.4516868591309</t>
   </si>
   <si>
     <t xml:space="preserve">22.3135852813721</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7924175262451</t>
+    <t xml:space="preserve">22.7924156188965</t>
   </si>
   <si>
     <t xml:space="preserve">23.3191337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6487674713135</t>
+    <t xml:space="preserve">22.6487693786621</t>
   </si>
   <si>
     <t xml:space="preserve">22.4093532562256</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">22.0262870788574</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6432209014893</t>
+    <t xml:space="preserve">21.6432228088379</t>
   </si>
   <si>
     <t xml:space="preserve">21.4038047790527</t>
@@ -2642,16 +2642,16 @@
     <t xml:space="preserve">20.7813243865967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9305210113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5162143707275</t>
+    <t xml:space="preserve">21.9305191040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5162162780762</t>
   </si>
   <si>
     <t xml:space="preserve">23.9416160583496</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4627819061279</t>
+    <t xml:space="preserve">23.4627838134766</t>
   </si>
   <si>
     <t xml:space="preserve">23.4148998260498</t>
@@ -2660,19 +2660,19 @@
     <t xml:space="preserve">23.1754856109619</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2712497711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5106658935547</t>
+    <t xml:space="preserve">23.2712516784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5106678009033</t>
   </si>
   <si>
     <t xml:space="preserve">23.22336769104</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7500801086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6064338684082</t>
+    <t xml:space="preserve">23.7500820159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6064319610596</t>
   </si>
   <si>
     <t xml:space="preserve">23.0797176361084</t>
@@ -2681,28 +2681,28 @@
     <t xml:space="preserve">23.797966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7021980285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.654317855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.031831741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5585517883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8403034210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6008834838867</t>
+    <t xml:space="preserve">23.7022018432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6543159484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0318336486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5585498809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8403015136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6008853912354</t>
   </si>
   <si>
     <t xml:space="preserve">22.2657032012939</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5953369140625</t>
+    <t xml:space="preserve">21.5953388214111</t>
   </si>
   <si>
     <t xml:space="preserve">22.2178211212158</t>
@@ -2720,46 +2720,46 @@
     <t xml:space="preserve">24.4683303833008</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0373840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8458499908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4738807678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7611770629883</t>
+    <t xml:space="preserve">24.0373821258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8458480834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4738788604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7611789703369</t>
   </si>
   <si>
     <t xml:space="preserve">26.1442432403564</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8569431304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.809061050415</t>
+    <t xml:space="preserve">25.8569450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8090629577637</t>
   </si>
   <si>
     <t xml:space="preserve">25.9527130126953</t>
   </si>
   <si>
-    <t xml:space="preserve">25.665412902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4794254302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5751914978027</t>
+    <t xml:space="preserve">25.6654109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4794273376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5751953125</t>
   </si>
   <si>
     <t xml:space="preserve">27.4849758148193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3892097473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3413238525391</t>
+    <t xml:space="preserve">27.3892078399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3413257598877</t>
   </si>
   <si>
     <t xml:space="preserve">27.8680419921875</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">28.2989902496338</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7722759246826</t>
+    <t xml:space="preserve">27.772274017334</t>
   </si>
   <si>
     <t xml:space="preserve">27.628625869751</t>
@@ -2789,10 +2789,10 @@
     <t xml:space="preserve">27.2455596923828</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9582576751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1497936248779</t>
+    <t xml:space="preserve">26.9582595825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1497917175293</t>
   </si>
   <si>
     <t xml:space="preserve">27.054027557373</t>
@@ -2801,25 +2801,25 @@
     <t xml:space="preserve">26.718843460083</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9287757873535</t>
+    <t xml:space="preserve">26.9287776947021</t>
   </si>
   <si>
     <t xml:space="preserve">26.2543506622314</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8207931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4354076385498</t>
+    <t xml:space="preserve">25.8207950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4354057312012</t>
   </si>
   <si>
     <t xml:space="preserve">24.5682926177979</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7128105163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1347332000732</t>
+    <t xml:space="preserve">24.7128124237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1347351074219</t>
   </si>
   <si>
     <t xml:space="preserve">24.760986328125</t>
@@ -2837,16 +2837,16 @@
     <t xml:space="preserve">26.8324298858643</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4470443725586</t>
+    <t xml:space="preserve">26.4470462799072</t>
   </si>
   <si>
     <t xml:space="preserve">25.9171390533447</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8689651489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4835834503174</t>
+    <t xml:space="preserve">25.8689670562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4835815429688</t>
   </si>
   <si>
     <t xml:space="preserve">25.7244491577148</t>
@@ -2870,19 +2870,19 @@
     <t xml:space="preserve">26.1580047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6281032562256</t>
+    <t xml:space="preserve">25.628101348877</t>
   </si>
   <si>
     <t xml:space="preserve">24.8573303222656</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6762752532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5317554473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0500240325928</t>
+    <t xml:space="preserve">25.6762733459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5317535400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0500221252441</t>
   </si>
   <si>
     <t xml:space="preserve">24.4719467163086</t>
@@ -2891,16 +2891,16 @@
     <t xml:space="preserve">22.9785804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7858848571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6530017852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0267505645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9304046630859</t>
+    <t xml:space="preserve">22.7858867645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.653003692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0267524719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9304065704346</t>
   </si>
   <si>
     <t xml:space="preserve">23.2194442749023</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">21.5815582275391</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6413669586182</t>
+    <t xml:space="preserve">22.6413650512695</t>
   </si>
   <si>
     <t xml:space="preserve">22.8340606689453</t>
@@ -2930,13 +2930,13 @@
     <t xml:space="preserve">22.4968490600586</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1114654541016</t>
+    <t xml:space="preserve">22.1114635467529</t>
   </si>
   <si>
     <t xml:space="preserve">23.1712703704834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1596374511719</t>
+    <t xml:space="preserve">22.1596355438232</t>
   </si>
   <si>
     <t xml:space="preserve">22.063289642334</t>
@@ -2963,22 +2963,22 @@
     <t xml:space="preserve">18.9609413146973</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1536312103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1323623657227</t>
+    <t xml:space="preserve">19.1536331176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1323642730713</t>
   </si>
   <si>
     <t xml:space="preserve">16.8991317749023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9569396972656</t>
+    <t xml:space="preserve">16.9569416046143</t>
   </si>
   <si>
     <t xml:space="preserve">18.0167484283447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.15163230896</t>
+    <t xml:space="preserve">18.1516304016113</t>
   </si>
   <si>
     <t xml:space="preserve">17.5542869567871</t>
@@ -2990,13 +2990,13 @@
     <t xml:space="preserve">17.8433246612549</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4964771270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6719017028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2672481536865</t>
+    <t xml:space="preserve">17.4964790344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6719036102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2672462463379</t>
   </si>
   <si>
     <t xml:space="preserve">18.3250560760498</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">18.6911716461182</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3828639984131</t>
+    <t xml:space="preserve">18.3828620910645</t>
   </si>
   <si>
     <t xml:space="preserve">18.7682476043701</t>
@@ -3017,49 +3017,49 @@
     <t xml:space="preserve">19.1921730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6064624786377</t>
+    <t xml:space="preserve">19.6064605712891</t>
   </si>
   <si>
     <t xml:space="preserve">19.1150951385498</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2114410400391</t>
+    <t xml:space="preserve">19.2114429473877</t>
   </si>
   <si>
     <t xml:space="preserve">18.6333637237549</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7662487030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6526336669922</t>
+    <t xml:space="preserve">17.7662467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6526355743408</t>
   </si>
   <si>
     <t xml:space="preserve">18.4021339416504</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7297115325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4137706756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7509803771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1343650817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7489795684814</t>
+    <t xml:space="preserve">18.7297096252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4137687683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7509822845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1343669891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7489776611328</t>
   </si>
   <si>
     <t xml:space="preserve">18.9224014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3655967712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.269250869751</t>
+    <t xml:space="preserve">19.3655948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2692489624023</t>
   </si>
   <si>
     <t xml:space="preserve">17.5350170135498</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">18.0938262939453</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7991523742676</t>
+    <t xml:space="preserve">19.7991542816162</t>
   </si>
   <si>
     <t xml:space="preserve">20.040018081665</t>
@@ -3080,22 +3080,22 @@
     <t xml:space="preserve">21.0034809112549</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7144412994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0516548156738</t>
+    <t xml:space="preserve">20.7144432067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0516529083252</t>
   </si>
   <si>
     <t xml:space="preserve">21.4852123260498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4370384216309</t>
+    <t xml:space="preserve">21.4370403289795</t>
   </si>
   <si>
     <t xml:space="preserve">21.8705978393555</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4005031585693</t>
+    <t xml:space="preserve">22.4005012512207</t>
   </si>
   <si>
     <t xml:space="preserve">23.1230983734131</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">19.8954982757568</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2327098846436</t>
+    <t xml:space="preserve">20.2327117919922</t>
   </si>
   <si>
     <t xml:space="preserve">20.4735774993896</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">19.8473243713379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.249979019165</t>
+    <t xml:space="preserve">19.2499809265137</t>
   </si>
   <si>
     <t xml:space="preserve">18.7875175476074</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">18.5948257446289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5735549926758</t>
+    <t xml:space="preserve">17.5735569000244</t>
   </si>
   <si>
     <t xml:space="preserve">18.8067874908447</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">18.2287082672119</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0745544433594</t>
+    <t xml:space="preserve">18.074556350708</t>
   </si>
   <si>
     <t xml:space="preserve">18.5562877655029</t>
@@ -3173,19 +3173,19 @@
     <t xml:space="preserve">17.9782104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5755558013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3174228668213</t>
+    <t xml:space="preserve">18.5755577087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3174209594727</t>
   </si>
   <si>
     <t xml:space="preserve">18.8453235626221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9802131652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4619426727295</t>
+    <t xml:space="preserve">18.9802112579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4619407653809</t>
   </si>
   <si>
     <t xml:space="preserve">18.1709022521973</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">17.708438873291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9204006195068</t>
+    <t xml:space="preserve">17.9204025268555</t>
   </si>
   <si>
     <t xml:space="preserve">17.6313610076904</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">18.2094402313232</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2479801177979</t>
+    <t xml:space="preserve">18.2479782104492</t>
   </si>
   <si>
     <t xml:space="preserve">17.669900894165</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3423233032227</t>
+    <t xml:space="preserve">17.3423252105713</t>
   </si>
   <si>
     <t xml:space="preserve">16.6293621063232</t>
@@ -3218,16 +3218,16 @@
     <t xml:space="preserve">15.9934778213501</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4559383392334</t>
+    <t xml:space="preserve">16.455940246582</t>
   </si>
   <si>
     <t xml:space="preserve">16.205436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0512847900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2247066497803</t>
+    <t xml:space="preserve">16.0512828826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2247085571289</t>
   </si>
   <si>
     <t xml:space="preserve">15.4153995513916</t>
@@ -3236,13 +3236,13 @@
     <t xml:space="preserve">15.5502834320068</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3575897216797</t>
+    <t xml:space="preserve">15.357590675354</t>
   </si>
   <si>
     <t xml:space="preserve">16.7257099151611</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1283588409424</t>
+    <t xml:space="preserve">16.128360748291</t>
   </si>
   <si>
     <t xml:space="preserve">16.7642459869385</t>
@@ -3251,16 +3251,16 @@
     <t xml:space="preserve">16.8798637390137</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1110954284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4386692047119</t>
+    <t xml:space="preserve">17.1110935211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4386711120605</t>
   </si>
   <si>
     <t xml:space="preserve">17.2459774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1689014434814</t>
+    <t xml:space="preserve">17.1688995361328</t>
   </si>
   <si>
     <t xml:space="preserve">17.1303615570068</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">18.8838653564453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8260593414307</t>
+    <t xml:space="preserve">18.826057434082</t>
   </si>
   <si>
     <t xml:space="preserve">19.5582866668701</t>
@@ -3281,10 +3281,10 @@
     <t xml:space="preserve">20.088191986084</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1363639831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7028064727783</t>
+    <t xml:space="preserve">20.1363658905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.702808380127</t>
   </si>
   <si>
     <t xml:space="preserve">20.5699234008789</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">20.7626152038574</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8589611053467</t>
+    <t xml:space="preserve">20.8589630126953</t>
   </si>
   <si>
     <t xml:space="preserve">20.7899551391602</t>
@@ -4599,6 +4599,9 @@
   </si>
   <si>
     <t xml:space="preserve">46.9000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.75</t>
   </si>
 </sst>
 </file>
@@ -69963,7 +69966,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6911805556</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>42695</v>
@@ -69984,6 +69987,32 @@
         <v>1528</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6911111111</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>43544</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>46.9500007629395</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>46.7000007629395</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1529</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="1530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="1531">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6962623596191</t>
+    <t xml:space="preserve">15.6962594985962</t>
   </si>
   <si>
     <t xml:space="preserve">DAN.MI</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">15.8255233764648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3269386291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6344547271729</t>
+    <t xml:space="preserve">15.3269376754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6344556808472</t>
   </si>
   <si>
     <t xml:space="preserve">14.3112964630127</t>
@@ -65,82 +65,82 @@
     <t xml:space="preserve">14.1358680725098</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9604387283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1940927505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8801670074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9724988937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3723459243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0371294021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2217893600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0009517669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1579151153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.434907913208</t>
+    <t xml:space="preserve">13.9604396820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1940908432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8801679611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9724969863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3723478317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.037130355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.221791267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0009536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1579170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4349098205566</t>
   </si>
   <si>
     <t xml:space="preserve">16.1948509216309</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4718418121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2289524078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7119026184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.576229095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2133159637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4100341796875</t>
+    <t xml:space="preserve">16.4718437194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2289581298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7119007110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5762338638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2133140563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4100351333618</t>
   </si>
   <si>
     <t xml:space="preserve">15.0407114028931</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0499439239502</t>
+    <t xml:space="preserve">15.0499429702759</t>
   </si>
   <si>
     <t xml:space="preserve">15.4562005996704</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2069063186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1053438186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0194187164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3425750732422</t>
+    <t xml:space="preserve">15.2069053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1053447723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0194206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3425769805908</t>
   </si>
   <si>
     <t xml:space="preserve">16.8780994415283</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0350608825684</t>
+    <t xml:space="preserve">17.0350666046143</t>
   </si>
   <si>
     <t xml:space="preserve">17.1735553741455</t>
@@ -155,22 +155,22 @@
     <t xml:space="preserve">16.4626064300537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4533767700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9427318572998</t>
+    <t xml:space="preserve">16.4533729553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9427299499512</t>
   </si>
   <si>
     <t xml:space="preserve">16.7488346099854</t>
   </si>
   <si>
-    <t xml:space="preserve">17.293586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4228496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4874820709229</t>
+    <t xml:space="preserve">17.2935848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4874801635742</t>
   </si>
   <si>
     <t xml:space="preserve">17.5521144866943</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">16.6472702026367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3397521972656</t>
+    <t xml:space="preserve">17.3397541046143</t>
   </si>
   <si>
     <t xml:space="preserve">17.6352119445801</t>
@@ -191,28 +191,28 @@
     <t xml:space="preserve">17.3766841888428</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5798168182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1273937225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3241119384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.665735244751</t>
+    <t xml:space="preserve">17.5798149108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1273918151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3241138458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6657390594482</t>
   </si>
   <si>
     <t xml:space="preserve">17.053524017334</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4043865203857</t>
+    <t xml:space="preserve">17.4043846130371</t>
   </si>
   <si>
     <t xml:space="preserve">16.6842021942139</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6380386352539</t>
+    <t xml:space="preserve">16.6380367279053</t>
   </si>
   <si>
     <t xml:space="preserve">17.238187789917</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">17.912202835083</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7183113098145</t>
+    <t xml:space="preserve">17.7183055877686</t>
   </si>
   <si>
     <t xml:space="preserve">18.4661884307861</t>
@@ -251,82 +251,82 @@
     <t xml:space="preserve">18.5585193634033</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2168941497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4477252960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1522617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0137691497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5890426635742</t>
+    <t xml:space="preserve">18.2168960571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4477272033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1522655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0137672424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5890445709229</t>
   </si>
   <si>
     <t xml:space="preserve">17.26589012146</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6075096130371</t>
+    <t xml:space="preserve">17.6075134277344</t>
   </si>
   <si>
     <t xml:space="preserve">17.2843532562256</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1920204162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8873291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9519653320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6749706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4256744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2594814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3610458374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8596305847168</t>
+    <t xml:space="preserve">17.192024230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8873310089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.951961517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6749649047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4256763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2594795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3610420227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8596324920654</t>
   </si>
   <si>
     <t xml:space="preserve">16.5641708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5272407531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2779445648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4782466888428</t>
+    <t xml:space="preserve">16.5272388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.277946472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4782524108887</t>
   </si>
   <si>
     <t xml:space="preserve">16.6288032531738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6103420257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3582172393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.108922958374</t>
+    <t xml:space="preserve">16.6103382110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3582191467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1089267730713</t>
   </si>
   <si>
     <t xml:space="preserve">17.1550884246826</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9178552627563</t>
+    <t xml:space="preserve">15.9178533554077</t>
   </si>
   <si>
     <t xml:space="preserve">15.9547891616821</t>
@@ -335,34 +335,34 @@
     <t xml:space="preserve">15.0591773986816</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8652830123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1699743270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4377326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0655860900879</t>
+    <t xml:space="preserve">14.8652839660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1699752807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4377336502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0655879974365</t>
   </si>
   <si>
     <t xml:space="preserve">15.0868759155273</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5513582229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9853134155273</t>
+    <t xml:space="preserve">14.5513553619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9853105545044</t>
   </si>
   <si>
     <t xml:space="preserve">14.6252212524414</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7821836471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5115966796875</t>
+    <t xml:space="preserve">14.7821846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5115985870361</t>
   </si>
   <si>
     <t xml:space="preserve">15.1330404281616</t>
@@ -374,19 +374,19 @@
     <t xml:space="preserve">14.0989360809326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3574628829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7544841766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5023651123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4192705154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6039323806763</t>
+    <t xml:space="preserve">14.3574619293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7544870376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5023679733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4192686080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6039295196533</t>
   </si>
   <si>
     <t xml:space="preserve">15.3546342849731</t>
@@ -395,124 +395,124 @@
     <t xml:space="preserve">15.4284992218018</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4008045196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4839019775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2502460479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7239618301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4931344985962</t>
+    <t xml:space="preserve">15.400803565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4839010238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2502498626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7239627838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4931364059448</t>
   </si>
   <si>
     <t xml:space="preserve">16.2317790985107</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9363231658936</t>
+    <t xml:space="preserve">15.9363241195679</t>
   </si>
   <si>
     <t xml:space="preserve">16.1856155395508</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2871799468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1763820648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0932807922363</t>
+    <t xml:space="preserve">16.2871780395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1763801574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0932846069336</t>
   </si>
   <si>
     <t xml:space="preserve">17.2566566467285</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9242630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7211322784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7580680847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2751159667969</t>
+    <t xml:space="preserve">16.9242610931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.721134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7580642700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7275428771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2751178741455</t>
   </si>
   <si>
     <t xml:space="preserve">17.1458549499512</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3120498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4505500793457</t>
+    <t xml:space="preserve">17.3120555877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4505519866943</t>
   </si>
   <si>
     <t xml:space="preserve">16.204080581665</t>
   </si>
   <si>
-    <t xml:space="preserve">15.890154838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8624572753906</t>
+    <t xml:space="preserve">15.8901538848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.862455368042</t>
   </si>
   <si>
     <t xml:space="preserve">15.9270877838135</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0563507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7424249649048</t>
+    <t xml:space="preserve">16.0563488006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7424259185791</t>
   </si>
   <si>
     <t xml:space="preserve">15.7701263427734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6685590744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5946960449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7147254943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1394462585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8134651184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1671485900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6408634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6500978469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8070554733276</t>
+    <t xml:space="preserve">15.6685619354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5946969985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.714729309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1394500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8134670257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1671504974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6408624649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6500968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8070592880249</t>
   </si>
   <si>
     <t xml:space="preserve">15.4654340744019</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2623071670532</t>
+    <t xml:space="preserve">15.2623062133789</t>
   </si>
   <si>
     <t xml:space="preserve">15.3366193771362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4109354019165</t>
+    <t xml:space="preserve">15.4109344482422</t>
   </si>
   <si>
     <t xml:space="preserve">15.6524562835693</t>
@@ -521,34 +521,34 @@
     <t xml:space="preserve">15.7360610961914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8939762115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6245880126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0765199661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4295129776001</t>
+    <t xml:space="preserve">15.8939809799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.624587059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0765180587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4295139312744</t>
   </si>
   <si>
     <t xml:space="preserve">15.522403717041</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5131196975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1601238250732</t>
+    <t xml:space="preserve">15.5131177902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1601247787476</t>
   </si>
   <si>
     <t xml:space="preserve">15.8661098480225</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3305759429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9311323165894</t>
+    <t xml:space="preserve">16.3305721282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.931134223938</t>
   </si>
   <si>
     <t xml:space="preserve">15.4945392608643</t>
@@ -557,10 +557,10 @@
     <t xml:space="preserve">15.6060085296631</t>
   </si>
   <si>
-    <t xml:space="preserve">15.318039894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8846912384033</t>
+    <t xml:space="preserve">15.3180418014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8846864700317</t>
   </si>
   <si>
     <t xml:space="preserve">16.0518970489502</t>
@@ -569,76 +569,76 @@
     <t xml:space="preserve">15.8382415771484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5813846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1851902008057</t>
+    <t xml:space="preserve">16.5813865661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.185188293457</t>
   </si>
   <si>
     <t xml:space="preserve">17.2595024108887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.138744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2223491668701</t>
+    <t xml:space="preserve">17.1387462615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2223453521729</t>
   </si>
   <si>
     <t xml:space="preserve">17.027271270752</t>
   </si>
   <si>
-    <t xml:space="preserve">16.952953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4884929656982</t>
+    <t xml:space="preserve">16.9529571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4884910583496</t>
   </si>
   <si>
     <t xml:space="preserve">17.0922966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9065093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1666107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7425479888916</t>
+    <t xml:space="preserve">16.9065113067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1666126251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.742546081543</t>
   </si>
   <si>
     <t xml:space="preserve">17.9004650115967</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9376239776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8818836212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4299545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9037075042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9501533508301</t>
+    <t xml:space="preserve">17.9376220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8818855285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4299583435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9037094116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9501552581787</t>
   </si>
   <si>
     <t xml:space="preserve">19.5539569854736</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6282730102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1173629760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9129981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4610691070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3310165405273</t>
+    <t xml:space="preserve">19.6282711029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1173610687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9129962921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4610652923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3310146331787</t>
   </si>
   <si>
     <t xml:space="preserve">19.1823863983154</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">19.0802059173584</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8572616577148</t>
+    <t xml:space="preserve">18.8572597503662</t>
   </si>
   <si>
     <t xml:space="preserve">19.0151786804199</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">18.9408645629883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9315738677979</t>
+    <t xml:space="preserve">18.9315757751465</t>
   </si>
   <si>
     <t xml:space="preserve">18.7550792694092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5785827636719</t>
+    <t xml:space="preserve">18.5785846710205</t>
   </si>
   <si>
     <t xml:space="preserve">18.4020881652832</t>
@@ -671,91 +671,91 @@
     <t xml:space="preserve">18.1141204833984</t>
   </si>
   <si>
-    <t xml:space="preserve">18.457820892334</t>
+    <t xml:space="preserve">18.4578227996826</t>
   </si>
   <si>
     <t xml:space="preserve">18.5321369171143</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4671096801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3742179870605</t>
+    <t xml:space="preserve">18.4671115875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3742198944092</t>
   </si>
   <si>
     <t xml:space="preserve">18.485689163208</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2813282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3277721405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5135593414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6157398223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6250305175781</t>
+    <t xml:space="preserve">18.2813243865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3277702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.513557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6157379150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6250286102295</t>
   </si>
   <si>
     <t xml:space="preserve">18.7272109985352</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0430469512939</t>
+    <t xml:space="preserve">19.0430488586426</t>
   </si>
   <si>
     <t xml:space="preserve">19.4146194458008</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0894947052002</t>
+    <t xml:space="preserve">19.0894927978516</t>
   </si>
   <si>
     <t xml:space="preserve">19.126651763916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3681755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4517765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9594421386719</t>
+    <t xml:space="preserve">19.3681735992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4517784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9594440460205</t>
   </si>
   <si>
     <t xml:space="preserve">19.2474098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5075130462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.098783493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2195415496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3495941162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0337581634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.228832244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3867492675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2845706939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9162425994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0091361999512</t>
+    <t xml:space="preserve">19.507511138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0987815856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2195434570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3495922088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0337600708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2288360595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3867511749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2845668792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9162406921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0091323852539</t>
   </si>
   <si>
     <t xml:space="preserve">20.3807067871094</t>
@@ -764,13 +764,13 @@
     <t xml:space="preserve">20.6222286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8544597625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9659328460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9473514556885</t>
+    <t xml:space="preserve">20.8544578552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9659309387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9473552703857</t>
   </si>
   <si>
     <t xml:space="preserve">20.148473739624</t>
@@ -779,16 +779,16 @@
     <t xml:space="preserve">20.6129379272461</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3899974822998</t>
+    <t xml:space="preserve">20.3899955749512</t>
   </si>
   <si>
     <t xml:space="preserve">20.2506580352783</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5757789611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6500930786133</t>
+    <t xml:space="preserve">20.5757808685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6500968933105</t>
   </si>
   <si>
     <t xml:space="preserve">20.6036491394043</t>
@@ -803,34 +803,34 @@
     <t xml:space="preserve">20.6593837738037</t>
   </si>
   <si>
-    <t xml:space="preserve">20.482889175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8173027038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8637466430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4550189971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7801475524902</t>
+    <t xml:space="preserve">20.4828853607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8173007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.863748550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4550228118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7801456451416</t>
   </si>
   <si>
     <t xml:space="preserve">21.6440486907959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.495418548584</t>
+    <t xml:space="preserve">21.4954204559326</t>
   </si>
   <si>
     <t xml:space="preserve">21.3653717041016</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3189239501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1331405639648</t>
+    <t xml:space="preserve">21.3189277648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1331386566162</t>
   </si>
   <si>
     <t xml:space="preserve">21.1238479614258</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">21.1052703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3467922210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2260322570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6408061981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1702938079834</t>
+    <t xml:space="preserve">21.346794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2260303497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6408042907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1702976226807</t>
   </si>
   <si>
     <t xml:space="preserve">20.9566383361816</t>
@@ -863,19 +863,19 @@
     <t xml:space="preserve">21.114559173584</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2538986206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2446098327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3375015258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2817687988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9380664825439</t>
+    <t xml:space="preserve">21.2538967132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2446117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3374996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2817668914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9380626678467</t>
   </si>
   <si>
     <t xml:space="preserve">21.1795845031738</t>
@@ -884,31 +884,31 @@
     <t xml:space="preserve">20.7336978912354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3156814575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3992824554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4085712432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3249683380127</t>
+    <t xml:space="preserve">20.3156795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.399284362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4085693359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3249664306641</t>
   </si>
   <si>
     <t xml:space="preserve">20.6315155029297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2785224914551</t>
+    <t xml:space="preserve">20.2785205841064</t>
   </si>
   <si>
     <t xml:space="preserve">20.0462913513184</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2135009765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.795482635498</t>
+    <t xml:space="preserve">20.2134990692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7954807281494</t>
   </si>
   <si>
     <t xml:space="preserve">19.9069519042969</t>
@@ -920,16 +920,16 @@
     <t xml:space="preserve">20.2971038818359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5479145050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4364414215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9533977508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8326377868652</t>
+    <t xml:space="preserve">20.5479164123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4364395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9533996582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8326358795166</t>
   </si>
   <si>
     <t xml:space="preserve">19.8883743286133</t>
@@ -941,55 +941,55 @@
     <t xml:space="preserve">19.9255313873291</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0741596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9998435974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1113147735596</t>
+    <t xml:space="preserve">20.074161529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9998455047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1113166809082</t>
   </si>
   <si>
     <t xml:space="preserve">19.6747188568115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6686744689941</t>
+    <t xml:space="preserve">20.6686725616455</t>
   </si>
   <si>
     <t xml:space="preserve">20.2413654327393</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9719753265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7304534912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4178619384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1298942565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4921741485596</t>
+    <t xml:space="preserve">19.9719772338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7304553985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4178657531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1298961639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4921760559082</t>
   </si>
   <si>
     <t xml:space="preserve">20.8451709747314</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3435478210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5664920806885</t>
+    <t xml:space="preserve">20.3435497283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5664901733398</t>
   </si>
   <si>
     <t xml:space="preserve">20.8916149139404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1981601715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7244071960449</t>
+    <t xml:space="preserve">21.1981620788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7244110107422</t>
   </si>
   <si>
     <t xml:space="preserve">20.4736003875732</t>
@@ -998,13 +998,13 @@
     <t xml:space="preserve">20.3342609405518</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3714179992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8790817260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.841926574707</t>
+    <t xml:space="preserve">20.3714199066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8790836334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8419303894043</t>
   </si>
   <si>
     <t xml:space="preserve">19.767614364624</t>
@@ -1013,76 +1013,76 @@
     <t xml:space="preserve">19.9812660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">20.092737197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5200462341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9905529022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5353832244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2567005157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7829475402832</t>
+    <t xml:space="preserve">20.0927352905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5200443267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9905567169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5353813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2566986083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7829494476318</t>
   </si>
   <si>
     <t xml:space="preserve">18.8386821746826</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6343154907227</t>
+    <t xml:space="preserve">18.6343193054199</t>
   </si>
   <si>
     <t xml:space="preserve">18.996603012085</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6807632446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5600051879883</t>
+    <t xml:space="preserve">18.6807651519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5600070953369</t>
   </si>
   <si>
     <t xml:space="preserve">18.6621875762939</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4392471313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8108139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1359424591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.977933883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9499282836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.529857635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3058166503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9044151306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8484039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6430339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6710395812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9417514801025</t>
+    <t xml:space="preserve">18.4392433166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8108158111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1359386444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9779300689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9499263763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5298519134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3058185577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9044132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8484058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6430377960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6710414886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9417533874512</t>
   </si>
   <si>
     <t xml:space="preserve">17.895076751709</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">17.9697570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2684745788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4645080566406</t>
+    <t xml:space="preserve">18.2684764862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4645099639893</t>
   </si>
   <si>
     <t xml:space="preserve">18.5858612060547</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">18.4084987640381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1657905578613</t>
+    <t xml:space="preserve">18.16579246521</t>
   </si>
   <si>
     <t xml:space="preserve">18.4925155639648</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">18.3618259429932</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2218017578125</t>
+    <t xml:space="preserve">18.2218036651611</t>
   </si>
   <si>
     <t xml:space="preserve">18.6698760986328</t>
@@ -1133,64 +1133,64 @@
     <t xml:space="preserve">18.3524894714355</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3804950714111</t>
+    <t xml:space="preserve">18.3804969787598</t>
   </si>
   <si>
     <t xml:space="preserve">18.4458408355713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4831790924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4738464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6605434417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7072200775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5951976776123</t>
+    <t xml:space="preserve">18.4831771850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4738445281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6605415344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7072162628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5951995849609</t>
   </si>
   <si>
     <t xml:space="preserve">18.3898296356201</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5018482208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9032516479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1832981109619</t>
+    <t xml:space="preserve">18.5018463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9032497406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1833000183105</t>
   </si>
   <si>
     <t xml:space="preserve">19.4633483886719</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7433948516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5368671417236</t>
+    <t xml:space="preserve">19.7433967590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.536865234375</t>
   </si>
   <si>
     <t xml:space="preserve">21.2836608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5637092590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.517032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.377010345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6103820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4703578948975</t>
+    <t xml:space="preserve">21.5637073516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5170345306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3770084381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6103839874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4703598022461</t>
   </si>
   <si>
     <t xml:space="preserve">21.7504062652588</t>
@@ -1199,19 +1199,19 @@
     <t xml:space="preserve">21.7970848083496</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0036125183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4435138702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0502891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6302146911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7702407836914</t>
+    <t xml:space="preserve">21.0036144256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4435157775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0502872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6302185058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7702388763428</t>
   </si>
   <si>
     <t xml:space="preserve">20.7235660552979</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">21.0969619750977</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1903133392334</t>
+    <t xml:space="preserve">21.1903114318848</t>
   </si>
   <si>
     <t xml:space="preserve">21.1436367034912</t>
@@ -1235,43 +1235,43 @@
     <t xml:space="preserve">21.7037334442139</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2171535491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8904323577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0771293640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9837818145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.816915512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.236988067627</t>
+    <t xml:space="preserve">22.217155456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8904342651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0771312713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9837799072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8169136047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2369861602783</t>
   </si>
   <si>
     <t xml:space="preserve">20.3034915924072</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2101402282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9102630615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5835399627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.956937789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3303375244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3968410491943</t>
+    <t xml:space="preserve">20.2101440429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9102611541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5835380554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9569358825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3303337097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.396842956543</t>
   </si>
   <si>
     <t xml:space="preserve">20.4901924133301</t>
@@ -1283,19 +1283,19 @@
     <t xml:space="preserve">18.9966011047363</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0432758331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1366271972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3233222961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7900695800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6033725738525</t>
+    <t xml:space="preserve">19.0432739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.136625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3233242034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7900714874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6033744812012</t>
   </si>
   <si>
     <t xml:space="preserve">20.3501682281494</t>
@@ -1304,28 +1304,28 @@
     <t xml:space="preserve">20.2568187713623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9767684936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1634712219238</t>
+    <t xml:space="preserve">19.9767723083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1634674072266</t>
   </si>
   <si>
     <t xml:space="preserve">20.0234470367432</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8834190368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9300937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4166736602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5566997528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5100231170654</t>
+    <t xml:space="preserve">19.8834209442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9300956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4166698455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.556697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5100212097168</t>
   </si>
   <si>
     <t xml:space="preserve">19.6500453948975</t>
@@ -1334,34 +1334,34 @@
     <t xml:space="preserve">19.6967220306396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2766494750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2299766540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3699989318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8367462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4236850738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0701179504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.717716217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3093013763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7013673782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7678747177124</t>
+    <t xml:space="preserve">19.2766456604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2299747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3699970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8367481231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4236869812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0701160430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7177143096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3093004226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7013654708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7678718566895</t>
   </si>
   <si>
     <t xml:space="preserve">14.4691543579102</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">14.805212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4026489257812</t>
+    <t xml:space="preserve">15.4026498794556</t>
   </si>
   <si>
     <t xml:space="preserve">15.62668800354</t>
@@ -1385,64 +1385,64 @@
     <t xml:space="preserve">15.3279714584351</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4586582183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8693952560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.794716835022</t>
+    <t xml:space="preserve">15.4586591720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8693981170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7947177886963</t>
   </si>
   <si>
     <t xml:space="preserve">15.6640291213989</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5893516540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3839778900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0105810165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8602876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5784873962402</t>
+    <t xml:space="preserve">15.5893497467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3839797973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0105838775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8602867126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5784883499146</t>
   </si>
   <si>
     <t xml:space="preserve">14.4094076156616</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4469795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9166488647461</t>
+    <t xml:space="preserve">14.4469804763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9166498184204</t>
   </si>
   <si>
     <t xml:space="preserve">14.9354343414307</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6536350250244</t>
+    <t xml:space="preserve">14.6536340713501</t>
   </si>
   <si>
     <t xml:space="preserve">15.14208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4426755905151</t>
+    <t xml:space="preserve">15.4426765441895</t>
   </si>
   <si>
     <t xml:space="preserve">15.2735958099365</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0712451934814</t>
+    <t xml:space="preserve">14.0712461471558</t>
   </si>
   <si>
     <t xml:space="preserve">13.920952796936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6015777587891</t>
+    <t xml:space="preserve">13.6015787124634</t>
   </si>
   <si>
     <t xml:space="preserve">13.7330856323242</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">14.1651802062988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1463928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2215423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9585266113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6391525268555</t>
+    <t xml:space="preserve">14.1463947296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2215404510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9585256576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6391534805298</t>
   </si>
   <si>
     <t xml:space="preserve">13.6203651428223</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">13.7894458770752</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0524597167969</t>
+    <t xml:space="preserve">14.0524616241455</t>
   </si>
   <si>
     <t xml:space="preserve">14.2027540206909</t>
@@ -1481,10 +1481,10 @@
     <t xml:space="preserve">14.5221261978149</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7475690841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2172365188599</t>
+    <t xml:space="preserve">14.7475671768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2172374725342</t>
   </si>
   <si>
     <t xml:space="preserve">15.1233034133911</t>
@@ -1493,25 +1493,25 @@
     <t xml:space="preserve">15.029369354248</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0669422149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8978614807129</t>
+    <t xml:space="preserve">15.0669431686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8978605270386</t>
   </si>
   <si>
     <t xml:space="preserve">15.1045160293579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1608753204346</t>
+    <t xml:space="preserve">15.1608762741089</t>
   </si>
   <si>
     <t xml:space="preserve">15.1984491348267</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5366106033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9687061309814</t>
+    <t xml:space="preserve">15.5366125106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9687032699585</t>
   </si>
   <si>
     <t xml:space="preserve">16.8141059875488</t>
@@ -1520,28 +1520,28 @@
     <t xml:space="preserve">16.8892517089844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9080390930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4947319030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.419584274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2692928314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3632259368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9874906539917</t>
+    <t xml:space="preserve">16.9080410003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4947338104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4195861816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2692890167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.363224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.987491607666</t>
   </si>
   <si>
     <t xml:space="preserve">15.8747682571411</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8184108734131</t>
+    <t xml:space="preserve">15.8184099197388</t>
   </si>
   <si>
     <t xml:space="preserve">16.1377849578857</t>
@@ -1553,16 +1553,16 @@
     <t xml:space="preserve">16.2505035400391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.62624168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.513521194458</t>
+    <t xml:space="preserve">16.6262378692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5135192871094</t>
   </si>
   <si>
     <t xml:space="preserve">16.2880802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4383735656738</t>
+    <t xml:space="preserve">16.4383697509766</t>
   </si>
   <si>
     <t xml:space="preserve">16.4571590423584</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">16.2317199707031</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6074504852295</t>
+    <t xml:space="preserve">16.6074542999268</t>
   </si>
   <si>
     <t xml:space="preserve">16.7201728820801</t>
@@ -1580,13 +1580,13 @@
     <t xml:space="preserve">16.4759464263916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3256511688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8559827804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9499187469482</t>
+    <t xml:space="preserve">16.3256492614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8559837341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.949914932251</t>
   </si>
   <si>
     <t xml:space="preserve">15.9311304092407</t>
@@ -1598,52 +1598,52 @@
     <t xml:space="preserve">16.0062789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3444385528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4007968902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5323047637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7765350341797</t>
+    <t xml:space="preserve">16.3444404602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4007987976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5323066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7765312194824</t>
   </si>
   <si>
     <t xml:space="preserve">16.9456119537354</t>
   </si>
   <si>
-    <t xml:space="preserve">17.471643447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2794723510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2606830596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2418975830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1103897094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5280017852783</t>
+    <t xml:space="preserve">17.4716396331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.279468536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.260684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2418956756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1103916168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.528003692627</t>
   </si>
   <si>
     <t xml:space="preserve">17.1334800720215</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0019760131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9831867218018</t>
+    <t xml:space="preserve">17.0019721984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9831886291504</t>
   </si>
   <si>
     <t xml:space="preserve">16.7389583587646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6450252532959</t>
+    <t xml:space="preserve">16.6450233459473</t>
   </si>
   <si>
     <t xml:space="preserve">16.9643993377686</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">17.0583343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1522636413574</t>
+    <t xml:space="preserve">17.1522674560547</t>
   </si>
   <si>
     <t xml:space="preserve">17.2274131774902</t>
@@ -1667,13 +1667,13 @@
     <t xml:space="preserve">16.2129325866699</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4990367889404</t>
+    <t xml:space="preserve">15.4990377426147</t>
   </si>
   <si>
     <t xml:space="preserve">15.517822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4614629745483</t>
+    <t xml:space="preserve">15.4614639282227</t>
   </si>
   <si>
     <t xml:space="preserve">15.1796617507935</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">14.8039283752441</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0857286453247</t>
+    <t xml:space="preserve">15.085729598999</t>
   </si>
   <si>
     <t xml:space="preserve">14.7663545608521</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">14.9730072021484</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8415021896362</t>
+    <t xml:space="preserve">14.8415012359619</t>
   </si>
   <si>
     <t xml:space="preserve">14.5033407211304</t>
@@ -1703,22 +1703,22 @@
     <t xml:space="preserve">14.6724214553833</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3718347549438</t>
+    <t xml:space="preserve">14.3718338012695</t>
   </si>
   <si>
     <t xml:space="preserve">14.822714805603</t>
   </si>
   <si>
-    <t xml:space="preserve">14.559700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4657669067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6348485946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5741815567017</t>
+    <t xml:space="preserve">14.5596990585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4657678604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6348476409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5741844177246</t>
   </si>
   <si>
     <t xml:space="preserve">15.4051036834717</t>
@@ -1727,37 +1727,37 @@
     <t xml:space="preserve">15.3863153457642</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6681175231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2360229492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5929708480835</t>
+    <t xml:space="preserve">15.668116569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2360219955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5929698944092</t>
   </si>
   <si>
     <t xml:space="preserve">15.4238901138306</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3299551010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0481567382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8790760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5409135818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7851419448853</t>
+    <t xml:space="preserve">15.3299570083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0481557846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.879075050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5409145355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7851409912109</t>
   </si>
   <si>
     <t xml:space="preserve">14.6160612106323</t>
   </si>
   <si>
-    <t xml:space="preserve">14.296688079834</t>
+    <t xml:space="preserve">14.2966871261597</t>
   </si>
   <si>
     <t xml:space="preserve">14.2778997421265</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">14.090033531189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9021654129028</t>
+    <t xml:space="preserve">13.9021663665771</t>
   </si>
   <si>
     <t xml:space="preserve">13.7706594467163</t>
@@ -1775,31 +1775,31 @@
     <t xml:space="preserve">14.4281930923462</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2591152191162</t>
+    <t xml:space="preserve">14.2591142654419</t>
   </si>
   <si>
     <t xml:space="preserve">13.8082323074341</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8458061218262</t>
+    <t xml:space="preserve">13.8458051681519</t>
   </si>
   <si>
     <t xml:space="preserve">14.0336723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9397382736206</t>
+    <t xml:space="preserve">13.9397392272949</t>
   </si>
   <si>
     <t xml:space="preserve">14.2403268814087</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0148868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5972738265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9960994720459</t>
+    <t xml:space="preserve">14.0148859024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5972747802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9960985183716</t>
   </si>
   <si>
     <t xml:space="preserve">15.3675308227539</t>
@@ -1814,10 +1814,10 @@
     <t xml:space="preserve">14.4845533370972</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9917964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.292384147644</t>
+    <t xml:space="preserve">14.991795539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2923831939697</t>
   </si>
   <si>
     <t xml:space="preserve">15.0758924484253</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">15.0569295883179</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9052238464355</t>
+    <t xml:space="preserve">14.9052228927612</t>
   </si>
   <si>
     <t xml:space="preserve">14.8104057312012</t>
@@ -1841,37 +1841,37 @@
     <t xml:space="preserve">15.6827230453491</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4602203369141</t>
+    <t xml:space="preserve">16.4602222442627</t>
   </si>
   <si>
     <t xml:space="preserve">16.3274765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7016839981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6637573242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5310134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5499773025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551620483398</t>
+    <t xml:space="preserve">15.7016849517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6637592315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5310144424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5499782562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551610946655</t>
   </si>
   <si>
     <t xml:space="preserve">15.7585763931274</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7965030670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1757698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7206478118896</t>
+    <t xml:space="preserve">15.7965002059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1757678985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7206497192383</t>
   </si>
   <si>
     <t xml:space="preserve">15.6068677902222</t>
@@ -1883,28 +1883,28 @@
     <t xml:space="preserve">16.043025970459</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9861364364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4172353744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344287872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5689420700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4361991882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5879049301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.246563911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1138210296631</t>
+    <t xml:space="preserve">15.9861373901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4172344207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344306945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5689401626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4361982345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5879039764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2465629577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1138200759888</t>
   </si>
   <si>
     <t xml:space="preserve">14.9810771942139</t>
@@ -1913,19 +1913,19 @@
     <t xml:space="preserve">15.2086391448975</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7535152435303</t>
+    <t xml:space="preserve">14.7535161972046</t>
   </si>
   <si>
     <t xml:space="preserve">14.9431505203247</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5069923400879</t>
+    <t xml:space="preserve">14.5069913864136</t>
   </si>
   <si>
     <t xml:space="preserve">14.0329074859619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9380903244019</t>
+    <t xml:space="preserve">13.9380893707275</t>
   </si>
   <si>
     <t xml:space="preserve">14.2225408554077</t>
@@ -1934,13 +1934,13 @@
     <t xml:space="preserve">14.6018085479736</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7914428710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5828456878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3932113647461</t>
+    <t xml:space="preserve">14.7914438247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5828447341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3932123184204</t>
   </si>
   <si>
     <t xml:space="preserve">14.4311380386353</t>
@@ -1949,13 +1949,13 @@
     <t xml:space="preserve">14.6207723617554</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3363227844238</t>
+    <t xml:space="preserve">14.3363218307495</t>
   </si>
   <si>
     <t xml:space="preserve">14.2794313430786</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0518712997437</t>
+    <t xml:space="preserve">14.0518703460693</t>
   </si>
   <si>
     <t xml:space="preserve">13.6915655136108</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">13.0847387313843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8002872467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4210186004639</t>
+    <t xml:space="preserve">12.8002862930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4210195541382</t>
   </si>
   <si>
     <t xml:space="preserve">12.1744956970215</t>
@@ -1985,19 +1985,19 @@
     <t xml:space="preserve">11.9469347000122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4728498458862</t>
+    <t xml:space="preserve">11.4728507995605</t>
   </si>
   <si>
     <t xml:space="preserve">11.0366926193237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1264495849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95577812194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59547519683838</t>
+    <t xml:space="preserve">10.1264486312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95577907562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59547424316406</t>
   </si>
   <si>
     <t xml:space="preserve">8.91279220581055</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">9.41532325744629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09736633300781</t>
+    <t xml:space="preserve">8.09736824035645</t>
   </si>
   <si>
     <t xml:space="preserve">8.55248832702637</t>
@@ -2015,16 +2015,16 @@
     <t xml:space="preserve">9.10242652893066</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1643772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7522411346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9279708862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8951034545898</t>
+    <t xml:space="preserve">10.1643762588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7522420883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9279718399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8951053619385</t>
   </si>
   <si>
     <t xml:space="preserve">11.6055936813354</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">10.3350458145142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6194972991943</t>
+    <t xml:space="preserve">10.61949634552</t>
   </si>
   <si>
     <t xml:space="preserve">10.7332782745361</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">11.1125459671021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9039478302002</t>
+    <t xml:space="preserve">10.9039468765259</t>
   </si>
   <si>
     <t xml:space="preserve">10.5815696716309</t>
@@ -2063,28 +2063,28 @@
     <t xml:space="preserve">10.2023029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87992572784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2212648391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5057163238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4298629760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.771203994751</t>
+    <t xml:space="preserve">9.87992382049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.221266746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5057172775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4298639297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7712030410767</t>
   </si>
   <si>
     <t xml:space="preserve">10.7143144607544</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6953496932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8091316223145</t>
+    <t xml:space="preserve">10.6953506469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8091306686401</t>
   </si>
   <si>
     <t xml:space="preserve">10.8280954360962</t>
@@ -2096,28 +2096,28 @@
     <t xml:space="preserve">10.9987649917603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9418754577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4918127059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.567666053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0556545257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4159603118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5107774734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7952280044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0038251876831</t>
+    <t xml:space="preserve">10.9418745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4918117523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5676670074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0556554794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.415958404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5107765197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7952260971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0038242340088</t>
   </si>
   <si>
     <t xml:space="preserve">12.2882747650146</t>
@@ -2126,106 +2126,106 @@
     <t xml:space="preserve">12.2124223709106</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0986413955688</t>
+    <t xml:space="preserve">12.0986404418945</t>
   </si>
   <si>
     <t xml:space="preserve">11.8521175384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2263269424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0177278518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1883983612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0935831069946</t>
+    <t xml:space="preserve">11.2263250350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.017728805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1883993148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0935821533203</t>
   </si>
   <si>
     <t xml:space="preserve">10.8849840164185</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7901678085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6763868331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4108991622925</t>
+    <t xml:space="preserve">10.790168762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6763877868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4109001159668</t>
   </si>
   <si>
     <t xml:space="preserve">10.4488277435303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6574239730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2073612213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3401050567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2832145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0746192932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9798011779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6005334854126</t>
+    <t xml:space="preserve">10.6574230194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2073621749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.340106010437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2832164764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0746183395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9798021316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6005344390869</t>
   </si>
   <si>
     <t xml:space="preserve">10.3729734420776</t>
   </si>
   <si>
-    <t xml:space="preserve">10.467791557312</t>
+    <t xml:space="preserve">10.4677896499634</t>
   </si>
   <si>
     <t xml:space="preserve">11.6435194015503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4349241256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6814470291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5297403335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6245555877686</t>
+    <t xml:space="preserve">11.4349231719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6814460754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5297393798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6245584487915</t>
   </si>
   <si>
     <t xml:space="preserve">11.5487031936646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.662483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7383375167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2313852310181</t>
+    <t xml:space="preserve">11.6624841690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7383365631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2313842773438</t>
   </si>
   <si>
     <t xml:space="preserve">12.136568069458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1176042556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9658975601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9848604202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8141899108887</t>
+    <t xml:space="preserve">12.1176052093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9658966064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9848613739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.814190864563</t>
   </si>
   <si>
     <t xml:space="preserve">11.7573003768921</t>
@@ -2234,79 +2234,79 @@
     <t xml:space="preserve">11.245288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6485815048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6536388397217</t>
+    <t xml:space="preserve">12.6485805511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.653639793396</t>
   </si>
   <si>
     <t xml:space="preserve">13.3881521224976</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8622369766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5967502593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2364444732666</t>
+    <t xml:space="preserve">13.8622360229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5967493057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2364463806152</t>
   </si>
   <si>
     <t xml:space="preserve">13.4260787963867</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4640045166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1037015914917</t>
+    <t xml:space="preserve">13.4640054702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1036996841431</t>
   </si>
   <si>
     <t xml:space="preserve">13.3312616348267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1277236938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4071159362793</t>
+    <t xml:space="preserve">14.1277227401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7294931411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.407114982605</t>
   </si>
   <si>
     <t xml:space="preserve">13.1226644515991</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4829683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1795539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0227890014648</t>
+    <t xml:space="preserve">13.4829692840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.17955493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0227880477905</t>
   </si>
   <si>
     <t xml:space="preserve">12.0607147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3262023925781</t>
+    <t xml:space="preserve">12.3262014389038</t>
   </si>
   <si>
     <t xml:space="preserve">12.4399824142456</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8571767807007</t>
+    <t xml:space="preserve">12.857177734375</t>
   </si>
   <si>
     <t xml:space="preserve">12.8192510604858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0468101501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3122987747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4450426101685</t>
+    <t xml:space="preserve">13.0468111038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3122997283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4450416564941</t>
   </si>
   <si>
     <t xml:space="preserve">13.5588226318359</t>
@@ -2315,22 +2315,22 @@
     <t xml:space="preserve">13.6179914474487</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6371440887451</t>
+    <t xml:space="preserve">13.6371450424194</t>
   </si>
   <si>
     <t xml:space="preserve">13.4073057174683</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4456119537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3115377426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5030727386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8478307723999</t>
+    <t xml:space="preserve">13.4456129074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3115386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5030717849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8478298187256</t>
   </si>
   <si>
     <t xml:space="preserve">13.886137008667</t>
@@ -2342,37 +2342,37 @@
     <t xml:space="preserve">14.1734371185303</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1542825698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2117443084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9819040298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6946039199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4647655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7712182998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5988368988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5413789749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7903699874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7137565612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8669834136963</t>
+    <t xml:space="preserve">14.1542835235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2117433547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9819049835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6946048736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4647645950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7712173461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.598837852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5413780212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7903709411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7137575149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8669843673706</t>
   </si>
   <si>
     <t xml:space="preserve">14.1351299285889</t>
@@ -2381,13 +2381,13 @@
     <t xml:space="preserve">14.3458156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7097282409668</t>
+    <t xml:space="preserve">14.7097291946411</t>
   </si>
   <si>
     <t xml:space="preserve">14.6331148147583</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9970273971558</t>
+    <t xml:space="preserve">14.9970283508301</t>
   </si>
   <si>
     <t xml:space="preserve">15.0353345870972</t>
@@ -2396,37 +2396,37 @@
     <t xml:space="preserve">16.4909839630127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3377590179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.184534072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8206195831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9546928405762</t>
+    <t xml:space="preserve">16.3377571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1845321655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8206205368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9546909332275</t>
   </si>
   <si>
     <t xml:space="preserve">15.8014659881592</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6099348068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3226337432861</t>
+    <t xml:space="preserve">15.6099338531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3226346969604</t>
   </si>
   <si>
     <t xml:space="preserve">15.7440061569214</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3417882919312</t>
+    <t xml:space="preserve">15.3417873382568</t>
   </si>
   <si>
     <t xml:space="preserve">15.437554359436</t>
   </si>
   <si>
-    <t xml:space="preserve">15.724853515625</t>
+    <t xml:space="preserve">15.7248516082764</t>
   </si>
   <si>
     <t xml:space="preserve">15.858925819397</t>
@@ -2435,22 +2435,22 @@
     <t xml:space="preserve">16.2611446380615</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6059036254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.778284072876</t>
+    <t xml:space="preserve">16.6059055328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7782859802246</t>
   </si>
   <si>
     <t xml:space="preserve">16.6825180053711</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6442089080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7208251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7016735076904</t>
+    <t xml:space="preserve">16.6442108154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7208232879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7016716003418</t>
   </si>
   <si>
     <t xml:space="preserve">17.1613502502441</t>
@@ -2471,19 +2471,19 @@
     <t xml:space="preserve">16.4335231781006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9123592376709</t>
+    <t xml:space="preserve">16.9123573303223</t>
   </si>
   <si>
     <t xml:space="preserve">16.6633644104004</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9506645202637</t>
+    <t xml:space="preserve">16.950662612915</t>
   </si>
   <si>
     <t xml:space="preserve">16.931510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8548984527588</t>
+    <t xml:space="preserve">16.8549003601074</t>
   </si>
   <si>
     <t xml:space="preserve">17.9657897949219</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">18.3105487823486</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6321239471436</t>
+    <t xml:space="preserve">19.6321277618408</t>
   </si>
   <si>
     <t xml:space="preserve">19.9194240570068</t>
@@ -2507,13 +2507,13 @@
     <t xml:space="preserve">19.7757740020752</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7334384918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4940223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1109561920166</t>
+    <t xml:space="preserve">20.7334403991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4940242767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1109580993652</t>
   </si>
   <si>
     <t xml:space="preserve">19.9673080444336</t>
@@ -2522,43 +2522,43 @@
     <t xml:space="preserve">19.8715419769287</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0151901245117</t>
+    <t xml:space="preserve">20.0151920318604</t>
   </si>
   <si>
     <t xml:space="preserve">20.3982563018799</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5419082641602</t>
+    <t xml:space="preserve">20.5419063568115</t>
   </si>
   <si>
     <t xml:space="preserve">20.6376724243164</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9728565216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8770866394043</t>
+    <t xml:space="preserve">20.9728546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8770885467529</t>
   </si>
   <si>
     <t xml:space="preserve">20.3503742218018</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0630741119385</t>
+    <t xml:space="preserve">20.0630760192871</t>
   </si>
   <si>
     <t xml:space="preserve">20.9249706268311</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7278938293457</t>
+    <t xml:space="preserve">19.7278900146484</t>
   </si>
   <si>
     <t xml:space="preserve">19.4884757995605</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3448276519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5363578796387</t>
+    <t xml:space="preserve">19.3448257446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5363597869873</t>
   </si>
   <si>
     <t xml:space="preserve">19.823657989502</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">19.1532936096191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2546081542969</t>
+    <t xml:space="preserve">20.2546062469482</t>
   </si>
   <si>
     <t xml:space="preserve">20.4461402893066</t>
@@ -2576,16 +2576,16 @@
     <t xml:space="preserve">20.2067241668701</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1165027618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6911029815674</t>
+    <t xml:space="preserve">21.1165046691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.691104888916</t>
   </si>
   <si>
     <t xml:space="preserve">21.3080387115479</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7868728637695</t>
+    <t xml:space="preserve">21.7868709564209</t>
   </si>
   <si>
     <t xml:space="preserve">21.7389869689941</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">21.834753036499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5474529266357</t>
+    <t xml:space="preserve">21.5474548339844</t>
   </si>
   <si>
     <t xml:space="preserve">21.8826370239258</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">22.3135852813721</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7924156188965</t>
+    <t xml:space="preserve">22.7924194335938</t>
   </si>
   <si>
     <t xml:space="preserve">23.3191337585449</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">22.4093532562256</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0262870788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6432228088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4038047790527</t>
+    <t xml:space="preserve">22.0262851715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6432209014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4038028717041</t>
   </si>
   <si>
     <t xml:space="preserve">20.8292064666748</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">21.9305191040039</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5162162780762</t>
+    <t xml:space="preserve">24.5162143707275</t>
   </si>
   <si>
     <t xml:space="preserve">23.9416160583496</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">23.4627838134766</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4148998260498</t>
+    <t xml:space="preserve">23.4149017333984</t>
   </si>
   <si>
     <t xml:space="preserve">23.1754856109619</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">23.7500820159912</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6064319610596</t>
+    <t xml:space="preserve">23.6064338684082</t>
   </si>
   <si>
     <t xml:space="preserve">23.0797176361084</t>
@@ -2681,34 +2681,34 @@
     <t xml:space="preserve">23.797966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7022018432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6543159484863</t>
+    <t xml:space="preserve">23.7021980285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.654317855835</t>
   </si>
   <si>
     <t xml:space="preserve">23.0318336486816</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5585498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8403015136719</t>
+    <t xml:space="preserve">23.5585517883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8403034210205</t>
   </si>
   <si>
     <t xml:space="preserve">22.6008853912354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2657032012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5953388214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2178211212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1699371337891</t>
+    <t xml:space="preserve">22.2657012939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5953369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2178192138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1699352264404</t>
   </si>
   <si>
     <t xml:space="preserve">24.2289142608643</t>
@@ -2717,46 +2717,46 @@
     <t xml:space="preserve">23.8937339782715</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4683303833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0373821258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8458480834961</t>
+    <t xml:space="preserve">24.4683322906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0373840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8458499908447</t>
   </si>
   <si>
     <t xml:space="preserve">25.4738788604736</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7611789703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1442432403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8569450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8090629577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9527130126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6654109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4794273376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5751953125</t>
+    <t xml:space="preserve">25.7611770629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1442451477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8569431304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.809061050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9527111053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.665412902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4794254302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5751934051514</t>
   </si>
   <si>
     <t xml:space="preserve">27.4849758148193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3892078399658</t>
+    <t xml:space="preserve">27.3892097473145</t>
   </si>
   <si>
     <t xml:space="preserve">27.3413257598877</t>
@@ -2765,13 +2765,13 @@
     <t xml:space="preserve">27.8680419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4905242919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9638080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2989902496338</t>
+    <t xml:space="preserve">28.4905223846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.963809967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2989883422852</t>
   </si>
   <si>
     <t xml:space="preserve">27.772274017334</t>
@@ -2783,19 +2783,19 @@
     <t xml:space="preserve">27.7243919372559</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5328598022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2455596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9582595825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1497917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.054027557373</t>
+    <t xml:space="preserve">27.5328578948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2455615997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9582576751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1497936248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0540256500244</t>
   </si>
   <si>
     <t xml:space="preserve">26.718843460083</t>
@@ -4602,6 +4602,9 @@
   </si>
   <si>
     <t xml:space="preserve">46.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0999984741211</t>
   </si>
 </sst>
 </file>
@@ -69992,7 +69995,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6911111111</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>43544</v>
@@ -70013,6 +70016,32 @@
         <v>1529</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6911458333</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>53477</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>46.4000015258789</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>45.4500007629395</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>46.1500015258789</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>46.0999984741211</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1530</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="1535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="1536">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6962594985962</t>
+    <t xml:space="preserve">15.6962604522705</t>
   </si>
   <si>
     <t xml:space="preserve">DAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8255224227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3269395828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6344547271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3112964630127</t>
+    <t xml:space="preserve">15.8255214691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3269367218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6344566345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3112983703613</t>
   </si>
   <si>
     <t xml:space="preserve">14.0343036651611</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3851613998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1358699798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9604387283325</t>
+    <t xml:space="preserve">14.3851623535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1358690261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9604396820068</t>
   </si>
   <si>
     <t xml:space="preserve">13.1940927505493</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">12.8801670074463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9724979400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3723468780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.037130355835</t>
+    <t xml:space="preserve">12.9724998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3723459243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0371294021606</t>
   </si>
   <si>
     <t xml:space="preserve">13.221791267395</t>
@@ -89,139 +89,139 @@
     <t xml:space="preserve">16.0009536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1579132080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4349098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1948490142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4718437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2289543151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7119007110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5762329101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2133140563965</t>
+    <t xml:space="preserve">16.1579170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.434907913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1948509216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4718399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2289581298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7119026184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5762319564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2133121490479</t>
   </si>
   <si>
     <t xml:space="preserve">15.4100360870361</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0407123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0499439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4562005996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2069063186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1053428649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0194225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3425788879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8780975341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0350608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1735534667969</t>
+    <t xml:space="preserve">15.0407114028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0499448776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4561996459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2069044113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1053438186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0194206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3425769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8780956268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0350589752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1735572814941</t>
   </si>
   <si>
     <t xml:space="preserve">17.081226348877</t>
   </si>
   <si>
-    <t xml:space="preserve">16.822696685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.462610244751</t>
+    <t xml:space="preserve">16.8227005004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4626083374023</t>
   </si>
   <si>
     <t xml:space="preserve">16.4533748626709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9427299499512</t>
+    <t xml:space="preserve">16.9427280426025</t>
   </si>
   <si>
     <t xml:space="preserve">16.7488327026367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2935848236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4228534698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4874820709229</t>
+    <t xml:space="preserve">17.293586730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4228496551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4874801635742</t>
   </si>
   <si>
     <t xml:space="preserve">17.5521125793457</t>
   </si>
   <si>
-    <t xml:space="preserve">16.647274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3397521972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6352119445801</t>
+    <t xml:space="preserve">16.6472682952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3397541046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6352138519287</t>
   </si>
   <si>
     <t xml:space="preserve">16.9888954162598</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3766860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.57981300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1273880004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3241119384766</t>
+    <t xml:space="preserve">17.3766841888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5798149108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1273918151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3241100311279</t>
   </si>
   <si>
     <t xml:space="preserve">16.6657333374023</t>
   </si>
   <si>
-    <t xml:space="preserve">17.053524017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4043846130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6842021942139</t>
+    <t xml:space="preserve">17.0535278320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4043865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6842002868652</t>
   </si>
   <si>
     <t xml:space="preserve">16.6380386352539</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2381896972656</t>
+    <t xml:space="preserve">17.2381858825684</t>
   </si>
   <si>
     <t xml:space="preserve">17.68137550354</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7552433013916</t>
+    <t xml:space="preserve">17.7552394866943</t>
   </si>
   <si>
     <t xml:space="preserve">17.5244121551514</t>
@@ -230,40 +230,40 @@
     <t xml:space="preserve">17.9860649108887</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2353630065918</t>
+    <t xml:space="preserve">18.2353649139404</t>
   </si>
   <si>
     <t xml:space="preserve">18.143030166626</t>
   </si>
   <si>
-    <t xml:space="preserve">17.912202835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7183113098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4661865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5308208465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5585231781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2168960571289</t>
+    <t xml:space="preserve">17.9122047424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7183074951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4661903381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5308227539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.558521270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2168922424316</t>
   </si>
   <si>
     <t xml:space="preserve">18.4477214813232</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1522636413574</t>
+    <t xml:space="preserve">18.1522617340088</t>
   </si>
   <si>
     <t xml:space="preserve">18.0137672424316</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5890483856201</t>
+    <t xml:space="preserve">17.5890445709229</t>
   </si>
   <si>
     <t xml:space="preserve">17.2658882141113</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">17.6075115203857</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2843551635742</t>
+    <t xml:space="preserve">17.284351348877</t>
   </si>
   <si>
     <t xml:space="preserve">17.1920223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8873329162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9519653320312</t>
+    <t xml:space="preserve">16.8873310089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9519634246826</t>
   </si>
   <si>
     <t xml:space="preserve">16.6749706268311</t>
@@ -293,25 +293,25 @@
     <t xml:space="preserve">16.2594814300537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3610401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8596305847168</t>
+    <t xml:space="preserve">16.3610458374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8596324920654</t>
   </si>
   <si>
     <t xml:space="preserve">16.564172744751</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5272388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2779445648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4782466888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6288051605225</t>
+    <t xml:space="preserve">16.5272407531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.277946472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.47825050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6288032531738</t>
   </si>
   <si>
     <t xml:space="preserve">16.6103382110596</t>
@@ -320,193 +320,193 @@
     <t xml:space="preserve">17.3582191467285</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1089248657227</t>
+    <t xml:space="preserve">17.108922958374</t>
   </si>
   <si>
     <t xml:space="preserve">17.1550903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9178562164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9547882080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0591764450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8652820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1699771881104</t>
+    <t xml:space="preserve">15.9178514480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9547891616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0591773986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8652849197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1699752807617</t>
   </si>
   <si>
     <t xml:space="preserve">15.4377336502075</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0655822753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0868768692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5513572692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.985312461853</t>
+    <t xml:space="preserve">16.0655860900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.086877822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5513563156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9853115081787</t>
   </si>
   <si>
     <t xml:space="preserve">14.6252212524414</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7821855545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5115995407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1330413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.72678565979</t>
+    <t xml:space="preserve">14.7821846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5116004943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1330404281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7267866134644</t>
   </si>
   <si>
     <t xml:space="preserve">14.0989351272583</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3574619293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7544860839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.502368927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4192686080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.603928565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3546380996704</t>
+    <t xml:space="preserve">14.3574638366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7544841766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5023670196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4192695617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6039295196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3546342849731</t>
   </si>
   <si>
     <t xml:space="preserve">15.4285011291504</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4008026123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4839000701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2502479553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7239570617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4931335449219</t>
+    <t xml:space="preserve">15.4008016586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4838991165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2502460479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7239618301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4931344985962</t>
   </si>
   <si>
     <t xml:space="preserve">16.2317810058594</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9363203048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1856136322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2871799468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1763820648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0932846069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2566566467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9242610931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7211303710938</t>
+    <t xml:space="preserve">15.9363231658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1856155395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2871780395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.176383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.093282699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2566547393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9242649078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7211360931396</t>
   </si>
   <si>
     <t xml:space="preserve">16.7580661773682</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7275447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2751216888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1458549499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3120517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4505500793457</t>
+    <t xml:space="preserve">17.7275428771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2751178741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1458568572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3120498657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4505481719971</t>
   </si>
   <si>
     <t xml:space="preserve">16.2040786743164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8901567459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8624563217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9270877838135</t>
+    <t xml:space="preserve">15.890154838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.862455368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270896911621</t>
   </si>
   <si>
     <t xml:space="preserve">16.0563526153564</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7424249649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7701244354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6685600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5946960449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7147274017334</t>
+    <t xml:space="preserve">15.7424268722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7701253890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6685590744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5946950912476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7147283554077</t>
   </si>
   <si>
     <t xml:space="preserve">16.1394500732422</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8134632110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1671504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6408605575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6500940322876</t>
+    <t xml:space="preserve">16.8134651184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1671485900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6408634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6500949859619</t>
   </si>
   <si>
     <t xml:space="preserve">15.8070592880249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4654340744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2623062133789</t>
+    <t xml:space="preserve">15.4654350280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2623071670532</t>
   </si>
   <si>
     <t xml:space="preserve">15.3366203308105</t>
@@ -515,100 +515,100 @@
     <t xml:space="preserve">15.4109344482422</t>
   </si>
   <si>
-    <t xml:space="preserve">15.652458190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7360582351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8939771652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6245918273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0765190124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4295129776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5224056243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5131187438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1601228713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8661079406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3305740356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9311351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4945392608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6060094833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3180418014526</t>
+    <t xml:space="preserve">15.6524572372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7360620498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8939781188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6245889663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0765199661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4295148849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.522406578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131168365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1601238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8661098480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3305778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.931134223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4945383071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6060104370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.318042755127</t>
   </si>
   <si>
     <t xml:space="preserve">15.8846893310547</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0518970489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8382406234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5813884735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.185188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2595043182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.138744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2223491668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.027271270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9529571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4884910583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0922946929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9065113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1666088104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.742546081543</t>
+    <t xml:space="preserve">16.0518989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8382415771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5813865661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1851921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2595024108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1387481689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2223453521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0272731781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9529590606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.488489151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0922966003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9065093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1666107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7425479888916</t>
   </si>
   <si>
     <t xml:space="preserve">17.9004650115967</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9376201629639</t>
+    <t xml:space="preserve">17.9376220703125</t>
   </si>
   <si>
     <t xml:space="preserve">17.8818874359131</t>
@@ -617,13 +617,13 @@
     <t xml:space="preserve">18.4299545288086</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9037113189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9501571655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5539588928223</t>
+    <t xml:space="preserve">18.9037075042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9501533508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5539608001709</t>
   </si>
   <si>
     <t xml:space="preserve">19.6282730102539</t>
@@ -635,25 +635,25 @@
     <t xml:space="preserve">18.9130001068115</t>
   </si>
   <si>
-    <t xml:space="preserve">19.461067199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3310127258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1823844909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0802059173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8572635650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0151748657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9408683776855</t>
+    <t xml:space="preserve">19.4610652923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3310108184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1823883056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.080207824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8572597503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0151805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9408645629883</t>
   </si>
   <si>
     <t xml:space="preserve">18.9315757751465</t>
@@ -662,49 +662,49 @@
     <t xml:space="preserve">18.7550811767578</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5785827636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4020862579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1141185760498</t>
+    <t xml:space="preserve">18.5785846710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4020843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1141204833984</t>
   </si>
   <si>
     <t xml:space="preserve">18.4578227996826</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5321350097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.467113494873</t>
+    <t xml:space="preserve">18.5321369171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4671115875244</t>
   </si>
   <si>
     <t xml:space="preserve">18.3742179870605</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4856910705566</t>
+    <t xml:space="preserve">18.485689163208</t>
   </si>
   <si>
     <t xml:space="preserve">18.2813262939453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3277721405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.513557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6157417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6250286102295</t>
+    <t xml:space="preserve">18.3277702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5135593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6157379150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6250305175781</t>
   </si>
   <si>
     <t xml:space="preserve">18.7272129058838</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0430431365967</t>
+    <t xml:space="preserve">19.0430450439453</t>
   </si>
   <si>
     <t xml:space="preserve">19.4146194458008</t>
@@ -713,40 +713,40 @@
     <t xml:space="preserve">19.0894927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1266498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3681735992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4517765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9594459533691</t>
+    <t xml:space="preserve">19.126651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3681755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4517784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9594421386719</t>
   </si>
   <si>
     <t xml:space="preserve">19.2474117279053</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5075092315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0987815856934</t>
+    <t xml:space="preserve">19.507511138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.098783493042</t>
   </si>
   <si>
     <t xml:space="preserve">19.2195453643799</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3495941162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0337562561035</t>
+    <t xml:space="preserve">19.3495922088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0337581634521</t>
   </si>
   <si>
     <t xml:space="preserve">19.228832244873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3867530822754</t>
+    <t xml:space="preserve">19.386754989624</t>
   </si>
   <si>
     <t xml:space="preserve">19.2845706939697</t>
@@ -758,31 +758,31 @@
     <t xml:space="preserve">20.0091361999512</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3807048797607</t>
+    <t xml:space="preserve">20.3807067871094</t>
   </si>
   <si>
     <t xml:space="preserve">20.6222286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8544597625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9659290313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9473495483398</t>
+    <t xml:space="preserve">20.8544616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9659309387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9473514556885</t>
   </si>
   <si>
     <t xml:space="preserve">20.148473739624</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6129360198975</t>
+    <t xml:space="preserve">20.6129379272461</t>
   </si>
   <si>
     <t xml:space="preserve">20.3899955749512</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2506523132324</t>
+    <t xml:space="preserve">20.2506542205811</t>
   </si>
   <si>
     <t xml:space="preserve">20.5757808685303</t>
@@ -791,31 +791,31 @@
     <t xml:space="preserve">20.6500949859619</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6036491394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5014629364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.529333114624</t>
+    <t xml:space="preserve">20.6036472320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5014667510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5293350219727</t>
   </si>
   <si>
     <t xml:space="preserve">20.6593837738037</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4828853607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8173027038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8637466430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.455020904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7801475524902</t>
+    <t xml:space="preserve">20.4828872680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8173007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.863748550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4550170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7801456451416</t>
   </si>
   <si>
     <t xml:space="preserve">21.6440505981445</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">21.4954204559326</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3653697967529</t>
+    <t xml:space="preserve">21.3653717041016</t>
   </si>
   <si>
     <t xml:space="preserve">21.3189239501953</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">21.2724781036377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1052703857422</t>
+    <t xml:space="preserve">21.1052684783936</t>
   </si>
   <si>
     <t xml:space="preserve">21.3467903137207</t>
@@ -851,31 +851,31 @@
     <t xml:space="preserve">21.2260303497314</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6408061981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.170295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9566421508789</t>
+    <t xml:space="preserve">20.6408042907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1702938079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9566402435303</t>
   </si>
   <si>
     <t xml:space="preserve">21.114559173584</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2538967132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.244607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3375015258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2817668914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9380626678467</t>
+    <t xml:space="preserve">21.2538986206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2446117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3375034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2817687988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9380645751953</t>
   </si>
   <si>
     <t xml:space="preserve">21.1795845031738</t>
@@ -887,28 +887,28 @@
     <t xml:space="preserve">20.3156814575195</t>
   </si>
   <si>
-    <t xml:space="preserve">20.399284362793</t>
+    <t xml:space="preserve">20.3992805480957</t>
   </si>
   <si>
     <t xml:space="preserve">20.4085712432861</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3249683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6315135955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2785243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0462913513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2134990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.795482635498</t>
+    <t xml:space="preserve">20.3249702453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6315155029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2785224914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0462894439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2134971618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7954788208008</t>
   </si>
   <si>
     <t xml:space="preserve">19.9069519042969</t>
@@ -917,19 +917,19 @@
     <t xml:space="preserve">20.2692337036133</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2971019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5479145050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4364414215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9533977508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8326377868652</t>
+    <t xml:space="preserve">20.2971038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5479164123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4364433288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9533996582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8326396942139</t>
   </si>
   <si>
     <t xml:space="preserve">19.8883724212646</t>
@@ -938,37 +938,37 @@
     <t xml:space="preserve">19.7211666107178</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9255294799805</t>
+    <t xml:space="preserve">19.9255332946777</t>
   </si>
   <si>
     <t xml:space="preserve">20.0741577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9998435974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1113166809082</t>
+    <t xml:space="preserve">19.9998455047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1113185882568</t>
   </si>
   <si>
     <t xml:space="preserve">19.6747188568115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6686763763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2413692474365</t>
+    <t xml:space="preserve">20.6686744689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2413673400879</t>
   </si>
   <si>
     <t xml:space="preserve">19.9719753265381</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7304573059082</t>
+    <t xml:space="preserve">19.7304553985596</t>
   </si>
   <si>
     <t xml:space="preserve">20.4178619384766</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1298942565918</t>
+    <t xml:space="preserve">20.1298961639404</t>
   </si>
   <si>
     <t xml:space="preserve">20.4921760559082</t>
@@ -977,46 +977,46 @@
     <t xml:space="preserve">20.8451690673828</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3435497283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5664920806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8916168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1981639862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7244129180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4735984802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3342590332031</t>
+    <t xml:space="preserve">20.3435459136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5664939880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8916149139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1981601715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7244110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4736003875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3342609405518</t>
   </si>
   <si>
     <t xml:space="preserve">20.3714160919189</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8790874481201</t>
+    <t xml:space="preserve">19.8790836334229</t>
   </si>
   <si>
     <t xml:space="preserve">19.841926574707</t>
   </si>
   <si>
-    <t xml:space="preserve">19.767614364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9812660217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0927391052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5200443267822</t>
+    <t xml:space="preserve">19.7676124572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9812679290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.092737197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5200462341309</t>
   </si>
   <si>
     <t xml:space="preserve">19.9905548095703</t>
@@ -1025,19 +1025,19 @@
     <t xml:space="preserve">19.53537940979</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2566986083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7829475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8386840820312</t>
+    <t xml:space="preserve">19.2567005157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7829456329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8386859893799</t>
   </si>
   <si>
     <t xml:space="preserve">18.6343173980713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9966011047363</t>
+    <t xml:space="preserve">18.996603012085</t>
   </si>
   <si>
     <t xml:space="preserve">18.6807651519775</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">18.6621856689453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.439245223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8108177185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1359424591064</t>
+    <t xml:space="preserve">18.4392471313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8108158111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1359405517578</t>
   </si>
   <si>
     <t xml:space="preserve">18.9779300689697</t>
@@ -1064,16 +1064,16 @@
     <t xml:space="preserve">18.9499263763428</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5298538208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3058166503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9044151306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8484058380127</t>
+    <t xml:space="preserve">18.529857635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.305814743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.904411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8484039306641</t>
   </si>
   <si>
     <t xml:space="preserve">17.6430339813232</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">17.6710395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9417495727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8950786590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9697570800781</t>
+    <t xml:space="preserve">17.9417533874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8950748443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9697551727295</t>
   </si>
   <si>
     <t xml:space="preserve">18.2684764862061</t>
@@ -1100,76 +1100,76 @@
     <t xml:space="preserve">18.5858612060547</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4085006713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1657905578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4925174713135</t>
+    <t xml:space="preserve">18.4084968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.16579246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4925136566162</t>
   </si>
   <si>
     <t xml:space="preserve">18.3618240356445</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2218017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6698799133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7725620269775</t>
+    <t xml:space="preserve">18.2218036651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6698760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7725639343262</t>
   </si>
   <si>
     <t xml:space="preserve">18.697883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">18.688549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6138706207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3524894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3804950714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4458408355713</t>
+    <t xml:space="preserve">18.6885471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6138687133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3524913787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3804969787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4458389282227</t>
   </si>
   <si>
     <t xml:space="preserve">18.4831790924072</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4738426208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6605434417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.707218170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5952014923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3898296356201</t>
+    <t xml:space="preserve">18.4738483428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6605415344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7072200775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5951976776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3898315429688</t>
   </si>
   <si>
     <t xml:space="preserve">18.5018482208252</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9032516479492</t>
+    <t xml:space="preserve">18.9032497406006</t>
   </si>
   <si>
     <t xml:space="preserve">19.1832981109619</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4633464813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7433948516846</t>
+    <t xml:space="preserve">19.4633483886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7433986663818</t>
   </si>
   <si>
     <t xml:space="preserve">20.5368671417236</t>
@@ -1184,13 +1184,13 @@
     <t xml:space="preserve">21.5170345306396</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3770084381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6103820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4703598022461</t>
+    <t xml:space="preserve">21.377010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6103839874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4703578948975</t>
   </si>
   <si>
     <t xml:space="preserve">21.7504062652588</t>
@@ -1211,31 +1211,31 @@
     <t xml:space="preserve">20.6302165985107</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7702369689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7235641479492</t>
+    <t xml:space="preserve">20.7702388763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7235660552979</t>
   </si>
   <si>
     <t xml:space="preserve">21.0969638824463</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1903133392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1436367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8635883331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.676887512207</t>
+    <t xml:space="preserve">21.1903114318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1436386108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8635902404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6768894195557</t>
   </si>
   <si>
     <t xml:space="preserve">21.7037334442139</t>
   </si>
   <si>
-    <t xml:space="preserve">22.217155456543</t>
+    <t xml:space="preserve">22.2171535491943</t>
   </si>
   <si>
     <t xml:space="preserve">21.8904342651367</t>
@@ -1244,13 +1244,13 @@
     <t xml:space="preserve">22.0771312713623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9837799072266</t>
+    <t xml:space="preserve">21.9837779998779</t>
   </si>
   <si>
     <t xml:space="preserve">20.8169136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">21.236988067627</t>
+    <t xml:space="preserve">21.2369842529297</t>
   </si>
   <si>
     <t xml:space="preserve">20.3034934997559</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">20.2101440429688</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9102630615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5835399627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9569396972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3303356170654</t>
+    <t xml:space="preserve">20.9102649688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5835380554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9569358825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3303375244141</t>
   </si>
   <si>
     <t xml:space="preserve">20.396842956543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4901924133301</t>
+    <t xml:space="preserve">20.4901905059814</t>
   </si>
   <si>
     <t xml:space="preserve">20.116792678833</t>
@@ -1283,25 +1283,25 @@
     <t xml:space="preserve">19.0432758331299</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1366233825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3233242034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7900714874268</t>
+    <t xml:space="preserve">19.136625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3233261108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7900695800781</t>
   </si>
   <si>
     <t xml:space="preserve">19.6033725738525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3501682281494</t>
+    <t xml:space="preserve">20.3501663208008</t>
   </si>
   <si>
     <t xml:space="preserve">20.2568187713623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.976770401001</t>
+    <t xml:space="preserve">19.9767684936523</t>
   </si>
   <si>
     <t xml:space="preserve">20.1634674072266</t>
@@ -1310,13 +1310,13 @@
     <t xml:space="preserve">20.0234451293945</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8834190368652</t>
+    <t xml:space="preserve">19.8834171295166</t>
   </si>
   <si>
     <t xml:space="preserve">19.9300956726074</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4166717529297</t>
+    <t xml:space="preserve">19.4166698455811</t>
   </si>
   <si>
     <t xml:space="preserve">19.556697845459</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">19.5100231170654</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6500453948975</t>
+    <t xml:space="preserve">19.6500434875488</t>
   </si>
   <si>
     <t xml:space="preserve">19.6967239379883</t>
@@ -1334,19 +1334,19 @@
     <t xml:space="preserve">19.276647567749</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2299728393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3699989318848</t>
+    <t xml:space="preserve">19.2299766540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3699970245361</t>
   </si>
   <si>
     <t xml:space="preserve">19.8367462158203</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4236850738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0701160430908</t>
+    <t xml:space="preserve">21.4236869812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0701179504395</t>
   </si>
   <si>
     <t xml:space="preserve">17.7177143096924</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">15.3093004226685</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7013664245605</t>
+    <t xml:space="preserve">15.7013654708862</t>
   </si>
   <si>
     <t xml:space="preserve">14.7678728103638</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4691543579102</t>
+    <t xml:space="preserve">14.4691553115845</t>
   </si>
   <si>
     <t xml:space="preserve">14.8052129745483</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">15.62668800354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0000839233398</t>
+    <t xml:space="preserve">16.0000858306885</t>
   </si>
   <si>
     <t xml:space="preserve">15.5333375930786</t>
@@ -1382,37 +1382,37 @@
     <t xml:space="preserve">15.3279714584351</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4586582183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8693962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7947177886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6640291213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5893497467041</t>
+    <t xml:space="preserve">15.4586572647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8693971633911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7947187423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6640281677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5893478393555</t>
   </si>
   <si>
     <t xml:space="preserve">15.383978843689</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0105829238892</t>
+    <t xml:space="preserve">15.0105819702148</t>
   </si>
   <si>
     <t xml:space="preserve">14.8602876663208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5784873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4094076156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4469814300537</t>
+    <t xml:space="preserve">14.5784883499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4094066619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4469795227051</t>
   </si>
   <si>
     <t xml:space="preserve">14.9166488647461</t>
@@ -1421,13 +1421,13 @@
     <t xml:space="preserve">14.9354343414307</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6536340713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1420907974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4426774978638</t>
+    <t xml:space="preserve">14.6536359786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.14208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4426765441895</t>
   </si>
   <si>
     <t xml:space="preserve">15.2735958099365</t>
@@ -1439,34 +1439,34 @@
     <t xml:space="preserve">13.920952796936</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6015787124634</t>
+    <t xml:space="preserve">13.6015777587891</t>
   </si>
   <si>
     <t xml:space="preserve">13.7330856323242</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3342599868774</t>
+    <t xml:space="preserve">14.3342609405518</t>
   </si>
   <si>
     <t xml:space="preserve">14.1651811599731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1463947296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2215414047241</t>
+    <t xml:space="preserve">14.1463928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2215423583984</t>
   </si>
   <si>
     <t xml:space="preserve">13.9585256576538</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6391534805298</t>
+    <t xml:space="preserve">13.6391525268555</t>
   </si>
   <si>
     <t xml:space="preserve">13.6203651428223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7894458770752</t>
+    <t xml:space="preserve">13.7894449234009</t>
   </si>
   <si>
     <t xml:space="preserve">14.0524606704712</t>
@@ -1475,55 +1475,55 @@
     <t xml:space="preserve">14.2027540206909</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5221271514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7475662231445</t>
+    <t xml:space="preserve">14.5221261978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7475681304932</t>
   </si>
   <si>
     <t xml:space="preserve">15.2172365188599</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1233034133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.029369354248</t>
+    <t xml:space="preserve">15.1233024597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0293703079224</t>
   </si>
   <si>
     <t xml:space="preserve">15.0669431686401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8978605270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1045160293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1608762741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984491348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5366115570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9687032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8141059875488</t>
+    <t xml:space="preserve">14.8978614807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1045150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1608743667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1984481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366096496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9687042236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8141078948975</t>
   </si>
   <si>
     <t xml:space="preserve">16.8892517089844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9080390930176</t>
+    <t xml:space="preserve">16.9080410003662</t>
   </si>
   <si>
     <t xml:space="preserve">16.4947319030762</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4195861816406</t>
+    <t xml:space="preserve">16.419584274292</t>
   </si>
   <si>
     <t xml:space="preserve">16.2692928314209</t>
@@ -1532,43 +1532,43 @@
     <t xml:space="preserve">16.363224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.987491607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8747692108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8184099197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1377849578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1565723419189</t>
+    <t xml:space="preserve">15.9874906539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8747701644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8184108734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1377868652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1565742492676</t>
   </si>
   <si>
     <t xml:space="preserve">16.2505016326904</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6262397766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5135173797607</t>
+    <t xml:space="preserve">16.6262435913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.513521194458</t>
   </si>
   <si>
     <t xml:space="preserve">16.2880783081055</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4383716583252</t>
+    <t xml:space="preserve">16.4383735656738</t>
   </si>
   <si>
     <t xml:space="preserve">16.4571590423584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2317218780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6074523925781</t>
+    <t xml:space="preserve">16.2317199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6074504852295</t>
   </si>
   <si>
     <t xml:space="preserve">16.7201709747314</t>
@@ -1580,61 +1580,61 @@
     <t xml:space="preserve">16.3256492614746</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8559837341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9499158859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9311294555664</t>
+    <t xml:space="preserve">15.8559846878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9499187469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9311285018921</t>
   </si>
   <si>
     <t xml:space="preserve">16.1189975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0062770843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3444404602051</t>
+    <t xml:space="preserve">16.0062789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3444385528564</t>
   </si>
   <si>
     <t xml:space="preserve">16.4007968902588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5323066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7765331268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.945613861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4716396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.279468536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2606868743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2418937683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1103916168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5280017852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1334800720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0019721984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9831886291504</t>
+    <t xml:space="preserve">16.5323028564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7765350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9456157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4716415405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2794704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2606811523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2418975830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1103897094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5279998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1334819793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.001974105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9831867218018</t>
   </si>
   <si>
     <t xml:space="preserve">16.7389602661133</t>
@@ -1643,16 +1643,16 @@
     <t xml:space="preserve">16.6450233459473</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9643974304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.832893371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0583343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1522674560547</t>
+    <t xml:space="preserve">16.9643993377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8328952789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0583362579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1522655487061</t>
   </si>
   <si>
     <t xml:space="preserve">17.2274131774902</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">16.7577457427979</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2129344940186</t>
+    <t xml:space="preserve">16.2129306793213</t>
   </si>
   <si>
     <t xml:space="preserve">15.4990367889404</t>
@@ -1670,13 +1670,13 @@
     <t xml:space="preserve">15.5178232192993</t>
   </si>
   <si>
-    <t xml:space="preserve">15.461464881897</t>
+    <t xml:space="preserve">15.4614629745483</t>
   </si>
   <si>
     <t xml:space="preserve">15.1796617507935</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6912078857422</t>
+    <t xml:space="preserve">14.6912088394165</t>
   </si>
   <si>
     <t xml:space="preserve">14.8039283752441</t>
@@ -1685,19 +1685,19 @@
     <t xml:space="preserve">15.085729598999</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7663545608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9730072021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8415012359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5033407211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.672420501709</t>
+    <t xml:space="preserve">14.7663536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9730081558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8415021896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5033397674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6724214553833</t>
   </si>
   <si>
     <t xml:space="preserve">14.3718347549438</t>
@@ -1709,40 +1709,40 @@
     <t xml:space="preserve">14.559700012207</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4657678604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6348466873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5741844177246</t>
+    <t xml:space="preserve">14.4657669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6348485946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5741815567017</t>
   </si>
   <si>
     <t xml:space="preserve">15.4051036834717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3863172531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6681175231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2360229492188</t>
+    <t xml:space="preserve">15.3863153457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.668116569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2360219955444</t>
   </si>
   <si>
     <t xml:space="preserve">15.5929708480835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4238910675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3299570083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0481557846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8790740966797</t>
+    <t xml:space="preserve">15.4238901138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3299551010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0481567382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.879075050354</t>
   </si>
   <si>
     <t xml:space="preserve">14.5409135818481</t>
@@ -1751,28 +1751,28 @@
     <t xml:space="preserve">14.7851409912109</t>
   </si>
   <si>
-    <t xml:space="preserve">14.616060256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2966871261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2779006958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0900344848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9021663665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.770658493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4281940460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2591142654419</t>
+    <t xml:space="preserve">14.6160612106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.296688079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2778997421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0900325775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9021654129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7706594467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4281930923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2591152191162</t>
   </si>
   <si>
     <t xml:space="preserve">13.8082323074341</t>
@@ -1784,22 +1784,22 @@
     <t xml:space="preserve">14.0336723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9397401809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.240327835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0148859024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5972738265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9960985183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3675308227539</t>
+    <t xml:space="preserve">13.9397392272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2403268814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0148868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5972747802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9960994720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3675298690796</t>
   </si>
   <si>
     <t xml:space="preserve">14.183967590332</t>
@@ -1811,19 +1811,19 @@
     <t xml:space="preserve">14.4845533370972</t>
   </si>
   <si>
-    <t xml:space="preserve">14.991795539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2923831939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0758924484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0569305419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9052238464355</t>
+    <t xml:space="preserve">14.9917964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.292384147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0758934020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0569295883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9052228927612</t>
   </si>
   <si>
     <t xml:space="preserve">14.8104057312012</t>
@@ -1838,34 +1838,34 @@
     <t xml:space="preserve">15.6827230453491</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4602222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3274765014648</t>
+    <t xml:space="preserve">16.4602203369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3274784088135</t>
   </si>
   <si>
     <t xml:space="preserve">15.7016849517822</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6637582778931</t>
+    <t xml:space="preserve">15.6637573242188</t>
   </si>
   <si>
     <t xml:space="preserve">15.5310144424438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5499782562256</t>
+    <t xml:space="preserve">15.5499773025513</t>
   </si>
   <si>
     <t xml:space="preserve">15.4551620483398</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7585763931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7965021133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1757659912109</t>
+    <t xml:space="preserve">15.7585754394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7965030670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1757717132568</t>
   </si>
   <si>
     <t xml:space="preserve">15.720648765564</t>
@@ -1880,28 +1880,28 @@
     <t xml:space="preserve">16.043025970459</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9861364364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4172344207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344316482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5689401626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4361982345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5879039764404</t>
+    <t xml:space="preserve">15.986138343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.417236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344287872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.568941116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4361991882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5879068374634</t>
   </si>
   <si>
     <t xml:space="preserve">15.246563911438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1138191223145</t>
+    <t xml:space="preserve">15.1138200759888</t>
   </si>
   <si>
     <t xml:space="preserve">14.9810771942139</t>
@@ -1919,19 +1919,19 @@
     <t xml:space="preserve">14.5069923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0329065322876</t>
+    <t xml:space="preserve">14.0329074859619</t>
   </si>
   <si>
     <t xml:space="preserve">13.9380893707275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2225408554077</t>
+    <t xml:space="preserve">14.222541809082</t>
   </si>
   <si>
     <t xml:space="preserve">14.6018085479736</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7914428710938</t>
+    <t xml:space="preserve">14.7914438247681</t>
   </si>
   <si>
     <t xml:space="preserve">14.5828447341919</t>
@@ -1955,31 +1955,31 @@
     <t xml:space="preserve">14.0518703460693</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6915664672852</t>
+    <t xml:space="preserve">13.6915655136108</t>
   </si>
   <si>
     <t xml:space="preserve">13.1416273117065</t>
   </si>
   <si>
-    <t xml:space="preserve">13.008885383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3691892623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.08473777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8002862930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4210205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1744956970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9469337463379</t>
+    <t xml:space="preserve">13.0088844299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3691883087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0847387313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8002872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4210186004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1744966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9469347000122</t>
   </si>
   <si>
     <t xml:space="preserve">11.4728498458862</t>
@@ -1991,43 +1991,43 @@
     <t xml:space="preserve">10.1264486312866</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95577812194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59547519683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91279220581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41532421112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09736728668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55248832702637</t>
+    <t xml:space="preserve">9.95577907562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59547424316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91279315948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41532325744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09736633300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55248737335205</t>
   </si>
   <si>
     <t xml:space="preserve">9.10242652893066</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1643753051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7522411346436</t>
+    <t xml:space="preserve">10.1643762588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7522401809692</t>
   </si>
   <si>
     <t xml:space="preserve">11.9279708862305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8951044082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6055927276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9608373641968</t>
+    <t xml:space="preserve">12.8951034545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6055936813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9608392715454</t>
   </si>
   <si>
     <t xml:space="preserve">10.9229116439819</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">10.6384611129761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.06955909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3350458145142</t>
+    <t xml:space="preserve">10.0695581436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3350467681885</t>
   </si>
   <si>
     <t xml:space="preserve">10.6194972991943</t>
@@ -2048,22 +2048,22 @@
     <t xml:space="preserve">10.7332773208618</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1125450134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9039487838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5815696716309</t>
+    <t xml:space="preserve">11.1125459671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9039478302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5815706253052</t>
   </si>
   <si>
     <t xml:space="preserve">10.2023029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87992382049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2212657928467</t>
+    <t xml:space="preserve">9.87992477416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2212648391724</t>
   </si>
   <si>
     <t xml:space="preserve">10.5057172775269</t>
@@ -2072,25 +2072,25 @@
     <t xml:space="preserve">10.4298639297485</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7712030410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7143135070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6953506469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8091306686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8280954360962</t>
+    <t xml:space="preserve">10.771203994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7143144607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6953496932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8091316223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8280944824219</t>
   </si>
   <si>
     <t xml:space="preserve">10.5436429977417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9987659454346</t>
+    <t xml:space="preserve">10.9987649917603</t>
   </si>
   <si>
     <t xml:space="preserve">10.9418754577637</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">11.4918127059937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.567666053772</t>
+    <t xml:space="preserve">11.5676670074463</t>
   </si>
   <si>
     <t xml:space="preserve">11.0556545257568</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4159593582153</t>
+    <t xml:space="preserve">11.4159603118896</t>
   </si>
   <si>
     <t xml:space="preserve">11.5107765197754</t>
@@ -2114,19 +2114,19 @@
     <t xml:space="preserve">11.7952270507812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0038242340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.288275718689</t>
+    <t xml:space="preserve">12.0038251876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2882747650146</t>
   </si>
   <si>
     <t xml:space="preserve">12.2124214172363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0986404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8521165847778</t>
+    <t xml:space="preserve">12.0986413955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8521184921265</t>
   </si>
   <si>
     <t xml:space="preserve">11.2263259887695</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">11.0177278518677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1883983612061</t>
+    <t xml:space="preserve">11.1883993148804</t>
   </si>
   <si>
     <t xml:space="preserve">11.0935821533203</t>
@@ -2144,67 +2144,67 @@
     <t xml:space="preserve">10.8849840164185</t>
   </si>
   <si>
-    <t xml:space="preserve">10.790168762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6763877868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4109010696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4488286972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6574239730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2073631286621</t>
+    <t xml:space="preserve">10.7901678085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6763868331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4108991622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.448826789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6574249267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2073612213135</t>
   </si>
   <si>
     <t xml:space="preserve">11.340106010437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2832164764404</t>
+    <t xml:space="preserve">11.2832155227661</t>
   </si>
   <si>
     <t xml:space="preserve">11.0746183395386</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9798021316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6005344390869</t>
+    <t xml:space="preserve">10.9798011779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6005334854126</t>
   </si>
   <si>
     <t xml:space="preserve">10.3729724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4677896499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6435203552246</t>
+    <t xml:space="preserve">10.4677906036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6435194015503</t>
   </si>
   <si>
     <t xml:space="preserve">11.4349231719971</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6814470291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5297393798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6245584487915</t>
+    <t xml:space="preserve">11.6814460754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5297403335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6245565414429</t>
   </si>
   <si>
     <t xml:space="preserve">11.5487031936646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6624841690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7383375167847</t>
+    <t xml:space="preserve">11.662483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7383365631104</t>
   </si>
   <si>
     <t xml:space="preserve">12.2313852310181</t>
@@ -2213,28 +2213,28 @@
     <t xml:space="preserve">12.136568069458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1176052093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9658975601196</t>
+    <t xml:space="preserve">12.117603302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9658966064453</t>
   </si>
   <si>
     <t xml:space="preserve">11.9848613739014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.814190864563</t>
+    <t xml:space="preserve">11.8141899108887</t>
   </si>
   <si>
     <t xml:space="preserve">11.7573003768921</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2452898025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6485795974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.653639793396</t>
+    <t xml:space="preserve">11.245288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6485805511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6536388397217</t>
   </si>
   <si>
     <t xml:space="preserve">13.3881521224976</t>
@@ -2243,13 +2243,13 @@
     <t xml:space="preserve">13.8622360229492</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5967493057251</t>
+    <t xml:space="preserve">13.5967502593994</t>
   </si>
   <si>
     <t xml:space="preserve">13.2364454269409</t>
   </si>
   <si>
-    <t xml:space="preserve">13.426079750061</t>
+    <t xml:space="preserve">13.4260787963867</t>
   </si>
   <si>
     <t xml:space="preserve">13.4640054702759</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">13.3312616348267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1277227401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7294931411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.407114982605</t>
+    <t xml:space="preserve">14.1277236938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4071159362793</t>
   </si>
   <si>
     <t xml:space="preserve">13.1226654052734</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">13.4829683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">13.17955493927</t>
+    <t xml:space="preserve">13.1795539855957</t>
   </si>
   <si>
     <t xml:space="preserve">12.0227880477905</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">12.0607147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3262014389038</t>
+    <t xml:space="preserve">12.3262033462524</t>
   </si>
   <si>
     <t xml:space="preserve">12.4399814605713</t>
@@ -2294,16 +2294,16 @@
     <t xml:space="preserve">12.857177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8192510604858</t>
+    <t xml:space="preserve">12.8192501068115</t>
   </si>
   <si>
     <t xml:space="preserve">13.0468111038208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3122997283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4450416564941</t>
+    <t xml:space="preserve">13.3122987747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4450426101685</t>
   </si>
   <si>
     <t xml:space="preserve">13.5588226318359</t>
@@ -2312,16 +2312,16 @@
     <t xml:space="preserve">13.6179914474487</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6371450424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4073057174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4456129074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3115386962891</t>
+    <t xml:space="preserve">13.6371440887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4073047637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4456119537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3115377426147</t>
   </si>
   <si>
     <t xml:space="preserve">13.5030717849731</t>
@@ -2330,79 +2330,79 @@
     <t xml:space="preserve">13.8478298187256</t>
   </si>
   <si>
-    <t xml:space="preserve">13.886137008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7520637512207</t>
+    <t xml:space="preserve">13.8861379623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7520627975464</t>
   </si>
   <si>
     <t xml:space="preserve">14.1734371185303</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1542835235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2117433547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9819049835205</t>
+    <t xml:space="preserve">14.1542825698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2117443084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9819040298462</t>
   </si>
   <si>
     <t xml:space="preserve">13.6946048736572</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4647645950317</t>
+    <t xml:space="preserve">13.4647655487061</t>
   </si>
   <si>
     <t xml:space="preserve">13.7712173461914</t>
   </si>
   <si>
-    <t xml:space="preserve">13.598837852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5413780212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7903709411621</t>
+    <t xml:space="preserve">13.5988368988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5413789749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7903699874878</t>
   </si>
   <si>
     <t xml:space="preserve">13.7137575149536</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8669843673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1351299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3458156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7097291946411</t>
+    <t xml:space="preserve">13.8669834136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1351308822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3458166122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7097272872925</t>
   </si>
   <si>
     <t xml:space="preserve">14.6331148147583</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9970283508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0353345870972</t>
+    <t xml:space="preserve">14.9970273971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0353336334229</t>
   </si>
   <si>
     <t xml:space="preserve">16.4909839630127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3377571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1845321655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8206205368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9546909332275</t>
+    <t xml:space="preserve">16.3377590179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.184534072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8206195831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9546928405762</t>
   </si>
   <si>
     <t xml:space="preserve">15.8014659881592</t>
@@ -2414,16 +2414,16 @@
     <t xml:space="preserve">15.3226346969604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7440061569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3417873382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.437554359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7248516082764</t>
+    <t xml:space="preserve">15.7440071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3417892456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4375534057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7248525619507</t>
   </si>
   <si>
     <t xml:space="preserve">15.858925819397</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">16.6059055328369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7782859802246</t>
+    <t xml:space="preserve">16.778284072876</t>
   </si>
   <si>
     <t xml:space="preserve">16.6825180053711</t>
@@ -2444,22 +2444,22 @@
     <t xml:space="preserve">16.6442108154297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7208232879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7016716003418</t>
+    <t xml:space="preserve">16.7208251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7016735076904</t>
   </si>
   <si>
     <t xml:space="preserve">17.1613502502441</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1421966552734</t>
+    <t xml:space="preserve">17.1421985626221</t>
   </si>
   <si>
     <t xml:space="preserve">17.1996574401855</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9889698028564</t>
+    <t xml:space="preserve">16.9889678955078</t>
   </si>
   <si>
     <t xml:space="preserve">16.4526786804199</t>
@@ -2474,13 +2474,13 @@
     <t xml:space="preserve">16.6633644104004</t>
   </si>
   <si>
-    <t xml:space="preserve">16.950662612915</t>
+    <t xml:space="preserve">16.9506645202637</t>
   </si>
   <si>
     <t xml:space="preserve">16.931510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8549003601074</t>
+    <t xml:space="preserve">16.8548984527588</t>
   </si>
   <si>
     <t xml:space="preserve">17.9657897949219</t>
@@ -2492,28 +2492,28 @@
     <t xml:space="preserve">18.3105487823486</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6321277618408</t>
+    <t xml:space="preserve">19.6321239471436</t>
   </si>
   <si>
     <t xml:space="preserve">19.9194240570068</t>
   </si>
   <si>
-    <t xml:space="preserve">20.302490234375</t>
+    <t xml:space="preserve">20.3024921417236</t>
   </si>
   <si>
     <t xml:space="preserve">19.7757740020752</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7334403991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4940242767334</t>
+    <t xml:space="preserve">20.7334384918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4940223693848</t>
   </si>
   <si>
     <t xml:space="preserve">20.1109580993652</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9673080444336</t>
+    <t xml:space="preserve">19.967306137085</t>
   </si>
   <si>
     <t xml:space="preserve">19.8715419769287</t>
@@ -2525,13 +2525,13 @@
     <t xml:space="preserve">20.3982563018799</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5419063568115</t>
+    <t xml:space="preserve">20.5419082641602</t>
   </si>
   <si>
     <t xml:space="preserve">20.6376724243164</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9728546142578</t>
+    <t xml:space="preserve">20.9728565216064</t>
   </si>
   <si>
     <t xml:space="preserve">20.8770885467529</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">20.9249706268311</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7278900146484</t>
+    <t xml:space="preserve">19.7278919219971</t>
   </si>
   <si>
     <t xml:space="preserve">19.4884757995605</t>
@@ -2555,28 +2555,28 @@
     <t xml:space="preserve">19.3448257446289</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5363597869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.823657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1532936096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2546062469482</t>
+    <t xml:space="preserve">19.5363578796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8236598968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1532917022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2546081542969</t>
   </si>
   <si>
     <t xml:space="preserve">20.4461402893066</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2067241668701</t>
+    <t xml:space="preserve">20.2067222595215</t>
   </si>
   <si>
     <t xml:space="preserve">21.1165046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">21.691104888916</t>
+    <t xml:space="preserve">21.6911029815674</t>
   </si>
   <si>
     <t xml:space="preserve">21.3080387115479</t>
@@ -2585,19 +2585,19 @@
     <t xml:space="preserve">21.7868709564209</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7389869689941</t>
+    <t xml:space="preserve">21.7389888763428</t>
   </si>
   <si>
     <t xml:space="preserve">21.834753036499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5474548339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8826370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9784030914307</t>
+    <t xml:space="preserve">21.5474529266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8826351165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9784049987793</t>
   </si>
   <si>
     <t xml:space="preserve">21.212272644043</t>
@@ -2612,25 +2612,25 @@
     <t xml:space="preserve">22.3135852813721</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7924194335938</t>
+    <t xml:space="preserve">22.7924175262451</t>
   </si>
   <si>
     <t xml:space="preserve">23.3191337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6487693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4093532562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0262851715088</t>
+    <t xml:space="preserve">22.6487674713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.409351348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0262870788574</t>
   </si>
   <si>
     <t xml:space="preserve">21.6432209014893</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4038028717041</t>
+    <t xml:space="preserve">21.4038047790527</t>
   </si>
   <si>
     <t xml:space="preserve">20.8292064666748</t>
@@ -2639,16 +2639,16 @@
     <t xml:space="preserve">20.7813243865967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9305191040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5162143707275</t>
+    <t xml:space="preserve">21.9305210113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5162162780762</t>
   </si>
   <si>
     <t xml:space="preserve">23.9416160583496</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4627838134766</t>
+    <t xml:space="preserve">23.4627819061279</t>
   </si>
   <si>
     <t xml:space="preserve">23.4149017333984</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">23.1754856109619</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2712516784668</t>
+    <t xml:space="preserve">23.2712497711182</t>
   </si>
   <si>
     <t xml:space="preserve">23.5106678009033</t>
@@ -2669,16 +2669,16 @@
     <t xml:space="preserve">23.7500820159912</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6064338684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0797176361084</t>
+    <t xml:space="preserve">23.6064319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0797157287598</t>
   </si>
   <si>
     <t xml:space="preserve">23.797966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7021980285645</t>
+    <t xml:space="preserve">23.7021999359131</t>
   </si>
   <si>
     <t xml:space="preserve">23.654317855835</t>
@@ -2690,22 +2690,22 @@
     <t xml:space="preserve">23.5585517883301</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8403034210205</t>
+    <t xml:space="preserve">22.8402996063232</t>
   </si>
   <si>
     <t xml:space="preserve">22.6008853912354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2657012939453</t>
+    <t xml:space="preserve">22.2657032012939</t>
   </si>
   <si>
     <t xml:space="preserve">21.5953369140625</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2178192138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1699352264404</t>
+    <t xml:space="preserve">22.2178211212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1699371337891</t>
   </si>
   <si>
     <t xml:space="preserve">24.2289142608643</t>
@@ -2723,28 +2723,28 @@
     <t xml:space="preserve">23.8458499908447</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4738788604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7611770629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1442451477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8569431304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.809061050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9527111053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.665412902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4794254302979</t>
+    <t xml:space="preserve">25.4738807678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7611789703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1442432403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8569450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8090629577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9527130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6654109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4794273376465</t>
   </si>
   <si>
     <t xml:space="preserve">26.5751934051514</t>
@@ -2762,37 +2762,37 @@
     <t xml:space="preserve">27.8680419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4905223846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.963809967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2989883422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.772274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.628625869751</t>
+    <t xml:space="preserve">28.4905242919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9638080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2989902496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7722759246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6286239624023</t>
   </si>
   <si>
     <t xml:space="preserve">27.7243919372559</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5328578948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2455615997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9582576751709</t>
+    <t xml:space="preserve">27.5328598022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2455596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9582595825195</t>
   </si>
   <si>
     <t xml:space="preserve">27.1497936248779</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0540256500244</t>
+    <t xml:space="preserve">27.054027557373</t>
   </si>
   <si>
     <t xml:space="preserve">26.718843460083</t>
@@ -2804,25 +2804,25 @@
     <t xml:space="preserve">26.2543506622314</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8207950592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4354057312012</t>
+    <t xml:space="preserve">25.8207931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4354076385498</t>
   </si>
   <si>
     <t xml:space="preserve">24.5682926177979</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7128124237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1347351074219</t>
+    <t xml:space="preserve">24.7128105163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1347332000732</t>
   </si>
   <si>
     <t xml:space="preserve">24.760986328125</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6646385192871</t>
+    <t xml:space="preserve">24.6646404266357</t>
   </si>
   <si>
     <t xml:space="preserve">25.0981960296631</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">25.9171390533447</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8689670562744</t>
+    <t xml:space="preserve">25.868968963623</t>
   </si>
   <si>
     <t xml:space="preserve">25.4835815429688</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">25.7244491577148</t>
   </si>
   <si>
-    <t xml:space="preserve">25.146369934082</t>
+    <t xml:space="preserve">25.1463718414307</t>
   </si>
   <si>
     <t xml:space="preserve">25.579927444458</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">26.1098327636719</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0616588592529</t>
+    <t xml:space="preserve">26.0616569519043</t>
   </si>
   <si>
     <t xml:space="preserve">25.9653129577637</t>
@@ -2870,19 +2870,19 @@
     <t xml:space="preserve">25.628101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8573303222656</t>
+    <t xml:space="preserve">24.857328414917</t>
   </si>
   <si>
     <t xml:space="preserve">25.6762733459473</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5317535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0500221252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4719467163086</t>
+    <t xml:space="preserve">25.5317554473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0500240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.47194480896</t>
   </si>
   <si>
     <t xml:space="preserve">22.9785804748535</t>
@@ -2891,22 +2891,22 @@
     <t xml:space="preserve">22.7858867645264</t>
   </si>
   <si>
-    <t xml:space="preserve">23.653003692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0267524719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9304065704346</t>
+    <t xml:space="preserve">23.6530017852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0267543792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9304046630859</t>
   </si>
   <si>
     <t xml:space="preserve">23.2194442749023</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4121379852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4486751556396</t>
+    <t xml:space="preserve">23.4121360778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.448673248291</t>
   </si>
   <si>
     <t xml:space="preserve">21.9669437408447</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">21.5815582275391</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6413650512695</t>
+    <t xml:space="preserve">22.6413669586182</t>
   </si>
   <si>
     <t xml:space="preserve">22.8340606689453</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">22.063289642334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3888683319092</t>
+    <t xml:space="preserve">21.3888664245605</t>
   </si>
   <si>
     <t xml:space="preserve">21.1480007171631</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">19.5101146697998</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1845397949219</t>
+    <t xml:space="preserve">20.1845378875732</t>
   </si>
   <si>
     <t xml:space="preserve">19.9436721801758</t>
@@ -2963,22 +2963,22 @@
     <t xml:space="preserve">19.1536331176758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1323642730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8991317749023</t>
+    <t xml:space="preserve">18.1323623657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.899133682251</t>
   </si>
   <si>
     <t xml:space="preserve">16.9569416046143</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0167484283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1516304016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5542869567871</t>
+    <t xml:space="preserve">18.0167503356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.15163230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5542850494385</t>
   </si>
   <si>
     <t xml:space="preserve">18.3057861328125</t>
@@ -2987,10 +2987,10 @@
     <t xml:space="preserve">17.8433246612549</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4964790344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6719036102295</t>
+    <t xml:space="preserve">17.4964771270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6719017028809</t>
   </si>
   <si>
     <t xml:space="preserve">18.2672462463379</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">18.6911716461182</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3828620910645</t>
+    <t xml:space="preserve">18.3828639984131</t>
   </si>
   <si>
     <t xml:space="preserve">18.7682476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0765552520752</t>
+    <t xml:space="preserve">19.0765571594238</t>
   </si>
   <si>
     <t xml:space="preserve">19.1921730041504</t>
@@ -3032,16 +3032,16 @@
     <t xml:space="preserve">18.6526355743408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4021339416504</t>
+    <t xml:space="preserve">18.4021320343018</t>
   </si>
   <si>
     <t xml:space="preserve">18.7297096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4137687683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7509822845459</t>
+    <t xml:space="preserve">19.4137668609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7509803771973</t>
   </si>
   <si>
     <t xml:space="preserve">19.1343669891357</t>
@@ -3050,16 +3050,16 @@
     <t xml:space="preserve">18.7489776611328</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9224014282227</t>
+    <t xml:space="preserve">18.9224033355713</t>
   </si>
   <si>
     <t xml:space="preserve">19.3655948638916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2692489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5350170135498</t>
+    <t xml:space="preserve">19.2692470550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5350189208984</t>
   </si>
   <si>
     <t xml:space="preserve">17.7277088165283</t>
@@ -3080,10 +3080,10 @@
     <t xml:space="preserve">20.7144432067871</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0516529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4852123260498</t>
+    <t xml:space="preserve">21.0516548156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4852142333984</t>
   </si>
   <si>
     <t xml:space="preserve">21.4370403289795</t>
@@ -3092,10 +3092,10 @@
     <t xml:space="preserve">21.8705978393555</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4005012512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1230983734131</t>
+    <t xml:space="preserve">22.4005031585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1231002807617</t>
   </si>
   <si>
     <t xml:space="preserve">23.3157920837402</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">22.5450229644775</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2078094482422</t>
+    <t xml:space="preserve">22.2078075408936</t>
   </si>
   <si>
     <t xml:space="preserve">20.4254035949707</t>
@@ -3119,13 +3119,13 @@
     <t xml:space="preserve">20.2327117919922</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4735774993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8473243713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2499809265137</t>
+    <t xml:space="preserve">20.473575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8473262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.249979019165</t>
   </si>
   <si>
     <t xml:space="preserve">18.7875175476074</t>
@@ -3134,25 +3134,25 @@
     <t xml:space="preserve">18.5948257446289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5735569000244</t>
+    <t xml:space="preserve">17.5735549926758</t>
   </si>
   <si>
     <t xml:space="preserve">18.8067874908447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4984798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2287082672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.074556350708</t>
+    <t xml:space="preserve">18.4984817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2287101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0745582580566</t>
   </si>
   <si>
     <t xml:space="preserve">18.5562877655029</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7104396820068</t>
+    <t xml:space="preserve">18.7104415893555</t>
   </si>
   <si>
     <t xml:space="preserve">18.94167137146</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">18.2865180969238</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9782104492188</t>
+    <t xml:space="preserve">17.9782085418701</t>
   </si>
   <si>
     <t xml:space="preserve">18.5755577087402</t>
@@ -3182,22 +3182,22 @@
     <t xml:space="preserve">18.9802112579346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4619407653809</t>
+    <t xml:space="preserve">19.4619426727295</t>
   </si>
   <si>
     <t xml:space="preserve">18.1709022521973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.708438873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9204025268555</t>
+    <t xml:space="preserve">17.7084369659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9204006195068</t>
   </si>
   <si>
     <t xml:space="preserve">17.6313610076904</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2094402313232</t>
+    <t xml:space="preserve">18.2094383239746</t>
   </si>
   <si>
     <t xml:space="preserve">18.2479782104492</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">17.669900894165</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3423252105713</t>
+    <t xml:space="preserve">17.3423233032227</t>
   </si>
   <si>
     <t xml:space="preserve">16.6293621063232</t>
@@ -3218,13 +3218,13 @@
     <t xml:space="preserve">16.455940246582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.205436706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0512828826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2247085571289</t>
+    <t xml:space="preserve">16.2054386138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0512847900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2247066497803</t>
   </si>
   <si>
     <t xml:space="preserve">15.4153995513916</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">15.357590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7257099151611</t>
+    <t xml:space="preserve">16.7257080078125</t>
   </si>
   <si>
     <t xml:space="preserve">16.128360748291</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">17.1110935211182</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4386711120605</t>
+    <t xml:space="preserve">17.4386730194092</t>
   </si>
   <si>
     <t xml:space="preserve">17.2459774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1688995361328</t>
+    <t xml:space="preserve">17.1689014434814</t>
   </si>
   <si>
     <t xml:space="preserve">17.1303615570068</t>
@@ -3266,13 +3266,13 @@
     <t xml:space="preserve">17.9589405059814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8838653564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.826057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5582866668701</t>
+    <t xml:space="preserve">18.8838634490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8260555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5582885742188</t>
   </si>
   <si>
     <t xml:space="preserve">20.088191986084</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">20.3290576934814</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7626152038574</t>
+    <t xml:space="preserve">20.7626171112061</t>
   </si>
   <si>
     <t xml:space="preserve">20.8589630126953</t>
@@ -3305,13 +3305,13 @@
     <t xml:space="preserve">20.8875617980957</t>
   </si>
   <si>
-    <t xml:space="preserve">20.741153717041</t>
+    <t xml:space="preserve">20.7411518096924</t>
   </si>
   <si>
     <t xml:space="preserve">20.6435470581055</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4483375549316</t>
+    <t xml:space="preserve">20.448335647583</t>
   </si>
   <si>
     <t xml:space="preserve">20.6923503875732</t>
@@ -3320,13 +3320,13 @@
     <t xml:space="preserve">20.5947437286377</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5459403991699</t>
+    <t xml:space="preserve">20.5459423065186</t>
   </si>
   <si>
     <t xml:space="preserve">20.3019275665283</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3267841339111</t>
+    <t xml:space="preserve">21.3267860412598</t>
   </si>
   <si>
     <t xml:space="preserve">20.4971389770508</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">20.1555194854736</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1067161560059</t>
+    <t xml:space="preserve">20.1067180633545</t>
   </si>
   <si>
     <t xml:space="preserve">20.2531261444092</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">21.0827713012695</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7660083770752</t>
+    <t xml:space="preserve">21.7660102844238</t>
   </si>
   <si>
     <t xml:space="preserve">21.8636150360107</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">22.5956554412842</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9372730255127</t>
+    <t xml:space="preserve">22.9372749328613</t>
   </si>
   <si>
     <t xml:space="preserve">23.083683013916</t>
@@ -3392,10 +3392,10 @@
     <t xml:space="preserve">23.4741039276123</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2300910949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7181186676025</t>
+    <t xml:space="preserve">23.2300891876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7181167602539</t>
   </si>
   <si>
     <t xml:space="preserve">23.6693153381348</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">23.6205139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7669200897217</t>
+    <t xml:space="preserve">23.7669219970703</t>
   </si>
   <si>
     <t xml:space="preserve">23.8645267486572</t>
@@ -3413,22 +3413,22 @@
     <t xml:space="preserve">23.2788944244385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3276958465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9621315002441</t>
+    <t xml:space="preserve">23.3276977539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9621295928955</t>
   </si>
   <si>
     <t xml:space="preserve">24.6941719055176</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3286094665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.986988067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7917785644531</t>
+    <t xml:space="preserve">25.3286075592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9869899749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7917766571045</t>
   </si>
   <si>
     <t xml:space="preserve">24.4989624023438</t>
@@ -3437,25 +3437,25 @@
     <t xml:space="preserve">24.5965671539307</t>
   </si>
   <si>
-    <t xml:space="preserve">24.450159072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3037509918213</t>
+    <t xml:space="preserve">24.4501571655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3037490844727</t>
   </si>
   <si>
     <t xml:space="preserve">24.0109348297119</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7420635223389</t>
+    <t xml:space="preserve">22.7420616149902</t>
   </si>
   <si>
     <t xml:space="preserve">22.644458770752</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1812877655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8884735107422</t>
+    <t xml:space="preserve">23.1812896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8884716033936</t>
   </si>
   <si>
     <t xml:space="preserve">23.0348796844482</t>
@@ -3464,10 +3464,10 @@
     <t xml:space="preserve">23.1324863433838</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0597381591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2549476623535</t>
+    <t xml:space="preserve">24.0597362518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2549495697021</t>
   </si>
   <si>
     <t xml:space="preserve">24.3525543212891</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">22.3516426086426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9612216949463</t>
+    <t xml:space="preserve">21.9612197875977</t>
   </si>
   <si>
     <t xml:space="preserve">21.9124183654785</t>
@@ -3488,19 +3488,19 @@
     <t xml:space="preserve">22.3028392791748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5468521118164</t>
+    <t xml:space="preserve">22.546854019165</t>
   </si>
   <si>
     <t xml:space="preserve">22.7908668518066</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4980506896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6932601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6684055328369</t>
+    <t xml:space="preserve">22.4980487823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6932621002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6684036254883</t>
   </si>
   <si>
     <t xml:space="preserve">21.5707988739014</t>
@@ -3524,16 +3524,16 @@
     <t xml:space="preserve">21.4731941223145</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2291812896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0339679718018</t>
+    <t xml:space="preserve">21.2291793823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0339698791504</t>
   </si>
   <si>
     <t xml:space="preserve">21.1803779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0100231170654</t>
+    <t xml:space="preserve">22.0100212097168</t>
   </si>
   <si>
     <t xml:space="preserve">22.107629776001</t>
@@ -3548,7 +3548,7 @@
     <t xml:space="preserve">24.2061443328857</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1821994781494</t>
+    <t xml:space="preserve">25.1821975708008</t>
   </si>
   <si>
     <t xml:space="preserve">26.2558574676514</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">26.0118446350098</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8654365539551</t>
+    <t xml:space="preserve">25.8654384613037</t>
   </si>
   <si>
     <t xml:space="preserve">25.8166351318359</t>
@@ -3575,13 +3575,13 @@
     <t xml:space="preserve">27.0855045318604</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4022674560547</t>
+    <t xml:space="preserve">26.4022655487061</t>
   </si>
   <si>
     <t xml:space="preserve">26.548677444458</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4750156402588</t>
+    <t xml:space="preserve">25.4750175476074</t>
   </si>
   <si>
     <t xml:space="preserve">24.5477638244629</t>
@@ -3590,10 +3590,10 @@
     <t xml:space="preserve">24.88938331604</t>
   </si>
   <si>
-    <t xml:space="preserve">24.157341003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4013557434082</t>
+    <t xml:space="preserve">24.1573429107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4013576507568</t>
   </si>
   <si>
     <t xml:space="preserve">24.7429752349854</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">25.5726222991943</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6702270507812</t>
+    <t xml:space="preserve">25.6702251434326</t>
   </si>
   <si>
     <t xml:space="preserve">25.5238170623779</t>
@@ -4617,6 +4617,9 @@
   </si>
   <si>
     <t xml:space="preserve">45.8499984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4500007629395</t>
   </si>
 </sst>
 </file>
@@ -70215,7 +70218,7 @@
     </row>
     <row r="2511">
       <c r="A2511" s="1" t="n">
-        <v>45974.6911921296</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2511" t="n">
         <v>30827</v>
@@ -70236,6 +70239,32 @@
         <v>1528</v>
       </c>
       <c r="H2511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.691099537</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>37093</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>46.4500007629395</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>46.4500007629395</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>1535</v>
+      </c>
+      <c r="H2512" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="1538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="1539">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6962594985962</t>
+    <t xml:space="preserve">15.6962604522705</t>
   </si>
   <si>
     <t xml:space="preserve">DAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8255243301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3269357681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6344547271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.311297416687</t>
+    <t xml:space="preserve">15.8255224227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3269395828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6344556808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3112964630127</t>
   </si>
   <si>
     <t xml:space="preserve">14.0343036651611</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3851613998413</t>
+    <t xml:space="preserve">14.385160446167</t>
   </si>
   <si>
     <t xml:space="preserve">14.1358680725098</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">13.9604396820068</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1940937042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8801679611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9724979400635</t>
+    <t xml:space="preserve">13.194091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8801670074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9724969863892</t>
   </si>
   <si>
     <t xml:space="preserve">12.3723468780518</t>
@@ -89,43 +89,43 @@
     <t xml:space="preserve">16.0009517669678</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1579151153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4349060058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1948509216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4718437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2289543151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7119026184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5762300491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2133102416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4100370407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0407133102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0499429702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4562005996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2069053649902</t>
+    <t xml:space="preserve">16.1579170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.434907913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1948471069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4718418121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2289581298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7119007110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.576229095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2133140563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4100332260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0407104492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0499439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4561986923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2069063186646</t>
   </si>
   <si>
     <t xml:space="preserve">15.1053447723389</t>
@@ -134,25 +134,25 @@
     <t xml:space="preserve">16.0194187164307</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3425769805908</t>
+    <t xml:space="preserve">16.3425750732422</t>
   </si>
   <si>
     <t xml:space="preserve">16.8780975341797</t>
   </si>
   <si>
-    <t xml:space="preserve">17.035062789917</t>
+    <t xml:space="preserve">17.0350589752197</t>
   </si>
   <si>
     <t xml:space="preserve">17.1735553741455</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0812301635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8226985931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4626083374023</t>
+    <t xml:space="preserve">17.0812225341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.822696685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4626045227051</t>
   </si>
   <si>
     <t xml:space="preserve">16.4533748626709</t>
@@ -170,37 +170,37 @@
     <t xml:space="preserve">17.4228515625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4874820709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5521144866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6472702026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3397541046143</t>
+    <t xml:space="preserve">17.4874801635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.552116394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6472721099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3397521972656</t>
   </si>
   <si>
     <t xml:space="preserve">17.6352119445801</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9888954162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3766822814941</t>
+    <t xml:space="preserve">16.9888935089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3766841888428</t>
   </si>
   <si>
     <t xml:space="preserve">17.5798110961914</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1273918151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3241100311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6657314300537</t>
+    <t xml:space="preserve">17.1273880004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3241119384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.665735244751</t>
   </si>
   <si>
     <t xml:space="preserve">17.0535259246826</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">17.4043827056885</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6842041015625</t>
+    <t xml:space="preserve">16.6842021942139</t>
   </si>
   <si>
     <t xml:space="preserve">16.6380367279053</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">17.2381916046143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6813774108887</t>
+    <t xml:space="preserve">17.6813735961914</t>
   </si>
   <si>
     <t xml:space="preserve">17.7552375793457</t>
@@ -227,46 +227,46 @@
     <t xml:space="preserve">17.5244121551514</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9860687255859</t>
+    <t xml:space="preserve">17.9860668182373</t>
   </si>
   <si>
     <t xml:space="preserve">18.2353610992432</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1430320739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9122047424316</t>
+    <t xml:space="preserve">18.143030166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9122009277344</t>
   </si>
   <si>
     <t xml:space="preserve">17.7183094024658</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4661884307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5308208465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.558521270752</t>
+    <t xml:space="preserve">18.4661903381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.530818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5585231781006</t>
   </si>
   <si>
     <t xml:space="preserve">18.2168960571289</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4477233886719</t>
+    <t xml:space="preserve">18.4477214813232</t>
   </si>
   <si>
     <t xml:space="preserve">18.1522636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0137672424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5890464782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2658882141113</t>
+    <t xml:space="preserve">18.0137691497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5890426635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.26589012146</t>
   </si>
   <si>
     <t xml:space="preserve">17.6075134277344</t>
@@ -275,46 +275,46 @@
     <t xml:space="preserve">17.2843532562256</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1920261383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8873329162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.951961517334</t>
+    <t xml:space="preserve">17.192024230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8873348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9519634246826</t>
   </si>
   <si>
     <t xml:space="preserve">16.6749687194824</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4256782531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2594795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3610439300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8596286773682</t>
+    <t xml:space="preserve">16.4256801605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2594814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3610420227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8596305847168</t>
   </si>
   <si>
     <t xml:space="preserve">16.564172744751</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5272388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2779426574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4782485961914</t>
+    <t xml:space="preserve">16.5272369384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2779445648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4782524108887</t>
   </si>
   <si>
     <t xml:space="preserve">16.6288032531738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6103363037109</t>
+    <t xml:space="preserve">16.6103382110596</t>
   </si>
   <si>
     <t xml:space="preserve">17.3582172393799</t>
@@ -326,43 +326,43 @@
     <t xml:space="preserve">17.1550884246826</t>
   </si>
   <si>
-    <t xml:space="preserve">15.917857170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9547863006592</t>
+    <t xml:space="preserve">15.9178552627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9547891616821</t>
   </si>
   <si>
     <t xml:space="preserve">15.0591773986816</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8652820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1699752807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4377317428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0655860900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0868768692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5513563156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9853134155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6252212524414</t>
+    <t xml:space="preserve">14.8652839660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1699743270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4377336502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0655841827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0868759155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5513572692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9853115081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6252222061157</t>
   </si>
   <si>
     <t xml:space="preserve">14.7821855545044</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5115966796875</t>
+    <t xml:space="preserve">15.5116004943848</t>
   </si>
   <si>
     <t xml:space="preserve">15.1330404281616</t>
@@ -374,37 +374,37 @@
     <t xml:space="preserve">14.0989370346069</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3574619293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7544841766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.502366065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4192676544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.603928565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3546361923218</t>
+    <t xml:space="preserve">14.3574628829956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7544851303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5023651123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4192686080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6039304733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3546342849731</t>
   </si>
   <si>
     <t xml:space="preserve">15.4285020828247</t>
   </si>
   <si>
-    <t xml:space="preserve">15.400803565979</t>
+    <t xml:space="preserve">15.4008016586304</t>
   </si>
   <si>
     <t xml:space="preserve">15.4838981628418</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2502460479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7239599227905</t>
+    <t xml:space="preserve">16.2502479553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7239618301392</t>
   </si>
   <si>
     <t xml:space="preserve">15.4931344985962</t>
@@ -413,28 +413,28 @@
     <t xml:space="preserve">16.2317810058594</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9363241195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1856155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.287181854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1763858795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.093282699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2566547393799</t>
+    <t xml:space="preserve">15.9363203048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1856174468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2871761322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1763820648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0932846069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2566566467285</t>
   </si>
   <si>
     <t xml:space="preserve">16.9242630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.721134185791</t>
+    <t xml:space="preserve">16.7211380004883</t>
   </si>
   <si>
     <t xml:space="preserve">16.7580642700195</t>
@@ -446,19 +446,19 @@
     <t xml:space="preserve">17.2751178741455</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1458587646484</t>
+    <t xml:space="preserve">17.1458568572998</t>
   </si>
   <si>
     <t xml:space="preserve">17.3120517730713</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4505519866943</t>
+    <t xml:space="preserve">17.4505500793457</t>
   </si>
   <si>
     <t xml:space="preserve">16.204080581665</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8901538848877</t>
+    <t xml:space="preserve">15.8901557922363</t>
   </si>
   <si>
     <t xml:space="preserve">15.8624572753906</t>
@@ -467,61 +467,61 @@
     <t xml:space="preserve">15.9270877838135</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0563507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7424249649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7701244354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6685628890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5946960449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7147283554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1394481658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8134651184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1671504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6408615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6500949859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8070611953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4654321670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2623062133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3366184234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4109363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6524572372437</t>
+    <t xml:space="preserve">16.0563526153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7424259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7701234817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6685600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5946969985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7147274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1394519805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8134632110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1671466827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6408624649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6500959396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8070602416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4654359817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2623043060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3366231918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4109354019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.652458190918</t>
   </si>
   <si>
     <t xml:space="preserve">15.7360601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8939800262451</t>
+    <t xml:space="preserve">15.8939771652222</t>
   </si>
   <si>
     <t xml:space="preserve">15.6245861053467</t>
@@ -530,61 +530,61 @@
     <t xml:space="preserve">15.0765199661255</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4295148849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.522406578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5131168365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1601219177246</t>
+    <t xml:space="preserve">15.4295129776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5224056243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131196975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1601247787476</t>
   </si>
   <si>
     <t xml:space="preserve">15.8661079406738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3305721282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9311323165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4945402145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6060066223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.318042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8846883773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0518951416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8382425308228</t>
+    <t xml:space="preserve">16.3305740356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.931134223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4945383071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6060094833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3180418014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.884690284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0518989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8382406234741</t>
   </si>
   <si>
     <t xml:space="preserve">16.5813846588135</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1851921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2595024108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.138744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2223453521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0272693634033</t>
+    <t xml:space="preserve">17.1851863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2595043182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1387424468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2223472595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0272731781006</t>
   </si>
   <si>
     <t xml:space="preserve">16.9529571533203</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">16.4884910583496</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0922966003418</t>
+    <t xml:space="preserve">17.0922946929932</t>
   </si>
   <si>
     <t xml:space="preserve">16.9065113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1666107177734</t>
+    <t xml:space="preserve">17.1666126251221</t>
   </si>
   <si>
     <t xml:space="preserve">17.7425479888916</t>
@@ -608,22 +608,22 @@
     <t xml:space="preserve">17.9004650115967</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9376201629639</t>
+    <t xml:space="preserve">17.9376220703125</t>
   </si>
   <si>
     <t xml:space="preserve">17.8818874359131</t>
   </si>
   <si>
-    <t xml:space="preserve">18.42995262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9037075042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9501533508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5539569854736</t>
+    <t xml:space="preserve">18.4299564361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9037094116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9501552581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.553955078125</t>
   </si>
   <si>
     <t xml:space="preserve">19.6282730102539</t>
@@ -635,19 +635,19 @@
     <t xml:space="preserve">18.9129962921143</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4610652923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3310146331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1823883056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0802040100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8572597503662</t>
+    <t xml:space="preserve">19.461067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3310165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1823844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.080207824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8572616577148</t>
   </si>
   <si>
     <t xml:space="preserve">19.0151805877686</t>
@@ -656,67 +656,67 @@
     <t xml:space="preserve">18.9408664703369</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9315757751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7550811767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5785808563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4020862579346</t>
+    <t xml:space="preserve">18.9315738677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7550792694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5785827636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4020881652832</t>
   </si>
   <si>
     <t xml:space="preserve">18.1141185760498</t>
   </si>
   <si>
-    <t xml:space="preserve">18.457820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5321369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.467113494873</t>
+    <t xml:space="preserve">18.4578227996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5321388244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4671096801758</t>
   </si>
   <si>
     <t xml:space="preserve">18.3742198944092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.485689163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2813262939453</t>
+    <t xml:space="preserve">18.4856910705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2813243865967</t>
   </si>
   <si>
     <t xml:space="preserve">18.3277721405029</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5135593414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6157398223877</t>
+    <t xml:space="preserve">18.513557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6157379150391</t>
   </si>
   <si>
     <t xml:space="preserve">18.6250305175781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7272109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0430469512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4146213531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0894927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.126651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3681735992432</t>
+    <t xml:space="preserve">18.7272129058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0430488586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4146194458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0894947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1266498565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3681755065918</t>
   </si>
   <si>
     <t xml:space="preserve">19.4517765045166</t>
@@ -725,43 +725,43 @@
     <t xml:space="preserve">18.9594421386719</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2474136352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5075130462646</t>
+    <t xml:space="preserve">19.2474098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.507511138916</t>
   </si>
   <si>
     <t xml:space="preserve">19.0987815856934</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2195434570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3495960235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0337562561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2288341522217</t>
+    <t xml:space="preserve">19.2195453643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3495941162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0337581634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2288360595703</t>
   </si>
   <si>
     <t xml:space="preserve">19.3867511749268</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2845726013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9162406921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0091304779053</t>
+    <t xml:space="preserve">19.2845668792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9162425994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0091361999512</t>
   </si>
   <si>
     <t xml:space="preserve">20.3807067871094</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6222305297852</t>
+    <t xml:space="preserve">20.6222286224365</t>
   </si>
   <si>
     <t xml:space="preserve">20.8544597625732</t>
@@ -773,10 +773,10 @@
     <t xml:space="preserve">20.9473533630371</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1484718322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6129341125488</t>
+    <t xml:space="preserve">20.1484699249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6129360198975</t>
   </si>
   <si>
     <t xml:space="preserve">20.3899955749512</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">20.5757808685303</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6500911712646</t>
+    <t xml:space="preserve">20.6500930786133</t>
   </si>
   <si>
     <t xml:space="preserve">20.6036491394043</t>
@@ -797,34 +797,34 @@
     <t xml:space="preserve">20.5014667510986</t>
   </si>
   <si>
-    <t xml:space="preserve">20.529333114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6593818664551</t>
+    <t xml:space="preserve">20.5293350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.659387588501</t>
   </si>
   <si>
     <t xml:space="preserve">20.4828853607178</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8173046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.863748550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.455020904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7801418304443</t>
+    <t xml:space="preserve">20.8173007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8637466430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4550228118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7801475524902</t>
   </si>
   <si>
     <t xml:space="preserve">21.6440486907959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.495418548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3653678894043</t>
+    <t xml:space="preserve">21.4954204559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3653736114502</t>
   </si>
   <si>
     <t xml:space="preserve">21.3189239501953</t>
@@ -836,97 +836,97 @@
     <t xml:space="preserve">21.1238479614258</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9287757873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2724742889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1052684783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.346794128418</t>
+    <t xml:space="preserve">20.9287738800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2724781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1052722930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3467903137207</t>
   </si>
   <si>
     <t xml:space="preserve">21.2260322570801</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6408042907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.170295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9566421508789</t>
+    <t xml:space="preserve">20.6408023834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1702995300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9566402435303</t>
   </si>
   <si>
     <t xml:space="preserve">21.114559173584</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2539005279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.244607925415</t>
+    <t xml:space="preserve">21.2538967132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2446098327637</t>
   </si>
   <si>
     <t xml:space="preserve">21.3375015258789</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2817687988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9380645751953</t>
+    <t xml:space="preserve">21.2817668914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9380626678467</t>
   </si>
   <si>
     <t xml:space="preserve">21.1795825958252</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7336959838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3156833648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3992805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4085750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.32497215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6315174102783</t>
+    <t xml:space="preserve">20.7336978912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3156814575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3992862701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4085712432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3249702453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6315155029297</t>
   </si>
   <si>
     <t xml:space="preserve">20.2785243988037</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0462913513184</t>
+    <t xml:space="preserve">20.046293258667</t>
   </si>
   <si>
     <t xml:space="preserve">20.2134971618652</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7954788208008</t>
+    <t xml:space="preserve">19.7954769134521</t>
   </si>
   <si>
     <t xml:space="preserve">19.9069538116455</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2692317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2971038818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5479125976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4364433288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9533977508545</t>
+    <t xml:space="preserve">20.2692337036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2971019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5479145050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4364395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9533958435059</t>
   </si>
   <si>
     <t xml:space="preserve">19.8326377868652</t>
@@ -938,28 +938,28 @@
     <t xml:space="preserve">19.7211666107178</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9255313873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.074161529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9998455047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1113166809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6747207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6686744689941</t>
+    <t xml:space="preserve">19.9255294799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0741577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9998474121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1113147735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6747188568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6686725616455</t>
   </si>
   <si>
     <t xml:space="preserve">20.2413654327393</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9719772338867</t>
+    <t xml:space="preserve">19.9719753265381</t>
   </si>
   <si>
     <t xml:space="preserve">19.7304553985596</t>
@@ -968,43 +968,43 @@
     <t xml:space="preserve">20.4178638458252</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1298942565918</t>
+    <t xml:space="preserve">20.1298961639404</t>
   </si>
   <si>
     <t xml:space="preserve">20.4921760559082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8451690673828</t>
+    <t xml:space="preserve">20.8451709747314</t>
   </si>
   <si>
     <t xml:space="preserve">20.3435478210449</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5664901733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8916149139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1981620788574</t>
+    <t xml:space="preserve">20.5664882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8916130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1981658935547</t>
   </si>
   <si>
     <t xml:space="preserve">20.7244091033936</t>
   </si>
   <si>
-    <t xml:space="preserve">20.473596572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3342571258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3714179992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8790817260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.841926574707</t>
+    <t xml:space="preserve">20.4735984802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3342590332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3714160919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8790836334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8419284820557</t>
   </si>
   <si>
     <t xml:space="preserve">19.767614364624</t>
@@ -1013,16 +1013,16 @@
     <t xml:space="preserve">19.9812660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">20.092737197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5200424194336</t>
+    <t xml:space="preserve">20.0927352905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5200443267822</t>
   </si>
   <si>
     <t xml:space="preserve">19.9905567169189</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5353832244873</t>
+    <t xml:space="preserve">19.5353813171387</t>
   </si>
   <si>
     <t xml:space="preserve">19.2567005157471</t>
@@ -1031,298 +1031,298 @@
     <t xml:space="preserve">18.7829456329346</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8386821746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6343212127686</t>
+    <t xml:space="preserve">18.8386840820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6343154907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9966049194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6807689666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5600032806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6621875762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4392414093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8108139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1359405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9779300689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9499263763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5298538208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3058166503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9044132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8484039306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6430358886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6710414886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9417514801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8950786590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9697589874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2684783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4645099639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5858631134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4084987640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.16579246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4925136566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3618240356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2218017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6698760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7725658416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.697883605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6885471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6138687133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3524894714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3804950714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4458427429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4831771850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4738445281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6605434417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.707218170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5951976776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3898315429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5018463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9032497406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1833000183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4633502960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7433929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.536865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2836608886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5637092590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5170345306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.377010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6103839874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4703617095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7504062652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7970848083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0036125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4435157775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0502853393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6302165985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7702407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7235660552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0969638824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1903114318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1436367034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8635864257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6768894195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7037334442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.217155456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8904342651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0771312713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9837799072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8169136047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2369861602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3034934997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2101421356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9102592468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5835380554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.956937789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3303375244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3968410491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4901905059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.116792678833</t>
   </si>
   <si>
     <t xml:space="preserve">18.996603012085</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6807670593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5600070953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6621856689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.439245223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8108177185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1359405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9779319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9499282836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5298557281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3058166503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9044132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8484039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6430377960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6710376739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9417533874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8950786590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9697570800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2684764862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4645099639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5858631134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4085006713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.16579246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4925117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3618259429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2218036651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6698799133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7725620269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6978816986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.688549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6138668060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3524913787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3804931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4458408355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4831809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4738464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6605415344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.707218170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5951995849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3898296356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5018482208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9032516479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1833000183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4633502960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7433967590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.536865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2836627960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5637092590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5170345306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3770084381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6103839874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4703578948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7504081726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7970809936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0036106109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4435157775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0502853393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6302127838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7702388763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7235679626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0969619750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1903133392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1436405181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8635883331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6768913269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7037353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2171535491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8904342651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0771293640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9837818145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8169116973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2369861602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3034954071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2101421356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9102630615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5835399627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.956937789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3303375244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3968410491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4901943206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1167945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9966011047363</t>
-  </si>
-  <si>
     <t xml:space="preserve">19.0432758331299</t>
   </si>
   <si>
-    <t xml:space="preserve">19.136625289917</t>
+    <t xml:space="preserve">19.1366271972656</t>
   </si>
   <si>
     <t xml:space="preserve">19.3233242034912</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7900676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6033706665039</t>
+    <t xml:space="preserve">19.7900714874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6033725738525</t>
   </si>
   <si>
     <t xml:space="preserve">20.3501663208008</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2568168640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9767665863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1634674072266</t>
+    <t xml:space="preserve">20.2568206787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.976770401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1634693145752</t>
   </si>
   <si>
     <t xml:space="preserve">20.0234451293945</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8834209442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9300956726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4166717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5566959381104</t>
+    <t xml:space="preserve">19.8834190368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9300975799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4166736602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.556697845459</t>
   </si>
   <si>
     <t xml:space="preserve">19.5100231170654</t>
@@ -1331,46 +1331,46 @@
     <t xml:space="preserve">19.6500453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">19.696720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2766494750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2299728393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3699989318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8367443084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4236869812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0701198577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7177104949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3093004226685</t>
+    <t xml:space="preserve">19.6967220306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.276647567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2299747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3699970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8367462158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4236850738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0701179504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7177124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3093013763428</t>
   </si>
   <si>
     <t xml:space="preserve">15.7013654708862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7678728103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4691572189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8052129745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4026479721069</t>
+    <t xml:space="preserve">14.7678718566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4691553115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.805212020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4026508331299</t>
   </si>
   <si>
     <t xml:space="preserve">15.62668800354</t>
@@ -1379,19 +1379,19 @@
     <t xml:space="preserve">16.0000858306885</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5333385467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3279695510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4586582183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8693971633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7947177886963</t>
+    <t xml:space="preserve">15.5333366394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3279676437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4586601257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8693962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7947149276733</t>
   </si>
   <si>
     <t xml:space="preserve">15.6640281677246</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">15.5893487930298</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3839797973633</t>
+    <t xml:space="preserve">15.3839807510376</t>
   </si>
   <si>
     <t xml:space="preserve">15.0105819702148</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">14.8602876663208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5784883499146</t>
+    <t xml:space="preserve">14.5784873962402</t>
   </si>
   <si>
     <t xml:space="preserve">14.4094076156616</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4469814300537</t>
+    <t xml:space="preserve">14.4469795227051</t>
   </si>
   <si>
     <t xml:space="preserve">14.9166488647461</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">15.1420907974243</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4426774978638</t>
+    <t xml:space="preserve">15.4426765441895</t>
   </si>
   <si>
     <t xml:space="preserve">15.2735958099365</t>
@@ -1439,55 +1439,55 @@
     <t xml:space="preserve">14.0712461471558</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9209537506104</t>
+    <t xml:space="preserve">13.9209518432617</t>
   </si>
   <si>
     <t xml:space="preserve">13.6015777587891</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7330846786499</t>
+    <t xml:space="preserve">13.7330856323242</t>
   </si>
   <si>
     <t xml:space="preserve">14.3342609405518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1651811599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1463937759399</t>
+    <t xml:space="preserve">14.1651802062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1463928222656</t>
   </si>
   <si>
     <t xml:space="preserve">14.2215404510498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9585266113281</t>
+    <t xml:space="preserve">13.9585247039795</t>
   </si>
   <si>
     <t xml:space="preserve">13.6391525268555</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6203641891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7894449234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0524597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2027540206909</t>
+    <t xml:space="preserve">13.6203651428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7894468307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0524606704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2027549743652</t>
   </si>
   <si>
     <t xml:space="preserve">14.5221271514893</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7475690841675</t>
+    <t xml:space="preserve">14.7475681304932</t>
   </si>
   <si>
     <t xml:space="preserve">15.2172374725342</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1233024597168</t>
+    <t xml:space="preserve">15.1233034133911</t>
   </si>
   <si>
     <t xml:space="preserve">15.0293684005737</t>
@@ -1502,79 +1502,79 @@
     <t xml:space="preserve">15.1045160293579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1608753204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1984481811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5366106033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9687061309814</t>
+    <t xml:space="preserve">15.1608762741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.198450088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5366115570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9687032699585</t>
   </si>
   <si>
     <t xml:space="preserve">16.8141059875488</t>
   </si>
   <si>
-    <t xml:space="preserve">16.889253616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9080390930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4947319030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.419584274292</t>
+    <t xml:space="preserve">16.8892517089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9080410003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4947338104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4195861816406</t>
   </si>
   <si>
     <t xml:space="preserve">16.2692928314209</t>
   </si>
   <si>
-    <t xml:space="preserve">16.363224029541</t>
+    <t xml:space="preserve">16.3632259368896</t>
   </si>
   <si>
     <t xml:space="preserve">15.987491607666</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8747701644897</t>
+    <t xml:space="preserve">15.8747682571411</t>
   </si>
   <si>
     <t xml:space="preserve">15.8184108734131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.137788772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1565742492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2505016326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.62624168396</t>
+    <t xml:space="preserve">16.1377849578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1565704345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2505054473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6262397766113</t>
   </si>
   <si>
     <t xml:space="preserve">16.5135192871094</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2880783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4383735656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4571590423584</t>
+    <t xml:space="preserve">16.2880802154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4383716583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.457160949707</t>
   </si>
   <si>
     <t xml:space="preserve">16.2317180633545</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6074523925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7201709747314</t>
+    <t xml:space="preserve">16.6074542999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7201728820801</t>
   </si>
   <si>
     <t xml:space="preserve">16.4759464263916</t>
@@ -1583,10 +1583,10 @@
     <t xml:space="preserve">16.3256511688232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8559827804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9499187469482</t>
+    <t xml:space="preserve">15.8559818267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.949914932251</t>
   </si>
   <si>
     <t xml:space="preserve">15.9311285018921</t>
@@ -1595,22 +1595,22 @@
     <t xml:space="preserve">16.1189956665039</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0062789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3444385528564</t>
+    <t xml:space="preserve">16.0062770843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3444404602051</t>
   </si>
   <si>
     <t xml:space="preserve">16.4007987976074</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5323047637939</t>
+    <t xml:space="preserve">16.5323066711426</t>
   </si>
   <si>
     <t xml:space="preserve">16.7765331268311</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9456157684326</t>
+    <t xml:space="preserve">16.9456119537354</t>
   </si>
   <si>
     <t xml:space="preserve">17.4716396331787</t>
@@ -1619,25 +1619,25 @@
     <t xml:space="preserve">18.279468536377</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2606830596924</t>
+    <t xml:space="preserve">18.260684967041</t>
   </si>
   <si>
     <t xml:space="preserve">18.2418956756592</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1103916168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5279979705811</t>
+    <t xml:space="preserve">18.1103897094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.528003692627</t>
   </si>
   <si>
     <t xml:space="preserve">17.1334800720215</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0019721984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9831848144531</t>
+    <t xml:space="preserve">17.0019702911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9831867218018</t>
   </si>
   <si>
     <t xml:space="preserve">16.7389583587646</t>
@@ -1646,31 +1646,31 @@
     <t xml:space="preserve">16.6450252532959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9643993377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8328914642334</t>
+    <t xml:space="preserve">16.9643974304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8328952789307</t>
   </si>
   <si>
     <t xml:space="preserve">17.0583324432373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1522674560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2274131774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7577457427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2129325866699</t>
+    <t xml:space="preserve">17.1522655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2274150848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7577495574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2129306793213</t>
   </si>
   <si>
     <t xml:space="preserve">15.4990367889404</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5178232192993</t>
+    <t xml:space="preserve">15.517822265625</t>
   </si>
   <si>
     <t xml:space="preserve">15.4614639282227</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">14.6912078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8039293289185</t>
+    <t xml:space="preserve">14.8039283752441</t>
   </si>
   <si>
     <t xml:space="preserve">15.0857286453247</t>
@@ -1691,73 +1691,73 @@
     <t xml:space="preserve">14.7663545608521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9730091094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8415021896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5033416748047</t>
+    <t xml:space="preserve">14.9730081558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8415012359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5033397674561</t>
   </si>
   <si>
     <t xml:space="preserve">14.6724214553833</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3718357086182</t>
+    <t xml:space="preserve">14.3718338012695</t>
   </si>
   <si>
     <t xml:space="preserve">14.822714805603</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5597009658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4657678604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6348485946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5741815567017</t>
+    <t xml:space="preserve">14.559700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4657669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6348476409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5741834640503</t>
   </si>
   <si>
     <t xml:space="preserve">15.4051036834717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3863143920898</t>
+    <t xml:space="preserve">15.3863162994385</t>
   </si>
   <si>
     <t xml:space="preserve">15.6681175231934</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2360229492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5929708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4238891601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3299551010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0481567382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8790760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5409145355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7851419448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6160621643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.296688079834</t>
+    <t xml:space="preserve">15.2360219955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5929689407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4238901138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3299570083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0481548309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.879075050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5409135818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7851409912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6160612106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2966871261597</t>
   </si>
   <si>
     <t xml:space="preserve">14.2779006958008</t>
@@ -1766,64 +1766,64 @@
     <t xml:space="preserve">14.090033531189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9021663665771</t>
+    <t xml:space="preserve">13.9021654129028</t>
   </si>
   <si>
     <t xml:space="preserve">13.7706594467163</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4281930923462</t>
+    <t xml:space="preserve">14.4281940460205</t>
   </si>
   <si>
     <t xml:space="preserve">14.2591142654419</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8082313537598</t>
+    <t xml:space="preserve">13.8082323074341</t>
   </si>
   <si>
     <t xml:space="preserve">13.8458061218262</t>
   </si>
   <si>
-    <t xml:space="preserve">14.033673286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9397401809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2403259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0148878097534</t>
+    <t xml:space="preserve">14.0336723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9397382736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.240327835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0148859024048</t>
   </si>
   <si>
     <t xml:space="preserve">14.5972738265991</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9960994720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3675298690796</t>
+    <t xml:space="preserve">13.9960985183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3675308227539</t>
   </si>
   <si>
     <t xml:space="preserve">14.183967590332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1088209152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4845533370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9917964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2923831939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0758934020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0569305419922</t>
+    <t xml:space="preserve">14.1088199615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4845523834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9917945861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.292384147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0758924484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0569295883179</t>
   </si>
   <si>
     <t xml:space="preserve">14.9052228927612</t>
@@ -1832,79 +1832,79 @@
     <t xml:space="preserve">14.8104057312012</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8862590789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3793067932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6827230453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4602203369141</t>
+    <t xml:space="preserve">14.8862581253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3793077468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6827249526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4602222442627</t>
   </si>
   <si>
     <t xml:space="preserve">16.3274765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7016839981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6637573242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5310134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5499773025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551610946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7585763931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7965030670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1757698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.720648765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6068687438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.64479637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0430278778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9861354827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4172325134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344297409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5689430236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4361972808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5879058837891</t>
+    <t xml:space="preserve">15.7016849517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6637601852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5310144424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5499792098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551601409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7585754394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7965021133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1757678985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7206478118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6068677902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6447944641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.043025970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9861373901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4172344207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344306945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.568941116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4361982345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5879039764404</t>
   </si>
   <si>
     <t xml:space="preserve">15.246563911438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1138200759888</t>
+    <t xml:space="preserve">15.1138191223145</t>
   </si>
   <si>
     <t xml:space="preserve">14.9810771942139</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">14.7535171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9431495666504</t>
+    <t xml:space="preserve">14.9431505203247</t>
   </si>
   <si>
     <t xml:space="preserve">14.5069923400879</t>
@@ -1925,16 +1925,16 @@
     <t xml:space="preserve">14.0329074859619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9380912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2225408554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6018075942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7914438247681</t>
+    <t xml:space="preserve">13.9380893707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.222541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6018085479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7914428710938</t>
   </si>
   <si>
     <t xml:space="preserve">14.5828447341919</t>
@@ -1946,31 +1946,31 @@
     <t xml:space="preserve">14.4311380386353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6207723617554</t>
+    <t xml:space="preserve">14.6207714080811</t>
   </si>
   <si>
     <t xml:space="preserve">14.3363218307495</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2794322967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0518703460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6915664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1416282653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0088834762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3691892623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.08473777771</t>
+    <t xml:space="preserve">14.2794313430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.051869392395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6915655136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1416263580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.008885383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3691902160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0847387313843</t>
   </si>
   <si>
     <t xml:space="preserve">12.8002872467041</t>
@@ -1979,10 +1979,10 @@
     <t xml:space="preserve">12.4210195541382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1744956970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9469356536865</t>
+    <t xml:space="preserve">12.1744947433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9469347000122</t>
   </si>
   <si>
     <t xml:space="preserve">11.4728507995605</t>
@@ -1991,19 +1991,19 @@
     <t xml:space="preserve">11.0366926193237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1264486312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95577907562256</t>
+    <t xml:space="preserve">10.1264505386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95577812194824</t>
   </si>
   <si>
     <t xml:space="preserve">9.59547424316406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91279220581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41532230377197</t>
+    <t xml:space="preserve">8.91279125213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41532325744629</t>
   </si>
   <si>
     <t xml:space="preserve">8.09736728668213</t>
@@ -2015,55 +2015,55 @@
     <t xml:space="preserve">9.10242748260498</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1643753051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7522401809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9279699325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8951044082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6055927276611</t>
+    <t xml:space="preserve">10.1643772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7522420883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9279708862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8951053619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6055936813354</t>
   </si>
   <si>
     <t xml:space="preserve">10.9608392715454</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9229125976562</t>
+    <t xml:space="preserve">10.9229116439819</t>
   </si>
   <si>
     <t xml:space="preserve">10.6384611129761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0695600509644</t>
+    <t xml:space="preserve">10.0695581436157</t>
   </si>
   <si>
     <t xml:space="preserve">10.3350458145142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6194972991943</t>
+    <t xml:space="preserve">10.61949634552</t>
   </si>
   <si>
     <t xml:space="preserve">10.7332773208618</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1125459671021</t>
+    <t xml:space="preserve">11.1125450134277</t>
   </si>
   <si>
     <t xml:space="preserve">10.9039478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5815706253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2023038864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87992477416992</t>
+    <t xml:space="preserve">10.5815696716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2023029327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87992382049561</t>
   </si>
   <si>
     <t xml:space="preserve">10.2212657928467</t>
@@ -2075,58 +2075,58 @@
     <t xml:space="preserve">10.4298639297485</t>
   </si>
   <si>
-    <t xml:space="preserve">10.771203994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7143144607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6953496932983</t>
+    <t xml:space="preserve">10.7712030410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7143154144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6953506469727</t>
   </si>
   <si>
     <t xml:space="preserve">10.8091306686401</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8280944824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5436449050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9987649917603</t>
+    <t xml:space="preserve">10.8280954360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.543643951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9987659454346</t>
   </si>
   <si>
     <t xml:space="preserve">10.9418745040894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491813659668</t>
+    <t xml:space="preserve">11.4918117523193</t>
   </si>
   <si>
     <t xml:space="preserve">11.567666053772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0556535720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4159603118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5107765197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7952270507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0038251876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.288275718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2124214172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0986423492432</t>
+    <t xml:space="preserve">11.0556545257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4159593582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5107774734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7952260971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0038242340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2882747650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2124223709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0986413955688</t>
   </si>
   <si>
     <t xml:space="preserve">11.8521175384521</t>
@@ -2141,25 +2141,25 @@
     <t xml:space="preserve">11.1883993148804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.093581199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8849840164185</t>
+    <t xml:space="preserve">11.0935821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8849849700928</t>
   </si>
   <si>
     <t xml:space="preserve">10.7901678085327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6763887405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4108991622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.448826789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6574249267578</t>
+    <t xml:space="preserve">10.6763877868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4109001159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4488286972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6574230194092</t>
   </si>
   <si>
     <t xml:space="preserve">11.2073612213135</t>
@@ -2171,37 +2171,37 @@
     <t xml:space="preserve">11.2832155227661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0746183395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9798011779785</t>
+    <t xml:space="preserve">11.0746192932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9798021316528</t>
   </si>
   <si>
     <t xml:space="preserve">10.6005353927612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3729734420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4677886962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6435194015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4349231719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6814470291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5297403335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6245565414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5487031936646</t>
+    <t xml:space="preserve">10.3729724884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4677896499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.643518447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4349241256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6814460754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5297393798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6245574951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5487041473389</t>
   </si>
   <si>
     <t xml:space="preserve">11.6624841690063</t>
@@ -2210,13 +2210,13 @@
     <t xml:space="preserve">11.7383375167847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2313861846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.136568069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1176052093506</t>
+    <t xml:space="preserve">12.2313842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1365690231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1176042556763</t>
   </si>
   <si>
     <t xml:space="preserve">11.9658975601196</t>
@@ -2225,22 +2225,22 @@
     <t xml:space="preserve">11.9848613739014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8141899108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7573003768921</t>
+    <t xml:space="preserve">11.814190864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7572994232178</t>
   </si>
   <si>
     <t xml:space="preserve">11.245288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6485795974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.653639793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3881511688232</t>
+    <t xml:space="preserve">12.6485805511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6536388397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3881521224976</t>
   </si>
   <si>
     <t xml:space="preserve">13.8622360229492</t>
@@ -2249,19 +2249,19 @@
     <t xml:space="preserve">13.5967493057251</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2364444732666</t>
+    <t xml:space="preserve">13.2364454269409</t>
   </si>
   <si>
     <t xml:space="preserve">13.4260787963867</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4640054702759</t>
+    <t xml:space="preserve">13.4640045166016</t>
   </si>
   <si>
     <t xml:space="preserve">13.1037006378174</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3312616348267</t>
+    <t xml:space="preserve">13.331262588501</t>
   </si>
   <si>
     <t xml:space="preserve">14.1277227401733</t>
@@ -2270,70 +2270,70 @@
     <t xml:space="preserve">13.7294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4071159362793</t>
+    <t xml:space="preserve">13.407114982605</t>
   </si>
   <si>
     <t xml:space="preserve">13.1226644515991</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4829683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.17955493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0227890014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.060715675354</t>
+    <t xml:space="preserve">13.4829692840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1795539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0227880477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0607147216797</t>
   </si>
   <si>
     <t xml:space="preserve">12.3262014389038</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4399824142456</t>
+    <t xml:space="preserve">12.4399814605713</t>
   </si>
   <si>
     <t xml:space="preserve">12.857177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8192520141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0468111038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3122978210449</t>
+    <t xml:space="preserve">12.8192510604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0468120574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3122987747192</t>
   </si>
   <si>
     <t xml:space="preserve">13.4450426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5588226318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6179904937744</t>
+    <t xml:space="preserve">13.5588216781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6179914474487</t>
   </si>
   <si>
     <t xml:space="preserve">13.6371440887451</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4073047637939</t>
+    <t xml:space="preserve">13.4073057174683</t>
   </si>
   <si>
     <t xml:space="preserve">13.4456119537354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3115386962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5030717849731</t>
+    <t xml:space="preserve">13.3115377426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5030727386475</t>
   </si>
   <si>
     <t xml:space="preserve">13.8478307723999</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8861360549927</t>
+    <t xml:space="preserve">13.886137008667</t>
   </si>
   <si>
     <t xml:space="preserve">13.7520637512207</t>
@@ -2348,25 +2348,25 @@
     <t xml:space="preserve">14.2117443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9819040298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6946048736572</t>
+    <t xml:space="preserve">13.9819049835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6946039199829</t>
   </si>
   <si>
     <t xml:space="preserve">13.4647655487061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7712173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.598837852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5413789749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7903709411621</t>
+    <t xml:space="preserve">13.7712182998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5988368988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5413780212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7903699874878</t>
   </si>
   <si>
     <t xml:space="preserve">13.7137575149536</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">13.8669834136963</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1351289749146</t>
+    <t xml:space="preserve">14.1351299285889</t>
   </si>
   <si>
     <t xml:space="preserve">14.3458156585693</t>
@@ -2384,82 +2384,82 @@
     <t xml:space="preserve">14.7097282409668</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6331148147583</t>
+    <t xml:space="preserve">14.6331157684326</t>
   </si>
   <si>
     <t xml:space="preserve">14.9970273971558</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0353345870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4909858703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3377590179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.184534072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8206195831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9546937942505</t>
+    <t xml:space="preserve">15.0353336334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4909839630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3377571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1845321655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8206214904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9546928405762</t>
   </si>
   <si>
     <t xml:space="preserve">15.8014659881592</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6099348068237</t>
+    <t xml:space="preserve">15.6099328994751</t>
   </si>
   <si>
     <t xml:space="preserve">15.3226337432861</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7440071105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3417892456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4375534057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7248544692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8589248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2611446380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6059036254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.778284072876</t>
+    <t xml:space="preserve">15.7440061569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3417882919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4375553131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7248525619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.858925819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2611427307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6059055328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7782859802246</t>
   </si>
   <si>
     <t xml:space="preserve">16.6825180053711</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6442108154297</t>
+    <t xml:space="preserve">16.6442089080811</t>
   </si>
   <si>
     <t xml:space="preserve">16.7208251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7016716003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1613483428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1421985626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1996555328369</t>
+    <t xml:space="preserve">16.7016735076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1613502502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1421966552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1996574401855</t>
   </si>
   <si>
     <t xml:space="preserve">16.9889698028564</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">16.4526786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4335269927979</t>
+    <t xml:space="preserve">16.4335250854492</t>
   </si>
   <si>
     <t xml:space="preserve">16.9123573303223</t>
@@ -2480,10 +2480,10 @@
     <t xml:space="preserve">16.9506645202637</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9315128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8548965454102</t>
+    <t xml:space="preserve">16.931510925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8548984527588</t>
   </si>
   <si>
     <t xml:space="preserve">17.9657897949219</t>
@@ -2492,16 +2492,16 @@
     <t xml:space="preserve">18.0807075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3105487823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6321239471436</t>
+    <t xml:space="preserve">18.3105506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6321258544922</t>
   </si>
   <si>
     <t xml:space="preserve">19.9194240570068</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3024921417236</t>
+    <t xml:space="preserve">20.302490234375</t>
   </si>
   <si>
     <t xml:space="preserve">19.7757740020752</t>
@@ -2519,10 +2519,10 @@
     <t xml:space="preserve">19.9673080444336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8715400695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0151920318604</t>
+    <t xml:space="preserve">19.8715419769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0151901245117</t>
   </si>
   <si>
     <t xml:space="preserve">20.3982563018799</t>
@@ -2531,25 +2531,25 @@
     <t xml:space="preserve">20.5419063568115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.637674331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9728565216064</t>
+    <t xml:space="preserve">20.6376724243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9728546142578</t>
   </si>
   <si>
     <t xml:space="preserve">20.8770885467529</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3503742218018</t>
+    <t xml:space="preserve">20.3503761291504</t>
   </si>
   <si>
     <t xml:space="preserve">20.0630741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9249725341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7278900146484</t>
+    <t xml:space="preserve">20.9249706268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7278919219971</t>
   </si>
   <si>
     <t xml:space="preserve">19.4884757995605</t>
@@ -2558,28 +2558,28 @@
     <t xml:space="preserve">19.3448276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5363597869873</t>
+    <t xml:space="preserve">19.5363578796387</t>
   </si>
   <si>
     <t xml:space="preserve">19.823657989502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1532917022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2546081542969</t>
+    <t xml:space="preserve">19.1532936096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2546062469482</t>
   </si>
   <si>
     <t xml:space="preserve">20.4461402893066</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2067222595215</t>
+    <t xml:space="preserve">20.2067241668701</t>
   </si>
   <si>
     <t xml:space="preserve">21.1165046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6911029815674</t>
+    <t xml:space="preserve">21.691104888916</t>
   </si>
   <si>
     <t xml:space="preserve">21.3080387115479</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">21.834753036499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5474548339844</t>
+    <t xml:space="preserve">21.5474529266357</t>
   </si>
   <si>
     <t xml:space="preserve">21.8826370239258</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">21.212272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">21.355920791626</t>
+    <t xml:space="preserve">21.3559188842773</t>
   </si>
   <si>
     <t xml:space="preserve">21.4516868591309</t>
@@ -2618,31 +2618,31 @@
     <t xml:space="preserve">22.7924175262451</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3191356658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6487674713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.409351348877</t>
+    <t xml:space="preserve">23.3191337585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6487693786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4093532562256</t>
   </si>
   <si>
     <t xml:space="preserve">22.0262870788574</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6432209014893</t>
+    <t xml:space="preserve">21.6432228088379</t>
   </si>
   <si>
     <t xml:space="preserve">21.4038047790527</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8292064666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.781322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9305210113525</t>
+    <t xml:space="preserve">20.8292083740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7813243865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9305191040039</t>
   </si>
   <si>
     <t xml:space="preserve">24.5162162780762</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">23.4148998260498</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1754837036133</t>
+    <t xml:space="preserve">23.1754856109619</t>
   </si>
   <si>
     <t xml:space="preserve">23.2712497711182</t>
@@ -2669,25 +2669,25 @@
     <t xml:space="preserve">23.22336769104</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7500820159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6064319610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0797176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7979679107666</t>
+    <t xml:space="preserve">23.7500801086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6064338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.079719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.797966003418</t>
   </si>
   <si>
     <t xml:space="preserve">23.7021999359131</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6543159484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.031831741333</t>
+    <t xml:space="preserve">23.654317855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0318355560303</t>
   </si>
   <si>
     <t xml:space="preserve">23.5585517883301</t>
@@ -2696,22 +2696,22 @@
     <t xml:space="preserve">22.8403034210205</t>
   </si>
   <si>
-    <t xml:space="preserve">22.600887298584</t>
+    <t xml:space="preserve">22.6008853912354</t>
   </si>
   <si>
     <t xml:space="preserve">22.2657032012939</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5953369140625</t>
+    <t xml:space="preserve">21.5953388214111</t>
   </si>
   <si>
     <t xml:space="preserve">22.2178211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1699371337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2289142608643</t>
+    <t xml:space="preserve">22.1699352264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2289123535156</t>
   </si>
   <si>
     <t xml:space="preserve">23.8937339782715</t>
@@ -2720,127 +2720,127 @@
     <t xml:space="preserve">24.4683303833008</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0373821258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8458499908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4738807678223</t>
+    <t xml:space="preserve">24.0373840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8458480834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4738788604736</t>
   </si>
   <si>
     <t xml:space="preserve">25.7611789703369</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1442451477051</t>
+    <t xml:space="preserve">26.1442413330078</t>
   </si>
   <si>
     <t xml:space="preserve">25.8569450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8090648651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9527111053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.665412902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4794254302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5751934051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4849739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3892097473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3413257598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8680400848389</t>
+    <t xml:space="preserve">25.8090629577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9527130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6654109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4794273376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.484977722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3892078399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3413238525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8680419921875</t>
   </si>
   <si>
     <t xml:space="preserve">28.4905242919922</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9638080596924</t>
+    <t xml:space="preserve">27.963809967041</t>
   </si>
   <si>
     <t xml:space="preserve">28.2989902496338</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7722721099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6286239624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7243938446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5328578948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2455596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9582614898682</t>
+    <t xml:space="preserve">27.772274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.628625869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7243919372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5328598022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2455615997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9582576751709</t>
   </si>
   <si>
     <t xml:space="preserve">27.1497917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0540256500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.718843460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9287757873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2543525695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8207931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4354095458984</t>
+    <t xml:space="preserve">27.054027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7188415527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9287776947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2543506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8207950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4354057312012</t>
   </si>
   <si>
     <t xml:space="preserve">24.5682926177979</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7128105163574</t>
+    <t xml:space="preserve">24.7128124237061</t>
   </si>
   <si>
     <t xml:space="preserve">24.1347351074219</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7609844207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6646404266357</t>
+    <t xml:space="preserve">24.760986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6646385192871</t>
   </si>
   <si>
     <t xml:space="preserve">25.0981960296631</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3988723754883</t>
+    <t xml:space="preserve">26.3988704681396</t>
   </si>
   <si>
     <t xml:space="preserve">26.8324298858643</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4470443725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9171409606934</t>
+    <t xml:space="preserve">26.4470462799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9171390533447</t>
   </si>
   <si>
     <t xml:space="preserve">25.8689670562744</t>
@@ -2849,10 +2849,10 @@
     <t xml:space="preserve">25.4835815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7244472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1463718414307</t>
+    <t xml:space="preserve">25.7244491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.146369934082</t>
   </si>
   <si>
     <t xml:space="preserve">25.579927444458</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">25.9653129577637</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1580066680908</t>
+    <t xml:space="preserve">26.1580047607422</t>
   </si>
   <si>
     <t xml:space="preserve">25.628101348877</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">24.8573303222656</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6762752532959</t>
+    <t xml:space="preserve">25.6762733459473</t>
   </si>
   <si>
     <t xml:space="preserve">25.5317535400391</t>
@@ -2894,34 +2894,34 @@
     <t xml:space="preserve">22.7858867645264</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6530017852783</t>
+    <t xml:space="preserve">23.653003692627</t>
   </si>
   <si>
     <t xml:space="preserve">23.0267524719238</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9304046630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.219446182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4121360778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.448673248291</t>
+    <t xml:space="preserve">22.9304065704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2194442749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4121379852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4486751556396</t>
   </si>
   <si>
     <t xml:space="preserve">21.9669437408447</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8224239349365</t>
+    <t xml:space="preserve">21.8224258422852</t>
   </si>
   <si>
     <t xml:space="preserve">21.5815582275391</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6413669586182</t>
+    <t xml:space="preserve">22.6413650512695</t>
   </si>
   <si>
     <t xml:space="preserve">22.8340606689453</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">22.4968490600586</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1114616394043</t>
+    <t xml:space="preserve">22.1114635467529</t>
   </si>
   <si>
     <t xml:space="preserve">23.1712703704834</t>
@@ -2939,10 +2939,10 @@
     <t xml:space="preserve">22.1596355438232</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0632915496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3888664245605</t>
+    <t xml:space="preserve">22.063289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3888683319092</t>
   </si>
   <si>
     <t xml:space="preserve">21.1480007171631</t>
@@ -2951,13 +2951,13 @@
     <t xml:space="preserve">20.52174949646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5101127624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1845378875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9436740875244</t>
+    <t xml:space="preserve">19.5101146697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1845397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9436721801758</t>
   </si>
   <si>
     <t xml:space="preserve">18.9609413146973</t>
@@ -2966,34 +2966,34 @@
     <t xml:space="preserve">19.1536331176758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1323623657227</t>
+    <t xml:space="preserve">18.1323642730713</t>
   </si>
   <si>
     <t xml:space="preserve">16.8991317749023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9569396972656</t>
+    <t xml:space="preserve">16.9569416046143</t>
   </si>
   <si>
     <t xml:space="preserve">18.0167484283447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.15163230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5542850494385</t>
+    <t xml:space="preserve">18.1516304016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5542869567871</t>
   </si>
   <si>
     <t xml:space="preserve">18.3057861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8433265686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4964771270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6719017028809</t>
+    <t xml:space="preserve">17.8433246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4964790344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6719036102295</t>
   </si>
   <si>
     <t xml:space="preserve">18.2672462463379</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">18.6911716461182</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3828639984131</t>
+    <t xml:space="preserve">18.3828620910645</t>
   </si>
   <si>
     <t xml:space="preserve">18.7682476043701</t>
@@ -3017,22 +3017,22 @@
     <t xml:space="preserve">19.1921730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6064624786377</t>
+    <t xml:space="preserve">19.6064605712891</t>
   </si>
   <si>
     <t xml:space="preserve">19.1150951385498</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2114410400391</t>
+    <t xml:space="preserve">19.2114429473877</t>
   </si>
   <si>
     <t xml:space="preserve">18.6333637237549</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7662487030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6526336669922</t>
+    <t xml:space="preserve">17.7662467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6526355743408</t>
   </si>
   <si>
     <t xml:space="preserve">18.4021339416504</t>
@@ -3044,10 +3044,10 @@
     <t xml:space="preserve">19.4137687683105</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7509784698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1343650817871</t>
+    <t xml:space="preserve">19.7509822845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1343669891357</t>
   </si>
   <si>
     <t xml:space="preserve">18.7489776611328</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">18.9224014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3655967712402</t>
+    <t xml:space="preserve">19.3655948638916</t>
   </si>
   <si>
     <t xml:space="preserve">19.2692489624023</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">18.0938262939453</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7991523742676</t>
+    <t xml:space="preserve">19.7991542816162</t>
   </si>
   <si>
     <t xml:space="preserve">20.040018081665</t>
@@ -3083,13 +3083,13 @@
     <t xml:space="preserve">20.7144432067871</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0516548156738</t>
+    <t xml:space="preserve">21.0516529083252</t>
   </si>
   <si>
     <t xml:space="preserve">21.4852123260498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4370384216309</t>
+    <t xml:space="preserve">21.4370403289795</t>
   </si>
   <si>
     <t xml:space="preserve">21.8705978393555</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">20.8107891082764</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8955001831055</t>
+    <t xml:space="preserve">19.8954982757568</t>
   </si>
   <si>
     <t xml:space="preserve">20.2327117919922</t>
@@ -3125,10 +3125,10 @@
     <t xml:space="preserve">20.4735774993896</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8473262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.249979019165</t>
+    <t xml:space="preserve">19.8473243713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2499809265137</t>
   </si>
   <si>
     <t xml:space="preserve">18.7875175476074</t>
@@ -3137,28 +3137,28 @@
     <t xml:space="preserve">18.5948257446289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5735530853271</t>
+    <t xml:space="preserve">17.5735569000244</t>
   </si>
   <si>
     <t xml:space="preserve">18.8067874908447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.498477935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2287101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0745544433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5562858581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7104415893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9416732788086</t>
+    <t xml:space="preserve">18.4984798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2287082672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.074556350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5562877655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7104396820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.94167137146</t>
   </si>
   <si>
     <t xml:space="preserve">18.5370178222656</t>
@@ -3167,25 +3167,25 @@
     <t xml:space="preserve">18.4406719207764</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2865161895752</t>
+    <t xml:space="preserve">18.2865180969238</t>
   </si>
   <si>
     <t xml:space="preserve">17.9782104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5755558013916</t>
+    <t xml:space="preserve">18.5755577087402</t>
   </si>
   <si>
     <t xml:space="preserve">19.3174209594727</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8453254699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9802093505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4619426727295</t>
+    <t xml:space="preserve">18.8453235626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9802112579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4619407653809</t>
   </si>
   <si>
     <t xml:space="preserve">18.1709022521973</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">17.9204025268555</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6313629150391</t>
+    <t xml:space="preserve">17.6313610076904</t>
   </si>
   <si>
     <t xml:space="preserve">18.2094402313232</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">18.2479782104492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6699028015137</t>
+    <t xml:space="preserve">17.669900894165</t>
   </si>
   <si>
     <t xml:space="preserve">17.3423252105713</t>
@@ -3215,40 +3215,40 @@
     <t xml:space="preserve">16.6293621063232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9934787750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4559383392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2054386138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0512847900391</t>
+    <t xml:space="preserve">15.9934778213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.455940246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.205436706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0512828826904</t>
   </si>
   <si>
     <t xml:space="preserve">16.2247085571289</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4153985977173</t>
+    <t xml:space="preserve">15.4153995513916</t>
   </si>
   <si>
     <t xml:space="preserve">15.5502834320068</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3575916290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7257080078125</t>
+    <t xml:space="preserve">15.357590675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7257099151611</t>
   </si>
   <si>
     <t xml:space="preserve">16.128360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7642478942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.879861831665</t>
+    <t xml:space="preserve">16.7642459869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8798637390137</t>
   </si>
   <si>
     <t xml:space="preserve">17.1110935211182</t>
@@ -3260,10 +3260,10 @@
     <t xml:space="preserve">17.2459774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1689014434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1303634643555</t>
+    <t xml:space="preserve">17.1688995361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1303615570068</t>
   </si>
   <si>
     <t xml:space="preserve">17.9589405059814</t>
@@ -3308,13 +3308,13 @@
     <t xml:space="preserve">20.8875617980957</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7411518096924</t>
+    <t xml:space="preserve">20.741153717041</t>
   </si>
   <si>
     <t xml:space="preserve">20.6435470581055</t>
   </si>
   <si>
-    <t xml:space="preserve">20.448335647583</t>
+    <t xml:space="preserve">20.4483375549316</t>
   </si>
   <si>
     <t xml:space="preserve">20.6923503875732</t>
@@ -3323,13 +3323,13 @@
     <t xml:space="preserve">20.5947437286377</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5459423065186</t>
+    <t xml:space="preserve">20.5459403991699</t>
   </si>
   <si>
     <t xml:space="preserve">20.3019275665283</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3267860412598</t>
+    <t xml:space="preserve">21.3267841339111</t>
   </si>
   <si>
     <t xml:space="preserve">20.4971389770508</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">20.1555194854736</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1067180633545</t>
+    <t xml:space="preserve">20.1067161560059</t>
   </si>
   <si>
     <t xml:space="preserve">20.2531261444092</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">21.0827713012695</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7660102844238</t>
+    <t xml:space="preserve">21.7660083770752</t>
   </si>
   <si>
     <t xml:space="preserve">21.8636150360107</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">22.5956554412842</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9372749328613</t>
+    <t xml:space="preserve">22.9372730255127</t>
   </si>
   <si>
     <t xml:space="preserve">23.083683013916</t>
@@ -3395,10 +3395,10 @@
     <t xml:space="preserve">23.4741039276123</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2300891876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7181167602539</t>
+    <t xml:space="preserve">23.2300910949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7181186676025</t>
   </si>
   <si>
     <t xml:space="preserve">23.6693153381348</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">23.6205139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7669219970703</t>
+    <t xml:space="preserve">23.7669200897217</t>
   </si>
   <si>
     <t xml:space="preserve">23.8645267486572</t>
@@ -3416,22 +3416,22 @@
     <t xml:space="preserve">23.2788944244385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3276977539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9621295928955</t>
+    <t xml:space="preserve">23.3276958465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9621315002441</t>
   </si>
   <si>
     <t xml:space="preserve">24.6941719055176</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3286075592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9869899749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7917766571045</t>
+    <t xml:space="preserve">25.3286094665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.986988067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7917785644531</t>
   </si>
   <si>
     <t xml:space="preserve">24.4989624023438</t>
@@ -3440,25 +3440,25 @@
     <t xml:space="preserve">24.5965671539307</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4501571655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3037490844727</t>
+    <t xml:space="preserve">24.450159072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3037509918213</t>
   </si>
   <si>
     <t xml:space="preserve">24.0109348297119</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7420616149902</t>
+    <t xml:space="preserve">22.7420635223389</t>
   </si>
   <si>
     <t xml:space="preserve">22.644458770752</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1812896728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8884716033936</t>
+    <t xml:space="preserve">23.1812877655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8884735107422</t>
   </si>
   <si>
     <t xml:space="preserve">23.0348796844482</t>
@@ -3467,10 +3467,10 @@
     <t xml:space="preserve">23.1324863433838</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0597362518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2549495697021</t>
+    <t xml:space="preserve">24.0597381591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2549476623535</t>
   </si>
   <si>
     <t xml:space="preserve">24.3525543212891</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">22.3516426086426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9612197875977</t>
+    <t xml:space="preserve">21.9612216949463</t>
   </si>
   <si>
     <t xml:space="preserve">21.9124183654785</t>
@@ -3491,19 +3491,19 @@
     <t xml:space="preserve">22.3028392791748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.546854019165</t>
+    <t xml:space="preserve">22.5468521118164</t>
   </si>
   <si>
     <t xml:space="preserve">22.7908668518066</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4980487823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6932621002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6684036254883</t>
+    <t xml:space="preserve">22.4980506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6932601928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6684055328369</t>
   </si>
   <si>
     <t xml:space="preserve">21.5707988739014</t>
@@ -3527,16 +3527,16 @@
     <t xml:space="preserve">21.4731941223145</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2291793823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0339698791504</t>
+    <t xml:space="preserve">21.2291812896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0339679718018</t>
   </si>
   <si>
     <t xml:space="preserve">21.1803779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0100212097168</t>
+    <t xml:space="preserve">22.0100231170654</t>
   </si>
   <si>
     <t xml:space="preserve">22.107629776001</t>
@@ -3551,7 +3551,7 @@
     <t xml:space="preserve">24.2061443328857</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1821975708008</t>
+    <t xml:space="preserve">25.1821994781494</t>
   </si>
   <si>
     <t xml:space="preserve">26.2558574676514</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">26.0118446350098</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8654384613037</t>
+    <t xml:space="preserve">25.8654365539551</t>
   </si>
   <si>
     <t xml:space="preserve">25.8166351318359</t>
@@ -3578,13 +3578,13 @@
     <t xml:space="preserve">27.0855045318604</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4022655487061</t>
+    <t xml:space="preserve">26.4022674560547</t>
   </si>
   <si>
     <t xml:space="preserve">26.548677444458</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4750175476074</t>
+    <t xml:space="preserve">25.4750156402588</t>
   </si>
   <si>
     <t xml:space="preserve">24.5477638244629</t>
@@ -3593,10 +3593,10 @@
     <t xml:space="preserve">24.88938331604</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1573429107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4013576507568</t>
+    <t xml:space="preserve">24.157341003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4013557434082</t>
   </si>
   <si>
     <t xml:space="preserve">24.7429752349854</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">25.5726222991943</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6702251434326</t>
+    <t xml:space="preserve">25.6702270507812</t>
   </si>
   <si>
     <t xml:space="preserve">25.5238170623779</t>
@@ -4626,6 +4626,9 @@
   </si>
   <si>
     <t xml:space="preserve">45.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0499992370605</t>
   </si>
 </sst>
 </file>
@@ -70276,7 +70279,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6912384259</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>31299</v>
@@ -70297,6 +70300,32 @@
         <v>1537</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.691099537</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>42139</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>45.1500015258789</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>44.2999992370605</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>44.5499992370605</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>45.0499992370605</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>1538</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -44,37 +44,37 @@
     <t xml:space="preserve">DAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8255214691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3269367218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6344566345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.311297416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0343036651611</t>
+    <t xml:space="preserve">15.8255233764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3269386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6344537734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3112964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0343027114868</t>
   </si>
   <si>
     <t xml:space="preserve">14.3851613998413</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1358690261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9604387283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1940927505493</t>
+    <t xml:space="preserve">14.1358680725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9604406356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.194091796875</t>
   </si>
   <si>
     <t xml:space="preserve">12.8801670074463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9724979400635</t>
+    <t xml:space="preserve">12.9724969863892</t>
   </si>
   <si>
     <t xml:space="preserve">12.3723468780518</t>
@@ -83,61 +83,61 @@
     <t xml:space="preserve">13.0371294021606</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2217922210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.000955581665</t>
+    <t xml:space="preserve">13.2217903137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0009517669678</t>
   </si>
   <si>
     <t xml:space="preserve">16.1579170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4349098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1948471069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4718379974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2289543151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7118988037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5762319564819</t>
+    <t xml:space="preserve">16.4349117279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1948490142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4718418121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2289562225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7119007110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5762310028076</t>
   </si>
   <si>
     <t xml:space="preserve">16.2133140563965</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4100360870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0407123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0499448776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4562005996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2069072723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1053409576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0194206237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3425750732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8780994415283</t>
+    <t xml:space="preserve">15.4100351333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0407114028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0499439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4561996459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2069053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1053428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.019416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3425769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8781032562256</t>
   </si>
   <si>
     <t xml:space="preserve">17.0350608825684</t>
@@ -146,25 +146,25 @@
     <t xml:space="preserve">17.1735553741455</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0812244415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8226947784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4626083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4533767700195</t>
+    <t xml:space="preserve">17.0812225341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8226985931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4626064300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4533748626709</t>
   </si>
   <si>
     <t xml:space="preserve">16.9427299499512</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7488307952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.293586730957</t>
+    <t xml:space="preserve">16.7488327026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2935848236084</t>
   </si>
   <si>
     <t xml:space="preserve">17.4228496551514</t>
@@ -173,73 +173,73 @@
     <t xml:space="preserve">17.4874820709229</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5521144866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6472682952881</t>
+    <t xml:space="preserve">17.5521125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6472702026367</t>
   </si>
   <si>
     <t xml:space="preserve">17.3397541046143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6352119445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9888954162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3766841888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.57981300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1273899078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3241100311279</t>
+    <t xml:space="preserve">17.6352100372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9888935089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3766860961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5798091888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1273918151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3241138458252</t>
   </si>
   <si>
     <t xml:space="preserve">16.6657333374023</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0535259246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4043827056885</t>
+    <t xml:space="preserve">17.053524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4043846130371</t>
   </si>
   <si>
     <t xml:space="preserve">16.6842021942139</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6380405426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2381896972656</t>
+    <t xml:space="preserve">16.6380386352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.238187789917</t>
   </si>
   <si>
     <t xml:space="preserve">17.68137550354</t>
   </si>
   <si>
-    <t xml:space="preserve">17.755241394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5244102478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9860687255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2353630065918</t>
+    <t xml:space="preserve">17.7552394866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9860668182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2353610992432</t>
   </si>
   <si>
     <t xml:space="preserve">18.143030166626</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9122009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7183094024658</t>
+    <t xml:space="preserve">17.912202835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7183074951172</t>
   </si>
   <si>
     <t xml:space="preserve">18.4661903381348</t>
@@ -248,34 +248,34 @@
     <t xml:space="preserve">18.5308208465576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5585193634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2168960571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4477252960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1522674560547</t>
+    <t xml:space="preserve">18.558521270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2168941497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4477233886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1522636413574</t>
   </si>
   <si>
     <t xml:space="preserve">18.0137691497803</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5890464782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2658863067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6075134277344</t>
+    <t xml:space="preserve">17.5890426635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2658882141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6075115203857</t>
   </si>
   <si>
     <t xml:space="preserve">17.2843532562256</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1920223236084</t>
+    <t xml:space="preserve">17.192024230957</t>
   </si>
   <si>
     <t xml:space="preserve">16.8873310089111</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">16.9519634246826</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6749706268311</t>
+    <t xml:space="preserve">16.6749687194824</t>
   </si>
   <si>
     <t xml:space="preserve">16.4256782531738</t>
@@ -296,19 +296,19 @@
     <t xml:space="preserve">16.3610439300537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8596324920654</t>
+    <t xml:space="preserve">16.8596343994141</t>
   </si>
   <si>
     <t xml:space="preserve">16.5641708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5272388458252</t>
+    <t xml:space="preserve">16.5272407531738</t>
   </si>
   <si>
     <t xml:space="preserve">16.2779445648193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4782485961914</t>
+    <t xml:space="preserve">17.4782524108887</t>
   </si>
   <si>
     <t xml:space="preserve">16.6288051605225</t>
@@ -323,97 +323,97 @@
     <t xml:space="preserve">17.1089267730713</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1550903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9178533554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9547910690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.059178352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8652820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1699743270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4377326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0655841827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.086874961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5513553619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9853105545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.62522315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7821855545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5115985870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1330413818359</t>
+    <t xml:space="preserve">17.1550884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.917857170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9547872543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0591764450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8652830123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1699733734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4377346038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0655822753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0868759155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5513572692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.985312461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6252222061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7821846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5115995407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1330423355103</t>
   </si>
   <si>
     <t xml:space="preserve">14.7267866134644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0989351272583</t>
+    <t xml:space="preserve">14.0989360809326</t>
   </si>
   <si>
     <t xml:space="preserve">14.357460975647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7544832229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5023698806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4192695617676</t>
+    <t xml:space="preserve">14.7544851303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5023679733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4192667007446</t>
   </si>
   <si>
     <t xml:space="preserve">15.6039304733276</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3546333312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4285011291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.400803565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4839000701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2502479553223</t>
+    <t xml:space="preserve">15.3546342849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4284992218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4008045196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4839019775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2502460479736</t>
   </si>
   <si>
     <t xml:space="preserve">15.7239599227905</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4931325912476</t>
+    <t xml:space="preserve">15.4931335449219</t>
   </si>
   <si>
     <t xml:space="preserve">16.2317810058594</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9363241195679</t>
+    <t xml:space="preserve">15.9363222122192</t>
   </si>
   <si>
     <t xml:space="preserve">16.1856174468994</t>
@@ -431,178 +431,178 @@
     <t xml:space="preserve">17.2566528320312</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9242610931396</t>
+    <t xml:space="preserve">16.9242630004883</t>
   </si>
   <si>
     <t xml:space="preserve">16.721134185791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7580661773682</t>
+    <t xml:space="preserve">16.7580680847168</t>
   </si>
   <si>
     <t xml:space="preserve">17.7275447845459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2751178741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1458549499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3120555877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4505500793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2040824890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8901557922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8624563217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9270896911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0563507080078</t>
+    <t xml:space="preserve">17.2751197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1458587646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3120517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4505481719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.204080581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8901538848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8624572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270877838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0563526153564</t>
   </si>
   <si>
     <t xml:space="preserve">15.7424249649048</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7701292037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6685590744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5946979522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7147274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1394500732422</t>
+    <t xml:space="preserve">15.7701263427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6685628890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5946950912476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.714729309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1394481658936</t>
   </si>
   <si>
     <t xml:space="preserve">16.8134651184082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1671485900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6408643722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6500940322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8070573806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4654331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2623043060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3366212844849</t>
+    <t xml:space="preserve">16.1671504974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6408624649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6500968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8070583343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4654340744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2623052597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3366203308105</t>
   </si>
   <si>
     <t xml:space="preserve">15.4109363555908</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6524543762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7360591888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8939800262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6245880126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0765199661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4295139312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.522406578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5131158828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1601219177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8661127090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3305759429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9311351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4945392608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6060085296631</t>
+    <t xml:space="preserve">15.652455329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7360610961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8939771652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.624587059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0765190124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4295129776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5224046707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131168365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1601228713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8661117553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3305740356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9311361312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4945402145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6060094833374</t>
   </si>
   <si>
     <t xml:space="preserve">15.3180418014526</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8846874237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0518989562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8382406234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5813846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.185188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2595024108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.138744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2223453521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0272731781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9529590606689</t>
+    <t xml:space="preserve">15.884690284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0518970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8382396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5813884735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1851863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2595043182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1387424468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2223472595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.027271270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9529571533203</t>
   </si>
   <si>
     <t xml:space="preserve">16.4884910583496</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0922966003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9065132141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1666107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7425479888916</t>
+    <t xml:space="preserve">17.0922946929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9065113067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1666088104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.742546081543</t>
   </si>
   <si>
     <t xml:space="preserve">17.9004650115967</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">17.9376201629639</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8818874359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4299545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9037094116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9501533508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.553955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6282711029053</t>
+    <t xml:space="preserve">17.8818836212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4299564361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9037075042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9501552581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5539569854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6282730102539</t>
   </si>
   <si>
     <t xml:space="preserve">19.1173610687256</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">19.4610652923584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3310165405273</t>
+    <t xml:space="preserve">19.3310127258301</t>
   </si>
   <si>
     <t xml:space="preserve">19.1823863983154</t>
@@ -647,55 +647,55 @@
     <t xml:space="preserve">19.0802059173584</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8572616577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0151767730713</t>
+    <t xml:space="preserve">18.8572597503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0151786804199</t>
   </si>
   <si>
     <t xml:space="preserve">18.9408645629883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9315738677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7550811767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5785827636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4020862579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1141204833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4578227996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5321388244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4671115875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3742179870605</t>
+    <t xml:space="preserve">18.9315757751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7550830841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5785846710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4020824432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1141166687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.457820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5321369171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.467113494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3742198944092</t>
   </si>
   <si>
     <t xml:space="preserve">18.4856929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2813262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3277702331543</t>
+    <t xml:space="preserve">18.2813243865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3277683258057</t>
   </si>
   <si>
     <t xml:space="preserve">18.5135593414307</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6157417297363</t>
+    <t xml:space="preserve">18.6157379150391</t>
   </si>
   <si>
     <t xml:space="preserve">18.6250286102295</t>
@@ -707,82 +707,82 @@
     <t xml:space="preserve">19.0430469512939</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4146194458008</t>
+    <t xml:space="preserve">19.4146213531494</t>
   </si>
   <si>
     <t xml:space="preserve">19.0894947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1266536712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3681735992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4517784118652</t>
+    <t xml:space="preserve">19.126651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3681716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4517765045166</t>
   </si>
   <si>
     <t xml:space="preserve">18.9594440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2474117279053</t>
+    <t xml:space="preserve">19.2474098205566</t>
   </si>
   <si>
     <t xml:space="preserve">19.507511138916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.098783493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2195434570312</t>
+    <t xml:space="preserve">19.0987815856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2195453643799</t>
   </si>
   <si>
     <t xml:space="preserve">19.3495922088623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0337581634521</t>
+    <t xml:space="preserve">19.0337600708008</t>
   </si>
   <si>
     <t xml:space="preserve">19.2288341522217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3867530822754</t>
+    <t xml:space="preserve">19.3867511749268</t>
   </si>
   <si>
     <t xml:space="preserve">19.2845706939697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9162445068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0091342926025</t>
+    <t xml:space="preserve">19.9162406921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0091361999512</t>
   </si>
   <si>
     <t xml:space="preserve">20.3807048797607</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6222248077393</t>
+    <t xml:space="preserve">20.6222267150879</t>
   </si>
   <si>
     <t xml:space="preserve">20.8544597625732</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9659328460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9473495483398</t>
+    <t xml:space="preserve">20.9659290313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9473533630371</t>
   </si>
   <si>
     <t xml:space="preserve">20.148473739624</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6129417419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3899936676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2506542205811</t>
+    <t xml:space="preserve">20.6129398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3899955749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2506561279297</t>
   </si>
   <si>
     <t xml:space="preserve">20.5757808685303</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">20.6500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6036491394043</t>
+    <t xml:space="preserve">20.6036472320557</t>
   </si>
   <si>
     <t xml:space="preserve">20.50146484375</t>
@@ -800,19 +800,19 @@
     <t xml:space="preserve">20.529333114624</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6593856811523</t>
+    <t xml:space="preserve">20.659387588501</t>
   </si>
   <si>
     <t xml:space="preserve">20.4828853607178</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8173027038574</t>
+    <t xml:space="preserve">20.8173007965088</t>
   </si>
   <si>
     <t xml:space="preserve">20.863748550415</t>
   </si>
   <si>
-    <t xml:space="preserve">20.455020904541</t>
+    <t xml:space="preserve">20.4550228118896</t>
   </si>
   <si>
     <t xml:space="preserve">20.7801475524902</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">21.6440505981445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4954223632812</t>
+    <t xml:space="preserve">21.495418548584</t>
   </si>
   <si>
     <t xml:space="preserve">21.3653697967529</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">21.3189239501953</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1331367492676</t>
+    <t xml:space="preserve">21.1331386566162</t>
   </si>
   <si>
     <t xml:space="preserve">21.1238479614258</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">20.9287757873535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2724761962891</t>
+    <t xml:space="preserve">21.2724800109863</t>
   </si>
   <si>
     <t xml:space="preserve">21.1052684783936</t>
@@ -851,46 +851,46 @@
     <t xml:space="preserve">21.2260284423828</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6408061981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1702976226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9566421508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.114559173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2539005279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.244607925415</t>
+    <t xml:space="preserve">20.6408042907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.170295715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9566402435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1145629882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2538986206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2446098327637</t>
   </si>
   <si>
     <t xml:space="preserve">21.3375015258789</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2817649841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9380664825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1795825958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.733699798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3156814575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3992805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4085750579834</t>
+    <t xml:space="preserve">21.2817668914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9380645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1795845031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7336978912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3156795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3992824554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4085731506348</t>
   </si>
   <si>
     <t xml:space="preserve">20.3249702453613</t>
@@ -899,16 +899,16 @@
     <t xml:space="preserve">20.6315135955811</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2785224914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0462913513184</t>
+    <t xml:space="preserve">20.2785205841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0462894439697</t>
   </si>
   <si>
     <t xml:space="preserve">20.2134990692139</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7954807281494</t>
+    <t xml:space="preserve">19.7954769134521</t>
   </si>
   <si>
     <t xml:space="preserve">19.9069499969482</t>
@@ -923,67 +923,67 @@
     <t xml:space="preserve">20.5479125976562</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4364395141602</t>
+    <t xml:space="preserve">20.4364414215088</t>
   </si>
   <si>
     <t xml:space="preserve">19.9533977508545</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8326377868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8883743286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7211647033691</t>
+    <t xml:space="preserve">19.832633972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8883724212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7211666107178</t>
   </si>
   <si>
     <t xml:space="preserve">19.9255313873291</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0741596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9998455047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1113166809082</t>
+    <t xml:space="preserve">20.0741577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9998435974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1113147735596</t>
   </si>
   <si>
     <t xml:space="preserve">19.6747188568115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6686706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2413673400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9719791412354</t>
+    <t xml:space="preserve">20.6686744689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2413654327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.971981048584</t>
   </si>
   <si>
     <t xml:space="preserve">19.7304573059082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4178619384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1298961639404</t>
+    <t xml:space="preserve">20.4178638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1298980712891</t>
   </si>
   <si>
     <t xml:space="preserve">20.4921760559082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8451728820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3435478210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5664920806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8916187286377</t>
+    <t xml:space="preserve">20.8451690673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3435497283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5664882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8916149139404</t>
   </si>
   <si>
     <t xml:space="preserve">21.1981620788574</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">20.7244091033936</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4736003875732</t>
+    <t xml:space="preserve">20.4736022949219</t>
   </si>
   <si>
     <t xml:space="preserve">20.3342590332031</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">20.3714179992676</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8790836334229</t>
+    <t xml:space="preserve">19.8790817260742</t>
   </si>
   <si>
     <t xml:space="preserve">19.8419284820557</t>
@@ -1013,16 +1013,16 @@
     <t xml:space="preserve">19.9812660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">20.092737197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5200462341309</t>
+    <t xml:space="preserve">20.0927391052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5200424194336</t>
   </si>
   <si>
     <t xml:space="preserve">19.9905548095703</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5353775024414</t>
+    <t xml:space="preserve">19.53537940979</t>
   </si>
   <si>
     <t xml:space="preserve">19.2567005157471</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">18.7829456329346</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8386840820312</t>
+    <t xml:space="preserve">18.8386859893799</t>
   </si>
   <si>
     <t xml:space="preserve">18.6343212127686</t>
@@ -1040,22 +1040,22 @@
     <t xml:space="preserve">18.9966011047363</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6807689666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5600051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6621875762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4392471313477</t>
+    <t xml:space="preserve">18.6807651519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5600032806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6621856689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4392433166504</t>
   </si>
   <si>
     <t xml:space="preserve">18.8108139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1359405517578</t>
+    <t xml:space="preserve">19.1359386444092</t>
   </si>
   <si>
     <t xml:space="preserve">18.9779319763184</t>
@@ -1064,31 +1064,31 @@
     <t xml:space="preserve">18.9499263763428</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5298557281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3058128356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9044151306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8484039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6430339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6710395812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9417533874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8950805664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9697570800781</t>
+    <t xml:space="preserve">18.5298538208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3058166503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9044132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8484020233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6430377960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6710414886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9417514801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.895076751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9697551727295</t>
   </si>
   <si>
     <t xml:space="preserve">18.2684764862061</t>
@@ -1097,22 +1097,22 @@
     <t xml:space="preserve">18.4645099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">18.585865020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4084987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1657886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4925117492676</t>
+    <t xml:space="preserve">18.5858631134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4085006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.16579246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4925136566162</t>
   </si>
   <si>
     <t xml:space="preserve">18.3618240356445</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2217998504639</t>
+    <t xml:space="preserve">18.2218017578125</t>
   </si>
   <si>
     <t xml:space="preserve">18.6698760986328</t>
@@ -1124,25 +1124,25 @@
     <t xml:space="preserve">18.697883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">18.688549041748</t>
+    <t xml:space="preserve">18.6885471343994</t>
   </si>
   <si>
     <t xml:space="preserve">18.6138687133789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3524875640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3804950714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4458389282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4831809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4738464355469</t>
+    <t xml:space="preserve">18.3524913787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3804931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4458408355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4831790924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4738445281982</t>
   </si>
   <si>
     <t xml:space="preserve">18.6605434417725</t>
@@ -1151,25 +1151,25 @@
     <t xml:space="preserve">18.707218170166</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5951995849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3898315429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5018501281738</t>
+    <t xml:space="preserve">18.5951976776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3898296356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5018463134766</t>
   </si>
   <si>
     <t xml:space="preserve">18.9032516479492</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1833000183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4633483886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7433948516846</t>
+    <t xml:space="preserve">19.1833038330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4633464813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7433967590332</t>
   </si>
   <si>
     <t xml:space="preserve">20.536865234375</t>
@@ -1181,10 +1181,10 @@
     <t xml:space="preserve">21.5637092590332</t>
   </si>
   <si>
-    <t xml:space="preserve">21.517032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.377010345459</t>
+    <t xml:space="preserve">21.5170345306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3770122528076</t>
   </si>
   <si>
     <t xml:space="preserve">21.6103839874268</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">21.4703598022461</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7504100799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.797082901001</t>
+    <t xml:space="preserve">21.7504081726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7970848083496</t>
   </si>
   <si>
     <t xml:space="preserve">21.0036125183105</t>
@@ -1211,34 +1211,34 @@
     <t xml:space="preserve">20.6302146911621</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7702369689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7235641479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0969581604004</t>
+    <t xml:space="preserve">20.7702407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7235660552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0969638824463</t>
   </si>
   <si>
     <t xml:space="preserve">21.1903095245361</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1436328887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8635883331299</t>
+    <t xml:space="preserve">21.1436367034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8635864257812</t>
   </si>
   <si>
     <t xml:space="preserve">20.6768913269043</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7037353515625</t>
+    <t xml:space="preserve">21.7037334442139</t>
   </si>
   <si>
     <t xml:space="preserve">22.2171535491943</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8904285430908</t>
+    <t xml:space="preserve">21.8904304504395</t>
   </si>
   <si>
     <t xml:space="preserve">22.0771293640137</t>
@@ -1250,13 +1250,13 @@
     <t xml:space="preserve">20.8169136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2369842529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3034954071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2101440429688</t>
+    <t xml:space="preserve">21.236988067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3034934997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2101421356201</t>
   </si>
   <si>
     <t xml:space="preserve">20.9102630615234</t>
@@ -1265,91 +1265,91 @@
     <t xml:space="preserve">20.5835380554199</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9569396972656</t>
+    <t xml:space="preserve">20.956937789917</t>
   </si>
   <si>
     <t xml:space="preserve">21.3303356170654</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3968410491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4901905059814</t>
+    <t xml:space="preserve">20.396842956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4901924133301</t>
   </si>
   <si>
     <t xml:space="preserve">20.1167945861816</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0432739257812</t>
+    <t xml:space="preserve">19.0432777404785</t>
   </si>
   <si>
     <t xml:space="preserve">19.136625289917</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3233261108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7900714874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6033725738525</t>
+    <t xml:space="preserve">19.3233222961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7900733947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6033706665039</t>
   </si>
   <si>
     <t xml:space="preserve">20.3501663208008</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2568187713623</t>
+    <t xml:space="preserve">20.2568168640137</t>
   </si>
   <si>
     <t xml:space="preserve">19.976770401001</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1634712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0234470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8834209442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9300975799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.416675567627</t>
+    <t xml:space="preserve">20.1634674072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0234432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8834190368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9300937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4166717529297</t>
   </si>
   <si>
     <t xml:space="preserve">19.556697845459</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5100250244141</t>
+    <t xml:space="preserve">19.5100231170654</t>
   </si>
   <si>
     <t xml:space="preserve">19.6500453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6967182159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2766513824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2299766540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3700008392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8367443084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4236869812012</t>
+    <t xml:space="preserve">19.6967220306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.276647567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2299728393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3699970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8367481231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4236850738525</t>
   </si>
   <si>
     <t xml:space="preserve">20.0701198577881</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7177143096924</t>
+    <t xml:space="preserve">17.7177124023438</t>
   </si>
   <si>
     <t xml:space="preserve">15.3092994689941</t>
@@ -1358,100 +1358,100 @@
     <t xml:space="preserve">15.7013673782349</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7678737640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4691553115845</t>
+    <t xml:space="preserve">14.7678728103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4691562652588</t>
   </si>
   <si>
     <t xml:space="preserve">14.805212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4026489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.62668800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0000839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5333385467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3279705047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4586582183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8693952560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7947149276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6640291213989</t>
+    <t xml:space="preserve">15.4026498794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6266889572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0000858306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5333395004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3279714584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4586572647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8693981170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.794716835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.664026260376</t>
   </si>
   <si>
     <t xml:space="preserve">15.5893478393555</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3839797973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0105810165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8602886199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5784883499146</t>
+    <t xml:space="preserve">15.383978843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0105819702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8602876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5784893035889</t>
   </si>
   <si>
     <t xml:space="preserve">14.4094085693359</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4469814300537</t>
+    <t xml:space="preserve">14.4469804763794</t>
   </si>
   <si>
     <t xml:space="preserve">14.9166479110718</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9354343414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6536359786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1420888900757</t>
+    <t xml:space="preserve">14.935435295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6536350250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.14208984375</t>
   </si>
   <si>
     <t xml:space="preserve">15.4426765441895</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2735967636108</t>
+    <t xml:space="preserve">15.2735958099365</t>
   </si>
   <si>
     <t xml:space="preserve">14.0712461471558</t>
   </si>
   <si>
-    <t xml:space="preserve">13.920952796936</t>
+    <t xml:space="preserve">13.9209537506104</t>
   </si>
   <si>
     <t xml:space="preserve">13.6015777587891</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7330846786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3342590332031</t>
+    <t xml:space="preserve">13.7330856323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3342609405518</t>
   </si>
   <si>
     <t xml:space="preserve">14.1651802062988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1463937759399</t>
+    <t xml:space="preserve">14.1463928222656</t>
   </si>
   <si>
     <t xml:space="preserve">14.2215414047241</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">13.9585256576538</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6391534805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6203651428223</t>
+    <t xml:space="preserve">13.6391525268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6203641891479</t>
   </si>
   <si>
     <t xml:space="preserve">13.7894468307495</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">14.5221271514893</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7475671768188</t>
+    <t xml:space="preserve">14.7475681304932</t>
   </si>
   <si>
     <t xml:space="preserve">15.2172365188599</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">14.8978605270386</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1045160293579</t>
+    <t xml:space="preserve">15.1045141220093</t>
   </si>
   <si>
     <t xml:space="preserve">15.1608743667603</t>
@@ -1505,37 +1505,37 @@
     <t xml:space="preserve">15.1984491348267</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5366115570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9687042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8141059875488</t>
+    <t xml:space="preserve">15.5366106033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9687051773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8141078948975</t>
   </si>
   <si>
     <t xml:space="preserve">16.8892517089844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9080390930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4947299957275</t>
+    <t xml:space="preserve">16.9080410003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4947319030762</t>
   </si>
   <si>
     <t xml:space="preserve">16.419584274292</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2692909240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3632278442383</t>
+    <t xml:space="preserve">16.2692890167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3632259368896</t>
   </si>
   <si>
     <t xml:space="preserve">15.987491607666</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8747730255127</t>
+    <t xml:space="preserve">15.8747720718384</t>
   </si>
   <si>
     <t xml:space="preserve">15.8184118270874</t>
@@ -1556,76 +1556,76 @@
     <t xml:space="preserve">16.5135192871094</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2880764007568</t>
+    <t xml:space="preserve">16.2880783081055</t>
   </si>
   <si>
     <t xml:space="preserve">16.4383735656738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4571571350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2317199707031</t>
+    <t xml:space="preserve">16.4571590423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2317180633545</t>
   </si>
   <si>
     <t xml:space="preserve">16.6074542999268</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7201709747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4759464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3256530761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8559827804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9499177932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9311294555664</t>
+    <t xml:space="preserve">16.7201728820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.475944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3256511688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8559818267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9499187469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9311285018921</t>
   </si>
   <si>
     <t xml:space="preserve">16.1189975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0062789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3444385528564</t>
+    <t xml:space="preserve">16.0062770843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3444366455078</t>
   </si>
   <si>
     <t xml:space="preserve">16.4007987976074</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5323066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7765350341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9456157684326</t>
+    <t xml:space="preserve">16.5323047637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7765331268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.945613861084</t>
   </si>
   <si>
     <t xml:space="preserve">17.4716396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">18.279468536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.260684967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2418994903564</t>
+    <t xml:space="preserve">18.2794704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2606830596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2418956756592</t>
   </si>
   <si>
     <t xml:space="preserve">18.1103916168213</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5280017852783</t>
+    <t xml:space="preserve">17.528003692627</t>
   </si>
   <si>
     <t xml:space="preserve">17.1334819793701</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">16.9831867218018</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7389602661133</t>
+    <t xml:space="preserve">16.738956451416</t>
   </si>
   <si>
     <t xml:space="preserve">16.6450252532959</t>
@@ -1646,16 +1646,16 @@
     <t xml:space="preserve">16.9643993377686</t>
   </si>
   <si>
-    <t xml:space="preserve">16.832893371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0583324432373</t>
+    <t xml:space="preserve">16.8328914642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0583343505859</t>
   </si>
   <si>
     <t xml:space="preserve">17.1522674560547</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2274131774902</t>
+    <t xml:space="preserve">17.2274112701416</t>
   </si>
   <si>
     <t xml:space="preserve">16.7577457427979</t>
@@ -1667,10 +1667,10 @@
     <t xml:space="preserve">15.4990367889404</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5178213119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4614639282227</t>
+    <t xml:space="preserve">15.517822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4614629745483</t>
   </si>
   <si>
     <t xml:space="preserve">15.1796617507935</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">15.0857286453247</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7663545608521</t>
+    <t xml:space="preserve">14.7663555145264</t>
   </si>
   <si>
     <t xml:space="preserve">14.9730081558228</t>
@@ -1697,46 +1697,46 @@
     <t xml:space="preserve">14.5033407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6724224090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3718347549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.822714805603</t>
+    <t xml:space="preserve">14.6724214553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3718338012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8227157592773</t>
   </si>
   <si>
     <t xml:space="preserve">14.5597009658813</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4657669067383</t>
+    <t xml:space="preserve">14.4657678604126</t>
   </si>
   <si>
     <t xml:space="preserve">14.6348476409912</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5741834640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4051027297974</t>
+    <t xml:space="preserve">15.5741844177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.405101776123</t>
   </si>
   <si>
     <t xml:space="preserve">15.3863162994385</t>
   </si>
   <si>
-    <t xml:space="preserve">15.668119430542</t>
+    <t xml:space="preserve">15.6681184768677</t>
   </si>
   <si>
     <t xml:space="preserve">15.2360219955444</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5929689407349</t>
+    <t xml:space="preserve">15.5929698944092</t>
   </si>
   <si>
     <t xml:space="preserve">15.4238910675049</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3299541473389</t>
+    <t xml:space="preserve">15.3299560546875</t>
   </si>
   <si>
     <t xml:space="preserve">15.0481567382812</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">14.2966871261597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2779006958008</t>
+    <t xml:space="preserve">14.2778997421265</t>
   </si>
   <si>
     <t xml:space="preserve">14.090033531189</t>
@@ -1775,25 +1775,25 @@
     <t xml:space="preserve">14.2591142654419</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8082323074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8458061218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0336723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9397411346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2403268814087</t>
+    <t xml:space="preserve">13.8082313537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8458070755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.033673286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9397392272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2403259277344</t>
   </si>
   <si>
     <t xml:space="preserve">14.0148868560791</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5972757339478</t>
+    <t xml:space="preserve">14.5972747802734</t>
   </si>
   <si>
     <t xml:space="preserve">13.9960994720459</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">14.1839666366577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1088199615479</t>
+    <t xml:space="preserve">14.1088190078735</t>
   </si>
   <si>
     <t xml:space="preserve">14.4845533370972</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">14.9917945861816</t>
   </si>
   <si>
-    <t xml:space="preserve">15.292384147644</t>
+    <t xml:space="preserve">15.2923851013184</t>
   </si>
   <si>
     <t xml:space="preserve">15.0758924484253</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">14.9052228927612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8104066848755</t>
+    <t xml:space="preserve">14.8104057312012</t>
   </si>
   <si>
     <t xml:space="preserve">14.8862590789795</t>
@@ -1841,25 +1841,25 @@
     <t xml:space="preserve">16.4602203369141</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3274765014648</t>
+    <t xml:space="preserve">16.3274784088135</t>
   </si>
   <si>
     <t xml:space="preserve">15.7016839981079</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6637563705444</t>
+    <t xml:space="preserve">15.6637582778931</t>
   </si>
   <si>
     <t xml:space="preserve">15.5310144424438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5499782562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551610946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7585754394531</t>
+    <t xml:space="preserve">15.5499773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7585763931274</t>
   </si>
   <si>
     <t xml:space="preserve">15.7965030670166</t>
@@ -1868,25 +1868,25 @@
     <t xml:space="preserve">16.1757698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">15.720648765564</t>
+    <t xml:space="preserve">15.7206497192383</t>
   </si>
   <si>
     <t xml:space="preserve">15.6068687438965</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6447954177856</t>
+    <t xml:space="preserve">15.6447944641113</t>
   </si>
   <si>
     <t xml:space="preserve">16.0430240631104</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9861373901367</t>
+    <t xml:space="preserve">15.9861354827881</t>
   </si>
   <si>
     <t xml:space="preserve">15.4172353744507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8344287872314</t>
+    <t xml:space="preserve">15.8344297409058</t>
   </si>
   <si>
     <t xml:space="preserve">15.5689430236816</t>
@@ -1904,13 +1904,13 @@
     <t xml:space="preserve">15.1138200759888</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9810771942139</t>
+    <t xml:space="preserve">14.9810781478882</t>
   </si>
   <si>
     <t xml:space="preserve">15.2086391448975</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7535161972046</t>
+    <t xml:space="preserve">14.7535152435303</t>
   </si>
   <si>
     <t xml:space="preserve">14.9431495666504</t>
@@ -1931,10 +1931,10 @@
     <t xml:space="preserve">14.6018085479736</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7914438247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5828456878662</t>
+    <t xml:space="preserve">14.7914428710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5828447341919</t>
   </si>
   <si>
     <t xml:space="preserve">14.3932123184204</t>
@@ -1943,13 +1943,13 @@
     <t xml:space="preserve">14.4311380386353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6207714080811</t>
+    <t xml:space="preserve">14.6207723617554</t>
   </si>
   <si>
     <t xml:space="preserve">14.3363218307495</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2794313430786</t>
+    <t xml:space="preserve">14.2794303894043</t>
   </si>
   <si>
     <t xml:space="preserve">14.0518703460693</t>
@@ -1961,31 +1961,31 @@
     <t xml:space="preserve">13.1416273117065</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0088844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3691902160645</t>
+    <t xml:space="preserve">13.0088834762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3691892623901</t>
   </si>
   <si>
     <t xml:space="preserve">13.0847387313843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8002862930298</t>
+    <t xml:space="preserve">12.8002872467041</t>
   </si>
   <si>
     <t xml:space="preserve">12.4210195541382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1744956970215</t>
+    <t xml:space="preserve">12.1744966506958</t>
   </si>
   <si>
     <t xml:space="preserve">11.9469347000122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4728507995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.036693572998</t>
+    <t xml:space="preserve">11.4728498458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0366926193237</t>
   </si>
   <si>
     <t xml:space="preserve">10.1264495849609</t>
@@ -2006,19 +2006,19 @@
     <t xml:space="preserve">8.09736728668213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55248928070068</t>
+    <t xml:space="preserve">8.55248832702637</t>
   </si>
   <si>
     <t xml:space="preserve">9.10242748260498</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1643762588501</t>
+    <t xml:space="preserve">10.1643772125244</t>
   </si>
   <si>
     <t xml:space="preserve">10.7522420883179</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9279699325562</t>
+    <t xml:space="preserve">11.9279708862305</t>
   </si>
   <si>
     <t xml:space="preserve">12.8951044082642</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">10.9608383178711</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9229106903076</t>
+    <t xml:space="preserve">10.9229116439819</t>
   </si>
   <si>
     <t xml:space="preserve">10.6384611129761</t>
@@ -2048,22 +2048,22 @@
     <t xml:space="preserve">10.7332782745361</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1125450134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9039468765259</t>
+    <t xml:space="preserve">11.1125459671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9039478302002</t>
   </si>
   <si>
     <t xml:space="preserve">10.5815706253052</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2023019790649</t>
+    <t xml:space="preserve">10.2023029327393</t>
   </si>
   <si>
     <t xml:space="preserve">9.87992477416992</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2212657928467</t>
+    <t xml:space="preserve">10.2212648391724</t>
   </si>
   <si>
     <t xml:space="preserve">10.5057163238525</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">10.7143144607544</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6953496932983</t>
+    <t xml:space="preserve">10.6953506469727</t>
   </si>
   <si>
     <t xml:space="preserve">10.8091306686401</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8280954360962</t>
+    <t xml:space="preserve">10.8280944824219</t>
   </si>
   <si>
     <t xml:space="preserve">10.543643951416</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">10.9418745040894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491813659668</t>
+    <t xml:space="preserve">11.4918127059937</t>
   </si>
   <si>
     <t xml:space="preserve">11.567666053772</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">12.2124223709106</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0986413955688</t>
+    <t xml:space="preserve">12.0986404418945</t>
   </si>
   <si>
     <t xml:space="preserve">11.8521175384521</t>
@@ -2138,16 +2138,16 @@
     <t xml:space="preserve">11.1884002685547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0935821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8849849700928</t>
+    <t xml:space="preserve">11.093581199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8849840164185</t>
   </si>
   <si>
     <t xml:space="preserve">10.7901678085327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6763877868652</t>
+    <t xml:space="preserve">10.6763868331909</t>
   </si>
   <si>
     <t xml:space="preserve">10.4108991622925</t>
@@ -2165,13 +2165,13 @@
     <t xml:space="preserve">11.340106010437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2832164764404</t>
+    <t xml:space="preserve">11.2832155227661</t>
   </si>
   <si>
     <t xml:space="preserve">11.0746183395386</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9798021316528</t>
+    <t xml:space="preserve">10.9798011779785</t>
   </si>
   <si>
     <t xml:space="preserve">10.6005344390869</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">11.6814470291138</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5297384262085</t>
+    <t xml:space="preserve">11.5297393798828</t>
   </si>
   <si>
     <t xml:space="preserve">11.6245565414429</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">12.2313842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.136568069458</t>
+    <t xml:space="preserve">12.1365690231323</t>
   </si>
   <si>
     <t xml:space="preserve">12.1176042556763</t>
@@ -2228,22 +2228,22 @@
     <t xml:space="preserve">11.7573003768921</t>
   </si>
   <si>
-    <t xml:space="preserve">11.245288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6485805511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6536388397217</t>
+    <t xml:space="preserve">11.2452878952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6485815048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.653639793396</t>
   </si>
   <si>
     <t xml:space="preserve">13.3881521224976</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8622360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5967493057251</t>
+    <t xml:space="preserve">13.8622369766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5967502593994</t>
   </si>
   <si>
     <t xml:space="preserve">13.2364444732666</t>
@@ -2267,16 +2267,16 @@
     <t xml:space="preserve">13.7294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.407114982605</t>
+    <t xml:space="preserve">13.4071159362793</t>
   </si>
   <si>
     <t xml:space="preserve">13.1226654052734</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4829692840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1795539855957</t>
+    <t xml:space="preserve">13.4829683303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.17955493927</t>
   </si>
   <si>
     <t xml:space="preserve">12.0227880477905</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">12.3262023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4399824142456</t>
+    <t xml:space="preserve">12.4399833679199</t>
   </si>
   <si>
     <t xml:space="preserve">12.857177734375</t>
@@ -2300,16 +2300,16 @@
     <t xml:space="preserve">13.0468101501465</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3122997283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4450416564941</t>
+    <t xml:space="preserve">13.3122987747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4450426101685</t>
   </si>
   <si>
     <t xml:space="preserve">13.5588226318359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6179914474487</t>
+    <t xml:space="preserve">13.6179904937744</t>
   </si>
   <si>
     <t xml:space="preserve">13.6371440887451</t>
@@ -2318,19 +2318,19 @@
     <t xml:space="preserve">13.4073047637939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4456129074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3115377426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5030727386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8478298187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.886137008667</t>
+    <t xml:space="preserve">13.4456119537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3115386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5030717849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8478307723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8861360549927</t>
   </si>
   <si>
     <t xml:space="preserve">13.7520637512207</t>
@@ -2360,19 +2360,19 @@
     <t xml:space="preserve">13.598837852478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5413780212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7903699874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7137584686279</t>
+    <t xml:space="preserve">13.5413789749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7903709411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7137575149536</t>
   </si>
   <si>
     <t xml:space="preserve">13.8669834136963</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1351299285889</t>
+    <t xml:space="preserve">14.1351289749146</t>
   </si>
   <si>
     <t xml:space="preserve">14.3458156585693</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">14.7097282409668</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6331157684326</t>
+    <t xml:space="preserve">14.6331148147583</t>
   </si>
   <si>
     <t xml:space="preserve">14.9970273971558</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">15.0353345870972</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4909839630127</t>
+    <t xml:space="preserve">16.4909858703613</t>
   </si>
   <si>
     <t xml:space="preserve">16.3377590179443</t>
@@ -2399,16 +2399,16 @@
     <t xml:space="preserve">16.184534072876</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8206176757812</t>
+    <t xml:space="preserve">15.8206195831299</t>
   </si>
   <si>
     <t xml:space="preserve">15.9546937942505</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8014669418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6099338531494</t>
+    <t xml:space="preserve">15.8014659881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6099348068237</t>
   </si>
   <si>
     <t xml:space="preserve">15.3226337432861</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">15.8589248657227</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2611465454102</t>
+    <t xml:space="preserve">16.2611446380615</t>
   </si>
   <si>
     <t xml:space="preserve">16.6059036254883</t>
@@ -2438,10 +2438,10 @@
     <t xml:space="preserve">16.778284072876</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6825199127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6442127227783</t>
+    <t xml:space="preserve">16.6825180053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6442108154297</t>
   </si>
   <si>
     <t xml:space="preserve">16.7208251953125</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">16.7016716003418</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1613502502441</t>
+    <t xml:space="preserve">17.1613483428955</t>
   </si>
   <si>
     <t xml:space="preserve">17.1421985626221</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">16.4526786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4335250854492</t>
+    <t xml:space="preserve">16.4335269927979</t>
   </si>
   <si>
     <t xml:space="preserve">16.9123573303223</t>
@@ -2480,22 +2480,22 @@
     <t xml:space="preserve">16.9315128326416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8548984527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9657878875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0807094573975</t>
+    <t xml:space="preserve">16.8548965454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9657897949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0807075500488</t>
   </si>
   <si>
     <t xml:space="preserve">18.3105487823486</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6321258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9194221496582</t>
+    <t xml:space="preserve">19.6321239471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9194240570068</t>
   </si>
   <si>
     <t xml:space="preserve">20.3024921417236</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">19.9673080444336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8715419769287</t>
+    <t xml:space="preserve">19.8715400695801</t>
   </si>
   <si>
     <t xml:space="preserve">20.0151920318604</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">20.5419063568115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6376724243164</t>
+    <t xml:space="preserve">20.637674331665</t>
   </si>
   <si>
     <t xml:space="preserve">20.9728565216064</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">20.9249725341797</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7278919219971</t>
+    <t xml:space="preserve">19.7278900146484</t>
   </si>
   <si>
     <t xml:space="preserve">19.4884757995605</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">19.3448276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5363578796387</t>
+    <t xml:space="preserve">19.5363597869873</t>
   </si>
   <si>
     <t xml:space="preserve">19.823657989502</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">19.1532917022705</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2546062469482</t>
+    <t xml:space="preserve">20.2546081542969</t>
   </si>
   <si>
     <t xml:space="preserve">20.4461402893066</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">21.1165046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6911010742188</t>
+    <t xml:space="preserve">21.6911029815674</t>
   </si>
   <si>
     <t xml:space="preserve">21.3080387115479</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">21.834753036499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5474529266357</t>
+    <t xml:space="preserve">21.5474548339844</t>
   </si>
   <si>
     <t xml:space="preserve">21.8826370239258</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">21.212272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3559226989746</t>
+    <t xml:space="preserve">21.355920791626</t>
   </si>
   <si>
     <t xml:space="preserve">21.4516868591309</t>
@@ -2612,19 +2612,19 @@
     <t xml:space="preserve">22.3135852813721</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7924194335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3191337585449</t>
+    <t xml:space="preserve">22.7924175262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3191356658936</t>
   </si>
   <si>
     <t xml:space="preserve">22.6487674713135</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4093532562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0262851715088</t>
+    <t xml:space="preserve">22.409351348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0262870788574</t>
   </si>
   <si>
     <t xml:space="preserve">21.6432209014893</t>
@@ -2642,25 +2642,25 @@
     <t xml:space="preserve">21.9305210113525</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5162143707275</t>
+    <t xml:space="preserve">24.5162162780762</t>
   </si>
   <si>
     <t xml:space="preserve">23.9416160583496</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4627819061279</t>
+    <t xml:space="preserve">23.4627838134766</t>
   </si>
   <si>
     <t xml:space="preserve">23.4148998260498</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1754856109619</t>
+    <t xml:space="preserve">23.1754837036133</t>
   </si>
   <si>
     <t xml:space="preserve">23.2712497711182</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5106678009033</t>
+    <t xml:space="preserve">23.5106658935547</t>
   </si>
   <si>
     <t xml:space="preserve">23.22336769104</t>
@@ -2672,10 +2672,10 @@
     <t xml:space="preserve">23.6064319610596</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0797157287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.797966003418</t>
+    <t xml:space="preserve">23.0797176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7979679107666</t>
   </si>
   <si>
     <t xml:space="preserve">23.7021999359131</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">22.1699371337891</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2289161682129</t>
+    <t xml:space="preserve">24.2289142608643</t>
   </si>
   <si>
     <t xml:space="preserve">23.8937339782715</t>
@@ -2720,22 +2720,22 @@
     <t xml:space="preserve">24.0373821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8458518981934</t>
+    <t xml:space="preserve">23.8458499908447</t>
   </si>
   <si>
     <t xml:space="preserve">25.4738807678223</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7611808776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1442432403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8569431304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8090629577637</t>
+    <t xml:space="preserve">25.7611789703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1442451477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8569450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8090648651123</t>
   </si>
   <si>
     <t xml:space="preserve">25.9527111053467</t>
@@ -2756,7 +2756,7 @@
     <t xml:space="preserve">27.3892097473145</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3413238525391</t>
+    <t xml:space="preserve">27.3413257598877</t>
   </si>
   <si>
     <t xml:space="preserve">27.8680400848389</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">28.2989902496338</t>
   </si>
   <si>
-    <t xml:space="preserve">27.772274017334</t>
+    <t xml:space="preserve">27.7722721099854</t>
   </si>
   <si>
     <t xml:space="preserve">27.6286239624023</t>
@@ -2786,16 +2786,16 @@
     <t xml:space="preserve">27.2455596923828</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9582595825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1497936248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.054027557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7188453674316</t>
+    <t xml:space="preserve">26.9582614898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1497917175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0540256500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.718843460083</t>
   </si>
   <si>
     <t xml:space="preserve">26.9287757873535</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">25.8207931518555</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4354076385498</t>
+    <t xml:space="preserve">25.4354095458984</t>
   </si>
   <si>
     <t xml:space="preserve">24.5682926177979</t>
@@ -2816,10 +2816,10 @@
     <t xml:space="preserve">24.7128105163574</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1347332000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.760986328125</t>
+    <t xml:space="preserve">24.1347351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7609844207764</t>
   </si>
   <si>
     <t xml:space="preserve">24.6646404266357</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">25.0981960296631</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3988704681396</t>
+    <t xml:space="preserve">26.3988723754883</t>
   </si>
   <si>
     <t xml:space="preserve">26.8324298858643</t>
@@ -2846,10 +2846,10 @@
     <t xml:space="preserve">25.4835815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7244491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.146369934082</t>
+    <t xml:space="preserve">25.7244472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1463718414307</t>
   </si>
   <si>
     <t xml:space="preserve">25.579927444458</t>
@@ -2861,13 +2861,13 @@
     <t xml:space="preserve">26.0616588592529</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9653148651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1580047607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6281032562256</t>
+    <t xml:space="preserve">25.9653129577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1580066680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.628101348877</t>
   </si>
   <si>
     <t xml:space="preserve">24.8573303222656</t>
@@ -2876,13 +2876,13 @@
     <t xml:space="preserve">25.6762752532959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5317554473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0500240325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.47194480896</t>
+    <t xml:space="preserve">25.5317535400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0500221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4719467163086</t>
   </si>
   <si>
     <t xml:space="preserve">22.9785804748535</t>
@@ -2900,7 +2900,7 @@
     <t xml:space="preserve">22.9304046630859</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2194442749023</t>
+    <t xml:space="preserve">23.219446182251</t>
   </si>
   <si>
     <t xml:space="preserve">23.4121360778809</t>
@@ -2921,13 +2921,13 @@
     <t xml:space="preserve">22.6413669586182</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8340625762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.49684715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1114635467529</t>
+    <t xml:space="preserve">22.8340606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4968490600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1114616394043</t>
   </si>
   <si>
     <t xml:space="preserve">23.1712703704834</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">22.1596355438232</t>
   </si>
   <si>
-    <t xml:space="preserve">22.063289642334</t>
+    <t xml:space="preserve">22.0632915496826</t>
   </si>
   <si>
     <t xml:space="preserve">21.3888664245605</t>
@@ -2948,16 +2948,16 @@
     <t xml:space="preserve">20.52174949646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5101146697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1845397949219</t>
+    <t xml:space="preserve">19.5101127624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1845378875732</t>
   </si>
   <si>
     <t xml:space="preserve">19.9436740875244</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9609432220459</t>
+    <t xml:space="preserve">18.9609413146973</t>
   </si>
   <si>
     <t xml:space="preserve">19.1536331176758</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">18.1323623657227</t>
   </si>
   <si>
-    <t xml:space="preserve">16.899133682251</t>
+    <t xml:space="preserve">16.8991317749023</t>
   </si>
   <si>
     <t xml:space="preserve">16.9569396972656</t>
@@ -2978,13 +2978,13 @@
     <t xml:space="preserve">18.15163230896</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5542869567871</t>
+    <t xml:space="preserve">17.5542850494385</t>
   </si>
   <si>
     <t xml:space="preserve">18.3057861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8433246612549</t>
+    <t xml:space="preserve">17.8433265686035</t>
   </si>
   <si>
     <t xml:space="preserve">17.4964771270752</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">18.2672462463379</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3250579833984</t>
+    <t xml:space="preserve">18.3250560760498</t>
   </si>
   <si>
     <t xml:space="preserve">18.6911716461182</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">19.2114410400391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6333618164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7662506103516</t>
+    <t xml:space="preserve">18.6333637237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7662487030029</t>
   </si>
   <si>
     <t xml:space="preserve">18.6526336669922</t>
@@ -3035,31 +3035,31 @@
     <t xml:space="preserve">18.4021339416504</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7297115325928</t>
+    <t xml:space="preserve">18.7297096252441</t>
   </si>
   <si>
     <t xml:space="preserve">19.4137687683105</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7509803771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1343631744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7489795684814</t>
+    <t xml:space="preserve">19.7509784698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1343650817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7489776611328</t>
   </si>
   <si>
     <t xml:space="preserve">18.9224014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3655948638916</t>
+    <t xml:space="preserve">19.3655967712402</t>
   </si>
   <si>
     <t xml:space="preserve">19.2692489624023</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5350189208984</t>
+    <t xml:space="preserve">17.5350170135498</t>
   </si>
   <si>
     <t xml:space="preserve">17.7277088165283</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">22.4005012512207</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1231002807617</t>
+    <t xml:space="preserve">23.1230983734131</t>
   </si>
   <si>
     <t xml:space="preserve">23.3157920837402</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">22.5450229644775</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2078075408936</t>
+    <t xml:space="preserve">22.2078094482422</t>
   </si>
   <si>
     <t xml:space="preserve">20.4254035949707</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">19.8473262786865</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2499809265137</t>
+    <t xml:space="preserve">19.249979019165</t>
   </si>
   <si>
     <t xml:space="preserve">18.7875175476074</t>
@@ -3149,19 +3149,19 @@
     <t xml:space="preserve">18.0745544433594</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5562877655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7104396820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.94167137146</t>
+    <t xml:space="preserve">18.5562858581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7104415893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9416732788086</t>
   </si>
   <si>
     <t xml:space="preserve">18.5370178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4406700134277</t>
+    <t xml:space="preserve">18.4406719207764</t>
   </si>
   <si>
     <t xml:space="preserve">18.2865161895752</t>
@@ -3176,10 +3176,10 @@
     <t xml:space="preserve">19.3174209594727</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8453235626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9802112579346</t>
+    <t xml:space="preserve">18.8453254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9802093505859</t>
   </si>
   <si>
     <t xml:space="preserve">19.4619426727295</t>
@@ -3188,31 +3188,31 @@
     <t xml:space="preserve">18.1709022521973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7084369659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9204006195068</t>
+    <t xml:space="preserve">17.708438873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9204025268555</t>
   </si>
   <si>
     <t xml:space="preserve">17.6313629150391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2094383239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2479801177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.669900894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3423233032227</t>
+    <t xml:space="preserve">18.2094402313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2479782104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6699028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3423252105713</t>
   </si>
   <si>
     <t xml:space="preserve">16.6293621063232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9934778213501</t>
+    <t xml:space="preserve">15.9934787750244</t>
   </si>
   <si>
     <t xml:space="preserve">16.4559383392334</t>
@@ -3227,13 +3227,13 @@
     <t xml:space="preserve">16.2247085571289</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4153995513916</t>
+    <t xml:space="preserve">15.4153985977173</t>
   </si>
   <si>
     <t xml:space="preserve">15.5502834320068</t>
   </si>
   <si>
-    <t xml:space="preserve">15.357590675354</t>
+    <t xml:space="preserve">15.3575916290283</t>
   </si>
   <si>
     <t xml:space="preserve">16.7257080078125</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">17.1110935211182</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4386692047119</t>
+    <t xml:space="preserve">17.4386711120605</t>
   </si>
   <si>
     <t xml:space="preserve">17.2459774017334</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">18.8838653564453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8260593414307</t>
+    <t xml:space="preserve">18.826057434082</t>
   </si>
   <si>
     <t xml:space="preserve">19.5582866668701</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">20.088191986084</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1363639831543</t>
+    <t xml:space="preserve">20.1363658905029</t>
   </si>
   <si>
     <t xml:space="preserve">19.702808380127</t>
@@ -3290,10 +3290,10 @@
     <t xml:space="preserve">20.3290576934814</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7626171112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8589611053467</t>
+    <t xml:space="preserve">20.7626152038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8589630126953</t>
   </si>
   <si>
     <t xml:space="preserve">20.7899551391602</t>
@@ -3305,13 +3305,13 @@
     <t xml:space="preserve">20.8875617980957</t>
   </si>
   <si>
-    <t xml:space="preserve">20.741153717041</t>
+    <t xml:space="preserve">20.7411518096924</t>
   </si>
   <si>
     <t xml:space="preserve">20.6435470581055</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4483375549316</t>
+    <t xml:space="preserve">20.448335647583</t>
   </si>
   <si>
     <t xml:space="preserve">20.6923503875732</t>
@@ -3320,13 +3320,13 @@
     <t xml:space="preserve">20.5947437286377</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5459403991699</t>
+    <t xml:space="preserve">20.5459423065186</t>
   </si>
   <si>
     <t xml:space="preserve">20.3019275665283</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3267841339111</t>
+    <t xml:space="preserve">21.3267860412598</t>
   </si>
   <si>
     <t xml:space="preserve">20.4971389770508</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">20.1555194854736</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1067161560059</t>
+    <t xml:space="preserve">20.1067180633545</t>
   </si>
   <si>
     <t xml:space="preserve">20.2531261444092</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">21.0827713012695</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7660083770752</t>
+    <t xml:space="preserve">21.7660102844238</t>
   </si>
   <si>
     <t xml:space="preserve">21.8636150360107</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">22.5956554412842</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9372730255127</t>
+    <t xml:space="preserve">22.9372749328613</t>
   </si>
   <si>
     <t xml:space="preserve">23.083683013916</t>
@@ -3392,10 +3392,10 @@
     <t xml:space="preserve">23.4741039276123</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2300910949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7181186676025</t>
+    <t xml:space="preserve">23.2300891876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7181167602539</t>
   </si>
   <si>
     <t xml:space="preserve">23.6693153381348</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">23.6205139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7669200897217</t>
+    <t xml:space="preserve">23.7669219970703</t>
   </si>
   <si>
     <t xml:space="preserve">23.8645267486572</t>
@@ -3413,22 +3413,22 @@
     <t xml:space="preserve">23.2788944244385</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3276958465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9621315002441</t>
+    <t xml:space="preserve">23.3276977539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9621295928955</t>
   </si>
   <si>
     <t xml:space="preserve">24.6941719055176</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3286094665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.986988067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7917785644531</t>
+    <t xml:space="preserve">25.3286075592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9869899749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7917766571045</t>
   </si>
   <si>
     <t xml:space="preserve">24.4989624023438</t>
@@ -3437,25 +3437,25 @@
     <t xml:space="preserve">24.5965671539307</t>
   </si>
   <si>
-    <t xml:space="preserve">24.450159072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3037509918213</t>
+    <t xml:space="preserve">24.4501571655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3037490844727</t>
   </si>
   <si>
     <t xml:space="preserve">24.0109348297119</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7420635223389</t>
+    <t xml:space="preserve">22.7420616149902</t>
   </si>
   <si>
     <t xml:space="preserve">22.644458770752</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1812877655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8884735107422</t>
+    <t xml:space="preserve">23.1812896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8884716033936</t>
   </si>
   <si>
     <t xml:space="preserve">23.0348796844482</t>
@@ -3464,10 +3464,10 @@
     <t xml:space="preserve">23.1324863433838</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0597381591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2549476623535</t>
+    <t xml:space="preserve">24.0597362518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2549495697021</t>
   </si>
   <si>
     <t xml:space="preserve">24.3525543212891</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">22.3516426086426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9612216949463</t>
+    <t xml:space="preserve">21.9612197875977</t>
   </si>
   <si>
     <t xml:space="preserve">21.9124183654785</t>
@@ -3488,19 +3488,19 @@
     <t xml:space="preserve">22.3028392791748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5468521118164</t>
+    <t xml:space="preserve">22.546854019165</t>
   </si>
   <si>
     <t xml:space="preserve">22.7908668518066</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4980506896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6932601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6684055328369</t>
+    <t xml:space="preserve">22.4980487823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6932621002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6684036254883</t>
   </si>
   <si>
     <t xml:space="preserve">21.5707988739014</t>
@@ -3524,16 +3524,16 @@
     <t xml:space="preserve">21.4731941223145</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2291812896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0339679718018</t>
+    <t xml:space="preserve">21.2291793823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0339698791504</t>
   </si>
   <si>
     <t xml:space="preserve">21.1803779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0100231170654</t>
+    <t xml:space="preserve">22.0100212097168</t>
   </si>
   <si>
     <t xml:space="preserve">22.107629776001</t>
@@ -3548,7 +3548,7 @@
     <t xml:space="preserve">24.2061443328857</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1821994781494</t>
+    <t xml:space="preserve">25.1821975708008</t>
   </si>
   <si>
     <t xml:space="preserve">26.2558574676514</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">26.0118446350098</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8654365539551</t>
+    <t xml:space="preserve">25.8654384613037</t>
   </si>
   <si>
     <t xml:space="preserve">25.8166351318359</t>
@@ -3575,13 +3575,13 @@
     <t xml:space="preserve">27.0855045318604</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4022674560547</t>
+    <t xml:space="preserve">26.4022655487061</t>
   </si>
   <si>
     <t xml:space="preserve">26.548677444458</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4750156402588</t>
+    <t xml:space="preserve">25.4750175476074</t>
   </si>
   <si>
     <t xml:space="preserve">24.5477638244629</t>
@@ -3590,10 +3590,10 @@
     <t xml:space="preserve">24.88938331604</t>
   </si>
   <si>
-    <t xml:space="preserve">24.157341003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4013557434082</t>
+    <t xml:space="preserve">24.1573429107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4013576507568</t>
   </si>
   <si>
     <t xml:space="preserve">24.7429752349854</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">25.5726222991943</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6702270507812</t>
+    <t xml:space="preserve">25.6702251434326</t>
   </si>
   <si>
     <t xml:space="preserve">25.5238170623779</t>
@@ -70331,7 +70331,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6912731481</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>36504</v>
@@ -70352,6 +70352,32 @@
         <v>1538</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6912037037</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>22517</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>45.7000007629395</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>46.3499984741211</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>46.0999984741211</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>1529</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="1540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="1541">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5902519226074</t>
+    <t xml:space="preserve">15.5902538299561</t>
   </si>
   <si>
     <t xml:space="preserve">DAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7186403274536</t>
+    <t xml:space="preserve">15.7186412811279</t>
   </si>
   <si>
     <t xml:space="preserve">15.2234239578247</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5356159210205</t>
+    <t xml:space="preserve">14.5356178283691</t>
   </si>
   <si>
     <t xml:space="preserve">14.2146425247192</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9395198822021</t>
+    <t xml:space="preserve">13.9395189285278</t>
   </si>
   <si>
     <t xml:space="preserve">14.2880067825317</t>
@@ -65,46 +65,46 @@
     <t xml:space="preserve">14.040397644043</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8661508560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1049833297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7931756973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8848838806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2887868881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9490785598755</t>
+    <t xml:space="preserve">13.866153717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1049823760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.793176651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8848848342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2887849807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9490795135498</t>
   </si>
   <si>
     <t xml:space="preserve">13.1324939727783</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8928823471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0487861633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3239059448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0854721069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.360595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1125984191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5990314483643</t>
+    <t xml:space="preserve">15.8928833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0487899780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3239116668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0854740142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3605937957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1125907897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5990333557129</t>
   </si>
   <si>
     <t xml:space="preserve">15.4710340499878</t>
@@ -113,37 +113,37 @@
     <t xml:space="preserve">16.1038131713867</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3059577941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9391317367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9483013153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3518142700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1042032241821</t>
+    <t xml:space="preserve">15.3059606552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9391307830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9482984542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3518114089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1042022705078</t>
   </si>
   <si>
     <t xml:space="preserve">15.0033254623413</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9112281799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2322025299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7641048431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9200115203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0575656890869</t>
+    <t xml:space="preserve">15.911226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2322044372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7641067504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9200096130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0575714111328</t>
   </si>
   <si>
     <t xml:space="preserve">16.9658622741699</t>
@@ -152,118 +152,118 @@
     <t xml:space="preserve">16.7090816497803</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3514213562012</t>
+    <t xml:space="preserve">16.3514251708984</t>
   </si>
   <si>
     <t xml:space="preserve">16.3422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">16.828296661377</t>
+    <t xml:space="preserve">16.8283023834229</t>
   </si>
   <si>
     <t xml:space="preserve">16.6357135772705</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1767883300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3051795959473</t>
+    <t xml:space="preserve">17.1767864227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3051815032959</t>
   </si>
   <si>
     <t xml:space="preserve">17.3693752288818</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4335689544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.534839630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2226448059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5161075592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8741550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2593231201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4610824584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0117168426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2138614654541</t>
+    <t xml:space="preserve">17.4335708618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5348377227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2226409912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5161056518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.874153137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2593269348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4610805511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.01171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2138633728027</t>
   </si>
   <si>
     <t xml:space="preserve">16.5531768798828</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9383506774902</t>
+    <t xml:space="preserve">16.9383487701416</t>
   </si>
   <si>
     <t xml:space="preserve">17.2868385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5715217590332</t>
+    <t xml:space="preserve">16.5715198516846</t>
   </si>
   <si>
     <t xml:space="preserve">16.5256652832031</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1217670440674</t>
+    <t xml:space="preserve">17.1217632293701</t>
   </si>
   <si>
     <t xml:space="preserve">17.5619583129883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6353225708008</t>
+    <t xml:space="preserve">17.6353244781494</t>
   </si>
   <si>
     <t xml:space="preserve">17.4060554504395</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8645915985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1122035980225</t>
+    <t xml:space="preserve">17.8645935058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1122055053711</t>
   </si>
   <si>
     <t xml:space="preserve">18.0204982757568</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7912254333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5986461639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3414707183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4056663513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4331817626953</t>
+    <t xml:space="preserve">17.7912273406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5986423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3414745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4056701660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.433177947998</t>
   </si>
   <si>
     <t xml:space="preserve">18.0938625335693</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3231334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0296688079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8921051025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4702491760254</t>
+    <t xml:space="preserve">18.3231315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0296669006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8921070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.470251083374</t>
   </si>
   <si>
     <t xml:space="preserve">17.1492767333984</t>
@@ -284,13 +284,13 @@
     <t xml:space="preserve">16.8374710083008</t>
   </si>
   <si>
-    <t xml:space="preserve">16.562349319458</t>
+    <t xml:space="preserve">16.5623512268066</t>
   </si>
   <si>
     <t xml:space="preserve">16.3147411346436</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1496658325195</t>
+    <t xml:space="preserve">16.1496639251709</t>
   </si>
   <si>
     <t xml:space="preserve">16.2505435943604</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">16.7457675933838</t>
   </si>
   <si>
-    <t xml:space="preserve">16.452299118042</t>
+    <t xml:space="preserve">16.4523029327393</t>
   </si>
   <si>
     <t xml:space="preserve">16.4156169891357</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1680107116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3602046966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5164966583252</t>
+    <t xml:space="preserve">16.1680088043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3602027893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5164947509766</t>
   </si>
   <si>
     <t xml:space="preserve">16.4981555938721</t>
@@ -320,13 +320,13 @@
     <t xml:space="preserve">17.2409820556641</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9933738708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0392265319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8103504180908</t>
+    <t xml:space="preserve">16.9933757781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0392284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8103485107422</t>
   </si>
   <si>
     <t xml:space="preserve">15.8470325469971</t>
@@ -338,22 +338,22 @@
     <t xml:space="preserve">14.7648868560791</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0675210952759</t>
+    <t xml:space="preserve">15.0675191879272</t>
   </si>
   <si>
     <t xml:space="preserve">15.3334703445435</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9570817947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9849843978882</t>
+    <t xml:space="preserve">15.9570798873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9849824905396</t>
   </si>
   <si>
     <t xml:space="preserve">14.4530801773071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8841037750244</t>
+    <t xml:space="preserve">14.884105682373</t>
   </si>
   <si>
     <t xml:space="preserve">14.5264463424683</t>
@@ -362,28 +362,28 @@
     <t xml:space="preserve">14.6823482513428</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4068374633789</t>
+    <t xml:space="preserve">15.4068365097046</t>
   </si>
   <si>
     <t xml:space="preserve">15.0308361053467</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6273221969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0037145614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2604951858521</t>
+    <t xml:space="preserve">14.6273241043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.003716468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2604942321777</t>
   </si>
   <si>
     <t xml:space="preserve">14.6548366546631</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3976678848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3151273727417</t>
+    <t xml:space="preserve">15.397668838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3151302337646</t>
   </si>
   <si>
     <t xml:space="preserve">15.4985437393188</t>
@@ -392,97 +392,97 @@
     <t xml:space="preserve">15.2509336471558</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3242998123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2967863082886</t>
+    <t xml:space="preserve">15.3242979049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2967882156372</t>
   </si>
   <si>
     <t xml:space="preserve">15.3793249130249</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1404933929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6177616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3884954452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1221523284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8286905288696</t>
+    <t xml:space="preserve">16.140495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6177644729614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3884944915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1221542358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8286876678467</t>
   </si>
   <si>
     <t xml:space="preserve">16.0762996673584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1771812438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0671329498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9845924377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1401062011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8099594116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6082077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6448841094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6078128814697</t>
+    <t xml:space="preserve">16.1771793365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0671291351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9845952987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1401081085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8099575042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6082038879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6448822021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.607816696167</t>
   </si>
   <si>
     <t xml:space="preserve">17.1584453582764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0300579071045</t>
+    <t xml:space="preserve">17.0300598144531</t>
   </si>
   <si>
     <t xml:space="preserve">17.1951313018799</t>
   </si>
   <si>
-    <t xml:space="preserve">17.332691192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0946388244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7828378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7553243637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8195190429688</t>
+    <t xml:space="preserve">17.3326873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0946407318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7828340530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7553262710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8195199966431</t>
   </si>
   <si>
     <t xml:space="preserve">15.9479093551636</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6361036300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6636190414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5627374649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4893732070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6085929870605</t>
+    <t xml:space="preserve">15.6361064910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6636180877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5627384185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893741607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6085948944092</t>
   </si>
   <si>
     <t xml:space="preserve">16.030445098877</t>
@@ -491,58 +491,58 @@
     <t xml:space="preserve">16.6999073028564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0579605102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5352268218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.544397354126</t>
+    <t xml:space="preserve">16.0579586029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.535228729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5443983078003</t>
   </si>
   <si>
     <t xml:space="preserve">15.7003021240234</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3609819412231</t>
+    <t xml:space="preserve">15.3609828948975</t>
   </si>
   <si>
     <t xml:space="preserve">15.1592283248901</t>
   </si>
   <si>
-    <t xml:space="preserve">15.233039855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3068513870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5467443466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6297798156738</t>
+    <t xml:space="preserve">15.2330408096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3068542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.546745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6297836303711</t>
   </si>
   <si>
     <t xml:space="preserve">15.7866334915161</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5190620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9746961593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3253049850464</t>
+    <t xml:space="preserve">15.5190629959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9746971130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.325306892395</t>
   </si>
   <si>
     <t xml:space="preserve">15.4175701141357</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4083423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0577354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7589530944824</t>
+    <t xml:space="preserve">15.4083452224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0577335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7589540481567</t>
   </si>
   <si>
     <t xml:space="preserve">16.2202796936035</t>
@@ -551,46 +551,46 @@
     <t xml:space="preserve">15.8235359191895</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3898906707764</t>
+    <t xml:space="preserve">15.3898916244507</t>
   </si>
   <si>
     <t xml:space="preserve">15.5006093978882</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2145881652832</t>
+    <t xml:space="preserve">15.2145872116089</t>
   </si>
   <si>
     <t xml:space="preserve">15.7774076461792</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9434852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7312717437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4694004058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0691242218018</t>
+    <t xml:space="preserve">15.9434833526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7312746047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4693984985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0691261291504</t>
   </si>
   <si>
     <t xml:space="preserve">17.142936706543</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0229930877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1060314178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9122734069824</t>
+    <t xml:space="preserve">17.0229911804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1060333251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9122714996338</t>
   </si>
   <si>
     <t xml:space="preserve">16.8384609222412</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3771362304688</t>
+    <t xml:space="preserve">16.3771305084229</t>
   </si>
   <si>
     <t xml:space="preserve">16.9768581390381</t>
@@ -602,19 +602,19 @@
     <t xml:space="preserve">17.0506706237793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6227207183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7795677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8164749145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.761116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3054809570312</t>
+    <t xml:space="preserve">17.6227169036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7795696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8164730072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7611122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3054866790771</t>
   </si>
   <si>
     <t xml:space="preserve">18.7760372161865</t>
@@ -623,37 +623,37 @@
     <t xml:space="preserve">18.8221683502197</t>
   </si>
   <si>
-    <t xml:space="preserve">19.421895980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4957065582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9882488250732</t>
+    <t xml:space="preserve">19.4218921661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4957103729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9882469177246</t>
   </si>
   <si>
     <t xml:space="preserve">18.7852630615234</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3296279907227</t>
+    <t xml:space="preserve">19.3296298980713</t>
   </si>
   <si>
     <t xml:space="preserve">19.2004566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0528354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9513416290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7299022674561</t>
+    <t xml:space="preserve">19.0528297424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9513397216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7299003601074</t>
   </si>
   <si>
     <t xml:space="preserve">18.886754989624</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8129425048828</t>
+    <t xml:space="preserve">18.8129405975342</t>
   </si>
   <si>
     <t xml:space="preserve">18.8037147521973</t>
@@ -665,16 +665,16 @@
     <t xml:space="preserve">18.4531059265137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2777996063232</t>
+    <t xml:space="preserve">18.2778034210205</t>
   </si>
   <si>
     <t xml:space="preserve">17.9917774200439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3331661224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4069747924805</t>
+    <t xml:space="preserve">18.3331623077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4069766998291</t>
   </si>
   <si>
     <t xml:space="preserve">18.3423881530762</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">18.2501220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">18.36083984375</t>
+    <t xml:space="preserve">18.3608417510986</t>
   </si>
   <si>
     <t xml:space="preserve">18.1578578948975</t>
@@ -692,19 +692,19 @@
     <t xml:space="preserve">18.2039890289307</t>
   </si>
   <si>
-    <t xml:space="preserve">18.388521194458</t>
+    <t xml:space="preserve">18.3885231018066</t>
   </si>
   <si>
     <t xml:space="preserve">18.4900150299072</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4992389678955</t>
+    <t xml:space="preserve">18.4992427825928</t>
   </si>
   <si>
     <t xml:space="preserve">18.6007289886475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9144325256348</t>
+    <t xml:space="preserve">18.914436340332</t>
   </si>
   <si>
     <t xml:space="preserve">19.2834968566895</t>
@@ -722,58 +722,58 @@
     <t xml:space="preserve">19.3204021453857</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8313961029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1174163818359</t>
+    <t xml:space="preserve">18.8313941955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1174182891846</t>
   </si>
   <si>
     <t xml:space="preserve">19.3757629394531</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9697971343994</t>
+    <t xml:space="preserve">18.9697895050049</t>
   </si>
   <si>
     <t xml:space="preserve">19.0897388458252</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2189121246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9052066802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0989646911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2558212280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1543254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7817325592041</t>
+    <t xml:space="preserve">19.2189102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9052085876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0989685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2558174133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1543235778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7817344665527</t>
   </si>
   <si>
     <t xml:space="preserve">19.8739967346191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2430591583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4829502105713</t>
+    <t xml:space="preserve">20.2430572509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4829483032227</t>
   </si>
   <si>
     <t xml:space="preserve">20.7136116027832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.824333190918</t>
+    <t xml:space="preserve">20.8243293762207</t>
   </si>
   <si>
     <t xml:space="preserve">20.8058776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0123977661133</t>
+    <t xml:space="preserve">20.0123958587646</t>
   </si>
   <si>
     <t xml:space="preserve">20.4737205505371</t>
@@ -794,25 +794,25 @@
     <t xml:space="preserve">20.4644947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3630046844482</t>
+    <t xml:space="preserve">20.3630027770996</t>
   </si>
   <si>
     <t xml:space="preserve">20.3906841278076</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5198535919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3445529937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6767082214355</t>
+    <t xml:space="preserve">20.5198554992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3445472717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6767063140869</t>
   </si>
   <si>
     <t xml:space="preserve">20.7228393554688</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3168716430664</t>
+    <t xml:space="preserve">20.316873550415</t>
   </si>
   <si>
     <t xml:space="preserve">20.639799118042</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">21.4978694915771</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3502445220947</t>
+    <t xml:space="preserve">21.3502426147461</t>
   </si>
   <si>
     <t xml:space="preserve">21.2210750579834</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1749439239502</t>
+    <t xml:space="preserve">21.1749420166016</t>
   </si>
   <si>
     <t xml:space="preserve">20.9904098510742</t>
@@ -836,55 +836,55 @@
     <t xml:space="preserve">20.9811820983887</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7874240875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1288070678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9627285003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.202615737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0826740264893</t>
+    <t xml:space="preserve">20.7874279022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1288051605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9627265930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2026214599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0826759338379</t>
   </si>
   <si>
     <t xml:space="preserve">20.5014019012451</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0273189544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8151035308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9719524383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1103572845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1011276245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1933917999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1380348205566</t>
+    <t xml:space="preserve">21.0273170471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8151073455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9719562530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1103553771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.101131439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1933898925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1380386352539</t>
   </si>
   <si>
     <t xml:space="preserve">20.79665184021</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0365390777588</t>
+    <t xml:space="preserve">21.0365409851074</t>
   </si>
   <si>
     <t xml:space="preserve">20.5936660766602</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1784763336182</t>
+    <t xml:space="preserve">20.1784725189209</t>
   </si>
   <si>
     <t xml:space="preserve">20.261510848999</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">20.2707366943359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1877002716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4921760559082</t>
+    <t xml:space="preserve">20.1876983642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4921741485596</t>
   </si>
   <si>
     <t xml:space="preserve">20.141565322876</t>
@@ -905,43 +905,43 @@
     <t xml:space="preserve">19.9109020233154</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0769786834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6617870330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7725067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1323375701904</t>
+    <t xml:space="preserve">20.0769805908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6617851257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7725028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1323394775391</t>
   </si>
   <si>
     <t xml:space="preserve">20.1600189208984</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4091396331787</t>
+    <t xml:space="preserve">20.4091358184814</t>
   </si>
   <si>
     <t xml:space="preserve">20.2984199523926</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8186378479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6986904144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7540531158447</t>
+    <t xml:space="preserve">19.818639755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.698694229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7540512084961</t>
   </si>
   <si>
     <t xml:space="preserve">19.5879745483398</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7909564971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9385814666748</t>
+    <t xml:space="preserve">19.790958404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9385833740234</t>
   </si>
   <si>
     <t xml:space="preserve">19.8647708892822</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">19.9754867553711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5418376922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5290832519531</t>
+    <t xml:space="preserve">19.5418395996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5290813446045</t>
   </si>
   <si>
     <t xml:space="preserve">20.1046619415283</t>
@@ -962,13 +962,13 @@
     <t xml:space="preserve">19.8370914459229</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5971984863281</t>
+    <t xml:space="preserve">19.5972023010254</t>
   </si>
   <si>
     <t xml:space="preserve">20.2799644470215</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9939441680908</t>
+    <t xml:space="preserve">19.9939384460449</t>
   </si>
   <si>
     <t xml:space="preserve">20.3537750244141</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">20.7043857574463</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2061500549316</t>
+    <t xml:space="preserve">20.2061538696289</t>
   </si>
   <si>
     <t xml:space="preserve">20.4275875091553</t>
@@ -986,31 +986,31 @@
     <t xml:space="preserve">20.7505187988281</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0549926757812</t>
+    <t xml:space="preserve">21.0549964904785</t>
   </si>
   <si>
     <t xml:space="preserve">20.5844402313232</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3353252410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.196928024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2338333129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7448215484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7079181671143</t>
+    <t xml:space="preserve">20.3353271484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1969261169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.233829498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7448234558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7079219818115</t>
   </si>
   <si>
     <t xml:space="preserve">19.634105682373</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8463153839111</t>
+    <t xml:space="preserve">19.8463172912598</t>
   </si>
   <si>
     <t xml:space="preserve">19.9570331573486</t>
@@ -1019,13 +1019,13 @@
     <t xml:space="preserve">20.3814563751221</t>
   </si>
   <si>
-    <t xml:space="preserve">19.855541229248</t>
+    <t xml:space="preserve">19.8555450439453</t>
   </si>
   <si>
     <t xml:space="preserve">19.4034442901611</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1266422271729</t>
+    <t xml:space="preserve">19.1266460418701</t>
   </si>
   <si>
     <t xml:space="preserve">18.6560916900635</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">18.7114505767822</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5084648132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8682994842529</t>
+    <t xml:space="preserve">18.5084686279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8683013916016</t>
   </si>
   <si>
     <t xml:space="preserve">18.5545978546143</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4346561431885</t>
+    <t xml:space="preserve">18.4346542358398</t>
   </si>
   <si>
     <t xml:space="preserve">18.5361461639404</t>
@@ -1058,37 +1058,37 @@
     <t xml:space="preserve">19.0067005157471</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8497562408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8219432830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4047069549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1821823120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7834911346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7278575897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5238761901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5516929626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8205757141113</t>
+    <t xml:space="preserve">18.8497581481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8219394683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4047088623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1821842193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7834892272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7278594970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5238742828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5516910552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.82057762146</t>
   </si>
   <si>
     <t xml:space="preserve">17.7742176055908</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8483924865723</t>
+    <t xml:space="preserve">17.8483905792236</t>
   </si>
   <si>
     <t xml:space="preserve">18.1450958251953</t>
@@ -1100,196 +1100,196 @@
     <t xml:space="preserve">18.4603366851807</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2841701507568</t>
+    <t xml:space="preserve">18.2841739654541</t>
   </si>
   <si>
     <t xml:space="preserve">18.0431041717529</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3676166534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2378120422363</t>
+    <t xml:space="preserve">18.3676204681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2378101348877</t>
   </si>
   <si>
     <t xml:space="preserve">18.0987358093262</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5437831878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6457767486572</t>
+    <t xml:space="preserve">18.5437850952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6457748413086</t>
   </si>
   <si>
     <t xml:space="preserve">18.5716018676758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5623302459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4881553649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2285385131836</t>
+    <t xml:space="preserve">18.5623264312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4881534576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2285442352295</t>
   </si>
   <si>
     <t xml:space="preserve">18.2563552856445</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3212623596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3583469390869</t>
+    <t xml:space="preserve">18.3212585449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3583488464355</t>
   </si>
   <si>
     <t xml:space="preserve">18.3490772247314</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5345115661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5808753967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.469612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2656269073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3768939971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7755832672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0537376403809</t>
+    <t xml:space="preserve">18.5345153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5808734893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4696140289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2656288146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3768901824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7755813598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0537395477295</t>
   </si>
   <si>
     <t xml:space="preserve">19.3318958282471</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6100521087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3981628417969</t>
+    <t xml:space="preserve">19.6100559234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3981647491455</t>
   </si>
   <si>
     <t xml:space="preserve">21.1399154663086</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4180736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3717136383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2326374053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4644317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3253517150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6035118103027</t>
+    <t xml:space="preserve">21.4180717468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.371711730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2326316833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4644298553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3253555297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6035079956055</t>
   </si>
   <si>
     <t xml:space="preserve">21.6498699188232</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8617610931396</t>
+    <t xml:space="preserve">20.861759185791</t>
   </si>
   <si>
     <t xml:space="preserve">20.3054447174072</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9081192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4908847808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6299629211426</t>
+    <t xml:space="preserve">20.9081172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4908828735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6299610137939</t>
   </si>
   <si>
     <t xml:space="preserve">20.5836029052734</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9544773101807</t>
+    <t xml:space="preserve">20.9544792175293</t>
   </si>
   <si>
     <t xml:space="preserve">21.0471954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0008354187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7226791381836</t>
+    <t xml:space="preserve">21.0008373260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7226810455322</t>
   </si>
   <si>
     <t xml:space="preserve">20.5372428894043</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5571479797363</t>
+    <t xml:space="preserve">21.557149887085</t>
   </si>
   <si>
     <t xml:space="preserve">22.0671043395996</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7425899505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9280242919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8353080749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6763210296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0935554504395</t>
+    <t xml:space="preserve">21.7425918579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9280261993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8353061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6763191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0935573577881</t>
   </si>
   <si>
     <t xml:space="preserve">20.1663665771484</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0736465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7690391540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4445247650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8153972625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1862754821777</t>
+    <t xml:space="preserve">20.0736446380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7690410614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.444522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8153991699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1862773895264</t>
   </si>
   <si>
     <t xml:space="preserve">20.2590866088867</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3518047332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9809284210205</t>
+    <t xml:space="preserve">20.3518028259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9809303283691</t>
   </si>
   <si>
     <t xml:space="preserve">18.9146614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0073776245117</t>
+    <t xml:space="preserve">19.007381439209</t>
   </si>
   <si>
     <t xml:space="preserve">19.1928195953369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6564178466797</t>
+    <t xml:space="preserve">19.6564140319824</t>
   </si>
   <si>
     <t xml:space="preserve">19.4709739685059</t>
@@ -1304,82 +1304,82 @@
     <t xml:space="preserve">19.8418502807617</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0272884368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8882122039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7491302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7954883575439</t>
+    <t xml:space="preserve">20.0272846221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8882102966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7491321563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7954940795898</t>
   </si>
   <si>
     <t xml:space="preserve">19.2855358123779</t>
   </si>
   <si>
-    <t xml:space="preserve">19.424617767334</t>
+    <t xml:space="preserve">19.4246158599854</t>
   </si>
   <si>
     <t xml:space="preserve">19.3782558441162</t>
   </si>
   <si>
-    <t xml:space="preserve">19.517333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5636920928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1464595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1000995635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2391757965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7027721405029</t>
+    <t xml:space="preserve">19.5173320770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5636959075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1464557647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.10009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2391796112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7027702331543</t>
   </si>
   <si>
     <t xml:space="preserve">21.2789936065674</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9345703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5980529785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.205904006958</t>
+    <t xml:space="preserve">19.9345722198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.598051071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2059049606323</t>
   </si>
   <si>
     <t xml:space="preserve">15.5953235626221</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6681346893311</t>
+    <t xml:space="preserve">14.6681337356567</t>
   </si>
   <si>
     <t xml:space="preserve">14.371434211731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7052211761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2986211776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5211486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8920211791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4284296035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2244482040405</t>
+    <t xml:space="preserve">14.7052221298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2986240386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5211477279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8920240402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4284286499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2244472503662</t>
   </si>
   <si>
     <t xml:space="preserve">15.3542537689209</t>
@@ -1388,22 +1388,22 @@
     <t xml:space="preserve">15.7622194290161</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6880416870117</t>
+    <t xml:space="preserve">15.688042640686</t>
   </si>
   <si>
     <t xml:space="preserve">15.5582361221313</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4840593338013</t>
+    <t xml:space="preserve">15.4840612411499</t>
   </si>
   <si>
     <t xml:space="preserve">15.2800788879395</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9092044830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7599258422852</t>
+    <t xml:space="preserve">14.9092016220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7599239349365</t>
   </si>
   <si>
     <t xml:space="preserve">14.4800271987915</t>
@@ -1415,22 +1415,22 @@
     <t xml:space="preserve">14.3494091033936</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8159046173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8345632553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5546674728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0398235321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3383808135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1704406738281</t>
+    <t xml:space="preserve">14.8159055709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8345642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5546684265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0398225784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3383798599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1704397201538</t>
   </si>
   <si>
     <t xml:space="preserve">13.9762115478516</t>
@@ -1448,79 +1448,79 @@
     <t xml:space="preserve">14.2374496459961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0695104598999</t>
+    <t xml:space="preserve">14.0695123672485</t>
   </si>
   <si>
     <t xml:space="preserve">14.0508518218994</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1254930496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8642539978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5470371246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5283765792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6963157653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9575519561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1068296432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4240484237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6479663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.114462852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0211639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.927864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9651832580566</t>
+    <t xml:space="preserve">14.1254920959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8642520904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5470361709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5283756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6963138580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9575529098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1068315505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4240465164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6479654312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1144618988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0211629867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9278631210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.965184211731</t>
   </si>
   <si>
     <t xml:space="preserve">14.7972440719604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0025033950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.058482170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0958003997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4316806793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8608560562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7005481719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7751865386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7938480377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3833293914795</t>
+    <t xml:space="preserve">15.0025014877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0584812164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0958013534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4316816329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8608541488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7005462646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7751884460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7938461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3833312988281</t>
   </si>
   <si>
     <t xml:space="preserve">16.3086891174316</t>
@@ -1529,37 +1529,37 @@
     <t xml:space="preserve">16.1594123840332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2527122497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8795156478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7675561904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7115783691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0287933349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.047456741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1407527923584</t>
+    <t xml:space="preserve">16.2527084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8795175552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7675542831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7115774154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0287914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0474548339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1407508850098</t>
   </si>
   <si>
     <t xml:space="preserve">16.5139503479004</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4019870758057</t>
+    <t xml:space="preserve">16.4019889831543</t>
   </si>
   <si>
     <t xml:space="preserve">16.178071975708</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3273468017578</t>
+    <t xml:space="preserve">16.3273506164551</t>
   </si>
   <si>
     <t xml:space="preserve">16.3460102081299</t>
@@ -1568,34 +1568,31 @@
     <t xml:space="preserve">16.1220932006836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4952907562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6072444915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3646717071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.215389251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7488946914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8421964645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8235340118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0101299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.898175239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2340507507324</t>
+    <t xml:space="preserve">16.495288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6072483062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3646697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2153930664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7488956451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8421974182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0101318359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8981742858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2340488433838</t>
   </si>
   <si>
     <t xml:space="preserve">16.2900295257568</t>
@@ -1604,37 +1601,37 @@
     <t xml:space="preserve">16.4206485748291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6632308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8311653137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3536396026611</t>
+    <t xml:space="preserve">16.6632289886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8311672210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3536415100098</t>
   </si>
   <si>
     <t xml:space="preserve">18.1560134887695</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1373538970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1186943054199</t>
+    <t xml:space="preserve">18.1373558044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1186962127686</t>
   </si>
   <si>
     <t xml:space="preserve">17.9880752563477</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4096240997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0177631378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8871459960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8684864044189</t>
+    <t xml:space="preserve">17.4096202850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.017765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8871479034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8684844970703</t>
   </si>
   <si>
     <t xml:space="preserve">16.6259078979492</t>
@@ -1643,13 +1640,13 @@
     <t xml:space="preserve">16.5326061248779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8498229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7192077636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9431209564209</t>
+    <t xml:space="preserve">16.8498249053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7192096710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9431285858154</t>
   </si>
   <si>
     <t xml:space="preserve">17.0364227294922</t>
@@ -1658,22 +1655,22 @@
     <t xml:space="preserve">17.1110649108887</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6445693969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1034336090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3943576812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4130172729492</t>
+    <t xml:space="preserve">16.644567489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1034317016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3943586349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4130182266235</t>
   </si>
   <si>
     <t xml:space="preserve">15.3570394515991</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0771427154541</t>
+    <t xml:space="preserve">15.0771417617798</t>
   </si>
   <si>
     <t xml:space="preserve">14.591986656189</t>
@@ -1682,7 +1679,7 @@
     <t xml:space="preserve">14.7039461135864</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9838418960571</t>
+    <t xml:space="preserve">14.9838428497314</t>
   </si>
   <si>
     <t xml:space="preserve">14.6666259765625</t>
@@ -1694,40 +1691,43 @@
     <t xml:space="preserve">14.741265296936</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4053869247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5733251571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2747688293457</t>
+    <t xml:space="preserve">14.405387878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5733270645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.27476978302</t>
   </si>
   <si>
     <t xml:space="preserve">14.7226057052612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.461368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3680667877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5360059738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4689989089966</t>
+    <t xml:space="preserve">14.4613676071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3680686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5360069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4689998626709</t>
   </si>
   <si>
     <t xml:space="preserve">15.3010606765747</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2824001312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5622968673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1331205368042</t>
+    <t xml:space="preserve">15.282398223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5622978210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1331214904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9092025756836</t>
   </si>
   <si>
     <t xml:space="preserve">15.4876594543457</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">15.3197202682495</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2264213562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9465217590332</t>
+    <t xml:space="preserve">15.2264194488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9465227127075</t>
   </si>
   <si>
     <t xml:space="preserve">14.7785844802856</t>
@@ -1748,94 +1748,94 @@
     <t xml:space="preserve">14.4427080154419</t>
   </si>
   <si>
-    <t xml:space="preserve">14.685284614563</t>
+    <t xml:space="preserve">14.6852865219116</t>
   </si>
   <si>
     <t xml:space="preserve">14.5173473358154</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2001295089722</t>
+    <t xml:space="preserve">14.2001314163208</t>
   </si>
   <si>
     <t xml:space="preserve">14.1814699172974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9948711395264</t>
+    <t xml:space="preserve">13.9948720932007</t>
   </si>
   <si>
     <t xml:space="preserve">13.8082733154297</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6776552200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3307495117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1628103256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7149753570557</t>
+    <t xml:space="preserve">13.6776542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3307485580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1628112792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7149744033813</t>
   </si>
   <si>
     <t xml:space="preserve">13.752293586731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9388914108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8455934524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1441507339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9202337265015</t>
+    <t xml:space="preserve">13.938892364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8455924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1441497802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9202327728271</t>
   </si>
   <si>
     <t xml:space="preserve">14.4986877441406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9015712738037</t>
+    <t xml:space="preserve">13.901572227478</t>
   </si>
   <si>
     <t xml:space="preserve">15.2637405395508</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0881719589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0135326385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3867292404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8905429840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1891012191772</t>
+    <t xml:space="preserve">14.088171005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0135316848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3867282867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8905439376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1891031265259</t>
   </si>
   <si>
     <t xml:space="preserve">14.9740743637085</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9552392959595</t>
+    <t xml:space="preserve">14.9552373886108</t>
   </si>
   <si>
     <t xml:space="preserve">14.8045568466187</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7103776931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7857208251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5768041610718</t>
+    <t xml:space="preserve">14.7103796005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.785719871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2754373550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5768060684204</t>
   </si>
   <si>
     <t xml:space="preserve">16.3490505218506</t>
@@ -1844,16 +1844,16 @@
     <t xml:space="preserve">16.2172031402588</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5956382751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5579690933228</t>
+    <t xml:space="preserve">15.5956373214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5579700469971</t>
   </si>
   <si>
     <t xml:space="preserve">15.4261207580566</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4449577331543</t>
+    <t xml:space="preserve">15.4449558258057</t>
   </si>
   <si>
     <t xml:space="preserve">15.3507795333862</t>
@@ -1862,31 +1862,31 @@
     <t xml:space="preserve">15.6521472930908</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6898145675659</t>
+    <t xml:space="preserve">15.6898155212402</t>
   </si>
   <si>
     <t xml:space="preserve">16.066520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6144752502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5014619827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5391330718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9346733093262</t>
+    <t xml:space="preserve">15.6144733428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5014629364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5391321182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9346742630005</t>
   </si>
   <si>
     <t xml:space="preserve">15.8781690597534</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3131093978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7274856567383</t>
+    <t xml:space="preserve">15.3131084442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7274866104126</t>
   </si>
   <si>
     <t xml:space="preserve">15.463791847229</t>
@@ -1895,13 +1895,13 @@
     <t xml:space="preserve">15.3319444656372</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4826278686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1435928344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0117444992065</t>
+    <t xml:space="preserve">15.482626914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1435918807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0117435455322</t>
   </si>
   <si>
     <t xml:space="preserve">14.8798961639404</t>
@@ -1910,55 +1910,55 @@
     <t xml:space="preserve">15.1059217453003</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6538743972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8422269821167</t>
+    <t xml:space="preserve">14.6538734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.842227935791</t>
   </si>
   <si>
     <t xml:space="preserve">14.4090156555176</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9381313323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8439540863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1264839172363</t>
+    <t xml:space="preserve">13.9381322860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.843955039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.126482963562</t>
   </si>
   <si>
     <t xml:space="preserve">14.5031900405884</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6915445327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.484356880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2960014343262</t>
+    <t xml:space="preserve">14.6915454864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4843559265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2960023880005</t>
   </si>
   <si>
     <t xml:space="preserve">14.3336734771729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5220260620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2394971847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.182991027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9569673538208</t>
+    <t xml:space="preserve">14.522027015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2394962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1829919815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9569664001465</t>
   </si>
   <si>
     <t xml:space="preserve">13.5990953445435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0528717041016</t>
+    <t xml:space="preserve">13.0528726577759</t>
   </si>
   <si>
     <t xml:space="preserve">12.9210243225098</t>
@@ -1967,13 +1967,13 @@
     <t xml:space="preserve">13.2788963317871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9963665008545</t>
+    <t xml:space="preserve">12.9963655471802</t>
   </si>
   <si>
     <t xml:space="preserve">12.7138357162476</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371295928955</t>
+    <t xml:space="preserve">12.3371286392212</t>
   </si>
   <si>
     <t xml:space="preserve">12.0922718048096</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">11.8662481307983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3953647613525</t>
+    <t xml:space="preserve">11.3953657150269</t>
   </si>
   <si>
     <t xml:space="preserve">10.9621515274048</t>
@@ -1991,49 +1991,49 @@
     <t xml:space="preserve">10.0580577850342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88854026794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53066921234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85259628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35173320770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0426778793335</t>
+    <t xml:space="preserve">9.88854122161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53066730499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8525972366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35173225402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04267692565918</t>
   </si>
   <si>
     <t xml:space="preserve">8.49472713470459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04094982147217</t>
+    <t xml:space="preserve">9.04094886779785</t>
   </si>
   <si>
     <t xml:space="preserve">10.0957279205322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6796236038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8474111557007</t>
+    <t xml:space="preserve">10.6796226501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.847412109375</t>
   </si>
   <si>
     <t xml:space="preserve">12.8080139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5272121429443</t>
+    <t xml:space="preserve">11.52721118927</t>
   </si>
   <si>
     <t xml:space="preserve">10.8868112564087</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8491411209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5666103363037</t>
+    <t xml:space="preserve">10.8491401672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.566611289978</t>
   </si>
   <si>
     <t xml:space="preserve">10.0015506744385</t>
@@ -2042,43 +2042,43 @@
     <t xml:space="preserve">10.2652454376221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5477743148804</t>
+    <t xml:space="preserve">10.5477752685547</t>
   </si>
   <si>
     <t xml:space="preserve">10.6607866287231</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0374927520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8303050994873</t>
+    <t xml:space="preserve">11.0374937057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.830304145813</t>
   </si>
   <si>
     <t xml:space="preserve">10.5101041793823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1333980560303</t>
+    <t xml:space="preserve">10.133397102356</t>
   </si>
   <si>
     <t xml:space="preserve">9.81319808959961</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1522331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4347639083862</t>
+    <t xml:space="preserve">10.1522340774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4347629547119</t>
   </si>
   <si>
     <t xml:space="preserve">10.3594217300415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6984577178955</t>
+    <t xml:space="preserve">10.6984567642212</t>
   </si>
   <si>
     <t xml:space="preserve">10.6419525146484</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6231164932251</t>
+    <t xml:space="preserve">10.6231155395508</t>
   </si>
   <si>
     <t xml:space="preserve">10.7361278533936</t>
@@ -2090,22 +2090,22 @@
     <t xml:space="preserve">10.4724340438843</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9244813919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8679752349854</t>
+    <t xml:space="preserve">10.9244823455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8679761886597</t>
   </si>
   <si>
     <t xml:space="preserve">11.4141988754272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.489541053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9809885025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3388586044312</t>
+    <t xml:space="preserve">11.4895401000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9809865951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3388576507568</t>
   </si>
   <si>
     <t xml:space="preserve">11.4330358505249</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">11.7155637741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9227523803711</t>
+    <t xml:space="preserve">11.9227533340454</t>
   </si>
   <si>
     <t xml:space="preserve">12.2052822113037</t>
@@ -2132,13 +2132,13 @@
     <t xml:space="preserve">11.150505065918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9433164596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1128349304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0186586380005</t>
+    <t xml:space="preserve">10.9433174133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1128339767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0186576843262</t>
   </si>
   <si>
     <t xml:space="preserve">10.8114700317383</t>
@@ -2147,37 +2147,37 @@
     <t xml:space="preserve">10.7172927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6042823791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3405857086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3782577514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5854454040527</t>
+    <t xml:space="preserve">10.6042814254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3405866622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3782587051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5854444503784</t>
   </si>
   <si>
     <t xml:space="preserve">11.1316680908203</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2635173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.207010269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9998235702515</t>
+    <t xml:space="preserve">11.2635183334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2070112228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9998226165771</t>
   </si>
   <si>
     <t xml:space="preserve">10.9056463241577</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5289402008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3029165267944</t>
+    <t xml:space="preserve">10.5289392471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3029155731201</t>
   </si>
   <si>
     <t xml:space="preserve">10.3970928192139</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">11.5648822784424</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3576946258545</t>
+    <t xml:space="preserve">11.3576936721802</t>
   </si>
   <si>
     <t xml:space="preserve">11.6025533676147</t>
@@ -2195,49 +2195,49 @@
     <t xml:space="preserve">11.4518690109253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.546046257019</t>
+    <t xml:space="preserve">11.5460472106934</t>
   </si>
   <si>
     <t xml:space="preserve">11.4707059860229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5837173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6590576171875</t>
+    <t xml:space="preserve">11.5837163925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6590585708618</t>
   </si>
   <si>
     <t xml:space="preserve">12.1487770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0546016693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0357637405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8850841522217</t>
+    <t xml:space="preserve">12.0546007156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0357646942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.885082244873</t>
   </si>
   <si>
     <t xml:space="preserve">11.9039182662964</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7344007492065</t>
+    <t xml:space="preserve">11.7343997955322</t>
   </si>
   <si>
     <t xml:space="preserve">11.6778936386108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1693410873413</t>
+    <t xml:space="preserve">11.169340133667</t>
   </si>
   <si>
     <t xml:space="preserve">12.5631542205811</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5614252090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2977304458618</t>
+    <t xml:space="preserve">13.5614242553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2977294921875</t>
   </si>
   <si>
     <t xml:space="preserve">13.7686138153076</t>
@@ -2246,34 +2246,34 @@
     <t xml:space="preserve">13.5049200057983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.147047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3354005813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3730726242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0152015686035</t>
+    <t xml:space="preserve">13.1470489501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3354015350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3730707168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0152006149292</t>
   </si>
   <si>
     <t xml:space="preserve">13.2412242889404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0323066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6367654800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3165664672852</t>
+    <t xml:space="preserve">14.0323085784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6367673873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3165674209595</t>
   </si>
   <si>
     <t xml:space="preserve">13.0340366363525</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3919076919556</t>
+    <t xml:space="preserve">13.3919067382812</t>
   </si>
   <si>
     <t xml:space="preserve">13.0905418395996</t>
@@ -2282,10 +2282,10 @@
     <t xml:space="preserve">11.9415884017944</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9792604446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2429533004761</t>
+    <t xml:space="preserve">11.9792594909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2429523468018</t>
   </si>
   <si>
     <t xml:space="preserve">12.3559646606445</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">12.7326717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9586963653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2223901748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3542385101318</t>
+    <t xml:space="preserve">12.9586954116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2223892211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3542375564575</t>
   </si>
   <si>
     <t xml:space="preserve">13.4672498703003</t>
@@ -2315,10 +2315,10 @@
     <t xml:space="preserve">13.5450410842896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3167552947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3548030853271</t>
+    <t xml:space="preserve">13.3167543411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3548021316528</t>
   </si>
   <si>
     <t xml:space="preserve">13.2216339111328</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">13.4118747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7543048858643</t>
+    <t xml:space="preserve">13.7543058395386</t>
   </si>
   <si>
     <t xml:space="preserve">13.7923526763916</t>
@@ -2336,22 +2336,22 @@
     <t xml:space="preserve">13.6591854095459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.077712059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0586881637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1157598495483</t>
+    <t xml:space="preserve">14.0777130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.058687210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1157608032227</t>
   </si>
   <si>
     <t xml:space="preserve">13.8874731063843</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6021146774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3738260269165</t>
+    <t xml:space="preserve">13.6021137237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3738269805908</t>
   </si>
   <si>
     <t xml:space="preserve">13.6782093048096</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">13.6972332000732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6211366653442</t>
+    <t xml:space="preserve">13.6211376190186</t>
   </si>
   <si>
     <t xml:space="preserve">13.7733278274536</t>
@@ -2381,115 +2381,115 @@
     <t xml:space="preserve">14.6103820800781</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5342855453491</t>
+    <t xml:space="preserve">14.5342864990234</t>
   </si>
   <si>
     <t xml:space="preserve">14.8957414627075</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9337892532349</t>
+    <t xml:space="preserve">14.9337882995605</t>
   </si>
   <si>
     <t xml:space="preserve">16.3796062469482</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2274150848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0752258300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.713770866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8469371795654</t>
+    <t xml:space="preserve">16.2274169921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0752277374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7137718200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8469381332397</t>
   </si>
   <si>
     <t xml:space="preserve">15.6947460174561</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5045070648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2191486358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6376752853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2381715774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3332929611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6186504364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7518177032471</t>
+    <t xml:space="preserve">15.504506111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2191476821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6376762390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2381725311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3332920074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6186494827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7518167495728</t>
   </si>
   <si>
     <t xml:space="preserve">16.1513214111328</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4937515258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6649684906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5698490142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5317974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6078948974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5888710021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.045446395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0264225006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0834922790527</t>
+    <t xml:space="preserve">16.4937534332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.664966583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5698509216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5317993164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6078929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5888690948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0454483032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0264205932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0834903717041</t>
   </si>
   <si>
     <t xml:space="preserve">16.8742294311523</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3415603637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3225364685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7981338500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5508232116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8361835479736</t>
+    <t xml:space="preserve">16.3415584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3225383758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7981357574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5508251190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.836181640625</t>
   </si>
   <si>
     <t xml:space="preserve">16.81715965271</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7410621643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8444519042969</t>
+    <t xml:space="preserve">16.7410640716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8444499969482</t>
   </si>
   <si>
     <t xml:space="preserve">17.9585971832275</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1868839263916</t>
+    <t xml:space="preserve">18.186882019043</t>
   </si>
   <si>
     <t xml:space="preserve">19.499532699585</t>
@@ -2498,37 +2498,37 @@
     <t xml:space="preserve">19.7848930358887</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1653728485107</t>
+    <t xml:space="preserve">20.1653709411621</t>
   </si>
   <si>
     <t xml:space="preserve">19.6422138214111</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5934085845947</t>
+    <t xml:space="preserve">20.5934104919434</t>
   </si>
   <si>
     <t xml:space="preserve">20.3556118011475</t>
   </si>
   <si>
-    <t xml:space="preserve">19.975133895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8324546813965</t>
+    <t xml:space="preserve">19.9751319885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8324527740479</t>
   </si>
   <si>
     <t xml:space="preserve">19.7373313903809</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8800106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2604885101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4031715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.498291015625</t>
+    <t xml:space="preserve">19.880012512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2604904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.403169631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4982891082764</t>
   </si>
   <si>
     <t xml:space="preserve">20.8312091827393</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">20.7360897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2129325866699</t>
+    <t xml:space="preserve">20.2129306793213</t>
   </si>
   <si>
     <t xml:space="preserve">19.9275722503662</t>
@@ -2546,13 +2546,13 @@
     <t xml:space="preserve">20.7836494445801</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5946559906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3568534851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2141761779785</t>
+    <t xml:space="preserve">19.594654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3568553924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2141742706299</t>
   </si>
   <si>
     <t xml:space="preserve">19.4044132232666</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">19.0239353179932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1178092956543</t>
+    <t xml:space="preserve">20.1178112030029</t>
   </si>
   <si>
     <t xml:space="preserve">20.3080501556396</t>
@@ -2573,16 +2573,16 @@
     <t xml:space="preserve">20.0702514648438</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9738903045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5446033477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1641292572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6397266387939</t>
+    <t xml:space="preserve">20.9738883972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.544605255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1641273498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6397247314453</t>
   </si>
   <si>
     <t xml:space="preserve">21.5921669006348</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">21.7348461151123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8299655914307</t>
+    <t xml:space="preserve">21.829963684082</t>
   </si>
   <si>
     <t xml:space="preserve">21.0690078735352</t>
@@ -2606,16 +2606,16 @@
     <t xml:space="preserve">21.2116870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3068046569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1628856658936</t>
+    <t xml:space="preserve">21.3068065643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1628837585449</t>
   </si>
   <si>
     <t xml:space="preserve">22.6384811401367</t>
   </si>
   <si>
-    <t xml:space="preserve">23.161642074585</t>
+    <t xml:space="preserve">23.1616439819336</t>
   </si>
   <si>
     <t xml:space="preserve">22.4958038330078</t>
@@ -2630,22 +2630,22 @@
     <t xml:space="preserve">21.4970474243164</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2592487335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6885299682617</t>
+    <t xml:space="preserve">21.2592506408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6885318756104</t>
   </si>
   <si>
     <t xml:space="preserve">20.6409683227539</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7824077606201</t>
+    <t xml:space="preserve">21.7824058532715</t>
   </si>
   <si>
     <t xml:space="preserve">24.3506393432617</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7799205780029</t>
+    <t xml:space="preserve">23.7799186706543</t>
   </si>
   <si>
     <t xml:space="preserve">23.3043212890625</t>
@@ -2654,16 +2654,16 @@
     <t xml:space="preserve">23.2567615509033</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0189628601074</t>
+    <t xml:space="preserve">23.0189609527588</t>
   </si>
   <si>
     <t xml:space="preserve">23.1140804290771</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3518772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0665245056152</t>
+    <t xml:space="preserve">23.351879119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0665225982666</t>
   </si>
   <si>
     <t xml:space="preserve">23.5896797180176</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">25.6823120117188</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6347560882568</t>
+    <t xml:space="preserve">25.6347522735596</t>
   </si>
   <si>
     <t xml:space="preserve">25.7774333953857</t>
@@ -2747,13 +2747,13 @@
     <t xml:space="preserve">26.3005886077881</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3957118988037</t>
+    <t xml:space="preserve">26.3957099914551</t>
   </si>
   <si>
     <t xml:space="preserve">27.2993469238281</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2042293548584</t>
+    <t xml:space="preserve">27.2042274475098</t>
   </si>
   <si>
     <t xml:space="preserve">27.1566677093506</t>
@@ -2780,10 +2780,10 @@
     <t xml:space="preserve">27.537145614624</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3469047546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0615482330322</t>
+    <t xml:space="preserve">27.3469066619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0615501403809</t>
   </si>
   <si>
     <t xml:space="preserve">26.7761898040771</t>
@@ -2792,16 +2792,16 @@
     <t xml:space="preserve">26.9664268493652</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8713092803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5383892059326</t>
+    <t xml:space="preserve">26.8713073730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.538387298584</t>
   </si>
   <si>
     <t xml:space="preserve">26.7469043731689</t>
   </si>
   <si>
-    <t xml:space="preserve">26.077033996582</t>
+    <t xml:space="preserve">26.0770359039307</t>
   </si>
   <si>
     <t xml:space="preserve">25.6464042663574</t>
@@ -2813,13 +2813,13 @@
     <t xml:space="preserve">24.4023628234863</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5459060668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9717350006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5937557220459</t>
+    <t xml:space="preserve">24.5459041595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9717330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5937538146973</t>
   </si>
   <si>
     <t xml:space="preserve">24.4980602264404</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">24.9286880493164</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2205772399902</t>
+    <t xml:space="preserve">26.2205791473389</t>
   </si>
   <si>
     <t xml:space="preserve">26.6512088775635</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">25.7421016693115</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6942520141602</t>
+    <t xml:space="preserve">25.6942539215088</t>
   </si>
   <si>
     <t xml:space="preserve">25.3114700317383</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5507106781006</t>
+    <t xml:space="preserve">25.550708770752</t>
   </si>
   <si>
     <t xml:space="preserve">24.9765377044678</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">25.8856430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7899513244629</t>
+    <t xml:space="preserve">25.7899475097656</t>
   </si>
   <si>
     <t xml:space="preserve">25.9813404083252</t>
@@ -2873,16 +2873,16 @@
     <t xml:space="preserve">24.6894493103027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5028610229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3593196868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8808403015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3066654205322</t>
+    <t xml:space="preserve">25.5028629302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.359317779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.880838394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3066673278809</t>
   </si>
   <si>
     <t xml:space="preserve">22.8233871459961</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">22.6319961547852</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4932518005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8712329864502</t>
+    <t xml:space="preserve">23.4932537078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8712348937988</t>
   </si>
   <si>
     <t xml:space="preserve">22.7755374908447</t>
@@ -2906,16 +2906,16 @@
     <t xml:space="preserve">23.2540149688721</t>
   </si>
   <si>
-    <t xml:space="preserve">22.297061920166</t>
+    <t xml:space="preserve">22.2970600128174</t>
   </si>
   <si>
     <t xml:space="preserve">21.81858253479</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6750373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4357986450195</t>
+    <t xml:space="preserve">21.6750392913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4358005523682</t>
   </si>
   <si>
     <t xml:space="preserve">22.4884510040283</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">22.3449096679688</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9621276855469</t>
+    <t xml:space="preserve">21.9621257781982</t>
   </si>
   <si>
     <t xml:space="preserve">23.0147762298584</t>
@@ -2936,16 +2936,16 @@
     <t xml:space="preserve">22.009973526001</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9142818450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2444114685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0051727294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3831481933594</t>
+    <t xml:space="preserve">21.9142799377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2444095611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0051708221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.383150100708</t>
   </si>
   <si>
     <t xml:space="preserve">19.378345489502</t>
@@ -2966,13 +2966,13 @@
     <t xml:space="preserve">18.0098991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7849998474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.842414855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8950691223145</t>
+    <t xml:space="preserve">16.7849979400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8424167633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8950672149658</t>
   </si>
   <si>
     <t xml:space="preserve">18.0290393829346</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">18.2012920379639</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5649337768555</t>
+    <t xml:space="preserve">18.5649356842041</t>
   </si>
   <si>
     <t xml:space="preserve">18.2587089538574</t>
@@ -3011,16 +3011,16 @@
     <t xml:space="preserve">18.9477157592773</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0625514984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4740428924561</t>
+    <t xml:space="preserve">19.0625534057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4740447998047</t>
   </si>
   <si>
     <t xml:space="preserve">18.9859962463379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0816917419434</t>
+    <t xml:space="preserve">19.0816898345947</t>
   </si>
   <si>
     <t xml:space="preserve">18.5075168609619</t>
@@ -3032,13 +3032,13 @@
     <t xml:space="preserve">18.5266571044922</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2778511047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.603214263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2826538085938</t>
+    <t xml:space="preserve">18.2778491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6032123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2826519012451</t>
   </si>
   <si>
     <t xml:space="preserve">19.6175842285156</t>
@@ -3047,19 +3047,19 @@
     <t xml:space="preserve">19.0051345825195</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6223526000977</t>
+    <t xml:space="preserve">18.622350692749</t>
   </si>
   <si>
     <t xml:space="preserve">18.7946033477783</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2348041534424</t>
+    <t xml:space="preserve">19.234806060791</t>
   </si>
   <si>
     <t xml:space="preserve">19.1391086578369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4165878295898</t>
+    <t xml:space="preserve">17.4165897369385</t>
   </si>
   <si>
     <t xml:space="preserve">17.6079788208008</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">20.8616275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5745429992676</t>
+    <t xml:space="preserve">20.5745410919189</t>
   </si>
   <si>
     <t xml:space="preserve">20.9094753265381</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">21.3401050567627</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2922592163086</t>
+    <t xml:space="preserve">21.29225730896</t>
   </si>
   <si>
     <t xml:space="preserve">21.7228889465332</t>
@@ -3098,82 +3098,82 @@
     <t xml:space="preserve">22.9669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1583232879639</t>
+    <t xml:space="preserve">23.1583213806152</t>
   </si>
   <si>
     <t xml:space="preserve">22.3927574157715</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0578193664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2874565124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6702346801758</t>
+    <t xml:space="preserve">22.0578231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2874546051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6702365875244</t>
   </si>
   <si>
     <t xml:space="preserve">19.7611293792725</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0960655212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3353042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7132835388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1199703216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6606292724609</t>
+    <t xml:space="preserve">20.0960636138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3353023529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7132816314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1199684143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6606311798096</t>
   </si>
   <si>
     <t xml:space="preserve">18.4692401885986</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4548664093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6797714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3735446929932</t>
+    <t xml:space="preserve">17.4548645019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6797695159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3735427856445</t>
   </si>
   <si>
     <t xml:space="preserve">18.1055965423584</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9524841308594</t>
+    <t xml:space="preserve">17.9524822235107</t>
   </si>
   <si>
     <t xml:space="preserve">18.4309597015381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5840721130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8137435913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4118213653564</t>
+    <t xml:space="preserve">18.5840740203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8137454986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4118232727051</t>
   </si>
   <si>
     <t xml:space="preserve">18.3161277770996</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1630115509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8567905426025</t>
+    <t xml:space="preserve">18.163013458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8567886352539</t>
   </si>
   <si>
     <t xml:space="preserve">18.4500999450684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1869564056396</t>
+    <t xml:space="preserve">19.186954498291</t>
   </si>
   <si>
     <t xml:space="preserve">18.7180480957031</t>
@@ -3182,25 +3182,25 @@
     <t xml:space="preserve">18.8520202636719</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3305015563965</t>
+    <t xml:space="preserve">19.3304996490479</t>
   </si>
   <si>
     <t xml:space="preserve">18.0481796264648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5888385772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7993698120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5122852325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0864562988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1247367858887</t>
+    <t xml:space="preserve">17.5888404846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7993717193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5122833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0864582061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.12473487854</t>
   </si>
   <si>
     <t xml:space="preserve">17.5505638122559</t>
@@ -3209,25 +3209,25 @@
     <t xml:space="preserve">17.2251987457275</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5170516967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8854608535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3447971343994</t>
+    <t xml:space="preserve">16.5170497894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.885461807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.344799041748</t>
   </si>
   <si>
     <t xml:space="preserve">16.0959911346436</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9428768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1151313781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3112869262695</t>
+    <t xml:space="preserve">15.9428777694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1151294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3112859725952</t>
   </si>
   <si>
     <t xml:space="preserve">15.4452600479126</t>
@@ -3239,22 +3239,22 @@
     <t xml:space="preserve">16.6127452850342</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0194339752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6510238647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7658596038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9955272674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3208923339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1295032501221</t>
+    <t xml:space="preserve">16.0194320678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6510257720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7658576965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9955291748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.320894241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1295013427734</t>
   </si>
   <si>
     <t xml:space="preserve">17.0529460906982</t>
@@ -3263,22 +3263,22 @@
     <t xml:space="preserve">17.0146675109863</t>
   </si>
   <si>
-    <t xml:space="preserve">17.837646484375</t>
+    <t xml:space="preserve">17.8376502990723</t>
   </si>
   <si>
     <t xml:space="preserve">18.756326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6989116668701</t>
+    <t xml:space="preserve">18.6989097595215</t>
   </si>
   <si>
     <t xml:space="preserve">19.4261932373047</t>
   </si>
   <si>
-    <t xml:space="preserve">19.952522277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0003662109375</t>
+    <t xml:space="preserve">19.9525203704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0003681182861</t>
   </si>
   <si>
     <t xml:space="preserve">19.5697402954102</t>
@@ -3290,10 +3290,10 @@
     <t xml:space="preserve">20.1917591094971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6223907470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7180843353271</t>
+    <t xml:space="preserve">20.6223888397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7180862426758</t>
   </si>
   <si>
     <t xml:space="preserve">20.649543762207</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">20.5525989532471</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4556522369385</t>
+    <t xml:space="preserve">20.4556503295898</t>
   </si>
   <si>
     <t xml:space="preserve">20.4071788787842</t>
@@ -3344,31 +3344,31 @@
     <t xml:space="preserve">20.8434371948242</t>
   </si>
   <si>
-    <t xml:space="preserve">20.69801902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9403839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6190052032471</t>
+    <t xml:space="preserve">20.6980171203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9403820037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6190071105957</t>
   </si>
   <si>
     <t xml:space="preserve">21.7159519195557</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4735851287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9098472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0067920684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.29762840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.218620300293</t>
+    <t xml:space="preserve">21.4735870361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9098453521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0067901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2976303100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2186183929443</t>
   </si>
   <si>
     <t xml:space="preserve">22.4430484771729</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">23.3640384674072</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3155632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0732002258301</t>
+    <t xml:space="preserve">23.3155651092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0731983184814</t>
   </si>
   <si>
     <t xml:space="preserve">23.5579299926758</t>
@@ -3401,19 +3401,19 @@
     <t xml:space="preserve">23.5094566345215</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4609832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6064033508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7033519744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.121675491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.17014503479</t>
+    <t xml:space="preserve">23.4609851837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6064052581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7033500671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1216735839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1701469421387</t>
   </si>
   <si>
     <t xml:space="preserve">23.8002948760986</t>
@@ -3422,25 +3422,25 @@
     <t xml:space="preserve">24.5273914337158</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1575450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8182315826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.624340057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3334999084473</t>
+    <t xml:space="preserve">25.157543182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8182334899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6243381500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3335018157959</t>
   </si>
   <si>
     <t xml:space="preserve">24.4304466247559</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2850284576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1396083831787</t>
+    <t xml:space="preserve">24.285026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1396064758301</t>
   </si>
   <si>
     <t xml:space="preserve">23.8487701416016</t>
@@ -3449,13 +3449,13 @@
     <t xml:space="preserve">22.5884666442871</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4915237426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0247268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7338886260986</t>
+    <t xml:space="preserve">22.4915218353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0247287750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.73388671875</t>
   </si>
   <si>
     <t xml:space="preserve">22.8793067932129</t>
@@ -3467,28 +3467,28 @@
     <t xml:space="preserve">23.8972415924072</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0911350250244</t>
+    <t xml:space="preserve">24.091136932373</t>
   </si>
   <si>
     <t xml:space="preserve">24.188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6854133605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2006855010986</t>
+    <t xml:space="preserve">22.6854152679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.20068359375</t>
   </si>
   <si>
     <t xml:space="preserve">21.8128986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7644271850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1522121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3945751190186</t>
+    <t xml:space="preserve">21.76442527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1522102355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3945770263672</t>
   </si>
   <si>
     <t xml:space="preserve">22.63694190979</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">22.3461017608643</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5399951934814</t>
+    <t xml:space="preserve">22.5399971008301</t>
   </si>
   <si>
     <t xml:space="preserve">21.5220603942871</t>
@@ -3512,31 +3512,31 @@
     <t xml:space="preserve">21.2796955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3766384124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9888572692871</t>
+    <t xml:space="preserve">21.3766403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9888553619385</t>
   </si>
   <si>
     <t xml:space="preserve">20.7949638366699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3281669616699</t>
+    <t xml:space="preserve">21.3281688690186</t>
   </si>
   <si>
     <t xml:space="preserve">21.0858020782471</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8919086456299</t>
+    <t xml:space="preserve">20.8919105529785</t>
   </si>
   <si>
     <t xml:space="preserve">21.0373306274414</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8613719940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9583168029785</t>
+    <t xml:space="preserve">21.8613700866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9583187103271</t>
   </si>
   <si>
     <t xml:space="preserve">21.6674785614014</t>
@@ -3548,25 +3548,25 @@
     <t xml:space="preserve">24.0426616668701</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0121231079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0785331726074</t>
+    <t xml:space="preserve">25.0121212005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0785312652588</t>
   </si>
   <si>
     <t xml:space="preserve">25.8361663818359</t>
   </si>
   <si>
-    <t xml:space="preserve">25.690746307373</t>
+    <t xml:space="preserve">25.6907482147217</t>
   </si>
   <si>
     <t xml:space="preserve">25.6422748565674</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7876949310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8846397399902</t>
+    <t xml:space="preserve">25.7876930236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8846416473389</t>
   </si>
   <si>
     <t xml:space="preserve">26.1754779815674</t>
@@ -3575,22 +3575,22 @@
     <t xml:space="preserve">26.9025745391846</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2239513397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3693714141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3029632568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3819713592529</t>
+    <t xml:space="preserve">26.223949432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3693733215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3029651641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3819732666016</t>
   </si>
   <si>
     <t xml:space="preserve">24.721284866333</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9941902160645</t>
+    <t xml:space="preserve">23.9941883087158</t>
   </si>
   <si>
     <t xml:space="preserve">24.2365550994873</t>
@@ -3602,16 +3602,16 @@
     <t xml:space="preserve">25.0605983734131</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3999080657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4968547821045</t>
+    <t xml:space="preserve">25.3999099731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4968528747559</t>
   </si>
   <si>
     <t xml:space="preserve">25.3514347076416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5453262329102</t>
+    <t xml:space="preserve">25.5453300476074</t>
   </si>
   <si>
     <t xml:space="preserve">25.8003883361816</t>
@@ -3626,13 +3626,13 @@
     <t xml:space="preserve">25.9965896606445</t>
   </si>
   <si>
-    <t xml:space="preserve">26.683292388916</t>
+    <t xml:space="preserve">26.6832942962646</t>
   </si>
   <si>
     <t xml:space="preserve">26.7813911437988</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5361423492432</t>
+    <t xml:space="preserve">26.5361404418945</t>
   </si>
   <si>
     <t xml:space="preserve">26.7323417663574</t>
@@ -3653,22 +3653,22 @@
     <t xml:space="preserve">26.4380416870117</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5851936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.762393951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5661964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6642971038818</t>
+    <t xml:space="preserve">26.5851917266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7623958587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5661945343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6642951965332</t>
   </si>
   <si>
     <t xml:space="preserve">28.1057472229004</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8414974212646</t>
+    <t xml:space="preserve">28.8414993286133</t>
   </si>
   <si>
     <t xml:space="preserve">29.1358013153076</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">29.184850692749</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8225040435791</t>
+    <t xml:space="preserve">29.8225021362305</t>
   </si>
   <si>
     <t xml:space="preserve">29.4791507720947</t>
@@ -3710,13 +3710,13 @@
     <t xml:space="preserve">29.4301013946533</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3620548248291</t>
+    <t xml:space="preserve">30.3620567321777</t>
   </si>
   <si>
     <t xml:space="preserve">29.9696521759033</t>
   </si>
   <si>
-    <t xml:space="preserve">30.558256149292</t>
+    <t xml:space="preserve">30.5582542419434</t>
   </si>
   <si>
     <t xml:space="preserve">30.4601535797119</t>
@@ -3728,10 +3728,10 @@
     <t xml:space="preserve">30.6563568115234</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8525581359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.607307434082</t>
+    <t xml:space="preserve">30.8525562286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6073055267334</t>
   </si>
   <si>
     <t xml:space="preserve">30.9016056060791</t>
@@ -3752,10 +3752,10 @@
     <t xml:space="preserve">30.0677528381348</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2639541625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1468563079834</t>
+    <t xml:space="preserve">30.2639560699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.146858215332</t>
   </si>
   <si>
     <t xml:space="preserve">31.3430595397949</t>
@@ -3767,10 +3767,10 @@
     <t xml:space="preserve">30.1658535003662</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3130035400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2940082550049</t>
+    <t xml:space="preserve">30.3130054473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2940063476562</t>
   </si>
   <si>
     <t xml:space="preserve">31.3921089172363</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">32.7655143737793</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3050689697266</t>
+    <t xml:space="preserve">33.3050651550293</t>
   </si>
   <si>
     <t xml:space="preserve">33.3541145324707</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">31.4902076721191</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7354564666748</t>
+    <t xml:space="preserve">31.7354583740234</t>
   </si>
   <si>
     <t xml:space="preserve">32.0788116455078</t>
@@ -3869,19 +3869,19 @@
     <t xml:space="preserve">34.433219909668</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5313186645508</t>
+    <t xml:space="preserve">34.531322479248</t>
   </si>
   <si>
     <t xml:space="preserve">34.7275199890137</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7085266113281</t>
+    <t xml:space="preserve">35.7085227966309</t>
   </si>
   <si>
     <t xml:space="preserve">36.0028266906738</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2971267700195</t>
+    <t xml:space="preserve">36.2971229553223</t>
   </si>
   <si>
     <t xml:space="preserve">35.512321472168</t>
@@ -3890,31 +3890,31 @@
     <t xml:space="preserve">36.6404762268066</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2480735778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6594696044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4632759094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7385787963867</t>
+    <t xml:space="preserve">36.2480773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6594734191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4632720947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7385749816895</t>
   </si>
   <si>
     <t xml:space="preserve">37.2290802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4933280944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2781295776367</t>
+    <t xml:space="preserve">36.4933242797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2781257629395</t>
   </si>
   <si>
     <t xml:space="preserve">36.5423774719238</t>
   </si>
   <si>
-    <t xml:space="preserve">37.523380279541</t>
+    <t xml:space="preserve">37.5233764648438</t>
   </si>
   <si>
     <t xml:space="preserve">37.4743309020996</t>
@@ -3923,13 +3923,13 @@
     <t xml:space="preserve">35.5613746643066</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8066253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7765693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2180213928223</t>
+    <t xml:space="preserve">35.8066215515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7765731811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2180252075195</t>
   </si>
   <si>
     <t xml:space="preserve">34.9237174987793</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">35.0218200683594</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1689720153809</t>
+    <t xml:space="preserve">35.1689682006836</t>
   </si>
   <si>
     <t xml:space="preserve">34.678466796875</t>
@@ -3947,34 +3947,34 @@
     <t xml:space="preserve">33.9917678833008</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3651733398438</t>
+    <t xml:space="preserve">35.3651695251465</t>
   </si>
   <si>
     <t xml:space="preserve">36.051872253418</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8556709289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7575721740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0898666381836</t>
+    <t xml:space="preserve">35.8556747436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7575759887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0898704528809</t>
   </si>
   <si>
     <t xml:space="preserve">33.9427146911621</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0408210754395</t>
+    <t xml:space="preserve">34.0408172607422</t>
   </si>
   <si>
     <t xml:space="preserve">34.3841667175293</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3161201477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2370223999023</t>
+    <t xml:space="preserve">35.3161239624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2370185852051</t>
   </si>
   <si>
     <t xml:space="preserve">32.4221611022949</t>
@@ -4004,7 +4004,7 @@
     <t xml:space="preserve">29.2339000701904</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9095458984375</t>
+    <t xml:space="preserve">27.9095478057861</t>
   </si>
   <si>
     <t xml:space="preserve">27.7133464813232</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">28.2528972625732</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3209457397461</t>
+    <t xml:space="preserve">27.3209438323975</t>
   </si>
   <si>
     <t xml:space="preserve">27.1247425079346</t>
@@ -4037,13 +4037,13 @@
     <t xml:space="preserve">26.6342430114746</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0266418457031</t>
+    <t xml:space="preserve">27.0266437530518</t>
   </si>
   <si>
     <t xml:space="preserve">26.9775924682617</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2908897399902</t>
+    <t xml:space="preserve">26.2908916473389</t>
   </si>
   <si>
     <t xml:space="preserve">26.1927909851074</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">26.0456390380859</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7022876739502</t>
+    <t xml:space="preserve">25.7022895812988</t>
   </si>
   <si>
     <t xml:space="preserve">25.8984889984131</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">25.309886932373</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1627368927002</t>
+    <t xml:space="preserve">25.1627349853516</t>
   </si>
   <si>
     <t xml:space="preserve">25.0155868530273</t>
@@ -4073,13 +4073,13 @@
     <t xml:space="preserve">24.672233581543</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4269847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8383808135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3288841247559</t>
+    <t xml:space="preserve">24.4269828796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8383827209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3288822174072</t>
   </si>
   <si>
     <t xml:space="preserve">25.4570388793945</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">24.5741348266602</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8193836212158</t>
+    <t xml:space="preserve">24.8193855285645</t>
   </si>
   <si>
     <t xml:space="preserve">24.3841934204102</t>
@@ -4632,6 +4632,9 @@
   </si>
   <si>
     <t xml:space="preserve">46.9000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4500007629395</t>
   </si>
 </sst>
 </file>
@@ -26204,7 +26207,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G817" t="s">
-        <v>524</v>
+        <v>178</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -26230,7 +26233,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G818" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26282,7 +26285,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G820" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -26308,7 +26311,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G821" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -26334,7 +26337,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G822" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -26360,7 +26363,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G823" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26386,7 +26389,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26438,7 +26441,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G826" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26464,7 +26467,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G827" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -26490,7 +26493,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G828" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -26516,7 +26519,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G829" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -26542,7 +26545,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G830" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -26568,7 +26571,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G831" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -26594,7 +26597,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G832" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -26620,7 +26623,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G833" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -26646,7 +26649,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G834" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -26672,7 +26675,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G835" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -26698,7 +26701,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G836" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -26750,7 +26753,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G838" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -26828,7 +26831,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G841" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -26854,7 +26857,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G842" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -26880,7 +26883,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G843" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -26906,7 +26909,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G844" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -26932,7 +26935,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G845" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -26958,7 +26961,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G846" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -26984,7 +26987,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G847" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27010,7 +27013,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G848" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -27036,7 +27039,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G849" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -27088,7 +27091,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G851" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27114,7 +27117,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G852" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -27166,7 +27169,7 @@
         <v>16.5</v>
       </c>
       <c r="G854" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -27192,7 +27195,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G855" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -27218,7 +27221,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G856" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -27270,7 +27273,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G858" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -27296,7 +27299,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G859" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -27322,7 +27325,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G860" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -27348,7 +27351,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G861" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -27374,7 +27377,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G862" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -27400,7 +27403,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G863" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -27452,7 +27455,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G865" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -27478,7 +27481,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G866" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -27504,7 +27507,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G867" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -27530,7 +27533,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G868" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -27582,7 +27585,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G870" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -27634,7 +27637,7 @@
         <v>15.5</v>
       </c>
       <c r="G872" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -27660,7 +27663,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G873" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -27686,7 +27689,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G874" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -27738,7 +27741,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G876" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -27764,7 +27767,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G877" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -27790,7 +27793,7 @@
         <v>16.5</v>
       </c>
       <c r="G878" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -27842,7 +27845,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G880" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -27868,7 +27871,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G881" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -27894,7 +27897,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G882" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -27920,7 +27923,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G883" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -27972,7 +27975,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G885" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -28024,7 +28027,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G887" t="s">
-        <v>462</v>
+        <v>571</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -28128,7 +28131,7 @@
         <v>16.5</v>
       </c>
       <c r="G891" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -28154,7 +28157,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G892" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -28336,7 +28339,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G899" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -28414,7 +28417,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G902" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -28466,7 +28469,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G904" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -28518,7 +28521,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G906" t="s">
-        <v>462</v>
+        <v>571</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -28544,7 +28547,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G907" t="s">
-        <v>462</v>
+        <v>571</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -28648,7 +28651,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G911" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -28700,7 +28703,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G913" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -28778,7 +28781,7 @@
         <v>15.5</v>
       </c>
       <c r="G916" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -29012,7 +29015,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G925" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -29376,7 +29379,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G939" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -29402,7 +29405,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G940" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -29428,7 +29431,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G941" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -29558,7 +29561,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G946" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -29584,7 +29587,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G947" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -29610,7 +29613,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G948" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -29636,7 +29639,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G949" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -29740,7 +29743,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G953" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -30000,7 +30003,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G963" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -30078,7 +30081,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G966" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -30156,7 +30159,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G969" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -30182,7 +30185,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G970" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -70412,7 +70415,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6911921296</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>57384</v>
@@ -70433,6 +70436,32 @@
         <v>1539</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6913078704</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>54474</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>47.5999984741211</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>45.9000015258789</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>47</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>47.4500007629395</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>1540</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="1544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="1545">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5902528762817</t>
+    <t xml:space="preserve">15.5902490615845</t>
   </si>
   <si>
     <t xml:space="preserve">DAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7186393737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2234210968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5356168746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2146415710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9395189285278</t>
+    <t xml:space="preserve">15.718638420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2234220504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5356159210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2146406173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9395179748535</t>
   </si>
   <si>
     <t xml:space="preserve">14.2880077362061</t>
   </si>
   <si>
-    <t xml:space="preserve">14.040397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.866153717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1049814224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.793176651001</t>
+    <t xml:space="preserve">14.0403966903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8661527633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1049833297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7931756973267</t>
   </si>
   <si>
     <t xml:space="preserve">12.8848848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2887859344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9490795135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.132493019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8928852081299</t>
+    <t xml:space="preserve">12.2887868881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9490804672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.132495880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8928871154785</t>
   </si>
   <si>
     <t xml:space="preserve">16.0487880706787</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3239059448242</t>
+    <t xml:space="preserve">16.3239078521729</t>
   </si>
   <si>
     <t xml:space="preserve">16.0854721069336</t>
@@ -101,37 +101,37 @@
     <t xml:space="preserve">16.3605937957764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1125926971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5990371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4710330963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1038131713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3059597015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9391298294067</t>
+    <t xml:space="preserve">17.1125946044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5990314483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4710321426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1038112640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3059587478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9391307830811</t>
   </si>
   <si>
     <t xml:space="preserve">14.9483003616333</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3518123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1042022705078</t>
+    <t xml:space="preserve">15.3518095016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1042032241821</t>
   </si>
   <si>
     <t xml:space="preserve">15.003324508667</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9112272262573</t>
+    <t xml:space="preserve">15.911229133606</t>
   </si>
   <si>
     <t xml:space="preserve">16.2322025299072</t>
@@ -140,70 +140,70 @@
     <t xml:space="preserve">16.7641067504883</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9200096130371</t>
+    <t xml:space="preserve">16.9200077056885</t>
   </si>
   <si>
     <t xml:space="preserve">17.0575714111328</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9658603668213</t>
+    <t xml:space="preserve">16.9658622741699</t>
   </si>
   <si>
     <t xml:space="preserve">16.7090816497803</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3514194488525</t>
+    <t xml:space="preserve">16.3514232635498</t>
   </si>
   <si>
     <t xml:space="preserve">16.3422508239746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8283023834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6357135772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1767902374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3051795959473</t>
+    <t xml:space="preserve">16.8283042907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6357154846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1767864227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3051776885986</t>
   </si>
   <si>
     <t xml:space="preserve">17.3693752288818</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4335689544678</t>
+    <t xml:space="preserve">17.4335670471191</t>
   </si>
   <si>
     <t xml:space="preserve">16.5348358154297</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2226428985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5161056518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8741550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2593288421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4610824584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0117168426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2138633728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5531787872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9383487701416</t>
+    <t xml:space="preserve">17.2226409912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5161075592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8741569519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2593269348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4610843658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0117130279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2138652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5531768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.938346862793</t>
   </si>
   <si>
     <t xml:space="preserve">17.2868385314941</t>
@@ -218,25 +218,25 @@
     <t xml:space="preserve">17.1217651367188</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5619621276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6353244781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4060573577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8645973205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1122016906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0204982757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7912292480469</t>
+    <t xml:space="preserve">17.5619602203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6353225708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4060592651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8645935058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1122035980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0204963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7912273406982</t>
   </si>
   <si>
     <t xml:space="preserve">17.5986442565918</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">18.3414707183838</t>
   </si>
   <si>
-    <t xml:space="preserve">18.405668258667</t>
+    <t xml:space="preserve">18.4056701660156</t>
   </si>
   <si>
     <t xml:space="preserve">18.4331817626953</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">18.0938625335693</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3231296539307</t>
+    <t xml:space="preserve">18.323127746582</t>
   </si>
   <si>
     <t xml:space="preserve">18.0296649932861</t>
@@ -266,13 +266,13 @@
     <t xml:space="preserve">17.470251083374</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1492786407471</t>
+    <t xml:space="preserve">17.1492748260498</t>
   </si>
   <si>
     <t xml:space="preserve">17.4885940551758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1676197052002</t>
+    <t xml:space="preserve">17.1676177978516</t>
   </si>
   <si>
     <t xml:space="preserve">17.0759124755859</t>
@@ -281,25 +281,25 @@
     <t xml:space="preserve">16.7732772827148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8374710083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5623512268066</t>
+    <t xml:space="preserve">16.8374729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.562349319458</t>
   </si>
   <si>
     <t xml:space="preserve">16.3147411346436</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1496677398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2505435943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7457637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4523029327393</t>
+    <t xml:space="preserve">16.1496658325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2505416870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7457656860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.452299118042</t>
   </si>
   <si>
     <t xml:space="preserve">16.4156188964844</t>
@@ -308,37 +308,37 @@
     <t xml:space="preserve">16.1680068969727</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3602046966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5164966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4981555938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2409839630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9933738708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0392265319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8103475570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.84703540802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9574699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7648839950562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0675182342529</t>
+    <t xml:space="preserve">17.3602066040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5164947509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4981536865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2409858703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9933757781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0392284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8103523254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8470335006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9574689865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7648849487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0675172805786</t>
   </si>
   <si>
     <t xml:space="preserve">15.3334712982178</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">15.9570798873901</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9849815368652</t>
+    <t xml:space="preserve">14.9849824905396</t>
   </si>
   <si>
     <t xml:space="preserve">14.4530801773071</t>
@@ -356,91 +356,91 @@
     <t xml:space="preserve">14.8841047286987</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5264463424683</t>
+    <t xml:space="preserve">14.5264472961426</t>
   </si>
   <si>
     <t xml:space="preserve">14.6823492050171</t>
   </si>
   <si>
-    <t xml:space="preserve">15.406834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0308361053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6273231506348</t>
+    <t xml:space="preserve">15.4068365097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0308351516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6273241043091</t>
   </si>
   <si>
     <t xml:space="preserve">14.0037145614624</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2604942321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6548376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3976669311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.315131187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4985437393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2509336471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3242998123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2967863082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3793230056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.140495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6177644729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3884963989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1221542358398</t>
+    <t xml:space="preserve">14.2604951858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6548357009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3976697921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3151292800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4985456466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2509346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3243007659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2967872619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3793268203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1404972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6177654266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3884954452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1221504211426</t>
   </si>
   <si>
     <t xml:space="preserve">15.8286914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0762996673584</t>
+    <t xml:space="preserve">16.076301574707</t>
   </si>
   <si>
     <t xml:space="preserve">16.1771793365479</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0671291351318</t>
+    <t xml:space="preserve">16.0671272277832</t>
   </si>
   <si>
     <t xml:space="preserve">15.9845943450928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1401062011719</t>
+    <t xml:space="preserve">17.1401042938232</t>
   </si>
   <si>
     <t xml:space="preserve">16.8099594116211</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6082057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6448879241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6078109741211</t>
+    <t xml:space="preserve">16.6082038879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.644889831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6078147888184</t>
   </si>
   <si>
     <t xml:space="preserve">17.158447265625</t>
@@ -449,190 +449,190 @@
     <t xml:space="preserve">17.0300579071045</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1951293945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.332691192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0946407318115</t>
+    <t xml:space="preserve">17.1951313018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3326950073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0946445465088</t>
   </si>
   <si>
     <t xml:space="preserve">15.7828340530396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7553253173828</t>
+    <t xml:space="preserve">15.7553272247314</t>
   </si>
   <si>
     <t xml:space="preserve">15.8195209503174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9479112625122</t>
+    <t xml:space="preserve">15.9479093551636</t>
   </si>
   <si>
     <t xml:space="preserve">15.6361045837402</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6636199951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5627384185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4893732070923</t>
+    <t xml:space="preserve">15.6636161804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5627393722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.489372253418</t>
   </si>
   <si>
     <t xml:space="preserve">15.6085948944092</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0304470062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6999111175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0579586029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5352258682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5443992614746</t>
+    <t xml:space="preserve">16.0304489135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6999092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0579624176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5352277755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5444002151489</t>
   </si>
   <si>
     <t xml:space="preserve">15.7003002166748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3609828948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1592264175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2330379486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3068532943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5467433929443</t>
+    <t xml:space="preserve">15.3609848022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1592283248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2330408096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3068542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5467443466187</t>
   </si>
   <si>
     <t xml:space="preserve">15.6297826766968</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7866334915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.519061088562</t>
+    <t xml:space="preserve">15.7866363525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5190629959106</t>
   </si>
   <si>
     <t xml:space="preserve">14.9746961593628</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3253059387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4175710678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4083452224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0577344894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7589550018311</t>
+    <t xml:space="preserve">15.3253040313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4175701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4083433151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0577354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7589530944824</t>
   </si>
   <si>
     <t xml:space="preserve">16.2202796936035</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8235378265381</t>
+    <t xml:space="preserve">15.8235397338867</t>
   </si>
   <si>
     <t xml:space="preserve">15.3898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5006074905396</t>
+    <t xml:space="preserve">15.5006084442139</t>
   </si>
   <si>
     <t xml:space="preserve">15.2145853042603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7774076461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9434843063354</t>
+    <t xml:space="preserve">15.7774057388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9434862136841</t>
   </si>
   <si>
     <t xml:space="preserve">15.731273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4693965911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0691242218018</t>
+    <t xml:space="preserve">16.4693984985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0691223144531</t>
   </si>
   <si>
     <t xml:space="preserve">17.142936706543</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0229911804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.106029510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9122734069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8384590148926</t>
+    <t xml:space="preserve">17.0229949951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1060314178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9122753143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8384571075439</t>
   </si>
   <si>
     <t xml:space="preserve">16.3771324157715</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9768600463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7923278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0506687164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6227149963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7795658111572</t>
+    <t xml:space="preserve">16.9768581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.792329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0506706237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6227169036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7795677185059</t>
   </si>
   <si>
     <t xml:space="preserve">17.8164749145508</t>
   </si>
   <si>
-    <t xml:space="preserve">17.761116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3054828643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7760353088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8221702575684</t>
+    <t xml:space="preserve">17.7611198425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3054847717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7760372161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8221664428711</t>
   </si>
   <si>
     <t xml:space="preserve">19.421895980835</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4957084655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9882488250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7852649688721</t>
+    <t xml:space="preserve">19.4957065582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9882469177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7852611541748</t>
   </si>
   <si>
     <t xml:space="preserve">19.3296279907227</t>
@@ -641,37 +641,37 @@
     <t xml:space="preserve">19.2004585266113</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0528316497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9513397216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7299022674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8867530822754</t>
+    <t xml:space="preserve">19.0528297424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9513416290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7298984527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.886754989624</t>
   </si>
   <si>
     <t xml:space="preserve">18.8129425048828</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8037147521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6284065246582</t>
+    <t xml:space="preserve">18.8037166595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6284122467041</t>
   </si>
   <si>
     <t xml:space="preserve">18.4531059265137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2778015136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9917812347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3331642150879</t>
+    <t xml:space="preserve">18.2778034210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9917793273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3331604003906</t>
   </si>
   <si>
     <t xml:space="preserve">18.4069747924805</t>
@@ -683,13 +683,13 @@
     <t xml:space="preserve">18.2501220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">18.36083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1578559875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.203987121582</t>
+    <t xml:space="preserve">18.3608417510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1578598022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2039852142334</t>
   </si>
   <si>
     <t xml:space="preserve">18.3885231018066</t>
@@ -698,70 +698,70 @@
     <t xml:space="preserve">18.4900150299072</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4992389678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6007328033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.914436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2834987640381</t>
+    <t xml:space="preserve">18.4992370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6007308959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9144325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2834968566895</t>
   </si>
   <si>
     <t xml:space="preserve">18.9605693817139</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9974746704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2373638153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3204021453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.831392288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1174201965332</t>
+    <t xml:space="preserve">18.9974765777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2373657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3204040527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8313941955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1174182891846</t>
   </si>
   <si>
     <t xml:space="preserve">19.3757629394531</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9697933197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0897388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2189121246338</t>
+    <t xml:space="preserve">18.9697914123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0897369384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2189083099365</t>
   </si>
   <si>
     <t xml:space="preserve">18.9052085876465</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0989646911621</t>
+    <t xml:space="preserve">19.0989627838135</t>
   </si>
   <si>
     <t xml:space="preserve">19.2558174133301</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1543254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7817287445068</t>
+    <t xml:space="preserve">19.1543235778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7817306518555</t>
   </si>
   <si>
     <t xml:space="preserve">19.8739967346191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2430591583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4829483032227</t>
+    <t xml:space="preserve">20.2430610656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4829502105713</t>
   </si>
   <si>
     <t xml:space="preserve">20.7136135101318</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">20.8243293762207</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8058776855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0123958587646</t>
+    <t xml:space="preserve">20.8058795928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.012393951416</t>
   </si>
   <si>
     <t xml:space="preserve">20.4737243652344</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2522850036621</t>
+    <t xml:space="preserve">20.2522869110107</t>
   </si>
   <si>
     <t xml:space="preserve">20.1138877868652</t>
@@ -788,16 +788,16 @@
     <t xml:space="preserve">20.4368152618408</t>
   </si>
   <si>
-    <t xml:space="preserve">20.510627746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4644947052002</t>
+    <t xml:space="preserve">20.5106258392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4644966125488</t>
   </si>
   <si>
     <t xml:space="preserve">20.3630065917969</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3906860351562</t>
+    <t xml:space="preserve">20.3906841278076</t>
   </si>
   <si>
     <t xml:space="preserve">20.5198554992676</t>
@@ -812,31 +812,31 @@
     <t xml:space="preserve">20.7228393554688</t>
   </si>
   <si>
-    <t xml:space="preserve">20.316873550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.639799118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4978694915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3502426147461</t>
+    <t xml:space="preserve">20.3168716430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6398029327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4978713989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3502464294434</t>
   </si>
   <si>
     <t xml:space="preserve">21.2210731506348</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1749401092529</t>
+    <t xml:space="preserve">21.1749382019043</t>
   </si>
   <si>
     <t xml:space="preserve">20.9904117584229</t>
   </si>
   <si>
-    <t xml:space="preserve">20.98118019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7874279022217</t>
+    <t xml:space="preserve">20.9811820983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.787425994873</t>
   </si>
   <si>
     <t xml:space="preserve">21.1288089752197</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">20.9627304077148</t>
   </si>
   <si>
-    <t xml:space="preserve">21.202615737915</t>
+    <t xml:space="preserve">21.2026195526123</t>
   </si>
   <si>
     <t xml:space="preserve">21.0826759338379</t>
@@ -854,16 +854,16 @@
     <t xml:space="preserve">20.5013999938965</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0273151397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8151035308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9719562530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1103496551514</t>
+    <t xml:space="preserve">21.0273170471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8151016235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9719581604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1103534698486</t>
   </si>
   <si>
     <t xml:space="preserve">21.1011295318604</t>
@@ -878,16 +878,16 @@
     <t xml:space="preserve">20.79665184021</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0365409851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5936698913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1784706115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2615089416504</t>
+    <t xml:space="preserve">21.0365428924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5936660766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1784725189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.261510848999</t>
   </si>
   <si>
     <t xml:space="preserve">20.2707386016846</t>
@@ -899,97 +899,97 @@
     <t xml:space="preserve">20.4921741485596</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1415672302246</t>
+    <t xml:space="preserve">20.141565322876</t>
   </si>
   <si>
     <t xml:space="preserve">19.9109039306641</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0769824981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6617870330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7725048065186</t>
+    <t xml:space="preserve">20.0769786834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6617851257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7725009918213</t>
   </si>
   <si>
     <t xml:space="preserve">20.1323413848877</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1600208282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4091339111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2984161376953</t>
+    <t xml:space="preserve">20.1600189208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4091377258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2984180450439</t>
   </si>
   <si>
     <t xml:space="preserve">19.8186378479004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.698694229126</t>
+    <t xml:space="preserve">19.6986904144287</t>
   </si>
   <si>
     <t xml:space="preserve">19.7540512084961</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5879726409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7909564971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9385833740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8647727966309</t>
+    <t xml:space="preserve">19.5879707336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.790958404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9385814666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8647708892822</t>
   </si>
   <si>
     <t xml:space="preserve">19.9754886627197</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5418434143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5290794372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1046581268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8370914459229</t>
+    <t xml:space="preserve">19.5418395996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5290813446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1046600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8370895385742</t>
   </si>
   <si>
     <t xml:space="preserve">19.5972003936768</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2799644470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9939422607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3537750244141</t>
+    <t xml:space="preserve">20.2799625396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9939403533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3537769317627</t>
   </si>
   <si>
     <t xml:space="preserve">20.7043857574463</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2061500549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4275913238525</t>
+    <t xml:space="preserve">20.2061538696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4275894165039</t>
   </si>
   <si>
     <t xml:space="preserve">20.7505187988281</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0549926757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5844402313232</t>
+    <t xml:space="preserve">21.0549945831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5844383239746</t>
   </si>
   <si>
     <t xml:space="preserve">20.3353252410889</t>
@@ -1010,10 +1010,10 @@
     <t xml:space="preserve">19.6341075897217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8463172912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9570350646973</t>
+    <t xml:space="preserve">19.8463191986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.95703125</t>
   </si>
   <si>
     <t xml:space="preserve">20.3814563751221</t>
@@ -1025,16 +1025,16 @@
     <t xml:space="preserve">19.4034423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1266441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6560878753662</t>
+    <t xml:space="preserve">19.1266479492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6560916900635</t>
   </si>
   <si>
     <t xml:space="preserve">18.7114505767822</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5084667205811</t>
+    <t xml:space="preserve">18.5084648132324</t>
   </si>
   <si>
     <t xml:space="preserve">18.8683032989502</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">18.4346542358398</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5361480712891</t>
+    <t xml:space="preserve">18.5361461639404</t>
   </si>
   <si>
     <t xml:space="preserve">18.3147068023682</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">18.6837730407715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0066967010498</t>
+    <t xml:space="preserve">19.0066986083984</t>
   </si>
   <si>
     <t xml:space="preserve">18.849760055542</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8219413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4047069549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1821823120117</t>
+    <t xml:space="preserve">18.8219394683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4047050476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1821804046631</t>
   </si>
   <si>
     <t xml:space="preserve">17.7834892272949</t>
@@ -1076,55 +1076,55 @@
     <t xml:space="preserve">17.7278594970703</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5238742828369</t>
+    <t xml:space="preserve">17.5238761901855</t>
   </si>
   <si>
     <t xml:space="preserve">17.5516948699951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8205738067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7742176055908</t>
+    <t xml:space="preserve">17.8205757141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7742195129395</t>
   </si>
   <si>
     <t xml:space="preserve">17.8483943939209</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1450939178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3398056030273</t>
+    <t xml:space="preserve">18.145092010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3398017883301</t>
   </si>
   <si>
     <t xml:space="preserve">18.4603366851807</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2841720581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0431022644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3676166534424</t>
+    <t xml:space="preserve">18.2841701507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0431041717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.367618560791</t>
   </si>
   <si>
     <t xml:space="preserve">18.2378120422363</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0987358093262</t>
+    <t xml:space="preserve">18.0987339019775</t>
   </si>
   <si>
     <t xml:space="preserve">18.5437870025635</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6457786560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5716018676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5623302459717</t>
+    <t xml:space="preserve">18.6457767486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5716037750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5623340606689</t>
   </si>
   <si>
     <t xml:space="preserve">18.4881553649902</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">18.2285404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2563591003418</t>
+    <t xml:space="preserve">18.2563571929932</t>
   </si>
   <si>
     <t xml:space="preserve">18.3212585449219</t>
@@ -1142,55 +1142,55 @@
     <t xml:space="preserve">18.3583469390869</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3490791320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5345134735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5808715820312</t>
+    <t xml:space="preserve">18.3490753173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5345153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5808734893799</t>
   </si>
   <si>
     <t xml:space="preserve">18.4696102142334</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2656307220459</t>
+    <t xml:space="preserve">18.2656288146973</t>
   </si>
   <si>
     <t xml:space="preserve">18.3768901824951</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7755832672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0537376403809</t>
+    <t xml:space="preserve">18.7755851745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0537395477295</t>
   </si>
   <si>
     <t xml:space="preserve">19.3318977355957</t>
   </si>
   <si>
-    <t xml:space="preserve">19.610050201416</t>
+    <t xml:space="preserve">19.6100540161133</t>
   </si>
   <si>
     <t xml:space="preserve">20.3981628417969</t>
   </si>
   <si>
-    <t xml:space="preserve">21.13991355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4180736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3717136383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2326335906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4644317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3253536224365</t>
+    <t xml:space="preserve">21.1399154663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4180717468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3717098236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2326354980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4644336700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3253517150879</t>
   </si>
   <si>
     <t xml:space="preserve">21.6035099029541</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">21.6498699188232</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8617610931396</t>
+    <t xml:space="preserve">20.8617572784424</t>
   </si>
   <si>
     <t xml:space="preserve">20.3054447174072</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">20.9081172943115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4908828735352</t>
+    <t xml:space="preserve">20.4908847808838</t>
   </si>
   <si>
     <t xml:space="preserve">20.6299629211426</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">20.5836048126221</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9544792175293</t>
+    <t xml:space="preserve">20.954475402832</t>
   </si>
   <si>
     <t xml:space="preserve">21.0471973419189</t>
@@ -1229,19 +1229,19 @@
     <t xml:space="preserve">20.7226810455322</t>
   </si>
   <si>
-    <t xml:space="preserve">20.537239074707</t>
+    <t xml:space="preserve">20.5372428894043</t>
   </si>
   <si>
     <t xml:space="preserve">21.5571517944336</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0671081542969</t>
+    <t xml:space="preserve">22.0671043395996</t>
   </si>
   <si>
     <t xml:space="preserve">21.7425880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9280261993408</t>
+    <t xml:space="preserve">21.9280242919922</t>
   </si>
   <si>
     <t xml:space="preserve">21.8353080749512</t>
@@ -1256,22 +1256,22 @@
     <t xml:space="preserve">20.1663665771484</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0736484527588</t>
+    <t xml:space="preserve">20.0736446380615</t>
   </si>
   <si>
     <t xml:space="preserve">20.7690410614014</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4445209503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8154010772705</t>
+    <t xml:space="preserve">20.444522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8153991699219</t>
   </si>
   <si>
     <t xml:space="preserve">21.1862754821777</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2590866088867</t>
+    <t xml:space="preserve">20.2590847015381</t>
   </si>
   <si>
     <t xml:space="preserve">20.351806640625</t>
@@ -1286,10 +1286,10 @@
     <t xml:space="preserve">19.0073795318604</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1928215026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6564102172852</t>
+    <t xml:space="preserve">19.1928176879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6564140319824</t>
   </si>
   <si>
     <t xml:space="preserve">19.4709739685059</t>
@@ -1298,118 +1298,118 @@
     <t xml:space="preserve">20.2127265930176</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1200084686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8418521881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0272903442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8882122039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7491302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7954921722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2855377197266</t>
+    <t xml:space="preserve">20.1200065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8418502807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0272884368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8882083892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7491321563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7954902648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2855358123779</t>
   </si>
   <si>
     <t xml:space="preserve">19.4246158599854</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3782539367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5173320770264</t>
+    <t xml:space="preserve">19.3782558441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.517333984375</t>
   </si>
   <si>
     <t xml:space="preserve">19.5636940002441</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1464595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1001014709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2391796112061</t>
+    <t xml:space="preserve">19.1464557647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.10009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2391738891602</t>
   </si>
   <si>
     <t xml:space="preserve">19.7027740478516</t>
   </si>
   <si>
-    <t xml:space="preserve">21.278995513916</t>
+    <t xml:space="preserve">21.2789936065674</t>
   </si>
   <si>
     <t xml:space="preserve">19.9345703125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.598051071167</t>
+    <t xml:space="preserve">17.5980529785156</t>
   </si>
   <si>
     <t xml:space="preserve">15.205904006958</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5953216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6681337356567</t>
+    <t xml:space="preserve">15.5953235626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6681346893311</t>
   </si>
   <si>
     <t xml:space="preserve">14.3714332580566</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7052202224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2986221313477</t>
+    <t xml:space="preserve">14.7052211761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2986211776733</t>
   </si>
   <si>
     <t xml:space="preserve">15.5211496353149</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8920202255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.428427696228</t>
+    <t xml:space="preserve">15.8920240402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4284296035767</t>
   </si>
   <si>
     <t xml:space="preserve">15.2244482040405</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3542547225952</t>
+    <t xml:space="preserve">15.3542518615723</t>
   </si>
   <si>
     <t xml:space="preserve">15.7622175216675</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6880435943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5582370758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4840631484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2800779342651</t>
+    <t xml:space="preserve">15.6880416870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5582361221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4840612411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2800788879395</t>
   </si>
   <si>
     <t xml:space="preserve">14.9092035293579</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7599239349365</t>
+    <t xml:space="preserve">14.7599248886108</t>
   </si>
   <si>
     <t xml:space="preserve">14.4800281524658</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3120899200439</t>
+    <t xml:space="preserve">14.3120908737183</t>
   </si>
   <si>
     <t xml:space="preserve">14.3494100570679</t>
@@ -1427,40 +1427,40 @@
     <t xml:space="preserve">15.0398225784302</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3383798599243</t>
+    <t xml:space="preserve">15.3383808135986</t>
   </si>
   <si>
     <t xml:space="preserve">15.1704425811768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9762115478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8269329071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5097169876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6403341293335</t>
+    <t xml:space="preserve">13.9762105941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8269338607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5097160339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6403350830078</t>
   </si>
   <si>
     <t xml:space="preserve">14.2374486923218</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0695114135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0508527755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1254901885986</t>
+    <t xml:space="preserve">14.0695123672485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0508518218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1254920959473</t>
   </si>
   <si>
     <t xml:space="preserve">13.8642520904541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5470361709595</t>
+    <t xml:space="preserve">13.5470371246338</t>
   </si>
   <si>
     <t xml:space="preserve">13.5283765792847</t>
@@ -1469,13 +1469,13 @@
     <t xml:space="preserve">13.6963148117065</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9575519561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1068305969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4240484237671</t>
+    <t xml:space="preserve">13.9575510025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1068315505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4240465164185</t>
   </si>
   <si>
     <t xml:space="preserve">14.6479654312134</t>
@@ -1484,70 +1484,70 @@
     <t xml:space="preserve">15.114462852478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0211629867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9278631210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.965184211731</t>
+    <t xml:space="preserve">15.0211620330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.927864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9651851654053</t>
   </si>
   <si>
     <t xml:space="preserve">14.7972431182861</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0025024414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0584802627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0958023071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4316816329956</t>
+    <t xml:space="preserve">15.0025014877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0584812164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0958013534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.431679725647</t>
   </si>
   <si>
     <t xml:space="preserve">15.8608551025391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7005462646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7751865386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7938442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3833293914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3086891174316</t>
+    <t xml:space="preserve">16.7005481719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7751846313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7938461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3833274841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3086910247803</t>
   </si>
   <si>
     <t xml:space="preserve">16.1594123840332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2527103424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8795137405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7675542831421</t>
+    <t xml:space="preserve">16.2527122497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8795156478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7675580978394</t>
   </si>
   <si>
     <t xml:space="preserve">15.7115774154663</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0287952423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0474529266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1407508850098</t>
+    <t xml:space="preserve">16.0287933349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0474548339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1407527923584</t>
   </si>
   <si>
     <t xml:space="preserve">16.5139484405518</t>
@@ -1562,31 +1562,31 @@
     <t xml:space="preserve">16.3273506164551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3460121154785</t>
+    <t xml:space="preserve">16.3460102081299</t>
   </si>
   <si>
     <t xml:space="preserve">16.1220951080322</t>
   </si>
   <si>
-    <t xml:space="preserve">16.495288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6072463989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.364673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2153911590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.748893737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8421926498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8235359191895</t>
+    <t xml:space="preserve">16.4952907562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6072444915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3646697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2153930664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7488985061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8421964645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8235340118408</t>
   </si>
   <si>
     <t xml:space="preserve">16.0101337432861</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">15.8981742858887</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2340545654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2900276184082</t>
+    <t xml:space="preserve">16.2340526580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2900295257568</t>
   </si>
   <si>
     <t xml:space="preserve">16.4206485748291</t>
@@ -1610,13 +1610,13 @@
     <t xml:space="preserve">16.8311672210693</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3536415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1560115814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1373519897461</t>
+    <t xml:space="preserve">17.3536396026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1560153961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1373538970947</t>
   </si>
   <si>
     <t xml:space="preserve">18.1186962127686</t>
@@ -1634,19 +1634,19 @@
     <t xml:space="preserve">16.8871440887451</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8684864044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6259078979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5326080322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8498249053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7192077636719</t>
+    <t xml:space="preserve">16.8684844970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6259059906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5326061248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8498229980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7192058563232</t>
   </si>
   <si>
     <t xml:space="preserve">16.9431247711182</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">17.11106300354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6445693969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1034297943115</t>
+    <t xml:space="preserve">16.644567489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1034336090088</t>
   </si>
   <si>
     <t xml:space="preserve">15.3943586349487</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">15.4130191802979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3570375442505</t>
+    <t xml:space="preserve">15.3570404052734</t>
   </si>
   <si>
     <t xml:space="preserve">15.0771408081055</t>
@@ -1679,10 +1679,10 @@
     <t xml:space="preserve">14.591986656189</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7039461135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9838409423828</t>
+    <t xml:space="preserve">14.7039442062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9838418960571</t>
   </si>
   <si>
     <t xml:space="preserve">14.6666259765625</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">14.8718843460083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7412643432617</t>
+    <t xml:space="preserve">14.7412662506104</t>
   </si>
   <si>
     <t xml:space="preserve">14.405387878418</t>
@@ -1721,28 +1721,28 @@
     <t xml:space="preserve">15.3010597229004</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2823991775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5622978210449</t>
+    <t xml:space="preserve">15.2824001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5623006820679</t>
   </si>
   <si>
     <t xml:space="preserve">15.1331214904785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9092044830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4876585006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3197202682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2264213562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9465236663818</t>
+    <t xml:space="preserve">14.9092025756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4876575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3197212219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2264204025269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9465246200562</t>
   </si>
   <si>
     <t xml:space="preserve">14.7785844802856</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">14.4427070617676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.685284614563</t>
+    <t xml:space="preserve">14.6852855682373</t>
   </si>
   <si>
     <t xml:space="preserve">14.5173463821411</t>
@@ -1763,13 +1763,13 @@
     <t xml:space="preserve">14.1814699172974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9948720932007</t>
+    <t xml:space="preserve">13.9948711395264</t>
   </si>
   <si>
     <t xml:space="preserve">13.808274269104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6776552200317</t>
+    <t xml:space="preserve">13.6776533126831</t>
   </si>
   <si>
     <t xml:space="preserve">14.3307495117188</t>
@@ -1778,46 +1778,46 @@
     <t xml:space="preserve">14.1628103256226</t>
   </si>
   <si>
-    <t xml:space="preserve">13.714973449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7522945404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9388914108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8455924987793</t>
+    <t xml:space="preserve">13.7149744033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.752293586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.938892364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8455944061279</t>
   </si>
   <si>
     <t xml:space="preserve">14.1441507339478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9202318191528</t>
+    <t xml:space="preserve">13.9202327728271</t>
   </si>
   <si>
     <t xml:space="preserve">14.4986877441406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9015712738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2637395858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0881719589233</t>
+    <t xml:space="preserve">13.9015731811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2637405395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0881729125977</t>
   </si>
   <si>
     <t xml:space="preserve">14.0135316848755</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3867273330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8905448913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1891031265259</t>
+    <t xml:space="preserve">14.3867292404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8905429840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1891021728516</t>
   </si>
   <si>
     <t xml:space="preserve">14.9740734100342</t>
@@ -1832,13 +1832,13 @@
     <t xml:space="preserve">14.7103796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7857217788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2754373550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5768060684204</t>
+    <t xml:space="preserve">14.785719871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2754383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5768051147461</t>
   </si>
   <si>
     <t xml:space="preserve">16.3490524291992</t>
@@ -1850,31 +1850,31 @@
     <t xml:space="preserve">15.5956382751465</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5579690933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4261207580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.44495677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3507795333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6521463394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6898145675659</t>
+    <t xml:space="preserve">15.5579681396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.426121711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4449558258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3507804870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6521472930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6898155212402</t>
   </si>
   <si>
     <t xml:space="preserve">16.066520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6144742965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5014610290527</t>
+    <t xml:space="preserve">15.6144752502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5014638900757</t>
   </si>
   <si>
     <t xml:space="preserve">15.5391321182251</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">15.9346742630005</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8781700134277</t>
+    <t xml:space="preserve">15.8781681060791</t>
   </si>
   <si>
     <t xml:space="preserve">15.3131093978882</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">15.7274866104126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4637928009033</t>
+    <t xml:space="preserve">15.4637937545776</t>
   </si>
   <si>
     <t xml:space="preserve">15.3319473266602</t>
@@ -1910,22 +1910,22 @@
     <t xml:space="preserve">14.8798980712891</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1059217453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6538743972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8422269821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4090147018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9381322860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8439540863037</t>
+    <t xml:space="preserve">15.1059226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6538734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8422260284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4090156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9381332397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.843955039978</t>
   </si>
   <si>
     <t xml:space="preserve">14.1264848709106</t>
@@ -1934,28 +1934,28 @@
     <t xml:space="preserve">14.5031909942627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6915454864502</t>
+    <t xml:space="preserve">14.6915445327759</t>
   </si>
   <si>
     <t xml:space="preserve">14.4843559265137</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2960014343262</t>
+    <t xml:space="preserve">14.2960023880005</t>
   </si>
   <si>
     <t xml:space="preserve">14.3336734771729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5220260620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2394981384277</t>
+    <t xml:space="preserve">14.522027015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2394971847534</t>
   </si>
   <si>
     <t xml:space="preserve">14.182991027832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9569683074951</t>
+    <t xml:space="preserve">13.9569673538208</t>
   </si>
   <si>
     <t xml:space="preserve">13.5990953445435</t>
@@ -1964,25 +1964,25 @@
     <t xml:space="preserve">13.0528707504272</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9210243225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2788963317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9963655471802</t>
+    <t xml:space="preserve">12.9210252761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2788953781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9963665008545</t>
   </si>
   <si>
     <t xml:space="preserve">12.7138366699219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371295928955</t>
+    <t xml:space="preserve">12.3371305465698</t>
   </si>
   <si>
     <t xml:space="preserve">12.0922718048096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.866247177124</t>
+    <t xml:space="preserve">11.8662481307983</t>
   </si>
   <si>
     <t xml:space="preserve">11.3953647613525</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">10.9621524810791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0580577850342</t>
+    <t xml:space="preserve">10.0580568313599</t>
   </si>
   <si>
     <t xml:space="preserve">9.88853931427002</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">9.53066825866699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85259628295898</t>
+    <t xml:space="preserve">8.8525972366333</t>
   </si>
   <si>
     <t xml:space="preserve">9.35173320770264</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">8.49472618103027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04094982147217</t>
+    <t xml:space="preserve">9.04095077514648</t>
   </si>
   <si>
     <t xml:space="preserve">10.0957279205322</t>
@@ -2021,10 +2021,10 @@
     <t xml:space="preserve">10.6796236038208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8474111557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8080129623413</t>
+    <t xml:space="preserve">11.847412109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8080139160156</t>
   </si>
   <si>
     <t xml:space="preserve">11.52721118927</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">10.8868103027344</t>
   </si>
   <si>
-    <t xml:space="preserve">10.849142074585</t>
+    <t xml:space="preserve">10.8491411209106</t>
   </si>
   <si>
     <t xml:space="preserve">10.566611289978</t>
@@ -2045,43 +2045,43 @@
     <t xml:space="preserve">10.2652454376221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.547776222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6607866287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0374927520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8303050994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.510103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.133397102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81319713592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1522331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4347629547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3594217300415</t>
+    <t xml:space="preserve">10.5477752685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6607875823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0374937057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.830304145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5101041793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1333980560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81319808959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.152232170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4347639083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3594226837158</t>
   </si>
   <si>
     <t xml:space="preserve">10.6984577178955</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6419515609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6231155395508</t>
+    <t xml:space="preserve">10.6419525146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6231164932251</t>
   </si>
   <si>
     <t xml:space="preserve">10.7361278533936</t>
@@ -2090,13 +2090,13 @@
     <t xml:space="preserve">10.7549638748169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4724349975586</t>
+    <t xml:space="preserve">10.4724340438843</t>
   </si>
   <si>
     <t xml:space="preserve">10.9244813919067</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8679761886597</t>
+    <t xml:space="preserve">10.8679752349854</t>
   </si>
   <si>
     <t xml:space="preserve">11.4141998291016</t>
@@ -2105,22 +2105,22 @@
     <t xml:space="preserve">11.489541053772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9809875488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3388576507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4330339431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7155628204346</t>
+    <t xml:space="preserve">10.9809865951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3388586044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4330358505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7155647277832</t>
   </si>
   <si>
     <t xml:space="preserve">11.9227533340454</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2052841186523</t>
+    <t xml:space="preserve">12.2052822113037</t>
   </si>
   <si>
     <t xml:space="preserve">12.1299409866333</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">12.0169296264648</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7720718383789</t>
+    <t xml:space="preserve">11.7720708847046</t>
   </si>
   <si>
     <t xml:space="preserve">11.1505060195923</t>
@@ -2141,22 +2141,22 @@
     <t xml:space="preserve">11.1128349304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0186586380005</t>
+    <t xml:space="preserve">11.0186576843262</t>
   </si>
   <si>
     <t xml:space="preserve">10.811469078064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7172937393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6042814254761</t>
+    <t xml:space="preserve">10.7172946929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6042804718018</t>
   </si>
   <si>
     <t xml:space="preserve">10.3405866622925</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3782587051392</t>
+    <t xml:space="preserve">10.3782577514648</t>
   </si>
   <si>
     <t xml:space="preserve">10.5854463577271</t>
@@ -2168,10 +2168,10 @@
     <t xml:space="preserve">11.2635173797607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2070112228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9998245239258</t>
+    <t xml:space="preserve">11.207010269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9998226165771</t>
   </si>
   <si>
     <t xml:space="preserve">10.9056463241577</t>
@@ -2189,25 +2189,25 @@
     <t xml:space="preserve">11.5648813247681</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3576936721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6025524139404</t>
+    <t xml:space="preserve">11.3576946258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6025533676147</t>
   </si>
   <si>
     <t xml:space="preserve">11.4518699645996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5460472106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4707069396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5837173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6590576171875</t>
+    <t xml:space="preserve">11.546046257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4707059860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5837182998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6590585708618</t>
   </si>
   <si>
     <t xml:space="preserve">12.1487760543823</t>
@@ -2216,28 +2216,28 @@
     <t xml:space="preserve">12.0546007156372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0357646942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.885082244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9039182662964</t>
+    <t xml:space="preserve">12.0357637405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8850831985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9039192199707</t>
   </si>
   <si>
     <t xml:space="preserve">11.7343997955322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6778945922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.169340133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5631542205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5614252090454</t>
+    <t xml:space="preserve">11.6778936386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1693410873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5631551742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5614242553711</t>
   </si>
   <si>
     <t xml:space="preserve">13.2977313995361</t>
@@ -2249,28 +2249,28 @@
     <t xml:space="preserve">13.504919052124</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1470489501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3354024887085</t>
+    <t xml:space="preserve">13.147047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3354015350342</t>
   </si>
   <si>
     <t xml:space="preserve">13.3730707168579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0152006149292</t>
+    <t xml:space="preserve">13.0152025222778</t>
   </si>
   <si>
     <t xml:space="preserve">13.2412252426147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0323076248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6367664337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3165674209595</t>
+    <t xml:space="preserve">14.0323085784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6367654800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3165664672852</t>
   </si>
   <si>
     <t xml:space="preserve">13.0340375900269</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">13.3919076919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0905408859253</t>
+    <t xml:space="preserve">13.0905418395996</t>
   </si>
   <si>
     <t xml:space="preserve">11.9415893554688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9792585372925</t>
+    <t xml:space="preserve">11.9792594909668</t>
   </si>
   <si>
     <t xml:space="preserve">12.2429533004761</t>
@@ -2294,22 +2294,22 @@
     <t xml:space="preserve">12.3559656143188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7703428268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7326717376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9586954116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2223892211914</t>
+    <t xml:space="preserve">12.7703418731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7326707839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9586944580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2223901748657</t>
   </si>
   <si>
     <t xml:space="preserve">13.3542366027832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4672479629517</t>
+    <t xml:space="preserve">13.467248916626</t>
   </si>
   <si>
     <t xml:space="preserve">13.5260181427002</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">13.3167543411255</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3548021316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2216339111328</t>
+    <t xml:space="preserve">13.3548030853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2216348648071</t>
   </si>
   <si>
     <t xml:space="preserve">13.4118747711182</t>
@@ -2342,16 +2342,16 @@
     <t xml:space="preserve">14.077712059021</t>
   </si>
   <si>
-    <t xml:space="preserve">14.058687210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1157598495483</t>
+    <t xml:space="preserve">14.0586881637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1157608032227</t>
   </si>
   <si>
     <t xml:space="preserve">13.8874731063843</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6021127700806</t>
+    <t xml:space="preserve">13.6021137237549</t>
   </si>
   <si>
     <t xml:space="preserve">13.3738269805908</t>
@@ -2360,7 +2360,7 @@
     <t xml:space="preserve">13.6782093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5069932937622</t>
+    <t xml:space="preserve">13.5069942474365</t>
   </si>
   <si>
     <t xml:space="preserve">13.4499225616455</t>
@@ -2369,16 +2369,16 @@
     <t xml:space="preserve">13.6972332000732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6211385726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7733287811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0396642684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.248927116394</t>
+    <t xml:space="preserve">13.6211376190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7733278274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0396633148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2489261627197</t>
   </si>
   <si>
     <t xml:space="preserve">14.6103820800781</t>
@@ -2387,22 +2387,22 @@
     <t xml:space="preserve">14.5342864990234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8957414627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9337902069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3796081542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2274150848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0752239227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.713770866394</t>
+    <t xml:space="preserve">14.8957405090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9337882995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3796062469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2274169921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0752277374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7137699127197</t>
   </si>
   <si>
     <t xml:space="preserve">15.8469371795654</t>
@@ -2411,16 +2411,16 @@
     <t xml:space="preserve">15.6947460174561</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5045070648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2191495895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6376762390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2381715774536</t>
+    <t xml:space="preserve">15.5045080184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2191486358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6376752853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2381734848022</t>
   </si>
   <si>
     <t xml:space="preserve">15.3332920074463</t>
@@ -2432,10 +2432,10 @@
     <t xml:space="preserve">15.7518167495728</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1513195037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4937534332275</t>
+    <t xml:space="preserve">16.1513214111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4937515258789</t>
   </si>
   <si>
     <t xml:space="preserve">16.664966583252</t>
@@ -2447,40 +2447,40 @@
     <t xml:space="preserve">16.5317993164062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6078910827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5888710021973</t>
+    <t xml:space="preserve">16.6078948974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5888729095459</t>
   </si>
   <si>
     <t xml:space="preserve">17.0454444885254</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0264205932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0834941864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.874231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3415622711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3225383758545</t>
+    <t xml:space="preserve">17.0264225006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0834922790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8742294311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3415603637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3225364685059</t>
   </si>
   <si>
     <t xml:space="preserve">16.7981338500977</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5508270263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8361835479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8171577453613</t>
+    <t xml:space="preserve">16.5508251190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.836181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.81715965271</t>
   </si>
   <si>
     <t xml:space="preserve">16.7410621643066</t>
@@ -2489,25 +2489,25 @@
     <t xml:space="preserve">17.8444519042969</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9585933685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.186882019043</t>
+    <t xml:space="preserve">17.9585952758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1868839263916</t>
   </si>
   <si>
     <t xml:space="preserve">19.499532699585</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7848930358887</t>
+    <t xml:space="preserve">19.78489112854</t>
   </si>
   <si>
     <t xml:space="preserve">20.1653709411621</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6422138214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5934104919434</t>
+    <t xml:space="preserve">19.6422119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5934085845947</t>
   </si>
   <si>
     <t xml:space="preserve">20.3556118011475</t>
@@ -2519,10 +2519,10 @@
     <t xml:space="preserve">19.8324508666992</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7373352050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8800106048584</t>
+    <t xml:space="preserve">19.7373332977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.880012512207</t>
   </si>
   <si>
     <t xml:space="preserve">20.2604904174805</t>
@@ -2534,13 +2534,13 @@
     <t xml:space="preserve">20.4982891082764</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8312091827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7360897064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2129306793213</t>
+    <t xml:space="preserve">20.8312110900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7360877990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2129325866699</t>
   </si>
   <si>
     <t xml:space="preserve">19.9275741577148</t>
@@ -2549,19 +2549,19 @@
     <t xml:space="preserve">20.7836494445801</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5946559906006</t>
+    <t xml:space="preserve">19.594654083252</t>
   </si>
   <si>
     <t xml:space="preserve">19.3568553924561</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2141742706299</t>
+    <t xml:space="preserve">19.2141761779785</t>
   </si>
   <si>
     <t xml:space="preserve">19.4044132232666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6897754669189</t>
+    <t xml:space="preserve">19.6897735595703</t>
   </si>
   <si>
     <t xml:space="preserve">19.0239353179932</t>
@@ -2579,19 +2579,19 @@
     <t xml:space="preserve">20.9738864898682</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5446071624756</t>
+    <t xml:space="preserve">21.544605255127</t>
   </si>
   <si>
     <t xml:space="preserve">21.1641292572021</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6397266387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5921669006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6872844696045</t>
+    <t xml:space="preserve">21.6397247314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5921649932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6872863769531</t>
   </si>
   <si>
     <t xml:space="preserve">21.4019260406494</t>
@@ -2600,28 +2600,28 @@
     <t xml:space="preserve">21.7348461151123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8299655914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0690059661865</t>
+    <t xml:space="preserve">21.8299674987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0690078735352</t>
   </si>
   <si>
     <t xml:space="preserve">21.2116870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3068084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1628837585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6384830474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1616401672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4958038330078</t>
+    <t xml:space="preserve">21.3068065643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1628856658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6384811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.161642074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4958019256592</t>
   </si>
   <si>
     <t xml:space="preserve">22.2580032348633</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">21.8775253295898</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4970474243164</t>
+    <t xml:space="preserve">21.497049331665</t>
   </si>
   <si>
     <t xml:space="preserve">21.2592487335205</t>
@@ -2639,16 +2639,16 @@
     <t xml:space="preserve">20.6885299682617</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6409721374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7824058532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3506374359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7799205780029</t>
+    <t xml:space="preserve">20.6409683227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7824077606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3506393432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7799167633057</t>
   </si>
   <si>
     <t xml:space="preserve">23.3043212890625</t>
@@ -2657,25 +2657,25 @@
     <t xml:space="preserve">23.2567596435547</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0189628601074</t>
+    <t xml:space="preserve">23.0189647674561</t>
   </si>
   <si>
     <t xml:space="preserve">23.1140804290771</t>
   </si>
   <si>
-    <t xml:space="preserve">23.351879119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.066520690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5896797180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.44700050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9238414764404</t>
+    <t xml:space="preserve">23.3518810272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0665225982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5896778106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4469985961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9238395690918</t>
   </si>
   <si>
     <t xml:space="preserve">23.6372413635254</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">23.5421199798584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4945621490479</t>
+    <t xml:space="preserve">23.4945602416992</t>
   </si>
   <si>
     <t xml:space="preserve">22.8762798309326</t>
@@ -2711,22 +2711,22 @@
     <t xml:space="preserve">22.0202045440674</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0652751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7323608398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3030776977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.875036239624</t>
+    <t xml:space="preserve">24.0652770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7323589324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3030796051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8750381469727</t>
   </si>
   <si>
     <t xml:space="preserve">23.6848011016846</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3018341064453</t>
+    <t xml:space="preserve">25.3018360137939</t>
   </si>
   <si>
     <t xml:space="preserve">25.5871925354004</t>
@@ -2738,10 +2738,10 @@
     <t xml:space="preserve">25.6823120117188</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6347522735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7774353027344</t>
+    <t xml:space="preserve">25.6347560882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7774333953857</t>
   </si>
   <si>
     <t xml:space="preserve">25.492073059082</t>
@@ -2753,16 +2753,16 @@
     <t xml:space="preserve">26.3957099914551</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2993488311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2042255401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.156665802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6798286437988</t>
+    <t xml:space="preserve">27.2993450164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2042274475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1566677093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6798248291016</t>
   </si>
   <si>
     <t xml:space="preserve">28.2981052398682</t>
@@ -2777,13 +2777,13 @@
     <t xml:space="preserve">27.5847053527832</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4420261383057</t>
+    <t xml:space="preserve">27.4420280456543</t>
   </si>
   <si>
     <t xml:space="preserve">27.5371475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3469085693359</t>
+    <t xml:space="preserve">27.3469066619873</t>
   </si>
   <si>
     <t xml:space="preserve">27.0615482330322</t>
@@ -2792,10 +2792,10 @@
     <t xml:space="preserve">26.7761898040771</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9664268493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8713092803955</t>
+    <t xml:space="preserve">26.9664287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8713073730469</t>
   </si>
   <si>
     <t xml:space="preserve">26.5383911132812</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">26.0770359039307</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6464042663574</t>
+    <t xml:space="preserve">25.6464023590088</t>
   </si>
   <si>
     <t xml:space="preserve">25.2636241912842</t>
@@ -2834,25 +2834,25 @@
     <t xml:space="preserve">26.2205791473389</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6512107849121</t>
+    <t xml:space="preserve">26.6512088775635</t>
   </si>
   <si>
     <t xml:space="preserve">26.2684268951416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7420997619629</t>
+    <t xml:space="preserve">25.7421016693115</t>
   </si>
   <si>
     <t xml:space="preserve">25.6942539215088</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3114719390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5507106781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9765357971191</t>
+    <t xml:space="preserve">25.3114700317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5507125854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9765377044678</t>
   </si>
   <si>
     <t xml:space="preserve">25.4071655273438</t>
@@ -2861,10 +2861,10 @@
     <t xml:space="preserve">25.9334926605225</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8856449127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7899475097656</t>
+    <t xml:space="preserve">25.8856410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7899494171143</t>
   </si>
   <si>
     <t xml:space="preserve">25.9813404083252</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">25.4550151824951</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6894493103027</t>
+    <t xml:space="preserve">24.6894474029541</t>
   </si>
   <si>
     <t xml:space="preserve">25.5028610229492</t>
@@ -2882,31 +2882,31 @@
     <t xml:space="preserve">25.359317779541</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8808422088623</t>
+    <t xml:space="preserve">24.8808403015137</t>
   </si>
   <si>
     <t xml:space="preserve">24.3066654205322</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8233871459961</t>
+    <t xml:space="preserve">22.8233852386475</t>
   </si>
   <si>
     <t xml:space="preserve">22.6319961547852</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4932537078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8712368011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7755393981934</t>
+    <t xml:space="preserve">23.4932518005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8712348937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7755374908447</t>
   </si>
   <si>
     <t xml:space="preserve">23.0626258850098</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2540168762207</t>
+    <t xml:space="preserve">23.2540149688721</t>
   </si>
   <si>
     <t xml:space="preserve">22.2970600128174</t>
@@ -2915,13 +2915,13 @@
     <t xml:space="preserve">21.81858253479</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6750411987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4358024597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.488452911377</t>
+    <t xml:space="preserve">21.6750392913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4358005523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4884510040283</t>
   </si>
   <si>
     <t xml:space="preserve">22.6798439025879</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">22.3449096679688</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9621257781982</t>
+    <t xml:space="preserve">21.9621276855469</t>
   </si>
   <si>
     <t xml:space="preserve">23.0147762298584</t>
@@ -2939,13 +2939,13 @@
     <t xml:space="preserve">22.009973526001</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9142799377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2444133758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0051708221436</t>
+    <t xml:space="preserve">21.9142818450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2444114685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0051727294922</t>
   </si>
   <si>
     <t xml:space="preserve">20.3831481933594</t>
@@ -2966,19 +2966,19 @@
     <t xml:space="preserve">19.0242729187012</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0099029541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7849998474121</t>
+    <t xml:space="preserve">18.0098991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7849979400635</t>
   </si>
   <si>
     <t xml:space="preserve">16.842414855957</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8950672149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0290412902832</t>
+    <t xml:space="preserve">17.8950691223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0290393829346</t>
   </si>
   <si>
     <t xml:space="preserve">17.4357280731201</t>
@@ -2990,16 +2990,16 @@
     <t xml:space="preserve">17.7228164672852</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3783111572266</t>
+    <t xml:space="preserve">17.3783092498779</t>
   </si>
   <si>
     <t xml:space="preserve">18.5457954406738</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1438751220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2012901306152</t>
+    <t xml:space="preserve">18.1438732147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2012920379639</t>
   </si>
   <si>
     <t xml:space="preserve">18.5649356842041</t>
@@ -3008,25 +3008,25 @@
     <t xml:space="preserve">18.2587089538574</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6414928436279</t>
+    <t xml:space="preserve">18.6414909362793</t>
   </si>
   <si>
     <t xml:space="preserve">18.9477157592773</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0625534057617</t>
+    <t xml:space="preserve">19.0625514984131</t>
   </si>
   <si>
     <t xml:space="preserve">19.4740428924561</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9859962463379</t>
+    <t xml:space="preserve">18.9859943389893</t>
   </si>
   <si>
     <t xml:space="preserve">19.0816917419434</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5075168609619</t>
+    <t xml:space="preserve">18.5075187683105</t>
   </si>
   <si>
     <t xml:space="preserve">17.6462574005127</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">18.603214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2826519012451</t>
+    <t xml:space="preserve">19.2826538085938</t>
   </si>
   <si>
     <t xml:space="preserve">19.6175842285156</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">18.622350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">18.794605255127</t>
+    <t xml:space="preserve">18.7946033477783</t>
   </si>
   <si>
     <t xml:space="preserve">19.2348041534424</t>
@@ -3065,25 +3065,25 @@
     <t xml:space="preserve">17.4165897369385</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6079788208008</t>
+    <t xml:space="preserve">17.6079769134521</t>
   </si>
   <si>
     <t xml:space="preserve">17.9716243743896</t>
   </si>
   <si>
-    <t xml:space="preserve">19.665433883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9046745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.861629486084</t>
+    <t xml:space="preserve">19.6654319763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9046726226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8616275787354</t>
   </si>
   <si>
     <t xml:space="preserve">20.5745429992676</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9094772338867</t>
+    <t xml:space="preserve">20.9094753265381</t>
   </si>
   <si>
     <t xml:space="preserve">21.3401050567627</t>
@@ -3095,43 +3095,43 @@
     <t xml:space="preserve">21.7228889465332</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2492141723633</t>
+    <t xml:space="preserve">22.2492122650146</t>
   </si>
   <si>
     <t xml:space="preserve">22.9669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1583213806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3927555084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0578231811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2874546051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.670238494873</t>
+    <t xml:space="preserve">23.1583232879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3927574157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0578212738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2874565124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6702346801758</t>
   </si>
   <si>
     <t xml:space="preserve">19.7611293792725</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0960636138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3353023529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7132835388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1199684143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6606311798096</t>
+    <t xml:space="preserve">20.0960655212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3353042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7132816314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1199703216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6606292724609</t>
   </si>
   <si>
     <t xml:space="preserve">18.4692401885986</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">17.9524841308594</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4309635162354</t>
+    <t xml:space="preserve">18.4309616088867</t>
   </si>
   <si>
     <t xml:space="preserve">18.5840740203857</t>
@@ -3164,13 +3164,13 @@
     <t xml:space="preserve">18.4118213653564</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3161239624023</t>
+    <t xml:space="preserve">18.316125869751</t>
   </si>
   <si>
     <t xml:space="preserve">18.163013458252</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8567867279053</t>
+    <t xml:space="preserve">17.8567886352539</t>
   </si>
   <si>
     <t xml:space="preserve">18.4500999450684</t>
@@ -3179,22 +3179,22 @@
     <t xml:space="preserve">19.186954498291</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7180461883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8520240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3304996490479</t>
+    <t xml:space="preserve">18.7180480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8520221710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3305015563965</t>
   </si>
   <si>
     <t xml:space="preserve">18.0481796264648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5888404846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7993717193604</t>
+    <t xml:space="preserve">17.5888385772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7993698120117</t>
   </si>
   <si>
     <t xml:space="preserve">17.5122852325439</t>
@@ -3206,31 +3206,31 @@
     <t xml:space="preserve">18.1247367858887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5505619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2251968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5170478820801</t>
+    <t xml:space="preserve">17.5505638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2251987457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5170497894287</t>
   </si>
   <si>
     <t xml:space="preserve">15.8854608535767</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3448009490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0959892272949</t>
+    <t xml:space="preserve">16.344799041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0959911346436</t>
   </si>
   <si>
     <t xml:space="preserve">15.9428768157959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1151294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3112869262695</t>
+    <t xml:space="preserve">16.1151313781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3112859725952</t>
   </si>
   <si>
     <t xml:space="preserve">15.4452590942383</t>
@@ -3242,16 +3242,16 @@
     <t xml:space="preserve">16.6127452850342</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0194339752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6510257720947</t>
+    <t xml:space="preserve">16.0194320678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6510238647461</t>
   </si>
   <si>
     <t xml:space="preserve">16.7658596038818</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9955291748047</t>
+    <t xml:space="preserve">16.9955272674561</t>
   </si>
   <si>
     <t xml:space="preserve">17.3208923339844</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">17.0529460906982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0146675109863</t>
+    <t xml:space="preserve">17.014669418335</t>
   </si>
   <si>
     <t xml:space="preserve">17.8376483917236</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">18.756326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6989078521729</t>
+    <t xml:space="preserve">18.6989097595215</t>
   </si>
   <si>
     <t xml:space="preserve">19.4261932373047</t>
@@ -3281,10 +3281,10 @@
     <t xml:space="preserve">19.9525203704834</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0003662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5697383880615</t>
+    <t xml:space="preserve">20.0003681182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5697402954102</t>
   </si>
   <si>
     <t xml:space="preserve">20.4309959411621</t>
@@ -4644,6 +4644,9 @@
   </si>
   <si>
     <t xml:space="preserve">47.7999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2000007629395</t>
   </si>
 </sst>
 </file>
@@ -70502,7 +70505,7 @@
     </row>
     <row r="2521">
       <c r="A2521" s="1" t="n">
-        <v>45988.6910069444</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2521" t="n">
         <v>25304</v>
@@ -70523,6 +70526,32 @@
         <v>1543</v>
       </c>
       <c r="H2521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>45989.6912615741</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>41573</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>48.7000007629395</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>47.9000015258789</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>48.2000007629395</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>1544</v>
+      </c>
+      <c r="H2522" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="1544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="1545">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,64 +38,64 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5902528762817</t>
+    <t xml:space="preserve">15.5902509689331</t>
   </si>
   <si>
     <t xml:space="preserve">DAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7186374664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2234210968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5356159210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2146425247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9395198822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2880058288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0403985977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8661518096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1049814224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7931776046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8848857879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2887859344482</t>
+    <t xml:space="preserve">15.7186403274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2234239578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5356168746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2146406173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9395189285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2880048751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.040397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.866153717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1049823760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7931747436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8848838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2887849807739</t>
   </si>
   <si>
     <t xml:space="preserve">12.9490795135498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1324939727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8928852081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0487899780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3239078521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.085470199585</t>
+    <t xml:space="preserve">13.1324949264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8928861618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0487880706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3239116668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0854759216309</t>
   </si>
   <si>
     <t xml:space="preserve">16.3605937957764</t>
@@ -107,61 +107,61 @@
     <t xml:space="preserve">16.5990333557129</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4710302352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1038112640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3059577941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9391288757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9483003616333</t>
+    <t xml:space="preserve">15.4710321426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1038131713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3059587478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9391307830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.948299407959</t>
   </si>
   <si>
     <t xml:space="preserve">15.3518133163452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1042003631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0033226013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9112300872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2322025299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7641086578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9200115203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0575714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9658660888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.709077835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3514232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3422527313232</t>
+    <t xml:space="preserve">15.1042022705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0033235549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.911226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2322044372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7641048431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9200077056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0575695037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9658603668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7090816497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3514213562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3422508239746</t>
   </si>
   <si>
     <t xml:space="preserve">16.8283004760742</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6357135772705</t>
+    <t xml:space="preserve">16.6357173919678</t>
   </si>
   <si>
     <t xml:space="preserve">17.1767883300781</t>
@@ -176,22 +176,22 @@
     <t xml:space="preserve">17.433572769165</t>
   </si>
   <si>
-    <t xml:space="preserve">16.534839630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2226448059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5161056518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8741569519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2593250274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4610824584961</t>
+    <t xml:space="preserve">16.5348377227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2226428985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5161094665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8741550445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2593231201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4610805511475</t>
   </si>
   <si>
     <t xml:space="preserve">17.0117149353027</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">16.2138614654541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5531787872314</t>
+    <t xml:space="preserve">16.5531806945801</t>
   </si>
   <si>
     <t xml:space="preserve">16.9383506774902</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">17.2868404388428</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5715198516846</t>
+    <t xml:space="preserve">16.5715179443359</t>
   </si>
   <si>
     <t xml:space="preserve">16.5256671905518</t>
@@ -218,40 +218,40 @@
     <t xml:space="preserve">17.1217651367188</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5619583129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6353244781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4060554504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.864595413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1122035980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0204963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7912311553955</t>
+    <t xml:space="preserve">17.5619621276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6353282928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4060573577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8645935058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1122016906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0204982757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7912292480469</t>
   </si>
   <si>
     <t xml:space="preserve">17.5986442565918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3414726257324</t>
+    <t xml:space="preserve">18.3414707183838</t>
   </si>
   <si>
     <t xml:space="preserve">18.4056663513184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4331817626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0938625335693</t>
+    <t xml:space="preserve">18.4331798553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0938606262207</t>
   </si>
   <si>
     <t xml:space="preserve">18.3231296539307</t>
@@ -260,31 +260,31 @@
     <t xml:space="preserve">18.0296669006348</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8921051025391</t>
+    <t xml:space="preserve">17.8921070098877</t>
   </si>
   <si>
     <t xml:space="preserve">17.4702529907227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1492767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4885959625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1676158905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0759105682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7732772827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8374729156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.562349319458</t>
+    <t xml:space="preserve">17.1492748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4885921478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1676177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0759086608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7732791900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8374710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5623512268066</t>
   </si>
   <si>
     <t xml:space="preserve">16.3147430419922</t>
@@ -293,16 +293,16 @@
     <t xml:space="preserve">16.1496677398682</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2505474090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7457618713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4523048400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.415620803833</t>
+    <t xml:space="preserve">16.2505416870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7457656860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4523010253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4156169891357</t>
   </si>
   <si>
     <t xml:space="preserve">16.1680088043213</t>
@@ -311,67 +311,67 @@
     <t xml:space="preserve">17.3602027893066</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5164966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4981555938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2409820556641</t>
+    <t xml:space="preserve">16.5164985656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4981536865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2409839630127</t>
   </si>
   <si>
     <t xml:space="preserve">16.9933700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0392284393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8103475570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8470335006714</t>
+    <t xml:space="preserve">17.0392265319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8103494644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8470306396484</t>
   </si>
   <si>
     <t xml:space="preserve">14.9574699401855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7648868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0675201416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3334722518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9570837020874</t>
+    <t xml:space="preserve">14.7648849487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0675191879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3334693908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9570798873901</t>
   </si>
   <si>
     <t xml:space="preserve">14.9849834442139</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4530811309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.884105682373</t>
+    <t xml:space="preserve">14.4530801773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8841037750244</t>
   </si>
   <si>
     <t xml:space="preserve">14.5264463424683</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6823492050171</t>
+    <t xml:space="preserve">14.6823472976685</t>
   </si>
   <si>
     <t xml:space="preserve">15.4068365097046</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0308361053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6273231506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0037145614624</t>
+    <t xml:space="preserve">15.030837059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6273260116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0037155151367</t>
   </si>
   <si>
     <t xml:space="preserve">14.2604951858521</t>
@@ -380,52 +380,52 @@
     <t xml:space="preserve">14.6548357009888</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3976678848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.315128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4985466003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2509355545044</t>
+    <t xml:space="preserve">15.3976669311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3151302337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4985418319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2509346008301</t>
   </si>
   <si>
     <t xml:space="preserve">15.3242998123169</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2967882156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3793239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.140495300293</t>
+    <t xml:space="preserve">15.2967872619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3793249130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1404972076416</t>
   </si>
   <si>
     <t xml:space="preserve">15.6177625656128</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3884963989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1221523284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8286905288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0762996673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1771755218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0671329498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9845905303955</t>
+    <t xml:space="preserve">15.3884954452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1221561431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8286914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.076301574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1771793365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0671291351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9845933914185</t>
   </si>
   <si>
     <t xml:space="preserve">17.1401062011719</t>
@@ -434,115 +434,115 @@
     <t xml:space="preserve">16.8099575042725</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6082038879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6448841094971</t>
+    <t xml:space="preserve">16.6082019805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6448860168457</t>
   </si>
   <si>
     <t xml:space="preserve">17.6078147888184</t>
   </si>
   <si>
-    <t xml:space="preserve">17.158447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0300579071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1951293945312</t>
+    <t xml:space="preserve">17.1584453582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0300559997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1951313018799</t>
   </si>
   <si>
     <t xml:space="preserve">17.332691192627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0946407318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7828369140625</t>
+    <t xml:space="preserve">16.0946426391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7828350067139</t>
   </si>
   <si>
     <t xml:space="preserve">15.7553262710571</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8195190429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9479112625122</t>
+    <t xml:space="preserve">15.8195199966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9479074478149</t>
   </si>
   <si>
     <t xml:space="preserve">15.6361036300659</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6636171340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5627365112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4893732070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6085939407349</t>
+    <t xml:space="preserve">15.6636190414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5627384185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893712997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6085910797119</t>
   </si>
   <si>
     <t xml:space="preserve">16.0304470062256</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6999130249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0579586029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5352277755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5443983078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7003030776978</t>
+    <t xml:space="preserve">16.6999092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0579605102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5352258682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5443992614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7002992630005</t>
   </si>
   <si>
     <t xml:space="preserve">15.3609828948975</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1592273712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2330389022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3068513870239</t>
+    <t xml:space="preserve">15.1592254638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2330408096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3068523406982</t>
   </si>
   <si>
     <t xml:space="preserve">15.5467443466187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6297817230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7866353988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5190601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9746961593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3253049850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4175691604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4083433151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0577354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7589559555054</t>
+    <t xml:space="preserve">15.6297807693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7866325378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5190649032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9746952056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3253059387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4175701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4083461761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0577363967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7589550018311</t>
   </si>
   <si>
     <t xml:space="preserve">16.2202816009521</t>
@@ -551,67 +551,67 @@
     <t xml:space="preserve">15.8235368728638</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5006084442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2145872116089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7774057388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9434871673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7312707901001</t>
+    <t xml:space="preserve">15.3898906707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5006093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2145853042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7774066925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9434833526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7312717437744</t>
   </si>
   <si>
     <t xml:space="preserve">16.4693984985352</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0691261291504</t>
+    <t xml:space="preserve">17.0691223144531</t>
   </si>
   <si>
     <t xml:space="preserve">17.1429347991943</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0229949951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1060333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9122734069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8384609222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3771324157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9768619537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7923278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.050666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6227188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7795677185059</t>
+    <t xml:space="preserve">17.0229911804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1060314178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9122714996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8384590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3771305084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9768581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7923259735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0506706237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6227207183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7795715332031</t>
   </si>
   <si>
     <t xml:space="preserve">17.8164749145508</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7611122131348</t>
+    <t xml:space="preserve">17.761116027832</t>
   </si>
   <si>
     <t xml:space="preserve">18.3054828643799</t>
@@ -620,70 +620,70 @@
     <t xml:space="preserve">18.7760372161865</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8221683502197</t>
+    <t xml:space="preserve">18.822172164917</t>
   </si>
   <si>
     <t xml:space="preserve">19.4218940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4957065582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9882469177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7852630615234</t>
+    <t xml:space="preserve">19.4957046508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9882431030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7852668762207</t>
   </si>
   <si>
     <t xml:space="preserve">19.3296298980713</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2004547119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0528354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9513397216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7299022674561</t>
+    <t xml:space="preserve">19.2004585266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0528335571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9513416290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7299041748047</t>
   </si>
   <si>
     <t xml:space="preserve">18.886754989624</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8129425048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8037166595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6284122467041</t>
+    <t xml:space="preserve">18.8129463195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8037147521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6284141540527</t>
   </si>
   <si>
     <t xml:space="preserve">18.4531059265137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2778015136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9917793273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3331642150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4069728851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3423862457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2501220703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.36083984375</t>
+    <t xml:space="preserve">18.2777996063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9917774200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3331623077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4069747924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3423843383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2501239776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3608417510986</t>
   </si>
   <si>
     <t xml:space="preserve">18.1578578948975</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">18.4900150299072</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4992389678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6007328033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9144344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2834968566895</t>
+    <t xml:space="preserve">18.4992408752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6007289886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.914436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2834987640381</t>
   </si>
   <si>
     <t xml:space="preserve">18.9605674743652</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">18.9974727630615</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2373638153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3204021453857</t>
+    <t xml:space="preserve">19.2373657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3204002380371</t>
   </si>
   <si>
     <t xml:space="preserve">18.8313941955566</t>
@@ -728,19 +728,19 @@
     <t xml:space="preserve">19.1174182891846</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3757629394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9697952270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0897388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2189140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9052066802979</t>
+    <t xml:space="preserve">19.3757610321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9697933197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0897369384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2189121246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9052085876465</t>
   </si>
   <si>
     <t xml:space="preserve">19.0989665985107</t>
@@ -749,37 +749,37 @@
     <t xml:space="preserve">19.2558193206787</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1543273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7817287445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8739948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2430610656738</t>
+    <t xml:space="preserve">19.1543235778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7817306518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8739986419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2430572509766</t>
   </si>
   <si>
     <t xml:space="preserve">20.4829502105713</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7136154174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.824333190918</t>
+    <t xml:space="preserve">20.7136135101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8243293762207</t>
   </si>
   <si>
     <t xml:space="preserve">20.8058776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0123920440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4737224578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2522850036621</t>
+    <t xml:space="preserve">20.0123977661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4737205505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2522869110107</t>
   </si>
   <si>
     <t xml:space="preserve">20.1138858795166</t>
@@ -788,73 +788,73 @@
     <t xml:space="preserve">20.4368152618408</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5106296539307</t>
+    <t xml:space="preserve">20.5106239318848</t>
   </si>
   <si>
     <t xml:space="preserve">20.4644947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3630046844482</t>
+    <t xml:space="preserve">20.3630027770996</t>
   </si>
   <si>
     <t xml:space="preserve">20.3906841278076</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5198574066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3445472717285</t>
+    <t xml:space="preserve">20.5198535919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3445491790771</t>
   </si>
   <si>
     <t xml:space="preserve">20.6767063140869</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7228393554688</t>
+    <t xml:space="preserve">20.7228412628174</t>
   </si>
   <si>
     <t xml:space="preserve">20.316873550415</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6398010253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4978675842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3502445220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2210712432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1749401092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9904079437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9811820983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7874240875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1288089752197</t>
+    <t xml:space="preserve">20.6398029327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4978713989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3502426147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2210750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1749420166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9904098510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9811840057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7874279022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1288108825684</t>
   </si>
   <si>
     <t xml:space="preserve">20.9627285003662</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2026176452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0826778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5014019012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0273170471191</t>
+    <t xml:space="preserve">21.2026195526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0826740264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5013999938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0273151397705</t>
   </si>
   <si>
     <t xml:space="preserve">20.8151035308838</t>
@@ -863,16 +863,16 @@
     <t xml:space="preserve">20.9719543457031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1011276245117</t>
+    <t xml:space="preserve">21.1103553771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1011295318604</t>
   </si>
   <si>
     <t xml:space="preserve">21.1933937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">21.138032913208</t>
+    <t xml:space="preserve">21.1380367279053</t>
   </si>
   <si>
     <t xml:space="preserve">20.79665184021</t>
@@ -887,118 +887,118 @@
     <t xml:space="preserve">20.1784744262695</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2615089416504</t>
+    <t xml:space="preserve">20.2615127563477</t>
   </si>
   <si>
     <t xml:space="preserve">20.2707366943359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1876983642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4921741485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1415634155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9109020233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0769786834717</t>
+    <t xml:space="preserve">20.1876945495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4921760559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1415672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9109058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0769805908203</t>
   </si>
   <si>
     <t xml:space="preserve">19.6617870330811</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7725067138672</t>
+    <t xml:space="preserve">19.7725048065186</t>
   </si>
   <si>
     <t xml:space="preserve">20.1323394775391</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1600208282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4091396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2984161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8186378479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6986923217773</t>
+    <t xml:space="preserve">20.1600189208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4091377258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2984199523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8186340332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6986904144287</t>
   </si>
   <si>
     <t xml:space="preserve">19.7540493011475</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5879745483398</t>
+    <t xml:space="preserve">19.5879726409912</t>
   </si>
   <si>
     <t xml:space="preserve">19.790958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9385795593262</t>
+    <t xml:space="preserve">19.9385833740234</t>
   </si>
   <si>
     <t xml:space="preserve">19.8647708892822</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9754867553711</t>
+    <t xml:space="preserve">19.9754905700684</t>
   </si>
   <si>
     <t xml:space="preserve">19.5418395996094</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5290794372559</t>
+    <t xml:space="preserve">20.5290832519531</t>
   </si>
   <si>
     <t xml:space="preserve">20.1046619415283</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8370914459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5971984863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2799644470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9939441680908</t>
+    <t xml:space="preserve">19.8370895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5972003936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2799625396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9939422607422</t>
   </si>
   <si>
     <t xml:space="preserve">20.3537769317627</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7043876647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2061519622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4275894165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7505207061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0549945831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5844383239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3353252410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1969261169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2338314056396</t>
+    <t xml:space="preserve">20.7043857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2061538696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4275875091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7505187988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0549926757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5844421386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3353271484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1969223022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2338333129883</t>
   </si>
   <si>
     <t xml:space="preserve">19.7448234558105</t>
@@ -1007,112 +1007,112 @@
     <t xml:space="preserve">19.7079181671143</t>
   </si>
   <si>
-    <t xml:space="preserve">19.634105682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8463153839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9570350646973</t>
+    <t xml:space="preserve">19.6341037750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8463172912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.95703125</t>
   </si>
   <si>
     <t xml:space="preserve">20.3814563751221</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8555431365967</t>
+    <t xml:space="preserve">19.8555450439453</t>
   </si>
   <si>
     <t xml:space="preserve">19.4034423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1266422271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6560897827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7114543914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5084667205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8683013916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5545997619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4346542358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5361480712891</t>
+    <t xml:space="preserve">19.1266441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6560916900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7114524841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5084648132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8683032989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5546016693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4346523284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5361461639404</t>
   </si>
   <si>
     <t xml:space="preserve">18.3147068023682</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6837673187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0067024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.849760055542</t>
+    <t xml:space="preserve">18.6837711334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0067005157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8497581481934</t>
   </si>
   <si>
     <t xml:space="preserve">18.8219413757324</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4047050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1821804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7834892272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7278614044189</t>
+    <t xml:space="preserve">18.4047069549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1821842193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7834930419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7278575897217</t>
   </si>
   <si>
     <t xml:space="preserve">17.5238761901855</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5516948699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8205757141113</t>
+    <t xml:space="preserve">17.5516929626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.82057762146</t>
   </si>
   <si>
     <t xml:space="preserve">17.7742195129395</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8483905792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1450958251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3398036956787</t>
+    <t xml:space="preserve">17.8483943939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.145092010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3398056030273</t>
   </si>
   <si>
     <t xml:space="preserve">18.4603366851807</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2841701507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0431022644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3676204681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2378120422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0987377166748</t>
+    <t xml:space="preserve">18.2841682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0431003570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3676166534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.237813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0987358093262</t>
   </si>
   <si>
     <t xml:space="preserve">18.5437850952148</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">18.5716018676758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5623321533203</t>
+    <t xml:space="preserve">18.5623302459717</t>
   </si>
   <si>
     <t xml:space="preserve">18.4881553649902</t>
@@ -1136,28 +1136,28 @@
     <t xml:space="preserve">18.2563571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3212623596191</t>
+    <t xml:space="preserve">18.3212585449219</t>
   </si>
   <si>
     <t xml:space="preserve">18.3583450317383</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3490772247314</t>
+    <t xml:space="preserve">18.3490734100342</t>
   </si>
   <si>
     <t xml:space="preserve">18.5345134735107</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5808734893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4696102142334</t>
+    <t xml:space="preserve">18.5808715820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.469612121582</t>
   </si>
   <si>
     <t xml:space="preserve">18.2656288146973</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3768920898438</t>
+    <t xml:space="preserve">18.3768882751465</t>
   </si>
   <si>
     <t xml:space="preserve">18.7755813598633</t>
@@ -1169,31 +1169,31 @@
     <t xml:space="preserve">19.3318977355957</t>
   </si>
   <si>
-    <t xml:space="preserve">19.610050201416</t>
+    <t xml:space="preserve">19.6100540161133</t>
   </si>
   <si>
     <t xml:space="preserve">20.3981628417969</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1399154663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4180698394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.371711730957</t>
+    <t xml:space="preserve">21.13991355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4180736541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3717136383057</t>
   </si>
   <si>
     <t xml:space="preserve">21.2326354980469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4644298553467</t>
+    <t xml:space="preserve">21.4644336700439</t>
   </si>
   <si>
     <t xml:space="preserve">21.3253536224365</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6035060882568</t>
+    <t xml:space="preserve">21.6035099029541</t>
   </si>
   <si>
     <t xml:space="preserve">21.6498699188232</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">20.3054447174072</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9081172943115</t>
+    <t xml:space="preserve">20.9081192016602</t>
   </si>
   <si>
     <t xml:space="preserve">20.4908828735352</t>
@@ -1214,19 +1214,19 @@
     <t xml:space="preserve">20.6299591064453</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5836048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9544773101807</t>
+    <t xml:space="preserve">20.5836029052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.954475402832</t>
   </si>
   <si>
     <t xml:space="preserve">21.0471954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0008354187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7226810455322</t>
+    <t xml:space="preserve">21.0008335113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7226791381836</t>
   </si>
   <si>
     <t xml:space="preserve">20.5372409820557</t>
@@ -1241,10 +1241,10 @@
     <t xml:space="preserve">21.7425899505615</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9280242919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8353042602539</t>
+    <t xml:space="preserve">21.9280261993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8353080749512</t>
   </si>
   <si>
     <t xml:space="preserve">20.6763191223145</t>
@@ -1253,76 +1253,76 @@
     <t xml:space="preserve">21.0935554504395</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1663665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0736465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7690410614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4445209503174</t>
+    <t xml:space="preserve">20.1663684844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0736484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7690391540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.444522857666</t>
   </si>
   <si>
     <t xml:space="preserve">20.8154010772705</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1862773895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2590885162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.351806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9809284210205</t>
+    <t xml:space="preserve">21.1862754821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2590866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3518028259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9809303283691</t>
   </si>
   <si>
     <t xml:space="preserve">18.9146614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0073795318604</t>
+    <t xml:space="preserve">19.007381439209</t>
   </si>
   <si>
     <t xml:space="preserve">19.1928176879883</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6564140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4709758758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2127246856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1200084686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8418502807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0272884368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8882122039795</t>
+    <t xml:space="preserve">19.6564159393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4709739685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2127265930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1200103759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8418483734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0272903442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8882102966309</t>
   </si>
   <si>
     <t xml:space="preserve">19.7491302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7954921722412</t>
+    <t xml:space="preserve">19.7954902648926</t>
   </si>
   <si>
     <t xml:space="preserve">19.2855358123779</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4246158599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3782577514648</t>
+    <t xml:space="preserve">19.4246139526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3782558441162</t>
   </si>
   <si>
     <t xml:space="preserve">19.517333984375</t>
@@ -1331,64 +1331,64 @@
     <t xml:space="preserve">19.5636940002441</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1464614868164</t>
+    <t xml:space="preserve">19.1464576721191</t>
   </si>
   <si>
     <t xml:space="preserve">19.1000995635986</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2391796112061</t>
+    <t xml:space="preserve">19.2391777038574</t>
   </si>
   <si>
     <t xml:space="preserve">19.7027721405029</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2789936065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9345722198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5980491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2059049606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5953216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6681356430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.371434211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7052221298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.298623085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5211496353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8920211791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4284296035767</t>
+    <t xml:space="preserve">21.278995513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9345684051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5980529785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2059030532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5953245162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6681346893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3714332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7052211761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2986211776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5211477279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8920230865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4284286499023</t>
   </si>
   <si>
     <t xml:space="preserve">15.2244482040405</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3542537689209</t>
+    <t xml:space="preserve">15.3542528152466</t>
   </si>
   <si>
     <t xml:space="preserve">15.7622165679932</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6880416870117</t>
+    <t xml:space="preserve">15.688042640686</t>
   </si>
   <si>
     <t xml:space="preserve">15.5582370758057</t>
@@ -1397,43 +1397,43 @@
     <t xml:space="preserve">15.4840602874756</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2800779342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9092044830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7599258422852</t>
+    <t xml:space="preserve">15.2800788879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9092025756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7599248886108</t>
   </si>
   <si>
     <t xml:space="preserve">14.4800281524658</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3120889663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3494091033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8159036636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8345623016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5546674728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0398225784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3383798599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1704406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9762125015259</t>
+    <t xml:space="preserve">14.3120899200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3494081497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8159055709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8345642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.554666519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0398235321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3383817672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1704416275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9762105941772</t>
   </si>
   <si>
     <t xml:space="preserve">13.8269329071045</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">13.6403341293335</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2374486923218</t>
+    <t xml:space="preserve">14.2374505996704</t>
   </si>
   <si>
     <t xml:space="preserve">14.0695114135742</t>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve">14.0508518218994</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1254911422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8642530441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5470361709595</t>
+    <t xml:space="preserve">14.1254901885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8642520904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5470380783081</t>
   </si>
   <si>
     <t xml:space="preserve">13.5283765792847</t>
@@ -1469,19 +1469,19 @@
     <t xml:space="preserve">13.6963148117065</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9575519561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1068286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4240474700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6479663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.114462852478</t>
+    <t xml:space="preserve">13.9575529098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1068315505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4240484237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.647967338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1144618988037</t>
   </si>
   <si>
     <t xml:space="preserve">15.0211629867554</t>
@@ -1490,19 +1490,19 @@
     <t xml:space="preserve">14.9278631210327</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9651832580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7972450256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0025033950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0584812164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0958023071289</t>
+    <t xml:space="preserve">14.965184211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7972440719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0025024414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.058482170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0958013534546</t>
   </si>
   <si>
     <t xml:space="preserve">15.4316806793213</t>
@@ -1514,34 +1514,34 @@
     <t xml:space="preserve">16.7005481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7751846313477</t>
+    <t xml:space="preserve">16.7751865386963</t>
   </si>
   <si>
     <t xml:space="preserve">16.7938480377197</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3833293914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3086891174316</t>
+    <t xml:space="preserve">16.3833312988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3086929321289</t>
   </si>
   <si>
     <t xml:space="preserve">16.1594104766846</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2527103424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8795156478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7675561904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7115793228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0287971496582</t>
+    <t xml:space="preserve">16.2527122497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8795137405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7675542831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7115783691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0287933349609</t>
   </si>
   <si>
     <t xml:space="preserve">16.0474548339844</t>
@@ -1550,13 +1550,13 @@
     <t xml:space="preserve">16.1407508850098</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5139465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4019889831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.178071975708</t>
+    <t xml:space="preserve">16.5139484405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4019908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1780700683594</t>
   </si>
   <si>
     <t xml:space="preserve">16.3273506164551</t>
@@ -1565,19 +1565,19 @@
     <t xml:space="preserve">16.3460121154785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1220951080322</t>
+    <t xml:space="preserve">16.122091293335</t>
   </si>
   <si>
     <t xml:space="preserve">16.495288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6072463989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3646717071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2153930664062</t>
+    <t xml:space="preserve">16.6072483062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.364673614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2153911590576</t>
   </si>
   <si>
     <t xml:space="preserve">15.7488946914673</t>
@@ -1586,34 +1586,34 @@
     <t xml:space="preserve">15.8421945571899</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8235349655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0101337432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8981733322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2340526580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2900295257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4206485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6632289886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8311653137207</t>
+    <t xml:space="preserve">15.8235330581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0101356506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8981742858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2340507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2900314331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4206504821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6632270812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8311672210693</t>
   </si>
   <si>
     <t xml:space="preserve">17.3536415100098</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1560134887695</t>
+    <t xml:space="preserve">18.1560115814209</t>
   </si>
   <si>
     <t xml:space="preserve">18.1373538970947</t>
@@ -1622,58 +1622,58 @@
     <t xml:space="preserve">18.1186943054199</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9880771636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4096202850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0177631378174</t>
+    <t xml:space="preserve">17.9880752563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4096183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.017765045166</t>
   </si>
   <si>
     <t xml:space="preserve">16.8871459960938</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8684883117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6259059906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5326080322266</t>
+    <t xml:space="preserve">16.8684864044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6259098052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5326061248779</t>
   </si>
   <si>
     <t xml:space="preserve">16.8498249053955</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7192039489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9431228637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0364227294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1110610961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6445693969727</t>
+    <t xml:space="preserve">16.7192096710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9431247711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0364265441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1110649108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.644567489624</t>
   </si>
   <si>
     <t xml:space="preserve">16.1034317016602</t>
   </si>
   <si>
-    <t xml:space="preserve">15.394359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4130191802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3570384979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0771408081055</t>
+    <t xml:space="preserve">15.3943576812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4130182266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3570375442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0771398544312</t>
   </si>
   <si>
     <t xml:space="preserve">14.5919876098633</t>
@@ -1682,22 +1682,22 @@
     <t xml:space="preserve">14.7039461135864</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9838428497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6666259765625</t>
+    <t xml:space="preserve">14.9838438034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6666269302368</t>
   </si>
   <si>
     <t xml:space="preserve">14.871883392334</t>
   </si>
   <si>
-    <t xml:space="preserve">14.741265296936</t>
+    <t xml:space="preserve">14.7412643432617</t>
   </si>
   <si>
     <t xml:space="preserve">14.4053869247437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5733251571655</t>
+    <t xml:space="preserve">14.5733270645142</t>
   </si>
   <si>
     <t xml:space="preserve">14.27476978302</t>
@@ -1706,103 +1706,103 @@
     <t xml:space="preserve">14.7226047515869</t>
   </si>
   <si>
-    <t xml:space="preserve">14.461368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3680667877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5360059738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4689970016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3010606765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2823991775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5622978210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1331205368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4876575469971</t>
+    <t xml:space="preserve">14.4613666534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3680686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5360069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4689979553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3010587692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2824001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5622968673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1331214904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4876594543457</t>
   </si>
   <si>
     <t xml:space="preserve">15.3197202682495</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2264204025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9465227127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7785844802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4427080154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.685284614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173473358154</t>
+    <t xml:space="preserve">15.2264213562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9465236663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.77858543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4427070617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6852855682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173463821411</t>
   </si>
   <si>
     <t xml:space="preserve">14.2001304626465</t>
   </si>
   <si>
-    <t xml:space="preserve">14.181471824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9948720932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8082733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6776552200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3307495117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1628103256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.714973449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7522945404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.938892364502</t>
+    <t xml:space="preserve">14.1814699172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.994873046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8082723617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6776542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3307485580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1628122329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7149753570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.752293586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9388914108276</t>
   </si>
   <si>
     <t xml:space="preserve">13.8455934524536</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1441497802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9202327728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4986886978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9015712738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2637395858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0881729125977</t>
+    <t xml:space="preserve">14.1441488265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9202337265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4986877441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.901572227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2637414932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.088171005249</t>
   </si>
   <si>
     <t xml:space="preserve">14.0135316848755</t>
@@ -1811,22 +1811,22 @@
     <t xml:space="preserve">14.3867282867432</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8905439376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1891031265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9740734100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9552392959595</t>
+    <t xml:space="preserve">14.8905429840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1891002655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9740743637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9552383422852</t>
   </si>
   <si>
     <t xml:space="preserve">14.8045568466187</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7103776931763</t>
+    <t xml:space="preserve">14.7103805541992</t>
   </si>
   <si>
     <t xml:space="preserve">14.7857208251953</t>
@@ -1835,82 +1835,82 @@
     <t xml:space="preserve">15.2754383087158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5768051147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3490505218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2172050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5956382751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5579710006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4261198043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4449577331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3507804870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6521472930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6898136138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0665225982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6144723892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5014629364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5391340255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9346742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8781681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3131084442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.727484703064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4637908935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3319463729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4826278686523</t>
+    <t xml:space="preserve">15.5768041610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3490524291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2172031402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5956373214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5579681396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.426121711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4449558258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3507785797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6521453857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6898164749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0665187835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6144733428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5014619827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5391311645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9346723556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8781709671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3131093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7274866104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4637928009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3319444656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4826288223267</t>
   </si>
   <si>
     <t xml:space="preserve">15.1435918807983</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0117444992065</t>
+    <t xml:space="preserve">15.0117435455322</t>
   </si>
   <si>
     <t xml:space="preserve">14.8798971176147</t>
   </si>
   <si>
-    <t xml:space="preserve">15.105920791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6538743972778</t>
+    <t xml:space="preserve">15.1059217453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6538734436035</t>
   </si>
   <si>
     <t xml:space="preserve">14.8422269821167</t>
@@ -1919,37 +1919,37 @@
     <t xml:space="preserve">14.4090147018433</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9381322860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8439540863037</t>
+    <t xml:space="preserve">13.9381313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8439559936523</t>
   </si>
   <si>
     <t xml:space="preserve">14.1264848709106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5031900405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6915454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4843559265137</t>
+    <t xml:space="preserve">14.5031909942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6915435791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4843549728394</t>
   </si>
   <si>
     <t xml:space="preserve">14.2960023880005</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3336734771729</t>
+    <t xml:space="preserve">14.3336725234985</t>
   </si>
   <si>
     <t xml:space="preserve">14.5220260620117</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2394962310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.182991027832</t>
+    <t xml:space="preserve">14.2394971847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1829919815063</t>
   </si>
   <si>
     <t xml:space="preserve">13.9569664001465</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">13.0528717041016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9210243225098</t>
+    <t xml:space="preserve">12.9210252761841</t>
   </si>
   <si>
     <t xml:space="preserve">13.2788963317871</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">12.7138357162476</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371295928955</t>
+    <t xml:space="preserve">12.3371315002441</t>
   </si>
   <si>
     <t xml:space="preserve">12.0922718048096</t>
@@ -1982,13 +1982,13 @@
     <t xml:space="preserve">11.8662481307983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3953647613525</t>
+    <t xml:space="preserve">11.3953638076782</t>
   </si>
   <si>
     <t xml:space="preserve">10.9621534347534</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0580577850342</t>
+    <t xml:space="preserve">10.0580568313599</t>
   </si>
   <si>
     <t xml:space="preserve">9.88853931427002</t>
@@ -1997,106 +1997,106 @@
     <t xml:space="preserve">9.53066921234131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85259628295898</t>
+    <t xml:space="preserve">8.85259819030762</t>
   </si>
   <si>
     <t xml:space="preserve">9.35173225402832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04267883300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49472618103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04095077514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0957279205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6796236038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8474111557007</t>
+    <t xml:space="preserve">8.0426778793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49472713470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0409517288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0957269668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6796226501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.847412109375</t>
   </si>
   <si>
     <t xml:space="preserve">12.8080129623413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5272121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.886812210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8491411209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5666103363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0015516281128</t>
+    <t xml:space="preserve">11.52721118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8868112564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8491401672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.566611289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0015506744385</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652454376221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5477752685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6607866287231</t>
+    <t xml:space="preserve">10.547776222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6607856750488</t>
   </si>
   <si>
     <t xml:space="preserve">11.0374937057495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.830304145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5101051330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1333980560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81319808959961</t>
+    <t xml:space="preserve">10.8303050994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5101041793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1333990097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81319904327393</t>
   </si>
   <si>
     <t xml:space="preserve">10.1522340774536</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4347639083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3594217300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6984577178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6419525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6231164932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7361278533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7549638748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4724349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9244813919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.867974281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4141998291016</t>
+    <t xml:space="preserve">10.4347629547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3594226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6984567642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6419515609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6231155395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7361268997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7549629211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4724340438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9244823455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8679752349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4141979217529</t>
   </si>
   <si>
     <t xml:space="preserve">11.489541053772</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">10.9809875488281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3388576507568</t>
+    <t xml:space="preserve">11.3388586044312</t>
   </si>
   <si>
     <t xml:space="preserve">11.4330348968506</t>
@@ -2120,10 +2120,10 @@
     <t xml:space="preserve">12.2052822113037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1299409866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0169296264648</t>
+    <t xml:space="preserve">12.1299428939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0169286727905</t>
   </si>
   <si>
     <t xml:space="preserve">11.7720708847046</t>
@@ -2132,25 +2132,25 @@
     <t xml:space="preserve">11.1505060195923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9433174133301</t>
+    <t xml:space="preserve">10.9433183670044</t>
   </si>
   <si>
     <t xml:space="preserve">11.1128349304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0186586380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8114700317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7172927856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6042814254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3405866622925</t>
+    <t xml:space="preserve">11.0186576843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8114709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7172918319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6042823791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3405876159668</t>
   </si>
   <si>
     <t xml:space="preserve">10.3782587051392</t>
@@ -2159,28 +2159,28 @@
     <t xml:space="preserve">10.5854454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1316690444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2635173797607</t>
+    <t xml:space="preserve">11.1316699981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2635164260864</t>
   </si>
   <si>
     <t xml:space="preserve">11.207010269165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9998226165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9056453704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5289402008057</t>
+    <t xml:space="preserve">10.9998235702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9056463241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5289392471313</t>
   </si>
   <si>
     <t xml:space="preserve">10.3029165267944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3970909118652</t>
+    <t xml:space="preserve">10.3970928192139</t>
   </si>
   <si>
     <t xml:space="preserve">11.5648832321167</t>
@@ -2204,25 +2204,25 @@
     <t xml:space="preserve">11.5837173461914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6590576171875</t>
+    <t xml:space="preserve">11.6590595245361</t>
   </si>
   <si>
     <t xml:space="preserve">12.1487770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0546007156372</t>
+    <t xml:space="preserve">12.0545997619629</t>
   </si>
   <si>
     <t xml:space="preserve">12.0357646942139</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8850831985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9039182662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7343997955322</t>
+    <t xml:space="preserve">11.885082244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9039192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7344007492065</t>
   </si>
   <si>
     <t xml:space="preserve">11.6778936386108</t>
@@ -2231,22 +2231,22 @@
     <t xml:space="preserve">11.1693410873413</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5631542205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5614252090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2977294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7686128616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5049209594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.147047996521</t>
+    <t xml:space="preserve">12.5631532669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5614242553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2977304458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7686138153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.504919052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1470489501953</t>
   </si>
   <si>
     <t xml:space="preserve">13.3354015350342</t>
@@ -2258,172 +2258,172 @@
     <t xml:space="preserve">13.0152006149292</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2412261962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0323066711426</t>
+    <t xml:space="preserve">13.2412252426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0323076248169</t>
   </si>
   <si>
     <t xml:space="preserve">13.6367664337158</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3165674209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0340375900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3919086456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0905418395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9415893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9792594909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2429542541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3559646606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7703428268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7326717376709</t>
+    <t xml:space="preserve">13.3165655136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0340366363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3919067382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0905437469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9415884017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9792585372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2429533004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3559656143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7703418731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7326707839966</t>
   </si>
   <si>
     <t xml:space="preserve">12.9586954116821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2223882675171</t>
+    <t xml:space="preserve">13.2223901748657</t>
   </si>
   <si>
     <t xml:space="preserve">13.3542375564575</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4672479629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5260190963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5450410842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3167552947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3548021316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2216339111328</t>
+    <t xml:space="preserve">13.4672498703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5260171890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5450420379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3167543411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3548030853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2216348648071</t>
   </si>
   <si>
     <t xml:space="preserve">13.4118747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7543048858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7923536300659</t>
+    <t xml:space="preserve">13.7543058395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7923526763916</t>
   </si>
   <si>
     <t xml:space="preserve">13.6591854095459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.077712059021</t>
+    <t xml:space="preserve">14.0777111053467</t>
   </si>
   <si>
     <t xml:space="preserve">14.0586881637573</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1157608032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8874731063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6021127700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3738279342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6782093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5069942474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4499235153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6972322463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6211366653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7733287811279</t>
+    <t xml:space="preserve">14.115758895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8874740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6021146774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3738260269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6782102584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5069932937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4499216079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6972332000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6211376190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7733278274536</t>
   </si>
   <si>
     <t xml:space="preserve">14.0396642684937</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2489280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6103820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5342864990234</t>
+    <t xml:space="preserve">14.248927116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6103811264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5342855453491</t>
   </si>
   <si>
     <t xml:space="preserve">14.8957414627075</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9337902069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3796081542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2274169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0752258300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7137727737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8469362258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6947479248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5045070648193</t>
+    <t xml:space="preserve">14.9337892532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3796043395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2274150848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0752239227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.713770866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8469390869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6947460174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.504506111145</t>
   </si>
   <si>
     <t xml:space="preserve">15.2191486358643</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6376752853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2381725311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3332920074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6186504364014</t>
+    <t xml:space="preserve">15.637677192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2381715774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3332929611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6186513900757</t>
   </si>
   <si>
     <t xml:space="preserve">15.7518177032471</t>
@@ -2432,19 +2432,19 @@
     <t xml:space="preserve">16.1513195037842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4937515258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6649703979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5698471069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5317993164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6078948974609</t>
+    <t xml:space="preserve">16.4937496185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6649684906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5698490142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5318012237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6078968048096</t>
   </si>
   <si>
     <t xml:space="preserve">16.5888710021973</t>
@@ -2453,49 +2453,49 @@
     <t xml:space="preserve">17.045446395874</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0264225006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.08349609375</t>
+    <t xml:space="preserve">17.0264205932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0834922790527</t>
   </si>
   <si>
     <t xml:space="preserve">16.874231338501</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3415622711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3225383758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7981357574463</t>
+    <t xml:space="preserve">16.3415584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3225364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7981338500977</t>
   </si>
   <si>
     <t xml:space="preserve">16.5508232116699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.836181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8171577453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7410621643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8444519042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9585933685303</t>
+    <t xml:space="preserve">16.8361835479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.81715965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7410640716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8444538116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9585952758789</t>
   </si>
   <si>
     <t xml:space="preserve">18.1868839263916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.499532699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.78489112854</t>
+    <t xml:space="preserve">19.4995346069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7848930358887</t>
   </si>
   <si>
     <t xml:space="preserve">20.1653709411621</t>
@@ -2504,13 +2504,13 @@
     <t xml:space="preserve">19.6422138214111</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5934104919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3556118011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.975133895874</t>
+    <t xml:space="preserve">20.5934085845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3556098937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9751319885254</t>
   </si>
   <si>
     <t xml:space="preserve">19.8324527740479</t>
@@ -2522,16 +2522,16 @@
     <t xml:space="preserve">19.8800106048584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2604885101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4031715393066</t>
+    <t xml:space="preserve">20.2604904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.403169631958</t>
   </si>
   <si>
     <t xml:space="preserve">20.498291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8312072753906</t>
+    <t xml:space="preserve">20.8312110900879</t>
   </si>
   <si>
     <t xml:space="preserve">20.7360897064209</t>
@@ -2549,58 +2549,58 @@
     <t xml:space="preserve">19.594654083252</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3568553924561</t>
+    <t xml:space="preserve">19.3568534851074</t>
   </si>
   <si>
     <t xml:space="preserve">19.2141761779785</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4044151306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6897754669189</t>
+    <t xml:space="preserve">19.4044132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6897735595703</t>
   </si>
   <si>
     <t xml:space="preserve">19.0239353179932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1178092956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3080520629883</t>
+    <t xml:space="preserve">20.1178112030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3080501556396</t>
   </si>
   <si>
     <t xml:space="preserve">20.0702514648438</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9738883972168</t>
+    <t xml:space="preserve">20.9738903045654</t>
   </si>
   <si>
     <t xml:space="preserve">21.544605255127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1641273498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6397266387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5921669006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6872844696045</t>
+    <t xml:space="preserve">21.1641292572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6397247314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5921649932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6872825622559</t>
   </si>
   <si>
     <t xml:space="preserve">21.4019260406494</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7348480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8299655914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0690059661865</t>
+    <t xml:space="preserve">21.7348461151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8299674987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0690097808838</t>
   </si>
   <si>
     <t xml:space="preserve">21.2116870880127</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">22.1628837585449</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6384811401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.161642074585</t>
+    <t xml:space="preserve">22.6384792327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1616439819336</t>
   </si>
   <si>
     <t xml:space="preserve">22.4958038330078</t>
@@ -2624,19 +2624,19 @@
     <t xml:space="preserve">22.2580051422119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8775253295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.497049331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2592506408691</t>
+    <t xml:space="preserve">21.8775272369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4970455169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2592468261719</t>
   </si>
   <si>
     <t xml:space="preserve">20.6885299682617</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6409702301025</t>
+    <t xml:space="preserve">20.6409683227539</t>
   </si>
   <si>
     <t xml:space="preserve">21.7824077606201</t>
@@ -2648,28 +2648,28 @@
     <t xml:space="preserve">23.7799205780029</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3043231964111</t>
+    <t xml:space="preserve">23.3043212890625</t>
   </si>
   <si>
     <t xml:space="preserve">23.2567615509033</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0189628601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1140785217285</t>
+    <t xml:space="preserve">23.0189609527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1140823364258</t>
   </si>
   <si>
     <t xml:space="preserve">23.351879119873</t>
   </si>
   <si>
-    <t xml:space="preserve">23.066520690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5896778106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.44700050354</t>
+    <t xml:space="preserve">23.0665225982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5896797180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4469985961914</t>
   </si>
   <si>
     <t xml:space="preserve">22.9238414764404</t>
@@ -2690,46 +2690,46 @@
     <t xml:space="preserve">23.3994407653809</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6860446929932</t>
+    <t xml:space="preserve">22.6860427856445</t>
   </si>
   <si>
     <t xml:space="preserve">22.4482440948486</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1153240203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4494876861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0677642822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0202045440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0652770996094</t>
+    <t xml:space="preserve">22.1153259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.44948387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0677661895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.020206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0652751922607</t>
   </si>
   <si>
     <t xml:space="preserve">23.7323608398438</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3030776977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.875036239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6848011016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3018341064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.587194442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9676685333252</t>
+    <t xml:space="preserve">24.3030757904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8750400543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6847991943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3018321990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5871925354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9676704406738</t>
   </si>
   <si>
     <t xml:space="preserve">25.6823120117188</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">25.6347541809082</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7774333953857</t>
+    <t xml:space="preserve">25.7774353027344</t>
   </si>
   <si>
     <t xml:space="preserve">25.492073059082</t>
@@ -2753,31 +2753,31 @@
     <t xml:space="preserve">27.2993488311768</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2042255401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.156665802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6798267364502</t>
+    <t xml:space="preserve">27.2042293548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1566677093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6798248291016</t>
   </si>
   <si>
     <t xml:space="preserve">28.2981033325195</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7749462127686</t>
+    <t xml:space="preserve">27.7749481201172</t>
   </si>
   <si>
     <t xml:space="preserve">28.1078624725342</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5847072601318</t>
+    <t xml:space="preserve">27.5847053527832</t>
   </si>
   <si>
     <t xml:space="preserve">27.4420261383057</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5371494293213</t>
+    <t xml:space="preserve">27.5371475219727</t>
   </si>
   <si>
     <t xml:space="preserve">27.3469066619873</t>
@@ -2786,16 +2786,16 @@
     <t xml:space="preserve">27.0615482330322</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7761898040771</t>
+    <t xml:space="preserve">26.7761878967285</t>
   </si>
   <si>
     <t xml:space="preserve">26.9664287567139</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8713092803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5383911132812</t>
+    <t xml:space="preserve">26.8713073730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5383892059326</t>
   </si>
   <si>
     <t xml:space="preserve">26.7469043731689</t>
@@ -2807,22 +2807,22 @@
     <t xml:space="preserve">25.6464042663574</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2636241912842</t>
+    <t xml:space="preserve">25.2636222839355</t>
   </si>
   <si>
     <t xml:space="preserve">24.4023628234863</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5459060668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9717350006104</t>
+    <t xml:space="preserve">24.5459041595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9717330932617</t>
   </si>
   <si>
     <t xml:space="preserve">24.5937557220459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4980602264404</t>
+    <t xml:space="preserve">24.4980583190918</t>
   </si>
   <si>
     <t xml:space="preserve">24.9286880493164</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">26.2684268951416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7421016693115</t>
+    <t xml:space="preserve">25.7420997619629</t>
   </si>
   <si>
     <t xml:space="preserve">25.6942539215088</t>
@@ -2852,16 +2852,16 @@
     <t xml:space="preserve">24.9765377044678</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4071655273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9334926605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8856449127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7899513244629</t>
+    <t xml:space="preserve">25.4071636199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9334945678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8856430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7899494171143</t>
   </si>
   <si>
     <t xml:space="preserve">25.9813404083252</t>
@@ -2870,10 +2870,10 @@
     <t xml:space="preserve">25.4550132751465</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6894493103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5028610229492</t>
+    <t xml:space="preserve">24.6894512176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5028591156006</t>
   </si>
   <si>
     <t xml:space="preserve">25.3593196868896</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">24.8808422088623</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3066673278809</t>
+    <t xml:space="preserve">24.3066654205322</t>
   </si>
   <si>
     <t xml:space="preserve">22.8233871459961</t>
@@ -2897,19 +2897,19 @@
     <t xml:space="preserve">22.8712348937988</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7755374908447</t>
+    <t xml:space="preserve">22.7755355834961</t>
   </si>
   <si>
     <t xml:space="preserve">23.0626258850098</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2540149688721</t>
+    <t xml:space="preserve">23.2540168762207</t>
   </si>
   <si>
     <t xml:space="preserve">22.2970600128174</t>
   </si>
   <si>
-    <t xml:space="preserve">21.81858253479</t>
+    <t xml:space="preserve">21.8185806274414</t>
   </si>
   <si>
     <t xml:space="preserve">21.6750392913818</t>
@@ -2927,13 +2927,13 @@
     <t xml:space="preserve">22.3449096679688</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9621276855469</t>
+    <t xml:space="preserve">21.9621295928955</t>
   </si>
   <si>
     <t xml:space="preserve">23.0147762298584</t>
   </si>
   <si>
-    <t xml:space="preserve">22.009973526001</t>
+    <t xml:space="preserve">22.0099754333496</t>
   </si>
   <si>
     <t xml:space="preserve">21.9142818450928</t>
@@ -2945,22 +2945,22 @@
     <t xml:space="preserve">21.0051727294922</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3831481933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.378345489502</t>
+    <t xml:space="preserve">20.383150100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3783473968506</t>
   </si>
   <si>
     <t xml:space="preserve">20.0482158660889</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8089790344238</t>
+    <t xml:space="preserve">19.8089771270752</t>
   </si>
   <si>
     <t xml:space="preserve">18.8328819274902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0242729187012</t>
+    <t xml:space="preserve">19.0242710113525</t>
   </si>
   <si>
     <t xml:space="preserve">18.0099010467529</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">16.7849998474121</t>
   </si>
   <si>
-    <t xml:space="preserve">16.842414855957</t>
+    <t xml:space="preserve">16.8424167633057</t>
   </si>
   <si>
     <t xml:space="preserve">17.8950672149658</t>
@@ -2981,13 +2981,13 @@
     <t xml:space="preserve">17.4357261657715</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1821517944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7228164672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3783111572266</t>
+    <t xml:space="preserve">18.1821537017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7228145599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3783092498779</t>
   </si>
   <si>
     <t xml:space="preserve">18.5457954406738</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">18.1438751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2012920379639</t>
+    <t xml:space="preserve">18.2012939453125</t>
   </si>
   <si>
     <t xml:space="preserve">18.5649356842041</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">18.6414928436279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9477138519287</t>
+    <t xml:space="preserve">18.9477157592773</t>
   </si>
   <si>
     <t xml:space="preserve">19.0625534057617</t>
@@ -3017,28 +3017,28 @@
     <t xml:space="preserve">19.4740428924561</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9859981536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0816917419434</t>
+    <t xml:space="preserve">18.9859962463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0816898345947</t>
   </si>
   <si>
     <t xml:space="preserve">18.5075168609619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6462593078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5266551971436</t>
+    <t xml:space="preserve">17.6462574005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5266590118408</t>
   </si>
   <si>
     <t xml:space="preserve">18.2778491973877</t>
   </si>
   <si>
-    <t xml:space="preserve">18.603214263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2826519012451</t>
+    <t xml:space="preserve">18.6032123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2826538085938</t>
   </si>
   <si>
     <t xml:space="preserve">19.6175861358643</t>
@@ -3050,7 +3050,7 @@
     <t xml:space="preserve">18.6223526000977</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7946033477783</t>
+    <t xml:space="preserve">18.794605255127</t>
   </si>
   <si>
     <t xml:space="preserve">19.2348041534424</t>
@@ -3059,10 +3059,10 @@
     <t xml:space="preserve">19.1391086578369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4165878295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6079807281494</t>
+    <t xml:space="preserve">17.4165897369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6079788208008</t>
   </si>
   <si>
     <t xml:space="preserve">17.9716243743896</t>
@@ -3077,22 +3077,22 @@
     <t xml:space="preserve">20.8616275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5745429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9094772338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3401031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.29225730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7228889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2492122650146</t>
+    <t xml:space="preserve">20.5745410919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9094753265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3401050567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2922592163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7228870391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2492141723633</t>
   </si>
   <si>
     <t xml:space="preserve">22.9669303894043</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">22.3927574157715</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0578193664551</t>
+    <t xml:space="preserve">22.0578212738037</t>
   </si>
   <si>
     <t xml:space="preserve">20.2874546051025</t>
@@ -3122,37 +3122,37 @@
     <t xml:space="preserve">20.3353023529053</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7132835388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1199684143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6606311798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.46923828125</t>
+    <t xml:space="preserve">19.7132816314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.119966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6606292724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4692401885986</t>
   </si>
   <si>
     <t xml:space="preserve">17.4548664093018</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6797714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3735446929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1055946350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9524841308594</t>
+    <t xml:space="preserve">18.6797695159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3735466003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.105598449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.952486038208</t>
   </si>
   <si>
     <t xml:space="preserve">18.4309616088867</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5840721130371</t>
+    <t xml:space="preserve">18.5840740203857</t>
   </si>
   <si>
     <t xml:space="preserve">18.8137435913086</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">18.4118213653564</t>
   </si>
   <si>
-    <t xml:space="preserve">18.316125869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1630115509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8567886352539</t>
+    <t xml:space="preserve">18.3161277770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.163013458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8567867279053</t>
   </si>
   <si>
     <t xml:space="preserve">18.450101852417</t>
@@ -3182,16 +3182,16 @@
     <t xml:space="preserve">18.8520221710205</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3304996490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0481796264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5888404846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7993717193604</t>
+    <t xml:space="preserve">19.3305015563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0481815338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5888385772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7993698120117</t>
   </si>
   <si>
     <t xml:space="preserve">17.5122833251953</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">18.1247367858887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5505638122559</t>
+    <t xml:space="preserve">17.5505619049072</t>
   </si>
   <si>
     <t xml:space="preserve">17.2251987457275</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">16.5170497894287</t>
   </si>
   <si>
-    <t xml:space="preserve">15.885458946228</t>
+    <t xml:space="preserve">15.8854608535767</t>
   </si>
   <si>
     <t xml:space="preserve">16.3447971343994</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">16.0959892272949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9428768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1151313781738</t>
+    <t xml:space="preserve">15.9428787231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1151294708252</t>
   </si>
   <si>
     <t xml:space="preserve">15.3112869262695</t>
@@ -3236,55 +3236,55 @@
     <t xml:space="preserve">15.2538690567017</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6127452850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0194358825684</t>
+    <t xml:space="preserve">16.6127471923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0194339752197</t>
   </si>
   <si>
     <t xml:space="preserve">16.6510238647461</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7658615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9955272674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3208923339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1295032501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0529441833496</t>
+    <t xml:space="preserve">16.7658596038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9955291748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.320894241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1295013427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0529479980469</t>
   </si>
   <si>
     <t xml:space="preserve">17.0146675109863</t>
   </si>
   <si>
-    <t xml:space="preserve">17.837646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.756326675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6989097595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4261932373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.952522277832</t>
+    <t xml:space="preserve">17.8376483917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7563247680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6989078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4261951446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9525203704834</t>
   </si>
   <si>
     <t xml:space="preserve">20.0003662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5697402954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4309997558594</t>
+    <t xml:space="preserve">19.5697383880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4309978485107</t>
   </si>
   <si>
     <t xml:space="preserve">20.1917591094971</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">20.3102321624756</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5525989532471</t>
+    <t xml:space="preserve">20.5525970458984</t>
   </si>
   <si>
     <t xml:space="preserve">20.4556522369385</t>
@@ -3341,37 +3341,37 @@
     <t xml:space="preserve">20.116340637207</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8434371948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.69801902771</t>
+    <t xml:space="preserve">20.8434352874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6980171203613</t>
   </si>
   <si>
     <t xml:space="preserve">20.9403839111328</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6190052032471</t>
+    <t xml:space="preserve">21.6190071105957</t>
   </si>
   <si>
     <t xml:space="preserve">21.7159519195557</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4735851287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9098472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0067920684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.29762840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.218620300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4430484771729</t>
+    <t xml:space="preserve">21.4735870361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9098453521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0067901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2976303100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2186183929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4430503845215</t>
   </si>
   <si>
     <t xml:space="preserve">22.7823619842529</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">23.3155632019043</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0732002258301</t>
+    <t xml:space="preserve">23.0731983184814</t>
   </si>
   <si>
     <t xml:space="preserve">23.5579299926758</t>
@@ -3404,13 +3404,13 @@
     <t xml:space="preserve">23.4609832763672</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6064033508301</t>
+    <t xml:space="preserve">23.6064052581787</t>
   </si>
   <si>
     <t xml:space="preserve">23.7033519744873</t>
   </si>
   <si>
-    <t xml:space="preserve">23.121675491333</t>
+    <t xml:space="preserve">23.1216735839844</t>
   </si>
   <si>
     <t xml:space="preserve">23.17014503479</t>
@@ -3428,19 +3428,19 @@
     <t xml:space="preserve">24.8182315826416</t>
   </si>
   <si>
-    <t xml:space="preserve">24.624340057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3334999084473</t>
+    <t xml:space="preserve">24.6243381500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3335018157959</t>
   </si>
   <si>
     <t xml:space="preserve">24.4304466247559</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2850284576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1396083831787</t>
+    <t xml:space="preserve">24.285026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1396064758301</t>
   </si>
   <si>
     <t xml:space="preserve">23.8487701416016</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">24.188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6854133605957</t>
+    <t xml:space="preserve">22.6854152679443</t>
   </si>
   <si>
     <t xml:space="preserve">22.2006855010986</t>
@@ -3482,13 +3482,13 @@
     <t xml:space="preserve">21.8128986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7644271850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1522121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3945751190186</t>
+    <t xml:space="preserve">21.76442527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1522102355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3945770263672</t>
   </si>
   <si>
     <t xml:space="preserve">22.63694190979</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">22.3461017608643</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5399951934814</t>
+    <t xml:space="preserve">22.5399971008301</t>
   </si>
   <si>
     <t xml:space="preserve">21.5220603942871</t>
@@ -3506,34 +3506,34 @@
     <t xml:space="preserve">21.4251136779785</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2312202453613</t>
+    <t xml:space="preserve">21.23122215271</t>
   </si>
   <si>
     <t xml:space="preserve">21.2796955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3766384124756</t>
+    <t xml:space="preserve">21.3766403198242</t>
   </si>
   <si>
     <t xml:space="preserve">20.9888572692871</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7949638366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3281669616699</t>
+    <t xml:space="preserve">20.7949619293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3281688690186</t>
   </si>
   <si>
     <t xml:space="preserve">21.0858020782471</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8919086456299</t>
+    <t xml:space="preserve">20.8919105529785</t>
   </si>
   <si>
     <t xml:space="preserve">21.0373306274414</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8613719940186</t>
+    <t xml:space="preserve">21.8613700866699</t>
   </si>
   <si>
     <t xml:space="preserve">21.9583168029785</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">21.6674785614014</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2491569519043</t>
+    <t xml:space="preserve">22.2491588592529</t>
   </si>
   <si>
     <t xml:space="preserve">24.0426616668701</t>
@@ -3551,13 +3551,13 @@
     <t xml:space="preserve">25.0121231079102</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0785331726074</t>
+    <t xml:space="preserve">26.0785312652588</t>
   </si>
   <si>
     <t xml:space="preserve">25.8361663818359</t>
   </si>
   <si>
-    <t xml:space="preserve">25.690746307373</t>
+    <t xml:space="preserve">25.6907482147217</t>
   </si>
   <si>
     <t xml:space="preserve">25.6422748565674</t>
@@ -3569,16 +3569,16 @@
     <t xml:space="preserve">25.8846397399902</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1754779815674</t>
+    <t xml:space="preserve">26.1754760742188</t>
   </si>
   <si>
     <t xml:space="preserve">26.9025745391846</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2239513397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3693714141846</t>
+    <t xml:space="preserve">26.223949432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3693733215332</t>
   </si>
   <si>
     <t xml:space="preserve">25.3029632568359</t>
@@ -3602,7 +3602,7 @@
     <t xml:space="preserve">25.0605983734131</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3999080657959</t>
+    <t xml:space="preserve">25.3999099731445</t>
   </si>
   <si>
     <t xml:space="preserve">25.4968547821045</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">25.3514347076416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5453262329102</t>
+    <t xml:space="preserve">25.5453281402588</t>
   </si>
   <si>
     <t xml:space="preserve">25.8003883361816</t>
@@ -4644,6 +4644,9 @@
   </si>
   <si>
     <t xml:space="preserve">48.2000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.75</t>
   </si>
 </sst>
 </file>
@@ -70554,7 +70557,7 @@
     </row>
     <row r="2523">
       <c r="A2523" s="1" t="n">
-        <v>45992.6911574074</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B2523" t="n">
         <v>31531</v>
@@ -70575,6 +70578,32 @@
         <v>1542</v>
       </c>
       <c r="H2523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>45993.6910532407</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>26383</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>48</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>47.7999992370605</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>1544</v>
+      </c>
+      <c r="H2524" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="1550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="1551">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5902528762817</t>
+    <t xml:space="preserve">15.5902519226074</t>
   </si>
   <si>
     <t xml:space="preserve">DAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7186412811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2234258651733</t>
+    <t xml:space="preserve">15.7186431884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2234220504761</t>
   </si>
   <si>
     <t xml:space="preserve">14.5356168746948</t>
@@ -59,64 +59,64 @@
     <t xml:space="preserve">13.9395189285278</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2880077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.040397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.866153717041</t>
+    <t xml:space="preserve">14.2880067825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0403985977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8661546707153</t>
   </si>
   <si>
     <t xml:space="preserve">13.1049833297729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.793176651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8848829269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2887849807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9490804672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.132493019104</t>
+    <t xml:space="preserve">12.7931776046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8848838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2887878417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9490814208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1324949264526</t>
   </si>
   <si>
     <t xml:space="preserve">15.8928852081299</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0487880706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3239116668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0854721069336</t>
+    <t xml:space="preserve">16.0487899780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3239097595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.085470199585</t>
   </si>
   <si>
     <t xml:space="preserve">16.360595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1125926971436</t>
+    <t xml:space="preserve">17.1125946044922</t>
   </si>
   <si>
     <t xml:space="preserve">16.5990333557129</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4710321426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1038150787354</t>
+    <t xml:space="preserve">15.4710311889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1038131713867</t>
   </si>
   <si>
     <t xml:space="preserve">15.3059587478638</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9391298294067</t>
+    <t xml:space="preserve">14.9391288757324</t>
   </si>
   <si>
     <t xml:space="preserve">14.948299407959</t>
@@ -125,40 +125,40 @@
     <t xml:space="preserve">15.3518123626709</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1042013168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.003324508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9112243652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2322025299072</t>
+    <t xml:space="preserve">15.1042003631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0033254623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9112253189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2322006225586</t>
   </si>
   <si>
     <t xml:space="preserve">16.7641048431396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9200096130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0575714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9658641815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7090797424316</t>
+    <t xml:space="preserve">16.9200115203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0575695037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9658603668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7090816497803</t>
   </si>
   <si>
     <t xml:space="preserve">16.3514213562012</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3422546386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8283004760742</t>
+    <t xml:space="preserve">16.3422508239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8283023834229</t>
   </si>
   <si>
     <t xml:space="preserve">16.6357154846191</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">17.1767883300781</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3051815032959</t>
+    <t xml:space="preserve">17.3051776885986</t>
   </si>
   <si>
     <t xml:space="preserve">17.3693771362305</t>
@@ -176,22 +176,22 @@
     <t xml:space="preserve">17.4335689544678</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5348339080811</t>
+    <t xml:space="preserve">16.5348358154297</t>
   </si>
   <si>
     <t xml:space="preserve">17.2226448059082</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5161037445068</t>
+    <t xml:space="preserve">17.5161075592041</t>
   </si>
   <si>
     <t xml:space="preserve">16.874153137207</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2593250274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4610862731934</t>
+    <t xml:space="preserve">17.2593269348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4610843658447</t>
   </si>
   <si>
     <t xml:space="preserve">17.0117149353027</t>
@@ -203,58 +203,58 @@
     <t xml:space="preserve">16.5531787872314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9383487701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2868404388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5715198516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5256690979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1217632293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5619602203369</t>
+    <t xml:space="preserve">16.938346862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2868385314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5715179443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5256652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1217670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5619621276855</t>
   </si>
   <si>
     <t xml:space="preserve">17.6353244781494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4060573577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8645935058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1122055053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0204944610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7912254333496</t>
+    <t xml:space="preserve">17.4060592651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8645915985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1122035980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0204982757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7912311553955</t>
   </si>
   <si>
     <t xml:space="preserve">17.5986423492432</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3414707183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4056701660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4331798553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0938606262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3231315612793</t>
+    <t xml:space="preserve">18.3414726257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.405668258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4331836700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0938663482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3231334686279</t>
   </si>
   <si>
     <t xml:space="preserve">18.0296669006348</t>
@@ -263,22 +263,22 @@
     <t xml:space="preserve">17.8921070098877</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4702529907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1492786407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4885940551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1676177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.07590675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7732753753662</t>
+    <t xml:space="preserve">17.470251083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1492767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4885959625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1676197052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0759105682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7732772827148</t>
   </si>
   <si>
     <t xml:space="preserve">16.8374729156494</t>
@@ -290,16 +290,16 @@
     <t xml:space="preserve">16.3147411346436</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1496677398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.250545501709</t>
+    <t xml:space="preserve">16.1496639251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2505435943604</t>
   </si>
   <si>
     <t xml:space="preserve">16.7457637786865</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4523010253906</t>
+    <t xml:space="preserve">16.452299118042</t>
   </si>
   <si>
     <t xml:space="preserve">16.4156188964844</t>
@@ -311,22 +311,22 @@
     <t xml:space="preserve">17.3602046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5164928436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4981555938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2409839630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9933738708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0392265319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8103485107422</t>
+    <t xml:space="preserve">16.5164966583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4981536865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2409820556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.993371963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0392284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8103494644165</t>
   </si>
   <si>
     <t xml:space="preserve">15.84703540802</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">14.9574699401855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7648859024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0675191879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3334693908691</t>
+    <t xml:space="preserve">14.7648868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0675210952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3334703445435</t>
   </si>
   <si>
     <t xml:space="preserve">15.9570817947388</t>
@@ -353,10 +353,10 @@
     <t xml:space="preserve">14.4530801773071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.884105682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5264453887939</t>
+    <t xml:space="preserve">14.8841047286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5264463424683</t>
   </si>
   <si>
     <t xml:space="preserve">14.6823492050171</t>
@@ -365,169 +365,169 @@
     <t xml:space="preserve">15.4068365097046</t>
   </si>
   <si>
-    <t xml:space="preserve">15.030834197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6273241043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0037136077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2604951858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6548347473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.397665977478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3151302337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4985446929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2509326934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3242998123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2967901229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3793268203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.140495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6177644729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3884973526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1221542358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8286905288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0762977600098</t>
+    <t xml:space="preserve">15.0308351516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6273231506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0037145614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2604961395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6548366546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.397668838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.315131187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4985437393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2509307861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3242988586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2967872619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3793258666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1404991149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6177654266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3884963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1221504211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8286914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.076301574707</t>
   </si>
   <si>
     <t xml:space="preserve">16.1771793365479</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0671291351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9845933914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1401062011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8099575042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6082019805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6448841094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6078128814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1584434509277</t>
+    <t xml:space="preserve">16.0671329498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9845924377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1401100158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8099594116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6082057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6448860168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6078147888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1584453582764</t>
   </si>
   <si>
     <t xml:space="preserve">17.0300579071045</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1951332092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3326930999756</t>
+    <t xml:space="preserve">17.1951313018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3326892852783</t>
   </si>
   <si>
     <t xml:space="preserve">16.0946426391602</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7828369140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7553272247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8195199966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9479112625122</t>
+    <t xml:space="preserve">15.7828340530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7553243637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8195190429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9479093551636</t>
   </si>
   <si>
     <t xml:space="preserve">15.6361045837402</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6636180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5627393722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4893712997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6085929870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.030445098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6999111175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0579624176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5352296829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5444011688232</t>
+    <t xml:space="preserve">15.6636152267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5627384185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893741607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6085939407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0304489135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6999130249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0579605102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.535228729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5443983078003</t>
   </si>
   <si>
     <t xml:space="preserve">15.7003021240234</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3609838485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1592283248901</t>
+    <t xml:space="preserve">15.3609819412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1592273712158</t>
   </si>
   <si>
     <t xml:space="preserve">15.2330408096313</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3068523406982</t>
+    <t xml:space="preserve">15.3068513870239</t>
   </si>
   <si>
     <t xml:space="preserve">15.5467405319214</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6297855377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7866306304932</t>
+    <t xml:space="preserve">15.6297836303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7866334915161</t>
   </si>
   <si>
     <t xml:space="preserve">15.5190629959106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9746961593628</t>
+    <t xml:space="preserve">14.9746952056885</t>
   </si>
   <si>
     <t xml:space="preserve">15.3253049850464</t>
@@ -536,19 +536,19 @@
     <t xml:space="preserve">15.4175691604614</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4083480834961</t>
+    <t xml:space="preserve">15.4083452224731</t>
   </si>
   <si>
     <t xml:space="preserve">15.0577354431152</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7589530944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2202796936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8235378265381</t>
+    <t xml:space="preserve">15.7589511871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2202777862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8235416412354</t>
   </si>
   <si>
     <t xml:space="preserve">15.3898916244507</t>
@@ -557,37 +557,37 @@
     <t xml:space="preserve">15.5006113052368</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2145862579346</t>
+    <t xml:space="preserve">15.2145872116089</t>
   </si>
   <si>
     <t xml:space="preserve">15.7774057388306</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9434852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7312726974487</t>
+    <t xml:space="preserve">15.9434862136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.731273651123</t>
   </si>
   <si>
     <t xml:space="preserve">16.4693984985352</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0691261291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1429347991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0229911804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1060314178467</t>
+    <t xml:space="preserve">17.0691242218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.142936706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0229930877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.106029510498</t>
   </si>
   <si>
     <t xml:space="preserve">16.9122753143311</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8384609222412</t>
+    <t xml:space="preserve">16.8384590148926</t>
   </si>
   <si>
     <t xml:space="preserve">16.3771305084229</t>
@@ -596,28 +596,28 @@
     <t xml:space="preserve">16.9768581390381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7923259735107</t>
+    <t xml:space="preserve">16.7923278808594</t>
   </si>
   <si>
     <t xml:space="preserve">17.0506706237793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6227149963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7795696258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8164749145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7611122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3054828643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7760334014893</t>
+    <t xml:space="preserve">17.6227169036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7795677185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8164730072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7611141204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3054809570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7760353088379</t>
   </si>
   <si>
     <t xml:space="preserve">18.8221664428711</t>
@@ -626,61 +626,61 @@
     <t xml:space="preserve">19.4218940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4957065582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9882488250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7852649688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3296337127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2004566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0528335571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9513416290283</t>
+    <t xml:space="preserve">19.4957046508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9882469177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7852630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3296318054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2004547119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0528297424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9513397216797</t>
   </si>
   <si>
     <t xml:space="preserve">18.7299022674561</t>
   </si>
   <si>
-    <t xml:space="preserve">18.886754989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8129425048828</t>
+    <t xml:space="preserve">18.8867568969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8129444122314</t>
   </si>
   <si>
     <t xml:space="preserve">18.8037166595459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6284160614014</t>
+    <t xml:space="preserve">18.6284122467041</t>
   </si>
   <si>
     <t xml:space="preserve">18.4531078338623</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2778015136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9917774200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3331623077393</t>
+    <t xml:space="preserve">18.2778034210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9917793273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3331642150879</t>
   </si>
   <si>
     <t xml:space="preserve">18.4069728851318</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3423862457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2501220703125</t>
+    <t xml:space="preserve">18.3423881530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2501239776611</t>
   </si>
   <si>
     <t xml:space="preserve">18.36083984375</t>
@@ -689,16 +689,16 @@
     <t xml:space="preserve">18.1578578948975</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2039909362793</t>
+    <t xml:space="preserve">18.2039890289307</t>
   </si>
   <si>
     <t xml:space="preserve">18.388521194458</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4900150299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4992408752441</t>
+    <t xml:space="preserve">18.49001121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4992427825928</t>
   </si>
   <si>
     <t xml:space="preserve">18.6007308959961</t>
@@ -707,49 +707,49 @@
     <t xml:space="preserve">18.9144344329834</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2835006713867</t>
+    <t xml:space="preserve">19.2834968566895</t>
   </si>
   <si>
     <t xml:space="preserve">18.9605674743652</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9974708557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2373638153076</t>
+    <t xml:space="preserve">18.9974765777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2373657226562</t>
   </si>
   <si>
     <t xml:space="preserve">19.3204021453857</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8313961029053</t>
+    <t xml:space="preserve">18.8313941955566</t>
   </si>
   <si>
     <t xml:space="preserve">19.1174163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3757610321045</t>
+    <t xml:space="preserve">19.3757629394531</t>
   </si>
   <si>
     <t xml:space="preserve">18.9697952270508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0897369384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2189102172852</t>
+    <t xml:space="preserve">19.0897388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2189121246338</t>
   </si>
   <si>
     <t xml:space="preserve">18.9052085876465</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0989665985107</t>
+    <t xml:space="preserve">19.0989685058594</t>
   </si>
   <si>
     <t xml:space="preserve">19.2558174133301</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1543254852295</t>
+    <t xml:space="preserve">19.1543216705322</t>
   </si>
   <si>
     <t xml:space="preserve">19.7817325592041</t>
@@ -758,25 +758,25 @@
     <t xml:space="preserve">19.8739967346191</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2430610656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4829502105713</t>
+    <t xml:space="preserve">20.2430591583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4829483032227</t>
   </si>
   <si>
     <t xml:space="preserve">20.7136116027832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8243312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8058776855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0123958587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.473726272583</t>
+    <t xml:space="preserve">20.8243293762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8058795928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.012393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4737243652344</t>
   </si>
   <si>
     <t xml:space="preserve">20.2522850036621</t>
@@ -785,34 +785,34 @@
     <t xml:space="preserve">20.1138858795166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4368133544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5106258392334</t>
+    <t xml:space="preserve">20.4368152618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.510627746582</t>
   </si>
   <si>
     <t xml:space="preserve">20.4644947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3630046844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.390682220459</t>
+    <t xml:space="preserve">20.363000869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3906841278076</t>
   </si>
   <si>
     <t xml:space="preserve">20.5198554992676</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3445491790771</t>
+    <t xml:space="preserve">20.3445510864258</t>
   </si>
   <si>
     <t xml:space="preserve">20.6767063140869</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7228412628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3168716430664</t>
+    <t xml:space="preserve">20.7228393554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.316873550415</t>
   </si>
   <si>
     <t xml:space="preserve">20.639799118042</t>
@@ -824,37 +824,37 @@
     <t xml:space="preserve">21.3502445220947</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2210712432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1749420166016</t>
+    <t xml:space="preserve">21.2210750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1749382019043</t>
   </si>
   <si>
     <t xml:space="preserve">20.9904098510742</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9811820983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7874298095703</t>
+    <t xml:space="preserve">20.9811840057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.787425994873</t>
   </si>
   <si>
     <t xml:space="preserve">21.1288070678711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9627323150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2026214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0826778411865</t>
+    <t xml:space="preserve">20.9627304077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2026195526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0826740264893</t>
   </si>
   <si>
     <t xml:space="preserve">20.5013999938965</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0273151397705</t>
+    <t xml:space="preserve">21.0273189544678</t>
   </si>
   <si>
     <t xml:space="preserve">20.8151016235352</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">21.101131439209</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1933917999268</t>
+    <t xml:space="preserve">21.193395614624</t>
   </si>
   <si>
     <t xml:space="preserve">21.138032913208</t>
@@ -887,67 +887,67 @@
     <t xml:space="preserve">20.1784725189209</t>
   </si>
   <si>
-    <t xml:space="preserve">20.261510848999</t>
+    <t xml:space="preserve">20.2615089416504</t>
   </si>
   <si>
     <t xml:space="preserve">20.2707386016846</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1876964569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4921722412109</t>
+    <t xml:space="preserve">20.1876983642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4921741485596</t>
   </si>
   <si>
     <t xml:space="preserve">20.1415672302246</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9109039306641</t>
+    <t xml:space="preserve">19.9109020233154</t>
   </si>
   <si>
     <t xml:space="preserve">20.0769786834717</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6617851257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7725067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1323413848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1600208282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4091377258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2984199523926</t>
+    <t xml:space="preserve">19.6617870330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7725048065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1323394775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1600170135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4091358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2984161376953</t>
   </si>
   <si>
     <t xml:space="preserve">19.8186378479004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6986885070801</t>
+    <t xml:space="preserve">19.6986904144287</t>
   </si>
   <si>
     <t xml:space="preserve">19.7540531158447</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5879745483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7909564971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9385833740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8647689819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9754886627197</t>
+    <t xml:space="preserve">19.5879707336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.790958404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9385852813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8647727966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9754905700684</t>
   </si>
   <si>
     <t xml:space="preserve">19.5418395996094</t>
@@ -956,22 +956,22 @@
     <t xml:space="preserve">20.5290813446045</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1046619415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.837085723877</t>
+    <t xml:space="preserve">20.1046600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8370876312256</t>
   </si>
   <si>
     <t xml:space="preserve">19.5972003936768</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2799606323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9939403533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3537750244141</t>
+    <t xml:space="preserve">20.2799625396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9939422607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3537769317627</t>
   </si>
   <si>
     <t xml:space="preserve">20.7043857574463</t>
@@ -983,130 +983,130 @@
     <t xml:space="preserve">20.4275913238525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7505168914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0549926757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5844421386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3353271484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1969242095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2338333129883</t>
+    <t xml:space="preserve">20.7505187988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0549945831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5844402313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3353252410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1969261169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2338314056396</t>
   </si>
   <si>
     <t xml:space="preserve">19.7448234558105</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7079219818115</t>
+    <t xml:space="preserve">19.7079200744629</t>
   </si>
   <si>
     <t xml:space="preserve">19.634105682373</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8463191986084</t>
+    <t xml:space="preserve">19.8463172912598</t>
   </si>
   <si>
     <t xml:space="preserve">19.9570331573486</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3814582824707</t>
+    <t xml:space="preserve">20.3814563751221</t>
   </si>
   <si>
     <t xml:space="preserve">19.8555431365967</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4034461975098</t>
+    <t xml:space="preserve">19.4034423828125</t>
   </si>
   <si>
     <t xml:space="preserve">19.1266460418701</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6560916900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7114486694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5084629058838</t>
+    <t xml:space="preserve">18.6560935974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7114505767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5084667205811</t>
   </si>
   <si>
     <t xml:space="preserve">18.8683032989502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5545978546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4346542358398</t>
+    <t xml:space="preserve">18.5546016693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4346561431885</t>
   </si>
   <si>
     <t xml:space="preserve">18.5361461639404</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3147106170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6837730407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0067024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.849760055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8219413757324</t>
+    <t xml:space="preserve">18.3147068023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6837711334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0067005157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8497581481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8219394683838</t>
   </si>
   <si>
     <t xml:space="preserve">18.4047088623047</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1821842193604</t>
+    <t xml:space="preserve">18.1821823120117</t>
   </si>
   <si>
     <t xml:space="preserve">17.7834911346436</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7278594970703</t>
+    <t xml:space="preserve">17.7278614044189</t>
   </si>
   <si>
     <t xml:space="preserve">17.5238761901855</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5516929626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.82057762146</t>
+    <t xml:space="preserve">17.5516948699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8205757141113</t>
   </si>
   <si>
     <t xml:space="preserve">17.7742195129395</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8483905792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1450958251953</t>
+    <t xml:space="preserve">17.8483924865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1450939178467</t>
   </si>
   <si>
     <t xml:space="preserve">18.3398036956787</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4603385925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2841701507568</t>
+    <t xml:space="preserve">18.460334777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2841720581055</t>
   </si>
   <si>
     <t xml:space="preserve">18.0431041717529</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3676166534424</t>
+    <t xml:space="preserve">18.367618560791</t>
   </si>
   <si>
     <t xml:space="preserve">18.2378101348877</t>
@@ -1118,22 +1118,22 @@
     <t xml:space="preserve">18.5437850952148</t>
   </si>
   <si>
-    <t xml:space="preserve">18.64577293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5716018676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5623302459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4881572723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2285423278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2563571929932</t>
+    <t xml:space="preserve">18.6457767486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5715999603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5623321533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4881553649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2285404205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2563591003418</t>
   </si>
   <si>
     <t xml:space="preserve">18.3212585449219</t>
@@ -1142,22 +1142,22 @@
     <t xml:space="preserve">18.3583469390869</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3490753173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.534517288208</t>
+    <t xml:space="preserve">18.3490772247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5345134735107</t>
   </si>
   <si>
     <t xml:space="preserve">18.5808734893799</t>
   </si>
   <si>
-    <t xml:space="preserve">18.469612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2656288146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3768920898438</t>
+    <t xml:space="preserve">18.4696102142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2656307220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3768882751465</t>
   </si>
   <si>
     <t xml:space="preserve">18.7755832672119</t>
@@ -1169,16 +1169,16 @@
     <t xml:space="preserve">19.3318977355957</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6100540161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3981647491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1399154663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4180698394775</t>
+    <t xml:space="preserve">19.610050201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3981609344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1399173736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4180717468262</t>
   </si>
   <si>
     <t xml:space="preserve">21.3717098236084</t>
@@ -1190,10 +1190,10 @@
     <t xml:space="preserve">21.4644317626953</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3253517150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6035060882568</t>
+    <t xml:space="preserve">21.3253536224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6035079956055</t>
   </si>
   <si>
     <t xml:space="preserve">21.6498699188232</t>
@@ -1202,25 +1202,25 @@
     <t xml:space="preserve">20.861759185791</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3054428100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9081192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4908828735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6299591064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5836029052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9544773101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0471992492676</t>
+    <t xml:space="preserve">20.3054447174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9081172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4908866882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6299610137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5836009979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9544792175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0471935272217</t>
   </si>
   <si>
     <t xml:space="preserve">21.0008373260498</t>
@@ -1229,103 +1229,103 @@
     <t xml:space="preserve">20.7226810455322</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5372409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5571479797363</t>
+    <t xml:space="preserve">20.5372428894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5571537017822</t>
   </si>
   <si>
     <t xml:space="preserve">22.0671043395996</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7425861358643</t>
+    <t xml:space="preserve">21.7425899505615</t>
   </si>
   <si>
     <t xml:space="preserve">21.9280281066895</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8353080749512</t>
+    <t xml:space="preserve">21.8353042602539</t>
   </si>
   <si>
     <t xml:space="preserve">20.6763191223145</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0935592651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1663665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0736484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7690391540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.444522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8153991699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.186279296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2590866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.351806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9809303283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8682994842529</t>
+    <t xml:space="preserve">21.0935554504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1663684844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0736503601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7690410614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4445209503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8153972625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1862735748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2590847015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3518028259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9809284210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8683013916016</t>
   </si>
   <si>
     <t xml:space="preserve">18.9146595001221</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0073795318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1928195953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6564121246338</t>
+    <t xml:space="preserve">19.0073776245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1928215026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6564140319824</t>
   </si>
   <si>
     <t xml:space="preserve">19.4709739685059</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2127265930176</t>
+    <t xml:space="preserve">20.2127246856689</t>
   </si>
   <si>
     <t xml:space="preserve">20.1200084686279</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8418483734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0272903442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8882083892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7491283416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7954883575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2855377197266</t>
+    <t xml:space="preserve">19.8418521881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0272884368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8882102966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7491302490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7954921722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2855339050293</t>
   </si>
   <si>
     <t xml:space="preserve">19.424617767334</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3782577514648</t>
+    <t xml:space="preserve">19.3782558441162</t>
   </si>
   <si>
     <t xml:space="preserve">19.5173320770264</t>
@@ -1340,82 +1340,82 @@
     <t xml:space="preserve">19.1000995635986</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2391815185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7027702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2789936065674</t>
+    <t xml:space="preserve">19.2391777038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7027721405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.278995513916</t>
   </si>
   <si>
     <t xml:space="preserve">19.9345684051514</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5980529785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.205904006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5953235626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6681346893311</t>
+    <t xml:space="preserve">17.598051071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2059049606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5953245162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6681327819824</t>
   </si>
   <si>
     <t xml:space="preserve">14.3714323043823</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7052192687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2986221313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5211477279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8920249938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.428427696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2244482040405</t>
+    <t xml:space="preserve">14.7052211761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.298623085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5211496353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8920240402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4284286499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2244491577148</t>
   </si>
   <si>
     <t xml:space="preserve">15.3542537689209</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7622156143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6880445480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.558235168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4840650558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2800779342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9092035293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7599248886108</t>
+    <t xml:space="preserve">15.7622175216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6880407333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5582370758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4840631484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2800798416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9092044830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7599239349365</t>
   </si>
   <si>
     <t xml:space="preserve">14.4800271987915</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3120899200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3494081497192</t>
+    <t xml:space="preserve">14.3120889663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3494100570679</t>
   </si>
   <si>
     <t xml:space="preserve">14.8159046173096</t>
@@ -1424,28 +1424,28 @@
     <t xml:space="preserve">14.8345632553101</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5546674728394</t>
+    <t xml:space="preserve">14.554666519165</t>
   </si>
   <si>
     <t xml:space="preserve">15.0398235321045</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3383808135986</t>
+    <t xml:space="preserve">15.3383798599243</t>
   </si>
   <si>
     <t xml:space="preserve">15.1704406738281</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9762125015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8269338607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5097160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6403341293335</t>
+    <t xml:space="preserve">13.9762115478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8269329071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5097169876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6403350830078</t>
   </si>
   <si>
     <t xml:space="preserve">14.2374496459961</t>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve">14.0695114135742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0508508682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1254930496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8642539978027</t>
+    <t xml:space="preserve">14.0508518218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1254911422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8642520904541</t>
   </si>
   <si>
     <t xml:space="preserve">13.5470371246338</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">13.9575529098511</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1068305969238</t>
+    <t xml:space="preserve">14.1068315505981</t>
   </si>
   <si>
     <t xml:space="preserve">14.4240474700928</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">14.6479654312134</t>
   </si>
   <si>
-    <t xml:space="preserve">15.114462852478</t>
+    <t xml:space="preserve">15.1144618988037</t>
   </si>
   <si>
     <t xml:space="preserve">15.0211629867554</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">14.9278631210327</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9651832580566</t>
+    <t xml:space="preserve">14.965184211731</t>
   </si>
   <si>
     <t xml:space="preserve">14.7972440719604</t>
@@ -1502,61 +1502,61 @@
     <t xml:space="preserve">15.0025024414062</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0584812164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0958003997803</t>
+    <t xml:space="preserve">15.058482170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0958023071289</t>
   </si>
   <si>
     <t xml:space="preserve">15.4316806793213</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8608560562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7005481719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7751884460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7938480377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3833293914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3086891174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1594104766846</t>
+    <t xml:space="preserve">15.8608531951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7005462646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7751846313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7938461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3833312988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3086910247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1594123840332</t>
   </si>
   <si>
     <t xml:space="preserve">16.2527103424072</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8795166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7675542831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.711576461792</t>
+    <t xml:space="preserve">15.8795156478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7675533294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7115745544434</t>
   </si>
   <si>
     <t xml:space="preserve">16.0287933349609</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0474548339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1407508850098</t>
+    <t xml:space="preserve">16.0474529266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1407527923584</t>
   </si>
   <si>
     <t xml:space="preserve">16.5139503479004</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4019889831543</t>
+    <t xml:space="preserve">16.4019908905029</t>
   </si>
   <si>
     <t xml:space="preserve">16.178071975708</t>
@@ -1565,55 +1565,55 @@
     <t xml:space="preserve">16.3273487091064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3460121154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1220951080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.495288848877</t>
+    <t xml:space="preserve">16.3460102081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1220970153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4952907562256</t>
   </si>
   <si>
     <t xml:space="preserve">16.6072463989258</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3646697998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2153911590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7488965988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8421964645386</t>
+    <t xml:space="preserve">16.3646717071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2153873443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7488946914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8421945571899</t>
   </si>
   <si>
     <t xml:space="preserve">15.8235359191895</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0101299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8981761932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2340488433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2900295257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4206504821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6632270812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8311653137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3536415100098</t>
+    <t xml:space="preserve">16.0101318359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8981742858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2340507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2900276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4206523895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6632251739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8311672210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3536396026611</t>
   </si>
   <si>
     <t xml:space="preserve">18.1560134887695</t>
@@ -1628,13 +1628,13 @@
     <t xml:space="preserve">17.9880752563477</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4096202850342</t>
+    <t xml:space="preserve">17.4096221923828</t>
   </si>
   <si>
     <t xml:space="preserve">17.017765045166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8871459960938</t>
+    <t xml:space="preserve">16.8871440887451</t>
   </si>
   <si>
     <t xml:space="preserve">16.8684864044189</t>
@@ -1643,13 +1643,13 @@
     <t xml:space="preserve">16.6259059906006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5326061248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8498249053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7192096710205</t>
+    <t xml:space="preserve">16.5326080322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8498229980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">16.9431266784668</t>
@@ -1658,79 +1658,79 @@
     <t xml:space="preserve">17.0364246368408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1110649108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6445693969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1034317016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.394359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4130172729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3570384979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0771417617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5919876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7039461135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9838418960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6666250228882</t>
+    <t xml:space="preserve">17.1110610961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6445713043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1034336090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3943586349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4130191802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3570394515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0771427154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.591986656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7039442062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9838428497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6666269302368</t>
   </si>
   <si>
     <t xml:space="preserve">14.871883392334</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7412662506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.405387878418</t>
+    <t xml:space="preserve">14.7412643432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4053888320923</t>
   </si>
   <si>
     <t xml:space="preserve">14.5733261108398</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2747707366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7226047515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.461368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.368067741394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5360069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4689998626709</t>
+    <t xml:space="preserve">14.2747688293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7226037979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4613666534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3680686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5360059738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4689989089966</t>
   </si>
   <si>
     <t xml:space="preserve">15.3010606765747</t>
   </si>
   <si>
-    <t xml:space="preserve">15.282398223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5622968673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1331205368042</t>
+    <t xml:space="preserve">15.2824001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5622978210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1331214904785</t>
   </si>
   <si>
     <t xml:space="preserve">15.4876594543457</t>
@@ -1739,13 +1739,13 @@
     <t xml:space="preserve">15.3197202682495</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2264204025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9465217590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.77858543396</t>
+    <t xml:space="preserve">15.2264213562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9465236663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7785844802856</t>
   </si>
   <si>
     <t xml:space="preserve">14.4427080154419</t>
@@ -1754,19 +1754,19 @@
     <t xml:space="preserve">14.685284614563</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5173463821411</t>
+    <t xml:space="preserve">14.5173473358154</t>
   </si>
   <si>
     <t xml:space="preserve">14.2001304626465</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1814699172974</t>
+    <t xml:space="preserve">14.1814708709717</t>
   </si>
   <si>
     <t xml:space="preserve">13.9948720932007</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8082733154297</t>
+    <t xml:space="preserve">13.808274269104</t>
   </si>
   <si>
     <t xml:space="preserve">13.6776542663574</t>
@@ -1775,16 +1775,16 @@
     <t xml:space="preserve">14.3307485580444</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1628122329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7149753570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.752293586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9388914108276</t>
+    <t xml:space="preserve">14.1628103256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7149744033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7522926330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9388933181763</t>
   </si>
   <si>
     <t xml:space="preserve">13.8455924987793</t>
@@ -1802,13 +1802,13 @@
     <t xml:space="preserve">13.9015712738037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2637414932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.088171005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0135335922241</t>
+    <t xml:space="preserve">15.2637405395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0881719589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0135307312012</t>
   </si>
   <si>
     <t xml:space="preserve">14.3867282867432</t>
@@ -1817,34 +1817,34 @@
     <t xml:space="preserve">14.8905448913574</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1891031265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9740743637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9552392959595</t>
+    <t xml:space="preserve">15.1891021728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9740734100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9552383422852</t>
   </si>
   <si>
     <t xml:space="preserve">14.8045568466187</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7103786468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7857208251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2754373550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5768041610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3490505218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2172031402588</t>
+    <t xml:space="preserve">14.7103805541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.785719871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2754383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5768051147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3490543365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2172050476074</t>
   </si>
   <si>
     <t xml:space="preserve">15.5956392288208</t>
@@ -1853,25 +1853,25 @@
     <t xml:space="preserve">15.5579690933228</t>
   </si>
   <si>
-    <t xml:space="preserve">15.426121711731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4449577331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3507804870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6521472930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6898155212402</t>
+    <t xml:space="preserve">15.4261198043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4449558258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3507795333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6521463394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6898136138916</t>
   </si>
   <si>
     <t xml:space="preserve">16.0665187835693</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6144752502441</t>
+    <t xml:space="preserve">15.6144733428955</t>
   </si>
   <si>
     <t xml:space="preserve">15.5014629364014</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">15.5391321182251</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9346742630005</t>
+    <t xml:space="preserve">15.9346761703491</t>
   </si>
   <si>
     <t xml:space="preserve">15.8781700134277</t>
@@ -1889,16 +1889,16 @@
     <t xml:space="preserve">15.3131093978882</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7274856567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.463791847229</t>
+    <t xml:space="preserve">15.7274866104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4637908935547</t>
   </si>
   <si>
     <t xml:space="preserve">15.3319454193115</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4826278686523</t>
+    <t xml:space="preserve">15.4826288223267</t>
   </si>
   <si>
     <t xml:space="preserve">15.1435918807983</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">15.0117435455322</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8798961639404</t>
+    <t xml:space="preserve">14.8798990249634</t>
   </si>
   <si>
     <t xml:space="preserve">15.1059217453003</t>
@@ -1919,16 +1919,16 @@
     <t xml:space="preserve">14.8422269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4090156555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9381313323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8439540863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1264839172363</t>
+    <t xml:space="preserve">14.4090147018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9381322860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.843955039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1264848709106</t>
   </si>
   <si>
     <t xml:space="preserve">14.5031900405884</t>
@@ -1937,16 +1937,16 @@
     <t xml:space="preserve">14.6915445327759</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4843559265137</t>
+    <t xml:space="preserve">14.4843549728394</t>
   </si>
   <si>
     <t xml:space="preserve">14.2960023880005</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3336734771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5220260620117</t>
+    <t xml:space="preserve">14.3336725234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.522027015686</t>
   </si>
   <si>
     <t xml:space="preserve">14.2394971847534</t>
@@ -1955,55 +1955,55 @@
     <t xml:space="preserve">14.182991027832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9569664001465</t>
+    <t xml:space="preserve">13.9569673538208</t>
   </si>
   <si>
     <t xml:space="preserve">13.5990953445435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0528717041016</t>
+    <t xml:space="preserve">13.0528707504272</t>
   </si>
   <si>
     <t xml:space="preserve">12.9210243225098</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2788963317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9963655471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7138357162476</t>
+    <t xml:space="preserve">13.2788953781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9963665008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7138366699219</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371295928955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0922718048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8662481307983</t>
+    <t xml:space="preserve">12.0922708511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.866247177124</t>
   </si>
   <si>
     <t xml:space="preserve">11.3953657150269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9621515274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0580577850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88854026794434</t>
+    <t xml:space="preserve">10.9621524810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0580568313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8885383605957</t>
   </si>
   <si>
     <t xml:space="preserve">9.53066825866699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85259628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35173225402832</t>
+    <t xml:space="preserve">8.8525972366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35173416137695</t>
   </si>
   <si>
     <t xml:space="preserve">8.0426778793335</t>
@@ -2012,31 +2012,31 @@
     <t xml:space="preserve">8.49472713470459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04095077514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0957288742065</t>
+    <t xml:space="preserve">9.04094982147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0957279205322</t>
   </si>
   <si>
     <t xml:space="preserve">10.6796236038208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8474111557007</t>
+    <t xml:space="preserve">11.847412109375</t>
   </si>
   <si>
     <t xml:space="preserve">12.8080139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5272121429443</t>
+    <t xml:space="preserve">11.52721118927</t>
   </si>
   <si>
     <t xml:space="preserve">10.8868112564087</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8491401672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5666103363037</t>
+    <t xml:space="preserve">10.8491411209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.566611289978</t>
   </si>
   <si>
     <t xml:space="preserve">10.0015506744385</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">10.2652454376221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5477743148804</t>
+    <t xml:space="preserve">10.5477752685547</t>
   </si>
   <si>
     <t xml:space="preserve">10.6607866287231</t>
@@ -2054,52 +2054,52 @@
     <t xml:space="preserve">11.0374927520752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.830304145813</t>
+    <t xml:space="preserve">10.8303060531616</t>
   </si>
   <si>
     <t xml:space="preserve">10.5101041793823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1333980560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81319808959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1522340774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4347639083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3594217300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6984577178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6419525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6231164932251</t>
+    <t xml:space="preserve">10.133397102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81319618225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.152232170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4347629547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3594226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6984586715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6419515609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6231155395508</t>
   </si>
   <si>
     <t xml:space="preserve">10.7361278533936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7549619674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4724340438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9244804382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8679752349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4141988754272</t>
+    <t xml:space="preserve">10.7549648284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.47243309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9244823455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.867977142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4141998291016</t>
   </si>
   <si>
     <t xml:space="preserve">11.489541053772</t>
@@ -2111,19 +2111,19 @@
     <t xml:space="preserve">11.3388586044312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4330358505249</t>
+    <t xml:space="preserve">11.4330368041992</t>
   </si>
   <si>
     <t xml:space="preserve">11.7155637741089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9227523803711</t>
+    <t xml:space="preserve">11.9227533340454</t>
   </si>
   <si>
     <t xml:space="preserve">12.2052822113037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1299419403076</t>
+    <t xml:space="preserve">12.1299409866333</t>
   </si>
   <si>
     <t xml:space="preserve">12.0169296264648</t>
@@ -2132,55 +2132,55 @@
     <t xml:space="preserve">11.7720718383789</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1505060195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9433164596558</t>
+    <t xml:space="preserve">11.150505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9433174133301</t>
   </si>
   <si>
     <t xml:space="preserve">11.1128349304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0186576843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8114700317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7172918319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6042823791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3405857086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3782577514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5854444503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1316690444946</t>
+    <t xml:space="preserve">11.0186586380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.811469078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7172946929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6042814254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3405866622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3782587051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5854454040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1316699981689</t>
   </si>
   <si>
     <t xml:space="preserve">11.2635173797607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2070112228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9998226165771</t>
+    <t xml:space="preserve">11.207010269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9998235702515</t>
   </si>
   <si>
     <t xml:space="preserve">10.9056463241577</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5289402008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3029165267944</t>
+    <t xml:space="preserve">10.52894115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3029155731201</t>
   </si>
   <si>
     <t xml:space="preserve">10.3970928192139</t>
@@ -2195,37 +2195,37 @@
     <t xml:space="preserve">11.6025533676147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4518690109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.546046257019</t>
+    <t xml:space="preserve">11.4518709182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5460472106934</t>
   </si>
   <si>
     <t xml:space="preserve">11.4707069396973</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5837173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6590576171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1487770080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0546007156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0357637405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8850831985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9039182662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7344007492065</t>
+    <t xml:space="preserve">11.5837182998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6590585708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1487760543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0545997619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0357646942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.885082244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9039173126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7343997955322</t>
   </si>
   <si>
     <t xml:space="preserve">11.6778936386108</t>
@@ -2246,79 +2246,79 @@
     <t xml:space="preserve">13.7686138153076</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5049200057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.147047996521</t>
+    <t xml:space="preserve">13.504919052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1470489501953</t>
   </si>
   <si>
     <t xml:space="preserve">13.3354015350342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3730726242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0152015686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2412252426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0323066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6367654800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3165674209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0340356826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3919076919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0905418395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9415884017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9792594909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2429533004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3559656143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7703418731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7326707839966</t>
+    <t xml:space="preserve">13.3730716705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0152006149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2412242889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0323085784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6367664337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3165664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0340375900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3919067382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0905408859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9415893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9792585372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2429523468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3559646606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7703428268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7326717376709</t>
   </si>
   <si>
     <t xml:space="preserve">12.9586963653564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.22239112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3542385101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4672498703003</t>
+    <t xml:space="preserve">13.2223892211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3542356491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.467248916626</t>
   </si>
   <si>
     <t xml:space="preserve">13.5260181427002</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5450410842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3167552947998</t>
+    <t xml:space="preserve">13.5450420379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3167543411255</t>
   </si>
   <si>
     <t xml:space="preserve">13.3548030853271</t>
@@ -2327,10 +2327,10 @@
     <t xml:space="preserve">13.2216339111328</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4118747711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7543048858643</t>
+    <t xml:space="preserve">13.4118738174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7543039321899</t>
   </si>
   <si>
     <t xml:space="preserve">13.7923526763916</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">14.077712059021</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0586881637573</t>
+    <t xml:space="preserve">14.058687210083</t>
   </si>
   <si>
     <t xml:space="preserve">14.1157598495483</t>
@@ -2351,10 +2351,10 @@
     <t xml:space="preserve">13.8874731063843</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6021146774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3738260269165</t>
+    <t xml:space="preserve">13.6021127700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3738269805908</t>
   </si>
   <si>
     <t xml:space="preserve">13.6782093048096</t>
@@ -2363,28 +2363,28 @@
     <t xml:space="preserve">13.5069942474365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4499225616455</t>
+    <t xml:space="preserve">13.4499235153198</t>
   </si>
   <si>
     <t xml:space="preserve">13.6972332000732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6211366653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7733278274536</t>
+    <t xml:space="preserve">13.6211385726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7733287811279</t>
   </si>
   <si>
     <t xml:space="preserve">14.0396642684937</t>
   </si>
   <si>
-    <t xml:space="preserve">14.248927116394</t>
+    <t xml:space="preserve">14.2489261627197</t>
   </si>
   <si>
     <t xml:space="preserve">14.6103820800781</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5342855453491</t>
+    <t xml:space="preserve">14.5342864990234</t>
   </si>
   <si>
     <t xml:space="preserve">14.8957414627075</t>
@@ -2393,13 +2393,13 @@
     <t xml:space="preserve">14.9337892532349</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3796062469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2274150848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0752258300781</t>
+    <t xml:space="preserve">16.3796081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2274131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0752239227295</t>
   </si>
   <si>
     <t xml:space="preserve">15.713770866394</t>
@@ -2414,31 +2414,31 @@
     <t xml:space="preserve">15.5045070648193</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2191486358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6376752853394</t>
+    <t xml:space="preserve">15.2191495895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6376762390137</t>
   </si>
   <si>
     <t xml:space="preserve">15.2381715774536</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3332929611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6186504364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7518177032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1513214111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4937515258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6649684906006</t>
+    <t xml:space="preserve">15.3332920074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6186494827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7518186569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1513195037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4937534332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.664966583252</t>
   </si>
   <si>
     <t xml:space="preserve">16.5698490142822</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">16.5317974090576</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6078948974609</t>
+    <t xml:space="preserve">16.6078910827637</t>
   </si>
   <si>
     <t xml:space="preserve">16.5888710021973</t>
@@ -2456,16 +2456,16 @@
     <t xml:space="preserve">17.045446395874</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0264225006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0834922790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8742294311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3415603637695</t>
+    <t xml:space="preserve">17.0264205932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0834941864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.874231338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3415622711182</t>
   </si>
   <si>
     <t xml:space="preserve">16.3225364685059</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">16.7981338500977</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5508232116699</t>
+    <t xml:space="preserve">16.5508251190186</t>
   </si>
   <si>
     <t xml:space="preserve">16.8361835479736</t>
@@ -2483,55 +2483,55 @@
     <t xml:space="preserve">16.81715965271</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7410621643066</t>
+    <t xml:space="preserve">16.7410640716553</t>
   </si>
   <si>
     <t xml:space="preserve">17.8444519042969</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9585971832275</t>
+    <t xml:space="preserve">17.9585933685303</t>
   </si>
   <si>
     <t xml:space="preserve">18.1868839263916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.499532699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7848930358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1653728485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6422138214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5934085845947</t>
+    <t xml:space="preserve">19.4995346069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.78489112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1653709411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6422119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5934104919434</t>
   </si>
   <si>
     <t xml:space="preserve">20.3556118011475</t>
   </si>
   <si>
-    <t xml:space="preserve">19.975133895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8324546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7373313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8800106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2604885101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4031715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.498291015625</t>
+    <t xml:space="preserve">19.9751319885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8324508666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7373332977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.880012512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2604923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.403169631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4982872009277</t>
   </si>
   <si>
     <t xml:space="preserve">20.8312091827393</t>
@@ -2543,52 +2543,52 @@
     <t xml:space="preserve">20.2129325866699</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9275722503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7836494445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5946559906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3568534851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2141761779785</t>
+    <t xml:space="preserve">19.9275760650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7836475372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.594654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3568553924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2141742706299</t>
   </si>
   <si>
     <t xml:space="preserve">19.4044132232666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6897754669189</t>
+    <t xml:space="preserve">19.6897735595703</t>
   </si>
   <si>
     <t xml:space="preserve">19.0239353179932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1178092956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3080501556396</t>
+    <t xml:space="preserve">20.1178112030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3080520629883</t>
   </si>
   <si>
     <t xml:space="preserve">20.0702514648438</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9738903045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5446033477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1641292572021</t>
+    <t xml:space="preserve">20.9738883972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5446071624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1641273498535</t>
   </si>
   <si>
     <t xml:space="preserve">21.6397266387939</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5921669006348</t>
+    <t xml:space="preserve">21.5921649932861</t>
   </si>
   <si>
     <t xml:space="preserve">21.6872844696045</t>
@@ -2600,31 +2600,31 @@
     <t xml:space="preserve">21.7348461151123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8299655914307</t>
+    <t xml:space="preserve">21.8299674987793</t>
   </si>
   <si>
     <t xml:space="preserve">21.0690078735352</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2116870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3068046569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1628856658936</t>
+    <t xml:space="preserve">21.2116851806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3068084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1628837585449</t>
   </si>
   <si>
     <t xml:space="preserve">22.6384811401367</t>
   </si>
   <si>
-    <t xml:space="preserve">23.161642074585</t>
+    <t xml:space="preserve">23.1616401672363</t>
   </si>
   <si>
     <t xml:space="preserve">22.4958038330078</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2580051422119</t>
+    <t xml:space="preserve">22.2580032348633</t>
   </si>
   <si>
     <t xml:space="preserve">21.8775253295898</t>
@@ -2639,13 +2639,13 @@
     <t xml:space="preserve">20.6885299682617</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6409683227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7824077606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3506393432617</t>
+    <t xml:space="preserve">20.6409721374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7824058532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3506355285645</t>
   </si>
   <si>
     <t xml:space="preserve">23.7799205780029</t>
@@ -2654,22 +2654,22 @@
     <t xml:space="preserve">23.3043212890625</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2567615509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0189628601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1140804290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3518772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0665245056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5896797180176</t>
+    <t xml:space="preserve">23.2567596435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0189647674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1140823364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.351879119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0665225982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5896778106689</t>
   </si>
   <si>
     <t xml:space="preserve">23.44700050354</t>
@@ -2681,40 +2681,40 @@
     <t xml:space="preserve">23.6372394561768</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5421199798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4945602416992</t>
+    <t xml:space="preserve">23.5421180725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4945621490479</t>
   </si>
   <si>
     <t xml:space="preserve">22.8762798309326</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3994407653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6860427856445</t>
+    <t xml:space="preserve">23.3994426727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6860446929932</t>
   </si>
   <si>
     <t xml:space="preserve">22.4482440948486</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1153240203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4494857788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0677642822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.020206451416</t>
+    <t xml:space="preserve">22.1153259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4494876861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0677661895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0202045440674</t>
   </si>
   <si>
     <t xml:space="preserve">24.0652770996094</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7323589324951</t>
+    <t xml:space="preserve">23.7323608398438</t>
   </si>
   <si>
     <t xml:space="preserve">24.3030776977539</t>
@@ -2726,52 +2726,52 @@
     <t xml:space="preserve">23.6847991943359</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3018321990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.587194442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9676685333252</t>
+    <t xml:space="preserve">25.3018341064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5871925354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9676704406738</t>
   </si>
   <si>
     <t xml:space="preserve">25.6823120117188</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6347560882568</t>
+    <t xml:space="preserve">25.6347522735596</t>
   </si>
   <si>
     <t xml:space="preserve">25.7774333953857</t>
   </si>
   <si>
-    <t xml:space="preserve">25.492073059082</t>
+    <t xml:space="preserve">25.4920749664307</t>
   </si>
   <si>
     <t xml:space="preserve">26.3005886077881</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3957118988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2993469238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2042293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1566677093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6798267364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2981033325195</t>
+    <t xml:space="preserve">26.3957099914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2993488311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2042255401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.156665802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6798286437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2981052398682</t>
   </si>
   <si>
     <t xml:space="preserve">27.7749462127686</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1078624725342</t>
+    <t xml:space="preserve">28.1078643798828</t>
   </si>
   <si>
     <t xml:space="preserve">27.5847053527832</t>
@@ -2783,31 +2783,31 @@
     <t xml:space="preserve">27.537145614624</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3469047546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0615482330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7761898040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9664268493652</t>
+    <t xml:space="preserve">27.3469085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0615501403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7761878967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9664287567139</t>
   </si>
   <si>
     <t xml:space="preserve">26.8713092803955</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5383892059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7469043731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.077033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6464042663574</t>
+    <t xml:space="preserve">26.5383911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7469062805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0770359039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6464061737061</t>
   </si>
   <si>
     <t xml:space="preserve">25.2636241912842</t>
@@ -2816,22 +2816,22 @@
     <t xml:space="preserve">24.4023628234863</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5459060668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9717350006104</t>
+    <t xml:space="preserve">24.5459041595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9717330932617</t>
   </si>
   <si>
     <t xml:space="preserve">24.5937557220459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4980602264404</t>
+    <t xml:space="preserve">24.4980583190918</t>
   </si>
   <si>
     <t xml:space="preserve">24.9286880493164</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2205772399902</t>
+    <t xml:space="preserve">26.2205791473389</t>
   </si>
   <si>
     <t xml:space="preserve">26.6512088775635</t>
@@ -2840,19 +2840,19 @@
     <t xml:space="preserve">26.2684268951416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7421016693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6942520141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3114700317383</t>
+    <t xml:space="preserve">25.7420997619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6942539215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3114719390869</t>
   </si>
   <si>
     <t xml:space="preserve">25.5507106781006</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9765377044678</t>
+    <t xml:space="preserve">24.9765357971191</t>
   </si>
   <si>
     <t xml:space="preserve">25.4071655273438</t>
@@ -2864,13 +2864,13 @@
     <t xml:space="preserve">25.8856430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7899513244629</t>
+    <t xml:space="preserve">25.7899475097656</t>
   </si>
   <si>
     <t xml:space="preserve">25.9813404083252</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4550132751465</t>
+    <t xml:space="preserve">25.4550151824951</t>
   </si>
   <si>
     <t xml:space="preserve">24.6894493103027</t>
@@ -2879,13 +2879,13 @@
     <t xml:space="preserve">25.5028610229492</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3593196868896</t>
+    <t xml:space="preserve">25.359317779541</t>
   </si>
   <si>
     <t xml:space="preserve">24.8808403015137</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3066654205322</t>
+    <t xml:space="preserve">24.3066673278809</t>
   </si>
   <si>
     <t xml:space="preserve">22.8233871459961</t>
@@ -2894,10 +2894,10 @@
     <t xml:space="preserve">22.6319961547852</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4932518005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8712329864502</t>
+    <t xml:space="preserve">23.4932537078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8712348937988</t>
   </si>
   <si>
     <t xml:space="preserve">22.7755374908447</t>
@@ -2906,22 +2906,22 @@
     <t xml:space="preserve">23.0626258850098</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2540149688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.297061920166</t>
+    <t xml:space="preserve">23.2540187835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2970600128174</t>
   </si>
   <si>
     <t xml:space="preserve">21.81858253479</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6750373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4357986450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4884510040283</t>
+    <t xml:space="preserve">21.6750411987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4358024597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.488452911377</t>
   </si>
   <si>
     <t xml:space="preserve">22.6798439025879</t>
@@ -2939,25 +2939,25 @@
     <t xml:space="preserve">22.009973526001</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9142818450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2444114685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0051727294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3831481933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.378345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0482158660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8089790344238</t>
+    <t xml:space="preserve">21.9142799377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2444133758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0051708221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.383150100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3783473968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0482196807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8089771270752</t>
   </si>
   <si>
     <t xml:space="preserve">18.8328819274902</t>
@@ -2966,13 +2966,13 @@
     <t xml:space="preserve">19.0242729187012</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0098991394043</t>
+    <t xml:space="preserve">18.0099029541016</t>
   </si>
   <si>
     <t xml:space="preserve">16.7849998474121</t>
   </si>
   <si>
-    <t xml:space="preserve">16.842414855957</t>
+    <t xml:space="preserve">16.8424167633057</t>
   </si>
   <si>
     <t xml:space="preserve">17.8950691223145</t>
@@ -2981,28 +2981,28 @@
     <t xml:space="preserve">18.0290393829346</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4357261657715</t>
+    <t xml:space="preserve">17.4357280731201</t>
   </si>
   <si>
     <t xml:space="preserve">18.1821517944336</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7228164672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3783092498779</t>
+    <t xml:space="preserve">17.7228145599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3783111572266</t>
   </si>
   <si>
     <t xml:space="preserve">18.5457954406738</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1438732147217</t>
+    <t xml:space="preserve">18.1438751220703</t>
   </si>
   <si>
     <t xml:space="preserve">18.2012920379639</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5649337768555</t>
+    <t xml:space="preserve">18.5649356842041</t>
   </si>
   <si>
     <t xml:space="preserve">18.2587089538574</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">18.9477157592773</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0625514984131</t>
+    <t xml:space="preserve">19.0625534057617</t>
   </si>
   <si>
     <t xml:space="preserve">19.4740428924561</t>
@@ -3029,25 +3029,25 @@
     <t xml:space="preserve">18.5075168609619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6462593078613</t>
+    <t xml:space="preserve">17.6462574005127</t>
   </si>
   <si>
     <t xml:space="preserve">18.5266571044922</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2778511047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.603214263916</t>
+    <t xml:space="preserve">18.2778491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6032161712646</t>
   </si>
   <si>
     <t xml:space="preserve">19.2826538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6175842285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0051345825195</t>
+    <t xml:space="preserve">19.6175861358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0051364898682</t>
   </si>
   <si>
     <t xml:space="preserve">18.6223526000977</t>
@@ -3071,67 +3071,67 @@
     <t xml:space="preserve">17.9716243743896</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6654319763184</t>
+    <t xml:space="preserve">19.6654357910156</t>
   </si>
   <si>
     <t xml:space="preserve">19.9046726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8616275787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5745429992676</t>
+    <t xml:space="preserve">20.861629486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5745410919189</t>
   </si>
   <si>
     <t xml:space="preserve">20.9094753265381</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3401050567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2922592163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7228889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2492122650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9669303894043</t>
+    <t xml:space="preserve">21.3401031494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.29225730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7228870391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2492141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9669284820557</t>
   </si>
   <si>
     <t xml:space="preserve">23.1583232879639</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3927574157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0578193664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2874565124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6702346801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7611293792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0960655212402</t>
+    <t xml:space="preserve">22.3927555084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0578231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2874546051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6702365875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7611274719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0960636138916</t>
   </si>
   <si>
     <t xml:space="preserve">20.3353042602539</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7132835388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1199703216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6606292724609</t>
+    <t xml:space="preserve">19.7132816314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1199684143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6606311798096</t>
   </si>
   <si>
     <t xml:space="preserve">18.4692401885986</t>
@@ -3152,10 +3152,10 @@
     <t xml:space="preserve">17.9524841308594</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4309597015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5840721130371</t>
+    <t xml:space="preserve">18.4309616088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5840740203857</t>
   </si>
   <si>
     <t xml:space="preserve">18.8137435913086</t>
@@ -3164,34 +3164,34 @@
     <t xml:space="preserve">18.4118213653564</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3161277770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1630115509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8567905426025</t>
+    <t xml:space="preserve">18.316125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.163013458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8567886352539</t>
   </si>
   <si>
     <t xml:space="preserve">18.4500999450684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1869564056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7180480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8520202636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3305015563965</t>
+    <t xml:space="preserve">19.186954498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7180461883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8520240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3304996490479</t>
   </si>
   <si>
     <t xml:space="preserve">18.0481796264648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5888385772705</t>
+    <t xml:space="preserve">17.5888404846191</t>
   </si>
   <si>
     <t xml:space="preserve">17.7993698120117</t>
@@ -3200,25 +3200,25 @@
     <t xml:space="preserve">17.5122852325439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0864562988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1247367858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5505638122559</t>
+    <t xml:space="preserve">18.0864582061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.12473487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5505619049072</t>
   </si>
   <si>
     <t xml:space="preserve">17.2251987457275</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5170516967773</t>
+    <t xml:space="preserve">16.5170497894287</t>
   </si>
   <si>
     <t xml:space="preserve">15.8854608535767</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3447971343994</t>
+    <t xml:space="preserve">16.344799041748</t>
   </si>
   <si>
     <t xml:space="preserve">16.0959911346436</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">15.9428768157959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1151313781738</t>
+    <t xml:space="preserve">16.1151294708252</t>
   </si>
   <si>
     <t xml:space="preserve">15.3112869262695</t>
@@ -3236,13 +3236,13 @@
     <t xml:space="preserve">15.4452600479126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2538690567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6127452850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0194339752197</t>
+    <t xml:space="preserve">15.2538681030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6127471923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0194320678711</t>
   </si>
   <si>
     <t xml:space="preserve">16.6510238647461</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">16.7658596038818</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9955272674561</t>
+    <t xml:space="preserve">16.9955291748047</t>
   </si>
   <si>
     <t xml:space="preserve">17.3208923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1295032501221</t>
+    <t xml:space="preserve">17.1295013427734</t>
   </si>
   <si>
     <t xml:space="preserve">17.0529460906982</t>
@@ -3266,25 +3266,25 @@
     <t xml:space="preserve">17.0146675109863</t>
   </si>
   <si>
-    <t xml:space="preserve">17.837646484375</t>
+    <t xml:space="preserve">17.8376483917236</t>
   </si>
   <si>
     <t xml:space="preserve">18.756326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6989116668701</t>
+    <t xml:space="preserve">18.6989097595215</t>
   </si>
   <si>
     <t xml:space="preserve">19.4261932373047</t>
   </si>
   <si>
-    <t xml:space="preserve">19.952522277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0003662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5697402954102</t>
+    <t xml:space="preserve">19.9525203704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0003681182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5697383880615</t>
   </si>
   <si>
     <t xml:space="preserve">20.4309978485107</t>
@@ -3293,10 +3293,10 @@
     <t xml:space="preserve">20.1917591094971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6223907470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7180843353271</t>
+    <t xml:space="preserve">20.622386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7180862426758</t>
   </si>
   <si>
     <t xml:space="preserve">20.649543762207</t>
@@ -3308,76 +3308,76 @@
     <t xml:space="preserve">20.7464904785156</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6010704040527</t>
+    <t xml:space="preserve">20.6010723114014</t>
   </si>
   <si>
     <t xml:space="preserve">20.5041236877441</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3102321624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5525989532471</t>
+    <t xml:space="preserve">20.3102340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5525970458984</t>
   </si>
   <si>
     <t xml:space="preserve">20.4556522369385</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4071788787842</t>
+    <t xml:space="preserve">20.4071769714355</t>
   </si>
   <si>
     <t xml:space="preserve">20.1648120880127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1827487945557</t>
+    <t xml:space="preserve">21.182746887207</t>
   </si>
   <si>
     <t xml:space="preserve">20.3587055206299</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0193939208984</t>
+    <t xml:space="preserve">20.0193920135498</t>
   </si>
   <si>
     <t xml:space="preserve">19.9709205627441</t>
   </si>
   <si>
-    <t xml:space="preserve">20.116340637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8434371948242</t>
+    <t xml:space="preserve">20.1163387298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8434352874756</t>
   </si>
   <si>
     <t xml:space="preserve">20.69801902771</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9403839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6190052032471</t>
+    <t xml:space="preserve">20.9403820037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6190032958984</t>
   </si>
   <si>
     <t xml:space="preserve">21.7159519195557</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4735851287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9098472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0067920684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.29762840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.218620300293</t>
+    <t xml:space="preserve">21.4735870361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9098453521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0067901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2976303100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2186183929443</t>
   </si>
   <si>
     <t xml:space="preserve">22.4430484771729</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7823619842529</t>
+    <t xml:space="preserve">22.7823600769043</t>
   </si>
   <si>
     <t xml:space="preserve">22.9277801513672</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">22.8308334350586</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4125118255615</t>
+    <t xml:space="preserve">23.4125099182129</t>
   </si>
   <si>
     <t xml:space="preserve">23.3640384674072</t>
@@ -3395,22 +3395,22 @@
     <t xml:space="preserve">23.3155632019043</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0732002258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5579299926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5094566345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4609832763672</t>
+    <t xml:space="preserve">23.0731983184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5579319000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5094585418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4609870910645</t>
   </si>
   <si>
     <t xml:space="preserve">23.6064033508301</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7033519744873</t>
+    <t xml:space="preserve">23.7033500671387</t>
   </si>
   <si>
     <t xml:space="preserve">23.121675491333</t>
@@ -3422,34 +3422,34 @@
     <t xml:space="preserve">23.8002948760986</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5273914337158</t>
+    <t xml:space="preserve">24.5273933410645</t>
   </si>
   <si>
     <t xml:space="preserve">25.1575450897217</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8182315826416</t>
+    <t xml:space="preserve">24.818229675293</t>
   </si>
   <si>
     <t xml:space="preserve">24.624340057373</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3334999084473</t>
+    <t xml:space="preserve">24.3335018157959</t>
   </si>
   <si>
     <t xml:space="preserve">24.4304466247559</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2850284576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1396083831787</t>
+    <t xml:space="preserve">24.285026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1396064758301</t>
   </si>
   <si>
     <t xml:space="preserve">23.8487701416016</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5884666442871</t>
+    <t xml:space="preserve">22.5884685516357</t>
   </si>
   <si>
     <t xml:space="preserve">22.4915237426758</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">23.0247268676758</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7338886260986</t>
+    <t xml:space="preserve">22.7338905334473</t>
   </si>
   <si>
     <t xml:space="preserve">22.8793067932129</t>
@@ -3467,19 +3467,19 @@
     <t xml:space="preserve">22.9762535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8972415924072</t>
+    <t xml:space="preserve">23.8972434997559</t>
   </si>
   <si>
     <t xml:space="preserve">24.0911350250244</t>
   </si>
   <si>
-    <t xml:space="preserve">24.188081741333</t>
+    <t xml:space="preserve">24.1880836486816</t>
   </si>
   <si>
     <t xml:space="preserve">22.6854133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2006855010986</t>
+    <t xml:space="preserve">22.20068359375</t>
   </si>
   <si>
     <t xml:space="preserve">21.8128986358643</t>
@@ -3488,10 +3488,10 @@
     <t xml:space="preserve">21.7644271850586</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1522121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3945751190186</t>
+    <t xml:space="preserve">22.1522102355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3945770263672</t>
   </si>
   <si>
     <t xml:space="preserve">22.63694190979</t>
@@ -3503,19 +3503,19 @@
     <t xml:space="preserve">22.5399951934814</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5220603942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4251136779785</t>
+    <t xml:space="preserve">21.5220623016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4251155853271</t>
   </si>
   <si>
     <t xml:space="preserve">21.2312202453613</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2796955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3766384124756</t>
+    <t xml:space="preserve">21.2796936035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3766403198242</t>
   </si>
   <si>
     <t xml:space="preserve">20.9888572692871</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">20.7949638366699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3281669616699</t>
+    <t xml:space="preserve">21.3281688690186</t>
   </si>
   <si>
     <t xml:space="preserve">21.0858020782471</t>
@@ -3539,28 +3539,28 @@
     <t xml:space="preserve">21.8613719940186</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9583168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6674785614014</t>
+    <t xml:space="preserve">21.9583187103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.66748046875</t>
   </si>
   <si>
     <t xml:space="preserve">22.2491569519043</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0426616668701</t>
+    <t xml:space="preserve">24.0426597595215</t>
   </si>
   <si>
     <t xml:space="preserve">25.0121231079102</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0785331726074</t>
+    <t xml:space="preserve">26.0785312652588</t>
   </si>
   <si>
     <t xml:space="preserve">25.8361663818359</t>
   </si>
   <si>
-    <t xml:space="preserve">25.690746307373</t>
+    <t xml:space="preserve">25.6907482147217</t>
   </si>
   <si>
     <t xml:space="preserve">25.6422748565674</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">26.2239513397217</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3693714141846</t>
+    <t xml:space="preserve">26.3693733215332</t>
   </si>
   <si>
     <t xml:space="preserve">25.3029632568359</t>
@@ -3590,10 +3590,10 @@
     <t xml:space="preserve">24.3819713592529</t>
   </si>
   <si>
-    <t xml:space="preserve">24.721284866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9941902160645</t>
+    <t xml:space="preserve">24.7212867736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9941883087158</t>
   </si>
   <si>
     <t xml:space="preserve">24.2365550994873</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">25.0605983734131</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3999080657959</t>
+    <t xml:space="preserve">25.3999099731445</t>
   </si>
   <si>
     <t xml:space="preserve">25.4968547821045</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">25.3514347076416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5453262329102</t>
+    <t xml:space="preserve">25.5453281402588</t>
   </si>
   <si>
     <t xml:space="preserve">25.8003883361816</t>
@@ -3629,13 +3629,13 @@
     <t xml:space="preserve">25.9965896606445</t>
   </si>
   <si>
-    <t xml:space="preserve">26.683292388916</t>
+    <t xml:space="preserve">26.6832942962646</t>
   </si>
   <si>
     <t xml:space="preserve">26.7813911437988</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5361423492432</t>
+    <t xml:space="preserve">26.5361404418945</t>
   </si>
   <si>
     <t xml:space="preserve">26.7323417663574</t>
@@ -3656,22 +3656,22 @@
     <t xml:space="preserve">26.4380416870117</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5851936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.762393951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5661964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6642971038818</t>
+    <t xml:space="preserve">26.5851917266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7623958587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5661945343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6642951965332</t>
   </si>
   <si>
     <t xml:space="preserve">28.1057472229004</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8414974212646</t>
+    <t xml:space="preserve">28.8414993286133</t>
   </si>
   <si>
     <t xml:space="preserve">29.1358013153076</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">29.184850692749</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8225040435791</t>
+    <t xml:space="preserve">29.8225021362305</t>
   </si>
   <si>
     <t xml:space="preserve">29.4791507720947</t>
@@ -3713,13 +3713,13 @@
     <t xml:space="preserve">29.4301013946533</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3620548248291</t>
+    <t xml:space="preserve">30.3620567321777</t>
   </si>
   <si>
     <t xml:space="preserve">29.9696521759033</t>
   </si>
   <si>
-    <t xml:space="preserve">30.558256149292</t>
+    <t xml:space="preserve">30.5582542419434</t>
   </si>
   <si>
     <t xml:space="preserve">30.4601535797119</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">30.6563568115234</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8525581359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.607307434082</t>
+    <t xml:space="preserve">30.8525562286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6073055267334</t>
   </si>
   <si>
     <t xml:space="preserve">30.9016056060791</t>
@@ -3755,10 +3755,10 @@
     <t xml:space="preserve">30.0677528381348</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2639541625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1468563079834</t>
+    <t xml:space="preserve">30.2639560699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.146858215332</t>
   </si>
   <si>
     <t xml:space="preserve">31.3430595397949</t>
@@ -3770,10 +3770,10 @@
     <t xml:space="preserve">30.1658535003662</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3130035400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2940082550049</t>
+    <t xml:space="preserve">30.3130054473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2940063476562</t>
   </si>
   <si>
     <t xml:space="preserve">31.3921089172363</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">32.7655143737793</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3050689697266</t>
+    <t xml:space="preserve">33.3050651550293</t>
   </si>
   <si>
     <t xml:space="preserve">33.3541145324707</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">31.4902076721191</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7354564666748</t>
+    <t xml:space="preserve">31.7354583740234</t>
   </si>
   <si>
     <t xml:space="preserve">32.0788116455078</t>
@@ -3872,19 +3872,19 @@
     <t xml:space="preserve">34.433219909668</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5313186645508</t>
+    <t xml:space="preserve">34.531322479248</t>
   </si>
   <si>
     <t xml:space="preserve">34.7275199890137</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7085266113281</t>
+    <t xml:space="preserve">35.7085227966309</t>
   </si>
   <si>
     <t xml:space="preserve">36.0028266906738</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2971267700195</t>
+    <t xml:space="preserve">36.2971229553223</t>
   </si>
   <si>
     <t xml:space="preserve">35.512321472168</t>
@@ -3893,31 +3893,31 @@
     <t xml:space="preserve">36.6404762268066</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2480735778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6594696044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4632759094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7385787963867</t>
+    <t xml:space="preserve">36.2480773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6594734191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4632720947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7385749816895</t>
   </si>
   <si>
     <t xml:space="preserve">37.2290802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4933280944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2781295776367</t>
+    <t xml:space="preserve">36.4933242797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2781257629395</t>
   </si>
   <si>
     <t xml:space="preserve">36.5423774719238</t>
   </si>
   <si>
-    <t xml:space="preserve">37.523380279541</t>
+    <t xml:space="preserve">37.5233764648438</t>
   </si>
   <si>
     <t xml:space="preserve">37.4743309020996</t>
@@ -3926,13 +3926,13 @@
     <t xml:space="preserve">35.5613746643066</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8066253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7765693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2180213928223</t>
+    <t xml:space="preserve">35.8066215515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7765731811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2180252075195</t>
   </si>
   <si>
     <t xml:space="preserve">34.9237174987793</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">35.0218200683594</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1689720153809</t>
+    <t xml:space="preserve">35.1689682006836</t>
   </si>
   <si>
     <t xml:space="preserve">34.678466796875</t>
@@ -3950,34 +3950,34 @@
     <t xml:space="preserve">33.9917678833008</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3651733398438</t>
+    <t xml:space="preserve">35.3651695251465</t>
   </si>
   <si>
     <t xml:space="preserve">36.051872253418</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8556709289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7575721740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0898666381836</t>
+    <t xml:space="preserve">35.8556747436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7575759887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0898704528809</t>
   </si>
   <si>
     <t xml:space="preserve">33.9427146911621</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0408210754395</t>
+    <t xml:space="preserve">34.0408172607422</t>
   </si>
   <si>
     <t xml:space="preserve">34.3841667175293</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3161201477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2370223999023</t>
+    <t xml:space="preserve">35.3161239624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2370185852051</t>
   </si>
   <si>
     <t xml:space="preserve">32.4221611022949</t>
@@ -4007,7 +4007,7 @@
     <t xml:space="preserve">29.2339000701904</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9095458984375</t>
+    <t xml:space="preserve">27.9095478057861</t>
   </si>
   <si>
     <t xml:space="preserve">27.7133464813232</t>
@@ -4031,7 +4031,7 @@
     <t xml:space="preserve">28.2528972625732</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3209457397461</t>
+    <t xml:space="preserve">27.3209438323975</t>
   </si>
   <si>
     <t xml:space="preserve">27.1247425079346</t>
@@ -4040,13 +4040,13 @@
     <t xml:space="preserve">26.6342430114746</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0266418457031</t>
+    <t xml:space="preserve">27.0266437530518</t>
   </si>
   <si>
     <t xml:space="preserve">26.9775924682617</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2908897399902</t>
+    <t xml:space="preserve">26.2908916473389</t>
   </si>
   <si>
     <t xml:space="preserve">26.1927909851074</t>
@@ -4055,7 +4055,7 @@
     <t xml:space="preserve">26.0456390380859</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7022876739502</t>
+    <t xml:space="preserve">25.7022895812988</t>
   </si>
   <si>
     <t xml:space="preserve">25.8984889984131</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">25.309886932373</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1627368927002</t>
+    <t xml:space="preserve">25.1627349853516</t>
   </si>
   <si>
     <t xml:space="preserve">25.0155868530273</t>
@@ -4076,13 +4076,13 @@
     <t xml:space="preserve">24.672233581543</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4269847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8383808135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3288841247559</t>
+    <t xml:space="preserve">24.4269828796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8383827209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3288822174072</t>
   </si>
   <si>
     <t xml:space="preserve">25.4570388793945</t>
@@ -4091,7 +4091,7 @@
     <t xml:space="preserve">24.5741348266602</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8193836212158</t>
+    <t xml:space="preserve">24.8193855285645</t>
   </si>
   <si>
     <t xml:space="preserve">24.3841934204102</t>
@@ -4662,6 +4662,9 @@
   </si>
   <si>
     <t xml:space="preserve">48.8499984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5999984741211</t>
   </si>
 </sst>
 </file>
@@ -70702,7 +70705,7 @@
     </row>
     <row r="2528">
       <c r="A2528" s="1" t="n">
-        <v>45999.6909953704</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2528" t="n">
         <v>24185</v>
@@ -70723,6 +70726,32 @@
         <v>1549</v>
       </c>
       <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.6910300926</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>21923</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>49.0499992370605</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>48.0999984741211</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>48.5999984741211</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>48.5999984741211</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>1550</v>
+      </c>
+      <c r="H2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="1553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="1554">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5902519226074</t>
+    <t xml:space="preserve">15.5902500152588</t>
   </si>
   <si>
     <t xml:space="preserve">DAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7186422348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2234220504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5356187820435</t>
+    <t xml:space="preserve">15.7186412811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2234230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5356168746948</t>
   </si>
   <si>
     <t xml:space="preserve">14.2146406173706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9395179748535</t>
+    <t xml:space="preserve">13.9395189285278</t>
   </si>
   <si>
     <t xml:space="preserve">14.2880077362061</t>
@@ -65,22 +65,22 @@
     <t xml:space="preserve">14.040397644043</t>
   </si>
   <si>
-    <t xml:space="preserve">13.866153717041</t>
+    <t xml:space="preserve">13.8661518096924</t>
   </si>
   <si>
     <t xml:space="preserve">13.1049823760986</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7931756973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8848838806152</t>
+    <t xml:space="preserve">12.793176651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8848848342896</t>
   </si>
   <si>
     <t xml:space="preserve">12.2887859344482</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9490804672241</t>
+    <t xml:space="preserve">12.9490795135498</t>
   </si>
   <si>
     <t xml:space="preserve">13.132493019104</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">16.0487880706787</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3239097595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0854721069336</t>
+    <t xml:space="preserve">16.3239078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0854740142822</t>
   </si>
   <si>
     <t xml:space="preserve">16.360595703125</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">17.1125946044922</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5990314483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4710321426392</t>
+    <t xml:space="preserve">16.5990333557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4710340499878</t>
   </si>
   <si>
     <t xml:space="preserve">16.1038131713867</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">15.3059606552124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9391298294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.948299407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3518142700195</t>
+    <t xml:space="preserve">14.9391288757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9483003616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3518133163452</t>
   </si>
   <si>
     <t xml:space="preserve">15.1042013168335</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">15.0033254623413</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9112243652344</t>
+    <t xml:space="preserve">15.9112281799316</t>
   </si>
   <si>
     <t xml:space="preserve">16.2322044372559</t>
@@ -140,25 +140,25 @@
     <t xml:space="preserve">16.7641086578369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9200077056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0575714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9658622741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7090797424316</t>
+    <t xml:space="preserve">16.9200115203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0575695037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9658641815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.709077835083</t>
   </si>
   <si>
     <t xml:space="preserve">16.3514213562012</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3422527313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8283042907715</t>
+    <t xml:space="preserve">16.3422508239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8283023834229</t>
   </si>
   <si>
     <t xml:space="preserve">16.6357154846191</t>
@@ -167,43 +167,43 @@
     <t xml:space="preserve">17.1767883300781</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3051795959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3693733215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4335708618164</t>
+    <t xml:space="preserve">17.3051776885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3693752288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4335670471191</t>
   </si>
   <si>
     <t xml:space="preserve">16.534839630127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2226428985596</t>
+    <t xml:space="preserve">17.2226448059082</t>
   </si>
   <si>
     <t xml:space="preserve">17.5161056518555</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8741512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2593250274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4610824584961</t>
+    <t xml:space="preserve">16.874153137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2593212127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4610843658447</t>
   </si>
   <si>
     <t xml:space="preserve">17.0117130279541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2138614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5531768798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9383506774902</t>
+    <t xml:space="preserve">16.2138595581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5531787872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9383487701416</t>
   </si>
   <si>
     <t xml:space="preserve">17.2868366241455</t>
@@ -212,10 +212,10 @@
     <t xml:space="preserve">16.5715198516846</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5256671905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1217651367188</t>
+    <t xml:space="preserve">16.5256690979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1217613220215</t>
   </si>
   <si>
     <t xml:space="preserve">17.5619583129883</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">17.8645935058594</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1122055053711</t>
+    <t xml:space="preserve">18.1122016906738</t>
   </si>
   <si>
     <t xml:space="preserve">18.0204944610596</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">17.7912273406982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5986461639404</t>
+    <t xml:space="preserve">17.5986442565918</t>
   </si>
   <si>
     <t xml:space="preserve">18.3414745330811</t>
@@ -248,76 +248,76 @@
     <t xml:space="preserve">18.405668258667</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4331798553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0938625335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3231296539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0296669006348</t>
+    <t xml:space="preserve">18.4331817626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0938606262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.323127746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0296688079834</t>
   </si>
   <si>
     <t xml:space="preserve">17.8921089172363</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4702529907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1492805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4885921478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1676158905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0759124755859</t>
+    <t xml:space="preserve">17.4702548980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1492767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4885902404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1676177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0759105682373</t>
   </si>
   <si>
     <t xml:space="preserve">16.7732753753662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8374729156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.562349319458</t>
+    <t xml:space="preserve">16.837474822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5623512268066</t>
   </si>
   <si>
     <t xml:space="preserve">16.3147392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1496658325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2505435943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7457637786865</t>
+    <t xml:space="preserve">16.1496620178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.250545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7457695007324</t>
   </si>
   <si>
     <t xml:space="preserve">16.452299118042</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4156188964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1680088043213</t>
+    <t xml:space="preserve">16.415620803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1680068969727</t>
   </si>
   <si>
     <t xml:space="preserve">17.3602046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5164966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4981555938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2409820556641</t>
+    <t xml:space="preserve">16.5164947509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4981536865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2409839630127</t>
   </si>
   <si>
     <t xml:space="preserve">16.9933757781982</t>
@@ -326,130 +326,130 @@
     <t xml:space="preserve">17.0392284393311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8103513717651</t>
+    <t xml:space="preserve">15.8103485107422</t>
   </si>
   <si>
     <t xml:space="preserve">15.8470306396484</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9574708938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7648868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0675191879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3334693908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9570808410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9849824905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4530801773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.884105682373</t>
+    <t xml:space="preserve">14.9574699401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7648878097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0675210952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3334674835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9570837020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9849815368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4530820846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8841037750244</t>
   </si>
   <si>
     <t xml:space="preserve">14.5264453887939</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6823482513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.406834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0308351516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6273241043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0037136077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2604942321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6548376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3976669311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.315131187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4985427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2509346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3242988586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2967872619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3793258666992</t>
+    <t xml:space="preserve">14.6823501586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4068355560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0308361053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6273231506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0037145614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2604932785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6548366546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.397668838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.315128326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4985437393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2509317398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3242979049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2967891693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3793239593506</t>
   </si>
   <si>
     <t xml:space="preserve">16.1404972076416</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6177625656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3884954452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1221542358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8286924362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0762996673584</t>
+    <t xml:space="preserve">15.6177635192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3884963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1221561431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8286895751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.076301574707</t>
   </si>
   <si>
     <t xml:space="preserve">16.1771755218506</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0671310424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9845914840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1401081085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8099575042725</t>
+    <t xml:space="preserve">16.0671329498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9845924377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1401062011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8099594116211</t>
   </si>
   <si>
     <t xml:space="preserve">16.6082038879395</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6448879241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.607816696167</t>
+    <t xml:space="preserve">16.6448841094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6078128814697</t>
   </si>
   <si>
     <t xml:space="preserve">17.158447265625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0300579071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1951313018799</t>
+    <t xml:space="preserve">17.0300559997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1951293945312</t>
   </si>
   <si>
     <t xml:space="preserve">17.3326892852783</t>
@@ -458,40 +458,40 @@
     <t xml:space="preserve">16.0946426391602</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7828369140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7553234100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8195199966431</t>
+    <t xml:space="preserve">15.7828378677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7553224563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8195190429688</t>
   </si>
   <si>
     <t xml:space="preserve">15.9479112625122</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6361036300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6636171340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5627374649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4893741607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6085939407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0304470062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6999092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0579586029053</t>
+    <t xml:space="preserve">15.6361064910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6636152267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5627365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893712997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6085929870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0304489135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6999073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0579605102539</t>
   </si>
   <si>
     <t xml:space="preserve">15.5352268218994</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">15.544397354126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7003021240234</t>
+    <t xml:space="preserve">15.7003030776978</t>
   </si>
   <si>
     <t xml:space="preserve">15.3609828948975</t>
@@ -509,67 +509,67 @@
     <t xml:space="preserve">15.1592273712158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.233039855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3068523406982</t>
+    <t xml:space="preserve">15.2330408096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3068513870239</t>
   </si>
   <si>
     <t xml:space="preserve">15.54674243927</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6297836303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7866344451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.519063949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9746952056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3253059387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4175710678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4083461761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0577344894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7589540481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2202777862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8235387802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3898906707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5006065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2145862579346</t>
+    <t xml:space="preserve">15.6297817230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7866353988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5190601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9746961593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.325306892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4175691604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4083433151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0577354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7589521408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2202816009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8235378265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.389892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5006084442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2145881652832</t>
   </si>
   <si>
     <t xml:space="preserve">15.7774066925049</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9434833526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.731273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4693965911865</t>
+    <t xml:space="preserve">15.9434852600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7312726974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4693984985352</t>
   </si>
   <si>
     <t xml:space="preserve">17.0691261291504</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">17.142936706543</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0229911804199</t>
+    <t xml:space="preserve">17.0229930877686</t>
   </si>
   <si>
     <t xml:space="preserve">17.1060314178467</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">16.9122714996338</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8384609222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3771343231201</t>
+    <t xml:space="preserve">16.8384628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3771324157715</t>
   </si>
   <si>
     <t xml:space="preserve">16.9768581390381</t>
@@ -599,25 +599,25 @@
     <t xml:space="preserve">16.792329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0506706237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6227149963379</t>
+    <t xml:space="preserve">17.0506725311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6227169036865</t>
   </si>
   <si>
     <t xml:space="preserve">17.7795696258545</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8164768218994</t>
+    <t xml:space="preserve">17.8164749145508</t>
   </si>
   <si>
     <t xml:space="preserve">17.7611141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3054847717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7760372161865</t>
+    <t xml:space="preserve">18.3054790496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7760391235352</t>
   </si>
   <si>
     <t xml:space="preserve">18.8221702575684</t>
@@ -626,91 +626,91 @@
     <t xml:space="preserve">19.421895980835</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4957103729248</t>
+    <t xml:space="preserve">19.4957065582275</t>
   </si>
   <si>
     <t xml:space="preserve">18.9882488250732</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7852611541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3296318054199</t>
+    <t xml:space="preserve">18.7852649688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3296279907227</t>
   </si>
   <si>
     <t xml:space="preserve">19.2004566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0528316497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9513416290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7299041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8867530822754</t>
+    <t xml:space="preserve">19.0528335571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.951343536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7299060821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8867588043213</t>
   </si>
   <si>
     <t xml:space="preserve">18.8129405975342</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8037147521973</t>
+    <t xml:space="preserve">18.8037166595459</t>
   </si>
   <si>
     <t xml:space="preserve">18.6284141540527</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4531078338623</t>
+    <t xml:space="preserve">18.4531059265137</t>
   </si>
   <si>
     <t xml:space="preserve">18.2778015136719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9917774200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3331642150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4069747924805</t>
+    <t xml:space="preserve">17.9917793273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3331604003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4069766998291</t>
   </si>
   <si>
     <t xml:space="preserve">18.3423862457275</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2501220703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.36083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1578578948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2039890289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.388521194458</t>
+    <t xml:space="preserve">18.2501201629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3608417510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1578559875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.203987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3885192871094</t>
   </si>
   <si>
     <t xml:space="preserve">18.49001121521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4992408752441</t>
+    <t xml:space="preserve">18.4992389678955</t>
   </si>
   <si>
     <t xml:space="preserve">18.6007328033447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.914436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2834968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9605655670166</t>
+    <t xml:space="preserve">18.9144344329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2834987640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9605693817139</t>
   </si>
   <si>
     <t xml:space="preserve">18.9974727630615</t>
@@ -731,37 +731,37 @@
     <t xml:space="preserve">19.3757629394531</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9697914123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0897407531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2189083099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9052066802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0989665985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2558174133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1543273925781</t>
+    <t xml:space="preserve">18.9697952270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0897388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2189102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9052085876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0989646911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2558193206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1543254852295</t>
   </si>
   <si>
     <t xml:space="preserve">19.7817325592041</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8739986419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2430553436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4829483032227</t>
+    <t xml:space="preserve">19.8739967346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2430572509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4829502105713</t>
   </si>
   <si>
     <t xml:space="preserve">20.7136154174805</t>
@@ -773,28 +773,28 @@
     <t xml:space="preserve">20.8058776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0123958587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4737243652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2522850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1138858795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4368152618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.510627746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4644947052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3630046844482</t>
+    <t xml:space="preserve">20.0123977661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4737205505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2522830963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.113883972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4368133544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5106296539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4644966125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3630027770996</t>
   </si>
   <si>
     <t xml:space="preserve">20.390682220459</t>
@@ -803,25 +803,25 @@
     <t xml:space="preserve">20.5198554992676</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3445472717285</t>
+    <t xml:space="preserve">20.3445510864258</t>
   </si>
   <si>
     <t xml:space="preserve">20.6767063140869</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7228374481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3168716430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6398029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4978713989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3502445220947</t>
+    <t xml:space="preserve">20.7228393554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.316873550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6398010253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4978694915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3502426147461</t>
   </si>
   <si>
     <t xml:space="preserve">21.2210750579834</t>
@@ -830,49 +830,49 @@
     <t xml:space="preserve">21.1749420166016</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9904117584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9811820983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7874279022217</t>
+    <t xml:space="preserve">20.9904098510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.98118019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.787425994873</t>
   </si>
   <si>
     <t xml:space="preserve">21.1288070678711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9627323150635</t>
+    <t xml:space="preserve">20.9627285003662</t>
   </si>
   <si>
     <t xml:space="preserve">21.2026195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0826759338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5013999938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0273170471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8151054382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.971960067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1011276245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1933898925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.138032913208</t>
+    <t xml:space="preserve">21.0826740264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5014038085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0273151397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8151035308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9719562530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1103534698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1011257171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.193395614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1380348205566</t>
   </si>
   <si>
     <t xml:space="preserve">20.7966537475586</t>
@@ -884,40 +884,40 @@
     <t xml:space="preserve">20.5936660766602</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1784744262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2615089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2707386016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1876964569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4921741485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.141565322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9109039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0769786834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6617832183838</t>
+    <t xml:space="preserve">20.1784763336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.261510848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2707347869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1876983642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4921760559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1415634155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9109020233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0769805908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6617851257324</t>
   </si>
   <si>
     <t xml:space="preserve">19.7725067138672</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1323394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1600170135498</t>
+    <t xml:space="preserve">20.1323413848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1600189208984</t>
   </si>
   <si>
     <t xml:space="preserve">20.4091377258301</t>
@@ -932,37 +932,37 @@
     <t xml:space="preserve">19.6986923217773</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7540493011475</t>
+    <t xml:space="preserve">19.7540512084961</t>
   </si>
   <si>
     <t xml:space="preserve">19.5879726409912</t>
   </si>
   <si>
-    <t xml:space="preserve">19.790958404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9385852813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8647708892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9754886627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.541841506958</t>
+    <t xml:space="preserve">19.7909603118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9385814666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8647689819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9754867553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5418395996094</t>
   </si>
   <si>
     <t xml:space="preserve">20.5290851593018</t>
   </si>
   <si>
-    <t xml:space="preserve">20.104663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8370876312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5972003936768</t>
+    <t xml:space="preserve">20.1046600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8370895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5971984863281</t>
   </si>
   <si>
     <t xml:space="preserve">20.2799644470215</t>
@@ -977,22 +977,22 @@
     <t xml:space="preserve">20.7043857574463</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2061500549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4275894165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7505168914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0549964904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5844402313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3353233337402</t>
+    <t xml:space="preserve">20.206148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4275913238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7505207061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0549945831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5844421386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3353271484375</t>
   </si>
   <si>
     <t xml:space="preserve">20.1969261169434</t>
@@ -1001,37 +1001,37 @@
     <t xml:space="preserve">20.2338333129883</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7448234558105</t>
+    <t xml:space="preserve">19.7448253631592</t>
   </si>
   <si>
     <t xml:space="preserve">19.7079181671143</t>
   </si>
   <si>
-    <t xml:space="preserve">19.634105682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8463172912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9570350646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3814601898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8555431365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4034404754639</t>
+    <t xml:space="preserve">19.6341075897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8463191986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9570331573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3814582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8555450439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4034423828125</t>
   </si>
   <si>
     <t xml:space="preserve">19.1266441345215</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6560916900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7114505767822</t>
+    <t xml:space="preserve">18.6560897827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7114524841309</t>
   </si>
   <si>
     <t xml:space="preserve">18.5084648132324</t>
@@ -1040,13 +1040,13 @@
     <t xml:space="preserve">18.8683013916016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5546016693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4346523284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5361461639404</t>
+    <t xml:space="preserve">18.5545997619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4346504211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5361442565918</t>
   </si>
   <si>
     <t xml:space="preserve">18.3147087097168</t>
@@ -1055,22 +1055,22 @@
     <t xml:space="preserve">18.6837711334229</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0067024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.849760055542</t>
+    <t xml:space="preserve">19.0067005157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8497581481934</t>
   </si>
   <si>
     <t xml:space="preserve">18.8219413757324</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4047069549561</t>
+    <t xml:space="preserve">18.4047050476074</t>
   </si>
   <si>
     <t xml:space="preserve">18.1821823120117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7834911346436</t>
+    <t xml:space="preserve">17.7834892272949</t>
   </si>
   <si>
     <t xml:space="preserve">17.7278594970703</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">17.5238780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5516948699951</t>
+    <t xml:space="preserve">17.5516929626465</t>
   </si>
   <si>
     <t xml:space="preserve">17.82057762146</t>
@@ -1091,34 +1091,34 @@
     <t xml:space="preserve">17.8483924865723</t>
   </si>
   <si>
-    <t xml:space="preserve">18.145092010498</t>
+    <t xml:space="preserve">18.1450958251953</t>
   </si>
   <si>
     <t xml:space="preserve">18.3398017883301</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4603404998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2841701507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0431041717529</t>
+    <t xml:space="preserve">18.4603366851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2841682434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0431022644043</t>
   </si>
   <si>
     <t xml:space="preserve">18.367618560791</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2378120422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0987319946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5437870025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6457786560059</t>
+    <t xml:space="preserve">18.237813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0987339019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5437831878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6457767486572</t>
   </si>
   <si>
     <t xml:space="preserve">18.5716018676758</t>
@@ -1127,52 +1127,52 @@
     <t xml:space="preserve">18.5623302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">18.488151550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2285423278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2563591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3212585449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3583488464355</t>
+    <t xml:space="preserve">18.4881553649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2285385131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2563571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3212623596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3583469390869</t>
   </si>
   <si>
     <t xml:space="preserve">18.3490772247314</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5345134735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5808734893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4696102142334</t>
+    <t xml:space="preserve">18.5345153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5808753967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.469612121582</t>
   </si>
   <si>
     <t xml:space="preserve">18.2656288146973</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3768920898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7755832672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0537376403809</t>
+    <t xml:space="preserve">18.3768939971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7755813598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0537395477295</t>
   </si>
   <si>
     <t xml:space="preserve">19.3318958282471</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6100521087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3981609344482</t>
+    <t xml:space="preserve">19.6100559234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3981628417969</t>
   </si>
   <si>
     <t xml:space="preserve">21.1399154663086</t>
@@ -1181,88 +1181,88 @@
     <t xml:space="preserve">21.4180717468262</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3717136383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2326316833496</t>
+    <t xml:space="preserve">21.371711730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2326354980469</t>
   </si>
   <si>
     <t xml:space="preserve">21.4644336700439</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3253555297852</t>
+    <t xml:space="preserve">21.3253517150879</t>
   </si>
   <si>
     <t xml:space="preserve">21.6035099029541</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6498718261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.861759185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3054447174072</t>
+    <t xml:space="preserve">21.6498699188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8617572784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3054466247559</t>
   </si>
   <si>
     <t xml:space="preserve">20.9081172943115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4908847808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6299610137939</t>
+    <t xml:space="preserve">20.4908809661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6299591064453</t>
   </si>
   <si>
     <t xml:space="preserve">20.5836009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9544792175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0471954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0008373260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7226791381836</t>
+    <t xml:space="preserve">20.954475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0471973419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0008354187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7226829528809</t>
   </si>
   <si>
     <t xml:space="preserve">20.5372428894043</t>
   </si>
   <si>
-    <t xml:space="preserve">21.557149887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0671005249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7425880432129</t>
+    <t xml:space="preserve">21.5571517944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.067102432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7425899505615</t>
   </si>
   <si>
     <t xml:space="preserve">21.9280242919922</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8353080749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6763229370117</t>
+    <t xml:space="preserve">21.8353099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6763210296631</t>
   </si>
   <si>
     <t xml:space="preserve">21.0935554504395</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1663684844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0736484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7690372467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4445190429688</t>
+    <t xml:space="preserve">20.1663665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0736465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7690391540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.444522857666</t>
   </si>
   <si>
     <t xml:space="preserve">20.8153991699219</t>
@@ -1271,13 +1271,13 @@
     <t xml:space="preserve">21.1862735748291</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2590866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3518047332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9809322357178</t>
+    <t xml:space="preserve">20.2590827941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.351806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9809284210205</t>
   </si>
   <si>
     <t xml:space="preserve">18.9146614074707</t>
@@ -1289,10 +1289,10 @@
     <t xml:space="preserve">19.1928176879883</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6564159393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4709720611572</t>
+    <t xml:space="preserve">19.6564121246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4709739685059</t>
   </si>
   <si>
     <t xml:space="preserve">20.2127246856689</t>
@@ -1301,13 +1301,13 @@
     <t xml:space="preserve">20.1200084686279</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8418521881104</t>
+    <t xml:space="preserve">19.8418483734131</t>
   </si>
   <si>
     <t xml:space="preserve">20.0272884368896</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8882102966309</t>
+    <t xml:space="preserve">19.8882122039795</t>
   </si>
   <si>
     <t xml:space="preserve">19.7491321563721</t>
@@ -1319,94 +1319,94 @@
     <t xml:space="preserve">19.2855358123779</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4246139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3782558441162</t>
+    <t xml:space="preserve">19.4246158599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3782577514648</t>
   </si>
   <si>
     <t xml:space="preserve">19.5173320770264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5636920928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1464576721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1000995635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2391777038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7027721405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2789974212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9345703125</t>
+    <t xml:space="preserve">19.5636901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1464557647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.10009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2391757965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7027702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.278995513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9345684051514</t>
   </si>
   <si>
     <t xml:space="preserve">17.598051071167</t>
   </si>
   <si>
-    <t xml:space="preserve">15.205904006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5953235626221</t>
+    <t xml:space="preserve">15.2059030532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5953254699707</t>
   </si>
   <si>
     <t xml:space="preserve">14.6681346893311</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3714332580566</t>
+    <t xml:space="preserve">14.3714323043823</t>
   </si>
   <si>
     <t xml:space="preserve">14.7052211761475</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2986211776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5211486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8920202255249</t>
+    <t xml:space="preserve">15.2986221313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5211458206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8920230865479</t>
   </si>
   <si>
     <t xml:space="preserve">15.428430557251</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2244491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3542537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7622213363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6880416870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5582361221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4840602874756</t>
+    <t xml:space="preserve">15.2244482040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3542528152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7622184753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.688042640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5582332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4840612411499</t>
   </si>
   <si>
     <t xml:space="preserve">15.2800798416138</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9092025756836</t>
+    <t xml:space="preserve">14.9092016220093</t>
   </si>
   <si>
     <t xml:space="preserve">14.7599248886108</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4800291061401</t>
+    <t xml:space="preserve">14.4800281524658</t>
   </si>
   <si>
     <t xml:space="preserve">14.3120889663696</t>
@@ -1415,25 +1415,25 @@
     <t xml:space="preserve">14.3494091033936</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8159046173096</t>
+    <t xml:space="preserve">14.8159036636353</t>
   </si>
   <si>
     <t xml:space="preserve">14.8345632553101</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5546674728394</t>
+    <t xml:space="preserve">14.554666519165</t>
   </si>
   <si>
     <t xml:space="preserve">15.0398225784302</t>
   </si>
   <si>
-    <t xml:space="preserve">15.33837890625</t>
+    <t xml:space="preserve">15.3383817672729</t>
   </si>
   <si>
     <t xml:space="preserve">15.1704416275024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9762105941772</t>
+    <t xml:space="preserve">13.9762115478516</t>
   </si>
   <si>
     <t xml:space="preserve">13.8269338607788</t>
@@ -1448,13 +1448,13 @@
     <t xml:space="preserve">14.2374496459961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0695104598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0508518218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1254920959473</t>
+    <t xml:space="preserve">14.0695114135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0508508682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1254911422729</t>
   </si>
   <si>
     <t xml:space="preserve">13.8642530441284</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">13.5470361709595</t>
   </si>
   <si>
-    <t xml:space="preserve">13.528374671936</t>
+    <t xml:space="preserve">13.5283765792847</t>
   </si>
   <si>
     <t xml:space="preserve">13.6963157653809</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">13.9575519561768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1068315505981</t>
+    <t xml:space="preserve">14.1068305969238</t>
   </si>
   <si>
     <t xml:space="preserve">14.4240474700928</t>
@@ -1481,13 +1481,13 @@
     <t xml:space="preserve">14.6479663848877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.114462852478</t>
+    <t xml:space="preserve">15.1144618988037</t>
   </si>
   <si>
     <t xml:space="preserve">15.0211629867554</t>
   </si>
   <si>
-    <t xml:space="preserve">14.927864074707</t>
+    <t xml:space="preserve">14.9278631210327</t>
   </si>
   <si>
     <t xml:space="preserve">14.965184211731</t>
@@ -1496,31 +1496,31 @@
     <t xml:space="preserve">14.7972431182861</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0025033950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0584812164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0958023071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4316806793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8608570098877</t>
+    <t xml:space="preserve">15.0025024414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0584802627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0958032608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.431679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8608541488647</t>
   </si>
   <si>
     <t xml:space="preserve">16.7005481719971</t>
   </si>
   <si>
-    <t xml:space="preserve">16.775182723999</t>
+    <t xml:space="preserve">16.7751846313477</t>
   </si>
   <si>
     <t xml:space="preserve">16.7938461303711</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3833293914795</t>
+    <t xml:space="preserve">16.3833274841309</t>
   </si>
   <si>
     <t xml:space="preserve">16.3086910247803</t>
@@ -1529,25 +1529,25 @@
     <t xml:space="preserve">16.1594123840332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2527122497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8795146942139</t>
+    <t xml:space="preserve">16.2527103424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8795137405396</t>
   </si>
   <si>
     <t xml:space="preserve">15.7675561904907</t>
   </si>
   <si>
-    <t xml:space="preserve">15.711576461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0287952423096</t>
+    <t xml:space="preserve">15.7115755081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0287933349609</t>
   </si>
   <si>
     <t xml:space="preserve">16.0474529266357</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1407508850098</t>
+    <t xml:space="preserve">16.1407527923584</t>
   </si>
   <si>
     <t xml:space="preserve">16.5139503479004</t>
@@ -1559,25 +1559,25 @@
     <t xml:space="preserve">16.178071975708</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3273525238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3460102081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1220932006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4952907562256</t>
+    <t xml:space="preserve">16.3273506164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3460083007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1220951080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.495288848877</t>
   </si>
   <si>
     <t xml:space="preserve">16.6072483062744</t>
   </si>
   <si>
-    <t xml:space="preserve">16.364673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2153930664062</t>
+    <t xml:space="preserve">16.3646697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2153911590576</t>
   </si>
   <si>
     <t xml:space="preserve">15.7488946914673</t>
@@ -1586,106 +1586,106 @@
     <t xml:space="preserve">15.8421945571899</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8235349655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0101356506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8981742858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2340488433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2900295257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4206485748291</t>
+    <t xml:space="preserve">15.8235340118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0101337432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8981771469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2340507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2900314331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4206504821777</t>
   </si>
   <si>
     <t xml:space="preserve">16.6632289886475</t>
   </si>
   <si>
-    <t xml:space="preserve">16.831169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3536415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1560153961182</t>
+    <t xml:space="preserve">16.8311653137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3536434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1560134887695</t>
   </si>
   <si>
     <t xml:space="preserve">18.137357711792</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1186943054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9880790710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4096202850342</t>
+    <t xml:space="preserve">18.1186923980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9880771636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4096221923828</t>
   </si>
   <si>
     <t xml:space="preserve">17.0177631378174</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8871459960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8684864044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.625904083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5326080322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8498268127441</t>
+    <t xml:space="preserve">16.8871440887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8684844970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6259078979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5326061248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8498249053955</t>
   </si>
   <si>
     <t xml:space="preserve">16.7192058563232</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9431247711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0364265441895</t>
+    <t xml:space="preserve">16.9431228637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0364246368408</t>
   </si>
   <si>
     <t xml:space="preserve">17.11106300354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.644567489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1034336090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3943576812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4130191802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3570384979248</t>
+    <t xml:space="preserve">16.6445693969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1034297943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3943586349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4130182266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3570394515991</t>
   </si>
   <si>
     <t xml:space="preserve">15.0771417617798</t>
   </si>
   <si>
-    <t xml:space="preserve">14.591986656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7039451599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9838418960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6666269302368</t>
+    <t xml:space="preserve">14.5919876098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7039470672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9838428497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6666259765625</t>
   </si>
   <si>
     <t xml:space="preserve">14.871883392334</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">14.741265296936</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4053888320923</t>
+    <t xml:space="preserve">14.405387878418</t>
   </si>
   <si>
     <t xml:space="preserve">14.5733270645142</t>
   </si>
   <si>
-    <t xml:space="preserve">14.27476978302</t>
+    <t xml:space="preserve">14.2747688293457</t>
   </si>
   <si>
     <t xml:space="preserve">14.7226047515869</t>
@@ -1709,13 +1709,13 @@
     <t xml:space="preserve">14.4613676071167</t>
   </si>
   <si>
-    <t xml:space="preserve">14.368067741394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5360069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4689998626709</t>
+    <t xml:space="preserve">14.3680686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5360059738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4689970016479</t>
   </si>
   <si>
     <t xml:space="preserve">15.3010597229004</t>
@@ -1736,106 +1736,106 @@
     <t xml:space="preserve">15.3197212219238</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2264184951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9465236663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.77858543396</t>
+    <t xml:space="preserve">15.2264175415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9465246200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7785844802856</t>
   </si>
   <si>
     <t xml:space="preserve">14.4427070617676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.685284614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173473358154</t>
+    <t xml:space="preserve">14.6852855682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173463821411</t>
   </si>
   <si>
     <t xml:space="preserve">14.2001314163208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1814699172974</t>
+    <t xml:space="preserve">14.181468963623</t>
   </si>
   <si>
     <t xml:space="preserve">13.9948711395264</t>
   </si>
   <si>
-    <t xml:space="preserve">13.808274269104</t>
+    <t xml:space="preserve">13.8082733154297</t>
   </si>
   <si>
     <t xml:space="preserve">13.6776542663574</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3307476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1628103256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7149744033813</t>
+    <t xml:space="preserve">14.3307485580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1628093719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7149753570557</t>
   </si>
   <si>
     <t xml:space="preserve">13.7522945404053</t>
   </si>
   <si>
-    <t xml:space="preserve">13.938892364502</t>
+    <t xml:space="preserve">13.9388914108276</t>
   </si>
   <si>
     <t xml:space="preserve">13.8455944061279</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1441488265991</t>
+    <t xml:space="preserve">14.1441497802734</t>
   </si>
   <si>
     <t xml:space="preserve">13.9202327728271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4986877441406</t>
+    <t xml:space="preserve">14.4986867904663</t>
   </si>
   <si>
     <t xml:space="preserve">13.901572227478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2637405395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.088171005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0135326385498</t>
+    <t xml:space="preserve">15.2637395858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0881719589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0135316848755</t>
   </si>
   <si>
     <t xml:space="preserve">14.3867282867432</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8905439376831</t>
+    <t xml:space="preserve">14.8905420303345</t>
   </si>
   <si>
     <t xml:space="preserve">15.1891012191772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9740734100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9552392959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8045568466187</t>
+    <t xml:space="preserve">14.9740724563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9552383422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8045558929443</t>
   </si>
   <si>
     <t xml:space="preserve">14.7103796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">14.785719871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2754392623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5768032073975</t>
+    <t xml:space="preserve">14.7857208251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2754383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5768051147461</t>
   </si>
   <si>
     <t xml:space="preserve">16.3490505218506</t>
@@ -1844,13 +1844,13 @@
     <t xml:space="preserve">16.2172050476074</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5956382751465</t>
+    <t xml:space="preserve">15.5956373214722</t>
   </si>
   <si>
     <t xml:space="preserve">15.5579681396484</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4261207580566</t>
+    <t xml:space="preserve">15.4261198043823</t>
   </si>
   <si>
     <t xml:space="preserve">15.44495677948</t>
@@ -1862,25 +1862,25 @@
     <t xml:space="preserve">15.6521472930908</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6898164749146</t>
+    <t xml:space="preserve">15.6898155212402</t>
   </si>
   <si>
     <t xml:space="preserve">16.0665225982666</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6144742965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5014629364014</t>
+    <t xml:space="preserve">15.6144723892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5014619827271</t>
   </si>
   <si>
     <t xml:space="preserve">15.5391330718994</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9346742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8781700134277</t>
+    <t xml:space="preserve">15.9346733093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8781709671021</t>
   </si>
   <si>
     <t xml:space="preserve">15.3131103515625</t>
@@ -1889,22 +1889,22 @@
     <t xml:space="preserve">15.7274866104126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.463791847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3319463729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4826278686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1435918807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0117435455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8798980712891</t>
+    <t xml:space="preserve">15.4637928009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3319454193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4826288223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.143590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0117444992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8798971176147</t>
   </si>
   <si>
     <t xml:space="preserve">15.1059226989746</t>
@@ -1913,187 +1913,187 @@
     <t xml:space="preserve">14.6538724899292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8422260284424</t>
+    <t xml:space="preserve">14.842227935791</t>
   </si>
   <si>
     <t xml:space="preserve">14.4090147018433</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9381332397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8439540863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1264848709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5031900405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6915454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4843549728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2960033416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3336725234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.522027015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2394971847534</t>
+    <t xml:space="preserve">13.9381313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.843955039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1264839172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5031909942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6915445327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4843559265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2960014343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3336744308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5220260620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2394962310791</t>
   </si>
   <si>
     <t xml:space="preserve">14.1829900741577</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9569664001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5990962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0528717041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9210252761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2788972854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9963665008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7138357162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3371305465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0922727584839</t>
+    <t xml:space="preserve">13.9569673538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5990953445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0528707504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9210262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2788963317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9963674545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7138366699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3371295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0922718048096</t>
   </si>
   <si>
     <t xml:space="preserve">11.8662481307983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3953657150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9621534347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0580577850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88853931427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53066825866699</t>
+    <t xml:space="preserve">11.3953647613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9621524810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0580568313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88854026794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53066921234131</t>
   </si>
   <si>
     <t xml:space="preserve">8.8525972366333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35173320770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0426778793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49472713470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0409517288208</t>
+    <t xml:space="preserve">9.35173416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04267883300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49472618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04094982147217</t>
   </si>
   <si>
     <t xml:space="preserve">10.0957279205322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6796226501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8474130630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8080129623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5272121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8868112564087</t>
+    <t xml:space="preserve">10.6796236038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.847412109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.808012008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5272130966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8868103027344</t>
   </si>
   <si>
     <t xml:space="preserve">10.8491411209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5666122436523</t>
+    <t xml:space="preserve">10.566611289978</t>
   </si>
   <si>
     <t xml:space="preserve">10.0015516281128</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2652444839478</t>
+    <t xml:space="preserve">10.2652454376221</t>
   </si>
   <si>
     <t xml:space="preserve">10.5477752685547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6607866287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0374946594238</t>
+    <t xml:space="preserve">10.6607875823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0374937057495</t>
   </si>
   <si>
     <t xml:space="preserve">10.8303050994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5101051330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1333990097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81319808959961</t>
+    <t xml:space="preserve">10.5101041793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.133397102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81319713592529</t>
   </si>
   <si>
     <t xml:space="preserve">10.1522331237793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4347639083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3594226837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6984577178955</t>
+    <t xml:space="preserve">10.4347629547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3594217300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6984567642212</t>
   </si>
   <si>
     <t xml:space="preserve">10.6419525146484</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6231155395508</t>
+    <t xml:space="preserve">10.6231164932251</t>
   </si>
   <si>
     <t xml:space="preserve">10.7361288070679</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7549629211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.47243309021</t>
+    <t xml:space="preserve">10.7549648284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4724340438843</t>
   </si>
   <si>
     <t xml:space="preserve">10.9244813919067</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8679761886597</t>
+    <t xml:space="preserve">10.8679752349854</t>
   </si>
   <si>
     <t xml:space="preserve">11.4141998291016</t>
@@ -2102,16 +2102,16 @@
     <t xml:space="preserve">11.4895401000977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9809865951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3388595581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4330339431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7155656814575</t>
+    <t xml:space="preserve">10.9809875488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3388586044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4330358505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7155647277832</t>
   </si>
   <si>
     <t xml:space="preserve">11.9227533340454</t>
@@ -2120,16 +2120,16 @@
     <t xml:space="preserve">12.205283164978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1299409866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0169296264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7720699310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1505060195923</t>
+    <t xml:space="preserve">12.1299419403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0169286727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7720718383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.150505065918</t>
   </si>
   <si>
     <t xml:space="preserve">10.9433164596558</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">11.1128349304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0186576843262</t>
+    <t xml:space="preserve">11.0186586380005</t>
   </si>
   <si>
     <t xml:space="preserve">10.811469078064</t>
@@ -2147,52 +2147,52 @@
     <t xml:space="preserve">10.7172927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6042804718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3405857086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3782596588135</t>
+    <t xml:space="preserve">10.6042814254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3405866622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3782587051392</t>
   </si>
   <si>
     <t xml:space="preserve">10.5854454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1316690444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2635173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2070112228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9998226165771</t>
+    <t xml:space="preserve">11.1316699981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2635164260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.207010269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9998235702515</t>
   </si>
   <si>
     <t xml:space="preserve">10.9056463241577</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5289402008057</t>
+    <t xml:space="preserve">10.5289392471313</t>
   </si>
   <si>
     <t xml:space="preserve">10.3029165267944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3970928192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5648822784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3576927185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6025514602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4518699645996</t>
+    <t xml:space="preserve">10.3970937728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5648813247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3576946258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6025533676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4518709182739</t>
   </si>
   <si>
     <t xml:space="preserve">11.546046257019</t>
@@ -2201,16 +2201,16 @@
     <t xml:space="preserve">11.4707059860229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5837182998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6590585708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1487770080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0546007156372</t>
+    <t xml:space="preserve">11.5837173461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6590576171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.148777961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0545997619629</t>
   </si>
   <si>
     <t xml:space="preserve">12.0357646942139</t>
@@ -2225,16 +2225,16 @@
     <t xml:space="preserve">11.7343997955322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6778936386108</t>
+    <t xml:space="preserve">11.6778926849365</t>
   </si>
   <si>
     <t xml:space="preserve">11.169340133667</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5631542205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5614261627197</t>
+    <t xml:space="preserve">12.5631551742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5614252090454</t>
   </si>
   <si>
     <t xml:space="preserve">13.2977304458618</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">13.7686138153076</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5049209594727</t>
+    <t xml:space="preserve">13.5049200057983</t>
   </si>
   <si>
     <t xml:space="preserve">13.147047996521</t>
@@ -2255,52 +2255,52 @@
     <t xml:space="preserve">13.3730716705322</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0152006149292</t>
+    <t xml:space="preserve">13.0152015686035</t>
   </si>
   <si>
     <t xml:space="preserve">13.2412252426147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0323066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6367654800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3165655136108</t>
+    <t xml:space="preserve">14.0323076248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6367664337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3165674209595</t>
   </si>
   <si>
     <t xml:space="preserve">13.0340375900269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3919076919556</t>
+    <t xml:space="preserve">13.3919086456299</t>
   </si>
   <si>
     <t xml:space="preserve">13.0905427932739</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9415884017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9792604446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2429523468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3559656143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7703418731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7326726913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9586944580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2223901748657</t>
+    <t xml:space="preserve">11.9415874481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9792594909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2429542541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3559646606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7703428268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7326717376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9586954116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.22239112854</t>
   </si>
   <si>
     <t xml:space="preserve">13.3542375564575</t>
@@ -2309,10 +2309,10 @@
     <t xml:space="preserve">13.467248916626</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5260181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5450410842896</t>
+    <t xml:space="preserve">13.5260190963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5450420379639</t>
   </si>
   <si>
     <t xml:space="preserve">13.3167543411255</t>
@@ -2321,19 +2321,19 @@
     <t xml:space="preserve">13.3548040390015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2216339111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4118757247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7543039321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7923526763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6591854095459</t>
+    <t xml:space="preserve">13.2216348648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4118747711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7543058395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7923536300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6591835021973</t>
   </si>
   <si>
     <t xml:space="preserve">14.077712059021</t>
@@ -2345,10 +2345,10 @@
     <t xml:space="preserve">14.1157608032227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8874731063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6021146774292</t>
+    <t xml:space="preserve">13.88747215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6021137237549</t>
   </si>
   <si>
     <t xml:space="preserve">13.3738269805908</t>
@@ -2357,28 +2357,28 @@
     <t xml:space="preserve">13.6782093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5069942474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4499225616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6972322463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6211385726929</t>
+    <t xml:space="preserve">13.5069932937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4499235153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6972332000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6211376190186</t>
   </si>
   <si>
     <t xml:space="preserve">13.7733287811279</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0396642684937</t>
+    <t xml:space="preserve">14.0396633148193</t>
   </si>
   <si>
     <t xml:space="preserve">14.248927116394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6103820800781</t>
+    <t xml:space="preserve">14.6103811264038</t>
   </si>
   <si>
     <t xml:space="preserve">14.5342864990234</t>
@@ -2390,40 +2390,40 @@
     <t xml:space="preserve">14.9337892532349</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3796062469482</t>
+    <t xml:space="preserve">16.3796081542969</t>
   </si>
   <si>
     <t xml:space="preserve">16.2274169921875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0752277374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7137680053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8469390869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6947469711304</t>
+    <t xml:space="preserve">16.0752258300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7137699127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8469381332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6947460174561</t>
   </si>
   <si>
     <t xml:space="preserve">15.5045070648193</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2191476821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6376752853394</t>
+    <t xml:space="preserve">15.2191486358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6376762390137</t>
   </si>
   <si>
     <t xml:space="preserve">15.2381734848022</t>
   </si>
   <si>
-    <t xml:space="preserve">15.333291053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.61865234375</t>
+    <t xml:space="preserve">15.3332920074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6186513900757</t>
   </si>
   <si>
     <t xml:space="preserve">15.7518167495728</t>
@@ -2438,28 +2438,28 @@
     <t xml:space="preserve">16.664966583252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5698490142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5318012237549</t>
+    <t xml:space="preserve">16.5698471069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5317993164062</t>
   </si>
   <si>
     <t xml:space="preserve">16.6078968048096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5888710021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.045446395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.026424407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0834922790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8742294311523</t>
+    <t xml:space="preserve">16.5888729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0454444885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0264225006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0834941864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8742275238037</t>
   </si>
   <si>
     <t xml:space="preserve">16.3415603637695</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">16.3225364685059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7981338500977</t>
+    <t xml:space="preserve">16.7981357574463</t>
   </si>
   <si>
     <t xml:space="preserve">16.5508232116699</t>
@@ -2477,28 +2477,28 @@
     <t xml:space="preserve">16.8361835479736</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8171615600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7410640716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8444499969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9585952758789</t>
+    <t xml:space="preserve">16.8171577453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7410621643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8444519042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9585933685303</t>
   </si>
   <si>
     <t xml:space="preserve">18.186882019043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4995346069336</t>
+    <t xml:space="preserve">19.4995307922363</t>
   </si>
   <si>
     <t xml:space="preserve">19.78489112854</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1653728485107</t>
+    <t xml:space="preserve">20.1653709411621</t>
   </si>
   <si>
     <t xml:space="preserve">19.6422119140625</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">20.3556098937988</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9751300811768</t>
+    <t xml:space="preserve">19.975133895874</t>
   </si>
   <si>
     <t xml:space="preserve">19.8324527740479</t>
@@ -2519,31 +2519,31 @@
     <t xml:space="preserve">19.7373332977295</t>
   </si>
   <si>
-    <t xml:space="preserve">19.880012512207</t>
+    <t xml:space="preserve">19.8800144195557</t>
   </si>
   <si>
     <t xml:space="preserve">20.2604904174805</t>
   </si>
   <si>
-    <t xml:space="preserve">20.403169631958</t>
+    <t xml:space="preserve">20.4031734466553</t>
   </si>
   <si>
     <t xml:space="preserve">20.4982891082764</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8312091827393</t>
+    <t xml:space="preserve">20.8312110900879</t>
   </si>
   <si>
     <t xml:space="preserve">20.7360897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2129325866699</t>
+    <t xml:space="preserve">20.2129306793213</t>
   </si>
   <si>
     <t xml:space="preserve">19.9275722503662</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7836494445801</t>
+    <t xml:space="preserve">20.7836475372314</t>
   </si>
   <si>
     <t xml:space="preserve">19.594654083252</t>
@@ -2552,10 +2552,10 @@
     <t xml:space="preserve">19.3568553924561</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2141761779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4044132232666</t>
+    <t xml:space="preserve">19.2141742706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4044151306152</t>
   </si>
   <si>
     <t xml:space="preserve">19.6897735595703</t>
@@ -2564,10 +2564,10 @@
     <t xml:space="preserve">19.0239334106445</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1178112030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3080501556396</t>
+    <t xml:space="preserve">20.1178131103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3080520629883</t>
   </si>
   <si>
     <t xml:space="preserve">20.0702495574951</t>
@@ -2576,13 +2576,13 @@
     <t xml:space="preserve">20.9738883972168</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5446033477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1641292572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6397266387939</t>
+    <t xml:space="preserve">21.544605255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1641273498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6397247314453</t>
   </si>
   <si>
     <t xml:space="preserve">21.5921669006348</t>
@@ -2597,13 +2597,13 @@
     <t xml:space="preserve">21.7348461151123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8299655914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0690097808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2116889953613</t>
+    <t xml:space="preserve">21.8299674987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0690078735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2116870880127</t>
   </si>
   <si>
     <t xml:space="preserve">21.3068065643311</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">22.1628837585449</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6384830474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1616401672363</t>
+    <t xml:space="preserve">22.6384811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.161642074585</t>
   </si>
   <si>
     <t xml:space="preserve">22.4958019256592</t>
@@ -2624,13 +2624,13 @@
     <t xml:space="preserve">22.2580051422119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8775234222412</t>
+    <t xml:space="preserve">21.8775253295898</t>
   </si>
   <si>
     <t xml:space="preserve">21.4970474243164</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2592468261719</t>
+    <t xml:space="preserve">21.2592506408691</t>
   </si>
   <si>
     <t xml:space="preserve">20.6885299682617</t>
@@ -2642,16 +2642,16 @@
     <t xml:space="preserve">21.7824058532715</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3506374359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7799186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3043193817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2567596435547</t>
+    <t xml:space="preserve">24.3506355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7799205780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3043212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.256763458252</t>
   </si>
   <si>
     <t xml:space="preserve">23.0189628601074</t>
@@ -2660,10 +2660,10 @@
     <t xml:space="preserve">23.1140804290771</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3518810272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0665225982666</t>
+    <t xml:space="preserve">23.351879119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.066520690918</t>
   </si>
   <si>
     <t xml:space="preserve">23.5896778106689</t>
@@ -2675,10 +2675,10 @@
     <t xml:space="preserve">22.9238395690918</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6372394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5421199798584</t>
+    <t xml:space="preserve">23.6372375488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.542121887207</t>
   </si>
   <si>
     <t xml:space="preserve">23.4945602416992</t>
@@ -2687,13 +2687,13 @@
     <t xml:space="preserve">22.8762798309326</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3994426727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6860446929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4482460021973</t>
+    <t xml:space="preserve">23.3994407653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6860427856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4482440948486</t>
   </si>
   <si>
     <t xml:space="preserve">22.1153259277344</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">21.4494857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0677661895752</t>
+    <t xml:space="preserve">22.0677642822266</t>
   </si>
   <si>
     <t xml:space="preserve">22.020206451416</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">23.7323608398438</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3030757904053</t>
+    <t xml:space="preserve">24.3030796051025</t>
   </si>
   <si>
     <t xml:space="preserve">23.8750381469727</t>
@@ -2723,61 +2723,61 @@
     <t xml:space="preserve">23.6848011016846</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3018360137939</t>
+    <t xml:space="preserve">25.3018341064453</t>
   </si>
   <si>
     <t xml:space="preserve">25.587194442749</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9676704406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6823101043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6347541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7774314880371</t>
+    <t xml:space="preserve">25.9676723480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6823139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6347522735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7774333953857</t>
   </si>
   <si>
     <t xml:space="preserve">25.492073059082</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3005886077881</t>
+    <t xml:space="preserve">26.3005905151367</t>
   </si>
   <si>
     <t xml:space="preserve">26.3957099914551</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2993450164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2042293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.156665802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6798248291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2981052398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7749462127686</t>
+    <t xml:space="preserve">27.2993469238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2042274475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1566677093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6798267364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2981033325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7749443054199</t>
   </si>
   <si>
     <t xml:space="preserve">28.1078643798828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5847053527832</t>
+    <t xml:space="preserve">27.5847072601318</t>
   </si>
   <si>
     <t xml:space="preserve">27.4420261383057</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5371494293213</t>
+    <t xml:space="preserve">27.5371475219727</t>
   </si>
   <si>
     <t xml:space="preserve">27.3469066619873</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">26.7761878967285</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9664287567139</t>
+    <t xml:space="preserve">26.9664306640625</t>
   </si>
   <si>
     <t xml:space="preserve">26.8713092803955</t>
@@ -2801,7 +2801,7 @@
     <t xml:space="preserve">26.7469043731689</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0770359039307</t>
+    <t xml:space="preserve">26.077033996582</t>
   </si>
   <si>
     <t xml:space="preserve">25.6464042663574</t>
@@ -2810,13 +2810,13 @@
     <t xml:space="preserve">25.2636222839355</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4023628234863</t>
+    <t xml:space="preserve">24.402364730835</t>
   </si>
   <si>
     <t xml:space="preserve">24.5459041595459</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9717311859131</t>
+    <t xml:space="preserve">23.9717330932617</t>
   </si>
   <si>
     <t xml:space="preserve">24.5937557220459</t>
@@ -2837,19 +2837,19 @@
     <t xml:space="preserve">26.2684268951416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7421016693115</t>
+    <t xml:space="preserve">25.7420997619629</t>
   </si>
   <si>
     <t xml:space="preserve">25.6942539215088</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3114700317383</t>
+    <t xml:space="preserve">25.3114719390869</t>
   </si>
   <si>
     <t xml:space="preserve">25.5507106781006</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9765357971191</t>
+    <t xml:space="preserve">24.9765377044678</t>
   </si>
   <si>
     <t xml:space="preserve">25.4071655273438</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">25.9334926605225</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8856430053711</t>
+    <t xml:space="preserve">25.8856449127197</t>
   </si>
   <si>
     <t xml:space="preserve">25.7899494171143</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">24.6894493103027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5028629302979</t>
+    <t xml:space="preserve">25.5028591156006</t>
   </si>
   <si>
     <t xml:space="preserve">25.3593196868896</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">22.8233871459961</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6319961547852</t>
+    <t xml:space="preserve">22.6319980621338</t>
   </si>
   <si>
     <t xml:space="preserve">23.4932537078857</t>
@@ -2900,7 +2900,7 @@
     <t xml:space="preserve">22.7755374908447</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0626239776611</t>
+    <t xml:space="preserve">23.0626258850098</t>
   </si>
   <si>
     <t xml:space="preserve">23.2540149688721</t>
@@ -2912,22 +2912,22 @@
     <t xml:space="preserve">21.81858253479</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6750392913818</t>
+    <t xml:space="preserve">21.6750411987305</t>
   </si>
   <si>
     <t xml:space="preserve">21.4358005523682</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4884510040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6798458099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3449077606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9621276855469</t>
+    <t xml:space="preserve">22.488452911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6798439025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3449096679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9621295928955</t>
   </si>
   <si>
     <t xml:space="preserve">23.0147762298584</t>
@@ -2936,13 +2936,13 @@
     <t xml:space="preserve">22.009973526001</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9142780303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2444095611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0051708221436</t>
+    <t xml:space="preserve">21.9142799377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2444114685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0051727294922</t>
   </si>
   <si>
     <t xml:space="preserve">20.383150100708</t>
@@ -2951,10 +2951,10 @@
     <t xml:space="preserve">19.3783473968506</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0482177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8089790344238</t>
+    <t xml:space="preserve">20.0482158660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8089771270752</t>
   </si>
   <si>
     <t xml:space="preserve">18.8328838348389</t>
@@ -2972,13 +2972,13 @@
     <t xml:space="preserve">16.8424167633057</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8950672149658</t>
+    <t xml:space="preserve">17.8950691223145</t>
   </si>
   <si>
     <t xml:space="preserve">18.0290393829346</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4357280731201</t>
+    <t xml:space="preserve">17.4357261657715</t>
   </si>
   <si>
     <t xml:space="preserve">18.1821517944336</t>
@@ -2993,10 +2993,10 @@
     <t xml:space="preserve">18.5457954406738</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1438732147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2012939453125</t>
+    <t xml:space="preserve">18.1438751220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2012920379639</t>
   </si>
   <si>
     <t xml:space="preserve">18.5649356842041</t>
@@ -3008,31 +3008,31 @@
     <t xml:space="preserve">18.6414909362793</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9477157592773</t>
+    <t xml:space="preserve">18.947717666626</t>
   </si>
   <si>
     <t xml:space="preserve">19.0625534057617</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4740447998047</t>
+    <t xml:space="preserve">19.4740409851074</t>
   </si>
   <si>
     <t xml:space="preserve">18.9859962463379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0816898345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5075149536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.64626121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5266571044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2778491973877</t>
+    <t xml:space="preserve">19.0816917419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5075168609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6462593078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5266590118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2778472900391</t>
   </si>
   <si>
     <t xml:space="preserve">18.603214263916</t>
@@ -3044,13 +3044,13 @@
     <t xml:space="preserve">19.6175861358643</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0051326751709</t>
+    <t xml:space="preserve">19.0051345825195</t>
   </si>
   <si>
     <t xml:space="preserve">18.6223526000977</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7946033477783</t>
+    <t xml:space="preserve">18.794605255127</t>
   </si>
   <si>
     <t xml:space="preserve">19.2348041534424</t>
@@ -3059,16 +3059,16 @@
     <t xml:space="preserve">19.1391086578369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4165916442871</t>
+    <t xml:space="preserve">17.4165897369385</t>
   </si>
   <si>
     <t xml:space="preserve">17.6079788208008</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9716243743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6654319763184</t>
+    <t xml:space="preserve">17.971622467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.665433883667</t>
   </si>
   <si>
     <t xml:space="preserve">19.9046726226807</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">20.8616275787354</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5745410919189</t>
+    <t xml:space="preserve">20.5745429992676</t>
   </si>
   <si>
     <t xml:space="preserve">20.9094753265381</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">22.2492122650146</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9669322967529</t>
+    <t xml:space="preserve">22.9669303894043</t>
   </si>
   <si>
     <t xml:space="preserve">23.1583213806152</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">22.3927574157715</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0578212738037</t>
+    <t xml:space="preserve">22.0578193664551</t>
   </si>
   <si>
     <t xml:space="preserve">20.2874546051025</t>
@@ -3119,34 +3119,34 @@
     <t xml:space="preserve">20.0960636138916</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3353023529053</t>
+    <t xml:space="preserve">20.3353042602539</t>
   </si>
   <si>
     <t xml:space="preserve">19.7132816314697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1199703216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6606311798096</t>
+    <t xml:space="preserve">19.119966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6606292724609</t>
   </si>
   <si>
     <t xml:space="preserve">18.4692401885986</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4548645019531</t>
+    <t xml:space="preserve">17.4548683166504</t>
   </si>
   <si>
     <t xml:space="preserve">18.6797695159912</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3735427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1055965423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9524822235107</t>
+    <t xml:space="preserve">18.3735466003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.105598449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9524841308594</t>
   </si>
   <si>
     <t xml:space="preserve">18.4309616088867</t>
@@ -3158,34 +3158,34 @@
     <t xml:space="preserve">18.8137435913086</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4118232727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.316125869751</t>
+    <t xml:space="preserve">18.4118213653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3161277770996</t>
   </si>
   <si>
     <t xml:space="preserve">18.163013458252</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8567886352539</t>
+    <t xml:space="preserve">17.8567867279053</t>
   </si>
   <si>
     <t xml:space="preserve">18.4500999450684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.186954498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7180461883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8520221710205</t>
+    <t xml:space="preserve">19.1869583129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7180480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8520240783691</t>
   </si>
   <si>
     <t xml:space="preserve">19.3304996490479</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0481796264648</t>
+    <t xml:space="preserve">18.0481815338135</t>
   </si>
   <si>
     <t xml:space="preserve">17.5888385772705</t>
@@ -3206,22 +3206,22 @@
     <t xml:space="preserve">17.5505619049072</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2251968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5170497894287</t>
+    <t xml:space="preserve">17.2251987457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5170516967773</t>
   </si>
   <si>
     <t xml:space="preserve">15.8854608535767</t>
   </si>
   <si>
-    <t xml:space="preserve">16.344799041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0959911346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9428777694702</t>
+    <t xml:space="preserve">16.3447971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0959892272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9428787231445</t>
   </si>
   <si>
     <t xml:space="preserve">16.1151294708252</t>
@@ -3236,22 +3236,22 @@
     <t xml:space="preserve">15.2538681030273</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6127452850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0194320678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6510257720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7658576965332</t>
+    <t xml:space="preserve">16.6127471923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0194339752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6510219573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7658596038818</t>
   </si>
   <si>
     <t xml:space="preserve">16.9955291748047</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3208923339844</t>
+    <t xml:space="preserve">17.320894241333</t>
   </si>
   <si>
     <t xml:space="preserve">17.1295013427734</t>
@@ -3260,16 +3260,16 @@
     <t xml:space="preserve">17.0529460906982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0146675109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8376502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.756326675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6989116668701</t>
+    <t xml:space="preserve">17.0146656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8376483917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7563247680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6989078521729</t>
   </si>
   <si>
     <t xml:space="preserve">19.4261932373047</t>
@@ -3278,10 +3278,10 @@
     <t xml:space="preserve">19.9525203704834</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0003662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5697402954102</t>
+    <t xml:space="preserve">20.0003681182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5697383880615</t>
   </si>
   <si>
     <t xml:space="preserve">20.4309978485107</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">20.1917591094971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6223907470703</t>
+    <t xml:space="preserve">20.6223888397217</t>
   </si>
   <si>
     <t xml:space="preserve">20.7180843353271</t>
@@ -3305,28 +3305,28 @@
     <t xml:space="preserve">20.7464904785156</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6010723114014</t>
+    <t xml:space="preserve">20.6010704040527</t>
   </si>
   <si>
     <t xml:space="preserve">20.5041236877441</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3102340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5525989532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4556503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4071769714355</t>
+    <t xml:space="preserve">20.3102321624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5525970458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4556522369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4071788787842</t>
   </si>
   <si>
     <t xml:space="preserve">20.1648120880127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.182746887207</t>
+    <t xml:space="preserve">21.1827487945557</t>
   </si>
   <si>
     <t xml:space="preserve">20.3587055206299</t>
@@ -3335,22 +3335,22 @@
     <t xml:space="preserve">20.0193939208984</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9709186553955</t>
+    <t xml:space="preserve">19.9709205627441</t>
   </si>
   <si>
     <t xml:space="preserve">20.116340637207</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8434371948242</t>
+    <t xml:space="preserve">20.8434352874756</t>
   </si>
   <si>
     <t xml:space="preserve">20.6980171203613</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9403820037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6190052032471</t>
+    <t xml:space="preserve">20.9403839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6190071105957</t>
   </si>
   <si>
     <t xml:space="preserve">21.7159519195557</t>
@@ -3371,10 +3371,10 @@
     <t xml:space="preserve">23.2186183929443</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4430484771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7823600769043</t>
+    <t xml:space="preserve">22.4430503845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7823619842529</t>
   </si>
   <si>
     <t xml:space="preserve">22.9277801513672</t>
@@ -3389,25 +3389,25 @@
     <t xml:space="preserve">23.3640384674072</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3155651092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0732002258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5579319000244</t>
+    <t xml:space="preserve">23.3155632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0731983184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5579299926758</t>
   </si>
   <si>
     <t xml:space="preserve">23.5094566345215</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4609851837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6064033508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7033500671387</t>
+    <t xml:space="preserve">23.4609832763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6064052581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7033519744873</t>
   </si>
   <si>
     <t xml:space="preserve">23.1216735839844</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">23.17014503479</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8002967834473</t>
+    <t xml:space="preserve">23.8002948760986</t>
   </si>
   <si>
     <t xml:space="preserve">24.5273914337158</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">24.8182315826416</t>
   </si>
   <si>
-    <t xml:space="preserve">24.624340057373</t>
+    <t xml:space="preserve">24.6243381500244</t>
   </si>
   <si>
     <t xml:space="preserve">24.3335018157959</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">24.4304466247559</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2850284576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1396083831787</t>
+    <t xml:space="preserve">24.285026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1396064758301</t>
   </si>
   <si>
     <t xml:space="preserve">23.8487701416016</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5884685516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4915218353271</t>
+    <t xml:space="preserve">22.5884666442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4915237426758</t>
   </si>
   <si>
     <t xml:space="preserve">23.0247268676758</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">22.9762535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8972434997559</t>
+    <t xml:space="preserve">23.8972415924072</t>
   </si>
   <si>
     <t xml:space="preserve">24.0911350250244</t>
@@ -3476,10 +3476,10 @@
     <t xml:space="preserve">22.6854152679443</t>
   </si>
   <si>
-    <t xml:space="preserve">22.20068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8129005432129</t>
+    <t xml:space="preserve">22.2006855010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8128986358643</t>
   </si>
   <si>
     <t xml:space="preserve">21.76442527771</t>
@@ -3488,25 +3488,25 @@
     <t xml:space="preserve">22.1522102355957</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3945751190186</t>
+    <t xml:space="preserve">22.3945770263672</t>
   </si>
   <si>
     <t xml:space="preserve">22.63694190979</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3461036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5399951934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5220623016357</t>
+    <t xml:space="preserve">22.3461017608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5399971008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5220603942871</t>
   </si>
   <si>
     <t xml:space="preserve">21.4251136779785</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2312202453613</t>
+    <t xml:space="preserve">21.23122215271</t>
   </si>
   <si>
     <t xml:space="preserve">21.2796955108643</t>
@@ -3515,34 +3515,34 @@
     <t xml:space="preserve">21.3766403198242</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9888553619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7949638366699</t>
+    <t xml:space="preserve">20.9888572692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7949619293213</t>
   </si>
   <si>
     <t xml:space="preserve">21.3281688690186</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0858039855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8919086456299</t>
+    <t xml:space="preserve">21.0858020782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8919105529785</t>
   </si>
   <si>
     <t xml:space="preserve">21.0373306274414</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8613719940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9583187103271</t>
+    <t xml:space="preserve">21.8613700866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9583168029785</t>
   </si>
   <si>
     <t xml:space="preserve">21.6674785614014</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2491569519043</t>
+    <t xml:space="preserve">22.2491588592529</t>
   </si>
   <si>
     <t xml:space="preserve">24.0426616668701</t>
@@ -3557,25 +3557,25 @@
     <t xml:space="preserve">25.8361663818359</t>
   </si>
   <si>
-    <t xml:space="preserve">25.690746307373</t>
+    <t xml:space="preserve">25.6907482147217</t>
   </si>
   <si>
     <t xml:space="preserve">25.6422748565674</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7876930236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8846416473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1754779815674</t>
+    <t xml:space="preserve">25.7876949310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8846397399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1754760742188</t>
   </si>
   <si>
     <t xml:space="preserve">26.9025745391846</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2239513397217</t>
+    <t xml:space="preserve">26.223949432373</t>
   </si>
   <si>
     <t xml:space="preserve">26.3693733215332</t>
@@ -3584,16 +3584,16 @@
     <t xml:space="preserve">25.3029632568359</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3819732666016</t>
+    <t xml:space="preserve">24.3819713592529</t>
   </si>
   <si>
     <t xml:space="preserve">24.721284866333</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9941864013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2365531921387</t>
+    <t xml:space="preserve">23.9941902160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2365550994873</t>
   </si>
   <si>
     <t xml:space="preserve">24.5758666992188</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">25.3514347076416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5453300476074</t>
+    <t xml:space="preserve">25.5453281402588</t>
   </si>
   <si>
     <t xml:space="preserve">25.8003883361816</t>
@@ -3626,13 +3626,13 @@
     <t xml:space="preserve">25.9965896606445</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6832942962646</t>
+    <t xml:space="preserve">26.683292388916</t>
   </si>
   <si>
     <t xml:space="preserve">26.7813911437988</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5361404418945</t>
+    <t xml:space="preserve">26.5361423492432</t>
   </si>
   <si>
     <t xml:space="preserve">26.7323417663574</t>
@@ -3653,22 +3653,22 @@
     <t xml:space="preserve">26.4380416870117</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5851917266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7623958587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5661945343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6642951965332</t>
+    <t xml:space="preserve">26.5851936340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.762393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5661964416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6642971038818</t>
   </si>
   <si>
     <t xml:space="preserve">28.1057472229004</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8414993286133</t>
+    <t xml:space="preserve">28.8414974212646</t>
   </si>
   <si>
     <t xml:space="preserve">29.1358013153076</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">29.184850692749</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8225021362305</t>
+    <t xml:space="preserve">29.8225040435791</t>
   </si>
   <si>
     <t xml:space="preserve">29.4791507720947</t>
@@ -3710,13 +3710,13 @@
     <t xml:space="preserve">29.4301013946533</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3620567321777</t>
+    <t xml:space="preserve">30.3620548248291</t>
   </si>
   <si>
     <t xml:space="preserve">29.9696521759033</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5582542419434</t>
+    <t xml:space="preserve">30.558256149292</t>
   </si>
   <si>
     <t xml:space="preserve">30.4601535797119</t>
@@ -3728,10 +3728,10 @@
     <t xml:space="preserve">30.6563568115234</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8525562286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6073055267334</t>
+    <t xml:space="preserve">30.8525581359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.607307434082</t>
   </si>
   <si>
     <t xml:space="preserve">30.9016056060791</t>
@@ -3752,10 +3752,10 @@
     <t xml:space="preserve">30.0677528381348</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2639560699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.146858215332</t>
+    <t xml:space="preserve">30.2639541625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1468563079834</t>
   </si>
   <si>
     <t xml:space="preserve">31.3430595397949</t>
@@ -3767,10 +3767,10 @@
     <t xml:space="preserve">30.1658535003662</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3130054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2940063476562</t>
+    <t xml:space="preserve">30.3130035400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2940082550049</t>
   </si>
   <si>
     <t xml:space="preserve">31.3921089172363</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">32.7655143737793</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3050651550293</t>
+    <t xml:space="preserve">33.3050689697266</t>
   </si>
   <si>
     <t xml:space="preserve">33.3541145324707</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">31.4902076721191</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7354583740234</t>
+    <t xml:space="preserve">31.7354564666748</t>
   </si>
   <si>
     <t xml:space="preserve">32.0788116455078</t>
@@ -3869,19 +3869,19 @@
     <t xml:space="preserve">34.433219909668</t>
   </si>
   <si>
-    <t xml:space="preserve">34.531322479248</t>
+    <t xml:space="preserve">34.5313186645508</t>
   </si>
   <si>
     <t xml:space="preserve">34.7275199890137</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7085227966309</t>
+    <t xml:space="preserve">35.7085266113281</t>
   </si>
   <si>
     <t xml:space="preserve">36.0028266906738</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2971229553223</t>
+    <t xml:space="preserve">36.2971267700195</t>
   </si>
   <si>
     <t xml:space="preserve">35.512321472168</t>
@@ -3890,31 +3890,31 @@
     <t xml:space="preserve">36.6404762268066</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2480773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6594734191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4632720947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7385749816895</t>
+    <t xml:space="preserve">36.2480735778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6594696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4632759094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7385787963867</t>
   </si>
   <si>
     <t xml:space="preserve">37.2290802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4933242797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2781257629395</t>
+    <t xml:space="preserve">36.4933280944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2781295776367</t>
   </si>
   <si>
     <t xml:space="preserve">36.5423774719238</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5233764648438</t>
+    <t xml:space="preserve">37.523380279541</t>
   </si>
   <si>
     <t xml:space="preserve">37.4743309020996</t>
@@ -3923,13 +3923,13 @@
     <t xml:space="preserve">35.5613746643066</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8066215515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7765731811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2180252075195</t>
+    <t xml:space="preserve">35.8066253662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7765693664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2180213928223</t>
   </si>
   <si>
     <t xml:space="preserve">34.9237174987793</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">35.0218200683594</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1689682006836</t>
+    <t xml:space="preserve">35.1689720153809</t>
   </si>
   <si>
     <t xml:space="preserve">34.678466796875</t>
@@ -3947,34 +3947,34 @@
     <t xml:space="preserve">33.9917678833008</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3651695251465</t>
+    <t xml:space="preserve">35.3651733398438</t>
   </si>
   <si>
     <t xml:space="preserve">36.051872253418</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8556747436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7575759887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0898704528809</t>
+    <t xml:space="preserve">35.8556709289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7575721740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0898666381836</t>
   </si>
   <si>
     <t xml:space="preserve">33.9427146911621</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0408172607422</t>
+    <t xml:space="preserve">34.0408210754395</t>
   </si>
   <si>
     <t xml:space="preserve">34.3841667175293</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3161239624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2370185852051</t>
+    <t xml:space="preserve">35.3161201477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2370223999023</t>
   </si>
   <si>
     <t xml:space="preserve">32.4221611022949</t>
@@ -4004,7 +4004,7 @@
     <t xml:space="preserve">29.2339000701904</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9095478057861</t>
+    <t xml:space="preserve">27.9095458984375</t>
   </si>
   <si>
     <t xml:space="preserve">27.7133464813232</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">28.2528972625732</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3209438323975</t>
+    <t xml:space="preserve">27.3209457397461</t>
   </si>
   <si>
     <t xml:space="preserve">27.1247425079346</t>
@@ -4037,13 +4037,13 @@
     <t xml:space="preserve">26.6342430114746</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0266437530518</t>
+    <t xml:space="preserve">27.0266418457031</t>
   </si>
   <si>
     <t xml:space="preserve">26.9775924682617</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2908916473389</t>
+    <t xml:space="preserve">26.2908897399902</t>
   </si>
   <si>
     <t xml:space="preserve">26.1927909851074</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">26.0456390380859</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7022895812988</t>
+    <t xml:space="preserve">25.7022876739502</t>
   </si>
   <si>
     <t xml:space="preserve">25.8984889984131</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">25.309886932373</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1627349853516</t>
+    <t xml:space="preserve">25.1627368927002</t>
   </si>
   <si>
     <t xml:space="preserve">25.0155868530273</t>
@@ -4073,13 +4073,13 @@
     <t xml:space="preserve">24.672233581543</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4269828796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8383827209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3288822174072</t>
+    <t xml:space="preserve">24.4269847869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8383808135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3288841247559</t>
   </si>
   <si>
     <t xml:space="preserve">25.4570388793945</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">24.5741348266602</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8193855285645</t>
+    <t xml:space="preserve">24.8193836212158</t>
   </si>
   <si>
     <t xml:space="preserve">24.3841934204102</t>
@@ -4671,6 +4671,9 @@
   </si>
   <si>
     <t xml:space="preserve">50.9000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2000007629395</t>
   </si>
 </sst>
 </file>
@@ -70815,7 +70818,7 @@
     </row>
     <row r="2532">
       <c r="A2532" s="1" t="n">
-        <v>46003.6911574074</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2532" t="n">
         <v>256823</v>
@@ -70836,6 +70839,32 @@
         <v>1552</v>
       </c>
       <c r="H2532" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" s="1" t="n">
+        <v>46006.6913078704</v>
+      </c>
+      <c r="B2533" t="n">
+        <v>69929</v>
+      </c>
+      <c r="C2533" t="n">
+        <v>51.2000007629395</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>50.2000007629395</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>51.0999984741211</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>51.2000007629395</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>1553</v>
+      </c>
+      <c r="H2533" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="1556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="1557">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5902509689331</t>
+    <t xml:space="preserve">15.5902519226074</t>
   </si>
   <si>
     <t xml:space="preserve">DAN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7186412811279</t>
+    <t xml:space="preserve">15.7186393737793</t>
   </si>
   <si>
     <t xml:space="preserve">15.2234220504761</t>
@@ -53,43 +53,43 @@
     <t xml:space="preserve">14.5356168746948</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2146415710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9395208358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2880086898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0403995513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8661527633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1049814224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7931776046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8848848342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2887868881226</t>
+    <t xml:space="preserve">14.2146406173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9395189285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2880067825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0403985977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.866153717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1049833297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7931785583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8848838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2887859344482</t>
   </si>
   <si>
     <t xml:space="preserve">12.9490804672241</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1324939727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8928871154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0487861633301</t>
+    <t xml:space="preserve">13.132493019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8928852081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0487899780273</t>
   </si>
   <si>
     <t xml:space="preserve">16.3239097595215</t>
@@ -98,16 +98,16 @@
     <t xml:space="preserve">16.0854721069336</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3605899810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1125946044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5990314483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4710350036621</t>
+    <t xml:space="preserve">16.3605918884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1125907897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5990333557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4710311889648</t>
   </si>
   <si>
     <t xml:space="preserve">16.1038131713867</t>
@@ -119,16 +119,16 @@
     <t xml:space="preserve">14.9391298294067</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9482984542847</t>
+    <t xml:space="preserve">14.948299407959</t>
   </si>
   <si>
     <t xml:space="preserve">15.3518123626709</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1042013168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0033235549927</t>
+    <t xml:space="preserve">15.1042022705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0033264160156</t>
   </si>
   <si>
     <t xml:space="preserve">15.9112281799316</t>
@@ -137,67 +137,67 @@
     <t xml:space="preserve">16.2322044372559</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7641086578369</t>
+    <t xml:space="preserve">16.7641067504883</t>
   </si>
   <si>
     <t xml:space="preserve">16.9200077056885</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0575656890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9658641815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7090797424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3514232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3422508239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.828296661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6357135772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1767883300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3051776885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3693733215332</t>
+    <t xml:space="preserve">17.0575695037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9658622741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7090816497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3514251708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3422527313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8283004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6357173919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1767902374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3051815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3693752288818</t>
   </si>
   <si>
     <t xml:space="preserve">17.4335670471191</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5348358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2226409912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5161075592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8741550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2593231201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4610786437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0117149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2138614654541</t>
+    <t xml:space="preserve">16.5348377227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2226428985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5161056518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8741569519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2593269348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4610824584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0117130279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2138633728027</t>
   </si>
   <si>
     <t xml:space="preserve">16.5531768798828</t>
@@ -206,49 +206,49 @@
     <t xml:space="preserve">16.9383487701416</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2868404388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5715179443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5256652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1217651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5619583129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6353206634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4060535430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8645915985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1122035980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0204963684082</t>
+    <t xml:space="preserve">17.2868385314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5715198516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5256671905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1217632293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5619602203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6353244781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4060554504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8645935058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1122055053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0204944610596</t>
   </si>
   <si>
     <t xml:space="preserve">17.7912292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5986442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3414707183838</t>
+    <t xml:space="preserve">17.5986423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3414688110352</t>
   </si>
   <si>
     <t xml:space="preserve">18.405668258667</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4331798553467</t>
+    <t xml:space="preserve">18.4331817626953</t>
   </si>
   <si>
     <t xml:space="preserve">18.0938625335693</t>
@@ -260,43 +260,43 @@
     <t xml:space="preserve">18.0296649932861</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8921070098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4702529907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1492748260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4885959625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1676197052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0759124755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7732772827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8374729156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.562349319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3147411346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1496677398682</t>
+    <t xml:space="preserve">17.8921089172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.470251083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1492767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4885940551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1676177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0759105682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7732753753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8374710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5623474121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3147392272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1496696472168</t>
   </si>
   <si>
     <t xml:space="preserve">16.2505435943604</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7457637786865</t>
+    <t xml:space="preserve">16.7457656860352</t>
   </si>
   <si>
     <t xml:space="preserve">16.452299118042</t>
@@ -314,37 +314,37 @@
     <t xml:space="preserve">16.5164966583252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4981536865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2409820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.993371963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0392284393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8103485107422</t>
+    <t xml:space="preserve">16.4981517791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2409839630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9933738708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0392265319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8103466033936</t>
   </si>
   <si>
     <t xml:space="preserve">15.8470325469971</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9574708938599</t>
+    <t xml:space="preserve">14.9574728012085</t>
   </si>
   <si>
     <t xml:space="preserve">14.7648849487305</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0675210952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3334693908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9570837020874</t>
+    <t xml:space="preserve">15.0675201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3334722518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9570779800415</t>
   </si>
   <si>
     <t xml:space="preserve">14.9849834442139</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">14.4530801773071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8841028213501</t>
+    <t xml:space="preserve">14.8841037750244</t>
   </si>
   <si>
     <t xml:space="preserve">14.5264463424683</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">14.6823482513428</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4068355560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0308361053467</t>
+    <t xml:space="preserve">15.406834602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0308380126953</t>
   </si>
   <si>
     <t xml:space="preserve">14.6273241043091</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0037155151367</t>
+    <t xml:space="preserve">14.0037145614624</t>
   </si>
   <si>
     <t xml:space="preserve">14.2604951858521</t>
@@ -383,19 +383,19 @@
     <t xml:space="preserve">15.3976669311523</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3151302337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4985427856445</t>
+    <t xml:space="preserve">15.315131187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4985456466675</t>
   </si>
   <si>
     <t xml:space="preserve">15.2509346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3243007659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2967882156372</t>
+    <t xml:space="preserve">15.3242988586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2967872619629</t>
   </si>
   <si>
     <t xml:space="preserve">15.3793249130249</t>
@@ -404,34 +404,34 @@
     <t xml:space="preserve">16.1404972076416</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6177616119385</t>
+    <t xml:space="preserve">15.6177635192871</t>
   </si>
   <si>
     <t xml:space="preserve">15.3884944915771</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1221561431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8286914825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0763034820557</t>
+    <t xml:space="preserve">16.1221523284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.828688621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0762996673584</t>
   </si>
   <si>
     <t xml:space="preserve">16.1771774291992</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0671329498291</t>
+    <t xml:space="preserve">16.0671310424805</t>
   </si>
   <si>
     <t xml:space="preserve">15.9845943450928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1401042938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8099594116211</t>
+    <t xml:space="preserve">17.1401100158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8099575042725</t>
   </si>
   <si>
     <t xml:space="preserve">16.6082038879395</t>
@@ -440,55 +440,55 @@
     <t xml:space="preserve">16.6448860168457</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6078109741211</t>
+    <t xml:space="preserve">17.6078128814697</t>
   </si>
   <si>
     <t xml:space="preserve">17.158447265625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0300559997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1951274871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.332691192627</t>
+    <t xml:space="preserve">17.0300540924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1951313018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3326930999756</t>
   </si>
   <si>
     <t xml:space="preserve">16.0946407318115</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7828350067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7553262710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8195190429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9479093551636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6361055374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6636180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5627393722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.489372253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6085939407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0304489135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6999073028564</t>
+    <t xml:space="preserve">15.7828369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7553253173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8195219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9479074478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6361036300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6636161804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5627422332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4893760681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6085948944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0304470062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6999111175537</t>
   </si>
   <si>
     <t xml:space="preserve">16.0579605102539</t>
@@ -497,79 +497,79 @@
     <t xml:space="preserve">15.5352277755737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.544397354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7003030776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3609828948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1592273712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2330417633057</t>
+    <t xml:space="preserve">15.5444002151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7003021240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3609819412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1592254638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2330389022827</t>
   </si>
   <si>
     <t xml:space="preserve">15.3068513870239</t>
   </si>
   <si>
-    <t xml:space="preserve">15.54674243927</t>
+    <t xml:space="preserve">15.5467414855957</t>
   </si>
   <si>
     <t xml:space="preserve">15.6297826766968</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7866315841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5190629959106</t>
+    <t xml:space="preserve">15.7866325378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5190601348877</t>
   </si>
   <si>
     <t xml:space="preserve">14.9746952056885</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3253040313721</t>
+    <t xml:space="preserve">15.3253049850464</t>
   </si>
   <si>
     <t xml:space="preserve">15.4175701141357</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4083433151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0577363967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7589521408081</t>
+    <t xml:space="preserve">15.4083452224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0577354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7589530944824</t>
   </si>
   <si>
     <t xml:space="preserve">16.2202816009521</t>
   </si>
   <si>
-    <t xml:space="preserve">15.823540687561</t>
+    <t xml:space="preserve">15.8235397338867</t>
   </si>
   <si>
     <t xml:space="preserve">15.3898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5006103515625</t>
+    <t xml:space="preserve">15.5006084442139</t>
   </si>
   <si>
     <t xml:space="preserve">15.2145881652832</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7774057388306</t>
+    <t xml:space="preserve">15.7774076461792</t>
   </si>
   <si>
     <t xml:space="preserve">15.9434852600098</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7312717437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4693984985352</t>
+    <t xml:space="preserve">15.7312726974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4693965911865</t>
   </si>
   <si>
     <t xml:space="preserve">17.0691242218018</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">16.9122695922852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8384609222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3771343231201</t>
+    <t xml:space="preserve">16.8384590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3771324157715</t>
   </si>
   <si>
     <t xml:space="preserve">16.9768600463867</t>
@@ -605,52 +605,52 @@
     <t xml:space="preserve">17.6227188110352</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7795677185059</t>
+    <t xml:space="preserve">17.7795696258545</t>
   </si>
   <si>
     <t xml:space="preserve">17.8164749145508</t>
   </si>
   <si>
-    <t xml:space="preserve">17.761116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3054790496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7760353088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8221683502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4218921661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4957046508789</t>
+    <t xml:space="preserve">17.7611122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3054809570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7760372161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8221664428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.421895980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4957065582275</t>
   </si>
   <si>
     <t xml:space="preserve">18.988245010376</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7852630615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3296279907227</t>
+    <t xml:space="preserve">18.7852611541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3296298980713</t>
   </si>
   <si>
     <t xml:space="preserve">19.2004566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0528335571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9513378143311</t>
+    <t xml:space="preserve">19.0528297424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.951343536377</t>
   </si>
   <si>
     <t xml:space="preserve">18.7299041748047</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8867511749268</t>
+    <t xml:space="preserve">18.886754989624</t>
   </si>
   <si>
     <t xml:space="preserve">18.8129405975342</t>
@@ -665,28 +665,28 @@
     <t xml:space="preserve">18.4531059265137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2778034210205</t>
+    <t xml:space="preserve">18.2777996063232</t>
   </si>
   <si>
     <t xml:space="preserve">17.9917812347412</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3331661224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4069728851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3423881530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2501239776611</t>
+    <t xml:space="preserve">18.3331642150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4069747924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3423862457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2501220703125</t>
   </si>
   <si>
     <t xml:space="preserve">18.3608417510986</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1578598022461</t>
+    <t xml:space="preserve">18.1578578948975</t>
   </si>
   <si>
     <t xml:space="preserve">18.2039890289307</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">18.388521194458</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4900131225586</t>
+    <t xml:space="preserve">18.4900150299072</t>
   </si>
   <si>
     <t xml:space="preserve">18.4992389678955</t>
@@ -707,34 +707,34 @@
     <t xml:space="preserve">18.914436340332</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2834968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9605655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9974765777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2373638153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3204021453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8313961029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1174201965332</t>
+    <t xml:space="preserve">19.2834949493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9605674743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9974746704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2373657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.320405960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8313941955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1174182891846</t>
   </si>
   <si>
     <t xml:space="preserve">19.3757629394531</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9697952270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0897369384766</t>
+    <t xml:space="preserve">18.9697933197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0897407531738</t>
   </si>
   <si>
     <t xml:space="preserve">19.2189121246338</t>
@@ -743,109 +743,109 @@
     <t xml:space="preserve">18.9052085876465</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0989685058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2558212280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1543254852295</t>
+    <t xml:space="preserve">19.0989665985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2558193206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1543273925781</t>
   </si>
   <si>
     <t xml:space="preserve">19.7817306518555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8739986419678</t>
+    <t xml:space="preserve">19.8739948272705</t>
   </si>
   <si>
     <t xml:space="preserve">20.2430572509766</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4829502105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7136154174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8243274688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8058795928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0123958587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4737243652344</t>
+    <t xml:space="preserve">20.4829483032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7136135101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8243293762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8058776855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.012393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4737205505371</t>
   </si>
   <si>
     <t xml:space="preserve">20.2522850036621</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1138877868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4368133544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5106296539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4644966125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.363000869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3906841278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5198574066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3445510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6767082214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7228374481201</t>
+    <t xml:space="preserve">20.113883972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4368152618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.510627746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4644947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3630027770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.390682220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5198554992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3445491790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6767063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7228393554688</t>
   </si>
   <si>
     <t xml:space="preserve">20.3168697357178</t>
   </si>
   <si>
-    <t xml:space="preserve">20.639799118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4978713989258</t>
+    <t xml:space="preserve">20.6398010253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4978694915771</t>
   </si>
   <si>
     <t xml:space="preserve">21.3502445220947</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2210731506348</t>
+    <t xml:space="preserve">21.2210712432861</t>
   </si>
   <si>
     <t xml:space="preserve">21.1749420166016</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9904098510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9811859130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.787425994873</t>
+    <t xml:space="preserve">20.9904079437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9811820983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7874240875244</t>
   </si>
   <si>
     <t xml:space="preserve">21.1288070678711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9627285003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.202615737915</t>
+    <t xml:space="preserve">20.9627304077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2026176452637</t>
   </si>
   <si>
     <t xml:space="preserve">21.0826759338379</t>
@@ -857,37 +857,37 @@
     <t xml:space="preserve">21.0273151397705</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8151016235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9719581604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1103534698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1011257171631</t>
+    <t xml:space="preserve">20.8151054382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9719543457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1103553771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1011276245117</t>
   </si>
   <si>
     <t xml:space="preserve">21.1933937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">21.138032913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.79665184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0365409851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5936660766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1784725189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2615070343018</t>
+    <t xml:space="preserve">21.1380348205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7966537475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0365390777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5936641693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1784744262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.261510848999</t>
   </si>
   <si>
     <t xml:space="preserve">20.2707386016846</t>
@@ -899,19 +899,19 @@
     <t xml:space="preserve">20.4921741485596</t>
   </si>
   <si>
-    <t xml:space="preserve">20.141565322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9109001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.076976776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6617870330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7725048065186</t>
+    <t xml:space="preserve">20.1415672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9109039306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0769805908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6617851257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7725009918213</t>
   </si>
   <si>
     <t xml:space="preserve">20.1323394775391</t>
@@ -923,61 +923,61 @@
     <t xml:space="preserve">20.4091377258301</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2984161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8186378479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6986904144287</t>
+    <t xml:space="preserve">20.2984180450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8186359405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6986923217773</t>
   </si>
   <si>
     <t xml:space="preserve">19.7540512084961</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5879745483398</t>
+    <t xml:space="preserve">19.5879726409912</t>
   </si>
   <si>
     <t xml:space="preserve">19.7909564971924</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9385833740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8647727966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9754848480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5418395996094</t>
+    <t xml:space="preserve">19.9385814666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8647708892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9754886627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.541841506958</t>
   </si>
   <si>
     <t xml:space="preserve">20.5290813446045</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1046600341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8370914459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5971965789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2799644470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9939441680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3537769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7043857574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2061538696289</t>
+    <t xml:space="preserve">20.1046619415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8370895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5972003936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2799625396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9939422607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3537750244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7043876647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2061557769775</t>
   </si>
   <si>
     <t xml:space="preserve">20.4275894165039</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">21.0549964904785</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5844402313232</t>
+    <t xml:space="preserve">20.5844421386719</t>
   </si>
   <si>
     <t xml:space="preserve">20.3353252410889</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1969242095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2338333129883</t>
+    <t xml:space="preserve">20.1969261169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.233829498291</t>
   </si>
   <si>
     <t xml:space="preserve">19.7448234558105</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7079200744629</t>
+    <t xml:space="preserve">19.7079181671143</t>
   </si>
   <si>
     <t xml:space="preserve">19.634105682373</t>
@@ -1013,10 +1013,10 @@
     <t xml:space="preserve">19.8463172912598</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9570350646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3814544677734</t>
+    <t xml:space="preserve">19.9570369720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3814563751221</t>
   </si>
   <si>
     <t xml:space="preserve">19.8555431365967</t>
@@ -1025,28 +1025,28 @@
     <t xml:space="preserve">19.4034423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1266479492188</t>
+    <t xml:space="preserve">19.1266422271729</t>
   </si>
   <si>
     <t xml:space="preserve">18.6560897827148</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7114524841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5084667205811</t>
+    <t xml:space="preserve">18.7114543914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5084686279297</t>
   </si>
   <si>
     <t xml:space="preserve">18.8683032989502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5545978546143</t>
+    <t xml:space="preserve">18.5545997619629</t>
   </si>
   <si>
     <t xml:space="preserve">18.4346542358398</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5361480712891</t>
+    <t xml:space="preserve">18.5361461639404</t>
   </si>
   <si>
     <t xml:space="preserve">18.3147068023682</t>
@@ -1058,16 +1058,16 @@
     <t xml:space="preserve">19.0067005157471</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8497562408447</t>
+    <t xml:space="preserve">18.849760055542</t>
   </si>
   <si>
     <t xml:space="preserve">18.8219432830811</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4047050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1821842193604</t>
+    <t xml:space="preserve">18.4047088623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1821823120117</t>
   </si>
   <si>
     <t xml:space="preserve">17.7834892272949</t>
@@ -1076,22 +1076,22 @@
     <t xml:space="preserve">17.7278594970703</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5238761901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5516929626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8205757141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7742195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8483943939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1450939178467</t>
+    <t xml:space="preserve">17.5238780975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5516948699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.82057762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7742176055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8483924865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.145092010498</t>
   </si>
   <si>
     <t xml:space="preserve">18.3398056030273</t>
@@ -1106,61 +1106,61 @@
     <t xml:space="preserve">18.0431022644043</t>
   </si>
   <si>
-    <t xml:space="preserve">18.367618560791</t>
+    <t xml:space="preserve">18.3676204681396</t>
   </si>
   <si>
     <t xml:space="preserve">18.2378120422363</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0987358093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5437831878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6457748413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5716018676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5623321533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4881534576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2285404205322</t>
+    <t xml:space="preserve">18.0987377166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5437870025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6457805633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5715980529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.562328338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4881553649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2285423278809</t>
   </si>
   <si>
     <t xml:space="preserve">18.2563571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3212642669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3583488464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3490772247314</t>
+    <t xml:space="preserve">18.3212585449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3583450317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3490753173828</t>
   </si>
   <si>
     <t xml:space="preserve">18.5345115661621</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5808734893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4696102142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2656269073486</t>
+    <t xml:space="preserve">18.5808773040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.469612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2656288146973</t>
   </si>
   <si>
     <t xml:space="preserve">18.3768901824951</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7755813598633</t>
+    <t xml:space="preserve">18.7755794525146</t>
   </si>
   <si>
     <t xml:space="preserve">19.0537395477295</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">19.3318958282471</t>
   </si>
   <si>
-    <t xml:space="preserve">19.610050201416</t>
+    <t xml:space="preserve">19.6100540161133</t>
   </si>
   <si>
     <t xml:space="preserve">20.3981628417969</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">21.13991355896</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4180717468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.371711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2326374053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4644298553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3253536224365</t>
+    <t xml:space="preserve">21.4180698394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3717136383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2326335906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4644317626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3253555297852</t>
   </si>
   <si>
     <t xml:space="preserve">21.6035099029541</t>
@@ -1202,37 +1202,37 @@
     <t xml:space="preserve">20.861759185791</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3054466247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9081172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4908847808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6299629211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5836048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9544792175293</t>
+    <t xml:space="preserve">20.3054485321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9081153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4908809661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6299610137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5836029052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9544773101807</t>
   </si>
   <si>
     <t xml:space="preserve">21.0471954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0008335113525</t>
+    <t xml:space="preserve">21.0008354187012</t>
   </si>
   <si>
     <t xml:space="preserve">20.7226810455322</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5372371673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5571517944336</t>
+    <t xml:space="preserve">20.5372409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.557149887085</t>
   </si>
   <si>
     <t xml:space="preserve">22.0671043395996</t>
@@ -1241,31 +1241,31 @@
     <t xml:space="preserve">21.7425918579102</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9280242919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8353061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6763172149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0935592651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1663665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0736446380615</t>
+    <t xml:space="preserve">21.9280261993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8353042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6763210296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0935554504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1663684844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0736484527588</t>
   </si>
   <si>
     <t xml:space="preserve">20.7690391540527</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4445247650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8153991699219</t>
+    <t xml:space="preserve">20.444522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8154010772705</t>
   </si>
   <si>
     <t xml:space="preserve">21.1862754821777</t>
@@ -1274,22 +1274,22 @@
     <t xml:space="preserve">20.2590847015381</t>
   </si>
   <si>
-    <t xml:space="preserve">20.351806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9809284210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8682994842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9146614074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0073795318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1928195953369</t>
+    <t xml:space="preserve">20.3518047332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9809246063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8683013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9146575927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.007381439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1928176879883</t>
   </si>
   <si>
     <t xml:space="preserve">19.6564140319824</t>
@@ -1307,28 +1307,28 @@
     <t xml:space="preserve">19.8418502807617</t>
   </si>
   <si>
-    <t xml:space="preserve">20.027286529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8882122039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7491283416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7954902648926</t>
+    <t xml:space="preserve">20.0272903442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8882141113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7491302490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7954921722412</t>
   </si>
   <si>
     <t xml:space="preserve">19.2855377197266</t>
   </si>
   <si>
-    <t xml:space="preserve">19.424617767334</t>
+    <t xml:space="preserve">19.4246158599854</t>
   </si>
   <si>
     <t xml:space="preserve">19.3782558441162</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5173320770264</t>
+    <t xml:space="preserve">19.517333984375</t>
   </si>
   <si>
     <t xml:space="preserve">19.5636940002441</t>
@@ -1337,85 +1337,85 @@
     <t xml:space="preserve">19.1464576721191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.10009765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2391757965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7027740478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2789936065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9345722198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5980529785156</t>
+    <t xml:space="preserve">19.1000995635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2391777038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7027721405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.278995513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9345684051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5980491638184</t>
   </si>
   <si>
     <t xml:space="preserve">15.2059049606323</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5953235626221</t>
+    <t xml:space="preserve">15.5953226089478</t>
   </si>
   <si>
     <t xml:space="preserve">14.6681346893311</t>
   </si>
   <si>
-    <t xml:space="preserve">14.371434211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7052202224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.298623085022</t>
+    <t xml:space="preserve">14.3714332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7052221298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2986221313477</t>
   </si>
   <si>
     <t xml:space="preserve">15.5211477279663</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8920211791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4284296035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2244462966919</t>
+    <t xml:space="preserve">15.8920230865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4284286499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2244472503662</t>
   </si>
   <si>
     <t xml:space="preserve">15.3542528152466</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7622156143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.688042640686</t>
+    <t xml:space="preserve">15.7622175216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6880445480347</t>
   </si>
   <si>
     <t xml:space="preserve">15.5582361221313</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4840593338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2800788879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9092044830322</t>
+    <t xml:space="preserve">15.4840612411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2800779342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9092035293579</t>
   </si>
   <si>
     <t xml:space="preserve">14.7599248886108</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4800271987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3120880126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3494081497192</t>
+    <t xml:space="preserve">14.4800281524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3120899200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3494091033936</t>
   </si>
   <si>
     <t xml:space="preserve">14.8159036636353</t>
@@ -1427,19 +1427,19 @@
     <t xml:space="preserve">14.5546674728394</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0398244857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3383798599243</t>
+    <t xml:space="preserve">15.0398225784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.33837890625</t>
   </si>
   <si>
     <t xml:space="preserve">15.1704406738281</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9762125015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8269329071045</t>
+    <t xml:space="preserve">13.9762115478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8269319534302</t>
   </si>
   <si>
     <t xml:space="preserve">13.5097160339355</t>
@@ -1448,22 +1448,22 @@
     <t xml:space="preserve">13.6403360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2374505996704</t>
+    <t xml:space="preserve">14.2374496459961</t>
   </si>
   <si>
     <t xml:space="preserve">14.0695114135742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0508518218994</t>
+    <t xml:space="preserve">14.0508527755737</t>
   </si>
   <si>
     <t xml:space="preserve">14.1254911422729</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8642520904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5470371246338</t>
+    <t xml:space="preserve">13.8642530441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5470361709595</t>
   </si>
   <si>
     <t xml:space="preserve">13.528374671936</t>
@@ -1472,145 +1472,145 @@
     <t xml:space="preserve">13.6963148117065</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9575519561768</t>
+    <t xml:space="preserve">13.9575510025024</t>
   </si>
   <si>
     <t xml:space="preserve">14.1068315505981</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4240484237671</t>
+    <t xml:space="preserve">14.4240474700928</t>
   </si>
   <si>
     <t xml:space="preserve">14.6479663848877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1144638061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0211629867554</t>
+    <t xml:space="preserve">15.1144609451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0211620330811</t>
   </si>
   <si>
     <t xml:space="preserve">14.9278631210327</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9651832580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7972431182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0025033950806</t>
+    <t xml:space="preserve">14.965184211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7972450256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0025024414062</t>
   </si>
   <si>
     <t xml:space="preserve">15.0584812164307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0958013534546</t>
+    <t xml:space="preserve">15.0958023071289</t>
   </si>
   <si>
     <t xml:space="preserve">15.4316816329956</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8608531951904</t>
+    <t xml:space="preserve">15.8608551025391</t>
   </si>
   <si>
     <t xml:space="preserve">16.7005462646484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7751884460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7938499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3833293914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3086910247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1594123840332</t>
+    <t xml:space="preserve">16.7751865386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7938461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3833312988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3086891174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1594104766846</t>
   </si>
   <si>
     <t xml:space="preserve">16.2527103424072</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8795156478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.767557144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.711576461792</t>
+    <t xml:space="preserve">15.8795146942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7675552368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7115755081177</t>
   </si>
   <si>
     <t xml:space="preserve">16.0287952423096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.047456741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1407527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.513952255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4019908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1780738830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3273506164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3460083007812</t>
+    <t xml:space="preserve">16.0474529266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1407508850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5139503479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4019889831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.178071975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3273525238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3460121154785</t>
   </si>
   <si>
     <t xml:space="preserve">16.1220932006836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.495288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6072444915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3646717071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2153873443604</t>
+    <t xml:space="preserve">16.4952907562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6072483062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.364673614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.215389251709</t>
   </si>
   <si>
     <t xml:space="preserve">15.7488946914673</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8421964645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8235368728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0101337432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8981761932373</t>
+    <t xml:space="preserve">15.8421955108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8235378265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0101318359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8981771469116</t>
   </si>
   <si>
     <t xml:space="preserve">16.2340488433838</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2900314331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4206485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6632289886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.831169128418</t>
+    <t xml:space="preserve">16.2900295257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4206504821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6632270812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8311653137207</t>
   </si>
   <si>
     <t xml:space="preserve">17.3536396026611</t>
@@ -1619,37 +1619,37 @@
     <t xml:space="preserve">18.1560134887695</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1373538970947</t>
+    <t xml:space="preserve">18.1373558044434</t>
   </si>
   <si>
     <t xml:space="preserve">18.1186943054199</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9880752563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4096202850342</t>
+    <t xml:space="preserve">17.9880771636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4096183776855</t>
   </si>
   <si>
     <t xml:space="preserve">17.0177631378174</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8871421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8684844970703</t>
+    <t xml:space="preserve">16.8871459960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8684864044189</t>
   </si>
   <si>
     <t xml:space="preserve">16.6259059906006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5326080322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8498249053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7192077636719</t>
+    <t xml:space="preserve">16.5326061248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8498268127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7192096710205</t>
   </si>
   <si>
     <t xml:space="preserve">16.9431228637695</t>
@@ -1661,28 +1661,28 @@
     <t xml:space="preserve">17.1110649108887</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6445693969727</t>
+    <t xml:space="preserve">16.644567489624</t>
   </si>
   <si>
     <t xml:space="preserve">16.1034336090088</t>
   </si>
   <si>
-    <t xml:space="preserve">15.394359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4130210876465</t>
+    <t xml:space="preserve">15.3943586349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4130182266235</t>
   </si>
   <si>
     <t xml:space="preserve">15.3570404052734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0771427154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5919876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7039451599121</t>
+    <t xml:space="preserve">15.0771417617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.591986656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7039461135864</t>
   </si>
   <si>
     <t xml:space="preserve">14.9838418960571</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">14.6666259765625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8718843460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7412643432617</t>
+    <t xml:space="preserve">14.8718824386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.741265296936</t>
   </si>
   <si>
     <t xml:space="preserve">14.405387878418</t>
@@ -1706,25 +1706,25 @@
     <t xml:space="preserve">14.27476978302</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7226047515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.461368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.368067741394</t>
+    <t xml:space="preserve">14.7226057052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4613676071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3680686950684</t>
   </si>
   <si>
     <t xml:space="preserve">14.5360069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4689970016479</t>
+    <t xml:space="preserve">15.4689979553223</t>
   </si>
   <si>
     <t xml:space="preserve">15.3010606765747</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2824010848999</t>
+    <t xml:space="preserve">15.2824001312256</t>
   </si>
   <si>
     <t xml:space="preserve">15.5622978210449</t>
@@ -1733,19 +1733,19 @@
     <t xml:space="preserve">15.1331195831299</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4876594543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3197183609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2264213562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9465236663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.77858543396</t>
+    <t xml:space="preserve">15.4876585006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3197193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2264223098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9465227127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7785844802856</t>
   </si>
   <si>
     <t xml:space="preserve">14.4427070617676</t>
@@ -1754,25 +1754,25 @@
     <t xml:space="preserve">14.685284614563</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5173473358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2001304626465</t>
+    <t xml:space="preserve">14.5173482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2001295089722</t>
   </si>
   <si>
     <t xml:space="preserve">14.1814699172974</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9948701858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8082752227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6776552200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3307485580444</t>
+    <t xml:space="preserve">13.9948720932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.808274269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6776542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3307476043701</t>
   </si>
   <si>
     <t xml:space="preserve">14.1628103256226</t>
@@ -1781,67 +1781,67 @@
     <t xml:space="preserve">13.7149753570557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7522926330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.938892364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8455944061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1441497802734</t>
+    <t xml:space="preserve">13.752293586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9388914108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8455934524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1441507339478</t>
   </si>
   <si>
     <t xml:space="preserve">13.9202327728271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4986867904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.901572227478</t>
+    <t xml:space="preserve">14.4986877441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9015731811523</t>
   </si>
   <si>
     <t xml:space="preserve">15.2637405395508</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0881719589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0135316848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3867273330688</t>
+    <t xml:space="preserve">14.088171005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0135335922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3867292404175</t>
   </si>
   <si>
     <t xml:space="preserve">14.8905439376831</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1891002655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9740724563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9552383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8045558929443</t>
+    <t xml:space="preserve">15.1891021728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9740753173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9552392959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8045568466187</t>
   </si>
   <si>
     <t xml:space="preserve">14.7103786468506</t>
   </si>
   <si>
-    <t xml:space="preserve">14.785719871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5768070220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3490524291992</t>
+    <t xml:space="preserve">14.7857208251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2754373550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5768060684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3490505218506</t>
   </si>
   <si>
     <t xml:space="preserve">16.2172031402588</t>
@@ -1850,46 +1850,46 @@
     <t xml:space="preserve">15.5956382751465</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5579690933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4261207580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4449577331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3507795333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6521463394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6898164749146</t>
+    <t xml:space="preserve">15.5579710006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4261226654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.44495677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3507804870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6521444320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6898155212402</t>
   </si>
   <si>
     <t xml:space="preserve">16.0665225982666</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6144742965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5014629364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5391330718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9346742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8781700134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3131084442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7274875640869</t>
+    <t xml:space="preserve">15.6144752502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5014619827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.539134979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9346761703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8781690597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3131093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7274885177612</t>
   </si>
   <si>
     <t xml:space="preserve">15.463791847229</t>
@@ -1904,34 +1904,34 @@
     <t xml:space="preserve">15.1435918807983</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0117444992065</t>
+    <t xml:space="preserve">15.0117435455322</t>
   </si>
   <si>
     <t xml:space="preserve">14.8798971176147</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1059217453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6538734436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8422260284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4090147018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9381322860718</t>
+    <t xml:space="preserve">15.1059226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6538753509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8422269821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4090156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9381313323975</t>
   </si>
   <si>
     <t xml:space="preserve">13.8439559936523</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1264848709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5031909942627</t>
+    <t xml:space="preserve">14.1264839172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5031900405884</t>
   </si>
   <si>
     <t xml:space="preserve">14.6915445327759</t>
@@ -1940,19 +1940,19 @@
     <t xml:space="preserve">14.4843559265137</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2960033416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3336725234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.522027015686</t>
+    <t xml:space="preserve">14.2960023880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3336734771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5220260620117</t>
   </si>
   <si>
     <t xml:space="preserve">14.2394971847534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1829919815063</t>
+    <t xml:space="preserve">14.182991027832</t>
   </si>
   <si>
     <t xml:space="preserve">13.9569664001465</t>
@@ -1961,25 +1961,25 @@
     <t xml:space="preserve">13.5990962982178</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0528726577759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9210252761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2788953781128</t>
+    <t xml:space="preserve">13.0528707504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9210243225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2788972854614</t>
   </si>
   <si>
     <t xml:space="preserve">12.9963665008545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7138357162476</t>
+    <t xml:space="preserve">12.7138366699219</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371295928955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0922718048096</t>
+    <t xml:space="preserve">12.0922698974609</t>
   </si>
   <si>
     <t xml:space="preserve">11.8662481307983</t>
@@ -1988,13 +1988,13 @@
     <t xml:space="preserve">11.3953657150269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9621524810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0580577850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88854026794434</t>
+    <t xml:space="preserve">10.9621515274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0580568313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88853931427002</t>
   </si>
   <si>
     <t xml:space="preserve">9.53066825866699</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">9.35173320770264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04267883300781</t>
+    <t xml:space="preserve">8.0426778793335</t>
   </si>
   <si>
     <t xml:space="preserve">8.49472618103027</t>
@@ -2021,28 +2021,28 @@
     <t xml:space="preserve">10.6796236038208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.847412109375</t>
+    <t xml:space="preserve">11.8474111557007</t>
   </si>
   <si>
     <t xml:space="preserve">12.8080129623413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5272121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8868112564087</t>
+    <t xml:space="preserve">11.5272102355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8868103027344</t>
   </si>
   <si>
     <t xml:space="preserve">10.8491411209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.566611289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0015516281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2652444839478</t>
+    <t xml:space="preserve">10.5666103363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0015506744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2652454376221</t>
   </si>
   <si>
     <t xml:space="preserve">10.5477752685547</t>
@@ -2051,10 +2051,10 @@
     <t xml:space="preserve">10.6607866287231</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0374927520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8303050994873</t>
+    <t xml:space="preserve">11.0374937057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8303060531616</t>
   </si>
   <si>
     <t xml:space="preserve">10.5101041793823</t>
@@ -2066,61 +2066,61 @@
     <t xml:space="preserve">9.81319808959961</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1522331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4347639083862</t>
+    <t xml:space="preserve">10.152232170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4347629547119</t>
   </si>
   <si>
     <t xml:space="preserve">10.3594226837158</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6984586715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6419534683228</t>
+    <t xml:space="preserve">10.6984577178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6419515609741</t>
   </si>
   <si>
     <t xml:space="preserve">10.6231155395508</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7361278533936</t>
+    <t xml:space="preserve">10.7361268997192</t>
   </si>
   <si>
     <t xml:space="preserve">10.7549638748169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4724349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9244804382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.867974281311</t>
+    <t xml:space="preserve">10.4724340438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9244823455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8679752349854</t>
   </si>
   <si>
     <t xml:space="preserve">11.4141988754272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4895401000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9809865951538</t>
+    <t xml:space="preserve">11.489541053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9809875488281</t>
   </si>
   <si>
     <t xml:space="preserve">11.3388586044312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4330358505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7155637741089</t>
+    <t xml:space="preserve">11.4330348968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7155647277832</t>
   </si>
   <si>
     <t xml:space="preserve">11.9227533340454</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2052822113037</t>
+    <t xml:space="preserve">12.205283164978</t>
   </si>
   <si>
     <t xml:space="preserve">12.1299409866333</t>
@@ -2129,10 +2129,10 @@
     <t xml:space="preserve">12.0169296264648</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7720718383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.150505065918</t>
+    <t xml:space="preserve">11.7720699310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1505060195923</t>
   </si>
   <si>
     <t xml:space="preserve">10.9433174133301</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">11.0186576843262</t>
   </si>
   <si>
-    <t xml:space="preserve">10.811469078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7172937393188</t>
+    <t xml:space="preserve">10.8114700317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7172918319702</t>
   </si>
   <si>
     <t xml:space="preserve">10.6042823791504</t>
@@ -2156,22 +2156,22 @@
     <t xml:space="preserve">10.3405857086182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3782577514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5854463577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1316690444946</t>
+    <t xml:space="preserve">10.3782587051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5854454040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1316699981689</t>
   </si>
   <si>
     <t xml:space="preserve">11.2635173797607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2070112228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9998226165771</t>
+    <t xml:space="preserve">11.207010269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9998235702515</t>
   </si>
   <si>
     <t xml:space="preserve">10.9056453704834</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">10.5289402008057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3029165267944</t>
+    <t xml:space="preserve">10.3029155731201</t>
   </si>
   <si>
     <t xml:space="preserve">10.3970918655396</t>
@@ -2195,28 +2195,28 @@
     <t xml:space="preserve">11.6025524139404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4518709182739</t>
+    <t xml:space="preserve">11.4518699645996</t>
   </si>
   <si>
     <t xml:space="preserve">11.546046257019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4707069396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5837173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6590595245361</t>
+    <t xml:space="preserve">11.4707059860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.58371925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6590585708618</t>
   </si>
   <si>
     <t xml:space="preserve">12.1487770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0545997619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0357656478882</t>
+    <t xml:space="preserve">12.0546007156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0357646942139</t>
   </si>
   <si>
     <t xml:space="preserve">11.8850831985474</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">11.9039192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7343997955322</t>
+    <t xml:space="preserve">11.7344007492065</t>
   </si>
   <si>
     <t xml:space="preserve">11.6778936386108</t>
@@ -2234,16 +2234,16 @@
     <t xml:space="preserve">11.169340133667</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5631542205811</t>
+    <t xml:space="preserve">12.5631532669067</t>
   </si>
   <si>
     <t xml:space="preserve">13.5614252090454</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2977294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7686128616333</t>
+    <t xml:space="preserve">13.2977313995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7686138153076</t>
   </si>
   <si>
     <t xml:space="preserve">13.504919052124</t>
@@ -2252,16 +2252,16 @@
     <t xml:space="preserve">13.1470489501953</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3354005813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3730726242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0152006149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2412261962891</t>
+    <t xml:space="preserve">13.3354015350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3730716705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0152015686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2412242889404</t>
   </si>
   <si>
     <t xml:space="preserve">14.0323076248169</t>
@@ -2276,103 +2276,103 @@
     <t xml:space="preserve">13.0340366363525</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3919067382812</t>
+    <t xml:space="preserve">13.3919076919556</t>
   </si>
   <si>
     <t xml:space="preserve">13.0905427932739</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9415884017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9792604446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2429523468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3559656143188</t>
+    <t xml:space="preserve">11.9415893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9792585372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2429533004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3559646606445</t>
   </si>
   <si>
     <t xml:space="preserve">12.7703428268433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7326726913452</t>
+    <t xml:space="preserve">12.7326717376709</t>
   </si>
   <si>
     <t xml:space="preserve">12.9586963653564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.22239112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3542366027832</t>
+    <t xml:space="preserve">13.2223882675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3542375564575</t>
   </si>
   <si>
     <t xml:space="preserve">13.467248916626</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5260171890259</t>
+    <t xml:space="preserve">13.5260190963745</t>
   </si>
   <si>
     <t xml:space="preserve">13.5450410842896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3167543411255</t>
+    <t xml:space="preserve">13.3167552947998</t>
   </si>
   <si>
     <t xml:space="preserve">13.3548030853271</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2216348648071</t>
+    <t xml:space="preserve">13.2216339111328</t>
   </si>
   <si>
     <t xml:space="preserve">13.4118747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7543048858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7923517227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6591854095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.077712059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0586862564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1157608032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.88747215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6021146774292</t>
+    <t xml:space="preserve">13.7543058395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7923536300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6591844558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0777130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.058687210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1157598495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8874740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6021127700806</t>
   </si>
   <si>
     <t xml:space="preserve">13.3738269805908</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6782093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5069942474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4499235153198</t>
+    <t xml:space="preserve">13.6782102584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5069932937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4499225616455</t>
   </si>
   <si>
     <t xml:space="preserve">13.6972332000732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6211366653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7733287811279</t>
+    <t xml:space="preserve">13.6211385726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7733278274536</t>
   </si>
   <si>
     <t xml:space="preserve">14.0396642684937</t>
@@ -2381,43 +2381,43 @@
     <t xml:space="preserve">14.2489280700684</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6103830337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5342855453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8957405090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9337892532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3796081542969</t>
+    <t xml:space="preserve">14.6103811264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5342864990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8957414627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9337902069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3796100616455</t>
   </si>
   <si>
     <t xml:space="preserve">16.2274150848389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0752258300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7137718200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8469390869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6947460174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5045070648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2191476821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6376752853394</t>
+    <t xml:space="preserve">16.0752239227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7137699127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8469381332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6947479248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5045080184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2191486358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.637674331665</t>
   </si>
   <si>
     <t xml:space="preserve">15.2381725311279</t>
@@ -2429,31 +2429,31 @@
     <t xml:space="preserve">15.6186504364014</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7518167495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1513195037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4937534332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.664966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5698471069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5317974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6078948974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5888710021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.045446395874</t>
+    <t xml:space="preserve">15.7518177032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1513214111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4937515258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6649684906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5698490142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5317993164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6078929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5888729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0454444885254</t>
   </si>
   <si>
     <t xml:space="preserve">17.0264225006104</t>
@@ -2471,19 +2471,19 @@
     <t xml:space="preserve">16.3225383758545</t>
   </si>
   <si>
-    <t xml:space="preserve">16.798131942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5508232116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8361854553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.81715965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7410621643066</t>
+    <t xml:space="preserve">16.7981338500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5508251190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8361835479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8171558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7410640716553</t>
   </si>
   <si>
     <t xml:space="preserve">17.8444519042969</t>
@@ -2495,31 +2495,31 @@
     <t xml:space="preserve">18.186882019043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.499532699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7848930358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1653728485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6422138214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5934085845947</t>
+    <t xml:space="preserve">19.4995346069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.78489112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1653709411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6422119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5934104919434</t>
   </si>
   <si>
     <t xml:space="preserve">20.3556098937988</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9751319885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8324527740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7373294830322</t>
+    <t xml:space="preserve">19.9751300811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8324508666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7373332977295</t>
   </si>
   <si>
     <t xml:space="preserve">19.8800106048584</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">20.2604885101318</t>
   </si>
   <si>
-    <t xml:space="preserve">20.403169631958</t>
+    <t xml:space="preserve">20.4031715393066</t>
   </si>
   <si>
     <t xml:space="preserve">20.498291015625</t>
@@ -2540,55 +2540,55 @@
     <t xml:space="preserve">20.7360897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2129325866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9275722503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7836494445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5946521759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3568553924561</t>
+    <t xml:space="preserve">20.2129306793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9275741577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7836513519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.594654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3568534851074</t>
   </si>
   <si>
     <t xml:space="preserve">19.2141761779785</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4044151306152</t>
+    <t xml:space="preserve">19.4044132232666</t>
   </si>
   <si>
     <t xml:space="preserve">19.6897754669189</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0239334106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1178131103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3080501556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0702495574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9738903045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.544605255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1641292572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6397266387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5921669006348</t>
+    <t xml:space="preserve">19.0239353179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1178112030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3080539703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0702514648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9738864898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5446071624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1641273498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6397285461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5921688079834</t>
   </si>
   <si>
     <t xml:space="preserve">21.6872863769531</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">21.0690078735352</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2116870880127</t>
+    <t xml:space="preserve">21.2116889953613</t>
   </si>
   <si>
     <t xml:space="preserve">21.3068065643311</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">22.6384811401367</t>
   </si>
   <si>
-    <t xml:space="preserve">23.161642074585</t>
+    <t xml:space="preserve">23.1616401672363</t>
   </si>
   <si>
     <t xml:space="preserve">22.4958038330078</t>
@@ -2627,25 +2627,25 @@
     <t xml:space="preserve">22.2580032348633</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8775253295898</t>
+    <t xml:space="preserve">21.8775234222412</t>
   </si>
   <si>
     <t xml:space="preserve">21.4970474243164</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2592468261719</t>
+    <t xml:space="preserve">21.2592487335205</t>
   </si>
   <si>
     <t xml:space="preserve">20.6885299682617</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6409721374512</t>
+    <t xml:space="preserve">20.6409702301025</t>
   </si>
   <si>
     <t xml:space="preserve">21.7824058532715</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3506393432617</t>
+    <t xml:space="preserve">24.3506355285645</t>
   </si>
   <si>
     <t xml:space="preserve">23.7799205780029</t>
@@ -2654,25 +2654,25 @@
     <t xml:space="preserve">23.3043231964111</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2567596435547</t>
+    <t xml:space="preserve">23.2567615509033</t>
   </si>
   <si>
     <t xml:space="preserve">23.0189609527588</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1140804290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3518772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0665225982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5896778106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.44700050354</t>
+    <t xml:space="preserve">23.1140785217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.351879119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.066520690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5896797180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4469985961914</t>
   </si>
   <si>
     <t xml:space="preserve">22.9238414764404</t>
@@ -2681,22 +2681,22 @@
     <t xml:space="preserve">23.6372413635254</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5421199798584</t>
+    <t xml:space="preserve">23.5421180725098</t>
   </si>
   <si>
     <t xml:space="preserve">23.4945621490479</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8762798309326</t>
+    <t xml:space="preserve">22.8762817382812</t>
   </si>
   <si>
     <t xml:space="preserve">23.3994407653809</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6860446929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4482460021973</t>
+    <t xml:space="preserve">22.6860427856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4482440948486</t>
   </si>
   <si>
     <t xml:space="preserve">22.1153259277344</t>
@@ -2708,13 +2708,13 @@
     <t xml:space="preserve">22.0677642822266</t>
   </si>
   <si>
-    <t xml:space="preserve">22.020206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0652770996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7323608398438</t>
+    <t xml:space="preserve">22.0202045440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.065279006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7323589324951</t>
   </si>
   <si>
     <t xml:space="preserve">24.3030757904053</t>
@@ -2723,22 +2723,22 @@
     <t xml:space="preserve">23.8750381469727</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6847972869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3018360137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5871906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9676723480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6823120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6347560882568</t>
+    <t xml:space="preserve">23.6848011016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3018341064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.587194442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9676685333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6823139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6347541809082</t>
   </si>
   <si>
     <t xml:space="preserve">25.7774333953857</t>
@@ -2747,37 +2747,37 @@
     <t xml:space="preserve">25.492073059082</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3005905151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3957099914551</t>
+    <t xml:space="preserve">26.3005886077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3957080841064</t>
   </si>
   <si>
     <t xml:space="preserve">27.2993469238281</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2042293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1566677093506</t>
+    <t xml:space="preserve">27.2042255401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.156665802002</t>
   </si>
   <si>
     <t xml:space="preserve">27.6798267364502</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2981052398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7749443054199</t>
+    <t xml:space="preserve">28.2981033325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7749481201172</t>
   </si>
   <si>
     <t xml:space="preserve">28.1078624725342</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5847034454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4420261383057</t>
+    <t xml:space="preserve">27.5847072601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4420280456543</t>
   </si>
   <si>
     <t xml:space="preserve">27.5371475219727</t>
@@ -2792,13 +2792,13 @@
     <t xml